--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3343" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCFF3531-008E-8B40-A470-576778B3560D}"/>
+  <xr:revisionPtr revIDLastSave="3352" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B4FEFF1-680E-49BA-B0DD-DB1965E21A14}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="510">
   <si>
     <t>Standard Card</t>
   </si>
@@ -655,9 +655,6 @@
     <t>Deploy Troops</t>
   </si>
   <si>
-    <t>Send Troops up to Leader's Level to War and gain 1 Coin per 2 Troops sent from the Royal Bank</t>
-  </si>
-  <si>
     <t>Provincial</t>
   </si>
   <si>
@@ -778,18 +775,12 @@
     <t>Gain 2 Commodities for each of your Leader's Level</t>
   </si>
   <si>
-    <t>Add 3 Coins to Royal Bank</t>
-  </si>
-  <si>
     <t>Give 1 Spy to each player</t>
   </si>
   <si>
     <t>Negotiate</t>
   </si>
   <si>
-    <t>Give 4 Troops to each player</t>
-  </si>
-  <si>
     <t>Recruit</t>
   </si>
   <si>
@@ -1411,9 +1402,6 @@
     <t>Players each roll $LLD6 and count all dice with a result higher than 3 as 1 point, adding any Investment bonuses to the total. The player with the highest total wins the round. On ties, both players reroll. Repeat this for best 2 out of 3 rounds.</t>
   </si>
   <si>
-    <t>If Greeks are victorious, give remaining attacking Greeks to the player who deployed the fewest Troops (break ties with Leader Level then with a Tie Trial or agreement). That player destroys 1 Troop per attacking Greek or 1 investment at level $D6 if they have no Troops.</t>
-  </si>
-  <si>
     <t>Trials</t>
   </si>
   <si>
@@ -1498,9 +1486,6 @@
     <t>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</t>
   </si>
   <si>
-    <t>Exchange up to LL Alliance tokens with a Player of your choice. The chosen Player must place a Leader of the same or higher level on this space.</t>
-  </si>
-  <si>
     <t>Prioritize</t>
   </si>
   <si>
@@ -1528,9 +1513,6 @@
     <t>Gain $L3 additional Coins from outside the Royal Bank when winning a Sue</t>
   </si>
   <si>
-    <t>Protector of the Poor</t>
-  </si>
-  <si>
     <t xml:space="preserve">   </t>
   </si>
   <si>
@@ -1571,6 +1553,27 @@
   </si>
   <si>
     <t>Exchange a random held Alliance Token, or one of your own if you hold none, with one of the choice of Player $R</t>
+  </si>
+  <si>
+    <t>Courtroom Gambling</t>
+  </si>
+  <si>
+    <t>Kingdom Advocates</t>
+  </si>
+  <si>
+    <t>Exchange Alliance tokens with a Player of your choice. The chosen Player must place a Leader on this space. Both players then exchange up to the lowest LL tokens.</t>
+  </si>
+  <si>
+    <t>If Greeks are victorious, give remaining attacking Greeks to the player who deployed the fewest Troops (break ties with deployment order then with a Tie Trial or agreement). That player destroys 1 Troop per attacking Greek or 1 investment at level $D6 if they have no Troops.</t>
+  </si>
+  <si>
+    <t>Add 1 Coin per Player to Royal Bank</t>
+  </si>
+  <si>
+    <t>Give 1 Troop per Player to each player</t>
+  </si>
+  <si>
+    <t>Send Troops up to Leader's Level to the Battlefield</t>
   </si>
 </sst>
 </file>
@@ -2495,7 +2498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2775,9 +2778,6 @@
       </extLst>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
@@ -4005,23 +4005,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5390625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5390625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.18359375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="39.01171875" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -4047,7 +4047,7 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>7</v>
       </c>
@@ -4073,15 +4073,15 @@
       <c r="I2" s="2"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>16</v>
@@ -4099,7 +4099,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>20</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>24</v>
@@ -4125,7 +4125,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>26</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>30</v>
@@ -4151,7 +4151,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>32</v>
       </c>
@@ -4177,7 +4177,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>39</v>
       </c>
@@ -4203,7 +4203,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>46</v>
       </c>
@@ -4214,10 +4214,10 @@
         <v>48</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>49</v>
@@ -4229,7 +4229,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>51</v>
       </c>
@@ -4243,19 +4243,19 @@
         <v>54</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>55</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>56</v>
       </c>
@@ -4266,10 +4266,10 @@
         <v>58</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>59</v>
@@ -4281,7 +4281,7 @@
       <c r="I10" s="2"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>61</v>
       </c>
@@ -4295,7 +4295,7 @@
         <v>64</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>65</v>
@@ -4307,7 +4307,7 @@
       <c r="I11" s="2"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>67</v>
       </c>
@@ -4333,15 +4333,15 @@
       <c r="I12" s="2"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>74</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>76</v>
@@ -4359,7 +4359,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>79</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>80</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>81</v>
@@ -4376,7 +4376,7 @@
         <v>82</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>83</v>
@@ -4385,7 +4385,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>84</v>
       </c>
@@ -4411,7 +4411,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>91</v>
       </c>
@@ -4437,7 +4437,7 @@
       <c r="I16" s="2"/>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>98</v>
       </c>
@@ -4463,12 +4463,12 @@
       <c r="I17" s="2"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>104</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>106</v>
@@ -4477,19 +4477,19 @@
         <v>107</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>108</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>109</v>
       </c>
@@ -4503,17 +4503,17 @@
         <v>112</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G19" s="25"/>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>113</v>
       </c>
@@ -4535,7 +4535,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>118</v>
       </c>
@@ -4557,7 +4557,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>123</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>126</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7"/>
@@ -4579,7 +4579,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>127</v>
       </c>
@@ -4601,7 +4601,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>132</v>
       </c>
@@ -4623,15 +4623,15 @@
       <c r="I24" s="3"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>137</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>139</v>
@@ -4645,21 +4645,21 @@
       <c r="I25" s="3"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>141</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>142</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4667,7 +4667,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>143</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>146</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4689,7 +4689,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>147</v>
       </c>
@@ -4703,7 +4703,7 @@
         <v>150</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4711,7 +4711,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>151</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>154</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4733,7 +4733,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>155</v>
       </c>
@@ -4755,7 +4755,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>160</v>
       </c>
@@ -4777,7 +4777,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>165</v>
       </c>
@@ -4795,7 +4795,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>168</v>
       </c>
@@ -4813,7 +4813,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>171</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>172</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="16"/>
@@ -4831,7 +4831,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>173</v>
       </c>
@@ -4849,15 +4849,15 @@
       <c r="I35" s="3"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>176</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4867,13 +4867,15 @@
       <c r="I36" s="3"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="B37" s="6"/>
+      <c r="B37" s="6" t="s">
+        <v>504</v>
+      </c>
       <c r="C37" s="15" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -4883,7 +4885,7 @@
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>178</v>
       </c>
@@ -4897,7 +4899,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>179</v>
       </c>
@@ -4911,7 +4913,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>180</v>
       </c>
@@ -4925,7 +4927,7 @@
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>181</v>
       </c>
@@ -4939,7 +4941,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>182</v>
       </c>
@@ -4953,7 +4955,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>183</v>
       </c>
@@ -4967,7 +4969,7 @@
       <c r="I43" s="3"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>184</v>
       </c>
@@ -4981,7 +4983,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>185</v>
       </c>
@@ -4995,7 +4997,7 @@
       <c r="I45" s="3"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>186</v>
       </c>
@@ -5009,7 +5011,7 @@
       <c r="I46" s="3"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>187</v>
       </c>
@@ -5023,7 +5025,7 @@
       <c r="I47" s="3"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>188</v>
       </c>
@@ -5037,7 +5039,7 @@
       <c r="I48" s="3"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>189</v>
       </c>
@@ -5051,7 +5053,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>190</v>
       </c>
@@ -5065,7 +5067,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="4"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>191</v>
       </c>
@@ -5079,7 +5081,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>192</v>
       </c>
@@ -5093,7 +5095,7 @@
       <c r="I52" s="3"/>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
         <v>193</v>
       </c>
@@ -5116,20 +5118,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D195C1D-DB02-1743-BBD2-99104C1FFD33}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.86328125" customWidth="1"/>
-    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.55859375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.26171875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.7890625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.16796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.0859375" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="51" t="s">
         <v>194</v>
       </c>
@@ -5149,7 +5151,7 @@
         <v>199</v>
       </c>
       <c r="G1" s="54" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="H1" s="54" t="s">
         <v>200</v>
@@ -5158,322 +5160,322 @@
         <v>201</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="47" t="s">
         <v>202</v>
       </c>
       <c r="B2" s="48" t="s">
+        <v>509</v>
+      </c>
+      <c r="C2" s="49" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="D2" s="50" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="E2" s="50" t="s">
         <v>205</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>207</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="H2" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="H2" s="50" t="s">
+      <c r="I2" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="I2" s="50" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="37" t="s">
+        <v>454</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>453</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>364</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="37" t="s">
-        <v>458</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>457</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>367</v>
-      </c>
-      <c r="E3" s="42" t="s">
+      <c r="F3" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="G3" s="42" t="s">
         <v>212</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="H3" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="I3" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="H3" s="42" t="s">
-        <v>330</v>
-      </c>
-      <c r="I3" s="42" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="37" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="81" x14ac:dyDescent="0.2">
-      <c r="A4" s="37" t="s">
+      <c r="B4" s="36" t="s">
         <v>215</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="C4" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="42" t="s">
         <v>216</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="D4" s="42" t="s">
+      <c r="E4" s="42" t="s">
         <v>217</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="F4" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="G4" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="H4" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="45"/>
+    </row>
+    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>333</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>221</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>450</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="I5" s="45"/>
+    </row>
+    <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A6" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>228</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="H6" s="42" t="s">
+        <v>506</v>
+      </c>
+      <c r="I6" s="45"/>
+    </row>
+    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" s="42" t="s">
         <v>497</v>
       </c>
-      <c r="G4" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="H4" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="I4" s="45"/>
-    </row>
-    <row r="5" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>336</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>223</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>453</v>
-      </c>
-      <c r="H5" s="42" t="s">
-        <v>329</v>
-      </c>
-      <c r="I5" s="45"/>
-    </row>
-    <row r="6" spans="1:9" ht="94.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>228</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>229</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>454</v>
-      </c>
-      <c r="H6" s="42" t="s">
-        <v>455</v>
-      </c>
-      <c r="I6" s="45"/>
-    </row>
-    <row r="7" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="37" t="s">
-        <v>230</v>
-      </c>
-      <c r="B7" s="36" t="s">
+      <c r="E7" s="42" t="s">
+        <v>331</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>366</v>
+      </c>
+      <c r="G7" s="42" t="s">
         <v>231</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>503</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>334</v>
-      </c>
-      <c r="F7" s="44" t="s">
-        <v>369</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>232</v>
       </c>
       <c r="H7" s="42"/>
       <c r="I7" s="45"/>
     </row>
-    <row r="8" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="C8" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D8" s="42" t="s">
         <v>234</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="D8" s="42" t="s">
+      <c r="E8" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="F8" s="42" t="s">
         <v>235</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>335</v>
-      </c>
-      <c r="F8" s="42" t="s">
-        <v>236</v>
       </c>
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
       <c r="I8" s="45"/>
     </row>
-    <row r="9" spans="1:9" ht="108" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="B9" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="C9" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="C9" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="D9" s="42" t="s">
+      <c r="E9" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="F9" s="42" t="s">
         <v>240</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>241</v>
       </c>
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
       <c r="I9" s="45"/>
     </row>
-    <row r="10" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>242</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="C10" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>507</v>
+      </c>
+      <c r="E10" s="42" t="s">
         <v>243</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>204</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>244</v>
-      </c>
-      <c r="E10" s="42" t="s">
-        <v>245</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
       <c r="I10" s="45"/>
     </row>
-    <row r="11" spans="1:9" ht="68.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>484</v>
+        <v>505</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="42" t="s">
-        <v>247</v>
+        <v>508</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
       <c r="I11" s="45"/>
     </row>
-    <row r="12" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D12" s="42"/>
       <c r="E12" s="42" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F12" s="44"/>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
       <c r="I12" s="45"/>
     </row>
-    <row r="13" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D13" s="42"/>
       <c r="E13" s="42" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F13" s="44"/>
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
       <c r="I13" s="45"/>
     </row>
-    <row r="14" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D14" s="42"/>
       <c r="E14" s="42" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
       <c r="I14" s="45"/>
     </row>
-    <row r="15" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="42"/>
@@ -5482,15 +5484,15 @@
       <c r="H15" s="42"/>
       <c r="I15" s="45"/>
     </row>
-    <row r="16" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D16" s="42"/>
       <c r="E16" s="42"/>
@@ -5499,15 +5501,15 @@
       <c r="H16" s="42"/>
       <c r="I16" s="45"/>
     </row>
-    <row r="17" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D17" s="42"/>
       <c r="E17" s="42"/>
@@ -5516,15 +5518,15 @@
       <c r="H17" s="42"/>
       <c r="I17" s="45"/>
     </row>
-    <row r="18" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="42"/>
@@ -5533,15 +5535,15 @@
       <c r="H18" s="42"/>
       <c r="I18" s="45"/>
     </row>
-    <row r="19" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="42"/>
@@ -5550,15 +5552,15 @@
       <c r="H19" s="42"/>
       <c r="I19" s="45"/>
     </row>
-    <row r="20" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
@@ -5567,15 +5569,15 @@
       <c r="H20" s="42"/>
       <c r="I20" s="45"/>
     </row>
-    <row r="21" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
@@ -5584,15 +5586,15 @@
       <c r="H21" s="42"/>
       <c r="I21" s="45"/>
     </row>
-    <row r="22" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -5601,15 +5603,15 @@
       <c r="H22" s="42"/>
       <c r="I22" s="45"/>
     </row>
-    <row r="23" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="39" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D23" s="43"/>
       <c r="E23" s="43"/>
@@ -5626,39 +5628,39 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920DF489-FE6D-4819-BD1A-323DFAE597A3}">
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="30.66796875" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="72"/>
       <c r="B1" s="65" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="65" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1" s="64" t="s">
+        <v>272</v>
+      </c>
+      <c r="E1" s="64" t="s">
         <v>273</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="F1" s="64" t="s">
         <v>274</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="G1" s="64" t="s">
         <v>275</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="I1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="74" t="s">
         <v>276</v>
-      </c>
-      <c r="F1" s="64" t="s">
-        <v>277</v>
-      </c>
-      <c r="G1" s="64" t="s">
-        <v>278</v>
-      </c>
-      <c r="I1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="74" t="s">
-        <v>279</v>
       </c>
       <c r="B2" s="75" t="s">
         <v>119</v>
@@ -5679,12 +5681,12 @@
         <v>156</v>
       </c>
       <c r="I2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="74" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B3" s="76" t="s">
         <v>47</v>
@@ -5705,12 +5707,12 @@
         <v>169</v>
       </c>
       <c r="I3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B4" s="67" t="s">
         <v>85</v>
@@ -5731,12 +5733,12 @@
         <v>148</v>
       </c>
       <c r="I4" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="74" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B5" s="73" t="s">
         <v>174</v>
@@ -5757,12 +5759,12 @@
         <v>27</v>
       </c>
       <c r="I5" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="97" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B6" s="98" t="s">
         <v>135</v>
@@ -5783,560 +5785,560 @@
         <v>154</v>
       </c>
       <c r="I6" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="77" t="s">
+        <v>281</v>
+      </c>
+      <c r="B7" s="77" t="s">
+        <v>282</v>
+      </c>
+      <c r="C7" s="74" t="s">
+        <v>385</v>
+      </c>
+      <c r="D7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E7" s="74" t="s">
         <v>284</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="F7" t="s">
         <v>285</v>
-      </c>
-      <c r="C7" s="74" t="s">
-        <v>388</v>
-      </c>
-      <c r="D7" t="s">
-        <v>286</v>
-      </c>
-      <c r="E7" s="74" t="s">
-        <v>287</v>
-      </c>
-      <c r="F7" t="s">
-        <v>288</v>
       </c>
       <c r="G7" s="74" t="s">
         <v>201</v>
       </c>
       <c r="I7" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="95" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B8" s="95" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C8" s="91" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D8" s="95" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E8" s="91" t="s">
+        <v>270</v>
+      </c>
+      <c r="F8" s="95" t="s">
+        <v>271</v>
+      </c>
+      <c r="G8" s="92" t="s">
+        <v>272</v>
+      </c>
+      <c r="I8" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="63" t="s">
+        <v>337</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>274</v>
+      </c>
+      <c r="C9" t="s">
+        <v>272</v>
+      </c>
+      <c r="D9" s="63" t="s">
+        <v>271</v>
+      </c>
+      <c r="E9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="G9" s="76" t="s">
         <v>273</v>
       </c>
-      <c r="F8" s="95" t="s">
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="96" t="s">
+        <v>338</v>
+      </c>
+      <c r="B10" s="96" t="s">
+        <v>272</v>
+      </c>
+      <c r="C10" s="93" t="s">
+        <v>275</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>270</v>
+      </c>
+      <c r="E10" s="93" t="s">
         <v>274</v>
       </c>
-      <c r="G8" s="92" t="s">
-        <v>275</v>
-      </c>
-      <c r="I8" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="63" t="s">
-        <v>340</v>
-      </c>
-      <c r="B9" s="63" t="s">
-        <v>277</v>
-      </c>
-      <c r="C9" t="s">
-        <v>275</v>
-      </c>
-      <c r="D9" s="63" t="s">
-        <v>274</v>
-      </c>
-      <c r="E9" t="s">
-        <v>278</v>
-      </c>
-      <c r="F9" s="63" t="s">
+      <c r="F10" s="96" t="s">
         <v>273</v>
       </c>
-      <c r="G9" s="76" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="96" t="s">
-        <v>341</v>
-      </c>
-      <c r="B10" s="96" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10" s="93" t="s">
-        <v>278</v>
-      </c>
-      <c r="D10" s="96" t="s">
-        <v>273</v>
-      </c>
-      <c r="E10" s="93" t="s">
-        <v>277</v>
-      </c>
-      <c r="F10" s="96" t="s">
-        <v>276</v>
-      </c>
       <c r="G10" s="94" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="94.5" x14ac:dyDescent="0.2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="68.25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>387</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="68.25" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:9" ht="175.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="189" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>412</v>
-      </c>
       <c r="G24" s="2" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="255.75" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="345" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>417</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="81" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D26" s="2" t="s">
+    </row>
+    <row r="27" spans="1:9" ht="255" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E27" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="202.5" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="148.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:9" ht="195" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" ht="94.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I30" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>202</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="2"/>
       <c r="D35" s="2"/>
@@ -6344,111 +6346,111 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="I37" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="I38" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="I39" t="s">
         <v>362</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="I39" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G40" s="2"/>
       <c r="I40" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -6457,7 +6459,7 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -6466,7 +6468,7 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -6475,7 +6477,7 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -6483,173 +6485,173 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F47" s="2" t="s">
+    </row>
+    <row r="49" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
-      <c r="B48" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="C48" s="2" t="s">
+      <c r="C49" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="G48" s="2" t="s">
+      <c r="F49" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
         <v>440</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B49" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B50" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G50" s="2"/>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B53" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B54" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="F54" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>202</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -6657,85 +6659,85 @@
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="2:7" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B59" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B60" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -6751,73 +6753,73 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="37.5" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="36" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="4" width="30.66796875" style="26" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.14453125" style="26"/>
+    <col min="1" max="4" width="30.7109375" style="26" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D1" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="E1" s="110" t="s">
-        <v>204</v>
+      <c r="E1" s="109" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="31" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="E2" s="111"/>
+        <v>229</v>
+      </c>
+      <c r="E2" s="110"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="30" t="s">
-        <v>251</v>
-      </c>
       <c r="C3" s="29" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="E3" s="111"/>
+        <v>244</v>
+      </c>
+      <c r="E3" s="110"/>
     </row>
     <row r="4" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A4" s="34" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D4" s="34"/>
       <c r="E4" s="62" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -6836,52 +6838,52 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="30.66796875" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="B1" s="30" t="s">
-        <v>265</v>
-      </c>
       <c r="C1" s="29" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>267</v>
-      </c>
-      <c r="E1" s="112" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E1" s="111" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D2" s="55"/>
-      <c r="E2" s="113"/>
-    </row>
-    <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="112"/>
+    </row>
+    <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="57" t="s">
-        <v>289</v>
-      </c>
-      <c r="B3" s="114" t="s">
-        <v>290</v>
-      </c>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="116"/>
+        <v>286</v>
+      </c>
+      <c r="B3" s="113" t="s">
+        <v>287</v>
+      </c>
+      <c r="C3" s="114"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6897,13 +6899,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{435A2588-0653-4FD0-85C3-EF9530FC726F}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="15" width="17.890625" customWidth="1"/>
+    <col min="1" max="14" width="7.7109375" customWidth="1"/>
+    <col min="15" max="15" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60">
         <v>0</v>
       </c>
@@ -6947,143 +6949,143 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="60">
         <v>39</v>
       </c>
-      <c r="B2" s="119" t="s">
-        <v>291</v>
-      </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
+      <c r="B2" s="118" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
       <c r="N2" s="60">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="60">
         <v>38</v>
       </c>
-      <c r="B3" s="121"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122"/>
+      <c r="B3" s="120"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
       <c r="N3" s="60">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="60">
         <v>37</v>
       </c>
-      <c r="B4" s="117" t="s">
-        <v>292</v>
-      </c>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
+      <c r="B4" s="116" t="s">
+        <v>289</v>
+      </c>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
+      <c r="K4" s="117"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
       <c r="N4" s="60">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="60">
         <v>36</v>
       </c>
-      <c r="B5" s="123" t="s">
-        <v>293</v>
-      </c>
-      <c r="C5" s="124"/>
-      <c r="D5" s="127" t="s">
-        <v>293</v>
-      </c>
-      <c r="E5" s="128"/>
-      <c r="F5" s="127" t="s">
-        <v>293</v>
-      </c>
-      <c r="G5" s="128"/>
-      <c r="H5" s="127" t="s">
-        <v>293</v>
-      </c>
-      <c r="I5" s="128"/>
-      <c r="J5" s="127" t="s">
-        <v>293</v>
-      </c>
-      <c r="K5" s="128"/>
-      <c r="L5" s="127" t="s">
-        <v>293</v>
-      </c>
-      <c r="M5" s="131"/>
+      <c r="B5" s="122" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="123"/>
+      <c r="D5" s="126" t="s">
+        <v>290</v>
+      </c>
+      <c r="E5" s="127"/>
+      <c r="F5" s="126" t="s">
+        <v>290</v>
+      </c>
+      <c r="G5" s="127"/>
+      <c r="H5" s="126" t="s">
+        <v>290</v>
+      </c>
+      <c r="I5" s="127"/>
+      <c r="J5" s="126" t="s">
+        <v>290</v>
+      </c>
+      <c r="K5" s="127"/>
+      <c r="L5" s="126" t="s">
+        <v>290</v>
+      </c>
+      <c r="M5" s="130"/>
       <c r="N5" s="60">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="60">
         <v>35</v>
       </c>
-      <c r="B6" s="123"/>
-      <c r="C6" s="124"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="129"/>
-      <c r="F6" s="123"/>
-      <c r="G6" s="129"/>
-      <c r="H6" s="123"/>
-      <c r="I6" s="129"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="129"/>
-      <c r="L6" s="123"/>
-      <c r="M6" s="124"/>
+      <c r="B6" s="122"/>
+      <c r="C6" s="123"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="128"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="128"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="128"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="128"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="123"/>
       <c r="N6" s="60">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="60">
         <v>34</v>
       </c>
-      <c r="B7" s="125"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="125"/>
-      <c r="M7" s="126"/>
+      <c r="B7" s="124"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="124"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="124"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="124"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="124"/>
+      <c r="M7" s="125"/>
       <c r="N7" s="60">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="60">
         <v>33</v>
       </c>
@@ -7145,57 +7147,57 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CEB427C-0CB4-4E8D-8367-36F6DD891282}">
   <dimension ref="A1:BI6"/>
-  <sheetFormatPr defaultColWidth="19.7734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7734375" style="63"/>
-    <col min="2" max="2" width="19.7734375" style="76"/>
-    <col min="4" max="4" width="19.7734375" style="63"/>
-    <col min="6" max="6" width="19.7734375" style="63"/>
-    <col min="8" max="8" width="19.7734375" style="63"/>
-    <col min="10" max="10" width="19.7734375" style="63"/>
-    <col min="12" max="12" width="19.7734375" style="63"/>
-    <col min="14" max="14" width="19.7734375" style="63"/>
-    <col min="16" max="16" width="19.7734375" style="63"/>
-    <col min="18" max="18" width="19.7734375" style="63"/>
-    <col min="20" max="20" width="19.7734375" style="63"/>
-    <col min="22" max="22" width="19.7734375" style="63"/>
-    <col min="24" max="24" width="19.7734375" style="63"/>
-    <col min="26" max="26" width="19.7734375" style="63"/>
-    <col min="28" max="28" width="19.7734375" style="63"/>
-    <col min="30" max="30" width="19.7734375" style="82"/>
-    <col min="31" max="32" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.7734375" customWidth="1"/>
-    <col min="42" max="42" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.7734375" style="82" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="19.7734375" style="63" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="19.7734375" style="82" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="19.7734375" style="63"/>
+    <col min="1" max="1" width="19.7109375" style="63"/>
+    <col min="2" max="2" width="19.7109375" style="76"/>
+    <col min="4" max="4" width="19.7109375" style="63"/>
+    <col min="6" max="6" width="19.7109375" style="63"/>
+    <col min="8" max="8" width="19.7109375" style="63"/>
+    <col min="10" max="10" width="19.7109375" style="63"/>
+    <col min="12" max="12" width="19.7109375" style="63"/>
+    <col min="14" max="14" width="19.7109375" style="63"/>
+    <col min="16" max="16" width="19.7109375" style="63"/>
+    <col min="18" max="18" width="19.7109375" style="63"/>
+    <col min="20" max="20" width="19.7109375" style="63"/>
+    <col min="22" max="22" width="19.7109375" style="63"/>
+    <col min="24" max="24" width="19.7109375" style="63"/>
+    <col min="26" max="26" width="19.7109375" style="63"/>
+    <col min="28" max="28" width="19.7109375" style="63"/>
+    <col min="30" max="30" width="19.7109375" style="82"/>
+    <col min="31" max="32" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.7109375" customWidth="1"/>
+    <col min="42" max="42" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.7109375" style="82" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19.7109375" style="82" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="19.7109375" style="63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" s="80" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:61" s="80" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="str">
         <f>Cards!B2</f>
         <v>Fillibuster</v>
@@ -7242,7 +7244,7 @@
       </c>
       <c r="L1" s="78" t="str">
         <f>Cards!B13</f>
-        <v>Protector of the Poor</v>
+        <v>Courtroom Gambling</v>
       </c>
       <c r="M1" s="80" t="str">
         <f>Cards!B14</f>
@@ -7337,111 +7339,111 @@
         <v>Fire Temple</v>
       </c>
       <c r="AJ1" s="78" t="str">
-        <f>A1</f>
+        <f t="shared" ref="AJ1:AS2" si="0">A1</f>
         <v>Fillibuster</v>
       </c>
       <c r="AK1" s="80" t="str">
-        <f>B1</f>
+        <f t="shared" si="0"/>
         <v>Skillful Orators</v>
       </c>
       <c r="AL1" s="78" t="str">
-        <f>C1</f>
+        <f t="shared" si="0"/>
         <v>Collection Stations</v>
       </c>
       <c r="AM1" s="80" t="str">
-        <f>D1</f>
+        <f t="shared" si="0"/>
         <v>Brown Nose</v>
       </c>
       <c r="AN1" s="78" t="str">
-        <f>E1</f>
+        <f t="shared" si="0"/>
         <v>Mysterious Windfalls</v>
       </c>
       <c r="AO1" s="80" t="str">
-        <f>F1</f>
+        <f t="shared" si="0"/>
         <v>Lobbyists</v>
       </c>
       <c r="AP1" s="78" t="str">
-        <f>G1</f>
+        <f t="shared" si="0"/>
         <v>Eager Youth</v>
       </c>
       <c r="AQ1" s="80" t="str">
-        <f>H1</f>
+        <f t="shared" si="0"/>
         <v>Honorable Cause</v>
       </c>
       <c r="AR1" s="78" t="str">
-        <f>I1</f>
+        <f t="shared" si="0"/>
         <v>Loyal Citizenry</v>
       </c>
       <c r="AS1" s="80" t="str">
-        <f>J1</f>
+        <f t="shared" si="0"/>
         <v>Silvertounge</v>
       </c>
       <c r="AT1" s="78" t="str">
-        <f>K1</f>
+        <f t="shared" ref="AT1:BC2" si="1">K1</f>
         <v>Royal Bribes</v>
       </c>
       <c r="AU1" s="80" t="str">
-        <f>L1</f>
-        <v>Protector of the Poor</v>
+        <f t="shared" si="1"/>
+        <v>Courtroom Gambling</v>
       </c>
       <c r="AV1" s="78" t="str">
-        <f>M1</f>
+        <f t="shared" si="1"/>
         <v>Market Niche</v>
       </c>
       <c r="AW1" s="80" t="str">
-        <f>N1</f>
+        <f t="shared" si="1"/>
         <v>Genius Commanders</v>
       </c>
       <c r="AX1" s="81" t="str">
-        <f>O1</f>
+        <f t="shared" si="1"/>
         <v>Damage Redemption</v>
       </c>
       <c r="AY1" s="78" t="str">
-        <f>P1</f>
+        <f t="shared" si="1"/>
         <v>Undeniable Advisors</v>
       </c>
       <c r="AZ1" s="80" t="str">
-        <f>Q1</f>
+        <f t="shared" si="1"/>
         <v>Heavy Overtime</v>
       </c>
       <c r="BA1" s="78" t="str">
-        <f>R1</f>
+        <f t="shared" si="1"/>
         <v>Bulk Purchaser</v>
       </c>
       <c r="BB1" s="80" t="str">
-        <f>S1</f>
+        <f t="shared" si="1"/>
         <v>Valuable Cargo</v>
       </c>
       <c r="BC1" s="78" t="str">
-        <f>T1</f>
+        <f t="shared" si="1"/>
         <v>Elite Troops</v>
       </c>
       <c r="BD1" s="80" t="str">
-        <f>U1</f>
+        <f t="shared" ref="BD1:BM2" si="2">U1</f>
         <v>Bazaar</v>
       </c>
       <c r="BE1" s="78" t="str">
-        <f>V1</f>
+        <f t="shared" si="2"/>
         <v>Caravansaray</v>
       </c>
       <c r="BF1" s="80" t="str">
-        <f>W1</f>
+        <f t="shared" si="2"/>
         <v>War Machines</v>
       </c>
       <c r="BG1" s="78" t="str">
-        <f>X1</f>
+        <f t="shared" si="2"/>
         <v>Mock Trials</v>
       </c>
       <c r="BH1" s="81" t="str">
-        <f>Y1</f>
+        <f t="shared" si="2"/>
         <v>Desperate Attorneys</v>
       </c>
       <c r="BI1" s="78" t="str">
-        <f>Z1</f>
+        <f t="shared" si="2"/>
         <v>Eager Laborers</v>
       </c>
     </row>
-    <row r="2" spans="1:61" s="103" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:61" s="103" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="104" t="str">
         <f>Cards!C2</f>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
@@ -7583,111 +7585,111 @@
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
       </c>
       <c r="AJ2" s="104" t="str">
-        <f>A2</f>
+        <f t="shared" si="0"/>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
       </c>
       <c r="AK2" s="103" t="str">
-        <f>B2</f>
+        <f t="shared" si="0"/>
         <v>Move the Law $L6 additional places forward in the queue during Prioritize</v>
       </c>
       <c r="AL2" s="104" t="str">
-        <f>C2</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve">You may gain up to $L6 additional Coins when Taxing other Players </v>
       </c>
       <c r="AM2" s="103" t="str">
-        <f>D2</f>
+        <f t="shared" si="0"/>
         <v>Gain $L3 additional Coins during Flatter</v>
       </c>
       <c r="AN2" s="104" t="str">
-        <f>E2</f>
+        <f t="shared" si="0"/>
         <v>Gain $L3 more Commodities per Coin when Buying from the Undermarket</v>
       </c>
       <c r="AO2" s="103" t="str">
-        <f>F2</f>
+        <f t="shared" si="0"/>
         <v>Add $L3 additional Law cards to the bottom of the queue during Petition</v>
       </c>
       <c r="AP2" s="104" t="str">
-        <f>G2</f>
+        <f t="shared" si="0"/>
         <v>Gain 1 additional Troop for free after Recruiting every 4 - $L3 Troops</v>
       </c>
       <c r="AQ2" s="103" t="str">
-        <f>H2</f>
+        <f t="shared" si="0"/>
         <v>Gain 1 additional Spy for free after Infiltrating every 4 - $L3 Spies</v>
       </c>
       <c r="AR2" s="104" t="str">
-        <f>I2</f>
+        <f t="shared" si="0"/>
         <v>Purchase up to $L6 additional Troops during Recruit</v>
       </c>
       <c r="AS2" s="103" t="str">
-        <f>J2</f>
+        <f t="shared" si="0"/>
         <v>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</v>
       </c>
       <c r="AT2" s="104" t="str">
-        <f>K2</f>
+        <f t="shared" si="1"/>
         <v>Gain $L3 more Commodities per Coin when Buying from the Court</v>
       </c>
       <c r="AU2" s="103" t="str">
-        <f>L2</f>
+        <f t="shared" si="1"/>
         <v>Gain $L3 additional Coins from outside the Royal Bank when winning a Sue</v>
       </c>
       <c r="AV2" s="104" t="str">
-        <f>M2</f>
+        <f t="shared" si="1"/>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Undermarket</v>
       </c>
       <c r="AW2" s="103" t="str">
-        <f>N2</f>
+        <f t="shared" si="1"/>
         <v>Draw $L6 additional cards from any decks during Brainstorm</v>
       </c>
       <c r="AX2" s="105" t="str">
-        <f>O2</f>
+        <f t="shared" si="1"/>
         <v>Purchase $L3 Spies (at normal cost) when targeted by a Scheme</v>
       </c>
       <c r="AY2" s="104" t="str">
-        <f>P2</f>
+        <f t="shared" si="1"/>
         <v>You may repeat Court Actions with level 7 - $L6 Leaders</v>
       </c>
       <c r="AZ2" s="103" t="str">
-        <f>Q2</f>
+        <f t="shared" si="1"/>
         <v>You may repeat $L3 Provincial Actions per round</v>
       </c>
       <c r="BA2" s="104" t="str">
-        <f>R2</f>
+        <f t="shared" si="1"/>
         <v>Trade up to $L3 additional Coins when Buying from the Court</v>
       </c>
       <c r="BB2" s="103" t="str">
-        <f>S2</f>
+        <f t="shared" si="1"/>
         <v>Trade for up to $L3 additional Coins when Selling to the Court</v>
       </c>
       <c r="BC2" s="104" t="str">
-        <f>T2</f>
+        <f t="shared" si="1"/>
         <v>Gain $L3 additional Coins from the Royal Bank when Deploying Troops</v>
       </c>
       <c r="BD2" s="103" t="str">
-        <f>U2</f>
+        <f t="shared" si="2"/>
         <v>Provides private Buy Action at Market Rate + $L3</v>
       </c>
       <c r="BE2" s="104" t="str">
-        <f>V2</f>
+        <f t="shared" si="2"/>
         <v>Provides private Sell Action at Market Rate - $L3</v>
       </c>
       <c r="BF2" s="103" t="str">
-        <f>W2</f>
+        <f t="shared" si="2"/>
         <v>Purchase and immediately add up to $L3 Troops to your force when deploying them</v>
       </c>
       <c r="BG2" s="104" t="str">
-        <f>X2</f>
+        <f t="shared" si="2"/>
         <v>Add $L3 Hits to each Roll during a Sue</v>
       </c>
       <c r="BH2" s="105" t="str">
-        <f>Y2</f>
+        <f t="shared" si="2"/>
         <v>Add $L6 additional dice to each Roll during a Sue</v>
       </c>
       <c r="BI2" s="104" t="str">
-        <f>Z2</f>
+        <f t="shared" si="2"/>
         <v>Collect $L6 additional Commodities during Harvests</v>
       </c>
     </row>
-    <row r="3" spans="1:61" s="80" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:61" s="80" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="78" t="str">
         <f>Cards!D2</f>
         <v>Full Coffers</v>
@@ -7809,128 +7811,128 @@
         <v>Worthless Procrastinators</v>
       </c>
       <c r="AE3" s="78" t="str">
-        <f t="shared" ref="AE3:BH3" si="0">A3</f>
+        <f t="shared" ref="AE3:BH3" si="3">A3</f>
         <v>Full Coffers</v>
       </c>
       <c r="AF3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve">Decentralized Wealth </v>
       </c>
       <c r="AG3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Second Thoughts</v>
       </c>
       <c r="AH3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Changing Times</v>
       </c>
       <c r="AI3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Stable Economies</v>
       </c>
       <c r="AJ3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Unreasonable Distractions</v>
       </c>
       <c r="AK3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Irregular Partiality</v>
       </c>
       <c r="AL3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Royal Amendment</v>
       </c>
       <c r="AM3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Honorable Accontability</v>
       </c>
       <c r="AN3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Frivolous Pursuits</v>
       </c>
       <c r="AO3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Economic Backbone</v>
       </c>
       <c r="AP3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Collective Ownership</v>
       </c>
       <c r="AQ3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Aggressive Tactics</v>
       </c>
       <c r="AR3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Home Defense</v>
       </c>
       <c r="AS3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Valuable Advisors</v>
       </c>
       <c r="AT3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Chattering Windbags</v>
       </c>
       <c r="AU3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Realistic Priorities</v>
       </c>
       <c r="AV3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Threat to the Throne</v>
       </c>
       <c r="AW3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Stone Foundations</v>
       </c>
       <c r="AX3" s="81" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Environmental Guardians</v>
       </c>
       <c r="AY3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Resilient Officer Corps</v>
       </c>
       <c r="AZ3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Bloated Bureaucracy</v>
       </c>
       <c r="BA3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Police Force</v>
       </c>
       <c r="BB3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Equal Partners</v>
       </c>
       <c r="BC3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Criminal Identification</v>
       </c>
       <c r="BD3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Honorable Marketplace</v>
       </c>
       <c r="BE3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Engaged Empire</v>
       </c>
       <c r="BF3" s="80" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Suspicious Advisors</v>
       </c>
       <c r="BG3" s="78" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Contingency Plans</v>
       </c>
       <c r="BH3" s="81" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>Worthless Procrastinators</v>
       </c>
       <c r="BI3" s="78"/>
     </row>
-    <row r="4" spans="1:61" s="85" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:61" s="85" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="83" t="str">
         <f>Cards!E2</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
@@ -8052,128 +8054,128 @@
         <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
       </c>
       <c r="AE4" s="83" t="str">
-        <f t="shared" ref="AE4" si="1">A4</f>
+        <f t="shared" ref="AE4" si="4">A4</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
       <c r="AF4" s="83" t="str">
-        <f t="shared" ref="AF4" si="2">B4</f>
+        <f t="shared" ref="AF4" si="5">B4</f>
         <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
       <c r="AG4" s="85" t="str">
-        <f t="shared" ref="AG4" si="3">C4</f>
+        <f t="shared" ref="AG4" si="6">C4</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
       <c r="AH4" s="83" t="str">
-        <f t="shared" ref="AH4" si="4">D4</f>
+        <f t="shared" ref="AH4" si="7">D4</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
       <c r="AI4" s="85" t="str">
-        <f t="shared" ref="AI4" si="5">E4</f>
+        <f t="shared" ref="AI4" si="8">E4</f>
         <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
       </c>
       <c r="AJ4" s="83" t="str">
-        <f t="shared" ref="AJ4" si="6">F4</f>
+        <f t="shared" ref="AJ4" si="9">F4</f>
         <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
       </c>
       <c r="AK4" s="85" t="str">
-        <f t="shared" ref="AK4" si="7">G4</f>
+        <f t="shared" ref="AK4" si="10">G4</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
       <c r="AL4" s="83" t="str">
-        <f t="shared" ref="AL4" si="8">H4</f>
+        <f t="shared" ref="AL4" si="11">H4</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
       <c r="AM4" s="85" t="str">
-        <f t="shared" ref="AM4" si="9">I4</f>
+        <f t="shared" ref="AM4" si="12">I4</f>
         <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy Troops</v>
       </c>
       <c r="AN4" s="83" t="str">
-        <f t="shared" ref="AN4" si="10">J4</f>
+        <f t="shared" ref="AN4" si="13">J4</f>
         <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy Troops</v>
       </c>
       <c r="AO4" s="85" t="str">
-        <f t="shared" ref="AO4" si="11">K4</f>
+        <f t="shared" ref="AO4" si="14">K4</f>
         <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
       </c>
       <c r="AP4" s="83" t="str">
-        <f t="shared" ref="AP4" si="12">L4</f>
+        <f t="shared" ref="AP4" si="15">L4</f>
         <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
       </c>
       <c r="AQ4" s="85" t="str">
-        <f t="shared" ref="AQ4" si="13">M4</f>
+        <f t="shared" ref="AQ4" si="16">M4</f>
         <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
       </c>
       <c r="AR4" s="83" t="str">
-        <f t="shared" ref="AR4" si="14">N4</f>
+        <f t="shared" ref="AR4" si="17">N4</f>
         <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
       </c>
       <c r="AS4" s="85" t="str">
-        <f t="shared" ref="AS4" si="15">O4</f>
+        <f t="shared" ref="AS4" si="18">O4</f>
         <v>Each Player must have at least $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
       </c>
       <c r="AT4" s="83" t="str">
-        <f t="shared" ref="AT4" si="16">P4</f>
+        <f t="shared" ref="AT4" si="19">P4</f>
         <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
       </c>
       <c r="AU4" s="85" t="str">
-        <f t="shared" ref="AU4" si="17">Q4</f>
+        <f t="shared" ref="AU4" si="20">Q4</f>
         <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
       </c>
       <c r="AV4" s="83" t="str">
-        <f t="shared" ref="AV4" si="18">R4</f>
+        <f t="shared" ref="AV4" si="21">R4</f>
         <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
       </c>
       <c r="AW4" s="85" t="str">
-        <f t="shared" ref="AW4" si="19">S4</f>
+        <f t="shared" ref="AW4" si="22">S4</f>
         <v>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
       <c r="AX4" s="86" t="str">
-        <f t="shared" ref="AX4" si="20">T4</f>
+        <f t="shared" ref="AX4" si="23">T4</f>
         <v>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
       <c r="AY4" s="83" t="str">
-        <f t="shared" ref="AY4" si="21">U4</f>
+        <f t="shared" ref="AY4" si="24">U4</f>
         <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
       <c r="AZ4" s="85" t="str">
-        <f t="shared" ref="AZ4" si="22">V4</f>
+        <f t="shared" ref="AZ4" si="25">V4</f>
         <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
       <c r="BA4" s="83" t="str">
-        <f t="shared" ref="BA4" si="23">W4</f>
+        <f t="shared" ref="BA4" si="26">W4</f>
         <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</v>
       </c>
       <c r="BB4" s="85" t="str">
-        <f t="shared" ref="BB4" si="24">X4</f>
+        <f t="shared" ref="BB4" si="27">X4</f>
         <v>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</v>
       </c>
       <c r="BC4" s="83" t="str">
-        <f t="shared" ref="BC4" si="25">Y4</f>
+        <f t="shared" ref="BC4" si="28">Y4</f>
         <v>At least $L3 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
       <c r="BD4" s="85" t="str">
-        <f t="shared" ref="BD4" si="26">Z4</f>
+        <f t="shared" ref="BD4" si="29">Z4</f>
         <v>No more than $L3 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
       <c r="BE4" s="83" t="str">
-        <f t="shared" ref="BE4" si="27">AA4</f>
+        <f t="shared" ref="BE4" si="30">AA4</f>
         <v>At least $L3 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
       <c r="BF4" s="85" t="str">
-        <f t="shared" ref="BF4" si="28">AB4</f>
+        <f t="shared" ref="BF4" si="31">AB4</f>
         <v>No more than $L3 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
       <c r="BG4" s="83" t="str">
-        <f t="shared" ref="BG4" si="29">AC4</f>
+        <f t="shared" ref="BG4" si="32">AC4</f>
         <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
       </c>
       <c r="BH4" s="86" t="str">
-        <f t="shared" ref="BH4" si="30">AD4</f>
+        <f t="shared" ref="BH4" si="33">AD4</f>
         <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
       </c>
       <c r="BI4" s="83"/>
     </row>
-    <row r="5" spans="1:61" s="89" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:61" s="89" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="87" t="str">
         <f>Cards!F2</f>
         <v>Fickle Mercenaries</v>
@@ -8243,179 +8245,179 @@
         <v>Backroom Deal</v>
       </c>
       <c r="R5" s="87" t="str">
-        <f t="shared" ref="R5:AH5" si="31">A5</f>
+        <f t="shared" ref="R5:AH5" si="34">A5</f>
         <v>Fickle Mercenaries</v>
       </c>
       <c r="S5" s="89" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Blatant Thievery</v>
       </c>
       <c r="T5" s="87" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Double Agents</v>
       </c>
       <c r="U5" s="89" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Questionable Reallocation</v>
       </c>
       <c r="V5" s="87" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Blackmail</v>
       </c>
       <c r="W5" s="89" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Invalid Paperwork</v>
       </c>
       <c r="X5" s="87" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Insider Trading</v>
       </c>
       <c r="Y5" s="89" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Whispers of the People</v>
       </c>
       <c r="Z5" s="87" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Dangerous Monopolies</v>
       </c>
       <c r="AA5" s="89" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Corporate Takeover</v>
       </c>
       <c r="AB5" s="87" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Sabotage</v>
       </c>
       <c r="AC5" s="89" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Poor Management</v>
       </c>
       <c r="AD5" s="90" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Assassination</v>
       </c>
       <c r="AE5" s="87" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Betrayal</v>
       </c>
       <c r="AF5" s="87" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Intimidate</v>
       </c>
       <c r="AG5" s="89" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Humiliate</v>
       </c>
       <c r="AH5" s="87" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>Backroom Deal</v>
       </c>
       <c r="AI5" s="89" t="str">
-        <f t="shared" ref="AI5:AY5" si="32">A5</f>
+        <f t="shared" ref="AI5:AY5" si="35">A5</f>
         <v>Fickle Mercenaries</v>
       </c>
       <c r="AJ5" s="87" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Blatant Thievery</v>
       </c>
       <c r="AK5" s="89" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Double Agents</v>
       </c>
       <c r="AL5" s="87" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Questionable Reallocation</v>
       </c>
       <c r="AM5" s="89" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Blackmail</v>
       </c>
       <c r="AN5" s="87" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Invalid Paperwork</v>
       </c>
       <c r="AO5" s="89" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Insider Trading</v>
       </c>
       <c r="AP5" s="87" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Whispers of the People</v>
       </c>
       <c r="AQ5" s="89" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Dangerous Monopolies</v>
       </c>
       <c r="AR5" s="87" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Corporate Takeover</v>
       </c>
       <c r="AS5" s="89" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Sabotage</v>
       </c>
       <c r="AT5" s="87" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Poor Management</v>
       </c>
       <c r="AU5" s="89" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Assassination</v>
       </c>
       <c r="AV5" s="87" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Betrayal</v>
       </c>
       <c r="AW5" s="89" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Intimidate</v>
       </c>
       <c r="AX5" s="90" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Humiliate</v>
       </c>
       <c r="AY5" s="87" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="35"/>
         <v>Backroom Deal</v>
       </c>
       <c r="BA5" s="87" t="str">
-        <f>AA1</f>
+        <f t="shared" ref="BA5:BI6" si="36">AA1</f>
         <v>Wary Guards</v>
       </c>
       <c r="BB5" s="89" t="str">
-        <f>AB1</f>
+        <f t="shared" si="36"/>
         <v>Information Security</v>
       </c>
       <c r="BC5" s="87" t="str">
-        <f>AC1</f>
+        <f t="shared" si="36"/>
         <v>Blood Pact</v>
       </c>
       <c r="BD5" s="89" t="str">
-        <f>AD1</f>
+        <f t="shared" si="36"/>
         <v>Expert Broker</v>
       </c>
       <c r="BE5" s="87" t="str">
-        <f>AE1</f>
+        <f t="shared" si="36"/>
         <v>Codependent Relationship</v>
       </c>
       <c r="BF5" s="89" t="str">
-        <f>AF1</f>
+        <f t="shared" si="36"/>
         <v>Dangerous Promises</v>
       </c>
       <c r="BG5" s="87" t="str">
-        <f>AG1</f>
+        <f t="shared" si="36"/>
         <v>Large Middle Class</v>
       </c>
       <c r="BH5" s="87" t="str">
-        <f>AH1</f>
+        <f t="shared" si="36"/>
         <v>Innovation Hub</v>
       </c>
       <c r="BI5" s="87" t="str">
-        <f>AI1</f>
+        <f t="shared" si="36"/>
         <v>Fire Temple</v>
       </c>
     </row>
-    <row r="6" spans="1:61" s="85" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:61" s="85" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="83" t="str">
         <f>Cards!G2</f>
         <v>Give $D6 Troops to Player $R</v>
@@ -8485,175 +8487,175 @@
         <v>Exchange a random held Alliance Token, or one of your own if you hold none, with one of the choice of Player $R</v>
       </c>
       <c r="R6" s="83" t="str">
-        <f t="shared" ref="R6:AH6" si="33">A6</f>
+        <f t="shared" ref="R6:AH6" si="37">A6</f>
         <v>Give $D6 Troops to Player $R</v>
       </c>
       <c r="S6" s="85" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Give $D6 Coins to Player $R</v>
       </c>
       <c r="T6" s="83" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Give $D6 Spies to Player $R</v>
       </c>
       <c r="U6" s="85" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Give $D6 Commodities to Player $R</v>
       </c>
       <c r="V6" s="83" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Give the King's Favor to Player $R</v>
       </c>
       <c r="W6" s="85" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Player $R may peek at the Law card at the top of the queue &amp; put it on the bottom of the queue if they want</v>
       </c>
       <c r="X6" s="83" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Give $D6 random Cards from your hand to Player $R</v>
       </c>
       <c r="Y6" s="85" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Rearrange $D3 Law cards from the top of the queue</v>
       </c>
       <c r="Z6" s="83" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Destroy an Investment at level $D6</v>
       </c>
       <c r="AA6" s="85" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Send an Investment at level $D6 to Player $R</v>
       </c>
       <c r="AB6" s="83" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Downgrade an Investment at level $D6</v>
       </c>
       <c r="AC6" s="85" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Downgrade an Investment at level $D6</v>
       </c>
       <c r="AD6" s="86" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Kill a Leader at level $D6</v>
       </c>
       <c r="AE6" s="83" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Send a Leader at level $D6 to Player $R</v>
       </c>
       <c r="AF6" s="83" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Demote a Leader at level $D6</v>
       </c>
       <c r="AG6" s="85" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Demote a Leader at level $D6</v>
       </c>
       <c r="AH6" s="83" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>Exchange a random held Alliance Token, or one of your own if you hold none, with one of the choice of Player $R</v>
       </c>
       <c r="AI6" s="85" t="str">
-        <f t="shared" ref="AI6:AY6" si="34">A6</f>
+        <f t="shared" ref="AI6:AY6" si="38">A6</f>
         <v>Give $D6 Troops to Player $R</v>
       </c>
       <c r="AJ6" s="83" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Give $D6 Coins to Player $R</v>
       </c>
       <c r="AK6" s="85" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Give $D6 Spies to Player $R</v>
       </c>
       <c r="AL6" s="83" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Give $D6 Commodities to Player $R</v>
       </c>
       <c r="AM6" s="85" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Give the King's Favor to Player $R</v>
       </c>
       <c r="AN6" s="83" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Player $R may peek at the Law card at the top of the queue &amp; put it on the bottom of the queue if they want</v>
       </c>
       <c r="AO6" s="85" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Give $D6 random Cards from your hand to Player $R</v>
       </c>
       <c r="AP6" s="83" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Rearrange $D3 Law cards from the top of the queue</v>
       </c>
       <c r="AQ6" s="85" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Destroy an Investment at level $D6</v>
       </c>
       <c r="AR6" s="83" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Send an Investment at level $D6 to Player $R</v>
       </c>
       <c r="AS6" s="85" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Downgrade an Investment at level $D6</v>
       </c>
       <c r="AT6" s="83" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Downgrade an Investment at level $D6</v>
       </c>
       <c r="AU6" s="85" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Kill a Leader at level $D6</v>
       </c>
       <c r="AV6" s="83" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Send a Leader at level $D6 to Player $R</v>
       </c>
       <c r="AW6" s="85" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Demote a Leader at level $D6</v>
       </c>
       <c r="AX6" s="86" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Demote a Leader at level $D6</v>
       </c>
       <c r="AY6" s="83" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>Exchange a random held Alliance Token, or one of your own if you hold none, with one of the choice of Player $R</v>
       </c>
       <c r="BA6" s="83" t="str">
-        <f>AA2</f>
+        <f t="shared" si="36"/>
         <v>Subtract $L3 from Scheme Guard rolls</v>
       </c>
-      <c r="BB6" s="109" t="str">
-        <f>AB2</f>
+      <c r="BB6" s="85" t="str">
+        <f t="shared" si="36"/>
         <v>Subtract $L3 from Scheme Card rolls</v>
       </c>
       <c r="BC6" s="83" t="str">
-        <f>AC2</f>
+        <f t="shared" si="36"/>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Undermarket</v>
       </c>
       <c r="BD6" s="85" t="str">
-        <f>AD2</f>
+        <f t="shared" si="36"/>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
       </c>
       <c r="BE6" s="83" t="str">
-        <f>AE2</f>
+        <f t="shared" si="36"/>
         <v>Trade up to $L3 additional Coins when Buying from the Undermarket</v>
       </c>
       <c r="BF6" s="85" t="str">
-        <f>AF2</f>
+        <f t="shared" si="36"/>
         <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
       </c>
       <c r="BG6" s="83" t="str">
-        <f>AG2</f>
+        <f t="shared" si="36"/>
         <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
       </c>
       <c r="BH6" s="83" t="str">
-        <f>AH2</f>
+        <f t="shared" si="36"/>
         <v>Provides private Monetize Action at Market Rate + $L3</v>
       </c>
       <c r="BI6" s="83" t="str">
-        <f>AI2</f>
+        <f t="shared" si="36"/>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
       </c>
     </row>
@@ -8666,295 +8668,295 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BDA35E-BFC3-134A-A064-89D65A8B31CF}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.50390625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D1" t="s">
+        <v>314</v>
+      </c>
+      <c r="E1" t="s">
         <v>315</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>316</v>
       </c>
-      <c r="D1" t="s">
-        <v>317</v>
-      </c>
-      <c r="E1" t="s">
-        <v>318</v>
-      </c>
-      <c r="F1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D2">
         <v>27.7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D3">
         <v>27.7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D4">
         <v>30.75</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E7" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E8" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E10" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E11" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E12" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E13" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -8965,90 +8967,90 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC83F89-2724-CA43-A519-59213A612B31}">
   <dimension ref="A1:U55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.13671875" style="106" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.72265625" customWidth="1"/>
-    <col min="4" max="4" width="8.33984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.27734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.22265625" style="108" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.43359375" style="108" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.22265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.43359375" style="108" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="11.8359375" style="108" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.9140625" style="108" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" style="106" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="108" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="108" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="108" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="11.85546875" style="108" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" style="108" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C1" t="s">
+        <v>463</v>
+      </c>
+      <c r="D1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1" t="s">
         <v>465</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
+        <v>495</v>
+      </c>
+      <c r="G1" t="s">
+        <v>494</v>
+      </c>
+      <c r="H1" t="s">
         <v>466</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
         <v>467</v>
       </c>
-      <c r="D1" t="s">
+      <c r="J1" t="s">
+        <v>492</v>
+      </c>
+      <c r="K1" t="s">
         <v>468</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>469</v>
       </c>
-      <c r="F1" t="s">
-        <v>501</v>
-      </c>
-      <c r="G1" t="s">
-        <v>500</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>470</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>471</v>
       </c>
-      <c r="J1" t="s">
-        <v>498</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>472</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>473</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>474</v>
       </c>
-      <c r="N1" t="s">
+      <c r="R1" t="s">
         <v>475</v>
       </c>
-      <c r="O1" t="s">
+      <c r="S1" t="s">
         <v>476</v>
       </c>
-      <c r="P1" t="s">
+      <c r="T1" t="s">
         <v>477</v>
       </c>
-      <c r="Q1" t="s">
-        <v>478</v>
-      </c>
-      <c r="R1" t="s">
-        <v>479</v>
-      </c>
-      <c r="S1" t="s">
-        <v>480</v>
-      </c>
-      <c r="T1" t="s">
-        <v>481</v>
-      </c>
       <c r="U1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="106">
         <v>46075</v>
       </c>
@@ -9092,7 +9094,7 @@
         <v>0.92638888888888893</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="106">
         <v>46089</v>
       </c>
@@ -9148,7 +9150,7 @@
         <v>0.86527777777777781</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C4" s="107" t="b">
         <v>0</v>
       </c>
@@ -9156,7 +9158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C5" s="107" t="b">
         <v>0</v>
       </c>
@@ -9164,7 +9166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C6" s="107" t="b">
         <v>0</v>
       </c>
@@ -9172,7 +9174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C7" s="107" t="b">
         <v>0</v>
       </c>
@@ -9180,7 +9182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C8" s="107" t="b">
         <v>0</v>
       </c>
@@ -9188,7 +9190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C9" s="107" t="b">
         <v>0</v>
       </c>
@@ -9196,7 +9198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C10" s="107" t="b">
         <v>0</v>
       </c>
@@ -9204,7 +9206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C11" s="107" t="b">
         <v>0</v>
       </c>
@@ -9212,7 +9214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C12" s="107" t="b">
         <v>0</v>
       </c>
@@ -9220,7 +9222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C13" s="107" t="b">
         <v>0</v>
       </c>
@@ -9228,7 +9230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C14" s="107" t="b">
         <v>0</v>
       </c>
@@ -9236,7 +9238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C15" s="107" t="b">
         <v>0</v>
       </c>
@@ -9244,7 +9246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C16" s="107" t="b">
         <v>0</v>
       </c>
@@ -9252,7 +9254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C17" s="107" t="b">
         <v>0</v>
       </c>
@@ -9260,7 +9262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C18" s="107" t="b">
         <v>0</v>
       </c>
@@ -9268,7 +9270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C19" s="107" t="b">
         <v>0</v>
       </c>
@@ -9276,7 +9278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C20" s="107" t="b">
         <v>0</v>
       </c>
@@ -9284,7 +9286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C21" s="107" t="b">
         <v>0</v>
       </c>
@@ -9292,7 +9294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C22" s="107" t="b">
         <v>0</v>
       </c>
@@ -9300,7 +9302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C23" s="107" t="b">
         <v>0</v>
       </c>
@@ -9308,7 +9310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C24" s="107" t="b">
         <v>0</v>
       </c>
@@ -9316,7 +9318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C25" s="107" t="b">
         <v>0</v>
       </c>
@@ -9324,7 +9326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C26" s="107" t="b">
         <v>0</v>
       </c>
@@ -9332,7 +9334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C27" s="107" t="b">
         <v>0</v>
       </c>
@@ -9340,7 +9342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C28" s="107" t="b">
         <v>0</v>
       </c>
@@ -9348,7 +9350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C29" s="107" t="b">
         <v>0</v>
       </c>
@@ -9356,7 +9358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C30" s="107" t="b">
         <v>0</v>
       </c>
@@ -9364,7 +9366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C31" s="107" t="b">
         <v>0</v>
       </c>
@@ -9372,7 +9374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C32" s="107" t="b">
         <v>0</v>
       </c>
@@ -9380,7 +9382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C33" s="107" t="b">
         <v>0</v>
       </c>
@@ -9388,7 +9390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C34" s="107" t="b">
         <v>0</v>
       </c>
@@ -9396,7 +9398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C35" s="107" t="b">
         <v>0</v>
       </c>
@@ -9404,7 +9406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C36" s="107" t="b">
         <v>0</v>
       </c>
@@ -9412,7 +9414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C37" s="107" t="b">
         <v>0</v>
       </c>
@@ -9420,7 +9422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C38" s="107" t="b">
         <v>0</v>
       </c>
@@ -9428,7 +9430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C39" s="107" t="b">
         <v>0</v>
       </c>
@@ -9436,7 +9438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C40" s="107" t="b">
         <v>0</v>
       </c>
@@ -9444,7 +9446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C41" s="107" t="b">
         <v>0</v>
       </c>
@@ -9452,7 +9454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C42" s="107" t="b">
         <v>0</v>
       </c>
@@ -9460,7 +9462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C43" s="107" t="b">
         <v>0</v>
       </c>
@@ -9468,7 +9470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C44" s="107" t="b">
         <v>0</v>
       </c>
@@ -9476,7 +9478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C45" s="107" t="b">
         <v>0</v>
       </c>
@@ -9484,7 +9486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C46" s="107" t="b">
         <v>0</v>
       </c>
@@ -9492,7 +9494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C47" s="107" t="b">
         <v>0</v>
       </c>
@@ -9500,7 +9502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C48" s="107" t="b">
         <v>0</v>
       </c>
@@ -9508,7 +9510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C49" s="107" t="b">
         <v>0</v>
       </c>
@@ -9516,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C50" s="107" t="b">
         <v>0</v>
       </c>
@@ -9524,7 +9526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C51" s="107" t="b">
         <v>0</v>
       </c>
@@ -9532,7 +9534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C52" s="107" t="b">
         <v>0</v>
       </c>
@@ -9540,7 +9542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C53" s="107" t="b">
         <v>0</v>
       </c>
@@ -9548,7 +9550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C54" s="107" t="b">
         <v>0</v>
       </c>
@@ -9556,7 +9558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C55" s="107" t="b">
         <v>0</v>
       </c>

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3352" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B4FEFF1-680E-49BA-B0DD-DB1965E21A14}"/>
+  <xr:revisionPtr revIDLastSave="3365" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3914F54C-9B9D-401F-A4C7-EB6EA0DFAF21}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="513">
   <si>
     <t>Standard Card</t>
   </si>
@@ -1574,6 +1574,15 @@
   </si>
   <si>
     <t>Send Troops up to Leader's Level to the Battlefield</t>
+  </si>
+  <si>
+    <t>Donate</t>
+  </si>
+  <si>
+    <t>Pay up to Leader's Level Coins to the Royal Bank and immediately gain half the Coins paid in Honor</t>
+  </si>
+  <si>
+    <t>Pay up to Leader's Level Coins to the Royal Bank and immediately gain half the Coins paid in Honor. Immediately demote the Leader used.</t>
   </si>
 </sst>
 </file>
@@ -3684,6 +3693,10 @@
 </FeaturePropertyBags>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5117,7 +5130,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D195C1D-DB02-1743-BBD2-99104C1FFD33}">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -5501,15 +5514,15 @@
       <c r="H16" s="42"/>
       <c r="I16" s="45"/>
     </row>
-    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>259</v>
+        <v>510</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>260</v>
+        <v>512</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D17" s="42"/>
       <c r="E17" s="42"/>
@@ -5518,12 +5531,12 @@
       <c r="H17" s="42"/>
       <c r="I17" s="45"/>
     </row>
-    <row r="18" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>261</v>
@@ -5535,12 +5548,12 @@
       <c r="H18" s="42"/>
       <c r="I18" s="45"/>
     </row>
-    <row r="19" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C19" s="38" t="s">
         <v>261</v>
@@ -5554,10 +5567,10 @@
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
-        <v>480</v>
+        <v>264</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>481</v>
+        <v>265</v>
       </c>
       <c r="C20" s="38" t="s">
         <v>261</v>
@@ -5571,10 +5584,10 @@
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
-        <v>251</v>
+        <v>480</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>267</v>
+        <v>481</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>261</v>
@@ -5588,10 +5601,10 @@
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C22" s="38" t="s">
         <v>261</v>
@@ -5603,22 +5616,56 @@
       <c r="H22" s="42"/>
       <c r="I22" s="45"/>
     </row>
-    <row r="23" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="39" t="s">
+    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>261</v>
+      </c>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="45"/>
+    </row>
+    <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="39" t="s">
         <v>257</v>
       </c>
-      <c r="B23" s="40" t="s">
+      <c r="B24" s="40" t="s">
         <v>269</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C24" s="41" t="s">
         <v>261</v>
       </c>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="46"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="45"/>
+    </row>
+    <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="39" t="s">
+        <v>510</v>
+      </c>
+      <c r="B25" s="40" t="s">
+        <v>511</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>261</v>
+      </c>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7419,7 +7466,7 @@
         <v>Elite Troops</v>
       </c>
       <c r="BD1" s="80" t="str">
-        <f t="shared" ref="BD1:BM2" si="2">U1</f>
+        <f t="shared" ref="BD1:BI2" si="2">U1</f>
         <v>Bazaar</v>
       </c>
       <c r="BE1" s="78" t="str">

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3365" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3914F54C-9B9D-401F-A4C7-EB6EA0DFAF21}"/>
+  <xr:revisionPtr revIDLastSave="3394" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BF81C7C-8420-4A84-91BD-B49F52503D96}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="520">
   <si>
     <t>Standard Card</t>
   </si>
@@ -1513,9 +1513,6 @@
     <t>Gain $L3 additional Coins from outside the Royal Bank when winning a Sue</t>
   </si>
   <si>
-    <t xml:space="preserve">   </t>
-  </si>
-  <si>
     <t>Move the Law $L6 additional places forward in the queue during Prioritize</t>
   </si>
   <si>
@@ -1583,6 +1580,30 @@
   </si>
   <si>
     <t>Pay up to Leader's Level Coins to the Royal Bank and immediately gain half the Coins paid in Honor. Immediately demote the Leader used.</t>
+  </si>
+  <si>
+    <t>Convert $L3 additional Coins during Court Donate</t>
+  </si>
+  <si>
+    <t>Convert $L3 additional Coins during Undermarket Donate</t>
+  </si>
+  <si>
+    <t>Abusive Power</t>
+  </si>
+  <si>
+    <t>Soup Kitchens</t>
+  </si>
+  <si>
+    <t>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</t>
+  </si>
+  <si>
+    <t>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</t>
+  </si>
+  <si>
+    <t>Stalled Front</t>
+  </si>
+  <si>
+    <t>Quality Strength</t>
   </si>
 </sst>
 </file>
@@ -4094,7 +4115,7 @@
         <v>487</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>16</v>
@@ -4262,7 +4283,7 @@
         <v>55</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
@@ -4351,7 +4372,7 @@
         <v>74</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>488</v>
@@ -4389,7 +4410,7 @@
         <v>82</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>83</v>
@@ -4481,7 +4502,7 @@
         <v>104</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>106</v>
@@ -4496,7 +4517,7 @@
         <v>108</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
@@ -4518,9 +4539,7 @@
       <c r="E19" s="15" t="s">
         <v>458</v>
       </c>
-      <c r="F19" s="23" t="s">
-        <v>489</v>
-      </c>
+      <c r="F19" s="23"/>
       <c r="G19" s="25"/>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
@@ -4800,15 +4819,19 @@
       <c r="C32" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="16"/>
+      <c r="D32" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>516</v>
+      </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
       <c r="H32" s="4"/>
       <c r="I32" s="3"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>168</v>
       </c>
@@ -4818,8 +4841,12 @@
       <c r="C33" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="16"/>
+      <c r="D33" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>517</v>
+      </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
       <c r="H33" s="4"/>
@@ -4834,7 +4861,7 @@
         <v>172</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="16"/>
@@ -4885,10 +4912,10 @@
         <v>177</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -4898,12 +4925,16 @@
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="16"/>
+      <c r="B38" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>512</v>
+      </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
       <c r="F38" s="6"/>
@@ -4912,12 +4943,16 @@
       <c r="I38" s="3"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="16"/>
+      <c r="B39" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>513</v>
+      </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
       <c r="F39" s="6"/>
@@ -5178,7 +5213,7 @@
         <v>202</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C2" s="49" t="s">
         <v>203</v>
@@ -5248,7 +5283,7 @@
         <v>217</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G4" s="42" t="s">
         <v>218</v>
@@ -5308,7 +5343,7 @@
         <v>451</v>
       </c>
       <c r="H6" s="42" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="I6" s="45"/>
     </row>
@@ -5323,7 +5358,7 @@
         <v>203</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E7" s="42" t="s">
         <v>331</v>
@@ -5394,7 +5429,7 @@
         <v>203</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E10" s="42" t="s">
         <v>243</v>
@@ -5409,14 +5444,14 @@
         <v>244</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>203</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="42" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
@@ -5516,10 +5551,10 @@
     </row>
     <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>253</v>
@@ -5652,10 +5687,10 @@
     </row>
     <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
+        <v>509</v>
+      </c>
+      <c r="B25" s="40" t="s">
         <v>510</v>
-      </c>
-      <c r="B25" s="40" t="s">
-        <v>511</v>
       </c>
       <c r="C25" s="41" t="s">
         <v>261</v>
@@ -9049,10 +9084,10 @@
         <v>465</v>
       </c>
       <c r="F1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1" t="s">
         <v>466</v>
@@ -9061,7 +9096,7 @@
         <v>467</v>
       </c>
       <c r="J1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="K1" t="s">
         <v>468</v>
@@ -9094,7 +9129,7 @@
         <v>477</v>
       </c>
       <c r="U1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3394" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BF81C7C-8420-4A84-91BD-B49F52503D96}"/>
+  <xr:revisionPtr revIDLastSave="3399" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FD2E225-2670-451F-AA6F-E1868A59396C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="524">
   <si>
     <t>Standard Card</t>
   </si>
@@ -1604,6 +1604,18 @@
   </si>
   <si>
     <t>Quality Strength</t>
+  </si>
+  <si>
+    <t>Move one of your Laws $D6 spaces back in the Queue</t>
+  </si>
+  <si>
+    <t>Move $D6 of your Laws one space back in the Queue</t>
+  </si>
+  <si>
+    <t>Rallied Opposition</t>
+  </si>
+  <si>
+    <t>Waning Support</t>
   </si>
 </sst>
 </file>
@@ -4539,8 +4551,12 @@
       <c r="E19" s="15" t="s">
         <v>458</v>
       </c>
-      <c r="F19" s="23"/>
-      <c r="G19" s="25"/>
+      <c r="F19" s="23" t="s">
+        <v>522</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>520</v>
+      </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
       <c r="J19" s="4"/>
@@ -4561,8 +4577,12 @@
       <c r="E20" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="7"/>
+      <c r="F20" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>521</v>
+      </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3399" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FD2E225-2670-451F-AA6F-E1868A59396C}"/>
+  <xr:revisionPtr revIDLastSave="3403" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5D1A1E9-6FEE-4738-94CE-64DDE07B3441}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -919,12 +919,6 @@
     <t>Persian</t>
   </si>
   <si>
-    <t>At least $L3 Players must use Court Actions or all Players suffer sanctions on Flatter</t>
-  </si>
-  <si>
-    <t>No more than $L3 Players may use Court Actions or all Players suffer sanctions on Flatter</t>
-  </si>
-  <si>
     <t>Law Cards</t>
   </si>
   <si>
@@ -1492,12 +1486,6 @@
     <t>Move a Law Leader's Level places forward in the queue, but never to become the Deliberated Law</t>
   </si>
   <si>
-    <t>At least $L3 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</t>
-  </si>
-  <si>
-    <t>No more than $L3 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</t>
-  </si>
-  <si>
     <t>Spend $L3 fewer Cards per Coin when Monetizing in the Undermarket</t>
   </si>
   <si>
@@ -1616,6 +1604,18 @@
   </si>
   <si>
     <t>Waning Support</t>
+  </si>
+  <si>
+    <t>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</t>
+  </si>
+  <si>
+    <t>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</t>
+  </si>
+  <si>
+    <t>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</t>
+  </si>
+  <si>
+    <t>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</t>
   </si>
 </sst>
 </file>
@@ -4124,10 +4124,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>16</v>
@@ -4159,7 +4159,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>24</v>
@@ -4185,7 +4185,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>30</v>
@@ -4260,10 +4260,10 @@
         <v>48</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>49</v>
@@ -4289,13 +4289,13 @@
         <v>54</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>55</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
@@ -4312,10 +4312,10 @@
         <v>58</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>59</v>
@@ -4341,7 +4341,7 @@
         <v>64</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>65</v>
@@ -4384,10 +4384,10 @@
         <v>74</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>76</v>
@@ -4413,7 +4413,7 @@
         <v>80</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>81</v>
@@ -4422,7 +4422,7 @@
         <v>82</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>83</v>
@@ -4514,7 +4514,7 @@
         <v>104</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>106</v>
@@ -4523,13 +4523,13 @@
         <v>107</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>108</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
@@ -4549,13 +4549,13 @@
         <v>112</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
@@ -4578,10 +4578,10 @@
         <v>117</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
@@ -4623,7 +4623,7 @@
         <v>126</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7"/>
@@ -4680,10 +4680,10 @@
         <v>137</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>139</v>
@@ -4702,16 +4702,16 @@
         <v>141</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>142</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>482</v>
+        <v>522</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4733,7 +4733,7 @@
         <v>146</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>483</v>
+        <v>523</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4755,7 +4755,7 @@
         <v>150</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>291</v>
+        <v>520</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4777,7 +4777,7 @@
         <v>154</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>292</v>
+        <v>521</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4840,10 +4840,10 @@
         <v>167</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -4862,10 +4862,10 @@
         <v>170</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -4881,7 +4881,7 @@
         <v>172</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="16"/>
@@ -4914,10 +4914,10 @@
         <v>176</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4932,10 +4932,10 @@
         <v>177</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -4950,10 +4950,10 @@
         <v>178</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -4968,10 +4968,10 @@
         <v>179</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -5219,7 +5219,7 @@
         <v>199</v>
       </c>
       <c r="G1" s="54" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H1" s="54" t="s">
         <v>200</v>
@@ -5233,7 +5233,7 @@
         <v>202</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C2" s="49" t="s">
         <v>203</v>
@@ -5259,16 +5259,16 @@
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C3" s="38" t="s">
         <v>203</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E3" s="42" t="s">
         <v>210</v>
@@ -5280,7 +5280,7 @@
         <v>212</v>
       </c>
       <c r="H3" s="42" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I3" s="42" t="s">
         <v>213</v>
@@ -5303,7 +5303,7 @@
         <v>217</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="G4" s="42" t="s">
         <v>218</v>
@@ -5318,7 +5318,7 @@
         <v>220</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>203</v>
@@ -5333,10 +5333,10 @@
         <v>223</v>
       </c>
       <c r="G5" s="42" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H5" s="42" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I5" s="45"/>
     </row>
@@ -5360,10 +5360,10 @@
         <v>228</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H6" s="42" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="I6" s="45"/>
     </row>
@@ -5378,13 +5378,13 @@
         <v>203</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G7" s="42" t="s">
         <v>231</v>
@@ -5406,7 +5406,7 @@
         <v>234</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F8" s="42" t="s">
         <v>235</v>
@@ -5449,7 +5449,7 @@
         <v>203</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E10" s="42" t="s">
         <v>243</v>
@@ -5464,14 +5464,14 @@
         <v>244</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C11" s="38" t="s">
         <v>203</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="42" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
@@ -5571,10 +5571,10 @@
     </row>
     <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C17" s="38" t="s">
         <v>253</v>
@@ -5639,10 +5639,10 @@
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>261</v>
@@ -5707,10 +5707,10 @@
     </row>
     <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C25" s="41" t="s">
         <v>261</v>
@@ -5757,7 +5757,7 @@
         <v>275</v>
       </c>
       <c r="I1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -5783,7 +5783,7 @@
         <v>156</v>
       </c>
       <c r="I2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -5809,7 +5809,7 @@
         <v>169</v>
       </c>
       <c r="I3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5835,7 +5835,7 @@
         <v>148</v>
       </c>
       <c r="I4" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5861,7 +5861,7 @@
         <v>27</v>
       </c>
       <c r="I5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5887,7 +5887,7 @@
         <v>154</v>
       </c>
       <c r="I6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5898,7 +5898,7 @@
         <v>282</v>
       </c>
       <c r="C7" s="74" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D7" t="s">
         <v>283</v>
@@ -5913,12 +5913,12 @@
         <v>201</v>
       </c>
       <c r="I7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="95" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B8" s="95" t="s">
         <v>273</v>
@@ -5939,12 +5939,12 @@
         <v>272</v>
       </c>
       <c r="I8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="63" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B9" s="63" t="s">
         <v>274</v>
@@ -5967,7 +5967,7 @@
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="96" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B10" s="96" t="s">
         <v>272</v>
@@ -5990,205 +5990,205 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -6196,111 +6196,111 @@
     </row>
     <row r="23" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>409</v>
-      </c>
       <c r="G24" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="345" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>428</v>
-      </c>
       <c r="F27" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="195" x14ac:dyDescent="0.25">
@@ -6308,63 +6308,63 @@
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>427</v>
       </c>
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>229</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>264</v>
       </c>
       <c r="I30" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -6376,65 +6376,65 @@
         <v>245</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>241</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>202</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -6450,10 +6450,10 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>264</v>
@@ -6467,7 +6467,7 @@
     </row>
     <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>245</v>
@@ -6476,19 +6476,19 @@
         <v>241</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="I37" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -6506,35 +6506,35 @@
         <v>245</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="I38" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>248</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>245</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I39" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -6542,14 +6542,14 @@
       <c r="B40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G40" s="2"/>
       <c r="I40" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -6589,19 +6589,19 @@
     </row>
     <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>264</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>241</v>
@@ -6609,47 +6609,47 @@
     </row>
     <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>266</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>232</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>229</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
@@ -6668,16 +6668,16 @@
         <v>229</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>264</v>
@@ -6688,44 +6688,44 @@
         <v>241</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>241</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>245</v>
@@ -6734,20 +6734,20 @@
         <v>202</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -6763,22 +6763,22 @@
     </row>
     <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>236</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
@@ -6789,16 +6789,16 @@
         <v>264</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>245</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
@@ -6812,28 +6812,28 @@
         <v>245</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>245</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>248</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>245</v>
@@ -6902,7 +6902,7 @@
         <v>248</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D3" s="30" t="s">
         <v>244</v>
@@ -6954,7 +6954,7 @@
         <v>262</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D1" s="30" t="s">
         <v>264</v>
@@ -8133,19 +8133,19 @@
       </c>
       <c r="Y4" s="85" t="str">
         <f>Cards!E26</f>
-        <v>At least $L3 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+        <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
       <c r="Z4" s="83" t="str">
         <f>Cards!E27</f>
-        <v>No more than $L3 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+        <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
       <c r="AA4" s="85" t="str">
         <f>Cards!E28</f>
-        <v>At least $L3 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
+        <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
       <c r="AB4" s="83" t="str">
         <f>Cards!E29</f>
-        <v>No more than $L3 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
+        <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
       <c r="AC4" s="85" t="str">
         <f>Cards!E30</f>
@@ -8253,19 +8253,19 @@
       </c>
       <c r="BC4" s="83" t="str">
         <f t="shared" ref="BC4" si="28">Y4</f>
-        <v>At least $L3 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+        <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
       <c r="BD4" s="85" t="str">
         <f t="shared" ref="BD4" si="29">Z4</f>
-        <v>No more than $L3 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+        <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
       <c r="BE4" s="83" t="str">
         <f t="shared" ref="BE4" si="30">AA4</f>
-        <v>At least $L3 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
+        <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
       <c r="BF4" s="85" t="str">
         <f t="shared" ref="BF4" si="31">AB4</f>
-        <v>No more than $L3 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
+        <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
       <c r="BG4" s="83" t="str">
         <f t="shared" ref="BG4" si="32">AC4</f>
@@ -8781,31 +8781,31 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D1" t="s">
         <v>312</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>313</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>314</v>
-      </c>
-      <c r="E1" t="s">
-        <v>315</v>
-      </c>
-      <c r="F1" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D2">
         <v>27.7</v>
@@ -8813,14 +8813,14 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D3">
         <v>27.7</v>
@@ -8828,14 +8828,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D4">
         <v>30.75</v>
@@ -8843,222 +8843,222 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E11" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
+        <v>316</v>
+      </c>
+      <c r="E12" t="s">
         <v>318</v>
-      </c>
-      <c r="E12" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
+        <v>316</v>
+      </c>
+      <c r="E13" t="s">
         <v>318</v>
-      </c>
-      <c r="E13" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -9089,67 +9089,67 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C1" t="s">
         <v>461</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>462</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>463</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
+        <v>490</v>
+      </c>
+      <c r="G1" t="s">
+        <v>489</v>
+      </c>
+      <c r="H1" t="s">
         <v>464</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>465</v>
       </c>
-      <c r="F1" t="s">
-        <v>494</v>
-      </c>
-      <c r="G1" t="s">
-        <v>493</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>487</v>
+      </c>
+      <c r="K1" t="s">
         <v>466</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>467</v>
       </c>
-      <c r="J1" t="s">
-        <v>491</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>468</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>469</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>470</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>471</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>472</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>473</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>474</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>475</v>
       </c>
-      <c r="S1" t="s">
-        <v>476</v>
-      </c>
-      <c r="T1" t="s">
-        <v>477</v>
-      </c>
       <c r="U1" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3403" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5D1A1E9-6FEE-4738-94CE-64DDE07B3441}"/>
+  <xr:revisionPtr revIDLastSave="3436" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37185AFA-472E-4E99-AEE5-A6FF8A9012A1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="526">
   <si>
     <t>Standard Card</t>
   </si>
@@ -346,9 +346,6 @@
     <t>Undeniable Advisors</t>
   </si>
   <si>
-    <t>You may repeat Court Actions with level 7 - $L6 Leaders</t>
-  </si>
-  <si>
     <t>Chattering Windbags</t>
   </si>
   <si>
@@ -1549,18 +1546,12 @@
     <t>Exchange Alliance tokens with a Player of your choice. The chosen Player must place a Leader on this space. Both players then exchange up to the lowest LL tokens.</t>
   </si>
   <si>
-    <t>If Greeks are victorious, give remaining attacking Greeks to the player who deployed the fewest Troops (break ties with deployment order then with a Tie Trial or agreement). That player destroys 1 Troop per attacking Greek or 1 investment at level $D6 if they have no Troops.</t>
-  </si>
-  <si>
     <t>Add 1 Coin per Player to Royal Bank</t>
   </si>
   <si>
     <t>Give 1 Troop per Player to each player</t>
   </si>
   <si>
-    <t>Send Troops up to Leader's Level to the Battlefield</t>
-  </si>
-  <si>
     <t>Donate</t>
   </si>
   <si>
@@ -1616,6 +1607,21 @@
   </si>
   <si>
     <t>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </t>
+  </si>
+  <si>
+    <t>Send Troops up to Leader's Level to the Battlefield and gain half Troops in Coins</t>
+  </si>
+  <si>
+    <t>You may repeat Undermarket Actions at double the penalty</t>
+  </si>
+  <si>
+    <t>Painful Progress</t>
+  </si>
+  <si>
+    <t>If Greeks are victorious, give remaining attacking Greeks to the player who deployed the fewest Troops (break ties with deployment order then with a Tie Trial or agreement). That player destroys 1 Troop per attacking Greek or downgrades 1 investment by $D6 levels if they have no Troops.</t>
   </si>
 </sst>
 </file>
@@ -2540,7 +2546,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2820,6 +2826,9 @@
       </extLst>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
@@ -4124,10 +4133,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>16</v>
@@ -4159,7 +4168,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>24</v>
@@ -4185,7 +4194,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>30</v>
@@ -4260,10 +4269,10 @@
         <v>48</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>49</v>
@@ -4289,13 +4298,13 @@
         <v>54</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>55</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
@@ -4312,10 +4321,10 @@
         <v>58</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>59</v>
@@ -4341,7 +4350,7 @@
         <v>64</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>65</v>
@@ -4384,10 +4393,10 @@
         <v>74</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>76</v>
@@ -4413,7 +4422,7 @@
         <v>80</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>81</v>
@@ -4422,7 +4431,7 @@
         <v>82</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>83</v>
@@ -4491,16 +4500,16 @@
         <v>99</v>
       </c>
       <c r="C17" s="15" t="s">
+        <v>521</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="E17" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="F17" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>97</v>
@@ -4511,25 +4520,25 @@
     </row>
     <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C18" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="E18" s="15" t="s">
+        <v>454</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E18" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>108</v>
-      </c>
       <c r="G18" s="7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
@@ -4537,25 +4546,25 @@
     </row>
     <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="D19" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="E19" s="15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
@@ -4563,25 +4572,25 @@
     </row>
     <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="E20" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>117</v>
-      </c>
       <c r="F20" s="6" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
@@ -4589,19 +4598,19 @@
     </row>
     <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="D21" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="E21" s="15" t="s">
         <v>121</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>122</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7"/>
@@ -4611,19 +4620,19 @@
     </row>
     <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="D22" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="E22" s="15" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7"/>
@@ -4633,19 +4642,19 @@
     </row>
     <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="D23" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="E23" s="15" t="s">
         <v>130</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>131</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="9"/>
@@ -4655,19 +4664,19 @@
     </row>
     <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="D24" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="E24" s="15" t="s">
         <v>135</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>136</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7"/>
@@ -4677,19 +4686,19 @@
     </row>
     <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>139</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>140</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
@@ -4699,19 +4708,19 @@
     </row>
     <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>142</v>
-      </c>
       <c r="E26" s="15" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4721,19 +4730,19 @@
     </row>
     <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="D27" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>146</v>
-      </c>
       <c r="E27" s="15" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4743,19 +4752,19 @@
     </row>
     <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="C28" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="D28" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>150</v>
-      </c>
       <c r="E28" s="15" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4765,19 +4774,19 @@
     </row>
     <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C29" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="D29" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="E29" s="15" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4787,19 +4796,19 @@
     </row>
     <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="D30" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="E30" s="15" t="s">
         <v>158</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>159</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7"/>
@@ -4809,19 +4818,19 @@
     </row>
     <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="D31" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="E31" s="15" t="s">
         <v>163</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>164</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7"/>
@@ -4831,19 +4840,19 @@
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="C32" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>167</v>
-      </c>
       <c r="D32" s="8" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -4853,19 +4862,19 @@
     </row>
     <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="C33" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>170</v>
-      </c>
       <c r="D33" s="6" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -4875,13 +4884,13 @@
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>172</v>
-      </c>
       <c r="C34" s="15" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="16"/>
@@ -4893,13 +4902,13 @@
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="C35" s="15" t="s">
         <v>174</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>175</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="16"/>
@@ -4911,13 +4920,13 @@
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>481</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>482</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4929,13 +4938,13 @@
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -4947,13 +4956,13 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -4965,13 +4974,13 @@
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -4981,12 +4990,16 @@
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="16"/>
+        <v>179</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>523</v>
+      </c>
       <c r="D40" s="6"/>
       <c r="E40" s="16"/>
       <c r="F40" s="6"/>
@@ -4997,7 +5010,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="16"/>
@@ -5011,7 +5024,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="16"/>
@@ -5025,7 +5038,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="16"/>
@@ -5039,7 +5052,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="16"/>
@@ -5053,7 +5066,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="16"/>
@@ -5067,7 +5080,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="16"/>
@@ -5081,7 +5094,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="16"/>
@@ -5095,7 +5108,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="16"/>
@@ -5109,7 +5122,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="16"/>
@@ -5123,7 +5136,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="16"/>
@@ -5137,7 +5150,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="16"/>
@@ -5151,7 +5164,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="16"/>
@@ -5165,7 +5178,7 @@
     </row>
     <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B53" s="10"/>
       <c r="C53" s="17"/>
@@ -5201,215 +5214,215 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="52" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="C1" s="53" t="s">
         <v>195</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="D1" s="54" t="s">
         <v>196</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="E1" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="F1" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="G1" s="54" t="s">
+        <v>449</v>
+      </c>
+      <c r="H1" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G1" s="54" t="s">
-        <v>450</v>
-      </c>
-      <c r="H1" s="54" t="s">
+      <c r="I1" s="55" t="s">
         <v>200</v>
-      </c>
-      <c r="I1" s="55" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="47" t="s">
+        <v>358</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>522</v>
+      </c>
+      <c r="C2" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="B2" s="48" t="s">
-        <v>504</v>
-      </c>
-      <c r="C2" s="49" t="s">
+      <c r="D2" s="50" t="s">
         <v>203</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="E2" s="50" t="s">
         <v>204</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>205</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="H2" s="50" t="s">
         <v>207</v>
       </c>
-      <c r="H2" s="50" t="s">
+      <c r="I2" s="50" t="s">
         <v>208</v>
-      </c>
-      <c r="I2" s="50" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E3" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="F3" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="G3" s="42" t="s">
         <v>211</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="H3" s="42" t="s">
+        <v>324</v>
+      </c>
+      <c r="I3" s="42" t="s">
         <v>212</v>
-      </c>
-      <c r="H3" s="42" t="s">
-        <v>325</v>
-      </c>
-      <c r="I3" s="42" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="C4" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="D4" s="42" t="s">
+      <c r="E4" s="42" t="s">
         <v>216</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="F4" s="42" t="s">
+        <v>485</v>
+      </c>
+      <c r="G4" s="42" t="s">
         <v>217</v>
       </c>
-      <c r="F4" s="42" t="s">
-        <v>486</v>
-      </c>
-      <c r="G4" s="42" t="s">
+      <c r="H4" s="42" t="s">
         <v>218</v>
-      </c>
-      <c r="H4" s="42" t="s">
-        <v>219</v>
       </c>
       <c r="I4" s="45"/>
     </row>
     <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D5" s="42" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" s="42" t="s">
+      <c r="E5" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="F5" s="42" t="s">
         <v>222</v>
       </c>
-      <c r="F5" s="42" t="s">
-        <v>223</v>
-      </c>
       <c r="G5" s="42" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H5" s="42" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I5" s="45"/>
     </row>
     <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A6" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="C6" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" s="42" t="s">
         <v>225</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="D6" s="42" t="s">
+      <c r="E6" s="42" t="s">
         <v>226</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="F6" s="42" t="s">
         <v>227</v>
       </c>
-      <c r="F6" s="42" t="s">
-        <v>228</v>
-      </c>
       <c r="G6" s="42" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H6" s="42" t="s">
-        <v>501</v>
+        <v>525</v>
       </c>
       <c r="I6" s="45"/>
     </row>
     <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="B7" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="C7" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>328</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>363</v>
+      </c>
+      <c r="G7" s="42" t="s">
         <v>230</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>492</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>329</v>
-      </c>
-      <c r="F7" s="44" t="s">
-        <v>364</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>231</v>
       </c>
       <c r="H7" s="42"/>
       <c r="I7" s="45"/>
     </row>
     <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="B8" s="35" t="s">
         <v>232</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="C8" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" s="42" t="s">
         <v>233</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="D8" s="42" t="s">
+      <c r="E8" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="F8" s="42" t="s">
         <v>234</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>330</v>
-      </c>
-      <c r="F8" s="42" t="s">
-        <v>235</v>
       </c>
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
@@ -5417,22 +5430,22 @@
     </row>
     <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
+        <v>235</v>
+      </c>
+      <c r="B9" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="C9" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D9" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="C9" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="D9" s="42" t="s">
+      <c r="E9" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="F9" s="42" t="s">
         <v>239</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>240</v>
       </c>
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
@@ -5440,19 +5453,19 @@
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>241</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="C10" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>500</v>
+      </c>
+      <c r="E10" s="42" t="s">
         <v>242</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>502</v>
-      </c>
-      <c r="E10" s="42" t="s">
-        <v>243</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
@@ -5461,17 +5474,17 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="42" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
@@ -5480,17 +5493,17 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="B12" s="35" t="s">
-        <v>246</v>
-      </c>
       <c r="C12" s="38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D12" s="42"/>
       <c r="E12" s="42" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F12" s="44"/>
       <c r="G12" s="42"/>
@@ -5499,17 +5512,17 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="B13" s="35" t="s">
         <v>248</v>
       </c>
-      <c r="B13" s="35" t="s">
-        <v>249</v>
-      </c>
       <c r="C13" s="38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D13" s="42"/>
       <c r="E13" s="42" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F13" s="44"/>
       <c r="G13" s="42"/>
@@ -5518,17 +5531,17 @@
     </row>
     <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" s="35" t="s">
         <v>251</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="C14" s="38" t="s">
         <v>252</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>253</v>
       </c>
       <c r="D14" s="42"/>
       <c r="E14" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="42"/>
@@ -5537,13 +5550,13 @@
     </row>
     <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="B15" s="35" t="s">
-        <v>256</v>
-      </c>
       <c r="C15" s="38" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="42"/>
@@ -5554,13 +5567,13 @@
     </row>
     <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="B16" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="B16" s="35" t="s">
-        <v>258</v>
-      </c>
       <c r="C16" s="38" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D16" s="42"/>
       <c r="E16" s="42"/>
@@ -5571,13 +5584,13 @@
     </row>
     <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D17" s="42"/>
       <c r="E17" s="42"/>
@@ -5588,13 +5601,13 @@
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="C18" s="38" t="s">
         <v>260</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>261</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="42"/>
@@ -5605,13 +5618,13 @@
     </row>
     <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="B19" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="B19" s="35" t="s">
-        <v>263</v>
-      </c>
       <c r="C19" s="38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="42"/>
@@ -5622,13 +5635,13 @@
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="B20" s="35" t="s">
-        <v>265</v>
-      </c>
       <c r="C20" s="38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
@@ -5639,13 +5652,13 @@
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="B21" s="35" t="s">
         <v>478</v>
       </c>
-      <c r="B21" s="35" t="s">
-        <v>479</v>
-      </c>
       <c r="C21" s="38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
@@ -5656,13 +5669,13 @@
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -5673,13 +5686,13 @@
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D23" s="42"/>
       <c r="E23" s="42"/>
@@ -5690,13 +5703,13 @@
     </row>
     <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="42"/>
@@ -5707,13 +5720,13 @@
     </row>
     <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D25" s="43"/>
       <c r="E25" s="43"/>
@@ -5739,33 +5752,33 @@
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="72"/>
       <c r="B1" s="65" t="s">
+        <v>269</v>
+      </c>
+      <c r="C1" s="65" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="D1" s="64" t="s">
         <v>271</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="E1" s="64" t="s">
         <v>272</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="F1" s="64" t="s">
         <v>273</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="G1" s="64" t="s">
         <v>274</v>
       </c>
-      <c r="G1" s="64" t="s">
-        <v>275</v>
-      </c>
       <c r="I1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B2" s="75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C2" s="68" t="s">
         <v>92</v>
@@ -5774,21 +5787,21 @@
         <v>99</v>
       </c>
       <c r="E2" s="69" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F2" s="63" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G2" s="69" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="74" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B3" s="76" t="s">
         <v>47</v>
@@ -5800,21 +5813,21 @@
         <v>15</v>
       </c>
       <c r="E3" s="66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F3" s="63" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G3" s="66" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B4" s="67" t="s">
         <v>85</v>
@@ -5823,27 +5836,27 @@
         <v>57</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G4" s="66" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="74" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B5" s="73" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C5" s="73" t="s">
         <v>80</v>
@@ -5855,21 +5868,21 @@
         <v>75</v>
       </c>
       <c r="F5" s="70" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G5" s="71" t="s">
         <v>27</v>
       </c>
       <c r="I5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="97" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B6" s="98" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C6" s="99" t="s">
         <v>42</v>
@@ -5878,317 +5891,317 @@
         <v>94</v>
       </c>
       <c r="E6" s="101" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F6" s="100" t="s">
         <v>81</v>
       </c>
       <c r="G6" s="102" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="77" t="s">
+        <v>280</v>
+      </c>
+      <c r="B7" s="77" t="s">
         <v>281</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="C7" s="74" t="s">
+        <v>382</v>
+      </c>
+      <c r="D7" t="s">
         <v>282</v>
       </c>
-      <c r="C7" s="74" t="s">
-        <v>383</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" s="74" t="s">
         <v>283</v>
       </c>
-      <c r="E7" s="74" t="s">
+      <c r="F7" t="s">
         <v>284</v>
       </c>
-      <c r="F7" t="s">
-        <v>285</v>
-      </c>
       <c r="G7" s="74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="95" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B8" s="95" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="91" t="s">
         <v>273</v>
       </c>
-      <c r="C8" s="91" t="s">
+      <c r="D8" s="95" t="s">
         <v>274</v>
       </c>
-      <c r="D8" s="95" t="s">
-        <v>275</v>
-      </c>
       <c r="E8" s="91" t="s">
+        <v>269</v>
+      </c>
+      <c r="F8" s="95" t="s">
         <v>270</v>
       </c>
-      <c r="F8" s="95" t="s">
+      <c r="G8" s="92" t="s">
         <v>271</v>
       </c>
-      <c r="G8" s="92" t="s">
-        <v>272</v>
-      </c>
       <c r="I8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="63" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B9" s="63" t="s">
+        <v>273</v>
+      </c>
+      <c r="C9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D9" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="E9" t="s">
         <v>274</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F9" s="63" t="s">
+        <v>269</v>
+      </c>
+      <c r="G9" s="76" t="s">
         <v>272</v>
-      </c>
-      <c r="D9" s="63" t="s">
-        <v>271</v>
-      </c>
-      <c r="E9" t="s">
-        <v>275</v>
-      </c>
-      <c r="F9" s="63" t="s">
-        <v>270</v>
-      </c>
-      <c r="G9" s="76" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="96" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B10" s="96" t="s">
+        <v>271</v>
+      </c>
+      <c r="C10" s="93" t="s">
+        <v>274</v>
+      </c>
+      <c r="D10" s="96" t="s">
+        <v>269</v>
+      </c>
+      <c r="E10" s="93" t="s">
+        <v>273</v>
+      </c>
+      <c r="F10" s="96" t="s">
         <v>272</v>
       </c>
-      <c r="C10" s="93" t="s">
-        <v>275</v>
-      </c>
-      <c r="D10" s="96" t="s">
+      <c r="G10" s="94" t="s">
         <v>270</v>
-      </c>
-      <c r="E10" s="93" t="s">
-        <v>274</v>
-      </c>
-      <c r="F10" s="96" t="s">
-        <v>273</v>
-      </c>
-      <c r="G10" s="94" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -6196,111 +6209,111 @@
     </row>
     <row r="23" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="E24" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="345" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>409</v>
-      </c>
       <c r="D25" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>413</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="195" x14ac:dyDescent="0.25">
@@ -6308,133 +6321,133 @@
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="G30" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I30" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="G32" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="G33" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -6450,16 +6463,16 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -6467,74 +6480,74 @@
     </row>
     <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="G37" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I37" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I39" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -6542,14 +6555,14 @@
       <c r="B40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G40" s="2"/>
       <c r="I40" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -6589,165 +6602,165 @@
     </row>
     <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>433</v>
-      </c>
       <c r="G47" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>437</v>
-      </c>
       <c r="F49" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G50" s="2"/>
     </row>
     <row r="52" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E52" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="G52" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="G54" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="G55" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -6763,80 +6776,80 @@
     </row>
     <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E58" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>354</v>
-      </c>
       <c r="G58" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
@@ -6864,64 +6877,66 @@
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="32" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D1" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="E1" s="110" t="s">
         <v>202</v>
-      </c>
-      <c r="E1" s="109" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="31" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="E2" s="110"/>
+        <v>228</v>
+      </c>
+      <c r="E2" s="111"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3" s="30" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="E3" s="110"/>
+        <v>243</v>
+      </c>
+      <c r="E3" s="111"/>
     </row>
     <row r="4" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A4" s="34" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>257</v>
-      </c>
-      <c r="D4" s="34"/>
+        <v>256</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>502</v>
+      </c>
       <c r="E4" s="62" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -6948,44 +6963,46 @@
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="E1" s="111" t="s">
-        <v>261</v>
+        <v>263</v>
+      </c>
+      <c r="E1" s="112" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>257</v>
-      </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="112"/>
+        <v>256</v>
+      </c>
+      <c r="D2" s="109" t="s">
+        <v>502</v>
+      </c>
+      <c r="E2" s="113"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="57" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="114" t="s">
         <v>286</v>
       </c>
-      <c r="B3" s="113" t="s">
-        <v>287</v>
-      </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="115"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7055,20 +7072,20 @@
       <c r="A2" s="60">
         <v>39</v>
       </c>
-      <c r="B2" s="118" t="s">
-        <v>288</v>
-      </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
+      <c r="B2" s="119" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
       <c r="N2" s="60">
         <v>14</v>
       </c>
@@ -7077,18 +7094,18 @@
       <c r="A3" s="60">
         <v>38</v>
       </c>
-      <c r="B3" s="120"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
+      <c r="B3" s="121"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="122"/>
       <c r="N3" s="60">
         <v>15</v>
       </c>
@@ -7097,20 +7114,20 @@
       <c r="A4" s="60">
         <v>37</v>
       </c>
-      <c r="B4" s="116" t="s">
-        <v>289</v>
-      </c>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117"/>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
+      <c r="B4" s="117" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="K4" s="118"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
       <c r="N4" s="60">
         <v>16</v>
       </c>
@@ -7119,30 +7136,30 @@
       <c r="A5" s="60">
         <v>36</v>
       </c>
-      <c r="B5" s="122" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="123"/>
-      <c r="D5" s="126" t="s">
-        <v>290</v>
-      </c>
-      <c r="E5" s="127"/>
-      <c r="F5" s="126" t="s">
-        <v>290</v>
-      </c>
-      <c r="G5" s="127"/>
-      <c r="H5" s="126" t="s">
-        <v>290</v>
-      </c>
-      <c r="I5" s="127"/>
-      <c r="J5" s="126" t="s">
-        <v>290</v>
-      </c>
-      <c r="K5" s="127"/>
-      <c r="L5" s="126" t="s">
-        <v>290</v>
-      </c>
-      <c r="M5" s="130"/>
+      <c r="B5" s="123" t="s">
+        <v>289</v>
+      </c>
+      <c r="C5" s="124"/>
+      <c r="D5" s="127" t="s">
+        <v>289</v>
+      </c>
+      <c r="E5" s="128"/>
+      <c r="F5" s="127" t="s">
+        <v>289</v>
+      </c>
+      <c r="G5" s="128"/>
+      <c r="H5" s="127" t="s">
+        <v>289</v>
+      </c>
+      <c r="I5" s="128"/>
+      <c r="J5" s="127" t="s">
+        <v>289</v>
+      </c>
+      <c r="K5" s="128"/>
+      <c r="L5" s="127" t="s">
+        <v>289</v>
+      </c>
+      <c r="M5" s="131"/>
       <c r="N5" s="60">
         <v>17</v>
       </c>
@@ -7151,18 +7168,18 @@
       <c r="A6" s="60">
         <v>35</v>
       </c>
-      <c r="B6" s="122"/>
-      <c r="C6" s="123"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="128"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="128"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="128"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="123"/>
+      <c r="B6" s="123"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="123"/>
+      <c r="K6" s="129"/>
+      <c r="L6" s="123"/>
+      <c r="M6" s="124"/>
       <c r="N6" s="60">
         <v>18</v>
       </c>
@@ -7171,18 +7188,18 @@
       <c r="A7" s="60">
         <v>34</v>
       </c>
-      <c r="B7" s="124"/>
-      <c r="C7" s="125"/>
-      <c r="D7" s="124"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="124"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="124"/>
-      <c r="M7" s="125"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="130"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="125"/>
+      <c r="M7" s="126"/>
       <c r="N7" s="60">
         <v>19</v>
       </c>
@@ -7608,7 +7625,7 @@
       </c>
       <c r="P2" s="104" t="str">
         <f>Cards!C17</f>
-        <v>You may repeat Court Actions with level 7 - $L6 Leaders</v>
+        <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
       </c>
       <c r="Q2" s="103" t="str">
         <f>Cards!C18</f>
@@ -7748,7 +7765,7 @@
       </c>
       <c r="AY2" s="104" t="str">
         <f t="shared" si="1"/>
-        <v>You may repeat Court Actions with level 7 - $L6 Leaders</v>
+        <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
       </c>
       <c r="AZ2" s="103" t="str">
         <f t="shared" si="1"/>
@@ -8781,31 +8798,31 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1" t="s">
         <v>310</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>311</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>312</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>313</v>
-      </c>
-      <c r="F1" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D2">
         <v>27.7</v>
@@ -8813,14 +8830,14 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D3">
         <v>27.7</v>
@@ -8828,14 +8845,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D4">
         <v>30.75</v>
@@ -8843,222 +8860,222 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E6" t="s">
         <v>316</v>
-      </c>
-      <c r="E6" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>315</v>
+      </c>
+      <c r="E10" t="s">
         <v>316</v>
-      </c>
-      <c r="E10" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
+        <v>315</v>
+      </c>
+      <c r="E11" t="s">
         <v>316</v>
-      </c>
-      <c r="E11" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -9080,7 +9097,7 @@
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" style="108" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.42578125" style="108" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="108" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" style="108" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="11.85546875" style="108" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.85546875" style="108" bestFit="1" customWidth="1"/>
@@ -9089,67 +9106,67 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B1" t="s">
         <v>459</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>460</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>461</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>462</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>489</v>
+      </c>
+      <c r="G1" t="s">
+        <v>488</v>
+      </c>
+      <c r="H1" t="s">
         <v>463</v>
       </c>
-      <c r="F1" t="s">
-        <v>490</v>
-      </c>
-      <c r="G1" t="s">
-        <v>489</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>464</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" s="108" t="s">
+        <v>486</v>
+      </c>
+      <c r="K1" t="s">
         <v>465</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>466</v>
+      </c>
+      <c r="M1" t="s">
+        <v>467</v>
+      </c>
+      <c r="N1" t="s">
+        <v>468</v>
+      </c>
+      <c r="O1" t="s">
+        <v>469</v>
+      </c>
+      <c r="P1" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>471</v>
+      </c>
+      <c r="R1" t="s">
+        <v>472</v>
+      </c>
+      <c r="S1" t="s">
+        <v>473</v>
+      </c>
+      <c r="T1" t="s">
+        <v>474</v>
+      </c>
+      <c r="U1" t="s">
         <v>487</v>
-      </c>
-      <c r="K1" t="s">
-        <v>466</v>
-      </c>
-      <c r="L1" t="s">
-        <v>467</v>
-      </c>
-      <c r="M1" t="s">
-        <v>468</v>
-      </c>
-      <c r="N1" t="s">
-        <v>469</v>
-      </c>
-      <c r="O1" t="s">
-        <v>470</v>
-      </c>
-      <c r="P1" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>472</v>
-      </c>
-      <c r="R1" t="s">
-        <v>473</v>
-      </c>
-      <c r="S1" t="s">
-        <v>474</v>
-      </c>
-      <c r="T1" t="s">
-        <v>475</v>
-      </c>
-      <c r="U1" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -9253,11 +9270,53 @@
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="106">
+        <v>46105</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
       <c r="C4" s="107" t="b">
         <v>0</v>
       </c>
       <c r="D4" s="107" t="b">
         <v>0</v>
+      </c>
+      <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>17</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4" s="108">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="I4" s="108">
+        <v>0.92777777777777781</v>
+      </c>
+      <c r="J4" s="108">
+        <v>0.78472222222222221</v>
+      </c>
+      <c r="K4" s="108">
+        <v>0.79236111111111107</v>
+      </c>
+      <c r="L4" s="108">
+        <v>0.81111111111111112</v>
+      </c>
+      <c r="M4" s="108">
+        <v>0.83194444444444449</v>
+      </c>
+      <c r="N4" s="108">
+        <v>0.85277777777777775</v>
+      </c>
+      <c r="O4" s="108">
+        <v>0.88263888888888886</v>
+      </c>
+      <c r="P4" s="108">
+        <v>0.92083333333333328</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3436" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37185AFA-472E-4E99-AEE5-A6FF8A9012A1}"/>
+  <xr:revisionPtr revIDLastSave="3573" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE269E95-B60B-4888-B96D-B58BAF152290}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="525">
   <si>
     <t>Standard Card</t>
   </si>
@@ -85,9 +85,6 @@
     <t>Fickle Mercenaries</t>
   </si>
   <si>
-    <t>Give $D6 Troops to Player $R</t>
-  </si>
-  <si>
     <t>2H</t>
   </si>
   <si>
@@ -103,9 +100,6 @@
     <t>Blatant Thievery</t>
   </si>
   <si>
-    <t>Give $D6 Coins to Player $R</t>
-  </si>
-  <si>
     <t>3H</t>
   </si>
   <si>
@@ -121,9 +115,6 @@
     <t>Double Agents</t>
   </si>
   <si>
-    <t>Give $D6 Spies to Player $R</t>
-  </si>
-  <si>
     <t>4H</t>
   </si>
   <si>
@@ -139,9 +130,6 @@
     <t>Questionable Reallocation</t>
   </si>
   <si>
-    <t>Give $D6 Commodities to Player $R</t>
-  </si>
-  <si>
     <t>5H</t>
   </si>
   <si>
@@ -160,9 +148,6 @@
     <t>Blackmail</t>
   </si>
   <si>
-    <t>Give the King's Favor to Player $R</t>
-  </si>
-  <si>
     <t>6H</t>
   </si>
   <si>
@@ -181,9 +166,6 @@
     <t>Invalid Paperwork</t>
   </si>
   <si>
-    <t>Player $R may peek at the Law card at the top of the queue &amp; put it on the bottom of the queue if they want</t>
-  </si>
-  <si>
     <t>7H</t>
   </si>
   <si>
@@ -196,9 +178,6 @@
     <t>Insider Trading</t>
   </si>
   <si>
-    <t>Give $D6 random Cards from your hand to Player $R</t>
-  </si>
-  <si>
     <t>8H</t>
   </si>
   <si>
@@ -226,9 +205,6 @@
     <t>Dangerous Monopolies</t>
   </si>
   <si>
-    <t>Destroy an Investment at level $D6</t>
-  </si>
-  <si>
     <t>10H</t>
   </si>
   <si>
@@ -244,9 +220,6 @@
     <t>Corporate Takeover</t>
   </si>
   <si>
-    <t>Send an Investment at level $D6 to Player $R</t>
-  </si>
-  <si>
     <t>JH</t>
   </si>
   <si>
@@ -265,9 +238,6 @@
     <t>Sabotage</t>
   </si>
   <si>
-    <t>Downgrade an Investment at level $D6</t>
-  </si>
-  <si>
     <t>QH</t>
   </si>
   <si>
@@ -295,9 +265,6 @@
     <t>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</t>
   </si>
   <si>
-    <t>Kill a Leader at level $D6</t>
-  </si>
-  <si>
     <t>AS</t>
   </si>
   <si>
@@ -316,9 +283,6 @@
     <t>Betrayal</t>
   </si>
   <si>
-    <t>Send a Leader at level $D6 to Player $R</t>
-  </si>
-  <si>
     <t>2S</t>
   </si>
   <si>
@@ -334,12 +298,6 @@
     <t>Each Player must have at least $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</t>
   </si>
   <si>
-    <t>Intimidate</t>
-  </si>
-  <si>
-    <t>Demote a Leader at level $D6</t>
-  </si>
-  <si>
     <t>3S</t>
   </si>
   <si>
@@ -352,9 +310,6 @@
     <t>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</t>
   </si>
   <si>
-    <t>Humiliate</t>
-  </si>
-  <si>
     <t>4S</t>
   </si>
   <si>
@@ -490,9 +445,6 @@
     <t>Wary Guards</t>
   </si>
   <si>
-    <t>Subtract $L3 from Scheme Guard rolls</t>
-  </si>
-  <si>
     <t>Engaged Empire</t>
   </si>
   <si>
@@ -670,9 +622,6 @@
     <t xml:space="preserve">Give 1 Honor to the player with the most Troops deployed. Break ties in favor of player who deployed first. </t>
   </si>
   <si>
-    <t>Target Player rolls a die. If the result is higher than half their Troops, the Scheme is executed. Otherwise, the Scheme fails. (Scheme Guard Roll)</t>
-  </si>
-  <si>
     <t>Generate Greek army (12 per player)</t>
   </si>
   <si>
@@ -1516,9 +1465,6 @@
     <t>Highest Score</t>
   </si>
   <si>
-    <t>Rearrange $D3 Law cards from the top of the queue</t>
-  </si>
-  <si>
     <t>Ratify deliberated Law and set value of next deliberated Law</t>
   </si>
   <si>
@@ -1534,9 +1480,6 @@
     <t>Assassination</t>
   </si>
   <si>
-    <t>Exchange a random held Alliance Token, or one of your own if you hold none, with one of the choice of Player $R</t>
-  </si>
-  <si>
     <t>Courtroom Gambling</t>
   </si>
   <si>
@@ -1585,12 +1528,6 @@
     <t>Quality Strength</t>
   </si>
   <si>
-    <t>Move one of your Laws $D6 spaces back in the Queue</t>
-  </si>
-  <si>
-    <t>Move $D6 of your Laws one space back in the Queue</t>
-  </si>
-  <si>
     <t>Rallied Opposition</t>
   </si>
   <si>
@@ -1622,6 +1559,66 @@
   </si>
   <si>
     <t>If Greeks are victorious, give remaining attacking Greeks to the player who deployed the fewest Troops (break ties with deployment order then with a Tie Trial or agreement). That player destroys 1 Troop per attacking Greek or downgrades 1 investment by $D6 levels if they have no Troops.</t>
+  </si>
+  <si>
+    <t>Exchange one Alliance Token with $R</t>
+  </si>
+  <si>
+    <t>Give $D6 Spies to $R</t>
+  </si>
+  <si>
+    <t>Give $2D6 Troops to $R</t>
+  </si>
+  <si>
+    <t>Move your foremost Law to the back of the Queue</t>
+  </si>
+  <si>
+    <t>Give $D6 random Cards of each type from your hand to $R</t>
+  </si>
+  <si>
+    <t>Rearrange the first $D6 Law cards in the Queue</t>
+  </si>
+  <si>
+    <t>Downgrade an Investment by $D6 levels</t>
+  </si>
+  <si>
+    <t>Downgrade an Investment at level $D6 by half and send it to $R</t>
+  </si>
+  <si>
+    <t>Demote a Leader by $D6 levels</t>
+  </si>
+  <si>
+    <t>Demote a Leader at level $D6 by half and send it to $R</t>
+  </si>
+  <si>
+    <t>Move your foremost Law $D6 spaces back in the Queue</t>
+  </si>
+  <si>
+    <t>Move $D6 of your Laws each one space back in the Queue</t>
+  </si>
+  <si>
+    <t>Intimidation</t>
+  </si>
+  <si>
+    <t>Humiliation</t>
+  </si>
+  <si>
+    <t>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</t>
+  </si>
+  <si>
+    <t>Give $2D6 Commodities to $R. Perform an Emergency Trade if needed.</t>
+  </si>
+  <si>
+    <t>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</t>
+  </si>
+  <si>
+    <t>Misaligned Strategy</t>
+  </si>
+  <si>
+    <t>Target Player rolls a die. If the result is a 6 or is higher than half their Troops, the Scheme is executed. Otherwise, the Scheme fails. (Scheme Guard Roll)</t>
+  </si>
+  <si>
+    <t>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</t>
   </si>
 </sst>
 </file>
@@ -2546,7 +2543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2894,6 +2891,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4122,7 +4122,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>13</v>
+        <v>507</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
@@ -4130,25 +4130,25 @@
     </row>
     <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>18</v>
-      </c>
       <c r="G3" s="7" t="s">
-        <v>19</v>
+        <v>519</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
@@ -4156,25 +4156,25 @@
     </row>
     <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="E4" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="G4" s="7" t="s">
-        <v>25</v>
+        <v>506</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="3"/>
@@ -4182,25 +4182,25 @@
     </row>
     <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="E5" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="G5" s="7" t="s">
-        <v>31</v>
+        <v>520</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
@@ -4208,25 +4208,25 @@
     </row>
     <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>38</v>
+      <c r="G6" s="7" t="s">
+        <v>521</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3"/>
@@ -4234,25 +4234,25 @@
     </row>
     <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="G7" s="7" t="s">
-        <v>45</v>
+        <v>508</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3"/>
@@ -4260,25 +4260,25 @@
     </row>
     <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>50</v>
+        <v>509</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
@@ -4286,25 +4286,25 @@
     </row>
     <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
@@ -4312,25 +4312,25 @@
     </row>
     <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>60</v>
+        <v>511</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
@@ -4338,25 +4338,25 @@
     </row>
     <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>66</v>
+        <v>512</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="2"/>
@@ -4364,25 +4364,25 @@
     </row>
     <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>73</v>
+        <v>511</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="2"/>
@@ -4390,25 +4390,25 @@
     </row>
     <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>73</v>
+        <v>511</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
@@ -4416,25 +4416,25 @@
     </row>
     <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>83</v>
+        <v>513</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
@@ -4442,25 +4442,25 @@
     </row>
     <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>90</v>
+        <v>514</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3"/>
@@ -4468,25 +4468,25 @@
     </row>
     <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>96</v>
+        <v>517</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>97</v>
+        <v>513</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="2"/>
@@ -4494,51 +4494,51 @@
     </row>
     <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>102</v>
+        <v>518</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>97</v>
+        <v>513</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="2"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
@@ -4546,25 +4546,25 @@
     </row>
     <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="F19" s="23" t="s">
+        <v>494</v>
+      </c>
+      <c r="G19" s="25" t="s">
         <v>515</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>513</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
@@ -4572,25 +4572,25 @@
     </row>
     <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F20" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>516</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>514</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
@@ -4598,41 +4598,45 @@
     </row>
     <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="F21" s="6"/>
-      <c r="G21" s="7"/>
+        <v>106</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>515</v>
+      </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
     </row>
     <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="7"/>
@@ -4642,19 +4646,19 @@
     </row>
     <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="9"/>
@@ -4664,19 +4668,19 @@
     </row>
     <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="7"/>
@@ -4686,19 +4690,19 @@
     </row>
     <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
@@ -4708,19 +4712,19 @@
     </row>
     <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4730,19 +4734,19 @@
     </row>
     <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4752,19 +4756,19 @@
     </row>
     <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>148</v>
+        <v>132</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>524</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>517</v>
+        <v>496</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4774,19 +4778,19 @@
     </row>
     <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>518</v>
+        <v>497</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4796,19 +4800,19 @@
     </row>
     <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7"/>
@@ -4818,19 +4822,19 @@
     </row>
     <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7"/>
@@ -4840,19 +4844,19 @@
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -4862,19 +4866,19 @@
     </row>
     <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -4884,13 +4888,13 @@
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="16"/>
@@ -4902,13 +4906,13 @@
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="16"/>
@@ -4920,13 +4924,13 @@
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4938,13 +4942,13 @@
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>498</v>
+        <v>479</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -4956,13 +4960,13 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -4974,13 +4978,13 @@
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -4992,13 +4996,13 @@
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>524</v>
+        <v>503</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="16"/>
@@ -5010,7 +5014,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="16"/>
@@ -5024,7 +5028,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="16"/>
@@ -5038,7 +5042,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="16"/>
@@ -5052,7 +5056,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="16"/>
@@ -5066,7 +5070,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="16"/>
@@ -5080,7 +5084,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="16"/>
@@ -5094,7 +5098,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="16"/>
@@ -5108,7 +5112,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="16"/>
@@ -5122,7 +5126,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="16"/>
@@ -5136,7 +5140,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="16"/>
@@ -5150,7 +5154,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="16"/>
@@ -5164,7 +5168,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="16"/>
@@ -5178,7 +5182,7 @@
     </row>
     <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="B53" s="10"/>
       <c r="C53" s="17"/>
@@ -5214,215 +5218,215 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="51" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="B1" s="52" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="D1" s="54" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="E1" s="54" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F1" s="54" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="G1" s="54" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="H1" s="54" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="I1" s="55" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="47" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="E2" s="50" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F2" s="50" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="G2" s="50" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="H2" s="50" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>208</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="F3" s="42" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="G3" s="42" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="H3" s="42" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="I3" s="42" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D4" s="42" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="G4" s="42" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="H4" s="42" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="I4" s="45"/>
     </row>
     <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="G5" s="42" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="H5" s="42" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="I5" s="45"/>
     </row>
     <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A6" s="37" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="F6" s="42" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="H6" s="42" t="s">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="I6" s="45"/>
     </row>
     <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="H7" s="42"/>
       <c r="I7" s="45"/>
     </row>
     <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
@@ -5430,22 +5434,22 @@
     </row>
     <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
@@ -5453,19 +5457,19 @@
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
@@ -5474,17 +5478,17 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="42" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
@@ -5493,17 +5497,17 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D12" s="42"/>
       <c r="E12" s="42" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="F12" s="44"/>
       <c r="G12" s="42"/>
@@ -5512,17 +5516,17 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="D13" s="42"/>
       <c r="E13" s="42" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="F13" s="44"/>
       <c r="G13" s="42"/>
@@ -5531,17 +5535,17 @@
     </row>
     <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D14" s="42"/>
       <c r="E14" s="42" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="42"/>
@@ -5550,13 +5554,13 @@
     </row>
     <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="42"/>
@@ -5567,13 +5571,13 @@
     </row>
     <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D16" s="42"/>
       <c r="E16" s="42"/>
@@ -5584,13 +5588,13 @@
     </row>
     <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D17" s="42"/>
       <c r="E17" s="42"/>
@@ -5601,13 +5605,13 @@
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="42"/>
@@ -5618,13 +5622,13 @@
     </row>
     <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="42"/>
@@ -5635,13 +5639,13 @@
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
@@ -5652,13 +5656,13 @@
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
@@ -5669,13 +5673,13 @@
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -5686,13 +5690,13 @@
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D23" s="42"/>
       <c r="E23" s="42"/>
@@ -5703,13 +5707,13 @@
     </row>
     <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="42"/>
@@ -5720,13 +5724,13 @@
     </row>
     <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>503</v>
+        <v>484</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="D25" s="43"/>
       <c r="E25" s="43"/>
@@ -5752,456 +5756,456 @@
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="72"/>
       <c r="B1" s="65" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="C1" s="65" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="D1" s="64" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="E1" s="64" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="F1" s="64" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="G1" s="64" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="I1" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="B2" s="75" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C2" s="68" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D2" s="69" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E2" s="69" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F2" s="63" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G2" s="69" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="I2" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="74" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="B3" s="76" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C3" s="67" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="66" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="F3" s="63" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="G3" s="66" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="I3" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="B4" s="67" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C4" s="67" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="E4" s="66" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="G4" s="66" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="I4" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="74" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="B5" s="73" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D5" s="70" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" s="70" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F5" s="70" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="G5" s="71" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="97" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="B6" s="98" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C6" s="99" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D6" s="100" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E6" s="101" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="F6" s="100" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G6" s="102" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="I6" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="77" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="B7" s="77" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="C7" s="74" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="D7" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="E7" s="74" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="F7" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="G7" s="74" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="I7" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="95" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="B8" s="95" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="C8" s="91" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="D8" s="95" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="E8" s="91" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="F8" s="95" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="G8" s="92" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="I8" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="63" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="B9" s="63" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="C9" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="D9" s="63" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="E9" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="F9" s="63" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="G9" s="76" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="96" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="B10" s="96" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C10" s="93" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="D10" s="96" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="E10" s="93" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="F10" s="96" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="G10" s="94" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="2" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -6209,111 +6213,111 @@
     </row>
     <row r="23" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="2" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="345" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="195" x14ac:dyDescent="0.25">
@@ -6321,133 +6325,133 @@
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="I30" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="2" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="2" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -6463,16 +6467,16 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
@@ -6480,74 +6484,74 @@
     </row>
     <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="I37" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="2" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="I38" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="2" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="I39" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -6555,14 +6559,14 @@
       <c r="B40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="G40" s="2"/>
       <c r="I40" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -6602,165 +6606,165 @@
     </row>
     <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>240</v>
-      </c>
       <c r="F50" s="2" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="G50" s="2"/>
     </row>
     <row r="52" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -6776,80 +6780,80 @@
     </row>
     <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="2" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
@@ -6877,66 +6881,66 @@
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="32" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="E1" s="110" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="31" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="E2" s="111"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3" s="30" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="E3" s="111"/>
     </row>
     <row r="4" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A4" s="34" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="E4" s="62" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -6963,42 +6967,42 @@
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="E1" s="112" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="D2" s="109" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="E2" s="113"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="57" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B3" s="114" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="C3" s="115"/>
       <c r="D3" s="115"/>
@@ -7073,7 +7077,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="119" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="C2" s="120"/>
       <c r="D2" s="120"/>
@@ -7115,7 +7119,7 @@
         <v>37</v>
       </c>
       <c r="B4" s="117" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C4" s="118"/>
       <c r="D4" s="118"/>
@@ -7137,27 +7141,27 @@
         <v>36</v>
       </c>
       <c r="B5" s="123" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="C5" s="124"/>
       <c r="D5" s="127" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="E5" s="128"/>
       <c r="F5" s="127" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="G5" s="128"/>
       <c r="H5" s="127" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="I5" s="128"/>
       <c r="J5" s="127" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="K5" s="128"/>
       <c r="L5" s="127" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="M5" s="131"/>
       <c r="N5" s="60">
@@ -7265,7 +7269,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CEB427C-0CB4-4E8D-8367-36F6DD891282}">
-  <dimension ref="A1:BI6"/>
+  <dimension ref="A1:BS6"/>
   <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" style="63"/>
@@ -7314,9 +7318,14 @@
     <col min="59" max="59" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
     <col min="60" max="60" width="19.7109375" style="82" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="19.7109375" style="63"/>
+    <col min="63" max="63" width="19.7109375" style="63"/>
+    <col min="65" max="65" width="19.7109375" style="63"/>
+    <col min="67" max="67" width="19.7109375" style="63"/>
+    <col min="69" max="69" width="19.7109375" style="63"/>
+    <col min="71" max="71" width="19.7109375" style="63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:61" s="80" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:71" s="80" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="78" t="str">
         <f>Cards!B2</f>
         <v>Fillibuster</v>
@@ -7458,111 +7467,141 @@
         <v>Fire Temple</v>
       </c>
       <c r="AJ1" s="78" t="str">
-        <f t="shared" ref="AJ1:AS2" si="0">A1</f>
+        <f>Cards!B37</f>
+        <v>Kingdom Advocates</v>
+      </c>
+      <c r="AK1" s="80" t="str">
+        <f>Cards!B38</f>
+        <v>Soup Kitchens</v>
+      </c>
+      <c r="AL1" s="78" t="str">
+        <f>Cards!B39</f>
+        <v>Abusive Power</v>
+      </c>
+      <c r="AM1" s="80" t="str">
+        <f>Cards!B40</f>
+        <v>Painful Progress</v>
+      </c>
+      <c r="AN1" s="78" t="str">
+        <f t="shared" ref="AN1:AW2" si="0">A1</f>
         <v>Fillibuster</v>
       </c>
-      <c r="AK1" s="80" t="str">
+      <c r="AO1" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Skillful Orators</v>
       </c>
-      <c r="AL1" s="78" t="str">
+      <c r="AP1" s="78" t="str">
         <f t="shared" si="0"/>
         <v>Collection Stations</v>
       </c>
-      <c r="AM1" s="80" t="str">
+      <c r="AQ1" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Brown Nose</v>
       </c>
-      <c r="AN1" s="78" t="str">
+      <c r="AR1" s="78" t="str">
         <f t="shared" si="0"/>
         <v>Mysterious Windfalls</v>
       </c>
-      <c r="AO1" s="80" t="str">
+      <c r="AS1" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Lobbyists</v>
       </c>
-      <c r="AP1" s="78" t="str">
+      <c r="AT1" s="78" t="str">
         <f t="shared" si="0"/>
         <v>Eager Youth</v>
       </c>
-      <c r="AQ1" s="80" t="str">
+      <c r="AU1" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Honorable Cause</v>
       </c>
-      <c r="AR1" s="78" t="str">
+      <c r="AV1" s="78" t="str">
         <f t="shared" si="0"/>
         <v>Loyal Citizenry</v>
       </c>
-      <c r="AS1" s="80" t="str">
+      <c r="AW1" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Silvertounge</v>
       </c>
-      <c r="AT1" s="78" t="str">
-        <f t="shared" ref="AT1:BC2" si="1">K1</f>
+      <c r="AX1" s="81" t="str">
+        <f t="shared" ref="AX1:BG2" si="1">K1</f>
         <v>Royal Bribes</v>
       </c>
-      <c r="AU1" s="80" t="str">
+      <c r="AY1" s="78" t="str">
         <f t="shared" si="1"/>
         <v>Courtroom Gambling</v>
       </c>
-      <c r="AV1" s="78" t="str">
+      <c r="AZ1" s="80" t="str">
         <f t="shared" si="1"/>
         <v>Market Niche</v>
       </c>
-      <c r="AW1" s="80" t="str">
+      <c r="BA1" s="78" t="str">
         <f t="shared" si="1"/>
         <v>Genius Commanders</v>
       </c>
-      <c r="AX1" s="81" t="str">
+      <c r="BB1" s="80" t="str">
         <f t="shared" si="1"/>
         <v>Damage Redemption</v>
       </c>
-      <c r="AY1" s="78" t="str">
+      <c r="BC1" s="78" t="str">
         <f t="shared" si="1"/>
         <v>Undeniable Advisors</v>
       </c>
-      <c r="AZ1" s="80" t="str">
+      <c r="BD1" s="80" t="str">
         <f t="shared" si="1"/>
         <v>Heavy Overtime</v>
       </c>
-      <c r="BA1" s="78" t="str">
+      <c r="BE1" s="78" t="str">
         <f t="shared" si="1"/>
         <v>Bulk Purchaser</v>
       </c>
-      <c r="BB1" s="80" t="str">
+      <c r="BF1" s="80" t="str">
         <f t="shared" si="1"/>
         <v>Valuable Cargo</v>
       </c>
-      <c r="BC1" s="78" t="str">
+      <c r="BG1" s="78" t="str">
         <f t="shared" si="1"/>
         <v>Elite Troops</v>
       </c>
-      <c r="BD1" s="80" t="str">
-        <f t="shared" ref="BD1:BI2" si="2">U1</f>
+      <c r="BH1" s="81" t="str">
+        <f t="shared" ref="BH1:BQ2" si="2">U1</f>
         <v>Bazaar</v>
       </c>
-      <c r="BE1" s="78" t="str">
+      <c r="BI1" s="78" t="str">
         <f t="shared" si="2"/>
         <v>Caravansaray</v>
       </c>
-      <c r="BF1" s="80" t="str">
+      <c r="BJ1" s="80" t="str">
         <f t="shared" si="2"/>
         <v>War Machines</v>
       </c>
-      <c r="BG1" s="78" t="str">
+      <c r="BK1" s="78" t="str">
         <f t="shared" si="2"/>
         <v>Mock Trials</v>
       </c>
-      <c r="BH1" s="81" t="str">
+      <c r="BL1" s="80" t="str">
         <f t="shared" si="2"/>
         <v>Desperate Attorneys</v>
       </c>
-      <c r="BI1" s="78" t="str">
+      <c r="BM1" s="78" t="str">
         <f t="shared" si="2"/>
         <v>Eager Laborers</v>
       </c>
-    </row>
-    <row r="2" spans="1:61" s="103" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BN1" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>Wary Guards</v>
+      </c>
+      <c r="BO1" s="78" t="str">
+        <f t="shared" si="2"/>
+        <v>Information Security</v>
+      </c>
+      <c r="BP1" s="80" t="str">
+        <f t="shared" si="2"/>
+        <v>Blood Pact</v>
+      </c>
+      <c r="BQ1" s="78"/>
+      <c r="BS1" s="78"/>
+    </row>
+    <row r="2" spans="1:71" s="103" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="104" t="str">
         <f>Cards!C2</f>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
@@ -7669,7 +7708,7 @@
       </c>
       <c r="AA2" s="103" t="str">
         <f>Cards!C28</f>
-        <v>Subtract $L3 from Scheme Guard rolls</v>
+        <v>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</v>
       </c>
       <c r="AB2" s="104" t="str">
         <f>Cards!C29</f>
@@ -7704,111 +7743,141 @@
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
       </c>
       <c r="AJ2" s="104" t="str">
+        <f>Cards!C37</f>
+        <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
+      </c>
+      <c r="AK2" s="103" t="str">
+        <f>Cards!C38</f>
+        <v>Convert $L3 additional Coins during Court Donate</v>
+      </c>
+      <c r="AL2" s="104" t="str">
+        <f>Cards!C39</f>
+        <v>Convert $L3 additional Coins during Undermarket Donate</v>
+      </c>
+      <c r="AM2" s="103" t="str">
+        <f>Cards!C40</f>
+        <v>You may repeat Undermarket Actions at double the penalty</v>
+      </c>
+      <c r="AN2" s="104" t="str">
         <f t="shared" si="0"/>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
       </c>
-      <c r="AK2" s="103" t="str">
+      <c r="AO2" s="103" t="str">
         <f t="shared" si="0"/>
         <v>Move the Law $L6 additional places forward in the queue during Prioritize</v>
       </c>
-      <c r="AL2" s="104" t="str">
+      <c r="AP2" s="104" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">You may gain up to $L6 additional Coins when Taxing other Players </v>
       </c>
-      <c r="AM2" s="103" t="str">
+      <c r="AQ2" s="103" t="str">
         <f t="shared" si="0"/>
         <v>Gain $L3 additional Coins during Flatter</v>
       </c>
-      <c r="AN2" s="104" t="str">
+      <c r="AR2" s="104" t="str">
         <f t="shared" si="0"/>
         <v>Gain $L3 more Commodities per Coin when Buying from the Undermarket</v>
       </c>
-      <c r="AO2" s="103" t="str">
+      <c r="AS2" s="103" t="str">
         <f t="shared" si="0"/>
         <v>Add $L3 additional Law cards to the bottom of the queue during Petition</v>
       </c>
-      <c r="AP2" s="104" t="str">
+      <c r="AT2" s="104" t="str">
         <f t="shared" si="0"/>
         <v>Gain 1 additional Troop for free after Recruiting every 4 - $L3 Troops</v>
       </c>
-      <c r="AQ2" s="103" t="str">
+      <c r="AU2" s="103" t="str">
         <f t="shared" si="0"/>
         <v>Gain 1 additional Spy for free after Infiltrating every 4 - $L3 Spies</v>
       </c>
-      <c r="AR2" s="104" t="str">
+      <c r="AV2" s="104" t="str">
         <f t="shared" si="0"/>
         <v>Purchase up to $L6 additional Troops during Recruit</v>
       </c>
-      <c r="AS2" s="103" t="str">
+      <c r="AW2" s="103" t="str">
         <f t="shared" si="0"/>
         <v>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</v>
       </c>
-      <c r="AT2" s="104" t="str">
+      <c r="AX2" s="105" t="str">
         <f t="shared" si="1"/>
         <v>Gain $L3 more Commodities per Coin when Buying from the Court</v>
       </c>
-      <c r="AU2" s="103" t="str">
+      <c r="AY2" s="104" t="str">
         <f t="shared" si="1"/>
         <v>Gain $L3 additional Coins from outside the Royal Bank when winning a Sue</v>
       </c>
-      <c r="AV2" s="104" t="str">
+      <c r="AZ2" s="103" t="str">
         <f t="shared" si="1"/>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Undermarket</v>
       </c>
-      <c r="AW2" s="103" t="str">
+      <c r="BA2" s="104" t="str">
         <f t="shared" si="1"/>
         <v>Draw $L6 additional cards from any decks during Brainstorm</v>
       </c>
-      <c r="AX2" s="105" t="str">
+      <c r="BB2" s="103" t="str">
         <f t="shared" si="1"/>
         <v>Purchase $L3 Spies (at normal cost) when targeted by a Scheme</v>
       </c>
-      <c r="AY2" s="104" t="str">
+      <c r="BC2" s="104" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
       </c>
-      <c r="AZ2" s="103" t="str">
+      <c r="BD2" s="103" t="str">
         <f t="shared" si="1"/>
         <v>You may repeat $L3 Provincial Actions per round</v>
       </c>
-      <c r="BA2" s="104" t="str">
+      <c r="BE2" s="104" t="str">
         <f t="shared" si="1"/>
         <v>Trade up to $L3 additional Coins when Buying from the Court</v>
       </c>
-      <c r="BB2" s="103" t="str">
+      <c r="BF2" s="103" t="str">
         <f t="shared" si="1"/>
         <v>Trade for up to $L3 additional Coins when Selling to the Court</v>
       </c>
-      <c r="BC2" s="104" t="str">
+      <c r="BG2" s="104" t="str">
         <f t="shared" si="1"/>
         <v>Gain $L3 additional Coins from the Royal Bank when Deploying Troops</v>
       </c>
-      <c r="BD2" s="103" t="str">
+      <c r="BH2" s="105" t="str">
         <f t="shared" si="2"/>
         <v>Provides private Buy Action at Market Rate + $L3</v>
       </c>
-      <c r="BE2" s="104" t="str">
+      <c r="BI2" s="104" t="str">
         <f t="shared" si="2"/>
         <v>Provides private Sell Action at Market Rate - $L3</v>
       </c>
-      <c r="BF2" s="103" t="str">
+      <c r="BJ2" s="103" t="str">
         <f t="shared" si="2"/>
         <v>Purchase and immediately add up to $L3 Troops to your force when deploying them</v>
       </c>
-      <c r="BG2" s="104" t="str">
+      <c r="BK2" s="104" t="str">
         <f t="shared" si="2"/>
         <v>Add $L3 Hits to each Roll during a Sue</v>
       </c>
-      <c r="BH2" s="105" t="str">
+      <c r="BL2" s="103" t="str">
         <f t="shared" si="2"/>
         <v>Add $L6 additional dice to each Roll during a Sue</v>
       </c>
-      <c r="BI2" s="104" t="str">
+      <c r="BM2" s="104" t="str">
         <f t="shared" si="2"/>
         <v>Collect $L6 additional Commodities during Harvests</v>
       </c>
-    </row>
-    <row r="3" spans="1:61" s="80" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BN2" s="103" t="str">
+        <f t="shared" si="2"/>
+        <v>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</v>
+      </c>
+      <c r="BO2" s="104" t="str">
+        <f t="shared" si="2"/>
+        <v>Subtract $L3 from Scheme Card rolls</v>
+      </c>
+      <c r="BP2" s="103" t="str">
+        <f t="shared" si="2"/>
+        <v>Spend $L3 fewer Commodities per Coin when Selling to the Undermarket</v>
+      </c>
+      <c r="BQ2" s="104"/>
+      <c r="BS2" s="104"/>
+    </row>
+    <row r="3" spans="1:71" s="80" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="78" t="str">
         <f>Cards!D2</f>
         <v>Full Coffers</v>
@@ -7930,128 +7999,158 @@
         <v>Worthless Procrastinators</v>
       </c>
       <c r="AE3" s="78" t="str">
-        <f t="shared" ref="AE3:BH3" si="3">A3</f>
+        <f>Cards!D32</f>
+        <v>Stalled Front</v>
+      </c>
+      <c r="AF3" s="78" t="str">
+        <f>Cards!D33</f>
+        <v>Quality Strength</v>
+      </c>
+      <c r="AG3" s="80" t="str">
+        <f t="shared" ref="AG3:BL3" si="3">A3</f>
         <v>Full Coffers</v>
       </c>
-      <c r="AF3" s="78" t="str">
+      <c r="AH3" s="78" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">Decentralized Wealth </v>
       </c>
-      <c r="AG3" s="80" t="str">
+      <c r="AI3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Second Thoughts</v>
       </c>
-      <c r="AH3" s="78" t="str">
+      <c r="AJ3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Changing Times</v>
       </c>
-      <c r="AI3" s="80" t="str">
+      <c r="AK3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Stable Economies</v>
       </c>
-      <c r="AJ3" s="78" t="str">
+      <c r="AL3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Unreasonable Distractions</v>
       </c>
-      <c r="AK3" s="80" t="str">
+      <c r="AM3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Irregular Partiality</v>
       </c>
-      <c r="AL3" s="78" t="str">
+      <c r="AN3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Royal Amendment</v>
       </c>
-      <c r="AM3" s="80" t="str">
+      <c r="AO3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Honorable Accontability</v>
       </c>
-      <c r="AN3" s="78" t="str">
+      <c r="AP3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Frivolous Pursuits</v>
       </c>
-      <c r="AO3" s="80" t="str">
+      <c r="AQ3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Economic Backbone</v>
       </c>
-      <c r="AP3" s="78" t="str">
+      <c r="AR3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Collective Ownership</v>
       </c>
-      <c r="AQ3" s="80" t="str">
+      <c r="AS3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Aggressive Tactics</v>
       </c>
-      <c r="AR3" s="78" t="str">
+      <c r="AT3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Home Defense</v>
       </c>
-      <c r="AS3" s="80" t="str">
+      <c r="AU3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Valuable Advisors</v>
       </c>
-      <c r="AT3" s="78" t="str">
+      <c r="AV3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Chattering Windbags</v>
       </c>
-      <c r="AU3" s="80" t="str">
+      <c r="AW3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Realistic Priorities</v>
       </c>
-      <c r="AV3" s="78" t="str">
+      <c r="AX3" s="81" t="str">
         <f t="shared" si="3"/>
         <v>Threat to the Throne</v>
       </c>
-      <c r="AW3" s="80" t="str">
+      <c r="AY3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Stone Foundations</v>
       </c>
-      <c r="AX3" s="81" t="str">
+      <c r="AZ3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Environmental Guardians</v>
       </c>
-      <c r="AY3" s="78" t="str">
+      <c r="BA3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Resilient Officer Corps</v>
       </c>
-      <c r="AZ3" s="80" t="str">
+      <c r="BB3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Bloated Bureaucracy</v>
       </c>
-      <c r="BA3" s="78" t="str">
+      <c r="BC3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Police Force</v>
       </c>
-      <c r="BB3" s="80" t="str">
+      <c r="BD3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Equal Partners</v>
       </c>
-      <c r="BC3" s="78" t="str">
+      <c r="BE3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Criminal Identification</v>
       </c>
-      <c r="BD3" s="80" t="str">
+      <c r="BF3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Honorable Marketplace</v>
       </c>
-      <c r="BE3" s="78" t="str">
+      <c r="BG3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Engaged Empire</v>
       </c>
-      <c r="BF3" s="80" t="str">
+      <c r="BH3" s="81" t="str">
         <f t="shared" si="3"/>
         <v>Suspicious Advisors</v>
       </c>
-      <c r="BG3" s="78" t="str">
+      <c r="BI3" s="78" t="str">
         <f t="shared" si="3"/>
         <v>Contingency Plans</v>
       </c>
-      <c r="BH3" s="81" t="str">
+      <c r="BJ3" s="80" t="str">
         <f t="shared" si="3"/>
         <v>Worthless Procrastinators</v>
       </c>
-      <c r="BI3" s="78"/>
-    </row>
-    <row r="4" spans="1:61" s="85" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BK3" s="78" t="str">
+        <f t="shared" si="3"/>
+        <v>Stalled Front</v>
+      </c>
+      <c r="BL3" s="80" t="str">
+        <f t="shared" si="3"/>
+        <v>Quality Strength</v>
+      </c>
+      <c r="BM3" s="78"/>
+      <c r="BN3" s="80" t="str">
+        <f>AH1</f>
+        <v>Innovation Hub</v>
+      </c>
+      <c r="BO3" s="78" t="str">
+        <f>AF1</f>
+        <v>Dangerous Promises</v>
+      </c>
+      <c r="BP3" s="80" t="str">
+        <f>AD1</f>
+        <v>Expert Broker</v>
+      </c>
+      <c r="BQ3" s="78"/>
+      <c r="BS3" s="78"/>
+    </row>
+    <row r="4" spans="1:71" s="85" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="83" t="str">
         <f>Cards!E2</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
@@ -8173,128 +8272,158 @@
         <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
       </c>
       <c r="AE4" s="83" t="str">
-        <f t="shared" ref="AE4" si="4">A4</f>
+        <f>Cards!E32</f>
+        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="AF4" s="83" t="str">
+        <f>Cards!E33</f>
+        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="AG4" s="85" t="str">
+        <f t="shared" ref="AG4:BL4" si="4">A4</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
-      <c r="AF4" s="83" t="str">
-        <f t="shared" ref="AF4" si="5">B4</f>
+      <c r="AH4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
-      <c r="AG4" s="85" t="str">
-        <f t="shared" ref="AG4" si="6">C4</f>
+      <c r="AI4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="AH4" s="83" t="str">
-        <f t="shared" ref="AH4" si="7">D4</f>
+      <c r="AJ4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="AI4" s="85" t="str">
-        <f t="shared" ref="AI4" si="8">E4</f>
+      <c r="AK4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
       </c>
-      <c r="AJ4" s="83" t="str">
-        <f t="shared" ref="AJ4" si="9">F4</f>
+      <c r="AL4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
       </c>
-      <c r="AK4" s="85" t="str">
-        <f t="shared" ref="AK4" si="10">G4</f>
+      <c r="AM4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="AL4" s="83" t="str">
-        <f t="shared" ref="AL4" si="11">H4</f>
+      <c r="AN4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="AM4" s="85" t="str">
-        <f t="shared" ref="AM4" si="12">I4</f>
+      <c r="AO4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy Troops</v>
       </c>
-      <c r="AN4" s="83" t="str">
-        <f t="shared" ref="AN4" si="13">J4</f>
+      <c r="AP4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy Troops</v>
       </c>
-      <c r="AO4" s="85" t="str">
-        <f t="shared" ref="AO4" si="14">K4</f>
+      <c r="AQ4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
       </c>
-      <c r="AP4" s="83" t="str">
-        <f t="shared" ref="AP4" si="15">L4</f>
+      <c r="AR4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
       </c>
-      <c r="AQ4" s="85" t="str">
-        <f t="shared" ref="AQ4" si="16">M4</f>
+      <c r="AS4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
       </c>
-      <c r="AR4" s="83" t="str">
-        <f t="shared" ref="AR4" si="17">N4</f>
+      <c r="AT4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
       </c>
-      <c r="AS4" s="85" t="str">
-        <f t="shared" ref="AS4" si="18">O4</f>
+      <c r="AU4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>Each Player must have at least $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
       </c>
-      <c r="AT4" s="83" t="str">
-        <f t="shared" ref="AT4" si="19">P4</f>
+      <c r="AV4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
       </c>
-      <c r="AU4" s="85" t="str">
-        <f t="shared" ref="AU4" si="20">Q4</f>
+      <c r="AW4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
       </c>
-      <c r="AV4" s="83" t="str">
-        <f t="shared" ref="AV4" si="21">R4</f>
+      <c r="AX4" s="86" t="str">
+        <f t="shared" si="4"/>
         <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
       </c>
-      <c r="AW4" s="85" t="str">
-        <f t="shared" ref="AW4" si="22">S4</f>
+      <c r="AY4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
-      <c r="AX4" s="86" t="str">
-        <f t="shared" ref="AX4" si="23">T4</f>
+      <c r="AZ4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
-      <c r="AY4" s="83" t="str">
-        <f t="shared" ref="AY4" si="24">U4</f>
+      <c r="BA4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
-      <c r="AZ4" s="85" t="str">
-        <f t="shared" ref="AZ4" si="25">V4</f>
+      <c r="BB4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
-      <c r="BA4" s="83" t="str">
-        <f t="shared" ref="BA4" si="26">W4</f>
+      <c r="BC4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</v>
       </c>
-      <c r="BB4" s="85" t="str">
-        <f t="shared" ref="BB4" si="27">X4</f>
+      <c r="BD4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</v>
       </c>
-      <c r="BC4" s="83" t="str">
-        <f t="shared" ref="BC4" si="28">Y4</f>
+      <c r="BE4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
-      <c r="BD4" s="85" t="str">
-        <f t="shared" ref="BD4" si="29">Z4</f>
+      <c r="BF4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
-      <c r="BE4" s="83" t="str">
-        <f t="shared" ref="BE4" si="30">AA4</f>
+      <c r="BG4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
-      <c r="BF4" s="85" t="str">
-        <f t="shared" ref="BF4" si="31">AB4</f>
+      <c r="BH4" s="86" t="str">
+        <f t="shared" si="4"/>
         <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
-      <c r="BG4" s="83" t="str">
-        <f t="shared" ref="BG4" si="32">AC4</f>
+      <c r="BI4" s="83" t="str">
+        <f t="shared" si="4"/>
         <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
       </c>
-      <c r="BH4" s="86" t="str">
-        <f t="shared" ref="BH4" si="33">AD4</f>
+      <c r="BJ4" s="85" t="str">
+        <f t="shared" si="4"/>
         <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
       </c>
-      <c r="BI4" s="83"/>
-    </row>
-    <row r="5" spans="1:61" s="89" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BK4" s="83" t="str">
+        <f t="shared" si="4"/>
+        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="BL4" s="85" t="str">
+        <f t="shared" si="4"/>
+        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="BM4" s="83"/>
+      <c r="BN4" s="103" t="str">
+        <f>AH2</f>
+        <v>Provides private Monetize Action at Market Rate + $L3</v>
+      </c>
+      <c r="BO4" s="104" t="str">
+        <f>AF2</f>
+        <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
+      </c>
+      <c r="BP4" s="132" t="str">
+        <f>AD2</f>
+        <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
+      </c>
+      <c r="BQ4" s="83"/>
+      <c r="BS4" s="83"/>
+    </row>
+    <row r="5" spans="1:71" s="89" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="87" t="str">
         <f>Cards!F2</f>
         <v>Fickle Mercenaries</v>
@@ -8353,430 +8482,492 @@
       </c>
       <c r="O5" s="89" t="str">
         <f>Cards!F16</f>
-        <v>Intimidate</v>
+        <v>Intimidation</v>
       </c>
       <c r="P5" s="87" t="str">
         <f>Cards!F17</f>
-        <v>Humiliate</v>
+        <v>Humiliation</v>
       </c>
       <c r="Q5" s="89" t="str">
         <f>Cards!F18</f>
         <v>Backroom Deal</v>
       </c>
       <c r="R5" s="87" t="str">
-        <f t="shared" ref="R5:AH5" si="34">A5</f>
+        <f>Cards!F19</f>
+        <v>Rallied Opposition</v>
+      </c>
+      <c r="S5" s="89" t="str">
+        <f>Cards!F20</f>
+        <v>Waning Support</v>
+      </c>
+      <c r="T5" s="87" t="str">
+        <f>Cards!F21</f>
+        <v>Misaligned Strategy</v>
+      </c>
+      <c r="U5" s="89" t="str">
+        <f t="shared" ref="U5:AN5" si="5">A5</f>
         <v>Fickle Mercenaries</v>
       </c>
-      <c r="S5" s="89" t="str">
-        <f t="shared" si="34"/>
+      <c r="V5" s="87" t="str">
+        <f t="shared" si="5"/>
         <v>Blatant Thievery</v>
       </c>
-      <c r="T5" s="87" t="str">
-        <f t="shared" si="34"/>
+      <c r="W5" s="89" t="str">
+        <f t="shared" si="5"/>
         <v>Double Agents</v>
       </c>
-      <c r="U5" s="89" t="str">
-        <f t="shared" si="34"/>
+      <c r="X5" s="87" t="str">
+        <f t="shared" si="5"/>
         <v>Questionable Reallocation</v>
       </c>
-      <c r="V5" s="87" t="str">
-        <f t="shared" si="34"/>
+      <c r="Y5" s="89" t="str">
+        <f t="shared" si="5"/>
         <v>Blackmail</v>
       </c>
-      <c r="W5" s="89" t="str">
-        <f t="shared" si="34"/>
+      <c r="Z5" s="87" t="str">
+        <f t="shared" si="5"/>
         <v>Invalid Paperwork</v>
       </c>
-      <c r="X5" s="87" t="str">
-        <f t="shared" si="34"/>
+      <c r="AA5" s="89" t="str">
+        <f t="shared" si="5"/>
         <v>Insider Trading</v>
       </c>
-      <c r="Y5" s="89" t="str">
-        <f t="shared" si="34"/>
+      <c r="AB5" s="87" t="str">
+        <f t="shared" si="5"/>
         <v>Whispers of the People</v>
       </c>
-      <c r="Z5" s="87" t="str">
-        <f t="shared" si="34"/>
+      <c r="AC5" s="89" t="str">
+        <f t="shared" si="5"/>
         <v>Dangerous Monopolies</v>
       </c>
-      <c r="AA5" s="89" t="str">
-        <f t="shared" si="34"/>
+      <c r="AD5" s="90" t="str">
+        <f t="shared" si="5"/>
         <v>Corporate Takeover</v>
       </c>
-      <c r="AB5" s="87" t="str">
-        <f t="shared" si="34"/>
+      <c r="AE5" s="87" t="str">
+        <f t="shared" si="5"/>
         <v>Sabotage</v>
       </c>
-      <c r="AC5" s="89" t="str">
-        <f t="shared" si="34"/>
+      <c r="AF5" s="87" t="str">
+        <f t="shared" si="5"/>
         <v>Poor Management</v>
       </c>
-      <c r="AD5" s="90" t="str">
-        <f t="shared" si="34"/>
+      <c r="AG5" s="89" t="str">
+        <f t="shared" si="5"/>
         <v>Assassination</v>
       </c>
-      <c r="AE5" s="87" t="str">
-        <f t="shared" si="34"/>
+      <c r="AH5" s="87" t="str">
+        <f t="shared" si="5"/>
         <v>Betrayal</v>
       </c>
-      <c r="AF5" s="87" t="str">
-        <f t="shared" si="34"/>
-        <v>Intimidate</v>
-      </c>
-      <c r="AG5" s="89" t="str">
-        <f t="shared" si="34"/>
-        <v>Humiliate</v>
-      </c>
-      <c r="AH5" s="87" t="str">
-        <f t="shared" si="34"/>
+      <c r="AI5" s="89" t="str">
+        <f t="shared" si="5"/>
+        <v>Intimidation</v>
+      </c>
+      <c r="AJ5" s="87" t="str">
+        <f t="shared" si="5"/>
+        <v>Humiliation</v>
+      </c>
+      <c r="AK5" s="89" t="str">
+        <f t="shared" si="5"/>
         <v>Backroom Deal</v>
       </c>
-      <c r="AI5" s="89" t="str">
-        <f t="shared" ref="AI5:AY5" si="35">A5</f>
+      <c r="AL5" s="87" t="str">
+        <f t="shared" si="5"/>
+        <v>Rallied Opposition</v>
+      </c>
+      <c r="AM5" s="89" t="str">
+        <f t="shared" si="5"/>
+        <v>Waning Support</v>
+      </c>
+      <c r="AN5" s="87" t="str">
+        <f t="shared" si="5"/>
+        <v>Misaligned Strategy</v>
+      </c>
+      <c r="AO5" s="89" t="str">
+        <f t="shared" ref="AO5:BH5" si="6">A5</f>
         <v>Fickle Mercenaries</v>
       </c>
-      <c r="AJ5" s="87" t="str">
-        <f t="shared" si="35"/>
+      <c r="AP5" s="87" t="str">
+        <f t="shared" si="6"/>
         <v>Blatant Thievery</v>
       </c>
-      <c r="AK5" s="89" t="str">
-        <f t="shared" si="35"/>
+      <c r="AQ5" s="89" t="str">
+        <f t="shared" si="6"/>
         <v>Double Agents</v>
       </c>
-      <c r="AL5" s="87" t="str">
-        <f t="shared" si="35"/>
+      <c r="AR5" s="87" t="str">
+        <f t="shared" si="6"/>
         <v>Questionable Reallocation</v>
       </c>
-      <c r="AM5" s="89" t="str">
-        <f t="shared" si="35"/>
+      <c r="AS5" s="89" t="str">
+        <f t="shared" si="6"/>
         <v>Blackmail</v>
       </c>
-      <c r="AN5" s="87" t="str">
-        <f t="shared" si="35"/>
+      <c r="AT5" s="87" t="str">
+        <f t="shared" si="6"/>
         <v>Invalid Paperwork</v>
       </c>
-      <c r="AO5" s="89" t="str">
-        <f t="shared" si="35"/>
+      <c r="AU5" s="89" t="str">
+        <f t="shared" si="6"/>
         <v>Insider Trading</v>
       </c>
-      <c r="AP5" s="87" t="str">
-        <f t="shared" si="35"/>
+      <c r="AV5" s="87" t="str">
+        <f t="shared" si="6"/>
         <v>Whispers of the People</v>
       </c>
-      <c r="AQ5" s="89" t="str">
-        <f t="shared" si="35"/>
+      <c r="AW5" s="89" t="str">
+        <f t="shared" si="6"/>
         <v>Dangerous Monopolies</v>
       </c>
-      <c r="AR5" s="87" t="str">
-        <f t="shared" si="35"/>
+      <c r="AX5" s="90" t="str">
+        <f t="shared" si="6"/>
         <v>Corporate Takeover</v>
       </c>
-      <c r="AS5" s="89" t="str">
-        <f t="shared" si="35"/>
+      <c r="AY5" s="87" t="str">
+        <f t="shared" si="6"/>
         <v>Sabotage</v>
       </c>
-      <c r="AT5" s="87" t="str">
-        <f t="shared" si="35"/>
+      <c r="AZ5" s="89" t="str">
+        <f t="shared" si="6"/>
         <v>Poor Management</v>
       </c>
-      <c r="AU5" s="89" t="str">
-        <f t="shared" si="35"/>
+      <c r="BA5" s="87" t="str">
+        <f t="shared" si="6"/>
         <v>Assassination</v>
       </c>
-      <c r="AV5" s="87" t="str">
-        <f t="shared" si="35"/>
+      <c r="BB5" s="89" t="str">
+        <f t="shared" si="6"/>
         <v>Betrayal</v>
       </c>
-      <c r="AW5" s="89" t="str">
-        <f t="shared" si="35"/>
-        <v>Intimidate</v>
-      </c>
-      <c r="AX5" s="90" t="str">
-        <f t="shared" si="35"/>
-        <v>Humiliate</v>
-      </c>
-      <c r="AY5" s="87" t="str">
-        <f t="shared" si="35"/>
+      <c r="BC5" s="87" t="str">
+        <f t="shared" si="6"/>
+        <v>Intimidation</v>
+      </c>
+      <c r="BD5" s="89" t="str">
+        <f t="shared" si="6"/>
+        <v>Humiliation</v>
+      </c>
+      <c r="BE5" s="87" t="str">
+        <f t="shared" si="6"/>
         <v>Backroom Deal</v>
       </c>
-      <c r="BA5" s="87" t="str">
-        <f t="shared" ref="BA5:BI6" si="36">AA1</f>
-        <v>Wary Guards</v>
-      </c>
-      <c r="BB5" s="89" t="str">
-        <f t="shared" si="36"/>
-        <v>Information Security</v>
-      </c>
-      <c r="BC5" s="87" t="str">
-        <f t="shared" si="36"/>
-        <v>Blood Pact</v>
-      </c>
-      <c r="BD5" s="89" t="str">
-        <f t="shared" si="36"/>
-        <v>Expert Broker</v>
-      </c>
-      <c r="BE5" s="87" t="str">
-        <f t="shared" si="36"/>
+      <c r="BF5" s="89" t="str">
+        <f t="shared" si="6"/>
+        <v>Rallied Opposition</v>
+      </c>
+      <c r="BG5" s="87" t="str">
+        <f t="shared" si="6"/>
+        <v>Waning Support</v>
+      </c>
+      <c r="BH5" s="87" t="str">
+        <f t="shared" si="6"/>
+        <v>Misaligned Strategy</v>
+      </c>
+      <c r="BI5" s="87"/>
+      <c r="BJ5" s="81" t="str">
+        <f>AM1</f>
+        <v>Painful Progress</v>
+      </c>
+      <c r="BK5" s="78" t="str">
+        <f>AL1</f>
+        <v>Abusive Power</v>
+      </c>
+      <c r="BL5" s="80" t="str">
+        <f>AK1</f>
+        <v>Soup Kitchens</v>
+      </c>
+      <c r="BM5" s="78" t="str">
+        <f>AJ1</f>
+        <v>Kingdom Advocates</v>
+      </c>
+      <c r="BN5" s="80" t="str">
+        <f>AI1</f>
+        <v>Fire Temple</v>
+      </c>
+      <c r="BO5" s="78" t="str">
+        <f>AG1</f>
+        <v>Large Middle Class</v>
+      </c>
+      <c r="BP5" s="79" t="str">
+        <f>AE1</f>
         <v>Codependent Relationship</v>
       </c>
-      <c r="BF5" s="89" t="str">
-        <f t="shared" si="36"/>
-        <v>Dangerous Promises</v>
-      </c>
-      <c r="BG5" s="87" t="str">
-        <f t="shared" si="36"/>
-        <v>Large Middle Class</v>
-      </c>
-      <c r="BH5" s="87" t="str">
-        <f t="shared" si="36"/>
-        <v>Innovation Hub</v>
-      </c>
-      <c r="BI5" s="87" t="str">
-        <f t="shared" si="36"/>
-        <v>Fire Temple</v>
-      </c>
-    </row>
-    <row r="6" spans="1:61" s="85" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BQ5" s="87"/>
+      <c r="BS5" s="87"/>
+    </row>
+    <row r="6" spans="1:71" s="85" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="83" t="str">
         <f>Cards!G2</f>
-        <v>Give $D6 Troops to Player $R</v>
+        <v>Give $2D6 Troops to $R</v>
       </c>
       <c r="B6" s="84" t="str">
         <f>Cards!G3</f>
-        <v>Give $D6 Coins to Player $R</v>
+        <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
       </c>
       <c r="C6" s="85" t="str">
         <f>Cards!G4</f>
-        <v>Give $D6 Spies to Player $R</v>
+        <v>Give $D6 Spies to $R</v>
       </c>
       <c r="D6" s="83" t="str">
         <f>Cards!G5</f>
-        <v>Give $D6 Commodities to Player $R</v>
+        <v>Give $2D6 Commodities to $R. Perform an Emergency Trade if needed.</v>
       </c>
       <c r="E6" s="85" t="str">
         <f>Cards!G6</f>
-        <v>Give the King's Favor to Player $R</v>
+        <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
       </c>
       <c r="F6" s="83" t="str">
         <f>Cards!G7</f>
-        <v>Player $R may peek at the Law card at the top of the queue &amp; put it on the bottom of the queue if they want</v>
+        <v>Move your foremost Law to the back of the Queue</v>
       </c>
       <c r="G6" s="85" t="str">
         <f>Cards!G8</f>
-        <v>Give $D6 random Cards from your hand to Player $R</v>
+        <v>Give $D6 random Cards of each type from your hand to $R</v>
       </c>
       <c r="H6" s="83" t="str">
         <f>Cards!G9</f>
-        <v>Rearrange $D3 Law cards from the top of the queue</v>
+        <v>Rearrange the first $D6 Law cards in the Queue</v>
       </c>
       <c r="I6" s="85" t="str">
         <f>Cards!G10</f>
-        <v>Destroy an Investment at level $D6</v>
+        <v>Downgrade an Investment by $D6 levels</v>
       </c>
       <c r="J6" s="83" t="str">
         <f>Cards!G11</f>
-        <v>Send an Investment at level $D6 to Player $R</v>
+        <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
       </c>
       <c r="K6" s="85" t="str">
         <f>Cards!G12</f>
-        <v>Downgrade an Investment at level $D6</v>
+        <v>Downgrade an Investment by $D6 levels</v>
       </c>
       <c r="L6" s="83" t="str">
         <f>Cards!G13</f>
-        <v>Downgrade an Investment at level $D6</v>
+        <v>Downgrade an Investment by $D6 levels</v>
       </c>
       <c r="M6" s="85" t="str">
         <f>Cards!G14</f>
-        <v>Kill a Leader at level $D6</v>
+        <v>Demote a Leader by $D6 levels</v>
       </c>
       <c r="N6" s="83" t="str">
         <f>Cards!G15</f>
-        <v>Send a Leader at level $D6 to Player $R</v>
+        <v>Demote a Leader at level $D6 by half and send it to $R</v>
       </c>
       <c r="O6" s="85" t="str">
         <f>Cards!G16</f>
-        <v>Demote a Leader at level $D6</v>
+        <v>Demote a Leader by $D6 levels</v>
       </c>
       <c r="P6" s="83" t="str">
         <f>Cards!G17</f>
-        <v>Demote a Leader at level $D6</v>
+        <v>Demote a Leader by $D6 levels</v>
       </c>
       <c r="Q6" s="85" t="str">
         <f>Cards!G18</f>
-        <v>Exchange a random held Alliance Token, or one of your own if you hold none, with one of the choice of Player $R</v>
+        <v>Exchange one Alliance Token with $R</v>
       </c>
       <c r="R6" s="83" t="str">
-        <f t="shared" ref="R6:AH6" si="37">A6</f>
-        <v>Give $D6 Troops to Player $R</v>
+        <f>Cards!G19</f>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
       <c r="S6" s="85" t="str">
-        <f t="shared" si="37"/>
-        <v>Give $D6 Coins to Player $R</v>
+        <f>Cards!G20</f>
+        <v>Move $D6 of your Laws each one space back in the Queue</v>
       </c>
       <c r="T6" s="83" t="str">
-        <f t="shared" si="37"/>
-        <v>Give $D6 Spies to Player $R</v>
+        <f>Cards!G21</f>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
       <c r="U6" s="85" t="str">
-        <f t="shared" si="37"/>
-        <v>Give $D6 Commodities to Player $R</v>
+        <f t="shared" ref="U6:AN6" si="7">A6</f>
+        <v>Give $2D6 Troops to $R</v>
       </c>
       <c r="V6" s="83" t="str">
-        <f t="shared" si="37"/>
-        <v>Give the King's Favor to Player $R</v>
+        <f t="shared" si="7"/>
+        <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
       </c>
       <c r="W6" s="85" t="str">
-        <f t="shared" si="37"/>
-        <v>Player $R may peek at the Law card at the top of the queue &amp; put it on the bottom of the queue if they want</v>
+        <f t="shared" si="7"/>
+        <v>Give $D6 Spies to $R</v>
       </c>
       <c r="X6" s="83" t="str">
-        <f t="shared" si="37"/>
-        <v>Give $D6 random Cards from your hand to Player $R</v>
+        <f t="shared" si="7"/>
+        <v>Give $2D6 Commodities to $R. Perform an Emergency Trade if needed.</v>
       </c>
       <c r="Y6" s="85" t="str">
-        <f t="shared" si="37"/>
-        <v>Rearrange $D3 Law cards from the top of the queue</v>
+        <f t="shared" si="7"/>
+        <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
       </c>
       <c r="Z6" s="83" t="str">
-        <f t="shared" si="37"/>
-        <v>Destroy an Investment at level $D6</v>
+        <f t="shared" si="7"/>
+        <v>Move your foremost Law to the back of the Queue</v>
       </c>
       <c r="AA6" s="85" t="str">
-        <f t="shared" si="37"/>
-        <v>Send an Investment at level $D6 to Player $R</v>
+        <f t="shared" si="7"/>
+        <v>Give $D6 random Cards of each type from your hand to $R</v>
       </c>
       <c r="AB6" s="83" t="str">
-        <f t="shared" si="37"/>
-        <v>Downgrade an Investment at level $D6</v>
+        <f t="shared" si="7"/>
+        <v>Rearrange the first $D6 Law cards in the Queue</v>
       </c>
       <c r="AC6" s="85" t="str">
-        <f t="shared" si="37"/>
-        <v>Downgrade an Investment at level $D6</v>
+        <f t="shared" si="7"/>
+        <v>Downgrade an Investment by $D6 levels</v>
       </c>
       <c r="AD6" s="86" t="str">
-        <f t="shared" si="37"/>
-        <v>Kill a Leader at level $D6</v>
+        <f t="shared" si="7"/>
+        <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
       </c>
       <c r="AE6" s="83" t="str">
-        <f t="shared" si="37"/>
-        <v>Send a Leader at level $D6 to Player $R</v>
+        <f t="shared" si="7"/>
+        <v>Downgrade an Investment by $D6 levels</v>
       </c>
       <c r="AF6" s="83" t="str">
-        <f t="shared" si="37"/>
-        <v>Demote a Leader at level $D6</v>
+        <f t="shared" si="7"/>
+        <v>Downgrade an Investment by $D6 levels</v>
       </c>
       <c r="AG6" s="85" t="str">
-        <f t="shared" si="37"/>
-        <v>Demote a Leader at level $D6</v>
+        <f t="shared" si="7"/>
+        <v>Demote a Leader by $D6 levels</v>
       </c>
       <c r="AH6" s="83" t="str">
-        <f t="shared" si="37"/>
-        <v>Exchange a random held Alliance Token, or one of your own if you hold none, with one of the choice of Player $R</v>
+        <f t="shared" si="7"/>
+        <v>Demote a Leader at level $D6 by half and send it to $R</v>
       </c>
       <c r="AI6" s="85" t="str">
-        <f t="shared" ref="AI6:AY6" si="38">A6</f>
-        <v>Give $D6 Troops to Player $R</v>
+        <f t="shared" si="7"/>
+        <v>Demote a Leader by $D6 levels</v>
       </c>
       <c r="AJ6" s="83" t="str">
-        <f t="shared" si="38"/>
-        <v>Give $D6 Coins to Player $R</v>
+        <f t="shared" si="7"/>
+        <v>Demote a Leader by $D6 levels</v>
       </c>
       <c r="AK6" s="85" t="str">
-        <f t="shared" si="38"/>
-        <v>Give $D6 Spies to Player $R</v>
+        <f t="shared" si="7"/>
+        <v>Exchange one Alliance Token with $R</v>
       </c>
       <c r="AL6" s="83" t="str">
-        <f t="shared" si="38"/>
-        <v>Give $D6 Commodities to Player $R</v>
+        <f t="shared" si="7"/>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
       <c r="AM6" s="85" t="str">
-        <f t="shared" si="38"/>
-        <v>Give the King's Favor to Player $R</v>
+        <f t="shared" si="7"/>
+        <v>Move $D6 of your Laws each one space back in the Queue</v>
       </c>
       <c r="AN6" s="83" t="str">
-        <f t="shared" si="38"/>
-        <v>Player $R may peek at the Law card at the top of the queue &amp; put it on the bottom of the queue if they want</v>
+        <f t="shared" si="7"/>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
       <c r="AO6" s="85" t="str">
-        <f t="shared" si="38"/>
-        <v>Give $D6 random Cards from your hand to Player $R</v>
+        <f t="shared" ref="AO6:BH6" si="8">A6</f>
+        <v>Give $2D6 Troops to $R</v>
       </c>
       <c r="AP6" s="83" t="str">
-        <f t="shared" si="38"/>
-        <v>Rearrange $D3 Law cards from the top of the queue</v>
+        <f t="shared" si="8"/>
+        <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
       </c>
       <c r="AQ6" s="85" t="str">
-        <f t="shared" si="38"/>
-        <v>Destroy an Investment at level $D6</v>
+        <f t="shared" si="8"/>
+        <v>Give $D6 Spies to $R</v>
       </c>
       <c r="AR6" s="83" t="str">
-        <f t="shared" si="38"/>
-        <v>Send an Investment at level $D6 to Player $R</v>
+        <f t="shared" si="8"/>
+        <v>Give $2D6 Commodities to $R. Perform an Emergency Trade if needed.</v>
       </c>
       <c r="AS6" s="85" t="str">
-        <f t="shared" si="38"/>
-        <v>Downgrade an Investment at level $D6</v>
+        <f t="shared" si="8"/>
+        <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
       </c>
       <c r="AT6" s="83" t="str">
-        <f t="shared" si="38"/>
-        <v>Downgrade an Investment at level $D6</v>
+        <f t="shared" si="8"/>
+        <v>Move your foremost Law to the back of the Queue</v>
       </c>
       <c r="AU6" s="85" t="str">
-        <f t="shared" si="38"/>
-        <v>Kill a Leader at level $D6</v>
+        <f t="shared" si="8"/>
+        <v>Give $D6 random Cards of each type from your hand to $R</v>
       </c>
       <c r="AV6" s="83" t="str">
-        <f t="shared" si="38"/>
-        <v>Send a Leader at level $D6 to Player $R</v>
+        <f t="shared" si="8"/>
+        <v>Rearrange the first $D6 Law cards in the Queue</v>
       </c>
       <c r="AW6" s="85" t="str">
-        <f t="shared" si="38"/>
-        <v>Demote a Leader at level $D6</v>
+        <f t="shared" si="8"/>
+        <v>Downgrade an Investment by $D6 levels</v>
       </c>
       <c r="AX6" s="86" t="str">
-        <f t="shared" si="38"/>
-        <v>Demote a Leader at level $D6</v>
+        <f t="shared" si="8"/>
+        <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
       </c>
       <c r="AY6" s="83" t="str">
-        <f t="shared" si="38"/>
-        <v>Exchange a random held Alliance Token, or one of your own if you hold none, with one of the choice of Player $R</v>
+        <f t="shared" si="8"/>
+        <v>Downgrade an Investment by $D6 levels</v>
+      </c>
+      <c r="AZ6" s="85" t="str">
+        <f t="shared" si="8"/>
+        <v>Downgrade an Investment by $D6 levels</v>
       </c>
       <c r="BA6" s="83" t="str">
-        <f t="shared" si="36"/>
-        <v>Subtract $L3 from Scheme Guard rolls</v>
+        <f t="shared" si="8"/>
+        <v>Demote a Leader by $D6 levels</v>
       </c>
       <c r="BB6" s="85" t="str">
-        <f t="shared" si="36"/>
-        <v>Subtract $L3 from Scheme Card rolls</v>
+        <f t="shared" si="8"/>
+        <v>Demote a Leader at level $D6 by half and send it to $R</v>
       </c>
       <c r="BC6" s="83" t="str">
-        <f t="shared" si="36"/>
-        <v>Spend $L3 fewer Commodities per Coin when Selling to the Undermarket</v>
+        <f t="shared" si="8"/>
+        <v>Demote a Leader by $D6 levels</v>
       </c>
       <c r="BD6" s="85" t="str">
-        <f t="shared" si="36"/>
-        <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
+        <f t="shared" si="8"/>
+        <v>Demote a Leader by $D6 levels</v>
       </c>
       <c r="BE6" s="83" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="8"/>
+        <v>Exchange one Alliance Token with $R</v>
+      </c>
+      <c r="BF6" s="85" t="str">
+        <f t="shared" si="8"/>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
+      </c>
+      <c r="BG6" s="83" t="str">
+        <f t="shared" si="8"/>
+        <v>Move $D6 of your Laws each one space back in the Queue</v>
+      </c>
+      <c r="BH6" s="83" t="str">
+        <f t="shared" si="8"/>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
+      </c>
+      <c r="BI6" s="83"/>
+      <c r="BJ6" s="86" t="str">
+        <f>AM2</f>
+        <v>You may repeat Undermarket Actions at double the penalty</v>
+      </c>
+      <c r="BK6" s="83" t="str">
+        <f>AL2</f>
+        <v>Convert $L3 additional Coins during Undermarket Donate</v>
+      </c>
+      <c r="BL6" s="85" t="str">
+        <f>AK2</f>
+        <v>Convert $L3 additional Coins during Court Donate</v>
+      </c>
+      <c r="BM6" s="83" t="str">
+        <f>AJ2</f>
+        <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
+      </c>
+      <c r="BN6" s="85" t="str">
+        <f>AI2</f>
+        <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
+      </c>
+      <c r="BO6" s="83" t="str">
+        <f>AG2</f>
+        <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
+      </c>
+      <c r="BP6" s="84" t="str">
+        <f>AE2</f>
         <v>Trade up to $L3 additional Coins when Buying from the Undermarket</v>
       </c>
-      <c r="BF6" s="85" t="str">
-        <f t="shared" si="36"/>
-        <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
-      </c>
-      <c r="BG6" s="83" t="str">
-        <f t="shared" si="36"/>
-        <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
-      </c>
-      <c r="BH6" s="83" t="str">
-        <f t="shared" si="36"/>
-        <v>Provides private Monetize Action at Market Rate + $L3</v>
-      </c>
-      <c r="BI6" s="83" t="str">
-        <f t="shared" si="36"/>
-        <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
-      </c>
+      <c r="BQ6" s="83"/>
+      <c r="BS6" s="83"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8798,31 +8989,31 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="C1" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="D1" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="E1" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="F1" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="D2">
         <v>27.7</v>
@@ -8830,14 +9021,14 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="D3">
         <v>27.7</v>
@@ -8845,14 +9036,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="D4">
         <v>30.75</v>
@@ -8860,222 +9051,222 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="E6" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="E7" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="E8" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="E10" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="E11" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="E12" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="E13" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -9088,7 +9279,7 @@
   <dimension ref="A1:U55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.140625" style="106" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" style="106" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" customWidth="1"/>
     <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
@@ -9106,67 +9297,67 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="B1" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="C1" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="D1" t="s">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="E1" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="F1" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="G1" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="H1" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="I1" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="J1" s="108" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="K1" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="L1" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="M1" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="N1" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="O1" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="P1" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>454</v>
+      </c>
+      <c r="R1" t="s">
+        <v>455</v>
+      </c>
+      <c r="S1" t="s">
+        <v>456</v>
+      </c>
+      <c r="T1" t="s">
+        <v>457</v>
+      </c>
+      <c r="U1" t="s">
         <v>470</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>471</v>
-      </c>
-      <c r="R1" t="s">
-        <v>472</v>
-      </c>
-      <c r="S1" t="s">
-        <v>473</v>
-      </c>
-      <c r="T1" t="s">
-        <v>474</v>
-      </c>
-      <c r="U1" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -9239,7 +9430,7 @@
         <v>0.68541666666666667</v>
       </c>
       <c r="I3" s="108">
-        <v>0.86041666666666672</v>
+        <v>0.86527777777777781</v>
       </c>
       <c r="J3" s="108">
         <v>0.6958333333333333</v>
@@ -9317,6 +9508,9 @@
       </c>
       <c r="P4" s="108">
         <v>0.92083333333333328</v>
+      </c>
+      <c r="U4" s="108">
+        <v>0.92777777777777781</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3573" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE269E95-B60B-4888-B96D-B58BAF152290}"/>
+  <xr:revisionPtr revIDLastSave="3628" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38D428B6-DD5E-5BAD-A10B-A879336AE14B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2543,7 +2543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2891,9 +2891,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3735,10 +3732,6 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -7563,7 +7556,7 @@
         <v>Elite Troops</v>
       </c>
       <c r="BH1" s="81" t="str">
-        <f t="shared" ref="BH1:BQ2" si="2">U1</f>
+        <f t="shared" ref="BH1:BP2" si="2">U1</f>
         <v>Bazaar</v>
       </c>
       <c r="BI1" s="78" t="str">
@@ -8416,7 +8409,7 @@
         <f>AF2</f>
         <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
       </c>
-      <c r="BP4" s="132" t="str">
+      <c r="BP4" s="103" t="str">
         <f>AD2</f>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
       </c>

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3628" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38D428B6-DD5E-5BAD-A10B-A879336AE14B}"/>
+  <xr:revisionPtr revIDLastSave="3920" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E6F7960-9CE9-48AE-ADF2-AFFB7CAA51F7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="541">
   <si>
     <t>Standard Card</t>
   </si>
@@ -88,27 +88,18 @@
     <t>2H</t>
   </si>
   <si>
-    <t>Legal Research</t>
-  </si>
-  <si>
     <t xml:space="preserve">Decentralized Wealth </t>
   </si>
   <si>
     <t>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</t>
   </si>
   <si>
-    <t>Blatant Thievery</t>
-  </si>
-  <si>
     <t>3H</t>
   </si>
   <si>
     <t>Collection Stations</t>
   </si>
   <si>
-    <t xml:space="preserve">You may gain up to $L6 additional Coins when Taxing other Players </t>
-  </si>
-  <si>
     <t>Second Thoughts</t>
   </si>
   <si>
@@ -175,9 +166,6 @@
     <t>Gain 1 additional Troop for free after Recruiting every 4 - $L3 Troops</t>
   </si>
   <si>
-    <t>Insider Trading</t>
-  </si>
-  <si>
     <t>8H</t>
   </si>
   <si>
@@ -190,18 +178,12 @@
     <t>Royal Amendment</t>
   </si>
   <si>
-    <t>Whispers of the People</t>
-  </si>
-  <si>
     <t>9H</t>
   </si>
   <si>
     <t>Loyal Citizenry</t>
   </si>
   <si>
-    <t>Purchase up to $L6 additional Troops during Recruit</t>
-  </si>
-  <si>
     <t>Dangerous Monopolies</t>
   </si>
   <si>
@@ -250,9 +232,6 @@
     <t>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</t>
   </si>
   <si>
-    <t>Poor Management</t>
-  </si>
-  <si>
     <t>KH</t>
   </si>
   <si>
@@ -322,9 +301,6 @@
     <t>Realistic Priorities</t>
   </si>
   <si>
-    <t>Backroom Deal</t>
-  </si>
-  <si>
     <t>5S</t>
   </si>
   <si>
@@ -859,9 +835,6 @@
     <t>Greek Reserves</t>
   </si>
   <si>
-    <t>Deployed Greeks</t>
-  </si>
-  <si>
     <t>Persian</t>
   </si>
   <si>
@@ -1066,9 +1039,6 @@
     <t>Negotiate with Chief Scribe</t>
   </si>
   <si>
-    <t>Master of Lies Schemes against Rival with himself as Receiver</t>
-  </si>
-  <si>
     <t>Deploy</t>
   </si>
   <si>
@@ -1192,9 +1162,6 @@
     <t>Take one of your unused leaders and place it on Flatter in the Court. Explain you would like the King's Favor since it is worth 1 Honor at the end of the game and that it breaks any tie during the game. Explain that the king also sends you home with some cash. Take 1 Coin (half your Leader's level) from the Royal Bank.</t>
   </si>
   <si>
-    <t>Take one of your unused leaders and place it on the Recruit space of the Province. Explain you want to get some Troops, so you will pay  2 Coins to the people of your Province. Put 2 Coins in the pile, not the Royal Bank, and take 2 Troops. Explain that the Coins do not go to the Royal Bank during Recruit.</t>
-  </si>
-  <si>
     <t>Take one of your unused leaders and place it on the Persian spaces of the Battlefield. Place 2 of your Troops in the same space. Explain you want to deploy 2 Troops to fight the Greeks. Since you are the player with the most Troops deployed, you will be the General at the end of the round and gain 1 Honor (Victory Point). Explain the king pays you for your Troops then take 1 Coin (half Troop count) from the Royal Bank.</t>
   </si>
   <si>
@@ -1207,12 +1174,6 @@
     <t>Deploy an unused leader and 2 Troops into the Battlefield then take 1 Coin from the Royal Bank. Explain you have Elite Troops which gets you more Coins during deployment then take 2 more Coins from the Royal Bank.</t>
   </si>
   <si>
-    <t>Place an unused leader on Prepare in the Court. Explain you want to know what the next few Laws are. You also have Legal Research, so look at any 4 Laws in the queue that are not your own. Explain you may not rearrange the Laws while looking at them.</t>
-  </si>
-  <si>
-    <t>Deploy 2 Troops and take 1 Coin from the Royal Bank.</t>
-  </si>
-  <si>
     <t>Place an unused leader on Brainstorm in the Province. Explain you want more cards then take a card from each deck for each level of your Leader (2 cards from each deck).</t>
   </si>
   <si>
@@ -1270,21 +1231,12 @@
     <t>6. There are still Greeks left, so we will play another round.</t>
   </si>
   <si>
-    <t>7. The king has many other financial interests and has made some money. I will add 3 Coins to the Royal Bank and adjust the Market Rate by 1 in a random direction. See rulebook for Market Rate adjustment details.</t>
-  </si>
-  <si>
     <t>8. I have the King's Favor, so I will start the next round.</t>
   </si>
   <si>
     <t>Scheme Instructions</t>
   </si>
   <si>
-    <t>At some point during the next round, place a Spy into the Scheme envelope with a Scheme card of your choice. Place a marker for the Warmongerer in the top left corner of the card and a marker for one of your Allies in the bottom right corner.</t>
-  </si>
-  <si>
-    <t>At some point during the next round, place a Spy into the Scheme envelope with a Scheme card of your choice. Place a marker for the Chief Scribe in the top left corner of the card and a your own marker in the bottom right corner.</t>
-  </si>
-  <si>
     <t>You are doing great! Keep up the good work.</t>
   </si>
   <si>
@@ -1477,9 +1429,6 @@
     <t>Heavy Overtime</t>
   </si>
   <si>
-    <t>Assassination</t>
-  </si>
-  <si>
     <t>Courtroom Gambling</t>
   </si>
   <si>
@@ -1561,9 +1510,6 @@
     <t>If Greeks are victorious, give remaining attacking Greeks to the player who deployed the fewest Troops (break ties with deployment order then with a Tie Trial or agreement). That player destroys 1 Troop per attacking Greek or downgrades 1 investment by $D6 levels if they have no Troops.</t>
   </si>
   <si>
-    <t>Exchange one Alliance Token with $R</t>
-  </si>
-  <si>
     <t>Give $D6 Spies to $R</t>
   </si>
   <si>
@@ -1576,9 +1522,6 @@
     <t>Give $D6 random Cards of each type from your hand to $R</t>
   </si>
   <si>
-    <t>Rearrange the first $D6 Law cards in the Queue</t>
-  </si>
-  <si>
     <t>Downgrade an Investment by $D6 levels</t>
   </si>
   <si>
@@ -1597,18 +1540,12 @@
     <t>Move $D6 of your Laws each one space back in the Queue</t>
   </si>
   <si>
-    <t>Intimidation</t>
-  </si>
-  <si>
     <t>Humiliation</t>
   </si>
   <si>
     <t>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</t>
   </si>
   <si>
-    <t>Give $2D6 Commodities to $R. Perform an Emergency Trade if needed.</t>
-  </si>
-  <si>
     <t>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</t>
   </si>
   <si>
@@ -1619,6 +1556,117 @@
   </si>
   <si>
     <t>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</t>
+  </si>
+  <si>
+    <t>Deploy 2 Troops for no Coins.</t>
+  </si>
+  <si>
+    <t>Court Sell for 2 Coins</t>
+  </si>
+  <si>
+    <t>7. The king has many other financial interests and has made some money. I will add 3 Coins to the Royal Bank and adjust the Market Rate by 1 in a random direction. See rulebook for Market Rate adjustment details. Roll until Market Rate increases to 3.</t>
+  </si>
+  <si>
+    <t>At some point during the next round, place a Spy into the Scheme envelope with Corporate Takeover. Place a marker for the Warmongerer in the top left corner of the card and a marker for one of your Allies in the bottom right corner.</t>
+  </si>
+  <si>
+    <t>At some point during the next round, place a Spy into the Scheme envelope with Intimidation. Place a marker for the Chief Scribe in the top left corner of the card.</t>
+  </si>
+  <si>
+    <t>Private Sell for 3 Coins</t>
+  </si>
+  <si>
+    <t>Flatter for 3 Coins</t>
+  </si>
+  <si>
+    <t>Infiltrate 3 Spies</t>
+  </si>
+  <si>
+    <t>Take one of your unused leaders and place it on the Recruit space of the Province. Explain you want to get some Troops, so you will pay  2 Coins to the people of your Province. Put 2 Coins in the pile, not the Royal Bank, and take 2 Troops + 1. Explain that the Coins do not go to the Royal Bank during Recruit.</t>
+  </si>
+  <si>
+    <t>Deploy $L3 additional Troops during Deploy</t>
+  </si>
+  <si>
+    <t>Iron Command</t>
+  </si>
+  <si>
+    <t>Build Level 2 Investment (Loyal Citizenry )</t>
+  </si>
+  <si>
+    <t>Negotiate with Veteran</t>
+  </si>
+  <si>
+    <t>Build Level 2 Investment (Soup Kitchens)</t>
+  </si>
+  <si>
+    <t>Increase Market Rate at Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You may keep up to $L6 additional Coins when Taxing other Players </t>
+  </si>
+  <si>
+    <t>Undermarket Monetize with Law and Scheme cards for 2 Coins</t>
+  </si>
+  <si>
+    <t>Veteran schemes against Rival with himself as Receiver</t>
+  </si>
+  <si>
+    <t>Court Donate</t>
+  </si>
+  <si>
+    <t>Private Monetize</t>
+  </si>
+  <si>
+    <t>Undermarket Donate</t>
+  </si>
+  <si>
+    <t>Chief Scribe trades Undeniable Advisors with Veteran for Eager Youth using an Alliance Token</t>
+  </si>
+  <si>
+    <t>Assassination Attempt</t>
+  </si>
+  <si>
+    <t>Purchase up to $L6 additional Troops during Recruit (at normal cost)</t>
+  </si>
+  <si>
+    <t>Localized Famine</t>
+  </si>
+  <si>
+    <t>Lose half your Commodities</t>
+  </si>
+  <si>
+    <t>Highway Robbery</t>
+  </si>
+  <si>
+    <t>Lose half your Coins</t>
+  </si>
+  <si>
+    <t>Camp Plague</t>
+  </si>
+  <si>
+    <t>Lose half your Troops</t>
+  </si>
+  <si>
+    <t>Weakening Grip</t>
+  </si>
+  <si>
+    <t>Lose half your Spies</t>
+  </si>
+  <si>
+    <t>Corporate Espionage</t>
+  </si>
+  <si>
+    <t>Disard half your cards of each type</t>
+  </si>
+  <si>
+    <t>Culture Shift</t>
+  </si>
+  <si>
+    <t>Blatant Extortion</t>
+  </si>
+  <si>
+    <t>Give $2D6 Commodities to $R</t>
   </si>
 </sst>
 </file>
@@ -1629,7 +1677,7 @@
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1638,21 +1686,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1681,14 +1715,6 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FFFFFF66"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1699,6 +1725,22 @@
       <b/>
       <sz val="16"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFEFBF04"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFEFBF04"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1719,19 +1761,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE269"/>
+        <fgColor rgb="FFCC3333"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE5CDA9"/>
+        <fgColor rgb="FF1C39BB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor rgb="FFEFBF04"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2543,7 +2585,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2620,29 +2662,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2702,32 +2744,20 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="180" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2756,16 +2786,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
@@ -2781,16 +2811,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
@@ -2823,74 +2853,98 @@
       </extLst>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2900,6 +2954,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FFEFBF04"/>
+      <color rgb="FFCC3333"/>
+      <color rgb="FF1C39BB"/>
       <color rgb="FFFFFF66"/>
       <color rgb="FFE5CDA9"/>
       <color rgb="FFFFE269"/>
@@ -3414,7 +3471,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFE269"/>
+          <a:srgbClr val="EFBF04"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:noFill/>
@@ -3485,7 +3542,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFE269"/>
+          <a:srgbClr val="EFBF04"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:noFill/>
@@ -3552,7 +3609,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="FFE269"/>
+          <a:srgbClr val="EFBF04"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:noFill/>
@@ -4060,7 +4117,7 @@
     <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
@@ -4115,7 +4172,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
@@ -4126,22 +4183,22 @@
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" s="6" t="s">
-        <v>17</v>
+        <v>539</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
@@ -4149,25 +4206,25 @@
     </row>
     <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="E4" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="G4" s="7" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="3"/>
@@ -4175,25 +4232,25 @@
     </row>
     <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="E5" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="G5" s="7" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
@@ -4201,25 +4258,25 @@
     </row>
     <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="E6" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>32</v>
-      </c>
       <c r="F6" s="6" t="s">
-        <v>33</v>
+        <v>536</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>521</v>
+        <v>491</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3"/>
@@ -4227,25 +4284,25 @@
     </row>
     <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="E7" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>38</v>
-      </c>
       <c r="F7" s="6" t="s">
-        <v>39</v>
+        <v>528</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3"/>
@@ -4253,25 +4310,25 @@
     </row>
     <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>509</v>
+        <v>530</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>531</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
@@ -4279,25 +4336,25 @@
     </row>
     <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>48</v>
+        <v>532</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>510</v>
+        <v>533</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
@@ -4305,25 +4362,25 @@
     </row>
     <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>51</v>
+        <v>527</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>52</v>
+        <v>534</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
@@ -4331,25 +4388,25 @@
     </row>
     <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>57</v>
+        <v>538</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="2"/>
@@ -4357,25 +4414,25 @@
     </row>
     <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="2"/>
@@ -4383,25 +4440,25 @@
     </row>
     <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
@@ -4409,25 +4466,25 @@
     </row>
     <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>477</v>
+        <v>46</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>513</v>
+        <v>492</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
@@ -4435,25 +4492,25 @@
     </row>
     <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3"/>
@@ -4461,25 +4518,25 @@
     </row>
     <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="2"/>
@@ -4487,25 +4544,25 @@
     </row>
     <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="2"/>
@@ -4513,25 +4570,25 @@
     </row>
     <row r="18" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>92</v>
+        <v>36</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
@@ -4539,25 +4596,25 @@
     </row>
     <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
@@ -4565,25 +4622,25 @@
     </row>
     <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>516</v>
+        <v>497</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
@@ -4591,25 +4648,25 @@
     </row>
     <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
@@ -4617,85 +4674,89 @@
     </row>
     <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="7"/>
+        <v>443</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>500</v>
+      </c>
       <c r="H22" s="4"/>
       <c r="I22" s="3"/>
       <c r="J22" s="4"/>
     </row>
     <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F23" s="6"/>
-      <c r="G23" s="9"/>
+      <c r="G23" s="7"/>
       <c r="H23" s="4"/>
       <c r="I23" s="3"/>
       <c r="J23" s="4"/>
     </row>
     <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F24" s="6"/>
-      <c r="G24" s="7"/>
+      <c r="G24" s="9"/>
       <c r="H24" s="4"/>
       <c r="I24" s="3"/>
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
@@ -4705,19 +4766,19 @@
     </row>
     <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4727,19 +4788,19 @@
     </row>
     <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4749,19 +4810,19 @@
     </row>
     <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>524</v>
+        <v>503</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4771,19 +4832,19 @@
     </row>
     <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4793,19 +4854,19 @@
     </row>
     <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7"/>
@@ -4815,19 +4876,19 @@
     </row>
     <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7"/>
@@ -4837,19 +4898,19 @@
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -4859,19 +4920,19 @@
     </row>
     <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -4881,13 +4942,13 @@
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="16"/>
@@ -4899,13 +4960,13 @@
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="16"/>
@@ -4917,13 +4978,13 @@
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4935,13 +4996,13 @@
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -4953,13 +5014,13 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -4971,13 +5032,13 @@
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -4989,13 +5050,13 @@
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="16"/>
@@ -5005,12 +5066,16 @@
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="16"/>
+        <v>156</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>513</v>
+      </c>
       <c r="D41" s="6"/>
       <c r="E41" s="16"/>
       <c r="F41" s="6"/>
@@ -5021,7 +5086,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="16"/>
@@ -5035,7 +5100,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="16"/>
@@ -5049,7 +5114,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="16"/>
@@ -5063,7 +5128,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="16"/>
@@ -5077,7 +5142,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="16"/>
@@ -5091,7 +5156,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="16"/>
@@ -5105,7 +5170,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="16"/>
@@ -5119,7 +5184,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="16"/>
@@ -5133,7 +5198,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="16"/>
@@ -5147,7 +5212,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="16"/>
@@ -5161,7 +5226,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="16"/>
@@ -5175,7 +5240,7 @@
     </row>
     <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B53" s="10"/>
       <c r="C53" s="17"/>
@@ -5189,7 +5254,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="0" firstPageNumber="0" fitToWidth="0" orientation="portrait" blackAndWhite="1" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup scale="37" firstPageNumber="0" fitToWidth="0" orientation="portrait" blackAndWhite="1" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5211,215 +5276,215 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="51" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B1" s="52" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D1" s="54" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E1" s="54" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="F1" s="54" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G1" s="54" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="H1" s="54" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I1" s="55" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="47" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E2" s="50" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="F2" s="50" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="G2" s="50" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="H2" s="50" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>523</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="C3" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>334</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="G3" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="D3" s="42" t="s">
-        <v>344</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>192</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>193</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>194</v>
-      </c>
       <c r="H3" s="42" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="I3" s="42" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D4" s="42" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="G4" s="42" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="H4" s="42" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="I4" s="45"/>
     </row>
     <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G5" s="42" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="H5" s="42" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="I5" s="45"/>
     </row>
     <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A6" s="37" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="F6" s="42" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="H6" s="42" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="I6" s="45"/>
     </row>
     <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H7" s="42"/>
       <c r="I7" s="45"/>
     </row>
     <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
@@ -5427,22 +5492,22 @@
     </row>
     <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
@@ -5450,19 +5515,19 @@
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
@@ -5471,17 +5536,17 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="42" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
@@ -5490,17 +5555,17 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D12" s="42"/>
       <c r="E12" s="42" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="F12" s="44"/>
       <c r="G12" s="42"/>
@@ -5509,17 +5574,17 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D13" s="42"/>
       <c r="E13" s="42" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="F13" s="44"/>
       <c r="G13" s="42"/>
@@ -5528,17 +5593,17 @@
     </row>
     <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D14" s="42"/>
       <c r="E14" s="42" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="42"/>
@@ -5547,13 +5612,13 @@
     </row>
     <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="42"/>
@@ -5564,13 +5629,13 @@
     </row>
     <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D16" s="42"/>
       <c r="E16" s="42"/>
@@ -5581,13 +5646,13 @@
     </row>
     <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D17" s="42"/>
       <c r="E17" s="42"/>
@@ -5598,13 +5663,13 @@
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="42"/>
@@ -5615,13 +5680,13 @@
     </row>
     <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="42"/>
@@ -5632,13 +5697,13 @@
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
@@ -5649,13 +5714,13 @@
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
@@ -5666,13 +5731,13 @@
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -5683,13 +5748,13 @@
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D23" s="42"/>
       <c r="E23" s="42"/>
@@ -5700,13 +5765,13 @@
     </row>
     <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="42"/>
@@ -5717,13 +5782,13 @@
     </row>
     <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D25" s="43"/>
       <c r="E25" s="43"/>
@@ -5734,6 +5799,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5747,707 +5813,703 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="72"/>
-      <c r="B1" s="65" t="s">
+      <c r="A1" s="68"/>
+      <c r="B1" s="61" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>246</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>248</v>
+      </c>
+      <c r="G1" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="I1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="70" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2" s="65" t="s">
+        <v>131</v>
+      </c>
+      <c r="I2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="70" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="72" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>449</v>
+      </c>
+      <c r="E3" s="62" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="G3" s="62" t="s">
+        <v>144</v>
+      </c>
+      <c r="I3" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="70" t="s">
         <v>252</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="B4" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="62" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" s="62" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="62" t="s">
+        <v>120</v>
+      </c>
+      <c r="G4" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="I4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="70" t="s">
         <v>253</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="B5" s="69" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="69" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="93" t="s">
         <v>254</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="B6" s="94" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="95" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="96" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="97" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="96" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="98" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="73" t="s">
         <v>255</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="B7" s="73" t="s">
         <v>256</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="C7" s="70" t="s">
+        <v>355</v>
+      </c>
+      <c r="D7" t="s">
         <v>257</v>
       </c>
-      <c r="I1" t="s">
+      <c r="E7" s="70" t="s">
+        <v>258</v>
+      </c>
+      <c r="F7" t="s">
+        <v>259</v>
+      </c>
+      <c r="G7" s="70" t="s">
+        <v>176</v>
+      </c>
+      <c r="I7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="91" t="s">
+        <v>307</v>
+      </c>
+      <c r="B8" s="91" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="87" t="s">
+        <v>248</v>
+      </c>
+      <c r="D8" s="91" t="s">
+        <v>249</v>
+      </c>
+      <c r="E8" s="87" t="s">
+        <v>244</v>
+      </c>
+      <c r="F8" s="91" t="s">
+        <v>245</v>
+      </c>
+      <c r="G8" s="88" t="s">
+        <v>246</v>
+      </c>
+      <c r="I8" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="59" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
-        <v>258</v>
-      </c>
-      <c r="B2" s="75" t="s">
-        <v>103</v>
-      </c>
-      <c r="C2" s="68" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="69" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="69" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" s="63" t="s">
-        <v>117</v>
-      </c>
-      <c r="G2" s="69" t="s">
-        <v>139</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="B9" s="59" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>245</v>
+      </c>
+      <c r="E9" t="s">
+        <v>249</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" s="72" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="92" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
-        <v>259</v>
-      </c>
-      <c r="B3" s="76" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="F3" s="63" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="66" t="s">
-        <v>152</v>
-      </c>
-      <c r="I3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
-        <v>260</v>
-      </c>
-      <c r="B4" s="67" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="67" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="66" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="66" t="s">
-        <v>128</v>
-      </c>
-      <c r="G4" s="66" t="s">
-        <v>132</v>
-      </c>
-      <c r="I4" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="74" t="s">
-        <v>261</v>
-      </c>
-      <c r="B5" s="73" t="s">
-        <v>157</v>
-      </c>
-      <c r="C5" s="73" t="s">
-        <v>70</v>
-      </c>
-      <c r="D5" s="70" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="70" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" s="70" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" s="71" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="97" t="s">
-        <v>262</v>
-      </c>
-      <c r="B6" s="98" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="99" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="100" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" s="101" t="s">
-        <v>130</v>
-      </c>
-      <c r="F6" s="100" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="102" t="s">
-        <v>137</v>
-      </c>
-      <c r="I6" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="77" t="s">
-        <v>263</v>
-      </c>
-      <c r="B7" s="77" t="s">
-        <v>264</v>
-      </c>
-      <c r="C7" s="74" t="s">
-        <v>365</v>
-      </c>
-      <c r="D7" t="s">
-        <v>265</v>
-      </c>
-      <c r="E7" s="74" t="s">
-        <v>266</v>
-      </c>
-      <c r="F7" t="s">
-        <v>267</v>
-      </c>
-      <c r="G7" s="74" t="s">
-        <v>184</v>
-      </c>
-      <c r="I7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="95" t="s">
-        <v>316</v>
-      </c>
-      <c r="B8" s="95" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" s="91" t="s">
-        <v>256</v>
-      </c>
-      <c r="D8" s="95" t="s">
-        <v>257</v>
-      </c>
-      <c r="E8" s="91" t="s">
-        <v>252</v>
-      </c>
-      <c r="F8" s="95" t="s">
-        <v>253</v>
-      </c>
-      <c r="G8" s="92" t="s">
-        <v>254</v>
-      </c>
-      <c r="I8" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="63" t="s">
-        <v>317</v>
-      </c>
-      <c r="B9" s="63" t="s">
-        <v>256</v>
-      </c>
-      <c r="C9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D9" s="63" t="s">
-        <v>253</v>
-      </c>
-      <c r="E9" t="s">
-        <v>257</v>
-      </c>
-      <c r="F9" s="63" t="s">
-        <v>252</v>
-      </c>
-      <c r="G9" s="76" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="96" t="s">
-        <v>318</v>
-      </c>
-      <c r="B10" s="96" t="s">
-        <v>254</v>
-      </c>
-      <c r="C10" s="93" t="s">
-        <v>257</v>
-      </c>
-      <c r="D10" s="96" t="s">
-        <v>252</v>
-      </c>
-      <c r="E10" s="93" t="s">
-        <v>256</v>
-      </c>
-      <c r="F10" s="96" t="s">
-        <v>255</v>
-      </c>
-      <c r="G10" s="94" t="s">
-        <v>253</v>
+      <c r="B10" s="92" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="89" t="s">
+        <v>249</v>
+      </c>
+      <c r="D10" s="92" t="s">
+        <v>244</v>
+      </c>
+      <c r="E10" s="89" t="s">
+        <v>248</v>
+      </c>
+      <c r="F10" s="92" t="s">
+        <v>247</v>
+      </c>
+      <c r="G10" s="90" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="2" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E22" s="2"/>
+        <v>365</v>
+      </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>382</v>
+        <v>512</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="2" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>387</v>
+        <v>323</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>388</v>
+        <v>504</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="345" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>399</v>
+        <v>203</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>408</v>
+        <v>506</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="195" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>395</v>
+      </c>
       <c r="D28" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>411</v>
+        <v>507</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>412</v>
+        <v>508</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>327</v>
+        <v>203</v>
+      </c>
+      <c r="C30" t="s">
+        <v>398</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="I30" t="s">
         <v>322</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="I30" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>227</v>
+        <v>505</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>223</v>
+        <v>325</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="2" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>329</v>
+        <v>511</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>333</v>
+        <v>313</v>
+      </c>
+      <c r="E32" t="s">
+        <v>215</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>322</v>
+        <v>444</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="2" t="s">
-        <v>333</v>
+        <v>515</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>185</v>
+        <v>312</v>
+      </c>
+      <c r="D33" t="s">
+        <v>516</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>321</v>
+        <v>517</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+        <v>337</v>
+      </c>
       <c r="G34" s="2"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -6460,106 +6522,101 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>218</v>
+        <v>368</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
+      <c r="I36" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>378</v>
-      </c>
       <c r="B37" s="2" t="s">
-        <v>227</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>341</v>
+        <v>210</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>336</v>
+        <v>520</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="I37" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>227</v>
+        <v>331</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>227</v>
+        <v>409</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="I38" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
+      <c r="B39" s="2" t="s">
+        <v>523</v>
+      </c>
       <c r="C39" s="2" t="s">
-        <v>339</v>
+        <v>236</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>425</v>
+        <v>219</v>
+      </c>
+      <c r="E39" t="s">
+        <v>522</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="I39" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2" t="s">
-        <v>341</v>
+      <c r="C40" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>524</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="G40" s="2"/>
       <c r="I40" t="s">
-        <v>343</v>
+        <v>521</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -6567,9 +6624,12 @@
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
+      <c r="E41" s="2"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
+      <c r="I41" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
@@ -6599,165 +6659,165 @@
     </row>
     <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="G50" s="2"/>
     </row>
     <row r="52" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="E54" s="2" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -6773,80 +6833,80 @@
     </row>
     <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="2" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
@@ -6856,6 +6916,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6874,66 +6935,66 @@
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="32" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="E1" s="110" t="s">
-        <v>186</v>
+        <v>331</v>
+      </c>
+      <c r="E1" s="106" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="31" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="E2" s="111"/>
+        <v>203</v>
+      </c>
+      <c r="E2" s="107"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3" s="30" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="E3" s="111"/>
+        <v>218</v>
+      </c>
+      <c r="E3" s="107"/>
     </row>
     <row r="4" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A4" s="34" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="C4" s="61" t="s">
-        <v>239</v>
+        <v>229</v>
+      </c>
+      <c r="C4" s="57" t="s">
+        <v>231</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>483</v>
-      </c>
-      <c r="E4" s="62" t="s">
-        <v>235</v>
+        <v>466</v>
+      </c>
+      <c r="E4" s="58" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -6941,8 +7002,8 @@
     <mergeCell ref="E1:E3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6960,46 +7021,46 @@
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="E1" s="112" t="s">
-        <v>243</v>
+        <v>238</v>
+      </c>
+      <c r="E1" s="108" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="D2" s="109" t="s">
-        <v>483</v>
-      </c>
-      <c r="E2" s="113"/>
+        <v>231</v>
+      </c>
+      <c r="D2" s="105" t="s">
+        <v>466</v>
+      </c>
+      <c r="E2" s="109"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="57" t="s">
-        <v>268</v>
-      </c>
-      <c r="B3" s="114" t="s">
-        <v>269</v>
-      </c>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="116"/>
+      <c r="A3" s="132" t="s">
+        <v>260</v>
+      </c>
+      <c r="B3" s="133" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="135"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7007,8 +7068,8 @@
     <mergeCell ref="B3:E3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7022,1945 +7083,1985 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60">
-        <v>0</v>
-      </c>
-      <c r="B1" s="60">
+      <c r="A1" s="110">
+        <v>0</v>
+      </c>
+      <c r="B1" s="111"/>
+      <c r="C1" s="110">
         <v>1</v>
       </c>
-      <c r="C1" s="60">
+      <c r="D1" s="111"/>
+      <c r="E1" s="110">
         <v>2</v>
       </c>
-      <c r="D1" s="60">
+      <c r="F1" s="111"/>
+      <c r="G1" s="110">
         <v>3</v>
       </c>
-      <c r="E1" s="60">
+      <c r="H1" s="111"/>
+      <c r="I1" s="110">
         <v>4</v>
       </c>
-      <c r="F1" s="60">
+      <c r="J1" s="111"/>
+      <c r="K1" s="110">
         <v>5</v>
       </c>
-      <c r="G1" s="60">
+      <c r="L1" s="111"/>
+      <c r="M1" s="110">
         <v>6</v>
       </c>
-      <c r="H1" s="60">
+      <c r="N1" s="111"/>
+    </row>
+    <row r="2" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="112">
+        <v>19</v>
+      </c>
+      <c r="B2" s="114" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" s="115"/>
+      <c r="D2" s="115"/>
+      <c r="E2" s="115"/>
+      <c r="F2" s="115"/>
+      <c r="G2" s="115"/>
+      <c r="H2" s="115"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="115"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="112">
         <v>7</v>
       </c>
-      <c r="I1" s="60">
+    </row>
+    <row r="3" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="113"/>
+      <c r="B3" s="117"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="118"/>
+      <c r="K3" s="118"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="119"/>
+      <c r="N3" s="113"/>
+    </row>
+    <row r="4" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="112">
+        <v>18</v>
+      </c>
+      <c r="B4" s="120"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
+      <c r="L4" s="121"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="112">
         <v>8</v>
       </c>
-      <c r="J1" s="60">
-        <v>9</v>
-      </c>
-      <c r="K1" s="60">
-        <v>10</v>
-      </c>
-      <c r="L1" s="60">
-        <v>11</v>
-      </c>
-      <c r="M1" s="60">
-        <v>12</v>
-      </c>
-      <c r="N1" s="60">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="60">
-        <v>39</v>
-      </c>
-      <c r="B2" s="119" t="s">
-        <v>270</v>
-      </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-      <c r="I2" s="120"/>
-      <c r="J2" s="120"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="120"/>
-      <c r="M2" s="120"/>
-      <c r="N2" s="60">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="60">
-        <v>38</v>
-      </c>
-      <c r="B3" s="121"/>
-      <c r="C3" s="122"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="122"/>
-      <c r="F3" s="122"/>
-      <c r="G3" s="122"/>
-      <c r="H3" s="122"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="60">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="60">
-        <v>37</v>
-      </c>
-      <c r="B4" s="117" t="s">
-        <v>271</v>
-      </c>
-      <c r="C4" s="118"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="60">
-        <v>16</v>
-      </c>
     </row>
     <row r="5" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="60">
-        <v>36</v>
-      </c>
+      <c r="A5" s="113"/>
       <c r="B5" s="123" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C5" s="124"/>
-      <c r="D5" s="127" t="s">
-        <v>272</v>
-      </c>
-      <c r="E5" s="128"/>
-      <c r="F5" s="127" t="s">
-        <v>272</v>
-      </c>
-      <c r="G5" s="128"/>
-      <c r="H5" s="127" t="s">
-        <v>272</v>
-      </c>
-      <c r="I5" s="128"/>
-      <c r="J5" s="127" t="s">
-        <v>272</v>
-      </c>
-      <c r="K5" s="128"/>
-      <c r="L5" s="127" t="s">
-        <v>272</v>
-      </c>
-      <c r="M5" s="131"/>
-      <c r="N5" s="60">
+      <c r="D5" s="125" t="s">
+        <v>263</v>
+      </c>
+      <c r="E5" s="126"/>
+      <c r="F5" s="125" t="s">
+        <v>263</v>
+      </c>
+      <c r="G5" s="126"/>
+      <c r="H5" s="125" t="s">
+        <v>263</v>
+      </c>
+      <c r="I5" s="126"/>
+      <c r="J5" s="125" t="s">
+        <v>263</v>
+      </c>
+      <c r="K5" s="126"/>
+      <c r="L5" s="125" t="s">
+        <v>263</v>
+      </c>
+      <c r="M5" s="127"/>
+      <c r="N5" s="113"/>
+    </row>
+    <row r="6" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="112">
         <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="60">
-        <v>35</v>
       </c>
       <c r="B6" s="123"/>
       <c r="C6" s="124"/>
       <c r="D6" s="123"/>
-      <c r="E6" s="129"/>
+      <c r="E6" s="128"/>
       <c r="F6" s="123"/>
-      <c r="G6" s="129"/>
+      <c r="G6" s="128"/>
       <c r="H6" s="123"/>
-      <c r="I6" s="129"/>
+      <c r="I6" s="128"/>
       <c r="J6" s="123"/>
-      <c r="K6" s="129"/>
+      <c r="K6" s="128"/>
       <c r="L6" s="123"/>
       <c r="M6" s="124"/>
-      <c r="N6" s="60">
-        <v>18</v>
+      <c r="N6" s="112">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="60">
-        <v>34</v>
-      </c>
-      <c r="B7" s="125"/>
-      <c r="C7" s="126"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="125"/>
-      <c r="M7" s="126"/>
-      <c r="N7" s="60">
-        <v>19</v>
-      </c>
+      <c r="A7" s="113"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="131"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="131"/>
+      <c r="J7" s="129"/>
+      <c r="K7" s="131"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="113"/>
     </row>
     <row r="8" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="60">
-        <v>33</v>
-      </c>
-      <c r="B8" s="60">
-        <v>32</v>
-      </c>
-      <c r="C8" s="60">
-        <v>31</v>
-      </c>
-      <c r="D8" s="60">
-        <v>30</v>
-      </c>
-      <c r="E8" s="60">
-        <v>29</v>
-      </c>
-      <c r="F8" s="60">
-        <v>28</v>
-      </c>
-      <c r="G8" s="60">
-        <v>27</v>
-      </c>
-      <c r="H8" s="60">
-        <v>26</v>
-      </c>
-      <c r="I8" s="60">
-        <v>25</v>
-      </c>
-      <c r="J8" s="60">
-        <v>24</v>
-      </c>
-      <c r="K8" s="60">
-        <v>23</v>
-      </c>
-      <c r="L8" s="60">
-        <v>22</v>
-      </c>
-      <c r="M8" s="58">
-        <v>21</v>
-      </c>
-      <c r="N8" s="59">
-        <v>20</v>
-      </c>
+      <c r="A8" s="110">
+        <v>16</v>
+      </c>
+      <c r="B8" s="111"/>
+      <c r="C8" s="110">
+        <v>15</v>
+      </c>
+      <c r="D8" s="111"/>
+      <c r="E8" s="110">
+        <v>14</v>
+      </c>
+      <c r="F8" s="111"/>
+      <c r="G8" s="110">
+        <v>13</v>
+      </c>
+      <c r="H8" s="111"/>
+      <c r="I8" s="110">
+        <v>12</v>
+      </c>
+      <c r="J8" s="111"/>
+      <c r="K8" s="110">
+        <v>11</v>
+      </c>
+      <c r="L8" s="111"/>
+      <c r="M8" s="110">
+        <v>10</v>
+      </c>
+      <c r="N8" s="111"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B4:M4"/>
-    <mergeCell ref="B2:M3"/>
+  <mergeCells count="27">
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="B5:C7"/>
     <mergeCell ref="D5:E7"/>
     <mergeCell ref="F5:G7"/>
     <mergeCell ref="H5:I7"/>
     <mergeCell ref="J5:K7"/>
     <mergeCell ref="L5:M7"/>
+    <mergeCell ref="B2:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CEB427C-0CB4-4E8D-8367-36F6DD891282}">
-  <dimension ref="A1:BS6"/>
+  <dimension ref="A1:CA6"/>
   <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" style="63"/>
-    <col min="2" max="2" width="19.7109375" style="76"/>
-    <col min="4" max="4" width="19.7109375" style="63"/>
-    <col min="6" max="6" width="19.7109375" style="63"/>
-    <col min="8" max="8" width="19.7109375" style="63"/>
-    <col min="10" max="10" width="19.7109375" style="63"/>
-    <col min="12" max="12" width="19.7109375" style="63"/>
-    <col min="14" max="14" width="19.7109375" style="63"/>
-    <col min="16" max="16" width="19.7109375" style="63"/>
-    <col min="18" max="18" width="19.7109375" style="63"/>
-    <col min="20" max="20" width="19.7109375" style="63"/>
-    <col min="22" max="22" width="19.7109375" style="63"/>
-    <col min="24" max="24" width="19.7109375" style="63"/>
-    <col min="26" max="26" width="19.7109375" style="63"/>
-    <col min="28" max="28" width="19.7109375" style="63"/>
-    <col min="30" max="30" width="19.7109375" style="82"/>
-    <col min="31" max="32" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" style="59"/>
+    <col min="2" max="2" width="19.7109375" style="72"/>
+    <col min="4" max="4" width="19.7109375" style="59"/>
+    <col min="6" max="6" width="19.7109375" style="59"/>
+    <col min="8" max="8" width="19.7109375" style="59"/>
+    <col min="10" max="10" width="19.7109375" style="59"/>
+    <col min="12" max="12" width="19.7109375" style="59"/>
+    <col min="14" max="14" width="19.7109375" style="59"/>
+    <col min="16" max="16" width="19.7109375" style="59"/>
+    <col min="18" max="18" width="19.7109375" style="59"/>
+    <col min="20" max="20" width="19.7109375" style="59"/>
+    <col min="22" max="22" width="19.7109375" style="59"/>
+    <col min="24" max="24" width="19.7109375" style="59"/>
+    <col min="26" max="26" width="19.7109375" style="59"/>
+    <col min="28" max="28" width="19.7109375" style="59"/>
+    <col min="30" max="30" width="19.7109375" style="78"/>
+    <col min="31" max="32" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="19.7109375" customWidth="1"/>
-    <col min="42" max="42" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.7109375" style="82" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.7109375" style="78" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="56" max="56" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="19.7109375" style="63" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="19.7109375" style="82" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="19.7109375" style="63"/>
-    <col min="63" max="63" width="19.7109375" style="63"/>
-    <col min="65" max="65" width="19.7109375" style="63"/>
-    <col min="67" max="67" width="19.7109375" style="63"/>
-    <col min="69" max="69" width="19.7109375" style="63"/>
-    <col min="71" max="71" width="19.7109375" style="63"/>
+    <col min="59" max="59" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19.7109375" style="78" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="19.7109375" style="59"/>
+    <col min="63" max="63" width="19.7109375" style="59"/>
+    <col min="65" max="65" width="19.7109375" style="59"/>
+    <col min="67" max="67" width="19.7109375" style="59"/>
+    <col min="69" max="70" width="19.7109375" style="59"/>
+    <col min="71" max="71" width="19.7109375" style="72"/>
+    <col min="73" max="73" width="19.7109375" style="59"/>
+    <col min="75" max="75" width="19.7109375" style="59"/>
+    <col min="77" max="77" width="19.7109375" style="59"/>
+    <col min="79" max="79" width="19.7109375" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:71" s="80" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="str">
+    <row r="1" spans="1:79" s="76" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="74" t="str">
         <f>Cards!B2</f>
         <v>Fillibuster</v>
       </c>
-      <c r="B1" s="79" t="str">
+      <c r="B1" s="75" t="str">
         <f>Cards!B3</f>
         <v>Skillful Orators</v>
       </c>
-      <c r="C1" s="80" t="str">
+      <c r="C1" s="76" t="str">
         <f>Cards!B4</f>
         <v>Collection Stations</v>
       </c>
-      <c r="D1" s="78" t="str">
+      <c r="D1" s="74" t="str">
         <f>Cards!B5</f>
         <v>Brown Nose</v>
       </c>
-      <c r="E1" s="80" t="str">
+      <c r="E1" s="76" t="str">
         <f>Cards!B6</f>
         <v>Mysterious Windfalls</v>
       </c>
-      <c r="F1" s="78" t="str">
+      <c r="F1" s="74" t="str">
         <f>Cards!B7</f>
         <v>Lobbyists</v>
       </c>
-      <c r="G1" s="80" t="str">
+      <c r="G1" s="76" t="str">
         <f>Cards!B8</f>
         <v>Eager Youth</v>
       </c>
-      <c r="H1" s="78" t="str">
+      <c r="H1" s="74" t="str">
         <f>Cards!B9</f>
         <v>Honorable Cause</v>
       </c>
-      <c r="I1" s="80" t="str">
+      <c r="I1" s="76" t="str">
         <f>Cards!B10</f>
         <v>Loyal Citizenry</v>
       </c>
-      <c r="J1" s="78" t="str">
+      <c r="J1" s="74" t="str">
         <f>Cards!B11</f>
         <v>Silvertounge</v>
       </c>
-      <c r="K1" s="80" t="str">
+      <c r="K1" s="76" t="str">
         <f>Cards!B12</f>
         <v>Royal Bribes</v>
       </c>
-      <c r="L1" s="78" t="str">
+      <c r="L1" s="74" t="str">
         <f>Cards!B13</f>
         <v>Courtroom Gambling</v>
       </c>
-      <c r="M1" s="80" t="str">
+      <c r="M1" s="76" t="str">
         <f>Cards!B14</f>
         <v>Market Niche</v>
       </c>
-      <c r="N1" s="78" t="str">
+      <c r="N1" s="74" t="str">
         <f>Cards!B15</f>
         <v>Genius Commanders</v>
       </c>
-      <c r="O1" s="80" t="str">
+      <c r="O1" s="76" t="str">
         <f>Cards!B16</f>
         <v>Damage Redemption</v>
       </c>
-      <c r="P1" s="78" t="str">
+      <c r="P1" s="74" t="str">
         <f>Cards!B17</f>
         <v>Undeniable Advisors</v>
       </c>
-      <c r="Q1" s="80" t="str">
+      <c r="Q1" s="76" t="str">
         <f>Cards!B18</f>
         <v>Heavy Overtime</v>
       </c>
-      <c r="R1" s="78" t="str">
+      <c r="R1" s="74" t="str">
         <f>Cards!B19</f>
         <v>Bulk Purchaser</v>
       </c>
-      <c r="S1" s="80" t="str">
+      <c r="S1" s="76" t="str">
         <f>Cards!B20</f>
         <v>Valuable Cargo</v>
       </c>
-      <c r="T1" s="78" t="str">
+      <c r="T1" s="74" t="str">
         <f>Cards!B21</f>
         <v>Elite Troops</v>
       </c>
-      <c r="U1" s="80" t="str">
+      <c r="U1" s="76" t="str">
         <f>Cards!B22</f>
         <v>Bazaar</v>
       </c>
-      <c r="V1" s="78" t="str">
+      <c r="V1" s="74" t="str">
         <f>Cards!B23</f>
         <v>Caravansaray</v>
       </c>
-      <c r="W1" s="80" t="str">
+      <c r="W1" s="76" t="str">
         <f>Cards!B24</f>
         <v>War Machines</v>
       </c>
-      <c r="X1" s="78" t="str">
+      <c r="X1" s="74" t="str">
         <f>Cards!B25</f>
         <v>Mock Trials</v>
       </c>
-      <c r="Y1" s="80" t="str">
+      <c r="Y1" s="76" t="str">
         <f>Cards!B26</f>
         <v>Desperate Attorneys</v>
       </c>
-      <c r="Z1" s="78" t="str">
+      <c r="Z1" s="74" t="str">
         <f>Cards!B27</f>
         <v>Eager Laborers</v>
       </c>
-      <c r="AA1" s="80" t="str">
+      <c r="AA1" s="76" t="str">
         <f>Cards!B28</f>
         <v>Wary Guards</v>
       </c>
-      <c r="AB1" s="78" t="str">
+      <c r="AB1" s="74" t="str">
         <f>Cards!B29</f>
         <v>Information Security</v>
       </c>
-      <c r="AC1" s="80" t="str">
+      <c r="AC1" s="76" t="str">
         <f>Cards!B30</f>
         <v>Blood Pact</v>
       </c>
-      <c r="AD1" s="81" t="str">
+      <c r="AD1" s="77" t="str">
         <f>Cards!B31</f>
         <v>Expert Broker</v>
       </c>
-      <c r="AE1" s="78" t="str">
+      <c r="AE1" s="74" t="str">
         <f>Cards!B32</f>
         <v>Codependent Relationship</v>
       </c>
-      <c r="AF1" s="78" t="str">
+      <c r="AF1" s="74" t="str">
         <f>Cards!B33</f>
         <v>Dangerous Promises</v>
       </c>
-      <c r="AG1" s="80" t="str">
+      <c r="AG1" s="76" t="str">
         <f>Cards!B34</f>
         <v>Large Middle Class</v>
       </c>
-      <c r="AH1" s="78" t="str">
+      <c r="AH1" s="74" t="str">
         <f>Cards!B35</f>
         <v>Innovation Hub</v>
       </c>
-      <c r="AI1" s="80" t="str">
+      <c r="AI1" s="76" t="str">
         <f>Cards!B36</f>
         <v>Fire Temple</v>
       </c>
-      <c r="AJ1" s="78" t="str">
+      <c r="AJ1" s="74" t="str">
         <f>Cards!B37</f>
         <v>Kingdom Advocates</v>
       </c>
-      <c r="AK1" s="80" t="str">
+      <c r="AK1" s="76" t="str">
         <f>Cards!B38</f>
         <v>Soup Kitchens</v>
       </c>
-      <c r="AL1" s="78" t="str">
+      <c r="AL1" s="74" t="str">
         <f>Cards!B39</f>
         <v>Abusive Power</v>
       </c>
-      <c r="AM1" s="80" t="str">
+      <c r="AM1" s="76" t="str">
         <f>Cards!B40</f>
         <v>Painful Progress</v>
       </c>
-      <c r="AN1" s="78" t="str">
-        <f t="shared" ref="AN1:AW2" si="0">A1</f>
+      <c r="AN1" s="74" t="str">
+        <f>Cards!B41</f>
+        <v>Iron Command</v>
+      </c>
+      <c r="AO1" s="76" t="str">
+        <f t="shared" ref="AO1:AX2" si="0">A1</f>
         <v>Fillibuster</v>
       </c>
-      <c r="AO1" s="80" t="str">
+      <c r="AP1" s="74" t="str">
         <f t="shared" si="0"/>
         <v>Skillful Orators</v>
       </c>
-      <c r="AP1" s="78" t="str">
+      <c r="AQ1" s="76" t="str">
         <f t="shared" si="0"/>
         <v>Collection Stations</v>
       </c>
-      <c r="AQ1" s="80" t="str">
+      <c r="AR1" s="74" t="str">
         <f t="shared" si="0"/>
         <v>Brown Nose</v>
       </c>
-      <c r="AR1" s="78" t="str">
+      <c r="AS1" s="76" t="str">
         <f t="shared" si="0"/>
         <v>Mysterious Windfalls</v>
       </c>
-      <c r="AS1" s="80" t="str">
+      <c r="AT1" s="74" t="str">
         <f t="shared" si="0"/>
         <v>Lobbyists</v>
       </c>
-      <c r="AT1" s="78" t="str">
+      <c r="AU1" s="76" t="str">
         <f t="shared" si="0"/>
         <v>Eager Youth</v>
       </c>
-      <c r="AU1" s="80" t="str">
+      <c r="AV1" s="74" t="str">
         <f t="shared" si="0"/>
         <v>Honorable Cause</v>
       </c>
-      <c r="AV1" s="78" t="str">
+      <c r="AW1" s="76" t="str">
         <f t="shared" si="0"/>
         <v>Loyal Citizenry</v>
       </c>
-      <c r="AW1" s="80" t="str">
+      <c r="AX1" s="77" t="str">
         <f t="shared" si="0"/>
         <v>Silvertounge</v>
       </c>
-      <c r="AX1" s="81" t="str">
-        <f t="shared" ref="AX1:BG2" si="1">K1</f>
+      <c r="AY1" s="74" t="str">
+        <f t="shared" ref="AY1:BH2" si="1">K1</f>
         <v>Royal Bribes</v>
       </c>
-      <c r="AY1" s="78" t="str">
+      <c r="AZ1" s="76" t="str">
         <f t="shared" si="1"/>
         <v>Courtroom Gambling</v>
       </c>
-      <c r="AZ1" s="80" t="str">
+      <c r="BA1" s="74" t="str">
         <f t="shared" si="1"/>
         <v>Market Niche</v>
       </c>
-      <c r="BA1" s="78" t="str">
+      <c r="BB1" s="76" t="str">
         <f t="shared" si="1"/>
         <v>Genius Commanders</v>
       </c>
-      <c r="BB1" s="80" t="str">
+      <c r="BC1" s="74" t="str">
         <f t="shared" si="1"/>
         <v>Damage Redemption</v>
       </c>
-      <c r="BC1" s="78" t="str">
+      <c r="BD1" s="76" t="str">
         <f t="shared" si="1"/>
         <v>Undeniable Advisors</v>
       </c>
-      <c r="BD1" s="80" t="str">
+      <c r="BE1" s="74" t="str">
         <f t="shared" si="1"/>
         <v>Heavy Overtime</v>
       </c>
-      <c r="BE1" s="78" t="str">
+      <c r="BF1" s="76" t="str">
         <f t="shared" si="1"/>
         <v>Bulk Purchaser</v>
       </c>
-      <c r="BF1" s="80" t="str">
+      <c r="BG1" s="74" t="str">
         <f t="shared" si="1"/>
         <v>Valuable Cargo</v>
       </c>
-      <c r="BG1" s="78" t="str">
+      <c r="BH1" s="77" t="str">
         <f t="shared" si="1"/>
         <v>Elite Troops</v>
       </c>
-      <c r="BH1" s="81" t="str">
-        <f t="shared" ref="BH1:BP2" si="2">U1</f>
+      <c r="BI1" s="74" t="str">
+        <f t="shared" ref="BI1:BR2" si="2">U1</f>
         <v>Bazaar</v>
       </c>
-      <c r="BI1" s="78" t="str">
+      <c r="BJ1" s="76" t="str">
         <f t="shared" si="2"/>
         <v>Caravansaray</v>
       </c>
-      <c r="BJ1" s="80" t="str">
+      <c r="BK1" s="74" t="str">
         <f t="shared" si="2"/>
         <v>War Machines</v>
       </c>
-      <c r="BK1" s="78" t="str">
+      <c r="BL1" s="76" t="str">
         <f t="shared" si="2"/>
         <v>Mock Trials</v>
       </c>
-      <c r="BL1" s="80" t="str">
+      <c r="BM1" s="74" t="str">
         <f t="shared" si="2"/>
         <v>Desperate Attorneys</v>
       </c>
-      <c r="BM1" s="78" t="str">
+      <c r="BN1" s="76" t="str">
         <f t="shared" si="2"/>
         <v>Eager Laborers</v>
       </c>
-      <c r="BN1" s="80" t="str">
+      <c r="BO1" s="74" t="str">
         <f t="shared" si="2"/>
         <v>Wary Guards</v>
       </c>
-      <c r="BO1" s="78" t="str">
+      <c r="BP1" s="76" t="str">
         <f t="shared" si="2"/>
         <v>Information Security</v>
       </c>
-      <c r="BP1" s="80" t="str">
+      <c r="BQ1" s="74" t="str">
         <f t="shared" si="2"/>
         <v>Blood Pact</v>
       </c>
-      <c r="BQ1" s="78"/>
-      <c r="BS1" s="78"/>
-    </row>
-    <row r="2" spans="1:71" s="103" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="str">
+      <c r="BR1" s="74" t="str">
+        <f t="shared" si="2"/>
+        <v>Expert Broker</v>
+      </c>
+      <c r="BS1" s="74"/>
+      <c r="BU1" s="74"/>
+      <c r="BW1" s="74"/>
+      <c r="BY1" s="74"/>
+      <c r="CA1" s="74"/>
+    </row>
+    <row r="2" spans="1:79" s="99" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="100" t="str">
         <f>Cards!C2</f>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
       </c>
-      <c r="B2" s="104" t="str">
+      <c r="B2" s="100" t="str">
         <f>Cards!C3</f>
         <v>Move the Law $L6 additional places forward in the queue during Prioritize</v>
       </c>
-      <c r="C2" s="103" t="str">
+      <c r="C2" s="99" t="str">
         <f>Cards!C4</f>
-        <v xml:space="preserve">You may gain up to $L6 additional Coins when Taxing other Players </v>
-      </c>
-      <c r="D2" s="104" t="str">
+        <v xml:space="preserve">You may keep up to $L6 additional Coins when Taxing other Players </v>
+      </c>
+      <c r="D2" s="100" t="str">
         <f>Cards!C5</f>
         <v>Gain $L3 additional Coins during Flatter</v>
       </c>
-      <c r="E2" s="103" t="str">
+      <c r="E2" s="99" t="str">
         <f>Cards!C6</f>
         <v>Gain $L3 more Commodities per Coin when Buying from the Undermarket</v>
       </c>
-      <c r="F2" s="104" t="str">
+      <c r="F2" s="100" t="str">
         <f>Cards!C7</f>
         <v>Add $L3 additional Law cards to the bottom of the queue during Petition</v>
       </c>
-      <c r="G2" s="103" t="str">
+      <c r="G2" s="99" t="str">
         <f>Cards!C8</f>
         <v>Gain 1 additional Troop for free after Recruiting every 4 - $L3 Troops</v>
       </c>
-      <c r="H2" s="104" t="str">
+      <c r="H2" s="100" t="str">
         <f>Cards!C9</f>
         <v>Gain 1 additional Spy for free after Infiltrating every 4 - $L3 Spies</v>
       </c>
-      <c r="I2" s="104" t="str">
+      <c r="I2" s="100" t="str">
         <f>Cards!C10</f>
-        <v>Purchase up to $L6 additional Troops during Recruit</v>
-      </c>
-      <c r="J2" s="104" t="str">
+        <v>Purchase up to $L6 additional Troops during Recruit (at normal cost)</v>
+      </c>
+      <c r="J2" s="100" t="str">
         <f>Cards!C11</f>
         <v>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</v>
       </c>
-      <c r="K2" s="103" t="str">
+      <c r="K2" s="99" t="str">
         <f>Cards!C12</f>
         <v>Gain $L3 more Commodities per Coin when Buying from the Court</v>
       </c>
-      <c r="L2" s="104" t="str">
+      <c r="L2" s="100" t="str">
         <f>Cards!C13</f>
         <v>Gain $L3 additional Coins from outside the Royal Bank when winning a Sue</v>
       </c>
-      <c r="M2" s="103" t="str">
+      <c r="M2" s="99" t="str">
         <f>Cards!C14</f>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Undermarket</v>
       </c>
-      <c r="N2" s="104" t="str">
+      <c r="N2" s="100" t="str">
         <f>Cards!C15</f>
         <v>Draw $L6 additional cards from any decks during Brainstorm</v>
       </c>
-      <c r="O2" s="103" t="str">
+      <c r="O2" s="99" t="str">
         <f>Cards!C16</f>
         <v>Purchase $L3 Spies (at normal cost) when targeted by a Scheme</v>
       </c>
-      <c r="P2" s="104" t="str">
+      <c r="P2" s="100" t="str">
         <f>Cards!C17</f>
         <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
       </c>
-      <c r="Q2" s="103" t="str">
+      <c r="Q2" s="99" t="str">
         <f>Cards!C18</f>
         <v>You may repeat $L3 Provincial Actions per round</v>
       </c>
-      <c r="R2" s="104" t="str">
+      <c r="R2" s="100" t="str">
         <f>Cards!C19</f>
         <v>Trade up to $L3 additional Coins when Buying from the Court</v>
       </c>
-      <c r="S2" s="103" t="str">
+      <c r="S2" s="99" t="str">
         <f>Cards!C20</f>
         <v>Trade for up to $L3 additional Coins when Selling to the Court</v>
       </c>
-      <c r="T2" s="104" t="str">
+      <c r="T2" s="100" t="str">
         <f>Cards!C21</f>
         <v>Gain $L3 additional Coins from the Royal Bank when Deploying Troops</v>
       </c>
-      <c r="U2" s="103" t="str">
+      <c r="U2" s="99" t="str">
         <f>Cards!C22</f>
         <v>Provides private Buy Action at Market Rate + $L3</v>
       </c>
-      <c r="V2" s="104" t="str">
+      <c r="V2" s="100" t="str">
         <f>Cards!C23</f>
         <v>Provides private Sell Action at Market Rate - $L3</v>
       </c>
-      <c r="W2" s="103" t="str">
+      <c r="W2" s="99" t="str">
         <f>Cards!C24</f>
         <v>Purchase and immediately add up to $L3 Troops to your force when deploying them</v>
       </c>
-      <c r="X2" s="104" t="str">
+      <c r="X2" s="100" t="str">
         <f>Cards!C25</f>
         <v>Add $L3 Hits to each Roll during a Sue</v>
       </c>
-      <c r="Y2" s="103" t="str">
+      <c r="Y2" s="99" t="str">
         <f>Cards!C26</f>
         <v>Add $L6 additional dice to each Roll during a Sue</v>
       </c>
-      <c r="Z2" s="104" t="str">
+      <c r="Z2" s="100" t="str">
         <f>Cards!C27</f>
         <v>Collect $L6 additional Commodities during Harvests</v>
       </c>
-      <c r="AA2" s="103" t="str">
+      <c r="AA2" s="99" t="str">
         <f>Cards!C28</f>
         <v>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</v>
       </c>
-      <c r="AB2" s="104" t="str">
+      <c r="AB2" s="100" t="str">
         <f>Cards!C29</f>
         <v>Subtract $L3 from Scheme Card rolls</v>
       </c>
-      <c r="AC2" s="103" t="str">
+      <c r="AC2" s="99" t="str">
         <f>Cards!C30</f>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Undermarket</v>
       </c>
-      <c r="AD2" s="105" t="str">
+      <c r="AD2" s="101" t="str">
         <f>Cards!C31</f>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
       </c>
-      <c r="AE2" s="104" t="str">
+      <c r="AE2" s="100" t="str">
         <f>Cards!C32</f>
         <v>Trade up to $L3 additional Coins when Buying from the Undermarket</v>
       </c>
-      <c r="AF2" s="104" t="str">
+      <c r="AF2" s="100" t="str">
         <f>Cards!C33</f>
         <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
       </c>
-      <c r="AG2" s="103" t="str">
+      <c r="AG2" s="99" t="str">
         <f>Cards!C34</f>
         <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
       </c>
-      <c r="AH2" s="104" t="str">
+      <c r="AH2" s="100" t="str">
         <f>Cards!C35</f>
         <v>Provides private Monetize Action at Market Rate + $L3</v>
       </c>
-      <c r="AI2" s="103" t="str">
+      <c r="AI2" s="99" t="str">
         <f>Cards!C36</f>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
       </c>
-      <c r="AJ2" s="104" t="str">
+      <c r="AJ2" s="100" t="str">
         <f>Cards!C37</f>
         <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
       </c>
-      <c r="AK2" s="103" t="str">
+      <c r="AK2" s="99" t="str">
         <f>Cards!C38</f>
         <v>Convert $L3 additional Coins during Court Donate</v>
       </c>
-      <c r="AL2" s="104" t="str">
+      <c r="AL2" s="100" t="str">
         <f>Cards!C39</f>
         <v>Convert $L3 additional Coins during Undermarket Donate</v>
       </c>
-      <c r="AM2" s="103" t="str">
+      <c r="AM2" s="99" t="str">
         <f>Cards!C40</f>
         <v>You may repeat Undermarket Actions at double the penalty</v>
       </c>
-      <c r="AN2" s="104" t="str">
+      <c r="AN2" s="100" t="str">
+        <f>Cards!C41</f>
+        <v>Deploy $L3 additional Troops during Deploy</v>
+      </c>
+      <c r="AO2" s="99" t="str">
         <f t="shared" si="0"/>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
       </c>
-      <c r="AO2" s="103" t="str">
+      <c r="AP2" s="100" t="str">
         <f t="shared" si="0"/>
         <v>Move the Law $L6 additional places forward in the queue during Prioritize</v>
       </c>
-      <c r="AP2" s="104" t="str">
+      <c r="AQ2" s="99" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">You may gain up to $L6 additional Coins when Taxing other Players </v>
-      </c>
-      <c r="AQ2" s="103" t="str">
+        <v xml:space="preserve">You may keep up to $L6 additional Coins when Taxing other Players </v>
+      </c>
+      <c r="AR2" s="100" t="str">
         <f t="shared" si="0"/>
         <v>Gain $L3 additional Coins during Flatter</v>
       </c>
-      <c r="AR2" s="104" t="str">
+      <c r="AS2" s="99" t="str">
         <f t="shared" si="0"/>
         <v>Gain $L3 more Commodities per Coin when Buying from the Undermarket</v>
       </c>
-      <c r="AS2" s="103" t="str">
+      <c r="AT2" s="100" t="str">
         <f t="shared" si="0"/>
         <v>Add $L3 additional Law cards to the bottom of the queue during Petition</v>
       </c>
-      <c r="AT2" s="104" t="str">
+      <c r="AU2" s="99" t="str">
         <f t="shared" si="0"/>
         <v>Gain 1 additional Troop for free after Recruiting every 4 - $L3 Troops</v>
       </c>
-      <c r="AU2" s="103" t="str">
+      <c r="AV2" s="100" t="str">
         <f t="shared" si="0"/>
         <v>Gain 1 additional Spy for free after Infiltrating every 4 - $L3 Spies</v>
       </c>
-      <c r="AV2" s="104" t="str">
+      <c r="AW2" s="99" t="str">
         <f t="shared" si="0"/>
-        <v>Purchase up to $L6 additional Troops during Recruit</v>
-      </c>
-      <c r="AW2" s="103" t="str">
+        <v>Purchase up to $L6 additional Troops during Recruit (at normal cost)</v>
+      </c>
+      <c r="AX2" s="101" t="str">
         <f t="shared" si="0"/>
         <v>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</v>
       </c>
-      <c r="AX2" s="105" t="str">
+      <c r="AY2" s="100" t="str">
         <f t="shared" si="1"/>
         <v>Gain $L3 more Commodities per Coin when Buying from the Court</v>
       </c>
-      <c r="AY2" s="104" t="str">
+      <c r="AZ2" s="99" t="str">
         <f t="shared" si="1"/>
         <v>Gain $L3 additional Coins from outside the Royal Bank when winning a Sue</v>
       </c>
-      <c r="AZ2" s="103" t="str">
+      <c r="BA2" s="100" t="str">
         <f t="shared" si="1"/>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Undermarket</v>
       </c>
-      <c r="BA2" s="104" t="str">
+      <c r="BB2" s="99" t="str">
         <f t="shared" si="1"/>
         <v>Draw $L6 additional cards from any decks during Brainstorm</v>
       </c>
-      <c r="BB2" s="103" t="str">
+      <c r="BC2" s="100" t="str">
         <f t="shared" si="1"/>
         <v>Purchase $L3 Spies (at normal cost) when targeted by a Scheme</v>
       </c>
-      <c r="BC2" s="104" t="str">
+      <c r="BD2" s="99" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
       </c>
-      <c r="BD2" s="103" t="str">
+      <c r="BE2" s="100" t="str">
         <f t="shared" si="1"/>
         <v>You may repeat $L3 Provincial Actions per round</v>
       </c>
-      <c r="BE2" s="104" t="str">
+      <c r="BF2" s="99" t="str">
         <f t="shared" si="1"/>
         <v>Trade up to $L3 additional Coins when Buying from the Court</v>
       </c>
-      <c r="BF2" s="103" t="str">
+      <c r="BG2" s="100" t="str">
         <f t="shared" si="1"/>
         <v>Trade for up to $L3 additional Coins when Selling to the Court</v>
       </c>
-      <c r="BG2" s="104" t="str">
+      <c r="BH2" s="101" t="str">
         <f t="shared" si="1"/>
         <v>Gain $L3 additional Coins from the Royal Bank when Deploying Troops</v>
       </c>
-      <c r="BH2" s="105" t="str">
+      <c r="BI2" s="100" t="str">
         <f t="shared" si="2"/>
         <v>Provides private Buy Action at Market Rate + $L3</v>
       </c>
-      <c r="BI2" s="104" t="str">
+      <c r="BJ2" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Provides private Sell Action at Market Rate - $L3</v>
       </c>
-      <c r="BJ2" s="103" t="str">
+      <c r="BK2" s="100" t="str">
         <f t="shared" si="2"/>
         <v>Purchase and immediately add up to $L3 Troops to your force when deploying them</v>
       </c>
-      <c r="BK2" s="104" t="str">
+      <c r="BL2" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Add $L3 Hits to each Roll during a Sue</v>
       </c>
-      <c r="BL2" s="103" t="str">
+      <c r="BM2" s="100" t="str">
         <f t="shared" si="2"/>
         <v>Add $L6 additional dice to each Roll during a Sue</v>
       </c>
-      <c r="BM2" s="104" t="str">
+      <c r="BN2" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Collect $L6 additional Commodities during Harvests</v>
       </c>
-      <c r="BN2" s="103" t="str">
+      <c r="BO2" s="100" t="str">
         <f t="shared" si="2"/>
         <v>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</v>
       </c>
-      <c r="BO2" s="104" t="str">
+      <c r="BP2" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Subtract $L3 from Scheme Card rolls</v>
       </c>
-      <c r="BP2" s="103" t="str">
+      <c r="BQ2" s="79" t="str">
         <f t="shared" si="2"/>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Undermarket</v>
       </c>
-      <c r="BQ2" s="104"/>
-      <c r="BS2" s="104"/>
-    </row>
-    <row r="3" spans="1:71" s="80" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="78" t="str">
+      <c r="BR2" s="100" t="str">
+        <f t="shared" si="2"/>
+        <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
+      </c>
+      <c r="BS2" s="79"/>
+      <c r="BU2" s="100"/>
+      <c r="BW2" s="100"/>
+      <c r="BY2" s="100"/>
+      <c r="CA2" s="100"/>
+    </row>
+    <row r="3" spans="1:79" s="76" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="74" t="str">
         <f>Cards!D2</f>
         <v>Full Coffers</v>
       </c>
-      <c r="B3" s="79" t="str">
+      <c r="B3" s="75" t="str">
         <f>Cards!D3</f>
         <v xml:space="preserve">Decentralized Wealth </v>
       </c>
-      <c r="C3" s="80" t="str">
+      <c r="C3" s="76" t="str">
         <f>Cards!D4</f>
         <v>Second Thoughts</v>
       </c>
-      <c r="D3" s="78" t="str">
+      <c r="D3" s="74" t="str">
         <f>Cards!D5</f>
         <v>Changing Times</v>
       </c>
-      <c r="E3" s="80" t="str">
+      <c r="E3" s="76" t="str">
         <f>Cards!D6</f>
         <v>Stable Economies</v>
       </c>
-      <c r="F3" s="78" t="str">
+      <c r="F3" s="74" t="str">
         <f>Cards!D7</f>
         <v>Unreasonable Distractions</v>
       </c>
-      <c r="G3" s="80" t="str">
+      <c r="G3" s="76" t="str">
         <f>Cards!D8</f>
         <v>Irregular Partiality</v>
       </c>
-      <c r="H3" s="78" t="str">
+      <c r="H3" s="74" t="str">
         <f>Cards!D9</f>
         <v>Royal Amendment</v>
       </c>
-      <c r="I3" s="80" t="str">
+      <c r="I3" s="76" t="str">
         <f>Cards!D10</f>
         <v>Honorable Accontability</v>
       </c>
-      <c r="J3" s="78" t="str">
+      <c r="J3" s="74" t="str">
         <f>Cards!D11</f>
         <v>Frivolous Pursuits</v>
       </c>
-      <c r="K3" s="80" t="str">
+      <c r="K3" s="76" t="str">
         <f>Cards!D12</f>
         <v>Economic Backbone</v>
       </c>
-      <c r="L3" s="78" t="str">
+      <c r="L3" s="74" t="str">
         <f>Cards!D13</f>
         <v>Collective Ownership</v>
       </c>
-      <c r="M3" s="80" t="str">
+      <c r="M3" s="76" t="str">
         <f>Cards!D14</f>
         <v>Aggressive Tactics</v>
       </c>
-      <c r="N3" s="78" t="str">
+      <c r="N3" s="74" t="str">
         <f>Cards!D15</f>
         <v>Home Defense</v>
       </c>
-      <c r="O3" s="80" t="str">
+      <c r="O3" s="76" t="str">
         <f>Cards!D16</f>
         <v>Valuable Advisors</v>
       </c>
-      <c r="P3" s="78" t="str">
+      <c r="P3" s="74" t="str">
         <f>Cards!D17</f>
         <v>Chattering Windbags</v>
       </c>
-      <c r="Q3" s="80" t="str">
+      <c r="Q3" s="76" t="str">
         <f>Cards!D18</f>
         <v>Realistic Priorities</v>
       </c>
-      <c r="R3" s="78" t="str">
+      <c r="R3" s="74" t="str">
         <f>Cards!D19</f>
         <v>Threat to the Throne</v>
       </c>
-      <c r="S3" s="80" t="str">
+      <c r="S3" s="76" t="str">
         <f>Cards!D20</f>
         <v>Stone Foundations</v>
       </c>
-      <c r="T3" s="78" t="str">
+      <c r="T3" s="74" t="str">
         <f>Cards!D21</f>
         <v>Environmental Guardians</v>
       </c>
-      <c r="U3" s="80" t="str">
+      <c r="U3" s="76" t="str">
         <f>Cards!D22</f>
         <v>Resilient Officer Corps</v>
       </c>
-      <c r="V3" s="78" t="str">
+      <c r="V3" s="74" t="str">
         <f>Cards!D23</f>
         <v>Bloated Bureaucracy</v>
       </c>
-      <c r="W3" s="80" t="str">
+      <c r="W3" s="76" t="str">
         <f>Cards!D24</f>
         <v>Police Force</v>
       </c>
-      <c r="X3" s="78" t="str">
+      <c r="X3" s="74" t="str">
         <f>Cards!D25</f>
         <v>Equal Partners</v>
       </c>
-      <c r="Y3" s="80" t="str">
+      <c r="Y3" s="76" t="str">
         <f>Cards!D26</f>
         <v>Criminal Identification</v>
       </c>
-      <c r="Z3" s="78" t="str">
+      <c r="Z3" s="74" t="str">
         <f>Cards!D27</f>
         <v>Honorable Marketplace</v>
       </c>
-      <c r="AA3" s="80" t="str">
+      <c r="AA3" s="76" t="str">
         <f>Cards!D28</f>
         <v>Engaged Empire</v>
       </c>
-      <c r="AB3" s="78" t="str">
+      <c r="AB3" s="74" t="str">
         <f>Cards!D29</f>
         <v>Suspicious Advisors</v>
       </c>
-      <c r="AC3" s="80" t="str">
+      <c r="AC3" s="76" t="str">
         <f>Cards!D30</f>
         <v>Contingency Plans</v>
       </c>
-      <c r="AD3" s="81" t="str">
+      <c r="AD3" s="77" t="str">
         <f>Cards!D31</f>
         <v>Worthless Procrastinators</v>
       </c>
-      <c r="AE3" s="78" t="str">
+      <c r="AE3" s="74" t="str">
         <f>Cards!D32</f>
         <v>Stalled Front</v>
       </c>
-      <c r="AF3" s="78" t="str">
+      <c r="AF3" s="74" t="str">
         <f>Cards!D33</f>
         <v>Quality Strength</v>
       </c>
-      <c r="AG3" s="80" t="str">
+      <c r="AG3" s="76" t="str">
         <f t="shared" ref="AG3:BL3" si="3">A3</f>
         <v>Full Coffers</v>
       </c>
-      <c r="AH3" s="78" t="str">
+      <c r="AH3" s="74" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">Decentralized Wealth </v>
       </c>
-      <c r="AI3" s="80" t="str">
+      <c r="AI3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Second Thoughts</v>
       </c>
-      <c r="AJ3" s="78" t="str">
+      <c r="AJ3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Changing Times</v>
       </c>
-      <c r="AK3" s="80" t="str">
+      <c r="AK3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Stable Economies</v>
       </c>
-      <c r="AL3" s="78" t="str">
+      <c r="AL3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Unreasonable Distractions</v>
       </c>
-      <c r="AM3" s="80" t="str">
+      <c r="AM3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Irregular Partiality</v>
       </c>
-      <c r="AN3" s="78" t="str">
+      <c r="AN3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Royal Amendment</v>
       </c>
-      <c r="AO3" s="80" t="str">
+      <c r="AO3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Honorable Accontability</v>
       </c>
-      <c r="AP3" s="78" t="str">
+      <c r="AP3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Frivolous Pursuits</v>
       </c>
-      <c r="AQ3" s="80" t="str">
+      <c r="AQ3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Economic Backbone</v>
       </c>
-      <c r="AR3" s="78" t="str">
+      <c r="AR3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Collective Ownership</v>
       </c>
-      <c r="AS3" s="80" t="str">
+      <c r="AS3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Aggressive Tactics</v>
       </c>
-      <c r="AT3" s="78" t="str">
+      <c r="AT3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Home Defense</v>
       </c>
-      <c r="AU3" s="80" t="str">
+      <c r="AU3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Valuable Advisors</v>
       </c>
-      <c r="AV3" s="78" t="str">
+      <c r="AV3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Chattering Windbags</v>
       </c>
-      <c r="AW3" s="80" t="str">
+      <c r="AW3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Realistic Priorities</v>
       </c>
-      <c r="AX3" s="81" t="str">
+      <c r="AX3" s="77" t="str">
         <f t="shared" si="3"/>
         <v>Threat to the Throne</v>
       </c>
-      <c r="AY3" s="78" t="str">
+      <c r="AY3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Stone Foundations</v>
       </c>
-      <c r="AZ3" s="80" t="str">
+      <c r="AZ3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Environmental Guardians</v>
       </c>
-      <c r="BA3" s="78" t="str">
+      <c r="BA3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Resilient Officer Corps</v>
       </c>
-      <c r="BB3" s="80" t="str">
+      <c r="BB3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Bloated Bureaucracy</v>
       </c>
-      <c r="BC3" s="78" t="str">
+      <c r="BC3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Police Force</v>
       </c>
-      <c r="BD3" s="80" t="str">
+      <c r="BD3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Equal Partners</v>
       </c>
-      <c r="BE3" s="78" t="str">
+      <c r="BE3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Criminal Identification</v>
       </c>
-      <c r="BF3" s="80" t="str">
+      <c r="BF3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Honorable Marketplace</v>
       </c>
-      <c r="BG3" s="78" t="str">
+      <c r="BG3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Engaged Empire</v>
       </c>
-      <c r="BH3" s="81" t="str">
+      <c r="BH3" s="77" t="str">
         <f t="shared" si="3"/>
         <v>Suspicious Advisors</v>
       </c>
-      <c r="BI3" s="78" t="str">
+      <c r="BI3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Contingency Plans</v>
       </c>
-      <c r="BJ3" s="80" t="str">
+      <c r="BJ3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Worthless Procrastinators</v>
       </c>
-      <c r="BK3" s="78" t="str">
+      <c r="BK3" s="74" t="str">
         <f t="shared" si="3"/>
         <v>Stalled Front</v>
       </c>
-      <c r="BL3" s="80" t="str">
+      <c r="BL3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Quality Strength</v>
       </c>
-      <c r="BM3" s="78"/>
-      <c r="BN3" s="80" t="str">
+      <c r="BM3" s="74"/>
+      <c r="BN3" s="76" t="str">
+        <f>AJ1</f>
+        <v>Kingdom Advocates</v>
+      </c>
+      <c r="BO3" s="74" t="str">
+        <f>AK1</f>
+        <v>Soup Kitchens</v>
+      </c>
+      <c r="BP3" s="76" t="str">
+        <f>AL1</f>
+        <v>Abusive Power</v>
+      </c>
+      <c r="BQ3" s="74" t="str">
+        <f>AM1</f>
+        <v>Painful Progress</v>
+      </c>
+      <c r="BR3" s="74" t="str">
+        <f>AN1</f>
+        <v>Iron Command</v>
+      </c>
+      <c r="BS3" s="75"/>
+      <c r="BU3" s="74"/>
+      <c r="BW3" s="74"/>
+      <c r="BY3" s="74"/>
+      <c r="CA3" s="74"/>
+    </row>
+    <row r="4" spans="1:79" s="81" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="79" t="str">
+        <f>Cards!E2</f>
+        <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
+      </c>
+      <c r="B4" s="80" t="str">
+        <f>Cards!E3</f>
+        <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
+      </c>
+      <c r="C4" s="81" t="str">
+        <f>Cards!E4</f>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="D4" s="79" t="str">
+        <f>Cards!E5</f>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="E4" s="81" t="str">
+        <f>Cards!E6</f>
+        <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
+      </c>
+      <c r="F4" s="79" t="str">
+        <f>Cards!E7</f>
+        <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
+      </c>
+      <c r="G4" s="81" t="str">
+        <f>Cards!E8</f>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="H4" s="79" t="str">
+        <f>Cards!E9</f>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="I4" s="81" t="str">
+        <f>Cards!E10</f>
+        <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy Troops</v>
+      </c>
+      <c r="J4" s="79" t="str">
+        <f>Cards!E11</f>
+        <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy Troops</v>
+      </c>
+      <c r="K4" s="81" t="str">
+        <f>Cards!E12</f>
+        <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
+      </c>
+      <c r="L4" s="79" t="str">
+        <f>Cards!E13</f>
+        <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
+      </c>
+      <c r="M4" s="81" t="str">
+        <f>Cards!E14</f>
+        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+      </c>
+      <c r="N4" s="79" t="str">
+        <f>Cards!E15</f>
+        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+      </c>
+      <c r="O4" s="81" t="str">
+        <f>Cards!E16</f>
+        <v>Each Player must have at least $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
+      </c>
+      <c r="P4" s="79" t="str">
+        <f>Cards!E17</f>
+        <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
+      </c>
+      <c r="Q4" s="81" t="str">
+        <f>Cards!E18</f>
+        <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
+      </c>
+      <c r="R4" s="79" t="str">
+        <f>Cards!E19</f>
+        <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
+      </c>
+      <c r="S4" s="81" t="str">
+        <f>Cards!E20</f>
+        <v>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+      </c>
+      <c r="T4" s="79" t="str">
+        <f>Cards!E21</f>
+        <v>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+      </c>
+      <c r="U4" s="81" t="str">
+        <f>Cards!E22</f>
+        <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
+      </c>
+      <c r="V4" s="79" t="str">
+        <f>Cards!E23</f>
+        <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
+      </c>
+      <c r="W4" s="81" t="str">
+        <f>Cards!E24</f>
+        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</v>
+      </c>
+      <c r="X4" s="79" t="str">
+        <f>Cards!E25</f>
+        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</v>
+      </c>
+      <c r="Y4" s="81" t="str">
+        <f>Cards!E26</f>
+        <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+      </c>
+      <c r="Z4" s="79" t="str">
+        <f>Cards!E27</f>
+        <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+      </c>
+      <c r="AA4" s="81" t="str">
+        <f>Cards!E28</f>
+        <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
+      </c>
+      <c r="AB4" s="79" t="str">
+        <f>Cards!E29</f>
+        <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
+      </c>
+      <c r="AC4" s="81" t="str">
+        <f>Cards!E30</f>
+        <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
+      </c>
+      <c r="AD4" s="82" t="str">
+        <f>Cards!E31</f>
+        <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
+      </c>
+      <c r="AE4" s="79" t="str">
+        <f>Cards!E32</f>
+        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="AF4" s="79" t="str">
+        <f>Cards!E33</f>
+        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="AG4" s="81" t="str">
+        <f t="shared" ref="AG4:BL4" si="4">A4</f>
+        <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
+      </c>
+      <c r="AH4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
+      </c>
+      <c r="AI4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AJ4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AK4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
+      </c>
+      <c r="AL4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
+      </c>
+      <c r="AM4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AN4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AO4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy Troops</v>
+      </c>
+      <c r="AP4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy Troops</v>
+      </c>
+      <c r="AQ4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
+      </c>
+      <c r="AR4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
+      </c>
+      <c r="AS4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+      </c>
+      <c r="AT4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+      </c>
+      <c r="AU4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>Each Player must have at least $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
+      </c>
+      <c r="AV4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
+      </c>
+      <c r="AW4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
+      </c>
+      <c r="AX4" s="82" t="str">
+        <f t="shared" si="4"/>
+        <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
+      </c>
+      <c r="AY4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+      </c>
+      <c r="AZ4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+      </c>
+      <c r="BA4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
+      </c>
+      <c r="BB4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
+      </c>
+      <c r="BC4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</v>
+      </c>
+      <c r="BD4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</v>
+      </c>
+      <c r="BE4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+      </c>
+      <c r="BF4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+      </c>
+      <c r="BG4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
+      </c>
+      <c r="BH4" s="82" t="str">
+        <f t="shared" si="4"/>
+        <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
+      </c>
+      <c r="BI4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
+      </c>
+      <c r="BJ4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
+      </c>
+      <c r="BK4" s="79" t="str">
+        <f t="shared" si="4"/>
+        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="BL4" s="81" t="str">
+        <f t="shared" si="4"/>
+        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="BM4" s="79"/>
+      <c r="BN4" s="99" t="str">
+        <f>AJ2</f>
+        <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
+      </c>
+      <c r="BO4" s="100" t="str">
+        <f>AK2</f>
+        <v>Convert $L3 additional Coins during Court Donate</v>
+      </c>
+      <c r="BP4" s="99" t="str">
+        <f>AL2</f>
+        <v>Convert $L3 additional Coins during Undermarket Donate</v>
+      </c>
+      <c r="BQ4" s="100" t="str">
+        <f>AM2</f>
+        <v>You may repeat Undermarket Actions at double the penalty</v>
+      </c>
+      <c r="BR4" s="79" t="str">
+        <f>AN2</f>
+        <v>Deploy $L3 additional Troops during Deploy</v>
+      </c>
+      <c r="BS4" s="80"/>
+      <c r="BU4" s="79"/>
+      <c r="BW4" s="79"/>
+      <c r="BY4" s="79"/>
+      <c r="CA4" s="79"/>
+    </row>
+    <row r="5" spans="1:79" s="85" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="83" t="str">
+        <f>Cards!F2</f>
+        <v>Fickle Mercenaries</v>
+      </c>
+      <c r="B5" s="84" t="str">
+        <f>Cards!F3</f>
+        <v>Blatant Extortion</v>
+      </c>
+      <c r="C5" s="85" t="str">
+        <f>Cards!F4</f>
+        <v>Double Agents</v>
+      </c>
+      <c r="D5" s="83" t="str">
+        <f>Cards!F5</f>
+        <v>Questionable Reallocation</v>
+      </c>
+      <c r="E5" s="85" t="str">
+        <f>Cards!F6</f>
+        <v>Corporate Espionage</v>
+      </c>
+      <c r="F5" s="83" t="str">
+        <f>Cards!F7</f>
+        <v>Localized Famine</v>
+      </c>
+      <c r="G5" s="85" t="str">
+        <f>Cards!F8</f>
+        <v>Highway Robbery</v>
+      </c>
+      <c r="H5" s="83" t="str">
+        <f>Cards!F9</f>
+        <v>Camp Plague</v>
+      </c>
+      <c r="I5" s="85" t="str">
+        <f>Cards!F10</f>
+        <v>Weakening Grip</v>
+      </c>
+      <c r="J5" s="83" t="str">
+        <f>Cards!F11</f>
+        <v>Culture Shift</v>
+      </c>
+      <c r="K5" s="85" t="str">
+        <f>Cards!F12</f>
+        <v>Corporate Takeover</v>
+      </c>
+      <c r="L5" s="83" t="str">
+        <f>Cards!F13</f>
+        <v>Sabotage</v>
+      </c>
+      <c r="M5" s="85" t="str">
+        <f>Cards!F14</f>
+        <v>Dangerous Monopolies</v>
+      </c>
+      <c r="N5" s="83" t="str">
+        <f>Cards!F15</f>
+        <v>Betrayal</v>
+      </c>
+      <c r="O5" s="85" t="str">
+        <f>Cards!F16</f>
+        <v>Assassination Attempt</v>
+      </c>
+      <c r="P5" s="83" t="str">
+        <f>Cards!F17</f>
+        <v>Humiliation</v>
+      </c>
+      <c r="Q5" s="85" t="str">
+        <f>Cards!F18</f>
+        <v>Invalid Paperwork</v>
+      </c>
+      <c r="R5" s="83" t="str">
+        <f>Cards!F19</f>
+        <v>Rallied Opposition</v>
+      </c>
+      <c r="S5" s="85" t="str">
+        <f>Cards!F20</f>
+        <v>Waning Support</v>
+      </c>
+      <c r="T5" s="83" t="str">
+        <f>Cards!F21</f>
+        <v>Misaligned Strategy</v>
+      </c>
+      <c r="U5" s="83" t="str">
+        <f>Cards!F22</f>
+        <v>Blackmail</v>
+      </c>
+      <c r="V5" s="83" t="str">
+        <f t="shared" ref="V5:AE6" si="5">A5</f>
+        <v>Fickle Mercenaries</v>
+      </c>
+      <c r="W5" s="85" t="str">
+        <f t="shared" si="5"/>
+        <v>Blatant Extortion</v>
+      </c>
+      <c r="X5" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>Double Agents</v>
+      </c>
+      <c r="Y5" s="85" t="str">
+        <f t="shared" si="5"/>
+        <v>Questionable Reallocation</v>
+      </c>
+      <c r="Z5" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>Corporate Espionage</v>
+      </c>
+      <c r="AA5" s="85" t="str">
+        <f t="shared" si="5"/>
+        <v>Localized Famine</v>
+      </c>
+      <c r="AB5" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>Highway Robbery</v>
+      </c>
+      <c r="AC5" s="85" t="str">
+        <f t="shared" si="5"/>
+        <v>Camp Plague</v>
+      </c>
+      <c r="AD5" s="86" t="str">
+        <f t="shared" si="5"/>
+        <v>Weakening Grip</v>
+      </c>
+      <c r="AE5" s="83" t="str">
+        <f t="shared" si="5"/>
+        <v>Culture Shift</v>
+      </c>
+      <c r="AF5" s="83" t="str">
+        <f t="shared" ref="AF5:AO6" si="6">K5</f>
+        <v>Corporate Takeover</v>
+      </c>
+      <c r="AG5" s="85" t="str">
+        <f t="shared" si="6"/>
+        <v>Sabotage</v>
+      </c>
+      <c r="AH5" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>Dangerous Monopolies</v>
+      </c>
+      <c r="AI5" s="85" t="str">
+        <f t="shared" si="6"/>
+        <v>Betrayal</v>
+      </c>
+      <c r="AJ5" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>Assassination Attempt</v>
+      </c>
+      <c r="AK5" s="85" t="str">
+        <f t="shared" si="6"/>
+        <v>Humiliation</v>
+      </c>
+      <c r="AL5" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>Invalid Paperwork</v>
+      </c>
+      <c r="AM5" s="85" t="str">
+        <f t="shared" si="6"/>
+        <v>Rallied Opposition</v>
+      </c>
+      <c r="AN5" s="83" t="str">
+        <f t="shared" si="6"/>
+        <v>Waning Support</v>
+      </c>
+      <c r="AO5" s="85" t="str">
+        <f t="shared" si="6"/>
+        <v>Misaligned Strategy</v>
+      </c>
+      <c r="AP5" s="83" t="str">
+        <f t="shared" ref="AP5:AY6" si="7">U5</f>
+        <v>Blackmail</v>
+      </c>
+      <c r="AQ5" s="85" t="str">
+        <f t="shared" ref="AQ5:AZ6" si="8">A5</f>
+        <v>Fickle Mercenaries</v>
+      </c>
+      <c r="AR5" s="83" t="str">
+        <f t="shared" si="8"/>
+        <v>Blatant Extortion</v>
+      </c>
+      <c r="AS5" s="85" t="str">
+        <f t="shared" si="8"/>
+        <v>Double Agents</v>
+      </c>
+      <c r="AT5" s="83" t="str">
+        <f t="shared" si="8"/>
+        <v>Questionable Reallocation</v>
+      </c>
+      <c r="AU5" s="85" t="str">
+        <f t="shared" si="8"/>
+        <v>Corporate Espionage</v>
+      </c>
+      <c r="AV5" s="83" t="str">
+        <f t="shared" si="8"/>
+        <v>Localized Famine</v>
+      </c>
+      <c r="AW5" s="85" t="str">
+        <f t="shared" si="8"/>
+        <v>Highway Robbery</v>
+      </c>
+      <c r="AX5" s="86" t="str">
+        <f t="shared" si="8"/>
+        <v>Camp Plague</v>
+      </c>
+      <c r="AY5" s="83" t="str">
+        <f t="shared" si="8"/>
+        <v>Weakening Grip</v>
+      </c>
+      <c r="AZ5" s="85" t="str">
+        <f t="shared" si="8"/>
+        <v>Culture Shift</v>
+      </c>
+      <c r="BA5" s="83" t="str">
+        <f t="shared" ref="BA5:BJ6" si="9">K5</f>
+        <v>Corporate Takeover</v>
+      </c>
+      <c r="BB5" s="85" t="str">
+        <f t="shared" si="9"/>
+        <v>Sabotage</v>
+      </c>
+      <c r="BC5" s="83" t="str">
+        <f t="shared" si="9"/>
+        <v>Dangerous Monopolies</v>
+      </c>
+      <c r="BD5" s="85" t="str">
+        <f t="shared" si="9"/>
+        <v>Betrayal</v>
+      </c>
+      <c r="BE5" s="83" t="str">
+        <f t="shared" si="9"/>
+        <v>Assassination Attempt</v>
+      </c>
+      <c r="BF5" s="85" t="str">
+        <f t="shared" si="9"/>
+        <v>Humiliation</v>
+      </c>
+      <c r="BG5" s="83" t="str">
+        <f t="shared" si="9"/>
+        <v>Invalid Paperwork</v>
+      </c>
+      <c r="BH5" s="83" t="str">
+        <f t="shared" si="9"/>
+        <v>Rallied Opposition</v>
+      </c>
+      <c r="BI5" s="83" t="str">
+        <f t="shared" si="9"/>
+        <v>Waning Support</v>
+      </c>
+      <c r="BJ5" s="85" t="str">
+        <f t="shared" si="9"/>
+        <v>Misaligned Strategy</v>
+      </c>
+      <c r="BK5" s="83" t="str">
+        <f t="shared" ref="BK5:BT6" si="10">U5</f>
+        <v>Blackmail</v>
+      </c>
+      <c r="BM5" s="74" t="str">
+        <f>AE1</f>
+        <v>Codependent Relationship</v>
+      </c>
+      <c r="BN5" s="76" t="str">
+        <f>AF1</f>
+        <v>Dangerous Promises</v>
+      </c>
+      <c r="BO5" s="74" t="str">
+        <f>AG1</f>
+        <v>Large Middle Class</v>
+      </c>
+      <c r="BP5" s="76" t="str">
         <f>AH1</f>
         <v>Innovation Hub</v>
       </c>
-      <c r="BO3" s="78" t="str">
-        <f>AF1</f>
-        <v>Dangerous Promises</v>
-      </c>
-      <c r="BP3" s="80" t="str">
-        <f>AD1</f>
-        <v>Expert Broker</v>
-      </c>
-      <c r="BQ3" s="78"/>
-      <c r="BS3" s="78"/>
-    </row>
-    <row r="4" spans="1:71" s="85" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="83" t="str">
-        <f>Cards!E2</f>
-        <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
-      </c>
-      <c r="B4" s="84" t="str">
-        <f>Cards!E3</f>
-        <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
-      </c>
-      <c r="C4" s="85" t="str">
-        <f>Cards!E4</f>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="D4" s="83" t="str">
-        <f>Cards!E5</f>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="E4" s="85" t="str">
-        <f>Cards!E6</f>
-        <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
-      </c>
-      <c r="F4" s="83" t="str">
-        <f>Cards!E7</f>
-        <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
-      </c>
-      <c r="G4" s="85" t="str">
-        <f>Cards!E8</f>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="H4" s="83" t="str">
-        <f>Cards!E9</f>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="I4" s="85" t="str">
-        <f>Cards!E10</f>
-        <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy Troops</v>
-      </c>
-      <c r="J4" s="83" t="str">
-        <f>Cards!E11</f>
-        <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy Troops</v>
-      </c>
-      <c r="K4" s="85" t="str">
-        <f>Cards!E12</f>
-        <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
-      </c>
-      <c r="L4" s="83" t="str">
-        <f>Cards!E13</f>
-        <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
-      </c>
-      <c r="M4" s="85" t="str">
-        <f>Cards!E14</f>
-        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
-      </c>
-      <c r="N4" s="83" t="str">
-        <f>Cards!E15</f>
-        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
-      </c>
-      <c r="O4" s="85" t="str">
-        <f>Cards!E16</f>
-        <v>Each Player must have at least $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
-      </c>
-      <c r="P4" s="83" t="str">
-        <f>Cards!E17</f>
-        <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
-      </c>
-      <c r="Q4" s="85" t="str">
-        <f>Cards!E18</f>
-        <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
-      </c>
-      <c r="R4" s="83" t="str">
-        <f>Cards!E19</f>
-        <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
-      </c>
-      <c r="S4" s="85" t="str">
-        <f>Cards!E20</f>
-        <v>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
-      </c>
-      <c r="T4" s="83" t="str">
-        <f>Cards!E21</f>
-        <v>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
-      </c>
-      <c r="U4" s="85" t="str">
-        <f>Cards!E22</f>
-        <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
-      </c>
-      <c r="V4" s="83" t="str">
-        <f>Cards!E23</f>
-        <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
-      </c>
-      <c r="W4" s="85" t="str">
-        <f>Cards!E24</f>
-        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</v>
-      </c>
-      <c r="X4" s="83" t="str">
-        <f>Cards!E25</f>
-        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</v>
-      </c>
-      <c r="Y4" s="85" t="str">
-        <f>Cards!E26</f>
-        <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
-      </c>
-      <c r="Z4" s="83" t="str">
-        <f>Cards!E27</f>
-        <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
-      </c>
-      <c r="AA4" s="85" t="str">
-        <f>Cards!E28</f>
-        <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
-      </c>
-      <c r="AB4" s="83" t="str">
-        <f>Cards!E29</f>
-        <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
-      </c>
-      <c r="AC4" s="85" t="str">
-        <f>Cards!E30</f>
-        <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
-      </c>
-      <c r="AD4" s="86" t="str">
-        <f>Cards!E31</f>
-        <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
-      </c>
-      <c r="AE4" s="83" t="str">
-        <f>Cards!E32</f>
-        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
-      </c>
-      <c r="AF4" s="83" t="str">
-        <f>Cards!E33</f>
-        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
-      </c>
-      <c r="AG4" s="85" t="str">
-        <f t="shared" ref="AG4:BL4" si="4">A4</f>
-        <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
-      </c>
-      <c r="AH4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
-      </c>
-      <c r="AI4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AJ4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AK4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
-      </c>
-      <c r="AL4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
-      </c>
-      <c r="AM4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AN4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AO4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy Troops</v>
-      </c>
-      <c r="AP4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy Troops</v>
-      </c>
-      <c r="AQ4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
-      </c>
-      <c r="AR4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
-      </c>
-      <c r="AS4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
-      </c>
-      <c r="AT4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
-      </c>
-      <c r="AU4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
-      </c>
-      <c r="AV4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
-      </c>
-      <c r="AW4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
-      </c>
-      <c r="AX4" s="86" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
-      </c>
-      <c r="AY4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
-      </c>
-      <c r="AZ4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
-      </c>
-      <c r="BA4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
-      </c>
-      <c r="BB4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
-      </c>
-      <c r="BC4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</v>
-      </c>
-      <c r="BD4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</v>
-      </c>
-      <c r="BE4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
-      </c>
-      <c r="BF4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
-      </c>
-      <c r="BG4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
-      </c>
-      <c r="BH4" s="86" t="str">
-        <f t="shared" si="4"/>
-        <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
-      </c>
-      <c r="BI4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
-      </c>
-      <c r="BJ4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
-      </c>
-      <c r="BK4" s="83" t="str">
-        <f t="shared" si="4"/>
-        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
-      </c>
-      <c r="BL4" s="85" t="str">
-        <f t="shared" si="4"/>
-        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
-      </c>
-      <c r="BM4" s="83"/>
-      <c r="BN4" s="103" t="str">
+      <c r="BQ5" s="74" t="str">
+        <f>AI1</f>
+        <v>Fire Temple</v>
+      </c>
+      <c r="BR5" s="83"/>
+      <c r="BS5" s="84"/>
+      <c r="BU5" s="83"/>
+      <c r="BW5" s="83"/>
+      <c r="BY5" s="83"/>
+      <c r="CA5" s="83"/>
+    </row>
+    <row r="6" spans="1:79" s="81" customFormat="1" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="79" t="str">
+        <f>Cards!G2</f>
+        <v>Give $2D6 Troops to $R</v>
+      </c>
+      <c r="B6" s="80" t="str">
+        <f>Cards!G3</f>
+        <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
+      </c>
+      <c r="C6" s="81" t="str">
+        <f>Cards!G4</f>
+        <v>Give $D6 Spies to $R</v>
+      </c>
+      <c r="D6" s="79" t="str">
+        <f>Cards!G5</f>
+        <v>Give $2D6 Commodities to $R</v>
+      </c>
+      <c r="E6" s="81" t="str">
+        <f>Cards!G6</f>
+        <v>Give $D6 random Cards of each type from your hand to $R</v>
+      </c>
+      <c r="F6" s="79" t="str">
+        <f>Cards!G7</f>
+        <v>Lose half your Commodities</v>
+      </c>
+      <c r="G6" s="81" t="str">
+        <f>Cards!G8</f>
+        <v>Lose half your Coins</v>
+      </c>
+      <c r="H6" s="79" t="str">
+        <f>Cards!G9</f>
+        <v>Lose half your Troops</v>
+      </c>
+      <c r="I6" s="81" t="str">
+        <f>Cards!G10</f>
+        <v>Lose half your Spies</v>
+      </c>
+      <c r="J6" s="79" t="str">
+        <f>Cards!G11</f>
+        <v>Disard half your cards of each type</v>
+      </c>
+      <c r="K6" s="81" t="str">
+        <f>Cards!G12</f>
+        <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
+      </c>
+      <c r="L6" s="79" t="str">
+        <f>Cards!G13</f>
+        <v>Downgrade an Investment by $D6 levels</v>
+      </c>
+      <c r="M6" s="81" t="str">
+        <f>Cards!G14</f>
+        <v>Downgrade an Investment by $D6 levels</v>
+      </c>
+      <c r="N6" s="79" t="str">
+        <f>Cards!G15</f>
+        <v>Demote a Leader at level $D6 by half and send it to $R</v>
+      </c>
+      <c r="O6" s="81" t="str">
+        <f>Cards!G16</f>
+        <v>Demote a Leader by $D6 levels</v>
+      </c>
+      <c r="P6" s="79" t="str">
+        <f>Cards!G17</f>
+        <v>Demote a Leader by $D6 levels</v>
+      </c>
+      <c r="Q6" s="81" t="str">
+        <f>Cards!G18</f>
+        <v>Move your foremost Law to the back of the Queue</v>
+      </c>
+      <c r="R6" s="79" t="str">
+        <f>Cards!G19</f>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
+      </c>
+      <c r="S6" s="81" t="str">
+        <f>Cards!G20</f>
+        <v>Move $D6 of your Laws each one space back in the Queue</v>
+      </c>
+      <c r="T6" s="79" t="str">
+        <f>Cards!G21</f>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
+      </c>
+      <c r="U6" s="79" t="str">
+        <f>Cards!G22</f>
+        <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
+      </c>
+      <c r="V6" s="79" t="str">
+        <f t="shared" si="5"/>
+        <v>Give $2D6 Troops to $R</v>
+      </c>
+      <c r="W6" s="81" t="str">
+        <f t="shared" si="5"/>
+        <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
+      </c>
+      <c r="X6" s="79" t="str">
+        <f t="shared" si="5"/>
+        <v>Give $D6 Spies to $R</v>
+      </c>
+      <c r="Y6" s="81" t="str">
+        <f t="shared" si="5"/>
+        <v>Give $2D6 Commodities to $R</v>
+      </c>
+      <c r="Z6" s="79" t="str">
+        <f t="shared" si="5"/>
+        <v>Give $D6 random Cards of each type from your hand to $R</v>
+      </c>
+      <c r="AA6" s="81" t="str">
+        <f t="shared" si="5"/>
+        <v>Lose half your Commodities</v>
+      </c>
+      <c r="AB6" s="79" t="str">
+        <f t="shared" si="5"/>
+        <v>Lose half your Coins</v>
+      </c>
+      <c r="AC6" s="81" t="str">
+        <f t="shared" si="5"/>
+        <v>Lose half your Troops</v>
+      </c>
+      <c r="AD6" s="82" t="str">
+        <f t="shared" si="5"/>
+        <v>Lose half your Spies</v>
+      </c>
+      <c r="AE6" s="79" t="str">
+        <f t="shared" si="5"/>
+        <v>Disard half your cards of each type</v>
+      </c>
+      <c r="AF6" s="79" t="str">
+        <f t="shared" si="6"/>
+        <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
+      </c>
+      <c r="AG6" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v>Downgrade an Investment by $D6 levels</v>
+      </c>
+      <c r="AH6" s="79" t="str">
+        <f t="shared" si="6"/>
+        <v>Downgrade an Investment by $D6 levels</v>
+      </c>
+      <c r="AI6" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v>Demote a Leader at level $D6 by half and send it to $R</v>
+      </c>
+      <c r="AJ6" s="79" t="str">
+        <f t="shared" si="6"/>
+        <v>Demote a Leader by $D6 levels</v>
+      </c>
+      <c r="AK6" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v>Demote a Leader by $D6 levels</v>
+      </c>
+      <c r="AL6" s="79" t="str">
+        <f t="shared" si="6"/>
+        <v>Move your foremost Law to the back of the Queue</v>
+      </c>
+      <c r="AM6" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
+      </c>
+      <c r="AN6" s="79" t="str">
+        <f t="shared" si="6"/>
+        <v>Move $D6 of your Laws each one space back in the Queue</v>
+      </c>
+      <c r="AO6" s="81" t="str">
+        <f t="shared" si="6"/>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
+      </c>
+      <c r="AP6" s="79" t="str">
+        <f t="shared" si="7"/>
+        <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
+      </c>
+      <c r="AQ6" s="81" t="str">
+        <f t="shared" si="8"/>
+        <v>Give $2D6 Troops to $R</v>
+      </c>
+      <c r="AR6" s="79" t="str">
+        <f t="shared" si="8"/>
+        <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
+      </c>
+      <c r="AS6" s="81" t="str">
+        <f t="shared" si="8"/>
+        <v>Give $D6 Spies to $R</v>
+      </c>
+      <c r="AT6" s="79" t="str">
+        <f t="shared" si="8"/>
+        <v>Give $2D6 Commodities to $R</v>
+      </c>
+      <c r="AU6" s="81" t="str">
+        <f t="shared" si="8"/>
+        <v>Give $D6 random Cards of each type from your hand to $R</v>
+      </c>
+      <c r="AV6" s="79" t="str">
+        <f t="shared" si="8"/>
+        <v>Lose half your Commodities</v>
+      </c>
+      <c r="AW6" s="81" t="str">
+        <f t="shared" si="8"/>
+        <v>Lose half your Coins</v>
+      </c>
+      <c r="AX6" s="82" t="str">
+        <f t="shared" si="8"/>
+        <v>Lose half your Troops</v>
+      </c>
+      <c r="AY6" s="79" t="str">
+        <f t="shared" si="8"/>
+        <v>Lose half your Spies</v>
+      </c>
+      <c r="AZ6" s="81" t="str">
+        <f t="shared" si="8"/>
+        <v>Disard half your cards of each type</v>
+      </c>
+      <c r="BA6" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
+      </c>
+      <c r="BB6" s="81" t="str">
+        <f t="shared" si="9"/>
+        <v>Downgrade an Investment by $D6 levels</v>
+      </c>
+      <c r="BC6" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>Downgrade an Investment by $D6 levels</v>
+      </c>
+      <c r="BD6" s="81" t="str">
+        <f t="shared" si="9"/>
+        <v>Demote a Leader at level $D6 by half and send it to $R</v>
+      </c>
+      <c r="BE6" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>Demote a Leader by $D6 levels</v>
+      </c>
+      <c r="BF6" s="81" t="str">
+        <f t="shared" si="9"/>
+        <v>Demote a Leader by $D6 levels</v>
+      </c>
+      <c r="BG6" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>Move your foremost Law to the back of the Queue</v>
+      </c>
+      <c r="BH6" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
+      </c>
+      <c r="BI6" s="79" t="str">
+        <f t="shared" si="9"/>
+        <v>Move $D6 of your Laws each one space back in the Queue</v>
+      </c>
+      <c r="BJ6" s="81" t="str">
+        <f t="shared" si="9"/>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
+      </c>
+      <c r="BK6" s="79" t="str">
+        <f t="shared" si="10"/>
+        <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
+      </c>
+      <c r="BM6" s="79" t="str">
+        <f>AE2</f>
+        <v>Trade up to $L3 additional Coins when Buying from the Undermarket</v>
+      </c>
+      <c r="BN6" s="81" t="str">
+        <f>AF2</f>
+        <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
+      </c>
+      <c r="BO6" s="79" t="str">
+        <f>AG2</f>
+        <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
+      </c>
+      <c r="BP6" s="81" t="str">
         <f>AH2</f>
         <v>Provides private Monetize Action at Market Rate + $L3</v>
       </c>
-      <c r="BO4" s="104" t="str">
-        <f>AF2</f>
-        <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
-      </c>
-      <c r="BP4" s="103" t="str">
-        <f>AD2</f>
-        <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
-      </c>
-      <c r="BQ4" s="83"/>
-      <c r="BS4" s="83"/>
-    </row>
-    <row r="5" spans="1:71" s="89" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="87" t="str">
-        <f>Cards!F2</f>
-        <v>Fickle Mercenaries</v>
-      </c>
-      <c r="B5" s="88" t="str">
-        <f>Cards!F3</f>
-        <v>Blatant Thievery</v>
-      </c>
-      <c r="C5" s="89" t="str">
-        <f>Cards!F4</f>
-        <v>Double Agents</v>
-      </c>
-      <c r="D5" s="87" t="str">
-        <f>Cards!F5</f>
-        <v>Questionable Reallocation</v>
-      </c>
-      <c r="E5" s="89" t="str">
-        <f>Cards!F6</f>
-        <v>Blackmail</v>
-      </c>
-      <c r="F5" s="87" t="str">
-        <f>Cards!F7</f>
-        <v>Invalid Paperwork</v>
-      </c>
-      <c r="G5" s="89" t="str">
-        <f>Cards!F8</f>
-        <v>Insider Trading</v>
-      </c>
-      <c r="H5" s="87" t="str">
-        <f>Cards!F9</f>
-        <v>Whispers of the People</v>
-      </c>
-      <c r="I5" s="89" t="str">
-        <f>Cards!F10</f>
-        <v>Dangerous Monopolies</v>
-      </c>
-      <c r="J5" s="87" t="str">
-        <f>Cards!F11</f>
-        <v>Corporate Takeover</v>
-      </c>
-      <c r="K5" s="89" t="str">
-        <f>Cards!F12</f>
-        <v>Sabotage</v>
-      </c>
-      <c r="L5" s="87" t="str">
-        <f>Cards!F13</f>
-        <v>Poor Management</v>
-      </c>
-      <c r="M5" s="89" t="str">
-        <f>Cards!F14</f>
-        <v>Assassination</v>
-      </c>
-      <c r="N5" s="87" t="str">
-        <f>Cards!F15</f>
-        <v>Betrayal</v>
-      </c>
-      <c r="O5" s="89" t="str">
-        <f>Cards!F16</f>
-        <v>Intimidation</v>
-      </c>
-      <c r="P5" s="87" t="str">
-        <f>Cards!F17</f>
-        <v>Humiliation</v>
-      </c>
-      <c r="Q5" s="89" t="str">
-        <f>Cards!F18</f>
-        <v>Backroom Deal</v>
-      </c>
-      <c r="R5" s="87" t="str">
-        <f>Cards!F19</f>
-        <v>Rallied Opposition</v>
-      </c>
-      <c r="S5" s="89" t="str">
-        <f>Cards!F20</f>
-        <v>Waning Support</v>
-      </c>
-      <c r="T5" s="87" t="str">
-        <f>Cards!F21</f>
-        <v>Misaligned Strategy</v>
-      </c>
-      <c r="U5" s="89" t="str">
-        <f t="shared" ref="U5:AN5" si="5">A5</f>
-        <v>Fickle Mercenaries</v>
-      </c>
-      <c r="V5" s="87" t="str">
-        <f t="shared" si="5"/>
-        <v>Blatant Thievery</v>
-      </c>
-      <c r="W5" s="89" t="str">
-        <f t="shared" si="5"/>
-        <v>Double Agents</v>
-      </c>
-      <c r="X5" s="87" t="str">
-        <f t="shared" si="5"/>
-        <v>Questionable Reallocation</v>
-      </c>
-      <c r="Y5" s="89" t="str">
-        <f t="shared" si="5"/>
-        <v>Blackmail</v>
-      </c>
-      <c r="Z5" s="87" t="str">
-        <f t="shared" si="5"/>
-        <v>Invalid Paperwork</v>
-      </c>
-      <c r="AA5" s="89" t="str">
-        <f t="shared" si="5"/>
-        <v>Insider Trading</v>
-      </c>
-      <c r="AB5" s="87" t="str">
-        <f t="shared" si="5"/>
-        <v>Whispers of the People</v>
-      </c>
-      <c r="AC5" s="89" t="str">
-        <f t="shared" si="5"/>
-        <v>Dangerous Monopolies</v>
-      </c>
-      <c r="AD5" s="90" t="str">
-        <f t="shared" si="5"/>
-        <v>Corporate Takeover</v>
-      </c>
-      <c r="AE5" s="87" t="str">
-        <f t="shared" si="5"/>
-        <v>Sabotage</v>
-      </c>
-      <c r="AF5" s="87" t="str">
-        <f t="shared" si="5"/>
-        <v>Poor Management</v>
-      </c>
-      <c r="AG5" s="89" t="str">
-        <f t="shared" si="5"/>
-        <v>Assassination</v>
-      </c>
-      <c r="AH5" s="87" t="str">
-        <f t="shared" si="5"/>
-        <v>Betrayal</v>
-      </c>
-      <c r="AI5" s="89" t="str">
-        <f t="shared" si="5"/>
-        <v>Intimidation</v>
-      </c>
-      <c r="AJ5" s="87" t="str">
-        <f t="shared" si="5"/>
-        <v>Humiliation</v>
-      </c>
-      <c r="AK5" s="89" t="str">
-        <f t="shared" si="5"/>
-        <v>Backroom Deal</v>
-      </c>
-      <c r="AL5" s="87" t="str">
-        <f t="shared" si="5"/>
-        <v>Rallied Opposition</v>
-      </c>
-      <c r="AM5" s="89" t="str">
-        <f t="shared" si="5"/>
-        <v>Waning Support</v>
-      </c>
-      <c r="AN5" s="87" t="str">
-        <f t="shared" si="5"/>
-        <v>Misaligned Strategy</v>
-      </c>
-      <c r="AO5" s="89" t="str">
-        <f t="shared" ref="AO5:BH5" si="6">A5</f>
-        <v>Fickle Mercenaries</v>
-      </c>
-      <c r="AP5" s="87" t="str">
-        <f t="shared" si="6"/>
-        <v>Blatant Thievery</v>
-      </c>
-      <c r="AQ5" s="89" t="str">
-        <f t="shared" si="6"/>
-        <v>Double Agents</v>
-      </c>
-      <c r="AR5" s="87" t="str">
-        <f t="shared" si="6"/>
-        <v>Questionable Reallocation</v>
-      </c>
-      <c r="AS5" s="89" t="str">
-        <f t="shared" si="6"/>
-        <v>Blackmail</v>
-      </c>
-      <c r="AT5" s="87" t="str">
-        <f t="shared" si="6"/>
-        <v>Invalid Paperwork</v>
-      </c>
-      <c r="AU5" s="89" t="str">
-        <f t="shared" si="6"/>
-        <v>Insider Trading</v>
-      </c>
-      <c r="AV5" s="87" t="str">
-        <f t="shared" si="6"/>
-        <v>Whispers of the People</v>
-      </c>
-      <c r="AW5" s="89" t="str">
-        <f t="shared" si="6"/>
-        <v>Dangerous Monopolies</v>
-      </c>
-      <c r="AX5" s="90" t="str">
-        <f t="shared" si="6"/>
-        <v>Corporate Takeover</v>
-      </c>
-      <c r="AY5" s="87" t="str">
-        <f t="shared" si="6"/>
-        <v>Sabotage</v>
-      </c>
-      <c r="AZ5" s="89" t="str">
-        <f t="shared" si="6"/>
-        <v>Poor Management</v>
-      </c>
-      <c r="BA5" s="87" t="str">
-        <f t="shared" si="6"/>
-        <v>Assassination</v>
-      </c>
-      <c r="BB5" s="89" t="str">
-        <f t="shared" si="6"/>
-        <v>Betrayal</v>
-      </c>
-      <c r="BC5" s="87" t="str">
-        <f t="shared" si="6"/>
-        <v>Intimidation</v>
-      </c>
-      <c r="BD5" s="89" t="str">
-        <f t="shared" si="6"/>
-        <v>Humiliation</v>
-      </c>
-      <c r="BE5" s="87" t="str">
-        <f t="shared" si="6"/>
-        <v>Backroom Deal</v>
-      </c>
-      <c r="BF5" s="89" t="str">
-        <f t="shared" si="6"/>
-        <v>Rallied Opposition</v>
-      </c>
-      <c r="BG5" s="87" t="str">
-        <f t="shared" si="6"/>
-        <v>Waning Support</v>
-      </c>
-      <c r="BH5" s="87" t="str">
-        <f t="shared" si="6"/>
-        <v>Misaligned Strategy</v>
-      </c>
-      <c r="BI5" s="87"/>
-      <c r="BJ5" s="81" t="str">
-        <f>AM1</f>
-        <v>Painful Progress</v>
-      </c>
-      <c r="BK5" s="78" t="str">
-        <f>AL1</f>
-        <v>Abusive Power</v>
-      </c>
-      <c r="BL5" s="80" t="str">
-        <f>AK1</f>
-        <v>Soup Kitchens</v>
-      </c>
-      <c r="BM5" s="78" t="str">
-        <f>AJ1</f>
-        <v>Kingdom Advocates</v>
-      </c>
-      <c r="BN5" s="80" t="str">
-        <f>AI1</f>
-        <v>Fire Temple</v>
-      </c>
-      <c r="BO5" s="78" t="str">
-        <f>AG1</f>
-        <v>Large Middle Class</v>
-      </c>
-      <c r="BP5" s="79" t="str">
-        <f>AE1</f>
-        <v>Codependent Relationship</v>
-      </c>
-      <c r="BQ5" s="87"/>
-      <c r="BS5" s="87"/>
-    </row>
-    <row r="6" spans="1:71" s="85" customFormat="1" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="83" t="str">
-        <f>Cards!G2</f>
-        <v>Give $2D6 Troops to $R</v>
-      </c>
-      <c r="B6" s="84" t="str">
-        <f>Cards!G3</f>
-        <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
-      </c>
-      <c r="C6" s="85" t="str">
-        <f>Cards!G4</f>
-        <v>Give $D6 Spies to $R</v>
-      </c>
-      <c r="D6" s="83" t="str">
-        <f>Cards!G5</f>
-        <v>Give $2D6 Commodities to $R. Perform an Emergency Trade if needed.</v>
-      </c>
-      <c r="E6" s="85" t="str">
-        <f>Cards!G6</f>
-        <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
-      </c>
-      <c r="F6" s="83" t="str">
-        <f>Cards!G7</f>
-        <v>Move your foremost Law to the back of the Queue</v>
-      </c>
-      <c r="G6" s="85" t="str">
-        <f>Cards!G8</f>
-        <v>Give $D6 random Cards of each type from your hand to $R</v>
-      </c>
-      <c r="H6" s="83" t="str">
-        <f>Cards!G9</f>
-        <v>Rearrange the first $D6 Law cards in the Queue</v>
-      </c>
-      <c r="I6" s="85" t="str">
-        <f>Cards!G10</f>
-        <v>Downgrade an Investment by $D6 levels</v>
-      </c>
-      <c r="J6" s="83" t="str">
-        <f>Cards!G11</f>
-        <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
-      </c>
-      <c r="K6" s="85" t="str">
-        <f>Cards!G12</f>
-        <v>Downgrade an Investment by $D6 levels</v>
-      </c>
-      <c r="L6" s="83" t="str">
-        <f>Cards!G13</f>
-        <v>Downgrade an Investment by $D6 levels</v>
-      </c>
-      <c r="M6" s="85" t="str">
-        <f>Cards!G14</f>
-        <v>Demote a Leader by $D6 levels</v>
-      </c>
-      <c r="N6" s="83" t="str">
-        <f>Cards!G15</f>
-        <v>Demote a Leader at level $D6 by half and send it to $R</v>
-      </c>
-      <c r="O6" s="85" t="str">
-        <f>Cards!G16</f>
-        <v>Demote a Leader by $D6 levels</v>
-      </c>
-      <c r="P6" s="83" t="str">
-        <f>Cards!G17</f>
-        <v>Demote a Leader by $D6 levels</v>
-      </c>
-      <c r="Q6" s="85" t="str">
-        <f>Cards!G18</f>
-        <v>Exchange one Alliance Token with $R</v>
-      </c>
-      <c r="R6" s="83" t="str">
-        <f>Cards!G19</f>
-        <v>Move your foremost Law $D6 spaces back in the Queue</v>
-      </c>
-      <c r="S6" s="85" t="str">
-        <f>Cards!G20</f>
-        <v>Move $D6 of your Laws each one space back in the Queue</v>
-      </c>
-      <c r="T6" s="83" t="str">
-        <f>Cards!G21</f>
-        <v>Move your foremost Law $D6 spaces back in the Queue</v>
-      </c>
-      <c r="U6" s="85" t="str">
-        <f t="shared" ref="U6:AN6" si="7">A6</f>
-        <v>Give $2D6 Troops to $R</v>
-      </c>
-      <c r="V6" s="83" t="str">
-        <f t="shared" si="7"/>
-        <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
-      </c>
-      <c r="W6" s="85" t="str">
-        <f t="shared" si="7"/>
-        <v>Give $D6 Spies to $R</v>
-      </c>
-      <c r="X6" s="83" t="str">
-        <f t="shared" si="7"/>
-        <v>Give $2D6 Commodities to $R. Perform an Emergency Trade if needed.</v>
-      </c>
-      <c r="Y6" s="85" t="str">
-        <f t="shared" si="7"/>
-        <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
-      </c>
-      <c r="Z6" s="83" t="str">
-        <f t="shared" si="7"/>
-        <v>Move your foremost Law to the back of the Queue</v>
-      </c>
-      <c r="AA6" s="85" t="str">
-        <f t="shared" si="7"/>
-        <v>Give $D6 random Cards of each type from your hand to $R</v>
-      </c>
-      <c r="AB6" s="83" t="str">
-        <f t="shared" si="7"/>
-        <v>Rearrange the first $D6 Law cards in the Queue</v>
-      </c>
-      <c r="AC6" s="85" t="str">
-        <f t="shared" si="7"/>
-        <v>Downgrade an Investment by $D6 levels</v>
-      </c>
-      <c r="AD6" s="86" t="str">
-        <f t="shared" si="7"/>
-        <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
-      </c>
-      <c r="AE6" s="83" t="str">
-        <f t="shared" si="7"/>
-        <v>Downgrade an Investment by $D6 levels</v>
-      </c>
-      <c r="AF6" s="83" t="str">
-        <f t="shared" si="7"/>
-        <v>Downgrade an Investment by $D6 levels</v>
-      </c>
-      <c r="AG6" s="85" t="str">
-        <f t="shared" si="7"/>
-        <v>Demote a Leader by $D6 levels</v>
-      </c>
-      <c r="AH6" s="83" t="str">
-        <f t="shared" si="7"/>
-        <v>Demote a Leader at level $D6 by half and send it to $R</v>
-      </c>
-      <c r="AI6" s="85" t="str">
-        <f t="shared" si="7"/>
-        <v>Demote a Leader by $D6 levels</v>
-      </c>
-      <c r="AJ6" s="83" t="str">
-        <f t="shared" si="7"/>
-        <v>Demote a Leader by $D6 levels</v>
-      </c>
-      <c r="AK6" s="85" t="str">
-        <f t="shared" si="7"/>
-        <v>Exchange one Alliance Token with $R</v>
-      </c>
-      <c r="AL6" s="83" t="str">
-        <f t="shared" si="7"/>
-        <v>Move your foremost Law $D6 spaces back in the Queue</v>
-      </c>
-      <c r="AM6" s="85" t="str">
-        <f t="shared" si="7"/>
-        <v>Move $D6 of your Laws each one space back in the Queue</v>
-      </c>
-      <c r="AN6" s="83" t="str">
-        <f t="shared" si="7"/>
-        <v>Move your foremost Law $D6 spaces back in the Queue</v>
-      </c>
-      <c r="AO6" s="85" t="str">
-        <f t="shared" ref="AO6:BH6" si="8">A6</f>
-        <v>Give $2D6 Troops to $R</v>
-      </c>
-      <c r="AP6" s="83" t="str">
-        <f t="shared" si="8"/>
-        <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
-      </c>
-      <c r="AQ6" s="85" t="str">
-        <f t="shared" si="8"/>
-        <v>Give $D6 Spies to $R</v>
-      </c>
-      <c r="AR6" s="83" t="str">
-        <f t="shared" si="8"/>
-        <v>Give $2D6 Commodities to $R. Perform an Emergency Trade if needed.</v>
-      </c>
-      <c r="AS6" s="85" t="str">
-        <f t="shared" si="8"/>
-        <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
-      </c>
-      <c r="AT6" s="83" t="str">
-        <f t="shared" si="8"/>
-        <v>Move your foremost Law to the back of the Queue</v>
-      </c>
-      <c r="AU6" s="85" t="str">
-        <f t="shared" si="8"/>
-        <v>Give $D6 random Cards of each type from your hand to $R</v>
-      </c>
-      <c r="AV6" s="83" t="str">
-        <f t="shared" si="8"/>
-        <v>Rearrange the first $D6 Law cards in the Queue</v>
-      </c>
-      <c r="AW6" s="85" t="str">
-        <f t="shared" si="8"/>
-        <v>Downgrade an Investment by $D6 levels</v>
-      </c>
-      <c r="AX6" s="86" t="str">
-        <f t="shared" si="8"/>
-        <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
-      </c>
-      <c r="AY6" s="83" t="str">
-        <f t="shared" si="8"/>
-        <v>Downgrade an Investment by $D6 levels</v>
-      </c>
-      <c r="AZ6" s="85" t="str">
-        <f t="shared" si="8"/>
-        <v>Downgrade an Investment by $D6 levels</v>
-      </c>
-      <c r="BA6" s="83" t="str">
-        <f t="shared" si="8"/>
-        <v>Demote a Leader by $D6 levels</v>
-      </c>
-      <c r="BB6" s="85" t="str">
-        <f t="shared" si="8"/>
-        <v>Demote a Leader at level $D6 by half and send it to $R</v>
-      </c>
-      <c r="BC6" s="83" t="str">
-        <f t="shared" si="8"/>
-        <v>Demote a Leader by $D6 levels</v>
-      </c>
-      <c r="BD6" s="85" t="str">
-        <f t="shared" si="8"/>
-        <v>Demote a Leader by $D6 levels</v>
-      </c>
-      <c r="BE6" s="83" t="str">
-        <f t="shared" si="8"/>
-        <v>Exchange one Alliance Token with $R</v>
-      </c>
-      <c r="BF6" s="85" t="str">
-        <f t="shared" si="8"/>
-        <v>Move your foremost Law $D6 spaces back in the Queue</v>
-      </c>
-      <c r="BG6" s="83" t="str">
-        <f t="shared" si="8"/>
-        <v>Move $D6 of your Laws each one space back in the Queue</v>
-      </c>
-      <c r="BH6" s="83" t="str">
-        <f t="shared" si="8"/>
-        <v>Move your foremost Law $D6 spaces back in the Queue</v>
-      </c>
-      <c r="BI6" s="83"/>
-      <c r="BJ6" s="86" t="str">
-        <f>AM2</f>
-        <v>You may repeat Undermarket Actions at double the penalty</v>
-      </c>
-      <c r="BK6" s="83" t="str">
-        <f>AL2</f>
-        <v>Convert $L3 additional Coins during Undermarket Donate</v>
-      </c>
-      <c r="BL6" s="85" t="str">
-        <f>AK2</f>
-        <v>Convert $L3 additional Coins during Court Donate</v>
-      </c>
-      <c r="BM6" s="83" t="str">
-        <f>AJ2</f>
-        <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
-      </c>
-      <c r="BN6" s="85" t="str">
+      <c r="BQ6" s="79" t="str">
         <f>AI2</f>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
       </c>
-      <c r="BO6" s="83" t="str">
-        <f>AG2</f>
-        <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
-      </c>
-      <c r="BP6" s="84" t="str">
-        <f>AE2</f>
-        <v>Trade up to $L3 additional Coins when Buying from the Undermarket</v>
-      </c>
-      <c r="BQ6" s="83"/>
-      <c r="BS6" s="83"/>
+      <c r="BR6" s="79"/>
+      <c r="BS6" s="80"/>
+      <c r="BU6" s="79"/>
+      <c r="BW6" s="79"/>
+      <c r="BY6" s="79"/>
+      <c r="CA6" s="79"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8982,31 +9083,31 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C1" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="D1" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="E1" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="F1" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D2">
         <v>27.7</v>
@@ -9014,14 +9115,14 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D3">
         <v>27.7</v>
@@ -9029,14 +9130,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D4">
         <v>30.75</v>
@@ -9044,226 +9145,227 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E6" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E7" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E8" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E10" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E11" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E12" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="E13" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9272,98 +9374,98 @@
   <dimension ref="A1:U55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" style="106" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" style="102" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" customWidth="1"/>
     <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="108" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="108" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="108" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="108" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="11.85546875" style="108" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" style="108" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="104" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="104" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="104" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="104" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="11.85546875" style="104" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" style="104" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C1" t="s">
+        <v>427</v>
+      </c>
+      <c r="D1" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1" t="s">
+        <v>429</v>
+      </c>
+      <c r="F1" t="s">
+        <v>456</v>
+      </c>
+      <c r="G1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H1" t="s">
+        <v>430</v>
+      </c>
+      <c r="I1" t="s">
+        <v>431</v>
+      </c>
+      <c r="J1" s="104" t="s">
+        <v>453</v>
+      </c>
+      <c r="K1" t="s">
+        <v>432</v>
+      </c>
+      <c r="L1" t="s">
+        <v>433</v>
+      </c>
+      <c r="M1" t="s">
+        <v>434</v>
+      </c>
+      <c r="N1" t="s">
+        <v>435</v>
+      </c>
+      <c r="O1" t="s">
+        <v>436</v>
+      </c>
+      <c r="P1" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>438</v>
+      </c>
+      <c r="R1" t="s">
+        <v>439</v>
+      </c>
+      <c r="S1" t="s">
+        <v>440</v>
+      </c>
+      <c r="T1" t="s">
         <v>441</v>
       </c>
-      <c r="B1" t="s">
-        <v>442</v>
-      </c>
-      <c r="C1" t="s">
-        <v>443</v>
-      </c>
-      <c r="D1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E1" t="s">
-        <v>445</v>
-      </c>
-      <c r="F1" t="s">
-        <v>472</v>
-      </c>
-      <c r="G1" t="s">
-        <v>471</v>
-      </c>
-      <c r="H1" t="s">
-        <v>446</v>
-      </c>
-      <c r="I1" t="s">
-        <v>447</v>
-      </c>
-      <c r="J1" s="108" t="s">
-        <v>469</v>
-      </c>
-      <c r="K1" t="s">
-        <v>448</v>
-      </c>
-      <c r="L1" t="s">
-        <v>449</v>
-      </c>
-      <c r="M1" t="s">
-        <v>450</v>
-      </c>
-      <c r="N1" t="s">
-        <v>451</v>
-      </c>
-      <c r="O1" t="s">
-        <v>452</v>
-      </c>
-      <c r="P1" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="U1" t="s">
         <v>454</v>
       </c>
-      <c r="R1" t="s">
-        <v>455</v>
-      </c>
-      <c r="S1" t="s">
-        <v>456</v>
-      </c>
-      <c r="T1" t="s">
-        <v>457</v>
-      </c>
-      <c r="U1" t="s">
-        <v>470</v>
-      </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="106">
+      <c r="A2" s="102">
         <v>46075</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
-      <c r="C2" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D2" s="107" t="b">
+      <c r="C2" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="103" t="b">
         <v>0</v>
       </c>
       <c r="E2">
@@ -9372,42 +9474,42 @@
       <c r="F2">
         <v>17</v>
       </c>
-      <c r="H2" s="108">
+      <c r="H2" s="104">
         <v>0.79166666666666663</v>
       </c>
-      <c r="I2" s="108">
+      <c r="I2" s="104">
         <v>0.93055555555555558</v>
       </c>
-      <c r="K2" s="108">
+      <c r="K2" s="104">
         <v>0.81458333333333333</v>
       </c>
-      <c r="L2" s="108">
+      <c r="L2" s="104">
         <v>0.83125000000000004</v>
       </c>
-      <c r="M2" s="108">
+      <c r="M2" s="104">
         <v>0.85486111111111107</v>
       </c>
-      <c r="N2" s="108">
+      <c r="N2" s="104">
         <v>0.87777777777777777</v>
       </c>
-      <c r="O2" s="108">
+      <c r="O2" s="104">
         <v>0.90069444444444446</v>
       </c>
-      <c r="P2" s="108">
+      <c r="P2" s="104">
         <v>0.92638888888888893</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="106">
+      <c r="A3" s="102">
         <v>46089</v>
       </c>
       <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" s="107" t="b">
+      <c r="C3" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="103" t="b">
         <v>0</v>
       </c>
       <c r="E3">
@@ -9419,51 +9521,51 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="108">
+      <c r="H3" s="104">
         <v>0.68541666666666667</v>
       </c>
-      <c r="I3" s="108">
+      <c r="I3" s="104">
         <v>0.86527777777777781</v>
       </c>
-      <c r="J3" s="108">
+      <c r="J3" s="104">
         <v>0.6958333333333333</v>
       </c>
-      <c r="K3" s="108">
+      <c r="K3" s="104">
         <v>0.70763888888888893</v>
       </c>
-      <c r="L3" s="108">
+      <c r="L3" s="104">
         <v>0.7270833333333333</v>
       </c>
-      <c r="M3" s="108">
+      <c r="M3" s="104">
         <v>0.75069444444444444</v>
       </c>
-      <c r="N3" s="108">
+      <c r="N3" s="104">
         <v>0.77500000000000002</v>
       </c>
-      <c r="O3" s="108">
+      <c r="O3" s="104">
         <v>0.80347222222222225</v>
       </c>
-      <c r="P3" s="108">
+      <c r="P3" s="104">
         <v>0.82986111111111116</v>
       </c>
-      <c r="Q3" s="108">
+      <c r="Q3" s="104">
         <v>0.86041666666666672</v>
       </c>
-      <c r="U3" s="108">
+      <c r="U3" s="104">
         <v>0.86527777777777781</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="106">
+      <c r="A4" s="102">
         <v>46105</v>
       </c>
       <c r="B4">
         <v>6</v>
       </c>
-      <c r="C4" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="107" t="b">
+      <c r="C4" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="103" t="b">
         <v>0</v>
       </c>
       <c r="E4">
@@ -9475,446 +9577,447 @@
       <c r="G4">
         <v>10</v>
       </c>
-      <c r="H4" s="108">
+      <c r="H4" s="104">
         <v>0.77500000000000002</v>
       </c>
-      <c r="I4" s="108">
+      <c r="I4" s="104">
         <v>0.92777777777777781</v>
       </c>
-      <c r="J4" s="108">
+      <c r="J4" s="104">
         <v>0.78472222222222221</v>
       </c>
-      <c r="K4" s="108">
+      <c r="K4" s="104">
         <v>0.79236111111111107</v>
       </c>
-      <c r="L4" s="108">
+      <c r="L4" s="104">
         <v>0.81111111111111112</v>
       </c>
-      <c r="M4" s="108">
+      <c r="M4" s="104">
         <v>0.83194444444444449</v>
       </c>
-      <c r="N4" s="108">
+      <c r="N4" s="104">
         <v>0.85277777777777775</v>
       </c>
-      <c r="O4" s="108">
+      <c r="O4" s="104">
         <v>0.88263888888888886</v>
       </c>
-      <c r="P4" s="108">
+      <c r="P4" s="104">
         <v>0.92083333333333328</v>
       </c>
-      <c r="U4" s="108">
+      <c r="U4" s="104">
         <v>0.92777777777777781</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C5" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="107" t="b">
+      <c r="C5" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C6" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="107" t="b">
+      <c r="C6" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C7" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="107" t="b">
+      <c r="C7" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C8" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="107" t="b">
+      <c r="C8" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C9" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="107" t="b">
+      <c r="C9" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C10" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="107" t="b">
+      <c r="C10" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C11" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="107" t="b">
+      <c r="C11" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C12" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="107" t="b">
+      <c r="C12" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C13" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="107" t="b">
+      <c r="C13" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C14" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="107" t="b">
+      <c r="C14" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C15" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" s="107" t="b">
+      <c r="C15" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C16" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="107" t="b">
+      <c r="C16" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C17" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="107" t="b">
+      <c r="C17" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C18" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" s="107" t="b">
+      <c r="C18" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C19" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" s="107" t="b">
+      <c r="C19" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="107" t="b">
+      <c r="C20" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="107" t="b">
+      <c r="C21" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="107" t="b">
+      <c r="C22" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="107" t="b">
+      <c r="C23" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" s="107" t="b">
+      <c r="C24" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="107" t="b">
+      <c r="C25" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="107" t="b">
+      <c r="C26" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" s="107" t="b">
+      <c r="C27" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" s="107" t="b">
+      <c r="C28" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C29" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" s="107" t="b">
+      <c r="C29" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C30" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" s="107" t="b">
+      <c r="C30" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C31" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="107" t="b">
+      <c r="C31" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" s="107" t="b">
+      <c r="C32" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" s="107" t="b">
+      <c r="C33" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" s="107" t="b">
+      <c r="C34" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D35" s="107" t="b">
+      <c r="C35" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" s="107" t="b">
+      <c r="C36" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" s="107" t="b">
+      <c r="C37" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" s="107" t="b">
+      <c r="C38" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D39" s="107" t="b">
+      <c r="C39" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D40" s="107" t="b">
+      <c r="C40" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D41" s="107" t="b">
+      <c r="C41" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D41" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" s="107" t="b">
+      <c r="C42" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C43" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D43" s="107" t="b">
+      <c r="C43" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C44" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D44" s="107" t="b">
+      <c r="C44" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C45" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D45" s="107" t="b">
+      <c r="C45" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D46" s="107" t="b">
+      <c r="C46" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D47" s="107" t="b">
+      <c r="C47" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D48" s="107" t="b">
+      <c r="C48" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D49" s="107" t="b">
+      <c r="C49" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D50" s="107" t="b">
+      <c r="C50" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D51" s="107" t="b">
+      <c r="C51" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D52" s="107" t="b">
+      <c r="C52" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D53" s="107" t="b">
+      <c r="C53" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C54" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" s="107" t="b">
+      <c r="C54" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" s="103" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C55" s="107" t="b">
-        <v>0</v>
-      </c>
-      <c r="D55" s="107" t="b">
+      <c r="C55" s="103" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" s="103" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3920" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E6F7960-9CE9-48AE-ADF2-AFFB7CAA51F7}"/>
+  <xr:revisionPtr revIDLastSave="3984" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA427B99-EB21-4C0E-964D-00F6EEEB84D3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="537">
   <si>
     <t>Standard Card</t>
   </si>
@@ -160,21 +160,9 @@
     <t>7H</t>
   </si>
   <si>
-    <t>Eager Youth</t>
-  </si>
-  <si>
-    <t>Gain 1 additional Troop for free after Recruiting every 4 - $L3 Troops</t>
-  </si>
-  <si>
     <t>8H</t>
   </si>
   <si>
-    <t>Honorable Cause</t>
-  </si>
-  <si>
-    <t>Gain 1 additional Spy for free after Infiltrating every 4 - $L3 Spies</t>
-  </si>
-  <si>
     <t>Royal Amendment</t>
   </si>
   <si>
@@ -190,9 +178,6 @@
     <t>10H</t>
   </si>
   <si>
-    <t>Silvertounge</t>
-  </si>
-  <si>
     <t>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</t>
   </si>
   <si>
@@ -223,9 +208,6 @@
     <t>QH</t>
   </si>
   <si>
-    <t>Flashy Combatants</t>
-  </si>
-  <si>
     <t>Collective Ownership</t>
   </si>
   <si>
@@ -274,9 +256,6 @@
     <t>Valuable Advisors</t>
   </si>
   <si>
-    <t>Each Player must have at least $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</t>
-  </si>
-  <si>
     <t>3S</t>
   </si>
   <si>
@@ -388,9 +367,6 @@
     <t>JS</t>
   </si>
   <si>
-    <t>Training Grounds</t>
-  </si>
-  <si>
     <t>Equal Partners</t>
   </si>
   <si>
@@ -1096,9 +1072,6 @@
     <t>Place one of your favors on the scoretrack on the outside of the Battlefield</t>
   </si>
   <si>
-    <t>Give each player 2 cards from each deck for their hand. Tell each player to keep the cards private.</t>
-  </si>
-  <si>
     <t>Take the King's Favor and place it in front of your shield</t>
   </si>
   <si>
@@ -1279,9 +1252,6 @@
     <t>Accuse Master of Lies</t>
   </si>
   <si>
-    <t>Honorable Accontability</t>
-  </si>
-  <si>
     <t>Desperate Attorneys</t>
   </si>
   <si>
@@ -1303,24 +1273,12 @@
     <t>Sue</t>
   </si>
   <si>
-    <t>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy Troops</t>
-  </si>
-  <si>
-    <t>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy Troops</t>
-  </si>
-  <si>
     <t>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</t>
   </si>
   <si>
     <t>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</t>
   </si>
   <si>
-    <t>Add $L3 Hits to each Roll during a Sue</t>
-  </si>
-  <si>
-    <t>Add $L6 additional dice to each Roll during a Sue</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -1396,9 +1354,6 @@
     <t>Skillful Orators</t>
   </si>
   <si>
-    <t>Gain $L3 additional Coins from outside the Royal Bank when winning a Sue</t>
-  </si>
-  <si>
     <t>Move the Law $L6 additional places forward in the queue during Prioritize</t>
   </si>
   <si>
@@ -1591,15 +1546,9 @@
     <t>Iron Command</t>
   </si>
   <si>
-    <t>Build Level 2 Investment (Loyal Citizenry )</t>
-  </si>
-  <si>
     <t>Negotiate with Veteran</t>
   </si>
   <si>
-    <t>Build Level 2 Investment (Soup Kitchens)</t>
-  </si>
-  <si>
     <t>Increase Market Rate at Night</t>
   </si>
   <si>
@@ -1667,6 +1616,45 @@
   </si>
   <si>
     <t>Give $2D6 Commodities to $R</t>
+  </si>
+  <si>
+    <t>One Man's Trash</t>
+  </si>
+  <si>
+    <t>Draw $L6 additional cards from the top of any discard pile during Brainstorm</t>
+  </si>
+  <si>
+    <t>Honorable Accountability</t>
+  </si>
+  <si>
+    <t>Add $L3 Hits to each Roll during a Trial</t>
+  </si>
+  <si>
+    <t>Add $L6 additional dice to each Roll during a Trial</t>
+  </si>
+  <si>
+    <t>Gain $L3 additional Coins from outside the Royal Bank when winning a Trial</t>
+  </si>
+  <si>
+    <t>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy</t>
+  </si>
+  <si>
+    <t>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy</t>
+  </si>
+  <si>
+    <t>Silver-Tongue</t>
+  </si>
+  <si>
+    <t>Each Player must have at least $L6 sponsored Laws in the Edicts or in the Queue or they will suffer sanctions on Tax</t>
+  </si>
+  <si>
+    <t>Provides Private Donate action with no penalty.</t>
+  </si>
+  <si>
+    <t>Boasting Propaganda</t>
+  </si>
+  <si>
+    <t>Build Level 2 Investment (Boasting Propaganda)</t>
   </si>
 </sst>
 </file>
@@ -1778,7 +1766,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="62">
+  <borders count="69">
     <border>
       <left/>
       <right/>
@@ -2581,11 +2569,100 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF505050"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF505050"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF505050"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2774,9 +2851,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2856,6 +2930,31 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
@@ -2868,6 +2967,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2880,6 +2988,33 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2892,7 +3027,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2905,45 +3040,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3789,6 +3885,10 @@
 </FeaturePropertyBags>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4172,7 +4272,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
@@ -4183,10 +4283,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>14</v>
@@ -4195,10 +4295,10 @@
         <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
@@ -4212,19 +4312,19 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="3"/>
@@ -4244,13 +4344,13 @@
         <v>23</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
@@ -4273,10 +4373,10 @@
         <v>29</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3"/>
@@ -4299,10 +4399,10 @@
         <v>35</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3"/>
@@ -4313,22 +4413,22 @@
         <v>37</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>39</v>
+        <v>510</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
@@ -4336,25 +4436,25 @@
     </row>
     <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>41</v>
+        <v>532</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
@@ -4362,25 +4462,25 @@
     </row>
     <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>527</v>
+        <v>49</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>411</v>
+        <v>526</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>419</v>
+        <v>530</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
@@ -4388,25 +4488,25 @@
     </row>
     <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>48</v>
+        <v>446</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>49</v>
+        <v>529</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>420</v>
+        <v>531</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="2"/>
@@ -4414,25 +4514,25 @@
     </row>
     <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>54</v>
+        <v>432</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="2"/>
@@ -4440,25 +4540,25 @@
     </row>
     <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>461</v>
+        <v>61</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>450</v>
+        <v>62</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
@@ -4466,25 +4566,25 @@
     </row>
     <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>446</v>
+        <v>68</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
@@ -4492,51 +4592,51 @@
     </row>
     <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>68</v>
+        <v>468</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>73</v>
+        <v>445</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>76</v>
+        <v>533</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="2"/>
@@ -4544,25 +4644,25 @@
     </row>
     <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>498</v>
-      </c>
       <c r="G17" s="7" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="2"/>
@@ -4570,25 +4670,25 @@
     </row>
     <row r="18" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>460</v>
+        <v>83</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
@@ -4596,25 +4696,25 @@
     </row>
     <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
@@ -4622,25 +4722,25 @@
     </row>
     <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
@@ -4648,25 +4748,25 @@
     </row>
     <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
@@ -4674,25 +4774,25 @@
     </row>
     <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="3"/>
@@ -4700,19 +4800,19 @@
     </row>
     <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" s="15" t="s">
-        <v>105</v>
+        <v>403</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>527</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7"/>
@@ -4722,19 +4822,19 @@
     </row>
     <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>109</v>
+        <v>402</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>110</v>
+        <v>528</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="9"/>
@@ -4744,19 +4844,19 @@
     </row>
     <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>423</v>
-      </c>
       <c r="D25" s="6" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
@@ -4766,19 +4866,19 @@
     </row>
     <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>412</v>
+        <v>116</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>424</v>
+        <v>488</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4788,19 +4888,19 @@
     </row>
     <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>121</v>
-      </c>
       <c r="D27" s="6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4810,19 +4910,19 @@
     </row>
     <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="C28" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>503</v>
-      </c>
       <c r="D28" s="6" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4832,19 +4932,19 @@
     </row>
     <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C29" s="16" t="s">
         <v>128</v>
       </c>
+      <c r="C29" s="15" t="s">
+        <v>129</v>
+      </c>
       <c r="D29" s="6" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4854,19 +4954,19 @@
     </row>
     <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7"/>
@@ -4876,7 +4976,7 @@
     </row>
     <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>136</v>
@@ -4885,10 +4985,10 @@
         <v>137</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7"/>
@@ -4898,19 +4998,19 @@
     </row>
     <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>142</v>
+        <v>443</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -4920,19 +5020,19 @@
     </row>
     <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -4942,13 +5042,13 @@
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>147</v>
+        <v>433</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="16"/>
@@ -4960,13 +5060,13 @@
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>149</v>
+        <v>447</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>150</v>
+        <v>444</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="16"/>
@@ -4978,13 +5078,13 @@
     </row>
     <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>448</v>
+        <v>534</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4996,13 +5096,13 @@
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -5014,13 +5114,13 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -5032,13 +5132,13 @@
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>470</v>
+        <v>498</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -5050,13 +5150,13 @@
     </row>
     <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>486</v>
+        <v>524</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>485</v>
+        <v>525</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="16"/>
@@ -5068,13 +5168,13 @@
     </row>
     <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>513</v>
+        <v>454</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="16"/>
@@ -5086,7 +5186,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="16"/>
@@ -5100,7 +5200,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="16"/>
@@ -5114,7 +5214,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="16"/>
@@ -5128,7 +5228,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="16"/>
@@ -5142,7 +5242,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="16"/>
@@ -5156,7 +5256,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="16"/>
@@ -5170,7 +5270,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="16"/>
@@ -5184,7 +5284,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="16"/>
@@ -5198,7 +5298,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="16"/>
@@ -5212,10 +5312,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="16"/>
+        <v>158</v>
+      </c>
+      <c r="B51" s="106"/>
+      <c r="C51" s="107"/>
       <c r="D51" s="6"/>
       <c r="E51" s="16"/>
       <c r="F51" s="6"/>
@@ -5226,10 +5326,10 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="16"/>
+        <v>159</v>
+      </c>
+      <c r="B52" s="106"/>
+      <c r="C52" s="107"/>
       <c r="D52" s="6"/>
       <c r="E52" s="16"/>
       <c r="F52" s="6"/>
@@ -5240,7 +5340,7 @@
     </row>
     <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B53" s="10"/>
       <c r="C53" s="17"/>
@@ -5276,215 +5376,215 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="51" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B1" s="52" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D1" s="54" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="E1" s="54" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F1" s="54" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="G1" s="54" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="H1" s="54" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I1" s="55" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="47" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E2" s="50" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F2" s="50" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G2" s="50" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="H2" s="50" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="C3" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" s="42" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="42" t="s">
-        <v>334</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>185</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>186</v>
-      </c>
       <c r="H3" s="42" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="I3" s="42" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D4" s="42" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="G4" s="42" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H4" s="42" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="I4" s="45"/>
     </row>
     <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C5" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="G5" s="42" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="H5" s="42" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="I5" s="45"/>
     </row>
     <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A6" s="37" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F6" s="42" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="H6" s="42" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="I6" s="45"/>
     </row>
     <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="F7" s="44" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="H7" s="42"/>
       <c r="I7" s="45"/>
     </row>
     <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
@@ -5492,22 +5592,22 @@
     </row>
     <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
@@ -5515,19 +5615,19 @@
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
@@ -5536,17 +5636,17 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="42" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
@@ -5555,17 +5655,17 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D12" s="42"/>
       <c r="E12" s="42" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="F12" s="44"/>
       <c r="G12" s="42"/>
@@ -5574,17 +5674,17 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D13" s="42"/>
       <c r="E13" s="42" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F13" s="44"/>
       <c r="G13" s="42"/>
@@ -5593,17 +5693,17 @@
     </row>
     <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D14" s="42"/>
       <c r="E14" s="42" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="42"/>
@@ -5612,13 +5712,13 @@
     </row>
     <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="42"/>
@@ -5629,13 +5729,13 @@
     </row>
     <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D16" s="42"/>
       <c r="E16" s="42"/>
@@ -5646,13 +5746,13 @@
     </row>
     <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D17" s="42"/>
       <c r="E17" s="42"/>
@@ -5663,13 +5763,13 @@
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="42"/>
@@ -5680,13 +5780,13 @@
     </row>
     <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="42"/>
@@ -5697,13 +5797,13 @@
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
@@ -5714,13 +5814,13 @@
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
@@ -5731,13 +5831,13 @@
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -5748,13 +5848,13 @@
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D23" s="42"/>
       <c r="E23" s="42"/>
@@ -5765,13 +5865,13 @@
     </row>
     <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="42"/>
@@ -5782,13 +5882,13 @@
     </row>
     <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="D25" s="43"/>
       <c r="E25" s="43"/>
@@ -5812,703 +5912,698 @@
     <col min="2" max="7" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="68"/>
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="67"/>
       <c r="B1" s="61" t="s">
+        <v>236</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>237</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>238</v>
+      </c>
+      <c r="E1" s="60" t="s">
+        <v>239</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1" s="60" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="69" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="70" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="108" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="112" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="69" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="63" t="s">
+        <v>532</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>435</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="59" t="s">
+        <v>402</v>
+      </c>
+      <c r="G3" s="63" t="s">
+        <v>136</v>
+      </c>
+      <c r="I3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="69" t="s">
         <v>244</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="B4" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="63" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="62" t="s">
+        <v>119</v>
+      </c>
+      <c r="E4" s="109" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="62" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="69" t="s">
         <v>245</v>
       </c>
-      <c r="D1" s="60" t="s">
-        <v>246</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>248</v>
-      </c>
-      <c r="G1" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="I1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="70" t="s">
-        <v>250</v>
-      </c>
-      <c r="B2" s="71" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="64" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="F2" s="59" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>131</v>
-      </c>
-      <c r="I2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
-        <v>251</v>
-      </c>
-      <c r="B3" s="72" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="62" t="s">
-        <v>449</v>
-      </c>
-      <c r="E3" s="62" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="I3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="70" t="s">
-        <v>252</v>
-      </c>
-      <c r="B4" s="63" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="D4" s="62" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="62" t="s">
-        <v>82</v>
-      </c>
-      <c r="F4" s="62" t="s">
-        <v>120</v>
-      </c>
-      <c r="G4" s="62" t="s">
-        <v>124</v>
-      </c>
-      <c r="I4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
-        <v>253</v>
-      </c>
-      <c r="B5" s="69" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="69" t="s">
-        <v>63</v>
+      <c r="B5" s="68" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>57</v>
       </c>
       <c r="D5" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="67" t="s">
-        <v>21</v>
+      <c r="E5" s="110" t="s">
+        <v>446</v>
+      </c>
+      <c r="F5" s="113" t="s">
+        <v>83</v>
+      </c>
+      <c r="G5" s="111" t="s">
+        <v>456</v>
       </c>
       <c r="I5" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="93" t="s">
-        <v>254</v>
-      </c>
-      <c r="B6" s="94" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="95" t="s">
+      <c r="A6" s="92" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" s="93" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="96" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="97" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="96" t="s">
-        <v>64</v>
-      </c>
-      <c r="G6" s="98" t="s">
-        <v>129</v>
+      <c r="D6" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="96" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="95" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="97" t="s">
+        <v>121</v>
       </c>
       <c r="I6" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="73" t="s">
-        <v>255</v>
-      </c>
-      <c r="B7" s="73" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" s="70" t="s">
-        <v>355</v>
+      <c r="A7" s="72" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" s="72" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>346</v>
       </c>
       <c r="D7" t="s">
-        <v>257</v>
-      </c>
-      <c r="E7" s="70" t="s">
-        <v>258</v>
+        <v>249</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>250</v>
       </c>
       <c r="F7" t="s">
-        <v>259</v>
-      </c>
-      <c r="G7" s="70" t="s">
-        <v>176</v>
+        <v>251</v>
+      </c>
+      <c r="G7" s="69" t="s">
+        <v>168</v>
       </c>
       <c r="I7" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="91" t="s">
-        <v>307</v>
-      </c>
-      <c r="B8" s="91" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="87" t="s">
-        <v>248</v>
-      </c>
-      <c r="D8" s="91" t="s">
-        <v>249</v>
-      </c>
-      <c r="E8" s="87" t="s">
-        <v>244</v>
-      </c>
-      <c r="F8" s="91" t="s">
-        <v>245</v>
-      </c>
-      <c r="G8" s="88" t="s">
-        <v>246</v>
+      <c r="A8" s="90" t="s">
+        <v>299</v>
+      </c>
+      <c r="B8" s="90" t="s">
+        <v>239</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" s="90" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="86" t="s">
+        <v>236</v>
+      </c>
+      <c r="F8" s="90" t="s">
+        <v>237</v>
+      </c>
+      <c r="G8" s="87" t="s">
+        <v>238</v>
       </c>
       <c r="I8" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="59" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D9" s="59" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E9" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="F9" s="59" t="s">
-        <v>244</v>
-      </c>
-      <c r="G9" s="72" t="s">
-        <v>247</v>
+        <v>236</v>
+      </c>
+      <c r="G9" s="71" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="92" t="s">
-        <v>309</v>
-      </c>
-      <c r="B10" s="92" t="s">
-        <v>246</v>
-      </c>
-      <c r="C10" s="89" t="s">
-        <v>249</v>
-      </c>
-      <c r="D10" s="92" t="s">
-        <v>244</v>
-      </c>
-      <c r="E10" s="89" t="s">
-        <v>248</v>
-      </c>
-      <c r="F10" s="92" t="s">
-        <v>247</v>
-      </c>
-      <c r="G10" s="90" t="s">
-        <v>245</v>
+      <c r="A10" s="91" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" s="91" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="88" t="s">
+        <v>241</v>
+      </c>
+      <c r="D10" s="91" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" s="88" t="s">
+        <v>240</v>
+      </c>
+      <c r="F10" s="91" t="s">
+        <v>239</v>
+      </c>
+      <c r="G10" s="89" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>363</v>
-      </c>
       <c r="B22" s="2" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
-        <v>365</v>
-      </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:9" ht="225" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="2" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="345" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="255" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="195" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C30" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="I30" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="E32" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
-      <c r="B33" s="2" t="s">
-        <v>515</v>
-      </c>
+      <c r="B33" s="2"/>
       <c r="C33" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D33" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="G34" s="2"/>
     </row>
@@ -6522,101 +6617,101 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="I36" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I37" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I38" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="2" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E39" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="I39" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="G40" s="2"/>
       <c r="I40" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -6628,7 +6723,7 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="I41" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -6659,165 +6754,165 @@
     </row>
     <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B47" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B50" s="2" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="G50" s="2"/>
     </row>
     <row r="52" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -6833,80 +6928,80 @@
     </row>
     <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="2" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
@@ -6935,66 +7030,66 @@
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="32" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>331</v>
-      </c>
-      <c r="E1" s="106" t="s">
-        <v>178</v>
+        <v>323</v>
+      </c>
+      <c r="E1" s="114" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="31" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="107"/>
+        <v>195</v>
+      </c>
+      <c r="E2" s="115"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3" s="30" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="E3" s="107"/>
+        <v>210</v>
+      </c>
+      <c r="E3" s="115"/>
     </row>
     <row r="4" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A4" s="34" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -7021,46 +7116,46 @@
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>238</v>
-      </c>
-      <c r="E1" s="108" t="s">
-        <v>235</v>
+        <v>230</v>
+      </c>
+      <c r="E1" s="116" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="D2" s="105" t="s">
-        <v>466</v>
-      </c>
-      <c r="E2" s="109"/>
+        <v>223</v>
+      </c>
+      <c r="D2" s="104" t="s">
+        <v>451</v>
+      </c>
+      <c r="E2" s="117"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="132" t="s">
-        <v>260</v>
-      </c>
-      <c r="B3" s="133" t="s">
-        <v>261</v>
-      </c>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="135"/>
+      <c r="A3" s="105" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" s="118" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="120"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7083,216 +7178,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="110">
-        <v>0</v>
-      </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="110">
+      <c r="A1" s="121">
+        <v>0</v>
+      </c>
+      <c r="B1" s="122"/>
+      <c r="C1" s="121">
         <v>1</v>
       </c>
-      <c r="D1" s="111"/>
-      <c r="E1" s="110">
+      <c r="D1" s="122"/>
+      <c r="E1" s="121">
         <v>2</v>
       </c>
-      <c r="F1" s="111"/>
-      <c r="G1" s="110">
+      <c r="F1" s="122"/>
+      <c r="G1" s="121">
         <v>3</v>
       </c>
-      <c r="H1" s="111"/>
-      <c r="I1" s="110">
+      <c r="H1" s="122"/>
+      <c r="I1" s="121">
         <v>4</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="110">
+      <c r="J1" s="122"/>
+      <c r="K1" s="121">
         <v>5</v>
       </c>
-      <c r="L1" s="111"/>
-      <c r="M1" s="110">
+      <c r="L1" s="122"/>
+      <c r="M1" s="121">
         <v>6</v>
       </c>
-      <c r="N1" s="111"/>
+      <c r="N1" s="122"/>
     </row>
     <row r="2" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="112">
+      <c r="A2" s="123">
         <v>19</v>
       </c>
-      <c r="B2" s="114" t="s">
-        <v>262</v>
-      </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="112">
+      <c r="B2" s="134" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="135"/>
+      <c r="M2" s="136"/>
+      <c r="N2" s="123">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="113"/>
-      <c r="B3" s="117"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="118"/>
-      <c r="K3" s="118"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="113"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="139"/>
+      <c r="N3" s="124"/>
     </row>
     <row r="4" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="112">
+      <c r="A4" s="123">
         <v>18</v>
       </c>
-      <c r="B4" s="120"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="121"/>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="121"/>
-      <c r="J4" s="121"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="121"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="112">
+      <c r="B4" s="140"/>
+      <c r="C4" s="141"/>
+      <c r="D4" s="141"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="141"/>
+      <c r="H4" s="141"/>
+      <c r="I4" s="141"/>
+      <c r="J4" s="141"/>
+      <c r="K4" s="141"/>
+      <c r="L4" s="141"/>
+      <c r="M4" s="142"/>
+      <c r="N4" s="123">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="113"/>
-      <c r="B5" s="123" t="s">
-        <v>263</v>
-      </c>
-      <c r="C5" s="124"/>
-      <c r="D5" s="125" t="s">
-        <v>263</v>
-      </c>
-      <c r="E5" s="126"/>
-      <c r="F5" s="125" t="s">
-        <v>263</v>
-      </c>
-      <c r="G5" s="126"/>
-      <c r="H5" s="125" t="s">
-        <v>263</v>
-      </c>
-      <c r="I5" s="126"/>
-      <c r="J5" s="125" t="s">
-        <v>263</v>
-      </c>
-      <c r="K5" s="126"/>
-      <c r="L5" s="125" t="s">
-        <v>263</v>
-      </c>
-      <c r="M5" s="127"/>
-      <c r="N5" s="113"/>
+      <c r="A5" s="124"/>
+      <c r="B5" s="125" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="126"/>
+      <c r="D5" s="129" t="s">
+        <v>255</v>
+      </c>
+      <c r="E5" s="130"/>
+      <c r="F5" s="129" t="s">
+        <v>255</v>
+      </c>
+      <c r="G5" s="130"/>
+      <c r="H5" s="129" t="s">
+        <v>255</v>
+      </c>
+      <c r="I5" s="130"/>
+      <c r="J5" s="129" t="s">
+        <v>255</v>
+      </c>
+      <c r="K5" s="130"/>
+      <c r="L5" s="129" t="s">
+        <v>255</v>
+      </c>
+      <c r="M5" s="133"/>
+      <c r="N5" s="124"/>
     </row>
     <row r="6" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="112">
+      <c r="A6" s="123">
         <v>17</v>
       </c>
-      <c r="B6" s="123"/>
-      <c r="C6" s="124"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="123"/>
-      <c r="G6" s="128"/>
-      <c r="H6" s="123"/>
-      <c r="I6" s="128"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="128"/>
-      <c r="L6" s="123"/>
-      <c r="M6" s="124"/>
-      <c r="N6" s="112">
+      <c r="B6" s="125"/>
+      <c r="C6" s="126"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="125"/>
+      <c r="G6" s="131"/>
+      <c r="H6" s="125"/>
+      <c r="I6" s="131"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="131"/>
+      <c r="L6" s="125"/>
+      <c r="M6" s="126"/>
+      <c r="N6" s="123">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="113"/>
-      <c r="B7" s="129"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="131"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="131"/>
-      <c r="J7" s="129"/>
-      <c r="K7" s="131"/>
-      <c r="L7" s="129"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="113"/>
+      <c r="A7" s="124"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="132"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="127"/>
+      <c r="I7" s="132"/>
+      <c r="J7" s="127"/>
+      <c r="K7" s="132"/>
+      <c r="L7" s="127"/>
+      <c r="M7" s="128"/>
+      <c r="N7" s="124"/>
     </row>
     <row r="8" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="110">
+      <c r="A8" s="121">
         <v>16</v>
       </c>
-      <c r="B8" s="111"/>
-      <c r="C8" s="110">
+      <c r="B8" s="122"/>
+      <c r="C8" s="121">
         <v>15</v>
       </c>
-      <c r="D8" s="111"/>
-      <c r="E8" s="110">
+      <c r="D8" s="122"/>
+      <c r="E8" s="121">
         <v>14</v>
       </c>
-      <c r="F8" s="111"/>
-      <c r="G8" s="110">
+      <c r="F8" s="122"/>
+      <c r="G8" s="121">
         <v>13</v>
       </c>
-      <c r="H8" s="111"/>
-      <c r="I8" s="110">
+      <c r="H8" s="122"/>
+      <c r="I8" s="121">
         <v>12</v>
       </c>
-      <c r="J8" s="111"/>
-      <c r="K8" s="110">
+      <c r="J8" s="122"/>
+      <c r="K8" s="121">
         <v>11</v>
       </c>
-      <c r="L8" s="111"/>
-      <c r="M8" s="110">
+      <c r="L8" s="122"/>
+      <c r="M8" s="121">
         <v>10</v>
       </c>
-      <c r="N8" s="111"/>
+      <c r="N8" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="F5:G7"/>
+    <mergeCell ref="H5:I7"/>
+    <mergeCell ref="J5:K7"/>
+    <mergeCell ref="L5:M7"/>
+    <mergeCell ref="B2:M4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
     <mergeCell ref="B5:C7"/>
     <mergeCell ref="D5:E7"/>
-    <mergeCell ref="F5:G7"/>
-    <mergeCell ref="H5:I7"/>
-    <mergeCell ref="J5:K7"/>
-    <mergeCell ref="L5:M7"/>
-    <mergeCell ref="B2:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -7305,7 +7400,7 @@
   <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" style="59"/>
-    <col min="2" max="2" width="19.7109375" style="72"/>
+    <col min="2" max="2" width="19.7109375" style="71"/>
     <col min="4" max="4" width="19.7109375" style="59"/>
     <col min="6" max="6" width="19.7109375" style="59"/>
     <col min="8" max="8" width="19.7109375" style="59"/>
@@ -7319,7 +7414,7 @@
     <col min="24" max="24" width="19.7109375" style="59"/>
     <col min="26" max="26" width="19.7109375" style="59"/>
     <col min="28" max="28" width="19.7109375" style="59"/>
-    <col min="30" max="30" width="19.7109375" style="78"/>
+    <col min="30" max="30" width="19.7109375" style="77"/>
     <col min="31" max="32" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
@@ -7338,7 +7433,7 @@
     <col min="47" max="47" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.7109375" style="78" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.7109375" style="77" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
@@ -7348,1720 +7443,1720 @@
     <col min="57" max="57" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="19.7109375" style="78" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19.7109375" style="77" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="19.7109375" style="59"/>
     <col min="63" max="63" width="19.7109375" style="59"/>
     <col min="65" max="65" width="19.7109375" style="59"/>
     <col min="67" max="67" width="19.7109375" style="59"/>
     <col min="69" max="70" width="19.7109375" style="59"/>
-    <col min="71" max="71" width="19.7109375" style="72"/>
+    <col min="71" max="71" width="19.7109375" style="71"/>
     <col min="73" max="73" width="19.7109375" style="59"/>
     <col min="75" max="75" width="19.7109375" style="59"/>
     <col min="77" max="77" width="19.7109375" style="59"/>
     <col min="79" max="79" width="19.7109375" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" s="76" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="str">
+    <row r="1" spans="1:79" s="75" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="73" t="str">
         <f>Cards!B2</f>
         <v>Fillibuster</v>
       </c>
-      <c r="B1" s="75" t="str">
+      <c r="B1" s="74" t="str">
         <f>Cards!B3</f>
         <v>Skillful Orators</v>
       </c>
-      <c r="C1" s="76" t="str">
+      <c r="C1" s="75" t="str">
         <f>Cards!B4</f>
         <v>Collection Stations</v>
       </c>
-      <c r="D1" s="74" t="str">
+      <c r="D1" s="73" t="str">
         <f>Cards!B5</f>
         <v>Brown Nose</v>
       </c>
-      <c r="E1" s="76" t="str">
+      <c r="E1" s="75" t="str">
         <f>Cards!B6</f>
         <v>Mysterious Windfalls</v>
       </c>
-      <c r="F1" s="74" t="str">
+      <c r="F1" s="73" t="str">
         <f>Cards!B7</f>
         <v>Lobbyists</v>
       </c>
-      <c r="G1" s="76" t="str">
+      <c r="G1" s="75" t="e">
+        <f>Cards!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H1" s="73" t="e">
+        <f>Cards!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I1" s="75" t="str">
         <f>Cards!B8</f>
-        <v>Eager Youth</v>
-      </c>
-      <c r="H1" s="74" t="str">
+        <v>Loyal Citizenry</v>
+      </c>
+      <c r="J1" s="73" t="str">
         <f>Cards!B9</f>
-        <v>Honorable Cause</v>
-      </c>
-      <c r="I1" s="76" t="str">
+        <v>Silver-Tongue</v>
+      </c>
+      <c r="K1" s="75" t="str">
         <f>Cards!B10</f>
-        <v>Loyal Citizenry</v>
-      </c>
-      <c r="J1" s="74" t="str">
+        <v>Royal Bribes</v>
+      </c>
+      <c r="L1" s="73" t="str">
         <f>Cards!B11</f>
-        <v>Silvertounge</v>
-      </c>
-      <c r="K1" s="76" t="str">
+        <v>Courtroom Gambling</v>
+      </c>
+      <c r="M1" s="75" t="str">
         <f>Cards!B12</f>
-        <v>Royal Bribes</v>
-      </c>
-      <c r="L1" s="74" t="str">
+        <v>Market Niche</v>
+      </c>
+      <c r="N1" s="73" t="str">
         <f>Cards!B13</f>
-        <v>Courtroom Gambling</v>
-      </c>
-      <c r="M1" s="76" t="str">
+        <v>Genius Commanders</v>
+      </c>
+      <c r="O1" s="75" t="str">
         <f>Cards!B14</f>
-        <v>Market Niche</v>
-      </c>
-      <c r="N1" s="74" t="str">
+        <v>Damage Redemption</v>
+      </c>
+      <c r="P1" s="73" t="str">
         <f>Cards!B15</f>
-        <v>Genius Commanders</v>
-      </c>
-      <c r="O1" s="76" t="str">
+        <v>Undeniable Advisors</v>
+      </c>
+      <c r="Q1" s="75" t="str">
         <f>Cards!B16</f>
-        <v>Damage Redemption</v>
-      </c>
-      <c r="P1" s="74" t="str">
+        <v>Heavy Overtime</v>
+      </c>
+      <c r="R1" s="73" t="str">
         <f>Cards!B17</f>
-        <v>Undeniable Advisors</v>
-      </c>
-      <c r="Q1" s="76" t="str">
+        <v>Bulk Purchaser</v>
+      </c>
+      <c r="S1" s="75" t="str">
         <f>Cards!B18</f>
-        <v>Heavy Overtime</v>
-      </c>
-      <c r="R1" s="74" t="str">
+        <v>Valuable Cargo</v>
+      </c>
+      <c r="T1" s="73" t="str">
         <f>Cards!B19</f>
-        <v>Bulk Purchaser</v>
-      </c>
-      <c r="S1" s="76" t="str">
+        <v>Elite Troops</v>
+      </c>
+      <c r="U1" s="75" t="str">
         <f>Cards!B20</f>
-        <v>Valuable Cargo</v>
-      </c>
-      <c r="T1" s="74" t="str">
+        <v>Bazaar</v>
+      </c>
+      <c r="V1" s="73" t="str">
         <f>Cards!B21</f>
-        <v>Elite Troops</v>
-      </c>
-      <c r="U1" s="76" t="str">
+        <v>Caravansaray</v>
+      </c>
+      <c r="W1" s="75" t="str">
         <f>Cards!B22</f>
-        <v>Bazaar</v>
-      </c>
-      <c r="V1" s="74" t="str">
+        <v>War Machines</v>
+      </c>
+      <c r="X1" s="73" t="str">
         <f>Cards!B23</f>
-        <v>Caravansaray</v>
-      </c>
-      <c r="W1" s="76" t="str">
+        <v>Mock Trials</v>
+      </c>
+      <c r="Y1" s="75" t="str">
         <f>Cards!B24</f>
-        <v>War Machines</v>
-      </c>
-      <c r="X1" s="74" t="str">
+        <v>Desperate Attorneys</v>
+      </c>
+      <c r="Z1" s="73" t="str">
         <f>Cards!B25</f>
-        <v>Mock Trials</v>
-      </c>
-      <c r="Y1" s="76" t="str">
+        <v>Eager Laborers</v>
+      </c>
+      <c r="AA1" s="75" t="str">
         <f>Cards!B26</f>
-        <v>Desperate Attorneys</v>
-      </c>
-      <c r="Z1" s="74" t="str">
+        <v>Wary Guards</v>
+      </c>
+      <c r="AB1" s="73" t="str">
         <f>Cards!B27</f>
-        <v>Eager Laborers</v>
-      </c>
-      <c r="AA1" s="76" t="str">
+        <v>Information Security</v>
+      </c>
+      <c r="AC1" s="75" t="str">
         <f>Cards!B28</f>
-        <v>Wary Guards</v>
-      </c>
-      <c r="AB1" s="74" t="str">
+        <v>Blood Pact</v>
+      </c>
+      <c r="AD1" s="76" t="str">
         <f>Cards!B29</f>
-        <v>Information Security</v>
-      </c>
-      <c r="AC1" s="76" t="str">
+        <v>Expert Broker</v>
+      </c>
+      <c r="AE1" s="73" t="str">
         <f>Cards!B30</f>
-        <v>Blood Pact</v>
-      </c>
-      <c r="AD1" s="77" t="str">
+        <v>Codependent Relationship</v>
+      </c>
+      <c r="AF1" s="73" t="str">
         <f>Cards!B31</f>
-        <v>Expert Broker</v>
-      </c>
-      <c r="AE1" s="74" t="str">
+        <v>Dangerous Promises</v>
+      </c>
+      <c r="AG1" s="75" t="str">
         <f>Cards!B32</f>
-        <v>Codependent Relationship</v>
-      </c>
-      <c r="AF1" s="74" t="str">
+        <v>Large Middle Class</v>
+      </c>
+      <c r="AH1" s="73" t="str">
         <f>Cards!B33</f>
-        <v>Dangerous Promises</v>
-      </c>
-      <c r="AG1" s="76" t="str">
+        <v>Innovation Hub</v>
+      </c>
+      <c r="AI1" s="75" t="str">
         <f>Cards!B34</f>
-        <v>Large Middle Class</v>
-      </c>
-      <c r="AH1" s="74" t="str">
+        <v>Fire Temple</v>
+      </c>
+      <c r="AJ1" s="73" t="str">
         <f>Cards!B35</f>
-        <v>Innovation Hub</v>
-      </c>
-      <c r="AI1" s="76" t="str">
+        <v>Kingdom Advocates</v>
+      </c>
+      <c r="AK1" s="75" t="str">
         <f>Cards!B36</f>
-        <v>Fire Temple</v>
-      </c>
-      <c r="AJ1" s="74" t="str">
+        <v>Soup Kitchens</v>
+      </c>
+      <c r="AL1" s="73" t="str">
         <f>Cards!B37</f>
-        <v>Kingdom Advocates</v>
-      </c>
-      <c r="AK1" s="76" t="str">
+        <v>Abusive Power</v>
+      </c>
+      <c r="AM1" s="75" t="str">
         <f>Cards!B38</f>
-        <v>Soup Kitchens</v>
-      </c>
-      <c r="AL1" s="74" t="str">
+        <v>Painful Progress</v>
+      </c>
+      <c r="AN1" s="73" t="str">
         <f>Cards!B39</f>
-        <v>Abusive Power</v>
-      </c>
-      <c r="AM1" s="76" t="str">
-        <f>Cards!B40</f>
-        <v>Painful Progress</v>
-      </c>
-      <c r="AN1" s="74" t="str">
-        <f>Cards!B41</f>
         <v>Iron Command</v>
       </c>
-      <c r="AO1" s="76" t="str">
+      <c r="AO1" s="75" t="str">
         <f t="shared" ref="AO1:AX2" si="0">A1</f>
         <v>Fillibuster</v>
       </c>
-      <c r="AP1" s="74" t="str">
+      <c r="AP1" s="73" t="str">
         <f t="shared" si="0"/>
         <v>Skillful Orators</v>
       </c>
-      <c r="AQ1" s="76" t="str">
+      <c r="AQ1" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Collection Stations</v>
       </c>
-      <c r="AR1" s="74" t="str">
+      <c r="AR1" s="73" t="str">
         <f t="shared" si="0"/>
         <v>Brown Nose</v>
       </c>
-      <c r="AS1" s="76" t="str">
+      <c r="AS1" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Mysterious Windfalls</v>
       </c>
-      <c r="AT1" s="74" t="str">
+      <c r="AT1" s="73" t="str">
         <f t="shared" si="0"/>
         <v>Lobbyists</v>
       </c>
-      <c r="AU1" s="76" t="str">
+      <c r="AU1" s="75" t="e">
         <f t="shared" si="0"/>
-        <v>Eager Youth</v>
-      </c>
-      <c r="AV1" s="74" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="AV1" s="73" t="e">
         <f t="shared" si="0"/>
-        <v>Honorable Cause</v>
-      </c>
-      <c r="AW1" s="76" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="AW1" s="75" t="str">
         <f t="shared" si="0"/>
         <v>Loyal Citizenry</v>
       </c>
-      <c r="AX1" s="77" t="str">
+      <c r="AX1" s="76" t="str">
         <f t="shared" si="0"/>
-        <v>Silvertounge</v>
-      </c>
-      <c r="AY1" s="74" t="str">
+        <v>Silver-Tongue</v>
+      </c>
+      <c r="AY1" s="73" t="str">
         <f t="shared" ref="AY1:BH2" si="1">K1</f>
         <v>Royal Bribes</v>
       </c>
-      <c r="AZ1" s="76" t="str">
+      <c r="AZ1" s="75" t="str">
         <f t="shared" si="1"/>
         <v>Courtroom Gambling</v>
       </c>
-      <c r="BA1" s="74" t="str">
+      <c r="BA1" s="73" t="str">
         <f t="shared" si="1"/>
         <v>Market Niche</v>
       </c>
-      <c r="BB1" s="76" t="str">
+      <c r="BB1" s="75" t="str">
         <f t="shared" si="1"/>
         <v>Genius Commanders</v>
       </c>
-      <c r="BC1" s="74" t="str">
+      <c r="BC1" s="73" t="str">
         <f t="shared" si="1"/>
         <v>Damage Redemption</v>
       </c>
-      <c r="BD1" s="76" t="str">
+      <c r="BD1" s="75" t="str">
         <f t="shared" si="1"/>
         <v>Undeniable Advisors</v>
       </c>
-      <c r="BE1" s="74" t="str">
+      <c r="BE1" s="73" t="str">
         <f t="shared" si="1"/>
         <v>Heavy Overtime</v>
       </c>
-      <c r="BF1" s="76" t="str">
+      <c r="BF1" s="75" t="str">
         <f t="shared" si="1"/>
         <v>Bulk Purchaser</v>
       </c>
-      <c r="BG1" s="74" t="str">
+      <c r="BG1" s="73" t="str">
         <f t="shared" si="1"/>
         <v>Valuable Cargo</v>
       </c>
-      <c r="BH1" s="77" t="str">
+      <c r="BH1" s="76" t="str">
         <f t="shared" si="1"/>
         <v>Elite Troops</v>
       </c>
-      <c r="BI1" s="74" t="str">
+      <c r="BI1" s="73" t="str">
         <f t="shared" ref="BI1:BR2" si="2">U1</f>
         <v>Bazaar</v>
       </c>
-      <c r="BJ1" s="76" t="str">
+      <c r="BJ1" s="75" t="str">
         <f t="shared" si="2"/>
         <v>Caravansaray</v>
       </c>
-      <c r="BK1" s="74" t="str">
+      <c r="BK1" s="73" t="str">
         <f t="shared" si="2"/>
         <v>War Machines</v>
       </c>
-      <c r="BL1" s="76" t="str">
+      <c r="BL1" s="75" t="str">
         <f t="shared" si="2"/>
         <v>Mock Trials</v>
       </c>
-      <c r="BM1" s="74" t="str">
+      <c r="BM1" s="73" t="str">
         <f t="shared" si="2"/>
         <v>Desperate Attorneys</v>
       </c>
-      <c r="BN1" s="76" t="str">
+      <c r="BN1" s="75" t="str">
         <f t="shared" si="2"/>
         <v>Eager Laborers</v>
       </c>
-      <c r="BO1" s="74" t="str">
+      <c r="BO1" s="73" t="str">
         <f t="shared" si="2"/>
         <v>Wary Guards</v>
       </c>
-      <c r="BP1" s="76" t="str">
+      <c r="BP1" s="75" t="str">
         <f t="shared" si="2"/>
         <v>Information Security</v>
       </c>
-      <c r="BQ1" s="74" t="str">
+      <c r="BQ1" s="73" t="str">
         <f t="shared" si="2"/>
         <v>Blood Pact</v>
       </c>
-      <c r="BR1" s="74" t="str">
+      <c r="BR1" s="73" t="str">
         <f t="shared" si="2"/>
         <v>Expert Broker</v>
       </c>
-      <c r="BS1" s="74"/>
-      <c r="BU1" s="74"/>
-      <c r="BW1" s="74"/>
-      <c r="BY1" s="74"/>
-      <c r="CA1" s="74"/>
-    </row>
-    <row r="2" spans="1:79" s="99" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="100" t="str">
+      <c r="BS1" s="73"/>
+      <c r="BU1" s="73"/>
+      <c r="BW1" s="73"/>
+      <c r="BY1" s="73"/>
+      <c r="CA1" s="73"/>
+    </row>
+    <row r="2" spans="1:79" s="98" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="99" t="str">
         <f>Cards!C2</f>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
       </c>
-      <c r="B2" s="100" t="str">
+      <c r="B2" s="99" t="str">
         <f>Cards!C3</f>
         <v>Move the Law $L6 additional places forward in the queue during Prioritize</v>
       </c>
-      <c r="C2" s="99" t="str">
+      <c r="C2" s="98" t="str">
         <f>Cards!C4</f>
         <v xml:space="preserve">You may keep up to $L6 additional Coins when Taxing other Players </v>
       </c>
-      <c r="D2" s="100" t="str">
+      <c r="D2" s="99" t="str">
         <f>Cards!C5</f>
         <v>Gain $L3 additional Coins during Flatter</v>
       </c>
-      <c r="E2" s="99" t="str">
+      <c r="E2" s="98" t="str">
         <f>Cards!C6</f>
         <v>Gain $L3 more Commodities per Coin when Buying from the Undermarket</v>
       </c>
-      <c r="F2" s="100" t="str">
+      <c r="F2" s="99" t="str">
         <f>Cards!C7</f>
         <v>Add $L3 additional Law cards to the bottom of the queue during Petition</v>
       </c>
-      <c r="G2" s="99" t="str">
+      <c r="G2" s="98" t="e">
+        <f>Cards!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H2" s="99" t="e">
+        <f>Cards!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I2" s="99" t="str">
         <f>Cards!C8</f>
-        <v>Gain 1 additional Troop for free after Recruiting every 4 - $L3 Troops</v>
-      </c>
-      <c r="H2" s="100" t="str">
+        <v>Purchase up to $L6 additional Troops during Recruit (at normal cost)</v>
+      </c>
+      <c r="J2" s="99" t="str">
         <f>Cards!C9</f>
-        <v>Gain 1 additional Spy for free after Infiltrating every 4 - $L3 Spies</v>
-      </c>
-      <c r="I2" s="100" t="str">
+        <v>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</v>
+      </c>
+      <c r="K2" s="98" t="str">
         <f>Cards!C10</f>
-        <v>Purchase up to $L6 additional Troops during Recruit (at normal cost)</v>
-      </c>
-      <c r="J2" s="100" t="str">
+        <v>Gain $L3 more Commodities per Coin when Buying from the Court</v>
+      </c>
+      <c r="L2" s="99" t="str">
         <f>Cards!C11</f>
-        <v>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</v>
-      </c>
-      <c r="K2" s="99" t="str">
+        <v>Gain $L3 additional Coins from outside the Royal Bank when winning a Trial</v>
+      </c>
+      <c r="M2" s="98" t="str">
         <f>Cards!C12</f>
-        <v>Gain $L3 more Commodities per Coin when Buying from the Court</v>
-      </c>
-      <c r="L2" s="100" t="str">
+        <v>Spend $L3 fewer Cards per Coin when Monetizing in the Undermarket</v>
+      </c>
+      <c r="N2" s="99" t="str">
         <f>Cards!C13</f>
-        <v>Gain $L3 additional Coins from outside the Royal Bank when winning a Sue</v>
-      </c>
-      <c r="M2" s="99" t="str">
+        <v>Draw $L6 additional cards from any decks during Brainstorm</v>
+      </c>
+      <c r="O2" s="98" t="str">
         <f>Cards!C14</f>
-        <v>Spend $L3 fewer Cards per Coin when Monetizing in the Undermarket</v>
-      </c>
-      <c r="N2" s="100" t="str">
+        <v>Purchase $L3 Spies (at normal cost) when targeted by a Scheme</v>
+      </c>
+      <c r="P2" s="99" t="str">
         <f>Cards!C15</f>
-        <v>Draw $L6 additional cards from any decks during Brainstorm</v>
-      </c>
-      <c r="O2" s="99" t="str">
+        <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
+      </c>
+      <c r="Q2" s="98" t="str">
         <f>Cards!C16</f>
-        <v>Purchase $L3 Spies (at normal cost) when targeted by a Scheme</v>
-      </c>
-      <c r="P2" s="100" t="str">
+        <v>You may repeat $L3 Provincial Actions per round</v>
+      </c>
+      <c r="R2" s="99" t="str">
         <f>Cards!C17</f>
-        <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
-      </c>
-      <c r="Q2" s="99" t="str">
+        <v>Trade up to $L3 additional Coins when Buying from the Court</v>
+      </c>
+      <c r="S2" s="98" t="str">
         <f>Cards!C18</f>
-        <v>You may repeat $L3 Provincial Actions per round</v>
-      </c>
-      <c r="R2" s="100" t="str">
+        <v>Trade for up to $L3 additional Coins when Selling to the Court</v>
+      </c>
+      <c r="T2" s="99" t="str">
         <f>Cards!C19</f>
-        <v>Trade up to $L3 additional Coins when Buying from the Court</v>
-      </c>
-      <c r="S2" s="99" t="str">
+        <v>Gain $L3 additional Coins from the Royal Bank when Deploying Troops</v>
+      </c>
+      <c r="U2" s="98" t="str">
         <f>Cards!C20</f>
-        <v>Trade for up to $L3 additional Coins when Selling to the Court</v>
-      </c>
-      <c r="T2" s="100" t="str">
+        <v>Provides private Buy Action at Market Rate + $L3</v>
+      </c>
+      <c r="V2" s="99" t="str">
         <f>Cards!C21</f>
-        <v>Gain $L3 additional Coins from the Royal Bank when Deploying Troops</v>
-      </c>
-      <c r="U2" s="99" t="str">
+        <v>Provides private Sell Action at Market Rate - $L3</v>
+      </c>
+      <c r="W2" s="98" t="str">
         <f>Cards!C22</f>
-        <v>Provides private Buy Action at Market Rate + $L3</v>
-      </c>
-      <c r="V2" s="100" t="str">
+        <v>Purchase and immediately add up to $L3 Troops to your force when deploying them</v>
+      </c>
+      <c r="X2" s="99" t="str">
         <f>Cards!C23</f>
-        <v>Provides private Sell Action at Market Rate - $L3</v>
-      </c>
-      <c r="W2" s="99" t="str">
+        <v>Add $L3 Hits to each Roll during a Trial</v>
+      </c>
+      <c r="Y2" s="98" t="str">
         <f>Cards!C24</f>
-        <v>Purchase and immediately add up to $L3 Troops to your force when deploying them</v>
-      </c>
-      <c r="X2" s="100" t="str">
+        <v>Add $L6 additional dice to each Roll during a Trial</v>
+      </c>
+      <c r="Z2" s="99" t="str">
         <f>Cards!C25</f>
-        <v>Add $L3 Hits to each Roll during a Sue</v>
-      </c>
-      <c r="Y2" s="99" t="str">
+        <v>Collect $L6 additional Commodities during Harvests</v>
+      </c>
+      <c r="AA2" s="98" t="str">
         <f>Cards!C26</f>
-        <v>Add $L6 additional dice to each Roll during a Sue</v>
-      </c>
-      <c r="Z2" s="100" t="str">
+        <v>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</v>
+      </c>
+      <c r="AB2" s="99" t="str">
         <f>Cards!C27</f>
-        <v>Collect $L6 additional Commodities during Harvests</v>
-      </c>
-      <c r="AA2" s="99" t="str">
+        <v>Subtract $L3 from Scheme Card rolls</v>
+      </c>
+      <c r="AC2" s="98" t="str">
         <f>Cards!C28</f>
-        <v>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</v>
-      </c>
-      <c r="AB2" s="100" t="str">
+        <v>Spend $L3 fewer Commodities per Coin when Selling to the Undermarket</v>
+      </c>
+      <c r="AD2" s="100" t="str">
         <f>Cards!C29</f>
-        <v>Subtract $L3 from Scheme Card rolls</v>
-      </c>
-      <c r="AC2" s="99" t="str">
+        <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
+      </c>
+      <c r="AE2" s="99" t="str">
         <f>Cards!C30</f>
-        <v>Spend $L3 fewer Commodities per Coin when Selling to the Undermarket</v>
-      </c>
-      <c r="AD2" s="101" t="str">
+        <v>Trade up to $L3 additional Coins when Buying from the Undermarket</v>
+      </c>
+      <c r="AF2" s="99" t="str">
         <f>Cards!C31</f>
-        <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
-      </c>
-      <c r="AE2" s="100" t="str">
+        <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
+      </c>
+      <c r="AG2" s="98" t="str">
         <f>Cards!C32</f>
-        <v>Trade up to $L3 additional Coins when Buying from the Undermarket</v>
-      </c>
-      <c r="AF2" s="100" t="str">
+        <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
+      </c>
+      <c r="AH2" s="99" t="str">
         <f>Cards!C33</f>
-        <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
-      </c>
-      <c r="AG2" s="99" t="str">
+        <v>Provides private Monetize Action at Market Rate + $L3</v>
+      </c>
+      <c r="AI2" s="98" t="str">
         <f>Cards!C34</f>
-        <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
-      </c>
-      <c r="AH2" s="100" t="str">
+        <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
+      </c>
+      <c r="AJ2" s="99" t="str">
         <f>Cards!C35</f>
-        <v>Provides private Monetize Action at Market Rate + $L3</v>
-      </c>
-      <c r="AI2" s="99" t="str">
+        <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
+      </c>
+      <c r="AK2" s="98" t="str">
         <f>Cards!C36</f>
-        <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
-      </c>
-      <c r="AJ2" s="100" t="str">
+        <v>Provides Private Donate action with no penalty.</v>
+      </c>
+      <c r="AL2" s="99" t="str">
         <f>Cards!C37</f>
-        <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
-      </c>
-      <c r="AK2" s="99" t="str">
+        <v>Convert $L3 additional Coins during Undermarket Donate</v>
+      </c>
+      <c r="AM2" s="98" t="str">
         <f>Cards!C38</f>
-        <v>Convert $L3 additional Coins during Court Donate</v>
-      </c>
-      <c r="AL2" s="100" t="str">
+        <v>You may repeat Undermarket Actions at double the penalty</v>
+      </c>
+      <c r="AN2" s="99" t="str">
         <f>Cards!C39</f>
-        <v>Convert $L3 additional Coins during Undermarket Donate</v>
-      </c>
-      <c r="AM2" s="99" t="str">
-        <f>Cards!C40</f>
-        <v>You may repeat Undermarket Actions at double the penalty</v>
-      </c>
-      <c r="AN2" s="100" t="str">
-        <f>Cards!C41</f>
         <v>Deploy $L3 additional Troops during Deploy</v>
       </c>
-      <c r="AO2" s="99" t="str">
+      <c r="AO2" s="98" t="str">
         <f t="shared" si="0"/>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
       </c>
-      <c r="AP2" s="100" t="str">
+      <c r="AP2" s="99" t="str">
         <f t="shared" si="0"/>
         <v>Move the Law $L6 additional places forward in the queue during Prioritize</v>
       </c>
-      <c r="AQ2" s="99" t="str">
+      <c r="AQ2" s="98" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">You may keep up to $L6 additional Coins when Taxing other Players </v>
       </c>
-      <c r="AR2" s="100" t="str">
+      <c r="AR2" s="99" t="str">
         <f t="shared" si="0"/>
         <v>Gain $L3 additional Coins during Flatter</v>
       </c>
-      <c r="AS2" s="99" t="str">
+      <c r="AS2" s="98" t="str">
         <f t="shared" si="0"/>
         <v>Gain $L3 more Commodities per Coin when Buying from the Undermarket</v>
       </c>
-      <c r="AT2" s="100" t="str">
+      <c r="AT2" s="99" t="str">
         <f t="shared" si="0"/>
         <v>Add $L3 additional Law cards to the bottom of the queue during Petition</v>
       </c>
-      <c r="AU2" s="99" t="str">
+      <c r="AU2" s="98" t="e">
         <f t="shared" si="0"/>
-        <v>Gain 1 additional Troop for free after Recruiting every 4 - $L3 Troops</v>
-      </c>
-      <c r="AV2" s="100" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="AV2" s="99" t="e">
         <f t="shared" si="0"/>
-        <v>Gain 1 additional Spy for free after Infiltrating every 4 - $L3 Spies</v>
-      </c>
-      <c r="AW2" s="99" t="str">
+        <v>#REF!</v>
+      </c>
+      <c r="AW2" s="98" t="str">
         <f t="shared" si="0"/>
         <v>Purchase up to $L6 additional Troops during Recruit (at normal cost)</v>
       </c>
-      <c r="AX2" s="101" t="str">
+      <c r="AX2" s="100" t="str">
         <f t="shared" si="0"/>
         <v>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</v>
       </c>
-      <c r="AY2" s="100" t="str">
+      <c r="AY2" s="99" t="str">
         <f t="shared" si="1"/>
         <v>Gain $L3 more Commodities per Coin when Buying from the Court</v>
       </c>
-      <c r="AZ2" s="99" t="str">
+      <c r="AZ2" s="98" t="str">
         <f t="shared" si="1"/>
-        <v>Gain $L3 additional Coins from outside the Royal Bank when winning a Sue</v>
-      </c>
-      <c r="BA2" s="100" t="str">
+        <v>Gain $L3 additional Coins from outside the Royal Bank when winning a Trial</v>
+      </c>
+      <c r="BA2" s="99" t="str">
         <f t="shared" si="1"/>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Undermarket</v>
       </c>
-      <c r="BB2" s="99" t="str">
+      <c r="BB2" s="98" t="str">
         <f t="shared" si="1"/>
         <v>Draw $L6 additional cards from any decks during Brainstorm</v>
       </c>
-      <c r="BC2" s="100" t="str">
+      <c r="BC2" s="99" t="str">
         <f t="shared" si="1"/>
         <v>Purchase $L3 Spies (at normal cost) when targeted by a Scheme</v>
       </c>
-      <c r="BD2" s="99" t="str">
+      <c r="BD2" s="98" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
       </c>
-      <c r="BE2" s="100" t="str">
+      <c r="BE2" s="99" t="str">
         <f t="shared" si="1"/>
         <v>You may repeat $L3 Provincial Actions per round</v>
       </c>
-      <c r="BF2" s="99" t="str">
+      <c r="BF2" s="98" t="str">
         <f t="shared" si="1"/>
         <v>Trade up to $L3 additional Coins when Buying from the Court</v>
       </c>
-      <c r="BG2" s="100" t="str">
+      <c r="BG2" s="99" t="str">
         <f t="shared" si="1"/>
         <v>Trade for up to $L3 additional Coins when Selling to the Court</v>
       </c>
-      <c r="BH2" s="101" t="str">
+      <c r="BH2" s="100" t="str">
         <f t="shared" si="1"/>
         <v>Gain $L3 additional Coins from the Royal Bank when Deploying Troops</v>
       </c>
-      <c r="BI2" s="100" t="str">
+      <c r="BI2" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Provides private Buy Action at Market Rate + $L3</v>
       </c>
-      <c r="BJ2" s="99" t="str">
+      <c r="BJ2" s="98" t="str">
         <f t="shared" si="2"/>
         <v>Provides private Sell Action at Market Rate - $L3</v>
       </c>
-      <c r="BK2" s="100" t="str">
+      <c r="BK2" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Purchase and immediately add up to $L3 Troops to your force when deploying them</v>
       </c>
-      <c r="BL2" s="99" t="str">
+      <c r="BL2" s="98" t="str">
         <f t="shared" si="2"/>
-        <v>Add $L3 Hits to each Roll during a Sue</v>
-      </c>
-      <c r="BM2" s="100" t="str">
+        <v>Add $L3 Hits to each Roll during a Trial</v>
+      </c>
+      <c r="BM2" s="99" t="str">
         <f t="shared" si="2"/>
-        <v>Add $L6 additional dice to each Roll during a Sue</v>
-      </c>
-      <c r="BN2" s="99" t="str">
+        <v>Add $L6 additional dice to each Roll during a Trial</v>
+      </c>
+      <c r="BN2" s="98" t="str">
         <f t="shared" si="2"/>
         <v>Collect $L6 additional Commodities during Harvests</v>
       </c>
-      <c r="BO2" s="100" t="str">
+      <c r="BO2" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</v>
       </c>
-      <c r="BP2" s="99" t="str">
+      <c r="BP2" s="98" t="str">
         <f t="shared" si="2"/>
         <v>Subtract $L3 from Scheme Card rolls</v>
       </c>
-      <c r="BQ2" s="79" t="str">
+      <c r="BQ2" s="78" t="str">
         <f t="shared" si="2"/>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Undermarket</v>
       </c>
-      <c r="BR2" s="100" t="str">
+      <c r="BR2" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
       </c>
-      <c r="BS2" s="79"/>
-      <c r="BU2" s="100"/>
-      <c r="BW2" s="100"/>
-      <c r="BY2" s="100"/>
-      <c r="CA2" s="100"/>
-    </row>
-    <row r="3" spans="1:79" s="76" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="str">
+      <c r="BS2" s="78"/>
+      <c r="BU2" s="99"/>
+      <c r="BW2" s="99"/>
+      <c r="BY2" s="99"/>
+      <c r="CA2" s="99"/>
+    </row>
+    <row r="3" spans="1:79" s="75" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="73" t="str">
         <f>Cards!D2</f>
         <v>Full Coffers</v>
       </c>
-      <c r="B3" s="75" t="str">
+      <c r="B3" s="74" t="str">
         <f>Cards!D3</f>
         <v xml:space="preserve">Decentralized Wealth </v>
       </c>
-      <c r="C3" s="76" t="str">
+      <c r="C3" s="75" t="str">
         <f>Cards!D4</f>
         <v>Second Thoughts</v>
       </c>
-      <c r="D3" s="74" t="str">
+      <c r="D3" s="73" t="str">
         <f>Cards!D5</f>
         <v>Changing Times</v>
       </c>
-      <c r="E3" s="76" t="str">
+      <c r="E3" s="75" t="str">
         <f>Cards!D6</f>
         <v>Stable Economies</v>
       </c>
-      <c r="F3" s="74" t="str">
+      <c r="F3" s="73" t="str">
         <f>Cards!D7</f>
         <v>Unreasonable Distractions</v>
       </c>
-      <c r="G3" s="76" t="str">
+      <c r="G3" s="75" t="str">
         <f>Cards!D8</f>
         <v>Irregular Partiality</v>
       </c>
-      <c r="H3" s="74" t="str">
+      <c r="H3" s="73" t="str">
         <f>Cards!D9</f>
         <v>Royal Amendment</v>
       </c>
-      <c r="I3" s="76" t="str">
+      <c r="I3" s="75" t="str">
         <f>Cards!D10</f>
-        <v>Honorable Accontability</v>
-      </c>
-      <c r="J3" s="74" t="str">
+        <v>Honorable Accountability</v>
+      </c>
+      <c r="J3" s="73" t="str">
         <f>Cards!D11</f>
         <v>Frivolous Pursuits</v>
       </c>
-      <c r="K3" s="76" t="str">
+      <c r="K3" s="75" t="str">
         <f>Cards!D12</f>
         <v>Economic Backbone</v>
       </c>
-      <c r="L3" s="74" t="str">
+      <c r="L3" s="73" t="str">
         <f>Cards!D13</f>
         <v>Collective Ownership</v>
       </c>
-      <c r="M3" s="76" t="str">
+      <c r="M3" s="75" t="str">
         <f>Cards!D14</f>
         <v>Aggressive Tactics</v>
       </c>
-      <c r="N3" s="74" t="str">
+      <c r="N3" s="73" t="str">
         <f>Cards!D15</f>
         <v>Home Defense</v>
       </c>
-      <c r="O3" s="76" t="str">
+      <c r="O3" s="75" t="str">
         <f>Cards!D16</f>
         <v>Valuable Advisors</v>
       </c>
-      <c r="P3" s="74" t="str">
+      <c r="P3" s="73" t="str">
         <f>Cards!D17</f>
         <v>Chattering Windbags</v>
       </c>
-      <c r="Q3" s="76" t="str">
+      <c r="Q3" s="75" t="str">
         <f>Cards!D18</f>
         <v>Realistic Priorities</v>
       </c>
-      <c r="R3" s="74" t="str">
+      <c r="R3" s="73" t="str">
         <f>Cards!D19</f>
         <v>Threat to the Throne</v>
       </c>
-      <c r="S3" s="76" t="str">
+      <c r="S3" s="75" t="str">
         <f>Cards!D20</f>
         <v>Stone Foundations</v>
       </c>
-      <c r="T3" s="74" t="str">
+      <c r="T3" s="73" t="str">
         <f>Cards!D21</f>
         <v>Environmental Guardians</v>
       </c>
-      <c r="U3" s="76" t="str">
+      <c r="U3" s="75" t="str">
         <f>Cards!D22</f>
         <v>Resilient Officer Corps</v>
       </c>
-      <c r="V3" s="74" t="str">
+      <c r="V3" s="73" t="str">
         <f>Cards!D23</f>
         <v>Bloated Bureaucracy</v>
       </c>
-      <c r="W3" s="76" t="str">
+      <c r="W3" s="75" t="str">
         <f>Cards!D24</f>
         <v>Police Force</v>
       </c>
-      <c r="X3" s="74" t="str">
+      <c r="X3" s="73" t="str">
         <f>Cards!D25</f>
         <v>Equal Partners</v>
       </c>
-      <c r="Y3" s="76" t="str">
+      <c r="Y3" s="75" t="str">
         <f>Cards!D26</f>
         <v>Criminal Identification</v>
       </c>
-      <c r="Z3" s="74" t="str">
+      <c r="Z3" s="73" t="str">
         <f>Cards!D27</f>
         <v>Honorable Marketplace</v>
       </c>
-      <c r="AA3" s="76" t="str">
+      <c r="AA3" s="75" t="str">
         <f>Cards!D28</f>
         <v>Engaged Empire</v>
       </c>
-      <c r="AB3" s="74" t="str">
+      <c r="AB3" s="73" t="str">
         <f>Cards!D29</f>
         <v>Suspicious Advisors</v>
       </c>
-      <c r="AC3" s="76" t="str">
+      <c r="AC3" s="75" t="str">
         <f>Cards!D30</f>
         <v>Contingency Plans</v>
       </c>
-      <c r="AD3" s="77" t="str">
+      <c r="AD3" s="76" t="str">
         <f>Cards!D31</f>
         <v>Worthless Procrastinators</v>
       </c>
-      <c r="AE3" s="74" t="str">
+      <c r="AE3" s="73" t="str">
         <f>Cards!D32</f>
         <v>Stalled Front</v>
       </c>
-      <c r="AF3" s="74" t="str">
+      <c r="AF3" s="73" t="str">
         <f>Cards!D33</f>
         <v>Quality Strength</v>
       </c>
-      <c r="AG3" s="76" t="str">
+      <c r="AG3" s="75" t="str">
         <f t="shared" ref="AG3:BL3" si="3">A3</f>
         <v>Full Coffers</v>
       </c>
-      <c r="AH3" s="74" t="str">
+      <c r="AH3" s="73" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">Decentralized Wealth </v>
       </c>
-      <c r="AI3" s="76" t="str">
+      <c r="AI3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Second Thoughts</v>
       </c>
-      <c r="AJ3" s="74" t="str">
+      <c r="AJ3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Changing Times</v>
       </c>
-      <c r="AK3" s="76" t="str">
+      <c r="AK3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Stable Economies</v>
       </c>
-      <c r="AL3" s="74" t="str">
+      <c r="AL3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Unreasonable Distractions</v>
       </c>
-      <c r="AM3" s="76" t="str">
+      <c r="AM3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Irregular Partiality</v>
       </c>
-      <c r="AN3" s="74" t="str">
+      <c r="AN3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Royal Amendment</v>
       </c>
-      <c r="AO3" s="76" t="str">
+      <c r="AO3" s="75" t="str">
         <f t="shared" si="3"/>
-        <v>Honorable Accontability</v>
-      </c>
-      <c r="AP3" s="74" t="str">
+        <v>Honorable Accountability</v>
+      </c>
+      <c r="AP3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Frivolous Pursuits</v>
       </c>
-      <c r="AQ3" s="76" t="str">
+      <c r="AQ3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Economic Backbone</v>
       </c>
-      <c r="AR3" s="74" t="str">
+      <c r="AR3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Collective Ownership</v>
       </c>
-      <c r="AS3" s="76" t="str">
+      <c r="AS3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Aggressive Tactics</v>
       </c>
-      <c r="AT3" s="74" t="str">
+      <c r="AT3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Home Defense</v>
       </c>
-      <c r="AU3" s="76" t="str">
+      <c r="AU3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Valuable Advisors</v>
       </c>
-      <c r="AV3" s="74" t="str">
+      <c r="AV3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Chattering Windbags</v>
       </c>
-      <c r="AW3" s="76" t="str">
+      <c r="AW3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Realistic Priorities</v>
       </c>
-      <c r="AX3" s="77" t="str">
+      <c r="AX3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Threat to the Throne</v>
       </c>
-      <c r="AY3" s="74" t="str">
+      <c r="AY3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Stone Foundations</v>
       </c>
-      <c r="AZ3" s="76" t="str">
+      <c r="AZ3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Environmental Guardians</v>
       </c>
-      <c r="BA3" s="74" t="str">
+      <c r="BA3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Resilient Officer Corps</v>
       </c>
-      <c r="BB3" s="76" t="str">
+      <c r="BB3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Bloated Bureaucracy</v>
       </c>
-      <c r="BC3" s="74" t="str">
+      <c r="BC3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Police Force</v>
       </c>
-      <c r="BD3" s="76" t="str">
+      <c r="BD3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Equal Partners</v>
       </c>
-      <c r="BE3" s="74" t="str">
+      <c r="BE3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Criminal Identification</v>
       </c>
-      <c r="BF3" s="76" t="str">
+      <c r="BF3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Honorable Marketplace</v>
       </c>
-      <c r="BG3" s="74" t="str">
+      <c r="BG3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Engaged Empire</v>
       </c>
-      <c r="BH3" s="77" t="str">
+      <c r="BH3" s="76" t="str">
         <f t="shared" si="3"/>
         <v>Suspicious Advisors</v>
       </c>
-      <c r="BI3" s="74" t="str">
+      <c r="BI3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Contingency Plans</v>
       </c>
-      <c r="BJ3" s="76" t="str">
+      <c r="BJ3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Worthless Procrastinators</v>
       </c>
-      <c r="BK3" s="74" t="str">
+      <c r="BK3" s="73" t="str">
         <f t="shared" si="3"/>
         <v>Stalled Front</v>
       </c>
-      <c r="BL3" s="76" t="str">
+      <c r="BL3" s="75" t="str">
         <f t="shared" si="3"/>
         <v>Quality Strength</v>
       </c>
-      <c r="BM3" s="74"/>
-      <c r="BN3" s="76" t="str">
-        <f>AJ1</f>
+      <c r="BM3" s="73"/>
+      <c r="BN3" s="75" t="str">
+        <f t="shared" ref="BN3:BR4" si="4">AJ1</f>
         <v>Kingdom Advocates</v>
       </c>
-      <c r="BO3" s="74" t="str">
-        <f>AK1</f>
+      <c r="BO3" s="73" t="str">
+        <f t="shared" si="4"/>
         <v>Soup Kitchens</v>
       </c>
-      <c r="BP3" s="76" t="str">
-        <f>AL1</f>
+      <c r="BP3" s="75" t="str">
+        <f t="shared" si="4"/>
         <v>Abusive Power</v>
       </c>
-      <c r="BQ3" s="74" t="str">
-        <f>AM1</f>
+      <c r="BQ3" s="73" t="str">
+        <f t="shared" si="4"/>
         <v>Painful Progress</v>
       </c>
-      <c r="BR3" s="74" t="str">
-        <f>AN1</f>
+      <c r="BR3" s="73" t="str">
+        <f t="shared" si="4"/>
         <v>Iron Command</v>
       </c>
-      <c r="BS3" s="75"/>
-      <c r="BU3" s="74"/>
-      <c r="BW3" s="74"/>
-      <c r="BY3" s="74"/>
-      <c r="CA3" s="74"/>
-    </row>
-    <row r="4" spans="1:79" s="81" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="79" t="str">
+      <c r="BS3" s="74"/>
+      <c r="BU3" s="73"/>
+      <c r="BW3" s="73"/>
+      <c r="BY3" s="73"/>
+      <c r="CA3" s="73"/>
+    </row>
+    <row r="4" spans="1:79" s="80" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="78" t="str">
         <f>Cards!E2</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
-      <c r="B4" s="80" t="str">
+      <c r="B4" s="79" t="str">
         <f>Cards!E3</f>
         <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
-      <c r="C4" s="81" t="str">
+      <c r="C4" s="80" t="str">
         <f>Cards!E4</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="D4" s="79" t="str">
+      <c r="D4" s="78" t="str">
         <f>Cards!E5</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="E4" s="81" t="str">
+      <c r="E4" s="80" t="str">
         <f>Cards!E6</f>
         <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
       </c>
-      <c r="F4" s="79" t="str">
+      <c r="F4" s="78" t="str">
         <f>Cards!E7</f>
         <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
       </c>
-      <c r="G4" s="81" t="str">
+      <c r="G4" s="80" t="str">
         <f>Cards!E8</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="H4" s="79" t="str">
+      <c r="H4" s="78" t="str">
         <f>Cards!E9</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="I4" s="81" t="str">
+      <c r="I4" s="80" t="str">
         <f>Cards!E10</f>
-        <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy Troops</v>
-      </c>
-      <c r="J4" s="79" t="str">
+        <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy</v>
+      </c>
+      <c r="J4" s="78" t="str">
         <f>Cards!E11</f>
-        <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy Troops</v>
-      </c>
-      <c r="K4" s="81" t="str">
+        <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy</v>
+      </c>
+      <c r="K4" s="80" t="str">
         <f>Cards!E12</f>
         <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
       </c>
-      <c r="L4" s="79" t="str">
+      <c r="L4" s="78" t="str">
         <f>Cards!E13</f>
         <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
       </c>
-      <c r="M4" s="81" t="str">
+      <c r="M4" s="80" t="str">
         <f>Cards!E14</f>
         <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
       </c>
-      <c r="N4" s="79" t="str">
+      <c r="N4" s="78" t="str">
         <f>Cards!E15</f>
         <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
       </c>
-      <c r="O4" s="81" t="str">
+      <c r="O4" s="80" t="str">
         <f>Cards!E16</f>
-        <v>Each Player must have at least $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
-      </c>
-      <c r="P4" s="79" t="str">
+        <v>Each Player must have at least $L6 sponsored Laws in the Edicts or in the Queue or they will suffer sanctions on Tax</v>
+      </c>
+      <c r="P4" s="78" t="str">
         <f>Cards!E17</f>
         <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
       </c>
-      <c r="Q4" s="81" t="str">
+      <c r="Q4" s="80" t="str">
         <f>Cards!E18</f>
         <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
       </c>
-      <c r="R4" s="79" t="str">
+      <c r="R4" s="78" t="str">
         <f>Cards!E19</f>
         <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
       </c>
-      <c r="S4" s="81" t="str">
+      <c r="S4" s="80" t="str">
         <f>Cards!E20</f>
         <v>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
-      <c r="T4" s="79" t="str">
+      <c r="T4" s="78" t="str">
         <f>Cards!E21</f>
         <v>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
-      <c r="U4" s="81" t="str">
+      <c r="U4" s="80" t="str">
         <f>Cards!E22</f>
         <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
-      <c r="V4" s="79" t="str">
+      <c r="V4" s="78" t="str">
         <f>Cards!E23</f>
         <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
-      <c r="W4" s="81" t="str">
+      <c r="W4" s="80" t="str">
         <f>Cards!E24</f>
         <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</v>
       </c>
-      <c r="X4" s="79" t="str">
+      <c r="X4" s="78" t="str">
         <f>Cards!E25</f>
         <v>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</v>
       </c>
-      <c r="Y4" s="81" t="str">
+      <c r="Y4" s="80" t="str">
         <f>Cards!E26</f>
         <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
-      <c r="Z4" s="79" t="str">
+      <c r="Z4" s="78" t="str">
         <f>Cards!E27</f>
         <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
-      <c r="AA4" s="81" t="str">
+      <c r="AA4" s="80" t="str">
         <f>Cards!E28</f>
         <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
-      <c r="AB4" s="79" t="str">
+      <c r="AB4" s="78" t="str">
         <f>Cards!E29</f>
         <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
-      <c r="AC4" s="81" t="str">
+      <c r="AC4" s="80" t="str">
         <f>Cards!E30</f>
         <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
       </c>
-      <c r="AD4" s="82" t="str">
+      <c r="AD4" s="81" t="str">
         <f>Cards!E31</f>
         <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
       </c>
-      <c r="AE4" s="79" t="str">
+      <c r="AE4" s="78" t="str">
         <f>Cards!E32</f>
         <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
       </c>
-      <c r="AF4" s="79" t="str">
+      <c r="AF4" s="78" t="str">
         <f>Cards!E33</f>
         <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
       </c>
-      <c r="AG4" s="81" t="str">
-        <f t="shared" ref="AG4:BL4" si="4">A4</f>
+      <c r="AG4" s="80" t="str">
+        <f t="shared" ref="AG4:BL4" si="5">A4</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
-      <c r="AH4" s="79" t="str">
+      <c r="AH4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
+      </c>
+      <c r="AI4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AJ4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AK4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
+      </c>
+      <c r="AL4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
+      </c>
+      <c r="AM4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AN4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AO4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy</v>
+      </c>
+      <c r="AP4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy</v>
+      </c>
+      <c r="AQ4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
+      </c>
+      <c r="AR4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
+      </c>
+      <c r="AS4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+      </c>
+      <c r="AT4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+      </c>
+      <c r="AU4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have at least $L6 sponsored Laws in the Edicts or in the Queue or they will suffer sanctions on Tax</v>
+      </c>
+      <c r="AV4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
+      </c>
+      <c r="AW4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
+      </c>
+      <c r="AX4" s="81" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
+      </c>
+      <c r="AY4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+      </c>
+      <c r="AZ4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+      </c>
+      <c r="BA4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
+      </c>
+      <c r="BB4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
+      </c>
+      <c r="BC4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</v>
+      </c>
+      <c r="BD4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</v>
+      </c>
+      <c r="BE4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+      </c>
+      <c r="BF4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+      </c>
+      <c r="BG4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
+      </c>
+      <c r="BH4" s="81" t="str">
+        <f t="shared" si="5"/>
+        <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
+      </c>
+      <c r="BI4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
+      </c>
+      <c r="BJ4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
+      </c>
+      <c r="BK4" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="BL4" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="BM4" s="78"/>
+      <c r="BN4" s="98" t="str">
         <f t="shared" si="4"/>
-        <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
-      </c>
-      <c r="AI4" s="81" t="str">
+        <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
+      </c>
+      <c r="BO4" s="99" t="str">
         <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AJ4" s="79" t="str">
+        <v>Provides Private Donate action with no penalty.</v>
+      </c>
+      <c r="BP4" s="98" t="str">
         <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AK4" s="81" t="str">
+        <v>Convert $L3 additional Coins during Undermarket Donate</v>
+      </c>
+      <c r="BQ4" s="99" t="str">
         <f t="shared" si="4"/>
-        <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
-      </c>
-      <c r="AL4" s="79" t="str">
+        <v>You may repeat Undermarket Actions at double the penalty</v>
+      </c>
+      <c r="BR4" s="78" t="str">
         <f t="shared" si="4"/>
-        <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
-      </c>
-      <c r="AM4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AN4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AO4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy Troops</v>
-      </c>
-      <c r="AP4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy Troops</v>
-      </c>
-      <c r="AQ4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
-      </c>
-      <c r="AR4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
-      </c>
-      <c r="AS4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
-      </c>
-      <c r="AT4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
-      </c>
-      <c r="AU4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
-      </c>
-      <c r="AV4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
-      </c>
-      <c r="AW4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
-      </c>
-      <c r="AX4" s="82" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
-      </c>
-      <c r="AY4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
-      </c>
-      <c r="AZ4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
-      </c>
-      <c r="BA4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
-      </c>
-      <c r="BB4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
-      </c>
-      <c r="BC4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</v>
-      </c>
-      <c r="BD4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</v>
-      </c>
-      <c r="BE4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
-      </c>
-      <c r="BF4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
-      </c>
-      <c r="BG4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
-      </c>
-      <c r="BH4" s="82" t="str">
-        <f t="shared" si="4"/>
-        <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
-      </c>
-      <c r="BI4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
-      </c>
-      <c r="BJ4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
-      </c>
-      <c r="BK4" s="79" t="str">
-        <f t="shared" si="4"/>
-        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
-      </c>
-      <c r="BL4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
-      </c>
-      <c r="BM4" s="79"/>
-      <c r="BN4" s="99" t="str">
-        <f>AJ2</f>
-        <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
-      </c>
-      <c r="BO4" s="100" t="str">
-        <f>AK2</f>
-        <v>Convert $L3 additional Coins during Court Donate</v>
-      </c>
-      <c r="BP4" s="99" t="str">
-        <f>AL2</f>
-        <v>Convert $L3 additional Coins during Undermarket Donate</v>
-      </c>
-      <c r="BQ4" s="100" t="str">
-        <f>AM2</f>
-        <v>You may repeat Undermarket Actions at double the penalty</v>
-      </c>
-      <c r="BR4" s="79" t="str">
-        <f>AN2</f>
         <v>Deploy $L3 additional Troops during Deploy</v>
       </c>
-      <c r="BS4" s="80"/>
-      <c r="BU4" s="79"/>
-      <c r="BW4" s="79"/>
-      <c r="BY4" s="79"/>
-      <c r="CA4" s="79"/>
-    </row>
-    <row r="5" spans="1:79" s="85" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="str">
+      <c r="BS4" s="79"/>
+      <c r="BU4" s="78"/>
+      <c r="BW4" s="78"/>
+      <c r="BY4" s="78"/>
+      <c r="CA4" s="78"/>
+    </row>
+    <row r="5" spans="1:79" s="84" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="82" t="str">
         <f>Cards!F2</f>
         <v>Fickle Mercenaries</v>
       </c>
-      <c r="B5" s="84" t="str">
+      <c r="B5" s="83" t="str">
         <f>Cards!F3</f>
         <v>Blatant Extortion</v>
       </c>
-      <c r="C5" s="85" t="str">
+      <c r="C5" s="84" t="str">
         <f>Cards!F4</f>
         <v>Double Agents</v>
       </c>
-      <c r="D5" s="83" t="str">
+      <c r="D5" s="82" t="str">
         <f>Cards!F5</f>
         <v>Questionable Reallocation</v>
       </c>
-      <c r="E5" s="85" t="str">
+      <c r="E5" s="84" t="str">
         <f>Cards!F6</f>
         <v>Corporate Espionage</v>
       </c>
-      <c r="F5" s="83" t="str">
+      <c r="F5" s="82" t="str">
         <f>Cards!F7</f>
         <v>Localized Famine</v>
       </c>
-      <c r="G5" s="85" t="str">
+      <c r="G5" s="84" t="str">
         <f>Cards!F8</f>
         <v>Highway Robbery</v>
       </c>
-      <c r="H5" s="83" t="str">
+      <c r="H5" s="82" t="str">
         <f>Cards!F9</f>
         <v>Camp Plague</v>
       </c>
-      <c r="I5" s="85" t="str">
+      <c r="I5" s="84" t="str">
         <f>Cards!F10</f>
         <v>Weakening Grip</v>
       </c>
-      <c r="J5" s="83" t="str">
+      <c r="J5" s="82" t="str">
         <f>Cards!F11</f>
         <v>Culture Shift</v>
       </c>
-      <c r="K5" s="85" t="str">
+      <c r="K5" s="84" t="str">
         <f>Cards!F12</f>
         <v>Corporate Takeover</v>
       </c>
-      <c r="L5" s="83" t="str">
+      <c r="L5" s="82" t="str">
         <f>Cards!F13</f>
         <v>Sabotage</v>
       </c>
-      <c r="M5" s="85" t="str">
+      <c r="M5" s="84" t="str">
         <f>Cards!F14</f>
         <v>Dangerous Monopolies</v>
       </c>
-      <c r="N5" s="83" t="str">
+      <c r="N5" s="82" t="str">
         <f>Cards!F15</f>
         <v>Betrayal</v>
       </c>
-      <c r="O5" s="85" t="str">
+      <c r="O5" s="84" t="str">
         <f>Cards!F16</f>
         <v>Assassination Attempt</v>
       </c>
-      <c r="P5" s="83" t="str">
+      <c r="P5" s="82" t="str">
         <f>Cards!F17</f>
         <v>Humiliation</v>
       </c>
-      <c r="Q5" s="85" t="str">
+      <c r="Q5" s="84" t="str">
         <f>Cards!F18</f>
         <v>Invalid Paperwork</v>
       </c>
-      <c r="R5" s="83" t="str">
+      <c r="R5" s="82" t="str">
         <f>Cards!F19</f>
         <v>Rallied Opposition</v>
       </c>
-      <c r="S5" s="85" t="str">
+      <c r="S5" s="84" t="str">
         <f>Cards!F20</f>
         <v>Waning Support</v>
       </c>
-      <c r="T5" s="83" t="str">
+      <c r="T5" s="82" t="str">
         <f>Cards!F21</f>
         <v>Misaligned Strategy</v>
       </c>
-      <c r="U5" s="83" t="str">
+      <c r="U5" s="82" t="str">
         <f>Cards!F22</f>
         <v>Blackmail</v>
       </c>
-      <c r="V5" s="83" t="str">
-        <f t="shared" ref="V5:AE6" si="5">A5</f>
+      <c r="V5" s="82" t="str">
+        <f t="shared" ref="V5:AE6" si="6">A5</f>
         <v>Fickle Mercenaries</v>
       </c>
-      <c r="W5" s="85" t="str">
-        <f t="shared" si="5"/>
+      <c r="W5" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>Blatant Extortion</v>
       </c>
-      <c r="X5" s="83" t="str">
-        <f t="shared" si="5"/>
+      <c r="X5" s="82" t="str">
+        <f t="shared" si="6"/>
         <v>Double Agents</v>
       </c>
-      <c r="Y5" s="85" t="str">
-        <f t="shared" si="5"/>
+      <c r="Y5" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>Questionable Reallocation</v>
       </c>
-      <c r="Z5" s="83" t="str">
-        <f t="shared" si="5"/>
+      <c r="Z5" s="82" t="str">
+        <f t="shared" si="6"/>
         <v>Corporate Espionage</v>
       </c>
-      <c r="AA5" s="85" t="str">
-        <f t="shared" si="5"/>
+      <c r="AA5" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>Localized Famine</v>
       </c>
-      <c r="AB5" s="83" t="str">
-        <f t="shared" si="5"/>
+      <c r="AB5" s="82" t="str">
+        <f t="shared" si="6"/>
         <v>Highway Robbery</v>
       </c>
-      <c r="AC5" s="85" t="str">
-        <f t="shared" si="5"/>
+      <c r="AC5" s="84" t="str">
+        <f t="shared" si="6"/>
         <v>Camp Plague</v>
       </c>
-      <c r="AD5" s="86" t="str">
-        <f t="shared" si="5"/>
+      <c r="AD5" s="85" t="str">
+        <f t="shared" si="6"/>
         <v>Weakening Grip</v>
       </c>
-      <c r="AE5" s="83" t="str">
-        <f t="shared" si="5"/>
+      <c r="AE5" s="82" t="str">
+        <f t="shared" si="6"/>
         <v>Culture Shift</v>
       </c>
-      <c r="AF5" s="83" t="str">
-        <f t="shared" ref="AF5:AO6" si="6">K5</f>
+      <c r="AF5" s="82" t="str">
+        <f t="shared" ref="AF5:AO6" si="7">K5</f>
         <v>Corporate Takeover</v>
       </c>
-      <c r="AG5" s="85" t="str">
-        <f t="shared" si="6"/>
+      <c r="AG5" s="84" t="str">
+        <f t="shared" si="7"/>
         <v>Sabotage</v>
       </c>
-      <c r="AH5" s="83" t="str">
-        <f t="shared" si="6"/>
+      <c r="AH5" s="82" t="str">
+        <f t="shared" si="7"/>
         <v>Dangerous Monopolies</v>
       </c>
-      <c r="AI5" s="85" t="str">
-        <f t="shared" si="6"/>
+      <c r="AI5" s="84" t="str">
+        <f t="shared" si="7"/>
         <v>Betrayal</v>
       </c>
-      <c r="AJ5" s="83" t="str">
-        <f t="shared" si="6"/>
+      <c r="AJ5" s="82" t="str">
+        <f t="shared" si="7"/>
         <v>Assassination Attempt</v>
       </c>
-      <c r="AK5" s="85" t="str">
-        <f t="shared" si="6"/>
+      <c r="AK5" s="84" t="str">
+        <f t="shared" si="7"/>
         <v>Humiliation</v>
       </c>
-      <c r="AL5" s="83" t="str">
-        <f t="shared" si="6"/>
+      <c r="AL5" s="82" t="str">
+        <f t="shared" si="7"/>
         <v>Invalid Paperwork</v>
       </c>
-      <c r="AM5" s="85" t="str">
-        <f t="shared" si="6"/>
+      <c r="AM5" s="84" t="str">
+        <f t="shared" si="7"/>
         <v>Rallied Opposition</v>
       </c>
-      <c r="AN5" s="83" t="str">
-        <f t="shared" si="6"/>
+      <c r="AN5" s="82" t="str">
+        <f t="shared" si="7"/>
         <v>Waning Support</v>
       </c>
-      <c r="AO5" s="85" t="str">
-        <f t="shared" si="6"/>
+      <c r="AO5" s="84" t="str">
+        <f t="shared" si="7"/>
         <v>Misaligned Strategy</v>
       </c>
-      <c r="AP5" s="83" t="str">
-        <f t="shared" ref="AP5:AY6" si="7">U5</f>
+      <c r="AP5" s="82" t="str">
+        <f t="shared" ref="AP5:AP6" si="8">U5</f>
         <v>Blackmail</v>
       </c>
-      <c r="AQ5" s="85" t="str">
-        <f t="shared" ref="AQ5:AZ6" si="8">A5</f>
+      <c r="AQ5" s="84" t="str">
+        <f t="shared" ref="AQ5:AZ6" si="9">A5</f>
         <v>Fickle Mercenaries</v>
       </c>
-      <c r="AR5" s="83" t="str">
-        <f t="shared" si="8"/>
+      <c r="AR5" s="82" t="str">
+        <f t="shared" si="9"/>
         <v>Blatant Extortion</v>
       </c>
-      <c r="AS5" s="85" t="str">
-        <f t="shared" si="8"/>
+      <c r="AS5" s="84" t="str">
+        <f t="shared" si="9"/>
         <v>Double Agents</v>
       </c>
-      <c r="AT5" s="83" t="str">
-        <f t="shared" si="8"/>
+      <c r="AT5" s="82" t="str">
+        <f t="shared" si="9"/>
         <v>Questionable Reallocation</v>
       </c>
-      <c r="AU5" s="85" t="str">
-        <f t="shared" si="8"/>
+      <c r="AU5" s="84" t="str">
+        <f t="shared" si="9"/>
         <v>Corporate Espionage</v>
       </c>
-      <c r="AV5" s="83" t="str">
-        <f t="shared" si="8"/>
+      <c r="AV5" s="82" t="str">
+        <f t="shared" si="9"/>
         <v>Localized Famine</v>
       </c>
-      <c r="AW5" s="85" t="str">
-        <f t="shared" si="8"/>
+      <c r="AW5" s="84" t="str">
+        <f t="shared" si="9"/>
         <v>Highway Robbery</v>
       </c>
-      <c r="AX5" s="86" t="str">
-        <f t="shared" si="8"/>
+      <c r="AX5" s="85" t="str">
+        <f t="shared" si="9"/>
         <v>Camp Plague</v>
       </c>
-      <c r="AY5" s="83" t="str">
-        <f t="shared" si="8"/>
+      <c r="AY5" s="82" t="str">
+        <f t="shared" si="9"/>
         <v>Weakening Grip</v>
       </c>
-      <c r="AZ5" s="85" t="str">
-        <f t="shared" si="8"/>
+      <c r="AZ5" s="84" t="str">
+        <f t="shared" si="9"/>
         <v>Culture Shift</v>
       </c>
-      <c r="BA5" s="83" t="str">
-        <f t="shared" ref="BA5:BJ6" si="9">K5</f>
+      <c r="BA5" s="82" t="str">
+        <f t="shared" ref="BA5:BJ6" si="10">K5</f>
         <v>Corporate Takeover</v>
       </c>
-      <c r="BB5" s="85" t="str">
-        <f t="shared" si="9"/>
+      <c r="BB5" s="84" t="str">
+        <f t="shared" si="10"/>
         <v>Sabotage</v>
       </c>
-      <c r="BC5" s="83" t="str">
-        <f t="shared" si="9"/>
+      <c r="BC5" s="82" t="str">
+        <f t="shared" si="10"/>
         <v>Dangerous Monopolies</v>
       </c>
-      <c r="BD5" s="85" t="str">
-        <f t="shared" si="9"/>
+      <c r="BD5" s="84" t="str">
+        <f t="shared" si="10"/>
         <v>Betrayal</v>
       </c>
-      <c r="BE5" s="83" t="str">
-        <f t="shared" si="9"/>
+      <c r="BE5" s="82" t="str">
+        <f t="shared" si="10"/>
         <v>Assassination Attempt</v>
       </c>
-      <c r="BF5" s="85" t="str">
-        <f t="shared" si="9"/>
+      <c r="BF5" s="84" t="str">
+        <f t="shared" si="10"/>
         <v>Humiliation</v>
       </c>
-      <c r="BG5" s="83" t="str">
-        <f t="shared" si="9"/>
+      <c r="BG5" s="82" t="str">
+        <f t="shared" si="10"/>
         <v>Invalid Paperwork</v>
       </c>
-      <c r="BH5" s="83" t="str">
-        <f t="shared" si="9"/>
+      <c r="BH5" s="82" t="str">
+        <f t="shared" si="10"/>
         <v>Rallied Opposition</v>
       </c>
-      <c r="BI5" s="83" t="str">
-        <f t="shared" si="9"/>
+      <c r="BI5" s="82" t="str">
+        <f t="shared" si="10"/>
         <v>Waning Support</v>
       </c>
-      <c r="BJ5" s="85" t="str">
-        <f t="shared" si="9"/>
+      <c r="BJ5" s="84" t="str">
+        <f t="shared" si="10"/>
         <v>Misaligned Strategy</v>
       </c>
-      <c r="BK5" s="83" t="str">
-        <f t="shared" ref="BK5:BT6" si="10">U5</f>
+      <c r="BK5" s="82" t="str">
+        <f t="shared" ref="BK5:BK6" si="11">U5</f>
         <v>Blackmail</v>
       </c>
-      <c r="BM5" s="74" t="str">
-        <f>AE1</f>
+      <c r="BM5" s="73" t="str">
+        <f t="shared" ref="BM5:BQ6" si="12">AE1</f>
         <v>Codependent Relationship</v>
       </c>
-      <c r="BN5" s="76" t="str">
-        <f>AF1</f>
+      <c r="BN5" s="75" t="str">
+        <f t="shared" si="12"/>
         <v>Dangerous Promises</v>
       </c>
-      <c r="BO5" s="74" t="str">
-        <f>AG1</f>
+      <c r="BO5" s="73" t="str">
+        <f t="shared" si="12"/>
         <v>Large Middle Class</v>
       </c>
-      <c r="BP5" s="76" t="str">
-        <f>AH1</f>
+      <c r="BP5" s="75" t="str">
+        <f t="shared" si="12"/>
         <v>Innovation Hub</v>
       </c>
-      <c r="BQ5" s="74" t="str">
-        <f>AI1</f>
+      <c r="BQ5" s="73" t="str">
+        <f t="shared" si="12"/>
         <v>Fire Temple</v>
       </c>
-      <c r="BR5" s="83"/>
-      <c r="BS5" s="84"/>
-      <c r="BU5" s="83"/>
-      <c r="BW5" s="83"/>
-      <c r="BY5" s="83"/>
-      <c r="CA5" s="83"/>
-    </row>
-    <row r="6" spans="1:79" s="81" customFormat="1" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79" t="str">
+      <c r="BR5" s="82"/>
+      <c r="BS5" s="83"/>
+      <c r="BU5" s="82"/>
+      <c r="BW5" s="82"/>
+      <c r="BY5" s="82"/>
+      <c r="CA5" s="82"/>
+    </row>
+    <row r="6" spans="1:79" s="80" customFormat="1" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="78" t="str">
         <f>Cards!G2</f>
         <v>Give $2D6 Troops to $R</v>
       </c>
-      <c r="B6" s="80" t="str">
+      <c r="B6" s="79" t="str">
         <f>Cards!G3</f>
         <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="C6" s="81" t="str">
+      <c r="C6" s="80" t="str">
         <f>Cards!G4</f>
         <v>Give $D6 Spies to $R</v>
       </c>
-      <c r="D6" s="79" t="str">
+      <c r="D6" s="78" t="str">
         <f>Cards!G5</f>
         <v>Give $2D6 Commodities to $R</v>
       </c>
-      <c r="E6" s="81" t="str">
+      <c r="E6" s="80" t="str">
         <f>Cards!G6</f>
         <v>Give $D6 random Cards of each type from your hand to $R</v>
       </c>
-      <c r="F6" s="79" t="str">
+      <c r="F6" s="78" t="str">
         <f>Cards!G7</f>
         <v>Lose half your Commodities</v>
       </c>
-      <c r="G6" s="81" t="str">
+      <c r="G6" s="80" t="str">
         <f>Cards!G8</f>
         <v>Lose half your Coins</v>
       </c>
-      <c r="H6" s="79" t="str">
+      <c r="H6" s="78" t="str">
         <f>Cards!G9</f>
         <v>Lose half your Troops</v>
       </c>
-      <c r="I6" s="81" t="str">
+      <c r="I6" s="80" t="str">
         <f>Cards!G10</f>
         <v>Lose half your Spies</v>
       </c>
-      <c r="J6" s="79" t="str">
+      <c r="J6" s="78" t="str">
         <f>Cards!G11</f>
         <v>Disard half your cards of each type</v>
       </c>
-      <c r="K6" s="81" t="str">
+      <c r="K6" s="80" t="str">
         <f>Cards!G12</f>
         <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
       </c>
-      <c r="L6" s="79" t="str">
+      <c r="L6" s="78" t="str">
         <f>Cards!G13</f>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="M6" s="81" t="str">
+      <c r="M6" s="80" t="str">
         <f>Cards!G14</f>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="N6" s="79" t="str">
+      <c r="N6" s="78" t="str">
         <f>Cards!G15</f>
         <v>Demote a Leader at level $D6 by half and send it to $R</v>
       </c>
-      <c r="O6" s="81" t="str">
+      <c r="O6" s="80" t="str">
         <f>Cards!G16</f>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="P6" s="79" t="str">
+      <c r="P6" s="78" t="str">
         <f>Cards!G17</f>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="Q6" s="81" t="str">
+      <c r="Q6" s="80" t="str">
         <f>Cards!G18</f>
         <v>Move your foremost Law to the back of the Queue</v>
       </c>
-      <c r="R6" s="79" t="str">
+      <c r="R6" s="78" t="str">
         <f>Cards!G19</f>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="S6" s="81" t="str">
+      <c r="S6" s="80" t="str">
         <f>Cards!G20</f>
         <v>Move $D6 of your Laws each one space back in the Queue</v>
       </c>
-      <c r="T6" s="79" t="str">
+      <c r="T6" s="78" t="str">
         <f>Cards!G21</f>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="U6" s="79" t="str">
+      <c r="U6" s="78" t="str">
         <f>Cards!G22</f>
         <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="V6" s="79" t="str">
-        <f t="shared" si="5"/>
+      <c r="V6" s="78" t="str">
+        <f t="shared" si="6"/>
         <v>Give $2D6 Troops to $R</v>
       </c>
-      <c r="W6" s="81" t="str">
-        <f t="shared" si="5"/>
+      <c r="W6" s="80" t="str">
+        <f t="shared" si="6"/>
         <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="X6" s="79" t="str">
-        <f t="shared" si="5"/>
+      <c r="X6" s="78" t="str">
+        <f t="shared" si="6"/>
         <v>Give $D6 Spies to $R</v>
       </c>
-      <c r="Y6" s="81" t="str">
-        <f t="shared" si="5"/>
+      <c r="Y6" s="80" t="str">
+        <f t="shared" si="6"/>
         <v>Give $2D6 Commodities to $R</v>
       </c>
-      <c r="Z6" s="79" t="str">
-        <f t="shared" si="5"/>
+      <c r="Z6" s="78" t="str">
+        <f t="shared" si="6"/>
         <v>Give $D6 random Cards of each type from your hand to $R</v>
       </c>
-      <c r="AA6" s="81" t="str">
-        <f t="shared" si="5"/>
+      <c r="AA6" s="80" t="str">
+        <f t="shared" si="6"/>
         <v>Lose half your Commodities</v>
       </c>
-      <c r="AB6" s="79" t="str">
-        <f t="shared" si="5"/>
+      <c r="AB6" s="78" t="str">
+        <f t="shared" si="6"/>
         <v>Lose half your Coins</v>
       </c>
-      <c r="AC6" s="81" t="str">
-        <f t="shared" si="5"/>
+      <c r="AC6" s="80" t="str">
+        <f t="shared" si="6"/>
         <v>Lose half your Troops</v>
       </c>
-      <c r="AD6" s="82" t="str">
-        <f t="shared" si="5"/>
+      <c r="AD6" s="81" t="str">
+        <f t="shared" si="6"/>
         <v>Lose half your Spies</v>
       </c>
-      <c r="AE6" s="79" t="str">
-        <f t="shared" si="5"/>
+      <c r="AE6" s="78" t="str">
+        <f t="shared" si="6"/>
         <v>Disard half your cards of each type</v>
       </c>
-      <c r="AF6" s="79" t="str">
-        <f t="shared" si="6"/>
+      <c r="AF6" s="78" t="str">
+        <f t="shared" si="7"/>
         <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
       </c>
-      <c r="AG6" s="81" t="str">
-        <f t="shared" si="6"/>
+      <c r="AG6" s="80" t="str">
+        <f t="shared" si="7"/>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="AH6" s="79" t="str">
-        <f t="shared" si="6"/>
+      <c r="AH6" s="78" t="str">
+        <f t="shared" si="7"/>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="AI6" s="81" t="str">
-        <f t="shared" si="6"/>
+      <c r="AI6" s="80" t="str">
+        <f t="shared" si="7"/>
         <v>Demote a Leader at level $D6 by half and send it to $R</v>
       </c>
-      <c r="AJ6" s="79" t="str">
-        <f t="shared" si="6"/>
+      <c r="AJ6" s="78" t="str">
+        <f t="shared" si="7"/>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="AK6" s="81" t="str">
-        <f t="shared" si="6"/>
+      <c r="AK6" s="80" t="str">
+        <f t="shared" si="7"/>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="AL6" s="79" t="str">
-        <f t="shared" si="6"/>
+      <c r="AL6" s="78" t="str">
+        <f t="shared" si="7"/>
         <v>Move your foremost Law to the back of the Queue</v>
       </c>
-      <c r="AM6" s="81" t="str">
-        <f t="shared" si="6"/>
+      <c r="AM6" s="80" t="str">
+        <f t="shared" si="7"/>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="AN6" s="79" t="str">
-        <f t="shared" si="6"/>
+      <c r="AN6" s="78" t="str">
+        <f t="shared" si="7"/>
         <v>Move $D6 of your Laws each one space back in the Queue</v>
       </c>
-      <c r="AO6" s="81" t="str">
-        <f t="shared" si="6"/>
+      <c r="AO6" s="80" t="str">
+        <f t="shared" si="7"/>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="AP6" s="79" t="str">
-        <f t="shared" si="7"/>
+      <c r="AP6" s="78" t="str">
+        <f t="shared" si="8"/>
         <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="AQ6" s="81" t="str">
-        <f t="shared" si="8"/>
+      <c r="AQ6" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>Give $2D6 Troops to $R</v>
       </c>
-      <c r="AR6" s="79" t="str">
-        <f t="shared" si="8"/>
+      <c r="AR6" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="AS6" s="81" t="str">
-        <f t="shared" si="8"/>
+      <c r="AS6" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>Give $D6 Spies to $R</v>
       </c>
-      <c r="AT6" s="79" t="str">
-        <f t="shared" si="8"/>
+      <c r="AT6" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Give $2D6 Commodities to $R</v>
       </c>
-      <c r="AU6" s="81" t="str">
-        <f t="shared" si="8"/>
+      <c r="AU6" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>Give $D6 random Cards of each type from your hand to $R</v>
       </c>
-      <c r="AV6" s="79" t="str">
-        <f t="shared" si="8"/>
+      <c r="AV6" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Lose half your Commodities</v>
       </c>
-      <c r="AW6" s="81" t="str">
-        <f t="shared" si="8"/>
+      <c r="AW6" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>Lose half your Coins</v>
       </c>
-      <c r="AX6" s="82" t="str">
-        <f t="shared" si="8"/>
+      <c r="AX6" s="81" t="str">
+        <f t="shared" si="9"/>
         <v>Lose half your Troops</v>
       </c>
-      <c r="AY6" s="79" t="str">
-        <f t="shared" si="8"/>
+      <c r="AY6" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Lose half your Spies</v>
       </c>
-      <c r="AZ6" s="81" t="str">
-        <f t="shared" si="8"/>
+      <c r="AZ6" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>Disard half your cards of each type</v>
       </c>
-      <c r="BA6" s="79" t="str">
-        <f t="shared" si="9"/>
+      <c r="BA6" s="78" t="str">
+        <f t="shared" si="10"/>
         <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
       </c>
-      <c r="BB6" s="81" t="str">
-        <f t="shared" si="9"/>
+      <c r="BB6" s="80" t="str">
+        <f t="shared" si="10"/>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="BC6" s="79" t="str">
-        <f t="shared" si="9"/>
+      <c r="BC6" s="78" t="str">
+        <f t="shared" si="10"/>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="BD6" s="81" t="str">
-        <f t="shared" si="9"/>
+      <c r="BD6" s="80" t="str">
+        <f t="shared" si="10"/>
         <v>Demote a Leader at level $D6 by half and send it to $R</v>
       </c>
-      <c r="BE6" s="79" t="str">
-        <f t="shared" si="9"/>
+      <c r="BE6" s="78" t="str">
+        <f t="shared" si="10"/>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="BF6" s="81" t="str">
-        <f t="shared" si="9"/>
+      <c r="BF6" s="80" t="str">
+        <f t="shared" si="10"/>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="BG6" s="79" t="str">
-        <f t="shared" si="9"/>
+      <c r="BG6" s="78" t="str">
+        <f t="shared" si="10"/>
         <v>Move your foremost Law to the back of the Queue</v>
       </c>
-      <c r="BH6" s="79" t="str">
-        <f t="shared" si="9"/>
+      <c r="BH6" s="78" t="str">
+        <f t="shared" si="10"/>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="BI6" s="79" t="str">
-        <f t="shared" si="9"/>
+      <c r="BI6" s="78" t="str">
+        <f t="shared" si="10"/>
         <v>Move $D6 of your Laws each one space back in the Queue</v>
       </c>
-      <c r="BJ6" s="81" t="str">
-        <f t="shared" si="9"/>
+      <c r="BJ6" s="80" t="str">
+        <f t="shared" si="10"/>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="BK6" s="79" t="str">
-        <f t="shared" si="10"/>
+      <c r="BK6" s="78" t="str">
+        <f t="shared" si="11"/>
         <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="BM6" s="79" t="str">
-        <f>AE2</f>
+      <c r="BM6" s="78" t="str">
+        <f t="shared" si="12"/>
         <v>Trade up to $L3 additional Coins when Buying from the Undermarket</v>
       </c>
-      <c r="BN6" s="81" t="str">
-        <f>AF2</f>
+      <c r="BN6" s="80" t="str">
+        <f t="shared" si="12"/>
         <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
       </c>
-      <c r="BO6" s="79" t="str">
-        <f>AG2</f>
+      <c r="BO6" s="78" t="str">
+        <f t="shared" si="12"/>
         <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
       </c>
-      <c r="BP6" s="81" t="str">
-        <f>AH2</f>
+      <c r="BP6" s="80" t="str">
+        <f t="shared" si="12"/>
         <v>Provides private Monetize Action at Market Rate + $L3</v>
       </c>
-      <c r="BQ6" s="79" t="str">
-        <f>AI2</f>
+      <c r="BQ6" s="78" t="str">
+        <f t="shared" si="12"/>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
       </c>
-      <c r="BR6" s="79"/>
-      <c r="BS6" s="80"/>
-      <c r="BU6" s="79"/>
-      <c r="BW6" s="79"/>
-      <c r="BY6" s="79"/>
-      <c r="CA6" s="79"/>
+      <c r="BR6" s="78"/>
+      <c r="BS6" s="79"/>
+      <c r="BU6" s="78"/>
+      <c r="BW6" s="78"/>
+      <c r="BY6" s="78"/>
+      <c r="CA6" s="78"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9083,31 +9178,31 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C1" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="F1" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D2">
         <v>27.7</v>
@@ -9115,14 +9210,14 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D3">
         <v>27.7</v>
@@ -9130,14 +9225,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="D4">
         <v>30.75</v>
@@ -9145,222 +9240,222 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E6" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E7" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E8" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E10" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E12" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E13" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -9374,98 +9469,98 @@
   <dimension ref="A1:U55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24" style="102" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" style="101" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" customWidth="1"/>
     <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="104" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="104" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="104" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="104" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="11.85546875" style="104" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" style="104" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="103" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="103" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="103" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="103" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="11.85546875" style="103" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" style="103" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1" t="s">
+        <v>413</v>
+      </c>
+      <c r="D1" t="s">
+        <v>414</v>
+      </c>
+      <c r="E1" t="s">
+        <v>415</v>
+      </c>
+      <c r="F1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G1" t="s">
+        <v>440</v>
+      </c>
+      <c r="H1" t="s">
+        <v>416</v>
+      </c>
+      <c r="I1" t="s">
+        <v>417</v>
+      </c>
+      <c r="J1" s="103" t="s">
+        <v>438</v>
+      </c>
+      <c r="K1" t="s">
+        <v>418</v>
+      </c>
+      <c r="L1" t="s">
+        <v>419</v>
+      </c>
+      <c r="M1" t="s">
+        <v>420</v>
+      </c>
+      <c r="N1" t="s">
+        <v>421</v>
+      </c>
+      <c r="O1" t="s">
+        <v>422</v>
+      </c>
+      <c r="P1" t="s">
+        <v>423</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>424</v>
+      </c>
+      <c r="R1" t="s">
         <v>425</v>
       </c>
-      <c r="B1" t="s">
+      <c r="S1" t="s">
         <v>426</v>
       </c>
-      <c r="C1" t="s">
+      <c r="T1" t="s">
         <v>427</v>
       </c>
-      <c r="D1" t="s">
-        <v>428</v>
-      </c>
-      <c r="E1" t="s">
-        <v>429</v>
-      </c>
-      <c r="F1" t="s">
-        <v>456</v>
-      </c>
-      <c r="G1" t="s">
-        <v>455</v>
-      </c>
-      <c r="H1" t="s">
-        <v>430</v>
-      </c>
-      <c r="I1" t="s">
-        <v>431</v>
-      </c>
-      <c r="J1" s="104" t="s">
-        <v>453</v>
-      </c>
-      <c r="K1" t="s">
-        <v>432</v>
-      </c>
-      <c r="L1" t="s">
-        <v>433</v>
-      </c>
-      <c r="M1" t="s">
-        <v>434</v>
-      </c>
-      <c r="N1" t="s">
-        <v>435</v>
-      </c>
-      <c r="O1" t="s">
-        <v>436</v>
-      </c>
-      <c r="P1" t="s">
-        <v>437</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>438</v>
-      </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>439</v>
       </c>
-      <c r="S1" t="s">
-        <v>440</v>
-      </c>
-      <c r="T1" t="s">
-        <v>441</v>
-      </c>
-      <c r="U1" t="s">
-        <v>454</v>
-      </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="102">
+      <c r="A2" s="101">
         <v>46075</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
-      <c r="C2" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D2" s="103" t="b">
+      <c r="C2" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="102" t="b">
         <v>0</v>
       </c>
       <c r="E2">
@@ -9474,42 +9569,42 @@
       <c r="F2">
         <v>17</v>
       </c>
-      <c r="H2" s="104">
+      <c r="H2" s="103">
         <v>0.79166666666666663</v>
       </c>
-      <c r="I2" s="104">
+      <c r="I2" s="103">
         <v>0.93055555555555558</v>
       </c>
-      <c r="K2" s="104">
+      <c r="K2" s="103">
         <v>0.81458333333333333</v>
       </c>
-      <c r="L2" s="104">
+      <c r="L2" s="103">
         <v>0.83125000000000004</v>
       </c>
-      <c r="M2" s="104">
+      <c r="M2" s="103">
         <v>0.85486111111111107</v>
       </c>
-      <c r="N2" s="104">
+      <c r="N2" s="103">
         <v>0.87777777777777777</v>
       </c>
-      <c r="O2" s="104">
+      <c r="O2" s="103">
         <v>0.90069444444444446</v>
       </c>
-      <c r="P2" s="104">
+      <c r="P2" s="103">
         <v>0.92638888888888893</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="102">
+      <c r="A3" s="101">
         <v>46089</v>
       </c>
       <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" s="103" t="b">
+      <c r="C3" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="102" t="b">
         <v>0</v>
       </c>
       <c r="E3">
@@ -9521,51 +9616,51 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="104">
+      <c r="H3" s="103">
         <v>0.68541666666666667</v>
       </c>
-      <c r="I3" s="104">
+      <c r="I3" s="103">
         <v>0.86527777777777781</v>
       </c>
-      <c r="J3" s="104">
+      <c r="J3" s="103">
         <v>0.6958333333333333</v>
       </c>
-      <c r="K3" s="104">
+      <c r="K3" s="103">
         <v>0.70763888888888893</v>
       </c>
-      <c r="L3" s="104">
+      <c r="L3" s="103">
         <v>0.7270833333333333</v>
       </c>
-      <c r="M3" s="104">
+      <c r="M3" s="103">
         <v>0.75069444444444444</v>
       </c>
-      <c r="N3" s="104">
+      <c r="N3" s="103">
         <v>0.77500000000000002</v>
       </c>
-      <c r="O3" s="104">
+      <c r="O3" s="103">
         <v>0.80347222222222225</v>
       </c>
-      <c r="P3" s="104">
+      <c r="P3" s="103">
         <v>0.82986111111111116</v>
       </c>
-      <c r="Q3" s="104">
+      <c r="Q3" s="103">
         <v>0.86041666666666672</v>
       </c>
-      <c r="U3" s="104">
+      <c r="U3" s="103">
         <v>0.86527777777777781</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="102">
+      <c r="A4" s="101">
         <v>46105</v>
       </c>
       <c r="B4">
         <v>6</v>
       </c>
-      <c r="C4" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="103" t="b">
+      <c r="C4" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="102" t="b">
         <v>0</v>
       </c>
       <c r="E4">
@@ -9577,442 +9672,487 @@
       <c r="G4">
         <v>10</v>
       </c>
-      <c r="H4" s="104">
+      <c r="H4" s="103">
         <v>0.77500000000000002</v>
       </c>
-      <c r="I4" s="104">
+      <c r="I4" s="103">
         <v>0.92777777777777781</v>
       </c>
-      <c r="J4" s="104">
+      <c r="J4" s="103">
         <v>0.78472222222222221</v>
       </c>
-      <c r="K4" s="104">
+      <c r="K4" s="103">
         <v>0.79236111111111107</v>
       </c>
-      <c r="L4" s="104">
+      <c r="L4" s="103">
         <v>0.81111111111111112</v>
       </c>
-      <c r="M4" s="104">
+      <c r="M4" s="103">
         <v>0.83194444444444449</v>
       </c>
-      <c r="N4" s="104">
+      <c r="N4" s="103">
         <v>0.85277777777777775</v>
       </c>
-      <c r="O4" s="104">
+      <c r="O4" s="103">
         <v>0.88263888888888886</v>
       </c>
-      <c r="P4" s="104">
+      <c r="P4" s="103">
         <v>0.92083333333333328</v>
       </c>
-      <c r="U4" s="104">
+      <c r="U4" s="103">
         <v>0.92777777777777781</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C5" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="103" t="b">
-        <v>0</v>
+      <c r="A5" s="101">
+        <v>46118</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5" s="103">
+        <v>0.78333333333333333</v>
+      </c>
+      <c r="I5" s="103">
+        <v>0.9194444444444444</v>
+      </c>
+      <c r="J5" s="103">
+        <v>0.7944444444444444</v>
+      </c>
+      <c r="K5" s="103">
+        <v>0.8041666666666667</v>
+      </c>
+      <c r="L5" s="103">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="M5" s="103">
+        <v>0.84166666666666667</v>
+      </c>
+      <c r="N5" s="103">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="O5" s="103">
+        <v>0.88958333333333328</v>
+      </c>
+      <c r="P5" s="103">
+        <v>0.91388888888888886</v>
+      </c>
+      <c r="U5" s="103">
+        <v>0.9194444444444444</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C6" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="103" t="b">
+      <c r="C6" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C7" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="103" t="b">
+      <c r="C7" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C8" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="103" t="b">
+      <c r="C8" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C9" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="103" t="b">
+      <c r="C9" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C10" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="103" t="b">
+      <c r="C10" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C11" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="103" t="b">
+      <c r="C11" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C12" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="103" t="b">
+      <c r="C12" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C13" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="103" t="b">
+      <c r="C13" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C14" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="103" t="b">
+      <c r="C14" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C15" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" s="103" t="b">
+      <c r="C15" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="C16" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="103" t="b">
+      <c r="C16" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C17" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="103" t="b">
+      <c r="C17" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C18" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" s="103" t="b">
+      <c r="C18" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C19" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" s="103" t="b">
+      <c r="C19" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="103" t="b">
+      <c r="C20" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="103" t="b">
+      <c r="C21" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="103" t="b">
+      <c r="C22" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="103" t="b">
+      <c r="C23" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" s="103" t="b">
+      <c r="C24" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="103" t="b">
+      <c r="C25" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="103" t="b">
+      <c r="C26" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" s="103" t="b">
+      <c r="C27" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" s="103" t="b">
+      <c r="C28" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C29" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" s="103" t="b">
+      <c r="C29" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C30" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" s="103" t="b">
+      <c r="C30" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C31" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="103" t="b">
+      <c r="C31" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" s="103" t="b">
+      <c r="C32" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" s="103" t="b">
+      <c r="C33" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" s="103" t="b">
+      <c r="C34" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D35" s="103" t="b">
+      <c r="C35" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" s="103" t="b">
+      <c r="C36" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" s="103" t="b">
+      <c r="C37" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" s="103" t="b">
+      <c r="C38" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D39" s="103" t="b">
+      <c r="C39" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D40" s="103" t="b">
+      <c r="C40" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D41" s="103" t="b">
+      <c r="C41" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D41" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" s="103" t="b">
+      <c r="C42" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C43" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D43" s="103" t="b">
+      <c r="C43" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C44" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D44" s="103" t="b">
+      <c r="C44" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C45" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D45" s="103" t="b">
+      <c r="C45" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D46" s="103" t="b">
+      <c r="C46" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D47" s="103" t="b">
+      <c r="C47" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D48" s="103" t="b">
+      <c r="C48" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D49" s="103" t="b">
+      <c r="C49" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D50" s="103" t="b">
+      <c r="C50" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D51" s="103" t="b">
+      <c r="C51" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D52" s="103" t="b">
+      <c r="C52" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D53" s="103" t="b">
+      <c r="C53" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C54" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" s="103" t="b">
+      <c r="C54" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" s="102" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C55" s="103" t="b">
-        <v>0</v>
-      </c>
-      <c r="D55" s="103" t="b">
+      <c r="C55" s="102" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" s="102" t="b">
         <v>0</v>
       </c>
     </row>

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3984" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA427B99-EB21-4C0E-964D-00F6EEEB84D3}"/>
+  <xr:revisionPtr revIDLastSave="4020" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A4ADEB1-1B0B-4B21-8355-52A9DF4AA46E}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="472">
   <si>
     <t>Standard Card</t>
   </si>
@@ -553,9 +553,6 @@
     <t>Schemes</t>
   </si>
   <si>
-    <t>Deploy Troops</t>
-  </si>
-  <si>
     <t>Provincial</t>
   </si>
   <si>
@@ -742,9 +739,6 @@
     <t>Gain the King's Favor &amp; gain half Leader's Level Coins from the Royal Bank. Players holding the King's Favor may not Flatter</t>
   </si>
   <si>
-    <t>Prepare</t>
-  </si>
-  <si>
     <t>Exchange up to Leader Level Coins for Commodities with the Royal Bank at Market Rate then decrease the Market Rate by 1</t>
   </si>
   <si>
@@ -967,24 +961,9 @@
     <t>Undermarket Buy with 2 Coins</t>
   </si>
   <si>
-    <t>Court Buy</t>
-  </si>
-  <si>
-    <t>Court Buy with 4 Coins</t>
-  </si>
-  <si>
     <t>Upgrade Eager Laborers by 2 Levels</t>
   </si>
   <si>
-    <t>Court Sell for 3 Coins</t>
-  </si>
-  <si>
-    <t>Private Sell for 2 Coins</t>
-  </si>
-  <si>
-    <t>Infiltrate 2 Spies</t>
-  </si>
-  <si>
     <t>Postpone with Level 1 Leader</t>
   </si>
   <si>
@@ -994,18 +973,12 @@
     <t>Petition both Laws</t>
   </si>
   <si>
-    <t>Build Level 2 Investment</t>
-  </si>
-  <si>
     <t>Deploy 2 Troops with 1 extra</t>
   </si>
   <si>
     <t>Private Sell</t>
   </si>
   <si>
-    <t>Court Monetize with Law and Scheme cards for 2 Coins</t>
-  </si>
-  <si>
     <t>Undermarket Sell for 4 Coins</t>
   </si>
   <si>
@@ -1039,84 +1012,9 @@
     <t>Instructions</t>
   </si>
   <si>
-    <t>Setup</t>
-  </si>
-  <si>
-    <t>Find starting Investments and Law</t>
-  </si>
-  <si>
-    <t>Place 4 Greeks per player in the Greek Reserves of the Battlefield</t>
-  </si>
-  <si>
-    <t>Place 3 Coins plus 1 per player in the Royal Bank</t>
-  </si>
-  <si>
-    <t>Place a non-player die in the Market Rate with value 3</t>
-  </si>
-  <si>
-    <t>Place your Investments in front of your shield and place a non-player die on each showing level 2</t>
-  </si>
-  <si>
-    <t>Place four of your player dice in front of your shield showing level 2. These are your Leaders.</t>
-  </si>
-  <si>
-    <t>Mark your Law and place it facedown near the Court</t>
-  </si>
-  <si>
-    <t>Without looking at the player Laws, stack them facedown near the Court in turn order. Each player's mark should be visible in the stack. The Veteran's Law should be on top, and the Crime Lord's should be on the bottom.</t>
-  </si>
-  <si>
-    <t>Take the dice, favors, and card markers of your color</t>
-  </si>
-  <si>
-    <t>Place one of your favors on the scoretrack on the outside of the Battlefield</t>
-  </si>
-  <si>
-    <t>Take the King's Favor and place it in front of your shield</t>
-  </si>
-  <si>
-    <t>Give 4 Troops to each player. Tell them to keep Troops in front of their shield.</t>
-  </si>
-  <si>
-    <t>Give 1 Spy to each player. Tell them to keep Spies behind their shield.</t>
-  </si>
-  <si>
-    <t>Give 3 Coins to each player. Tell them to keep Coins behind their shield.</t>
-  </si>
-  <si>
     <t>Spies, cards</t>
   </si>
   <si>
-    <t>Place 2 markers from each Player in each Scheme envelope. Then, give each player an envelope and tell them to keep it behind their shield.</t>
-  </si>
-  <si>
-    <t>Take the Troops and put them near you in plain sight of all players</t>
-  </si>
-  <si>
-    <t>Take the Spies and put them near you in plain sight of all players</t>
-  </si>
-  <si>
-    <t>Take the Coins and Commodities and put them near you in plain sight of all players</t>
-  </si>
-  <si>
-    <t>Take the Battlefield and non-player dice and put them near you in plain sight of all players</t>
-  </si>
-  <si>
-    <t>Take the Scheme envelopes</t>
-  </si>
-  <si>
-    <t>Once all players have collected their starting cards, shuffle the three decks. Give each player 2 cards from each deck for their hand. Tell each player to keep the cards private.</t>
-  </si>
-  <si>
-    <t>Startup</t>
-  </si>
-  <si>
-    <t>Set your Law to 2 when the Chief Scribe asks you</t>
-  </si>
-  <si>
-    <t>Reveal the top card in the Law queue and have the Veteran set the value. Read the deliberated Law and tell players it is not currently active but will be at the end of the round.</t>
-  </si>
-  <si>
     <t>Round 1</t>
   </si>
   <si>
@@ -1126,132 +1024,18 @@
     <t>Round 3</t>
   </si>
   <si>
-    <t>Night</t>
-  </si>
-  <si>
-    <t>Take one of your unused leaders and place it on the Buy space of the Court. Explain you want some Commodities and will pay the Court 2 Coins in exchange for 3 Commodities per Coin. The number of Commodities is determined by the Market Rate. Place 2 Coins in the Royal Bank and take 6 Commodities. Explain that you will lower the Market Rate by 1 since Commodities are now a little more rare.</t>
-  </si>
-  <si>
-    <t>Take one of your unused leaders and place it on Flatter in the Court. Explain you would like the King's Favor since it is worth 1 Honor at the end of the game and that it breaks any tie during the game. Explain that the king also sends you home with some cash. Take 1 Coin (half your Leader's level) from the Royal Bank.</t>
-  </si>
-  <si>
-    <t>Take one of your unused leaders and place it on the Persian spaces of the Battlefield. Place 2 of your Troops in the same space. Explain you want to deploy 2 Troops to fight the Greeks. Since you are the player with the most Troops deployed, you will be the General at the end of the round and gain 1 Honor (Victory Point). Explain the king pays you for your Troops then take 1 Coin (half Troop count) from the Royal Bank.</t>
-  </si>
-  <si>
-    <t>Take one of your unused leaders and place it in a Persian space of the Battlefield. Explain you also want to deploy 2 Troops, but you have War Machines which allows you to purchase more and deploy them immediately. Pay 1 Coin to gain 1 Troop then deploy 3 Troops. Since you now have the most Troops, you will be the General at the end of the round. The king then pays you half your deployed Troops (rounded up), so take 2 Coins from the Royal Bank.</t>
-  </si>
-  <si>
-    <t>Take one of your unused Leaders and place it on Harvest in the Province. Explain you want to get some Commodities, but the Court Buy space is already taken, nor would it get you any more than Harvest. Explain only one player per round may take Court actions. Instead, you will gain 2 Commodities, one for each of your Leader's level.</t>
-  </si>
-  <si>
-    <t>Deploy an unused leader and 2 Troops into the Battlefield then take 1 Coin from the Royal Bank. Explain you have Elite Troops which gets you more Coins during deployment then take 2 more Coins from the Royal Bank.</t>
-  </si>
-  <si>
-    <t>Place an unused leader on Brainstorm in the Province. Explain you want more cards then take a card from each deck for each level of your Leader (2 cards from each deck).</t>
-  </si>
-  <si>
-    <t>Brainstorm and gain 2 cards from each deck. Explain your Genius Commanders also give you two more cards. Take 2 Investments in addition to your other cards.</t>
-  </si>
-  <si>
-    <t>Place an unused leader on Promote in the Province and immediately increase its level by 1. Explain you want a more powerful leader and are willing to spend an action to get it.</t>
-  </si>
-  <si>
-    <t>Place an unused leader on Monetize in the Court. Explain you want some Coins and don't want your cards. This action allows you to gain Coins in exchange for the opposite of the Market Rate in cards (7 - Market Rate). You also have Market Niche, so discard 3 non-Scheme cards and take 1 Coin from the Royal Bank. Explain you do not change the Market Rate for selling ideas.</t>
-  </si>
-  <si>
-    <t>Place an unused leader on Sell in the Province Undermarket. Explain you want Coins in exchange for your Commodities since the Market Rate is so low. Normally, the Undermarket would be worse than the Court, but you have Blood Pact which makes it better for you. Pay 2 Commodities for 2 Coins from outside the Royal Bank. Explain you are dealing with the Undermarket, not the king, so you aren't restricted by the Royal Bank. Increase the Market Rate by 1 since Commodities are now less rare.</t>
-  </si>
-  <si>
-    <t>Place an unused leader on Buy in the Province Undermarket. Explain you want Commodities but have to take a worse rate since the Court Buy has already been used. Exchange 2 Coins for 4 Commodities outside the Royal Bank. Decrease the Market Rate by 1.</t>
-  </si>
-  <si>
-    <t>Place an unused leader on Negotiate in the Province. Explain you want to form an alliance with the Crime Lord, and he must put one of his unused leaders on the same space. Both players then exchange 2 favors, one for each leader level. Explain favors are worth Honor at the end of the game.</t>
-  </si>
-  <si>
-    <t>You have a card that allows you to Monetize at a better rate, so place an unused leader on that card. Then, discard 3 Schemes and 3 Laws to gain 2 Coins outside the Royal Bank.</t>
-  </si>
-  <si>
-    <t>You have no more leaders left, so you must pass for the rest of the round.</t>
-  </si>
-  <si>
-    <t>Place an unused leader on Commission in the Province. Explain you want another leader, so take a leader from behind your shield and place it on the same space with half the level of the first leader.</t>
-  </si>
-  <si>
-    <t>Harvest 1 Commodity for each of your leader's levels.</t>
-  </si>
-  <si>
-    <t>All players are out of leaders, so the round ends and moves to the event phase.</t>
-  </si>
-  <si>
-    <t>1. Explain there are no active Laws, so no one has to pay Taxes. Since no one broke any Laws, the King's Favor stays where it is.</t>
-  </si>
-  <si>
-    <t>2. Now, we fight the Greeks. I deployed the most Troops, so I am the General and will gain 1 Honor now. I will roll 1 die for each player, cut each die value in half (rounded up) then total the result. This is how many Greeks we have to fight. Each Greek and Persian Troop in the battle will kill each other, and whichever side has remaining troops wins (we win ties). If we win, each player who deployed Troops will gain 1 Honor. If we lose, the remaining Greeks will attack our Provinces. See rulebook for Battle details.</t>
-  </si>
-  <si>
-    <t>3. After the battle, everyone collects their leaders from the board.</t>
-  </si>
-  <si>
-    <t>4. I will take everyone's Sheme envelopes, mix them up, then open them one by one. If there are any Schemes, we will resolve them. Then, I will return the reset envelopes to players.</t>
-  </si>
-  <si>
-    <t>5. Since no one postponed this deliberated Law, it becomes active. From now on, all players must obey it or their leaders will have one less level when taking the sanctioned action and pay a tax at the end of the round. I will also reveal the next Law for deliberation. It was sponsored by the Master of Lies, so they will choose its value. This Law is not active until the end of the next round.</t>
-  </si>
-  <si>
-    <t>5. Set your Law to 2 when the Chief Scribe asks you</t>
-  </si>
-  <si>
-    <t>6. There are still Greeks left, so we will play another round.</t>
-  </si>
-  <si>
-    <t>8. I have the King's Favor, so I will start the next round.</t>
-  </si>
-  <si>
-    <t>Scheme Instructions</t>
-  </si>
-  <si>
-    <t>You are doing great! Keep up the good work.</t>
-  </si>
-  <si>
     <t>Court Buy with 2 Coins</t>
   </si>
   <si>
-    <t>Deploy 2 Troops with 1 War Machine</t>
-  </si>
-  <si>
-    <t>Court Monetize with 3 non-scheme cards</t>
-  </si>
-  <si>
-    <t>Undermarket Sell for 2 Coins</t>
-  </si>
-  <si>
-    <t>Brainstorm with 2 extra Investments</t>
-  </si>
-  <si>
-    <t>Negotiate with Crime Lord</t>
-  </si>
-  <si>
-    <t>Monetize with 3 Schemes and 3 Laws</t>
-  </si>
-  <si>
     <t>Change the boundary of an active Law to $L6</t>
   </si>
   <si>
     <t>Irregular Partiality</t>
   </si>
   <si>
-    <t>Place an unused leader on Accuse in the Province. Explain you want to fight the Master of Lies, and they must place one of their unused leaders on the same space. Both players then put 1 Coin into the Royal Bank and roll dice to resolve the Accuse. Each Accuse has three rounds. The player who rolls more hits wins a round. The player who wins the best two out of three rounds wins the Accuse. Each die rolled higher than 3 counts as a hit. Tied rounds are repeated unless a player has the King's Favor to break the tie. You have Training Grounds which give you an automatic two hits each Roll. Perform the Accuse. Whoever wins takes two Coins from the Royal Bank and gains 1 Honor.</t>
-  </si>
-  <si>
-    <t>Accuse Crime Lord</t>
-  </si>
-  <si>
     <t>Accuse Veteran</t>
   </si>
   <si>
-    <t>Accuse Master of Lies</t>
-  </si>
-  <si>
     <t>Desperate Attorneys</t>
   </si>
   <si>
@@ -1519,15 +1303,6 @@
     <t>Court Sell for 2 Coins</t>
   </si>
   <si>
-    <t>7. The king has many other financial interests and has made some money. I will add 3 Coins to the Royal Bank and adjust the Market Rate by 1 in a random direction. See rulebook for Market Rate adjustment details. Roll until Market Rate increases to 3.</t>
-  </si>
-  <si>
-    <t>At some point during the next round, place a Spy into the Scheme envelope with Corporate Takeover. Place a marker for the Warmongerer in the top left corner of the card and a marker for one of your Allies in the bottom right corner.</t>
-  </si>
-  <si>
-    <t>At some point during the next round, place a Spy into the Scheme envelope with Intimidation. Place a marker for the Chief Scribe in the top left corner of the card.</t>
-  </si>
-  <si>
     <t>Private Sell for 3 Coins</t>
   </si>
   <si>
@@ -1537,9 +1312,6 @@
     <t>Infiltrate 3 Spies</t>
   </si>
   <si>
-    <t>Take one of your unused leaders and place it on the Recruit space of the Province. Explain you want to get some Troops, so you will pay  2 Coins to the people of your Province. Put 2 Coins in the pile, not the Royal Bank, and take 2 Troops + 1. Explain that the Coins do not go to the Royal Bank during Recruit.</t>
-  </si>
-  <si>
     <t>Deploy $L3 additional Troops during Deploy</t>
   </si>
   <si>
@@ -1655,6 +1427,39 @@
   </si>
   <si>
     <t>Build Level 2 Investment (Boasting Propaganda)</t>
+  </si>
+  <si>
+    <t>Recruit 3 Troops</t>
+  </si>
+  <si>
+    <t>Buy with 2 Coins</t>
+  </si>
+  <si>
+    <t>Harvest 4 Commodities</t>
+  </si>
+  <si>
+    <t>Monetize for 1 Coin</t>
+  </si>
+  <si>
+    <t>Brainstorm for 6 cards</t>
+  </si>
+  <si>
+    <t>Brainstorm for 8 cards</t>
+  </si>
+  <si>
+    <t>Negotiate with the Crime Lord</t>
+  </si>
+  <si>
+    <t>Sue the Master of Lies</t>
+  </si>
+  <si>
+    <t>Monetize Schemes and Laws for 2 Coins</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Sue Crime Lord</t>
   </si>
 </sst>
 </file>
@@ -2976,6 +2781,60 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2986,60 +2845,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4272,7 +4077,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
@@ -4283,10 +4088,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>435</v>
+        <v>363</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>436</v>
+        <v>364</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>14</v>
@@ -4295,10 +4100,10 @@
         <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>522</v>
+        <v>446</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>484</v>
+        <v>412</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
@@ -4312,19 +4117,19 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>502</v>
+        <v>426</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>396</v>
+        <v>327</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>473</v>
+        <v>401</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="3"/>
@@ -4344,13 +4149,13 @@
         <v>23</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>396</v>
+        <v>327</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>523</v>
+        <v>447</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
@@ -4373,10 +4178,10 @@
         <v>29</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>519</v>
+        <v>443</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>476</v>
+        <v>404</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3"/>
@@ -4399,10 +4204,10 @@
         <v>35</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>511</v>
+        <v>435</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>512</v>
+        <v>436</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3"/>
@@ -4416,19 +4221,19 @@
         <v>41</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>510</v>
+        <v>434</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>397</v>
+        <v>328</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>396</v>
+        <v>327</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>513</v>
+        <v>437</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>514</v>
+        <v>438</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
@@ -4439,7 +4244,7 @@
         <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>532</v>
+        <v>456</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>44</v>
@@ -4448,13 +4253,13 @@
         <v>39</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>396</v>
+        <v>327</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>515</v>
+        <v>439</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>516</v>
+        <v>440</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
@@ -4471,16 +4276,16 @@
         <v>49</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>526</v>
+        <v>450</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>530</v>
+        <v>454</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>517</v>
+        <v>441</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>518</v>
+        <v>442</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
@@ -4491,22 +4296,22 @@
         <v>43</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>446</v>
+        <v>374</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>529</v>
+        <v>453</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>531</v>
+        <v>455</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>521</v>
+        <v>445</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>520</v>
+        <v>444</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="2"/>
@@ -4520,7 +4325,7 @@
         <v>57</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>432</v>
+        <v>360</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>50</v>
@@ -4532,7 +4337,7 @@
         <v>46</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>478</v>
+        <v>406</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="2"/>
@@ -4558,7 +4363,7 @@
         <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>477</v>
+        <v>405</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
@@ -4584,7 +4389,7 @@
         <v>42</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>477</v>
+        <v>405</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
@@ -4598,7 +4403,7 @@
         <v>71</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>468</v>
+        <v>396</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>63</v>
@@ -4610,7 +4415,7 @@
         <v>65</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>480</v>
+        <v>408</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3"/>
@@ -4621,7 +4426,7 @@
         <v>66</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>445</v>
+        <v>373</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>76</v>
@@ -4630,13 +4435,13 @@
         <v>69</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>533</v>
+        <v>457</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>509</v>
+        <v>433</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>479</v>
+        <v>407</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="2"/>
@@ -4659,10 +4464,10 @@
         <v>73</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>483</v>
+        <v>411</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>479</v>
+        <v>407</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="2"/>
@@ -4682,13 +4487,13 @@
         <v>77</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>409</v>
+        <v>337</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
@@ -4708,13 +4513,13 @@
         <v>81</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>410</v>
+        <v>338</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>462</v>
+        <v>390</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>481</v>
+        <v>409</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
@@ -4737,10 +4542,10 @@
         <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>463</v>
+        <v>391</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
@@ -4763,10 +4568,10 @@
         <v>91</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>486</v>
+        <v>414</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>481</v>
+        <v>409</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
@@ -4786,13 +4591,13 @@
         <v>95</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>429</v>
+        <v>357</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>485</v>
+        <v>413</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="3"/>
@@ -4803,10 +4608,10 @@
         <v>96</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>403</v>
+        <v>331</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>527</v>
+        <v>451</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>99</v>
@@ -4825,10 +4630,10 @@
         <v>101</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>528</v>
+        <v>452</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>104</v>
@@ -4872,13 +4677,13 @@
         <v>116</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>488</v>
+        <v>416</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>110</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>466</v>
+        <v>394</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4900,7 +4705,7 @@
         <v>114</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>467</v>
+        <v>395</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4922,7 +4727,7 @@
         <v>117</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>464</v>
+        <v>392</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4944,7 +4749,7 @@
         <v>121</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>465</v>
+        <v>393</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -5004,13 +4809,13 @@
         <v>139</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>443</v>
+        <v>371</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>460</v>
+        <v>388</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>458</v>
+        <v>386</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -5029,10 +4834,10 @@
         <v>142</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>461</v>
+        <v>389</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>459</v>
+        <v>387</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -5045,10 +4850,10 @@
         <v>138</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>433</v>
+        <v>361</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>434</v>
+        <v>362</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="16"/>
@@ -5063,10 +4868,10 @@
         <v>140</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>447</v>
+        <v>375</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>444</v>
+        <v>372</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="16"/>
@@ -5081,10 +4886,10 @@
         <v>143</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>457</v>
+        <v>385</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>534</v>
+        <v>458</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -5099,10 +4904,10 @@
         <v>144</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>455</v>
+        <v>383</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -5117,10 +4922,10 @@
         <v>145</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>471</v>
+        <v>399</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>470</v>
+        <v>398</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -5135,10 +4940,10 @@
         <v>146</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>499</v>
+        <v>423</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>498</v>
+        <v>422</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -5153,10 +4958,10 @@
         <v>147</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>524</v>
+        <v>448</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>525</v>
+        <v>449</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="16"/>
@@ -5171,10 +4976,10 @@
         <v>148</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>535</v>
+        <v>459</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>454</v>
+        <v>382</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="16"/>
@@ -5394,7 +5199,7 @@
         <v>166</v>
       </c>
       <c r="G1" s="54" t="s">
-        <v>406</v>
+        <v>334</v>
       </c>
       <c r="H1" s="54" t="s">
         <v>167</v>
@@ -5405,186 +5210,186 @@
     </row>
     <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="47" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>469</v>
+        <v>397</v>
       </c>
       <c r="C2" s="49" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="E2" s="50" t="s">
         <v>171</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>173</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="H2" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="H2" s="50" t="s">
-        <v>175</v>
-      </c>
       <c r="I2" s="50" t="s">
-        <v>487</v>
+        <v>415</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="37" t="s">
-        <v>408</v>
+        <v>336</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>407</v>
+        <v>335</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="E3" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="G3" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="H3" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="I3" s="42" t="s">
         <v>178</v>
-      </c>
-      <c r="H3" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="I3" s="42" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="B4" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="C4" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D4" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="42" t="s">
+      <c r="E4" s="42" t="s">
         <v>182</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="F4" s="42" t="s">
+        <v>365</v>
+      </c>
+      <c r="G4" s="42" t="s">
         <v>183</v>
       </c>
-      <c r="F4" s="42" t="s">
-        <v>437</v>
-      </c>
-      <c r="G4" s="42" t="s">
+      <c r="H4" s="42" t="s">
         <v>184</v>
-      </c>
-      <c r="H4" s="42" t="s">
-        <v>185</v>
       </c>
       <c r="I4" s="45"/>
     </row>
     <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="D5" s="42" t="s">
+      <c r="E5" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="F5" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="F5" s="42" t="s">
-        <v>189</v>
-      </c>
       <c r="G5" s="42" t="s">
-        <v>404</v>
+        <v>332</v>
       </c>
       <c r="H5" s="42" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I5" s="45"/>
     </row>
     <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A6" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="C6" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="42" t="s">
         <v>191</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="D6" s="42" t="s">
+      <c r="E6" s="42" t="s">
         <v>192</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="F6" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="F6" s="42" t="s">
-        <v>194</v>
-      </c>
       <c r="G6" s="42" t="s">
-        <v>405</v>
+        <v>333</v>
       </c>
       <c r="H6" s="42" t="s">
-        <v>472</v>
+        <v>400</v>
       </c>
       <c r="I6" s="45"/>
     </row>
     <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="C7" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="G7" s="42" t="s">
         <v>196</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="F7" s="44" t="s">
-        <v>328</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>197</v>
       </c>
       <c r="H7" s="42"/>
       <c r="I7" s="45"/>
     </row>
     <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="B8" s="35" t="s">
+      <c r="C8" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="C8" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="42" t="s">
+      <c r="E8" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="F8" s="42" t="s">
         <v>200</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>295</v>
-      </c>
-      <c r="F8" s="42" t="s">
-        <v>201</v>
       </c>
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
@@ -5592,22 +5397,22 @@
     </row>
     <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="C9" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="42" t="s">
         <v>203</v>
       </c>
-      <c r="C9" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="D9" s="42" t="s">
+      <c r="E9" s="42" t="s">
         <v>204</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="F9" s="42" t="s">
         <v>205</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>206</v>
       </c>
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
@@ -5615,19 +5420,19 @@
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" s="35" t="s">
         <v>207</v>
       </c>
-      <c r="B10" s="35" t="s">
+      <c r="C10" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>377</v>
+      </c>
+      <c r="E10" s="42" t="s">
         <v>208</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>449</v>
-      </c>
-      <c r="E10" s="42" t="s">
-        <v>209</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
@@ -5636,17 +5441,17 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>448</v>
+        <v>376</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="42" t="s">
-        <v>450</v>
+        <v>378</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
@@ -5655,17 +5460,17 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="B12" s="35" t="s">
-        <v>212</v>
-      </c>
       <c r="C12" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D12" s="42"/>
       <c r="E12" s="42" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F12" s="44"/>
       <c r="G12" s="42"/>
@@ -5674,17 +5479,17 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="B13" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="B13" s="35" t="s">
-        <v>215</v>
-      </c>
       <c r="C13" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D13" s="42"/>
       <c r="E13" s="42" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F13" s="44"/>
       <c r="G13" s="42"/>
@@ -5693,17 +5498,17 @@
     </row>
     <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="B14" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="C14" s="38" t="s">
         <v>218</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>219</v>
       </c>
       <c r="D14" s="42"/>
       <c r="E14" s="42" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="42"/>
@@ -5712,13 +5517,13 @@
     </row>
     <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="B15" s="35" t="s">
-        <v>222</v>
-      </c>
       <c r="C15" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="42"/>
@@ -5729,13 +5534,13 @@
     </row>
     <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="B16" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="B16" s="35" t="s">
-        <v>224</v>
-      </c>
       <c r="C16" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D16" s="42"/>
       <c r="E16" s="42"/>
@@ -5746,13 +5551,13 @@
     </row>
     <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
-        <v>451</v>
+        <v>379</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>453</v>
+        <v>381</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D17" s="42"/>
       <c r="E17" s="42"/>
@@ -5763,13 +5568,13 @@
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="B18" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="C18" s="38" t="s">
         <v>226</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>227</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="42"/>
@@ -5780,13 +5585,13 @@
     </row>
     <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="B19" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="B19" s="35" t="s">
-        <v>229</v>
-      </c>
       <c r="C19" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="42"/>
@@ -5797,13 +5602,13 @@
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="B20" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="B20" s="35" t="s">
-        <v>231</v>
-      </c>
       <c r="C20" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
@@ -5814,13 +5619,13 @@
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
-        <v>430</v>
+        <v>358</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>431</v>
+        <v>359</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
@@ -5831,13 +5636,13 @@
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -5848,13 +5653,13 @@
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D23" s="42"/>
       <c r="E23" s="42"/>
@@ -5865,13 +5670,13 @@
     </row>
     <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="42"/>
@@ -5882,13 +5687,13 @@
     </row>
     <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
-        <v>451</v>
+        <v>379</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>452</v>
+        <v>380</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D25" s="43"/>
       <c r="E25" s="43"/>
@@ -5905,7 +5710,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920DF489-FE6D-4819-BD1A-323DFAE597A3}">
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
@@ -5915,30 +5720,30 @@
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="67"/>
       <c r="B1" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1" s="60" t="s">
         <v>236</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="E1" s="60" t="s">
         <v>237</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="F1" s="60" t="s">
         <v>238</v>
       </c>
-      <c r="E1" s="60" t="s">
+      <c r="G1" s="60" t="s">
         <v>239</v>
       </c>
-      <c r="F1" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="G1" s="60" t="s">
-        <v>241</v>
-      </c>
       <c r="I1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="69" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B2" s="70" t="s">
         <v>88</v>
@@ -5959,38 +5764,38 @@
         <v>123</v>
       </c>
       <c r="I2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="69" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B3" s="71" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>532</v>
+        <v>456</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>435</v>
+        <v>363</v>
       </c>
       <c r="E3" s="109" t="s">
         <v>97</v>
       </c>
       <c r="F3" s="59" t="s">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="G3" s="63" t="s">
         <v>136</v>
       </c>
       <c r="I3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="69" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B4" s="63" t="s">
         <v>61</v>
@@ -6011,12 +5816,12 @@
         <v>116</v>
       </c>
       <c r="I4" t="s">
-        <v>428</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="69" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B5" s="68" t="s">
         <v>141</v>
@@ -6028,21 +5833,21 @@
         <v>17</v>
       </c>
       <c r="E5" s="110" t="s">
-        <v>446</v>
+        <v>374</v>
       </c>
       <c r="F5" s="113" t="s">
         <v>83</v>
       </c>
       <c r="G5" s="111" t="s">
-        <v>456</v>
+        <v>384</v>
       </c>
       <c r="I5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="92" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B6" s="93" t="s">
         <v>104</v>
@@ -6063,951 +5868,561 @@
         <v>121</v>
       </c>
       <c r="I6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="72" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="72" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>322</v>
+      </c>
+      <c r="D7" t="s">
         <v>247</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="E7" s="69" t="s">
         <v>248</v>
       </c>
-      <c r="C7" s="69" t="s">
-        <v>346</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>249</v>
-      </c>
-      <c r="E7" s="69" t="s">
-        <v>250</v>
-      </c>
-      <c r="F7" t="s">
-        <v>251</v>
       </c>
       <c r="G7" s="69" t="s">
         <v>168</v>
       </c>
       <c r="I7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="90" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B8" s="90" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>238</v>
+      </c>
+      <c r="D8" s="90" t="s">
         <v>239</v>
       </c>
-      <c r="C8" s="86" t="s">
-        <v>240</v>
-      </c>
-      <c r="D8" s="90" t="s">
-        <v>241</v>
-      </c>
       <c r="E8" s="86" t="s">
+        <v>234</v>
+      </c>
+      <c r="F8" s="90" t="s">
+        <v>235</v>
+      </c>
+      <c r="G8" s="87" t="s">
         <v>236</v>
       </c>
-      <c r="F8" s="90" t="s">
-        <v>237</v>
-      </c>
-      <c r="G8" s="87" t="s">
-        <v>238</v>
-      </c>
       <c r="I8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="59" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D9" s="59" t="s">
+        <v>235</v>
+      </c>
+      <c r="E9" t="s">
+        <v>239</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>234</v>
+      </c>
+      <c r="G9" s="71" t="s">
         <v>237</v>
-      </c>
-      <c r="E9" t="s">
-        <v>241</v>
-      </c>
-      <c r="F9" s="59" t="s">
-        <v>236</v>
-      </c>
-      <c r="G9" s="71" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B10" s="91" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="88" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" s="91" t="s">
+        <v>234</v>
+      </c>
+      <c r="E10" s="88" t="s">
         <v>238</v>
       </c>
-      <c r="C10" s="88" t="s">
-        <v>241</v>
-      </c>
-      <c r="D10" s="91" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="88" t="s">
-        <v>240</v>
-      </c>
       <c r="F10" s="91" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G10" s="89" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>348</v>
+        <v>461</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>302</v>
+      </c>
       <c r="E13" s="2" t="s">
-        <v>350</v>
+        <v>462</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>351</v>
+        <v>309</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>340</v>
+        <v>302</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>340</v>
+        <v>464</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>340</v>
+        <v>308</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>340</v>
+        <v>417</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>340</v>
+        <v>465</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>341</v>
+        <v>466</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>341</v>
+        <v>194</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>341</v>
+        <v>304</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>341</v>
+        <v>467</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>341</v>
+        <v>468</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>341</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>332</v>
+        <v>469</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>332</v>
+        <v>470</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>332</v>
+        <v>189</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>332</v>
+        <v>194</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>332</v>
+        <v>463</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="B18" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>336</v>
+        <v>194</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>326</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>336</v>
+        <v>419</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+      <c r="I18" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>337</v>
+        <v>206</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>337</v>
+        <v>418</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+      <c r="I19" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
-        <v>343</v>
+        <v>302</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>344</v>
+        <v>421</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>334</v>
+        <v>303</v>
+      </c>
+      <c r="E20" t="s">
+        <v>206</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>333</v>
+        <v>358</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
-      <c r="B21" s="2" t="s">
-        <v>342</v>
-      </c>
+      <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>356</v>
+        <v>302</v>
+      </c>
+      <c r="D21" t="s">
+        <v>424</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>345</v>
+        <v>460</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="F22" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>320</v>
+      </c>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:9" ht="225" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="255" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>325</v>
+      </c>
       <c r="B24" s="2" t="s">
-        <v>366</v>
+        <v>314</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>370</v>
+        <v>229</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>315</v>
+        <v>201</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>489</v>
+        <v>310</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="345" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+      <c r="I24" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
-        <v>368</v>
+        <v>210</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>369</v>
+        <v>213</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>372</v>
+        <v>314</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>373</v>
+        <v>329</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>398</v>
+        <v>471</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+        <v>431</v>
+      </c>
+      <c r="I25" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
-        <v>374</v>
+        <v>430</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>375</v>
+        <v>227</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
+      </c>
+      <c r="E26" t="s">
+        <v>429</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>377</v>
+        <v>210</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="255" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>381</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="I26" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="3"/>
+      <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>384</v>
+        <v>313</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>491</v>
+        <v>431</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="195" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="I27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C30" t="s">
-        <v>389</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="I30" t="s">
-        <v>314</v>
-      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="I28" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="I29" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
-      <c r="B31" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="3"/>
-      <c r="B32" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E32" t="s">
-        <v>207</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="3"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D33" t="s">
-        <v>500</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="3"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="2"/>
-      <c r="D34" s="2" t="s">
-        <v>329</v>
-      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="3"/>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>359</v>
-      </c>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-      <c r="I36" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="I37" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="3"/>
-      <c r="B38" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="I38" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-      <c r="B39" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E39" t="s">
-        <v>505</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="I39" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="3"/>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
-      <c r="C40" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>323</v>
-      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
       <c r="G40" s="2"/>
-      <c r="I40" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="I41" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-    </row>
-    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B47" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B48" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B49" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="52" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B54" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B55" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-    </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B58" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B59" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B61" s="3"/>
-      <c r="C61" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="3"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7030,66 +6445,66 @@
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="E1" s="114" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="31" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E2" s="115"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3" s="30" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>408</v>
+        <v>336</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E3" s="115"/>
     </row>
     <row r="4" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A4" s="34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>451</v>
+        <v>379</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -7116,42 +6531,42 @@
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>430</v>
+        <v>358</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E1" s="116" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D2" s="104" t="s">
-        <v>451</v>
+        <v>379</v>
       </c>
       <c r="E2" s="117"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="105" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B3" s="118" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C3" s="119"/>
       <c r="D3" s="119"/>
@@ -7178,209 +6593,189 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="121">
-        <v>0</v>
-      </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="121">
+      <c r="A1" s="139">
+        <v>0</v>
+      </c>
+      <c r="B1" s="140"/>
+      <c r="C1" s="139">
         <v>1</v>
       </c>
-      <c r="D1" s="122"/>
-      <c r="E1" s="121">
+      <c r="D1" s="140"/>
+      <c r="E1" s="139">
         <v>2</v>
       </c>
-      <c r="F1" s="122"/>
-      <c r="G1" s="121">
+      <c r="F1" s="140"/>
+      <c r="G1" s="139">
         <v>3</v>
       </c>
-      <c r="H1" s="122"/>
-      <c r="I1" s="121">
+      <c r="H1" s="140"/>
+      <c r="I1" s="139">
         <v>4</v>
       </c>
-      <c r="J1" s="122"/>
-      <c r="K1" s="121">
+      <c r="J1" s="140"/>
+      <c r="K1" s="139">
         <v>5</v>
       </c>
-      <c r="L1" s="122"/>
-      <c r="M1" s="121">
+      <c r="L1" s="140"/>
+      <c r="M1" s="139">
         <v>6</v>
       </c>
-      <c r="N1" s="122"/>
+      <c r="N1" s="140"/>
     </row>
     <row r="2" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="123">
+      <c r="A2" s="141">
         <v>19</v>
       </c>
-      <c r="B2" s="134" t="s">
-        <v>254</v>
-      </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="135"/>
-      <c r="M2" s="136"/>
-      <c r="N2" s="123">
+      <c r="B2" s="130" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="131"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="131"/>
+      <c r="F2" s="131"/>
+      <c r="G2" s="131"/>
+      <c r="H2" s="131"/>
+      <c r="I2" s="131"/>
+      <c r="J2" s="131"/>
+      <c r="K2" s="131"/>
+      <c r="L2" s="131"/>
+      <c r="M2" s="132"/>
+      <c r="N2" s="141">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="124"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="138"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="139"/>
-      <c r="N3" s="124"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
+      <c r="I3" s="134"/>
+      <c r="J3" s="134"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="134"/>
+      <c r="M3" s="135"/>
+      <c r="N3" s="142"/>
     </row>
     <row r="4" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="123">
+      <c r="A4" s="141">
         <v>18</v>
       </c>
-      <c r="B4" s="140"/>
-      <c r="C4" s="141"/>
-      <c r="D4" s="141"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="141"/>
-      <c r="I4" s="141"/>
-      <c r="J4" s="141"/>
-      <c r="K4" s="141"/>
-      <c r="L4" s="141"/>
-      <c r="M4" s="142"/>
-      <c r="N4" s="123">
+      <c r="B4" s="136"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137"/>
+      <c r="M4" s="138"/>
+      <c r="N4" s="141">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="124"/>
-      <c r="B5" s="125" t="s">
-        <v>255</v>
-      </c>
-      <c r="C5" s="126"/>
-      <c r="D5" s="129" t="s">
-        <v>255</v>
-      </c>
-      <c r="E5" s="130"/>
-      <c r="F5" s="129" t="s">
-        <v>255</v>
-      </c>
-      <c r="G5" s="130"/>
-      <c r="H5" s="129" t="s">
-        <v>255</v>
-      </c>
-      <c r="I5" s="130"/>
-      <c r="J5" s="129" t="s">
-        <v>255</v>
-      </c>
-      <c r="K5" s="130"/>
-      <c r="L5" s="129" t="s">
-        <v>255</v>
-      </c>
-      <c r="M5" s="133"/>
-      <c r="N5" s="124"/>
+      <c r="A5" s="142"/>
+      <c r="B5" s="123" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="128"/>
+      <c r="D5" s="121" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5" s="122"/>
+      <c r="F5" s="121" t="s">
+        <v>253</v>
+      </c>
+      <c r="G5" s="122"/>
+      <c r="H5" s="121" t="s">
+        <v>253</v>
+      </c>
+      <c r="I5" s="122"/>
+      <c r="J5" s="121" t="s">
+        <v>253</v>
+      </c>
+      <c r="K5" s="122"/>
+      <c r="L5" s="121" t="s">
+        <v>253</v>
+      </c>
+      <c r="M5" s="127"/>
+      <c r="N5" s="142"/>
     </row>
     <row r="6" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="123">
+      <c r="A6" s="141">
         <v>17</v>
       </c>
-      <c r="B6" s="125"/>
-      <c r="C6" s="126"/>
-      <c r="D6" s="125"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="125"/>
-      <c r="G6" s="131"/>
-      <c r="H6" s="125"/>
-      <c r="I6" s="131"/>
-      <c r="J6" s="125"/>
-      <c r="K6" s="131"/>
-      <c r="L6" s="125"/>
-      <c r="M6" s="126"/>
-      <c r="N6" s="123">
+      <c r="B6" s="123"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="124"/>
+      <c r="J6" s="123"/>
+      <c r="K6" s="124"/>
+      <c r="L6" s="123"/>
+      <c r="M6" s="128"/>
+      <c r="N6" s="141">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="124"/>
-      <c r="B7" s="127"/>
-      <c r="C7" s="128"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="127"/>
-      <c r="I7" s="132"/>
-      <c r="J7" s="127"/>
-      <c r="K7" s="132"/>
-      <c r="L7" s="127"/>
-      <c r="M7" s="128"/>
-      <c r="N7" s="124"/>
+      <c r="A7" s="142"/>
+      <c r="B7" s="125"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="126"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="126"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="126"/>
+      <c r="L7" s="125"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="142"/>
     </row>
     <row r="8" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="121">
+      <c r="A8" s="139">
         <v>16</v>
       </c>
-      <c r="B8" s="122"/>
-      <c r="C8" s="121">
+      <c r="B8" s="140"/>
+      <c r="C8" s="139">
         <v>15</v>
       </c>
-      <c r="D8" s="122"/>
-      <c r="E8" s="121">
+      <c r="D8" s="140"/>
+      <c r="E8" s="139">
         <v>14</v>
       </c>
-      <c r="F8" s="122"/>
-      <c r="G8" s="121">
+      <c r="F8" s="140"/>
+      <c r="G8" s="139">
         <v>13</v>
       </c>
-      <c r="H8" s="122"/>
-      <c r="I8" s="121">
+      <c r="H8" s="140"/>
+      <c r="I8" s="139">
         <v>12</v>
       </c>
-      <c r="J8" s="122"/>
-      <c r="K8" s="121">
+      <c r="J8" s="140"/>
+      <c r="K8" s="139">
         <v>11</v>
       </c>
-      <c r="L8" s="122"/>
-      <c r="M8" s="121">
+      <c r="L8" s="140"/>
+      <c r="M8" s="139">
         <v>10</v>
       </c>
-      <c r="N8" s="122"/>
+      <c r="N8" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="F5:G7"/>
-    <mergeCell ref="H5:I7"/>
-    <mergeCell ref="J5:K7"/>
-    <mergeCell ref="L5:M7"/>
-    <mergeCell ref="B2:M4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A6:A7"/>
@@ -7388,6 +6783,26 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B5:C7"/>
     <mergeCell ref="D5:E7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="F5:G7"/>
+    <mergeCell ref="H5:I7"/>
+    <mergeCell ref="J5:K7"/>
+    <mergeCell ref="L5:M7"/>
+    <mergeCell ref="B2:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -9178,31 +8593,31 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1" t="s">
         <v>275</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>276</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>277</v>
-      </c>
-      <c r="E1" t="s">
-        <v>278</v>
-      </c>
-      <c r="F1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D2">
         <v>27.7</v>
@@ -9210,14 +8625,14 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D3">
         <v>27.7</v>
@@ -9225,14 +8640,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D4">
         <v>30.75</v>
@@ -9240,222 +8655,222 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E8" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E12" t="s">
         <v>281</v>
-      </c>
-      <c r="E12" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
+        <v>279</v>
+      </c>
+      <c r="E13" t="s">
         <v>281</v>
-      </c>
-      <c r="E13" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -9487,67 +8902,67 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>411</v>
+        <v>339</v>
       </c>
       <c r="B1" t="s">
-        <v>412</v>
+        <v>340</v>
       </c>
       <c r="C1" t="s">
-        <v>413</v>
+        <v>341</v>
       </c>
       <c r="D1" t="s">
-        <v>414</v>
+        <v>342</v>
       </c>
       <c r="E1" t="s">
-        <v>415</v>
+        <v>343</v>
       </c>
       <c r="F1" t="s">
-        <v>441</v>
+        <v>369</v>
       </c>
       <c r="G1" t="s">
-        <v>440</v>
+        <v>368</v>
       </c>
       <c r="H1" t="s">
-        <v>416</v>
+        <v>344</v>
       </c>
       <c r="I1" t="s">
-        <v>417</v>
+        <v>345</v>
       </c>
       <c r="J1" s="103" t="s">
-        <v>438</v>
+        <v>366</v>
       </c>
       <c r="K1" t="s">
-        <v>418</v>
+        <v>346</v>
       </c>
       <c r="L1" t="s">
-        <v>419</v>
+        <v>347</v>
       </c>
       <c r="M1" t="s">
-        <v>420</v>
+        <v>348</v>
       </c>
       <c r="N1" t="s">
-        <v>421</v>
+        <v>349</v>
       </c>
       <c r="O1" t="s">
-        <v>422</v>
+        <v>350</v>
       </c>
       <c r="P1" t="s">
-        <v>423</v>
+        <v>351</v>
       </c>
       <c r="Q1" t="s">
-        <v>424</v>
+        <v>352</v>
       </c>
       <c r="R1" t="s">
-        <v>425</v>
+        <v>353</v>
       </c>
       <c r="S1" t="s">
-        <v>426</v>
+        <v>354</v>
       </c>
       <c r="T1" t="s">
-        <v>427</v>
+        <v>355</v>
       </c>
       <c r="U1" t="s">
-        <v>439</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4020" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A4ADEB1-1B0B-4B21-8355-52A9DF4AA46E}"/>
+  <xr:revisionPtr revIDLastSave="4069" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD2256F1-E359-C640-8357-E402C4190679}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -304,9 +304,6 @@
     <t>Stone Foundations</t>
   </si>
   <si>
-    <t>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</t>
-  </si>
-  <si>
     <t>7S</t>
   </si>
   <si>
@@ -319,9 +316,6 @@
     <t>Environmental Guardians</t>
   </si>
   <si>
-    <t>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</t>
-  </si>
-  <si>
     <t>8S</t>
   </si>
   <si>
@@ -361,18 +355,12 @@
     <t>Police Force</t>
   </si>
   <si>
-    <t>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</t>
-  </si>
-  <si>
     <t>JS</t>
   </si>
   <si>
     <t>Equal Partners</t>
   </si>
   <si>
-    <t>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</t>
-  </si>
-  <si>
     <t>QS</t>
   </si>
   <si>
@@ -385,9 +373,6 @@
     <t>Eager Laborers</t>
   </si>
   <si>
-    <t>Collect $L6 additional Commodities during Harvests</t>
-  </si>
-  <si>
     <t>Honorable Marketplace</t>
   </si>
   <si>
@@ -664,9 +649,6 @@
     <t>1 per every 3 Troops</t>
   </si>
   <si>
-    <t>Harvest</t>
-  </si>
-  <si>
     <t>Gain 2 Commodities for each of your Leader's Level</t>
   </si>
   <si>
@@ -1420,9 +1402,6 @@
     <t>Each Player must have at least $L6 sponsored Laws in the Edicts or in the Queue or they will suffer sanctions on Tax</t>
   </si>
   <si>
-    <t>Provides Private Donate action with no penalty.</t>
-  </si>
-  <si>
     <t>Boasting Propaganda</t>
   </si>
   <si>
@@ -1435,9 +1414,6 @@
     <t>Buy with 2 Coins</t>
   </si>
   <si>
-    <t>Harvest 4 Commodities</t>
-  </si>
-  <si>
     <t>Monetize for 1 Coin</t>
   </si>
   <si>
@@ -1460,6 +1436,30 @@
   </si>
   <si>
     <t>Sue Crime Lord</t>
+  </si>
+  <si>
+    <t>Collect</t>
+  </si>
+  <si>
+    <t>Each Player must Collect at least $L6 Commodities this round or they will suffer sanctions on Recruit</t>
+  </si>
+  <si>
+    <t>No Player may Collect more than $L6 Commodities this round or they will suffer sanctions on Recruit</t>
+  </si>
+  <si>
+    <t>Each Player must have at least $L6 Troops or they will suffer sanctions on Collect</t>
+  </si>
+  <si>
+    <t>Collect $L6 additional Commodities during Collect</t>
+  </si>
+  <si>
+    <t>No Player may have more than $L6 Troops or they will suffer sanctions on Collect</t>
+  </si>
+  <si>
+    <t>Collect 4 Commodities</t>
+  </si>
+  <si>
+    <t>Provides Private Donate action with no penalty and convert $L3 additional Coins.</t>
   </si>
 </sst>
 </file>
@@ -2467,7 +2467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2747,6 +2747,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2781,33 +2787,45 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2820,7 +2838,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2833,18 +2851,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3690,10 +3696,6 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4015,23 +4017,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="39" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5390625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.18359375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="39.01171875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -4057,7 +4059,7 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
         <v>7</v>
       </c>
@@ -4077,21 +4079,21 @@
         <v>12</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>14</v>
@@ -4100,16 +4102,16 @@
         <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>16</v>
       </c>
@@ -4117,25 +4119,25 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="3"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>20</v>
       </c>
@@ -4149,19 +4151,19 @@
         <v>23</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -4178,16 +4180,16 @@
         <v>29</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>31</v>
       </c>
@@ -4204,16 +4206,16 @@
         <v>35</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
@@ -4221,30 +4223,30 @@
         <v>41</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>44</v>
@@ -4253,19 +4255,19 @@
         <v>39</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>40</v>
       </c>
@@ -4276,48 +4278,48 @@
         <v>49</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="2"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>47</v>
       </c>
@@ -4325,7 +4327,7 @@
         <v>57</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>50</v>
@@ -4337,13 +4339,13 @@
         <v>46</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="2"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>53</v>
       </c>
@@ -4363,13 +4365,13 @@
         <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
@@ -4389,13 +4391,13 @@
         <v>42</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>60</v>
       </c>
@@ -4403,7 +4405,7 @@
         <v>71</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>63</v>
@@ -4415,18 +4417,18 @@
         <v>65</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>66</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>76</v>
@@ -4435,19 +4437,19 @@
         <v>69</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="2"/>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>70</v>
       </c>
@@ -4464,16 +4466,16 @@
         <v>73</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="2"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>74</v>
       </c>
@@ -4487,137 +4489,137 @@
         <v>77</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>78</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>88</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>89</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>81</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>82</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>85</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>86</v>
+        <v>465</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>91</v>
+        <v>466</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="3"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7"/>
@@ -4625,21 +4627,21 @@
       <c r="I23" s="3"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>105</v>
+        <v>467</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="9"/>
@@ -4647,21 +4649,21 @@
       <c r="I24" s="3"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>113</v>
+        <v>468</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>108</v>
+        <v>469</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
@@ -4669,21 +4671,21 @@
       <c r="I25" s="3"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4691,21 +4693,21 @@
       <c r="I26" s="3"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4713,21 +4715,21 @@
       <c r="I27" s="3"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4735,21 +4737,21 @@
       <c r="I28" s="3"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4757,21 +4759,21 @@
       <c r="I29" s="3"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7"/>
@@ -4779,21 +4781,21 @@
       <c r="I30" s="3"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7"/>
@@ -4801,21 +4803,21 @@
       <c r="I31" s="3"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -4823,21 +4825,21 @@
       <c r="I32" s="3"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -4845,15 +4847,15 @@
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="16"/>
@@ -4863,15 +4865,15 @@
       <c r="I34" s="3"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="16"/>
@@ -4881,15 +4883,15 @@
       <c r="I35" s="3"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4899,15 +4901,15 @@
       <c r="I36" s="3"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -4917,15 +4919,15 @@
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -4935,15 +4937,15 @@
       <c r="I38" s="3"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -4953,15 +4955,15 @@
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="16"/>
@@ -4971,15 +4973,15 @@
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="16"/>
@@ -4989,9 +4991,9 @@
       <c r="I41" s="3"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="16"/>
@@ -5003,9 +5005,9 @@
       <c r="I42" s="3"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="16"/>
@@ -5017,9 +5019,9 @@
       <c r="I43" s="3"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="11" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="16"/>
@@ -5031,9 +5033,9 @@
       <c r="I44" s="3"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="11" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="16"/>
@@ -5045,9 +5047,9 @@
       <c r="I45" s="3"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="11" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="16"/>
@@ -5059,9 +5061,9 @@
       <c r="I46" s="3"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="16"/>
@@ -5073,9 +5075,9 @@
       <c r="I47" s="3"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="16"/>
@@ -5087,9 +5089,9 @@
       <c r="I48" s="3"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="11" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="16"/>
@@ -5101,9 +5103,9 @@
       <c r="I49" s="3"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="11" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="16"/>
@@ -5115,9 +5117,9 @@
       <c r="I50" s="3"/>
       <c r="J50" s="4"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B51" s="106"/>
       <c r="C51" s="107"/>
@@ -5129,9 +5131,9 @@
       <c r="I51" s="3"/>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="11" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B52" s="106"/>
       <c r="C52" s="107"/>
@@ -5143,9 +5145,9 @@
       <c r="I52" s="3"/>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B53" s="10"/>
       <c r="C53" s="17"/>
@@ -5166,364 +5168,364 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D195C1D-DB02-1743-BBD2-99104C1FFD33}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.71875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" customWidth="1"/>
+    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.55859375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.26171875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.7890625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.16796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.0859375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>157</v>
+      </c>
+      <c r="C1" s="53" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="54" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="G1" s="54" t="s">
+        <v>328</v>
+      </c>
+      <c r="H1" s="54" t="s">
         <v>162</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="I1" s="55" t="s">
         <v>163</v>
       </c>
-      <c r="D1" s="54" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="47" t="s">
+        <v>308</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="D2" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="E2" s="50" t="s">
         <v>166</v>
       </c>
-      <c r="G1" s="54" t="s">
-        <v>334</v>
-      </c>
-      <c r="H1" s="54" t="s">
+      <c r="F2" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="G2" s="50" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
-        <v>314</v>
-      </c>
-      <c r="B2" s="48" t="s">
-        <v>397</v>
-      </c>
-      <c r="C2" s="49" t="s">
+      <c r="H2" s="50" t="s">
         <v>169</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="I2" s="50" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="37" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>170</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="F3" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="G3" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="H3" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="I3" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="H2" s="50" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="81" x14ac:dyDescent="0.2">
+      <c r="A4" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="I2" s="50" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>335</v>
-      </c>
-      <c r="C3" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>317</v>
-      </c>
-      <c r="E3" s="42" t="s">
+      <c r="B4" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="C4" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="E4" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="H3" s="42" t="s">
+      <c r="F4" s="42" t="s">
+        <v>359</v>
+      </c>
+      <c r="G4" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="I4" s="45"/>
+    </row>
+    <row r="5" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="I3" s="42" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
-        <v>179</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" s="42" t="s">
+      <c r="C5" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="42" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E5" s="42" t="s">
         <v>182</v>
       </c>
-      <c r="F4" s="42" t="s">
-        <v>365</v>
-      </c>
-      <c r="G4" s="42" t="s">
+      <c r="F5" s="42" t="s">
         <v>183</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="G5" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="I5" s="45"/>
+    </row>
+    <row r="6" spans="1:9" ht="108" x14ac:dyDescent="0.2">
+      <c r="A6" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="I4" s="45"/>
-    </row>
-    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="B6" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="35" t="s">
-        <v>294</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="D5" s="42" t="s">
+      <c r="C6" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E6" s="42" t="s">
         <v>187</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F6" s="42" t="s">
         <v>188</v>
       </c>
-      <c r="G5" s="42" t="s">
-        <v>332</v>
-      </c>
-      <c r="H5" s="42" t="s">
-        <v>287</v>
-      </c>
-      <c r="I5" s="45"/>
-    </row>
-    <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="G6" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="H6" s="42" t="s">
+        <v>394</v>
+      </c>
+      <c r="I6" s="45"/>
+    </row>
+    <row r="7" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B7" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="D6" s="42" t="s">
+      <c r="C7" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>364</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>313</v>
+      </c>
+      <c r="G7" s="42" t="s">
         <v>191</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>192</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>193</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>333</v>
-      </c>
-      <c r="H6" s="42" t="s">
-        <v>400</v>
-      </c>
-      <c r="I6" s="45"/>
-    </row>
-    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>370</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>292</v>
-      </c>
-      <c r="F7" s="44" t="s">
-        <v>319</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>196</v>
       </c>
       <c r="H7" s="42"/>
       <c r="I7" s="45"/>
     </row>
-    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A8" s="37" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
       <c r="I8" s="45"/>
     </row>
-    <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="108" x14ac:dyDescent="0.2">
       <c r="A9" s="37" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D9" s="42" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E9" s="42" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G9" s="42"/>
       <c r="H9" s="42"/>
       <c r="I9" s="45"/>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A10" s="37" t="s">
-        <v>206</v>
+        <v>464</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D10" s="42" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
       <c r="I10" s="45"/>
     </row>
-    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A11" s="37" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D11" s="42"/>
       <c r="E11" s="42" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
       <c r="I11" s="45"/>
     </row>
-    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A12" s="37" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B12" s="35" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D12" s="42"/>
       <c r="E12" s="42" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="F12" s="44"/>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
       <c r="I12" s="45"/>
     </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A13" s="37" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D13" s="42"/>
       <c r="E13" s="42" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F13" s="44"/>
       <c r="G13" s="42"/>
       <c r="H13" s="42"/>
       <c r="I13" s="45"/>
     </row>
-    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A14" s="37" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D14" s="42"/>
       <c r="E14" s="42" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F14" s="44"/>
       <c r="G14" s="42"/>
       <c r="H14" s="42"/>
       <c r="I14" s="45"/>
     </row>
-    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A15" s="37" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D15" s="42"/>
       <c r="E15" s="42"/>
@@ -5532,15 +5534,15 @@
       <c r="H15" s="42"/>
       <c r="I15" s="45"/>
     </row>
-    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A16" s="37" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D16" s="42"/>
       <c r="E16" s="42"/>
@@ -5549,15 +5551,15 @@
       <c r="H16" s="42"/>
       <c r="I16" s="45"/>
     </row>
-    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A17" s="37" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="D17" s="42"/>
       <c r="E17" s="42"/>
@@ -5566,15 +5568,15 @@
       <c r="H17" s="42"/>
       <c r="I17" s="45"/>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A18" s="37" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B18" s="35" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D18" s="42"/>
       <c r="E18" s="42"/>
@@ -5583,15 +5585,15 @@
       <c r="H18" s="42"/>
       <c r="I18" s="45"/>
     </row>
-    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A19" s="37" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D19" s="42"/>
       <c r="E19" s="42"/>
@@ -5600,15 +5602,15 @@
       <c r="H19" s="42"/>
       <c r="I19" s="45"/>
     </row>
-    <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A20" s="37" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B20" s="35" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D20" s="42"/>
       <c r="E20" s="42"/>
@@ -5617,15 +5619,15 @@
       <c r="H20" s="42"/>
       <c r="I20" s="45"/>
     </row>
-    <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A21" s="37" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C21" s="38" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
@@ -5634,15 +5636,15 @@
       <c r="H21" s="42"/>
       <c r="I21" s="45"/>
     </row>
-    <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A22" s="37" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B22" s="35" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
@@ -5651,15 +5653,15 @@
       <c r="H22" s="42"/>
       <c r="I22" s="45"/>
     </row>
-    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A23" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="C23" s="38" t="s">
         <v>220</v>
-      </c>
-      <c r="B23" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>226</v>
       </c>
       <c r="D23" s="42"/>
       <c r="E23" s="42"/>
@@ -5668,15 +5670,15 @@
       <c r="H23" s="42"/>
       <c r="I23" s="45"/>
     </row>
-    <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="39" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D24" s="42"/>
       <c r="E24" s="42"/>
@@ -5685,15 +5687,15 @@
       <c r="H24" s="42"/>
       <c r="I24" s="45"/>
     </row>
-    <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="39" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D25" s="43"/>
       <c r="E25" s="43"/>
@@ -5711,42 +5713,42 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920DF489-FE6D-4819-BD1A-323DFAE597A3}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="30.66796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="67"/>
       <c r="B1" s="61" t="s">
+        <v>228</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1" s="60" t="s">
+        <v>230</v>
+      </c>
+      <c r="E1" s="110" t="s">
+        <v>231</v>
+      </c>
+      <c r="F1" s="109" t="s">
+        <v>232</v>
+      </c>
+      <c r="G1" s="61" t="s">
+        <v>233</v>
+      </c>
+      <c r="I1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="69" t="s">
         <v>234</v>
       </c>
-      <c r="C1" s="61" t="s">
-        <v>235</v>
-      </c>
-      <c r="D1" s="60" t="s">
-        <v>236</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>237</v>
-      </c>
-      <c r="F1" s="60" t="s">
-        <v>238</v>
-      </c>
-      <c r="G1" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="I1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="69" t="s">
-        <v>240</v>
-      </c>
       <c r="B2" s="70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C2" s="64" t="s">
         <v>67</v>
@@ -5757,45 +5759,45 @@
       <c r="E2" s="108" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="112" t="s">
-        <v>102</v>
+      <c r="F2" s="114" t="s">
+        <v>100</v>
       </c>
       <c r="G2" s="64" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="69" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B3" s="71" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D3" s="62" t="s">
-        <v>363</v>
-      </c>
-      <c r="E3" s="109" t="s">
-        <v>97</v>
+        <v>357</v>
+      </c>
+      <c r="E3" s="111" t="s">
+        <v>95</v>
       </c>
       <c r="F3" s="59" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G3" s="63" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="69" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B4" s="63" t="s">
         <v>61</v>
@@ -5804,27 +5806,27 @@
         <v>21</v>
       </c>
       <c r="D4" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="E4" s="109" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="111" t="s">
         <v>75</v>
       </c>
       <c r="F4" s="62" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G4" s="63" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I4" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="69" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="B5" s="68" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C5" s="68" t="s">
         <v>57</v>
@@ -5832,25 +5834,25 @@
       <c r="D5" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="110" t="s">
-        <v>374</v>
-      </c>
-      <c r="F5" s="113" t="s">
+      <c r="E5" s="112" t="s">
+        <v>368</v>
+      </c>
+      <c r="F5" s="115" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="111" t="s">
-        <v>384</v>
+      <c r="G5" s="113" t="s">
+        <v>378</v>
       </c>
       <c r="I5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="92" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B6" s="93" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C6" s="94" t="s">
         <v>34</v>
@@ -5859,208 +5861,208 @@
         <v>69</v>
       </c>
       <c r="E6" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="88" t="s">
         <v>58</v>
       </c>
       <c r="G6" s="97" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="72" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="72" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>316</v>
+      </c>
+      <c r="D7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" s="69" t="s">
+        <v>242</v>
+      </c>
+      <c r="F7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G7" s="69" t="s">
+        <v>163</v>
+      </c>
+      <c r="I7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="90" t="s">
+        <v>291</v>
+      </c>
+      <c r="B8" s="90" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="90" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="86" t="s">
+        <v>228</v>
+      </c>
+      <c r="F8" s="90" t="s">
+        <v>229</v>
+      </c>
+      <c r="G8" s="87" t="s">
+        <v>230</v>
+      </c>
+      <c r="I8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="59" t="s">
+        <v>292</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>232</v>
+      </c>
+      <c r="C9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>229</v>
+      </c>
+      <c r="E9" t="s">
+        <v>233</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>228</v>
+      </c>
+      <c r="G9" s="71" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="91" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" s="91" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="88" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" s="91" t="s">
+        <v>228</v>
+      </c>
+      <c r="E10" s="88" t="s">
+        <v>232</v>
+      </c>
+      <c r="F10" s="91" t="s">
+        <v>231</v>
+      </c>
+      <c r="G10" s="89" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="72" t="s">
-        <v>245</v>
-      </c>
-      <c r="B7" s="72" t="s">
-        <v>246</v>
-      </c>
-      <c r="C7" s="69" t="s">
-        <v>322</v>
-      </c>
-      <c r="D7" t="s">
-        <v>247</v>
-      </c>
-      <c r="E7" s="69" t="s">
-        <v>248</v>
-      </c>
-      <c r="F7" t="s">
-        <v>249</v>
-      </c>
-      <c r="G7" s="69" t="s">
-        <v>168</v>
-      </c>
-      <c r="I7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="90" t="s">
-        <v>297</v>
-      </c>
-      <c r="B8" s="90" t="s">
-        <v>237</v>
-      </c>
-      <c r="C8" s="86" t="s">
-        <v>238</v>
-      </c>
-      <c r="D8" s="90" t="s">
-        <v>239</v>
-      </c>
-      <c r="E8" s="86" t="s">
-        <v>234</v>
-      </c>
-      <c r="F8" s="90" t="s">
-        <v>235</v>
-      </c>
-      <c r="G8" s="87" t="s">
-        <v>236</v>
-      </c>
-      <c r="I8" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="59" t="s">
-        <v>298</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>238</v>
-      </c>
-      <c r="C9" t="s">
-        <v>236</v>
-      </c>
-      <c r="D9" s="59" t="s">
-        <v>235</v>
-      </c>
-      <c r="E9" t="s">
-        <v>239</v>
-      </c>
-      <c r="F9" s="59" t="s">
-        <v>234</v>
-      </c>
-      <c r="G9" s="71" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="91" t="s">
-        <v>299</v>
-      </c>
-      <c r="B10" s="91" t="s">
-        <v>236</v>
-      </c>
-      <c r="C10" s="88" t="s">
-        <v>239</v>
-      </c>
-      <c r="D10" s="91" t="s">
-        <v>234</v>
-      </c>
-      <c r="E10" s="88" t="s">
-        <v>238</v>
-      </c>
-      <c r="F10" s="91" t="s">
-        <v>237</v>
-      </c>
-      <c r="G10" s="89" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>302</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="E14" s="2" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>463</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -6069,105 +6071,105 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="I18" t="s">
         <v>419</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="I18" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>206</v>
+        <v>464</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I19" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E20" t="s">
-        <v>206</v>
+        <v>464</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D21" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
       <c r="B22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
       <c r="B23" s="2"/>
       <c r="D23" s="2"/>
@@ -6175,98 +6177,98 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I24" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="I25" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E26" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="I26" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="G27" s="2"/>
       <c r="I27" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -6275,10 +6277,10 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="I28" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -6287,10 +6289,10 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="I29" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -6299,7 +6301,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -6307,7 +6309,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -6315,7 +6317,7 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -6323,7 +6325,7 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -6331,7 +6333,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -6339,7 +6341,7 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -6347,7 +6349,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -6355,7 +6357,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -6363,7 +6365,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -6371,7 +6373,7 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -6379,7 +6381,7 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -6387,7 +6389,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -6395,7 +6397,7 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -6403,7 +6405,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -6411,7 +6413,7 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="3"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -6419,7 +6421,7 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -6436,75 +6438,75 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="36" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="37.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="4" width="30.7109375" style="26" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="26"/>
+    <col min="1" max="4" width="30.66796875" style="26" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.14453125" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="32" t="s">
-        <v>206</v>
+        <v>464</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>314</v>
-      </c>
-      <c r="E1" s="114" t="s">
-        <v>169</v>
+        <v>308</v>
+      </c>
+      <c r="E1" s="116" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="31" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C2" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="D2" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="E2" s="115"/>
+      <c r="E2" s="117"/>
     </row>
     <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3" s="30" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E3" s="115"/>
+        <v>203</v>
+      </c>
+      <c r="E3" s="117"/>
     </row>
     <row r="4" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A4" s="34" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="57" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="C4" s="57" t="s">
-        <v>222</v>
-      </c>
       <c r="D4" s="34" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E4" s="58" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -6523,54 +6525,54 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="30.66796875" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="E1" s="116" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+      <c r="E1" s="118" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="B2" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>222</v>
-      </c>
       <c r="D2" s="104" t="s">
-        <v>379</v>
-      </c>
-      <c r="E2" s="117"/>
-    </row>
-    <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>373</v>
+      </c>
+      <c r="E2" s="119"/>
+    </row>
+    <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="105" t="s">
-        <v>250</v>
-      </c>
-      <c r="B3" s="118" t="s">
-        <v>251</v>
-      </c>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="120"/>
+        <v>244</v>
+      </c>
+      <c r="B3" s="120" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6586,196 +6588,216 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{435A2588-0653-4FD0-85C3-EF9530FC726F}">
   <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="14" width="7.7109375" customWidth="1"/>
-    <col min="15" max="15" width="17.85546875" customWidth="1"/>
+    <col min="1" max="14" width="7.6640625" customWidth="1"/>
+    <col min="15" max="15" width="17.890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="139">
-        <v>0</v>
-      </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="139">
+    <row r="1" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="123">
+        <v>0</v>
+      </c>
+      <c r="B1" s="124"/>
+      <c r="C1" s="123">
         <v>1</v>
       </c>
-      <c r="D1" s="140"/>
-      <c r="E1" s="139">
+      <c r="D1" s="124"/>
+      <c r="E1" s="123">
         <v>2</v>
       </c>
-      <c r="F1" s="140"/>
-      <c r="G1" s="139">
+      <c r="F1" s="124"/>
+      <c r="G1" s="123">
         <v>3</v>
       </c>
-      <c r="H1" s="140"/>
-      <c r="I1" s="139">
+      <c r="H1" s="124"/>
+      <c r="I1" s="123">
         <v>4</v>
       </c>
-      <c r="J1" s="140"/>
-      <c r="K1" s="139">
+      <c r="J1" s="124"/>
+      <c r="K1" s="123">
         <v>5</v>
       </c>
-      <c r="L1" s="140"/>
-      <c r="M1" s="139">
+      <c r="L1" s="124"/>
+      <c r="M1" s="123">
         <v>6</v>
       </c>
-      <c r="N1" s="140"/>
-    </row>
-    <row r="2" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="141">
+      <c r="N1" s="124"/>
+    </row>
+    <row r="2" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="125">
         <v>19</v>
       </c>
-      <c r="B2" s="130" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="132"/>
-      <c r="N2" s="141">
+      <c r="B2" s="136" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="137"/>
+      <c r="H2" s="137"/>
+      <c r="I2" s="137"/>
+      <c r="J2" s="137"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="137"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="125">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="142"/>
-      <c r="B3" s="133"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="134"/>
-      <c r="M3" s="135"/>
-      <c r="N3" s="142"/>
-    </row>
-    <row r="4" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="141">
+    <row r="3" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="126"/>
+      <c r="B3" s="139"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="140"/>
+      <c r="H3" s="140"/>
+      <c r="I3" s="140"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="141"/>
+      <c r="N3" s="126"/>
+    </row>
+    <row r="4" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="125">
         <v>18</v>
       </c>
-      <c r="B4" s="136"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137"/>
-      <c r="M4" s="138"/>
-      <c r="N4" s="141">
+      <c r="B4" s="142"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="143"/>
+      <c r="M4" s="144"/>
+      <c r="N4" s="125">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="142"/>
-      <c r="B5" s="123" t="s">
-        <v>253</v>
+    <row r="5" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="126"/>
+      <c r="B5" s="127" t="s">
+        <v>247</v>
       </c>
       <c r="C5" s="128"/>
-      <c r="D5" s="121" t="s">
-        <v>253</v>
-      </c>
-      <c r="E5" s="122"/>
-      <c r="F5" s="121" t="s">
-        <v>253</v>
-      </c>
-      <c r="G5" s="122"/>
-      <c r="H5" s="121" t="s">
-        <v>253</v>
-      </c>
-      <c r="I5" s="122"/>
-      <c r="J5" s="121" t="s">
-        <v>253</v>
-      </c>
-      <c r="K5" s="122"/>
-      <c r="L5" s="121" t="s">
-        <v>253</v>
-      </c>
-      <c r="M5" s="127"/>
-      <c r="N5" s="142"/>
-    </row>
-    <row r="6" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="141">
+      <c r="D5" s="131" t="s">
+        <v>247</v>
+      </c>
+      <c r="E5" s="132"/>
+      <c r="F5" s="131" t="s">
+        <v>247</v>
+      </c>
+      <c r="G5" s="132"/>
+      <c r="H5" s="131" t="s">
+        <v>247</v>
+      </c>
+      <c r="I5" s="132"/>
+      <c r="J5" s="131" t="s">
+        <v>247</v>
+      </c>
+      <c r="K5" s="132"/>
+      <c r="L5" s="131" t="s">
+        <v>247</v>
+      </c>
+      <c r="M5" s="135"/>
+      <c r="N5" s="126"/>
+    </row>
+    <row r="6" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="125">
         <v>17</v>
       </c>
-      <c r="B6" s="123"/>
+      <c r="B6" s="127"/>
       <c r="C6" s="128"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="123"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="123"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="124"/>
-      <c r="L6" s="123"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="127"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="127"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="127"/>
       <c r="M6" s="128"/>
-      <c r="N6" s="141">
+      <c r="N6" s="125">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="142"/>
-      <c r="B7" s="125"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="126"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="126"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="126"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="126"/>
-      <c r="L7" s="125"/>
-      <c r="M7" s="129"/>
-      <c r="N7" s="142"/>
-    </row>
-    <row r="8" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="139">
+    <row r="7" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="126"/>
+      <c r="B7" s="129"/>
+      <c r="C7" s="130"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="134"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="134"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="134"/>
+      <c r="J7" s="129"/>
+      <c r="K7" s="134"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="126"/>
+    </row>
+    <row r="8" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="123">
         <v>16</v>
       </c>
-      <c r="B8" s="140"/>
-      <c r="C8" s="139">
+      <c r="B8" s="124"/>
+      <c r="C8" s="123">
         <v>15</v>
       </c>
-      <c r="D8" s="140"/>
-      <c r="E8" s="139">
+      <c r="D8" s="124"/>
+      <c r="E8" s="123">
         <v>14</v>
       </c>
-      <c r="F8" s="140"/>
-      <c r="G8" s="139">
+      <c r="F8" s="124"/>
+      <c r="G8" s="123">
         <v>13</v>
       </c>
-      <c r="H8" s="140"/>
-      <c r="I8" s="139">
+      <c r="H8" s="124"/>
+      <c r="I8" s="123">
         <v>12</v>
       </c>
-      <c r="J8" s="140"/>
-      <c r="K8" s="139">
+      <c r="J8" s="124"/>
+      <c r="K8" s="123">
         <v>11</v>
       </c>
-      <c r="L8" s="140"/>
-      <c r="M8" s="139">
+      <c r="L8" s="124"/>
+      <c r="M8" s="123">
         <v>10</v>
       </c>
-      <c r="N8" s="140"/>
+      <c r="N8" s="124"/>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="F5:G7"/>
+    <mergeCell ref="H5:I7"/>
+    <mergeCell ref="J5:K7"/>
+    <mergeCell ref="L5:M7"/>
+    <mergeCell ref="B2:M4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A6:A7"/>
@@ -6783,26 +6805,6 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B5:C7"/>
     <mergeCell ref="D5:E7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="F5:G7"/>
-    <mergeCell ref="H5:I7"/>
-    <mergeCell ref="J5:K7"/>
-    <mergeCell ref="L5:M7"/>
-    <mergeCell ref="B2:M4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -6812,66 +6814,66 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CEB427C-0CB4-4E8D-8367-36F6DD891282}">
   <dimension ref="A1:CA6"/>
-  <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.7734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" style="59"/>
-    <col min="2" max="2" width="19.7109375" style="71"/>
-    <col min="4" max="4" width="19.7109375" style="59"/>
-    <col min="6" max="6" width="19.7109375" style="59"/>
-    <col min="8" max="8" width="19.7109375" style="59"/>
-    <col min="10" max="10" width="19.7109375" style="59"/>
-    <col min="12" max="12" width="19.7109375" style="59"/>
-    <col min="14" max="14" width="19.7109375" style="59"/>
-    <col min="16" max="16" width="19.7109375" style="59"/>
-    <col min="18" max="18" width="19.7109375" style="59"/>
-    <col min="20" max="20" width="19.7109375" style="59"/>
-    <col min="22" max="22" width="19.7109375" style="59"/>
-    <col min="24" max="24" width="19.7109375" style="59"/>
-    <col min="26" max="26" width="19.7109375" style="59"/>
-    <col min="28" max="28" width="19.7109375" style="59"/>
-    <col min="30" max="30" width="19.7109375" style="77"/>
-    <col min="31" max="32" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.7109375" customWidth="1"/>
-    <col min="42" max="42" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.7109375" style="77" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="19.7109375" style="59" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="19.7109375" style="77" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="19.7109375" style="59"/>
-    <col min="63" max="63" width="19.7109375" style="59"/>
-    <col min="65" max="65" width="19.7109375" style="59"/>
-    <col min="67" max="67" width="19.7109375" style="59"/>
-    <col min="69" max="70" width="19.7109375" style="59"/>
-    <col min="71" max="71" width="19.7109375" style="71"/>
-    <col min="73" max="73" width="19.7109375" style="59"/>
-    <col min="75" max="75" width="19.7109375" style="59"/>
-    <col min="77" max="77" width="19.7109375" style="59"/>
-    <col min="79" max="79" width="19.7109375" style="59"/>
+    <col min="1" max="1" width="19.7734375" style="59"/>
+    <col min="2" max="2" width="19.7734375" style="71"/>
+    <col min="4" max="4" width="19.7734375" style="59"/>
+    <col min="6" max="6" width="19.7734375" style="59"/>
+    <col min="8" max="8" width="19.7734375" style="59"/>
+    <col min="10" max="10" width="19.7734375" style="59"/>
+    <col min="12" max="12" width="19.7734375" style="59"/>
+    <col min="14" max="14" width="19.7734375" style="59"/>
+    <col min="16" max="16" width="19.7734375" style="59"/>
+    <col min="18" max="18" width="19.7734375" style="59"/>
+    <col min="20" max="20" width="19.7734375" style="59"/>
+    <col min="22" max="22" width="19.7734375" style="59"/>
+    <col min="24" max="24" width="19.7734375" style="59"/>
+    <col min="26" max="26" width="19.7734375" style="59"/>
+    <col min="28" max="28" width="19.7734375" style="59"/>
+    <col min="30" max="30" width="19.7734375" style="77"/>
+    <col min="31" max="32" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.7734375" customWidth="1"/>
+    <col min="42" max="42" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.7734375" style="77" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19.7734375" style="77" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="19.7734375" style="59"/>
+    <col min="63" max="63" width="19.7734375" style="59"/>
+    <col min="65" max="65" width="19.7734375" style="59"/>
+    <col min="67" max="67" width="19.7734375" style="59"/>
+    <col min="69" max="70" width="19.7734375" style="59"/>
+    <col min="71" max="71" width="19.7734375" style="71"/>
+    <col min="73" max="73" width="19.7734375" style="59"/>
+    <col min="75" max="75" width="19.7734375" style="59"/>
+    <col min="77" max="77" width="19.7734375" style="59"/>
+    <col min="79" max="79" width="19.7734375" style="59"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" s="75" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:79" s="75" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="73" t="str">
         <f>Cards!B2</f>
         <v>Fillibuster</v>
@@ -7158,7 +7160,7 @@
       <c r="BY1" s="73"/>
       <c r="CA1" s="73"/>
     </row>
-    <row r="2" spans="1:79" s="98" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:79" s="98" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="99" t="str">
         <f>Cards!C2</f>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
@@ -7261,7 +7263,7 @@
       </c>
       <c r="Z2" s="99" t="str">
         <f>Cards!C25</f>
-        <v>Collect $L6 additional Commodities during Harvests</v>
+        <v>Collect $L6 additional Commodities during Collect</v>
       </c>
       <c r="AA2" s="98" t="str">
         <f>Cards!C26</f>
@@ -7305,7 +7307,7 @@
       </c>
       <c r="AK2" s="98" t="str">
         <f>Cards!C36</f>
-        <v>Provides Private Donate action with no penalty.</v>
+        <v>Provides Private Donate action with no penalty and convert $L3 additional Coins.</v>
       </c>
       <c r="AL2" s="99" t="str">
         <f>Cards!C37</f>
@@ -7421,7 +7423,7 @@
       </c>
       <c r="BN2" s="98" t="str">
         <f t="shared" si="2"/>
-        <v>Collect $L6 additional Commodities during Harvests</v>
+        <v>Collect $L6 additional Commodities during Collect</v>
       </c>
       <c r="BO2" s="99" t="str">
         <f t="shared" si="2"/>
@@ -7445,7 +7447,7 @@
       <c r="BY2" s="99"/>
       <c r="CA2" s="99"/>
     </row>
-    <row r="3" spans="1:79" s="75" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:79" s="75" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="73" t="str">
         <f>Cards!D2</f>
         <v>Full Coffers</v>
@@ -7704,23 +7706,23 @@
       </c>
       <c r="BM3" s="73"/>
       <c r="BN3" s="75" t="str">
-        <f t="shared" ref="BN3:BR4" si="4">AJ1</f>
+        <f>AJ1</f>
         <v>Kingdom Advocates</v>
       </c>
       <c r="BO3" s="73" t="str">
-        <f t="shared" si="4"/>
+        <f>AK1</f>
         <v>Soup Kitchens</v>
       </c>
       <c r="BP3" s="75" t="str">
-        <f t="shared" si="4"/>
+        <f>AL1</f>
         <v>Abusive Power</v>
       </c>
       <c r="BQ3" s="73" t="str">
-        <f t="shared" si="4"/>
+        <f>AM1</f>
         <v>Painful Progress</v>
       </c>
       <c r="BR3" s="73" t="str">
-        <f t="shared" si="4"/>
+        <f>AN1</f>
         <v>Iron Command</v>
       </c>
       <c r="BS3" s="74"/>
@@ -7729,7 +7731,7 @@
       <c r="BY3" s="73"/>
       <c r="CA3" s="73"/>
     </row>
-    <row r="4" spans="1:79" s="80" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:79" s="80" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="78" t="str">
         <f>Cards!E2</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
@@ -7804,11 +7806,11 @@
       </c>
       <c r="S4" s="80" t="str">
         <f>Cards!E20</f>
-        <v>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+        <v>Each Player must Collect at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
       <c r="T4" s="78" t="str">
         <f>Cards!E21</f>
-        <v>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+        <v>No Player may Collect more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
       <c r="U4" s="80" t="str">
         <f>Cards!E22</f>
@@ -7820,11 +7822,11 @@
       </c>
       <c r="W4" s="80" t="str">
         <f>Cards!E24</f>
-        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</v>
+        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Collect</v>
       </c>
       <c r="X4" s="78" t="str">
         <f>Cards!E25</f>
-        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</v>
+        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Collect</v>
       </c>
       <c r="Y4" s="80" t="str">
         <f>Cards!E26</f>
@@ -7859,152 +7861,152 @@
         <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
       </c>
       <c r="AG4" s="80" t="str">
-        <f t="shared" ref="AG4:BL4" si="5">A4</f>
+        <f t="shared" ref="AG4:BL4" si="4">A4</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
       <c r="AH4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
       <c r="AI4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
       <c r="AJ4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
       <c r="AK4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
       </c>
       <c r="AL4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
       </c>
       <c r="AM4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
       <c r="AN4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
       <c r="AO4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy</v>
       </c>
       <c r="AP4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy</v>
       </c>
       <c r="AQ4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
       </c>
       <c r="AR4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
       </c>
       <c r="AS4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
       </c>
       <c r="AT4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
       </c>
       <c r="AU4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Each Player must have at least $L6 sponsored Laws in the Edicts or in the Queue or they will suffer sanctions on Tax</v>
       </c>
       <c r="AV4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
       </c>
       <c r="AW4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
       </c>
       <c r="AX4" s="81" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
       </c>
       <c r="AY4" s="78" t="str">
-        <f t="shared" si="5"/>
-        <v>Each Player must Harvest at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+        <f t="shared" si="4"/>
+        <v>Each Player must Collect at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
       <c r="AZ4" s="80" t="str">
-        <f t="shared" si="5"/>
-        <v>No Player may Harvest more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+        <f t="shared" si="4"/>
+        <v>No Player may Collect more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
       <c r="BA4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
       <c r="BB4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
       <c r="BC4" s="78" t="str">
-        <f t="shared" si="5"/>
-        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Harvest</v>
+        <f t="shared" si="4"/>
+        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Collect</v>
       </c>
       <c r="BD4" s="80" t="str">
-        <f t="shared" si="5"/>
-        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Harvest</v>
+        <f t="shared" si="4"/>
+        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Collect</v>
       </c>
       <c r="BE4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
       <c r="BF4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
       <c r="BG4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
       <c r="BH4" s="81" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
       <c r="BI4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
       </c>
       <c r="BJ4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
       </c>
       <c r="BK4" s="78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
       </c>
       <c r="BL4" s="80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
       </c>
       <c r="BM4" s="78"/>
       <c r="BN4" s="98" t="str">
-        <f t="shared" si="4"/>
+        <f>AJ2</f>
         <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
       </c>
       <c r="BO4" s="99" t="str">
-        <f t="shared" si="4"/>
-        <v>Provides Private Donate action with no penalty.</v>
+        <f>AK2</f>
+        <v>Provides Private Donate action with no penalty and convert $L3 additional Coins.</v>
       </c>
       <c r="BP4" s="98" t="str">
-        <f t="shared" si="4"/>
+        <f>AL2</f>
         <v>Convert $L3 additional Coins during Undermarket Donate</v>
       </c>
       <c r="BQ4" s="99" t="str">
-        <f t="shared" si="4"/>
+        <f>AM2</f>
         <v>You may repeat Undermarket Actions at double the penalty</v>
       </c>
       <c r="BR4" s="78" t="str">
-        <f t="shared" si="4"/>
+        <f>AN2</f>
         <v>Deploy $L3 additional Troops during Deploy</v>
       </c>
       <c r="BS4" s="79"/>
@@ -8013,7 +8015,7 @@
       <c r="BY4" s="78"/>
       <c r="CA4" s="78"/>
     </row>
-    <row r="5" spans="1:79" s="84" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:79" s="84" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="82" t="str">
         <f>Cards!F2</f>
         <v>Fickle Mercenaries</v>
@@ -8099,191 +8101,191 @@
         <v>Blackmail</v>
       </c>
       <c r="V5" s="82" t="str">
-        <f t="shared" ref="V5:AE6" si="6">A5</f>
+        <f t="shared" ref="V5:AE6" si="5">A5</f>
         <v>Fickle Mercenaries</v>
       </c>
       <c r="W5" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>Blatant Extortion</v>
+      </c>
+      <c r="X5" s="82" t="str">
+        <f t="shared" si="5"/>
+        <v>Double Agents</v>
+      </c>
+      <c r="Y5" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>Questionable Reallocation</v>
+      </c>
+      <c r="Z5" s="82" t="str">
+        <f t="shared" si="5"/>
+        <v>Corporate Espionage</v>
+      </c>
+      <c r="AA5" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>Localized Famine</v>
+      </c>
+      <c r="AB5" s="82" t="str">
+        <f t="shared" si="5"/>
+        <v>Highway Robbery</v>
+      </c>
+      <c r="AC5" s="84" t="str">
+        <f t="shared" si="5"/>
+        <v>Camp Plague</v>
+      </c>
+      <c r="AD5" s="85" t="str">
+        <f t="shared" si="5"/>
+        <v>Weakening Grip</v>
+      </c>
+      <c r="AE5" s="82" t="str">
+        <f t="shared" si="5"/>
+        <v>Culture Shift</v>
+      </c>
+      <c r="AF5" s="82" t="str">
+        <f t="shared" ref="AF5:AO6" si="6">K5</f>
+        <v>Corporate Takeover</v>
+      </c>
+      <c r="AG5" s="84" t="str">
         <f t="shared" si="6"/>
+        <v>Sabotage</v>
+      </c>
+      <c r="AH5" s="82" t="str">
+        <f t="shared" si="6"/>
+        <v>Dangerous Monopolies</v>
+      </c>
+      <c r="AI5" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>Betrayal</v>
+      </c>
+      <c r="AJ5" s="82" t="str">
+        <f t="shared" si="6"/>
+        <v>Assassination Attempt</v>
+      </c>
+      <c r="AK5" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>Humiliation</v>
+      </c>
+      <c r="AL5" s="82" t="str">
+        <f t="shared" si="6"/>
+        <v>Invalid Paperwork</v>
+      </c>
+      <c r="AM5" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>Rallied Opposition</v>
+      </c>
+      <c r="AN5" s="82" t="str">
+        <f t="shared" si="6"/>
+        <v>Waning Support</v>
+      </c>
+      <c r="AO5" s="84" t="str">
+        <f t="shared" si="6"/>
+        <v>Misaligned Strategy</v>
+      </c>
+      <c r="AP5" s="82" t="str">
+        <f t="shared" ref="AP5:AY6" si="7">U5</f>
+        <v>Blackmail</v>
+      </c>
+      <c r="AQ5" s="84" t="str">
+        <f t="shared" ref="AQ5:AZ6" si="8">A5</f>
+        <v>Fickle Mercenaries</v>
+      </c>
+      <c r="AR5" s="82" t="str">
+        <f t="shared" si="8"/>
         <v>Blatant Extortion</v>
       </c>
-      <c r="X5" s="82" t="str">
-        <f t="shared" si="6"/>
+      <c r="AS5" s="84" t="str">
+        <f t="shared" si="8"/>
         <v>Double Agents</v>
       </c>
-      <c r="Y5" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="AT5" s="82" t="str">
+        <f t="shared" si="8"/>
         <v>Questionable Reallocation</v>
       </c>
-      <c r="Z5" s="82" t="str">
-        <f t="shared" si="6"/>
+      <c r="AU5" s="84" t="str">
+        <f t="shared" si="8"/>
         <v>Corporate Espionage</v>
       </c>
-      <c r="AA5" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="AV5" s="82" t="str">
+        <f t="shared" si="8"/>
         <v>Localized Famine</v>
       </c>
-      <c r="AB5" s="82" t="str">
-        <f t="shared" si="6"/>
+      <c r="AW5" s="84" t="str">
+        <f t="shared" si="8"/>
         <v>Highway Robbery</v>
       </c>
-      <c r="AC5" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="AX5" s="85" t="str">
+        <f t="shared" si="8"/>
         <v>Camp Plague</v>
       </c>
-      <c r="AD5" s="85" t="str">
-        <f t="shared" si="6"/>
+      <c r="AY5" s="82" t="str">
+        <f t="shared" si="8"/>
         <v>Weakening Grip</v>
       </c>
-      <c r="AE5" s="82" t="str">
-        <f t="shared" si="6"/>
+      <c r="AZ5" s="84" t="str">
+        <f t="shared" si="8"/>
         <v>Culture Shift</v>
       </c>
-      <c r="AF5" s="82" t="str">
-        <f t="shared" ref="AF5:AO6" si="7">K5</f>
+      <c r="BA5" s="82" t="str">
+        <f t="shared" ref="BA5:BJ6" si="9">K5</f>
         <v>Corporate Takeover</v>
       </c>
-      <c r="AG5" s="84" t="str">
-        <f t="shared" si="7"/>
+      <c r="BB5" s="84" t="str">
+        <f t="shared" si="9"/>
         <v>Sabotage</v>
       </c>
-      <c r="AH5" s="82" t="str">
-        <f t="shared" si="7"/>
+      <c r="BC5" s="82" t="str">
+        <f t="shared" si="9"/>
         <v>Dangerous Monopolies</v>
       </c>
-      <c r="AI5" s="84" t="str">
-        <f t="shared" si="7"/>
+      <c r="BD5" s="84" t="str">
+        <f t="shared" si="9"/>
         <v>Betrayal</v>
       </c>
-      <c r="AJ5" s="82" t="str">
-        <f t="shared" si="7"/>
+      <c r="BE5" s="82" t="str">
+        <f t="shared" si="9"/>
         <v>Assassination Attempt</v>
       </c>
-      <c r="AK5" s="84" t="str">
-        <f t="shared" si="7"/>
+      <c r="BF5" s="84" t="str">
+        <f t="shared" si="9"/>
         <v>Humiliation</v>
       </c>
-      <c r="AL5" s="82" t="str">
-        <f t="shared" si="7"/>
+      <c r="BG5" s="82" t="str">
+        <f t="shared" si="9"/>
         <v>Invalid Paperwork</v>
       </c>
-      <c r="AM5" s="84" t="str">
-        <f t="shared" si="7"/>
+      <c r="BH5" s="82" t="str">
+        <f t="shared" si="9"/>
         <v>Rallied Opposition</v>
       </c>
-      <c r="AN5" s="82" t="str">
-        <f t="shared" si="7"/>
+      <c r="BI5" s="82" t="str">
+        <f t="shared" si="9"/>
         <v>Waning Support</v>
       </c>
-      <c r="AO5" s="84" t="str">
-        <f t="shared" si="7"/>
+      <c r="BJ5" s="84" t="str">
+        <f t="shared" si="9"/>
         <v>Misaligned Strategy</v>
       </c>
-      <c r="AP5" s="82" t="str">
-        <f t="shared" ref="AP5:AP6" si="8">U5</f>
+      <c r="BK5" s="82" t="str">
+        <f t="shared" ref="BK5:BT6" si="10">U5</f>
         <v>Blackmail</v>
       </c>
-      <c r="AQ5" s="84" t="str">
-        <f t="shared" ref="AQ5:AZ6" si="9">A5</f>
-        <v>Fickle Mercenaries</v>
-      </c>
-      <c r="AR5" s="82" t="str">
-        <f t="shared" si="9"/>
-        <v>Blatant Extortion</v>
-      </c>
-      <c r="AS5" s="84" t="str">
-        <f t="shared" si="9"/>
-        <v>Double Agents</v>
-      </c>
-      <c r="AT5" s="82" t="str">
-        <f t="shared" si="9"/>
-        <v>Questionable Reallocation</v>
-      </c>
-      <c r="AU5" s="84" t="str">
-        <f t="shared" si="9"/>
-        <v>Corporate Espionage</v>
-      </c>
-      <c r="AV5" s="82" t="str">
-        <f t="shared" si="9"/>
-        <v>Localized Famine</v>
-      </c>
-      <c r="AW5" s="84" t="str">
-        <f t="shared" si="9"/>
-        <v>Highway Robbery</v>
-      </c>
-      <c r="AX5" s="85" t="str">
-        <f t="shared" si="9"/>
-        <v>Camp Plague</v>
-      </c>
-      <c r="AY5" s="82" t="str">
-        <f t="shared" si="9"/>
-        <v>Weakening Grip</v>
-      </c>
-      <c r="AZ5" s="84" t="str">
-        <f t="shared" si="9"/>
-        <v>Culture Shift</v>
-      </c>
-      <c r="BA5" s="82" t="str">
-        <f t="shared" ref="BA5:BJ6" si="10">K5</f>
-        <v>Corporate Takeover</v>
-      </c>
-      <c r="BB5" s="84" t="str">
-        <f t="shared" si="10"/>
-        <v>Sabotage</v>
-      </c>
-      <c r="BC5" s="82" t="str">
-        <f t="shared" si="10"/>
-        <v>Dangerous Monopolies</v>
-      </c>
-      <c r="BD5" s="84" t="str">
-        <f t="shared" si="10"/>
-        <v>Betrayal</v>
-      </c>
-      <c r="BE5" s="82" t="str">
-        <f t="shared" si="10"/>
-        <v>Assassination Attempt</v>
-      </c>
-      <c r="BF5" s="84" t="str">
-        <f t="shared" si="10"/>
-        <v>Humiliation</v>
-      </c>
-      <c r="BG5" s="82" t="str">
-        <f t="shared" si="10"/>
-        <v>Invalid Paperwork</v>
-      </c>
-      <c r="BH5" s="82" t="str">
-        <f t="shared" si="10"/>
-        <v>Rallied Opposition</v>
-      </c>
-      <c r="BI5" s="82" t="str">
-        <f t="shared" si="10"/>
-        <v>Waning Support</v>
-      </c>
-      <c r="BJ5" s="84" t="str">
-        <f t="shared" si="10"/>
-        <v>Misaligned Strategy</v>
-      </c>
-      <c r="BK5" s="82" t="str">
-        <f t="shared" ref="BK5:BK6" si="11">U5</f>
-        <v>Blackmail</v>
-      </c>
       <c r="BM5" s="73" t="str">
-        <f t="shared" ref="BM5:BQ6" si="12">AE1</f>
+        <f>AE1</f>
         <v>Codependent Relationship</v>
       </c>
       <c r="BN5" s="75" t="str">
-        <f t="shared" si="12"/>
+        <f>AF1</f>
         <v>Dangerous Promises</v>
       </c>
       <c r="BO5" s="73" t="str">
-        <f t="shared" si="12"/>
+        <f>AG1</f>
         <v>Large Middle Class</v>
       </c>
       <c r="BP5" s="75" t="str">
-        <f t="shared" si="12"/>
+        <f>AH1</f>
         <v>Innovation Hub</v>
       </c>
       <c r="BQ5" s="73" t="str">
-        <f t="shared" si="12"/>
+        <f>AI1</f>
         <v>Fire Temple</v>
       </c>
       <c r="BR5" s="82"/>
@@ -8293,7 +8295,7 @@
       <c r="BY5" s="82"/>
       <c r="CA5" s="82"/>
     </row>
-    <row r="6" spans="1:79" s="80" customFormat="1" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:79" s="80" customFormat="1" ht="81.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="78" t="str">
         <f>Cards!G2</f>
         <v>Give $2D6 Troops to $R</v>
@@ -8379,191 +8381,191 @@
         <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
       </c>
       <c r="V6" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>Give $2D6 Troops to $R</v>
+      </c>
+      <c r="W6" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
+      </c>
+      <c r="X6" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>Give $D6 Spies to $R</v>
+      </c>
+      <c r="Y6" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Give $2D6 Commodities to $R</v>
+      </c>
+      <c r="Z6" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>Give $D6 random Cards of each type from your hand to $R</v>
+      </c>
+      <c r="AA6" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Lose half your Commodities</v>
+      </c>
+      <c r="AB6" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>Lose half your Coins</v>
+      </c>
+      <c r="AC6" s="80" t="str">
+        <f t="shared" si="5"/>
+        <v>Lose half your Troops</v>
+      </c>
+      <c r="AD6" s="81" t="str">
+        <f t="shared" si="5"/>
+        <v>Lose half your Spies</v>
+      </c>
+      <c r="AE6" s="78" t="str">
+        <f t="shared" si="5"/>
+        <v>Disard half your cards of each type</v>
+      </c>
+      <c r="AF6" s="78" t="str">
         <f t="shared" si="6"/>
+        <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
+      </c>
+      <c r="AG6" s="80" t="str">
+        <f t="shared" si="6"/>
+        <v>Downgrade an Investment by $D6 levels</v>
+      </c>
+      <c r="AH6" s="78" t="str">
+        <f t="shared" si="6"/>
+        <v>Downgrade an Investment by $D6 levels</v>
+      </c>
+      <c r="AI6" s="80" t="str">
+        <f t="shared" si="6"/>
+        <v>Demote a Leader at level $D6 by half and send it to $R</v>
+      </c>
+      <c r="AJ6" s="78" t="str">
+        <f t="shared" si="6"/>
+        <v>Demote a Leader by $D6 levels</v>
+      </c>
+      <c r="AK6" s="80" t="str">
+        <f t="shared" si="6"/>
+        <v>Demote a Leader by $D6 levels</v>
+      </c>
+      <c r="AL6" s="78" t="str">
+        <f t="shared" si="6"/>
+        <v>Move your foremost Law to the back of the Queue</v>
+      </c>
+      <c r="AM6" s="80" t="str">
+        <f t="shared" si="6"/>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
+      </c>
+      <c r="AN6" s="78" t="str">
+        <f t="shared" si="6"/>
+        <v>Move $D6 of your Laws each one space back in the Queue</v>
+      </c>
+      <c r="AO6" s="80" t="str">
+        <f t="shared" si="6"/>
+        <v>Move your foremost Law $D6 spaces back in the Queue</v>
+      </c>
+      <c r="AP6" s="78" t="str">
+        <f t="shared" si="7"/>
+        <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
+      </c>
+      <c r="AQ6" s="80" t="str">
+        <f t="shared" si="8"/>
         <v>Give $2D6 Troops to $R</v>
       </c>
-      <c r="W6" s="80" t="str">
-        <f t="shared" si="6"/>
+      <c r="AR6" s="78" t="str">
+        <f t="shared" si="8"/>
         <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="X6" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="AS6" s="80" t="str">
+        <f t="shared" si="8"/>
         <v>Give $D6 Spies to $R</v>
       </c>
-      <c r="Y6" s="80" t="str">
-        <f t="shared" si="6"/>
+      <c r="AT6" s="78" t="str">
+        <f t="shared" si="8"/>
         <v>Give $2D6 Commodities to $R</v>
       </c>
-      <c r="Z6" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="AU6" s="80" t="str">
+        <f t="shared" si="8"/>
         <v>Give $D6 random Cards of each type from your hand to $R</v>
       </c>
-      <c r="AA6" s="80" t="str">
-        <f t="shared" si="6"/>
+      <c r="AV6" s="78" t="str">
+        <f t="shared" si="8"/>
         <v>Lose half your Commodities</v>
       </c>
-      <c r="AB6" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="AW6" s="80" t="str">
+        <f t="shared" si="8"/>
         <v>Lose half your Coins</v>
       </c>
-      <c r="AC6" s="80" t="str">
-        <f t="shared" si="6"/>
+      <c r="AX6" s="81" t="str">
+        <f t="shared" si="8"/>
         <v>Lose half your Troops</v>
       </c>
-      <c r="AD6" s="81" t="str">
-        <f t="shared" si="6"/>
+      <c r="AY6" s="78" t="str">
+        <f t="shared" si="8"/>
         <v>Lose half your Spies</v>
       </c>
-      <c r="AE6" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="AZ6" s="80" t="str">
+        <f t="shared" si="8"/>
         <v>Disard half your cards of each type</v>
       </c>
-      <c r="AF6" s="78" t="str">
-        <f t="shared" si="7"/>
+      <c r="BA6" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
       </c>
-      <c r="AG6" s="80" t="str">
-        <f t="shared" si="7"/>
+      <c r="BB6" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="AH6" s="78" t="str">
-        <f t="shared" si="7"/>
+      <c r="BC6" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="AI6" s="80" t="str">
-        <f t="shared" si="7"/>
+      <c r="BD6" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>Demote a Leader at level $D6 by half and send it to $R</v>
       </c>
-      <c r="AJ6" s="78" t="str">
-        <f t="shared" si="7"/>
+      <c r="BE6" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="AK6" s="80" t="str">
-        <f t="shared" si="7"/>
+      <c r="BF6" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="AL6" s="78" t="str">
-        <f t="shared" si="7"/>
+      <c r="BG6" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Move your foremost Law to the back of the Queue</v>
       </c>
-      <c r="AM6" s="80" t="str">
-        <f t="shared" si="7"/>
+      <c r="BH6" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="AN6" s="78" t="str">
-        <f t="shared" si="7"/>
+      <c r="BI6" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Move $D6 of your Laws each one space back in the Queue</v>
       </c>
-      <c r="AO6" s="80" t="str">
-        <f t="shared" si="7"/>
+      <c r="BJ6" s="80" t="str">
+        <f t="shared" si="9"/>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="AP6" s="78" t="str">
-        <f t="shared" si="8"/>
+      <c r="BK6" s="78" t="str">
+        <f t="shared" si="10"/>
         <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="AQ6" s="80" t="str">
-        <f t="shared" si="9"/>
-        <v>Give $2D6 Troops to $R</v>
-      </c>
-      <c r="AR6" s="78" t="str">
-        <f t="shared" si="9"/>
-        <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
-      </c>
-      <c r="AS6" s="80" t="str">
-        <f t="shared" si="9"/>
-        <v>Give $D6 Spies to $R</v>
-      </c>
-      <c r="AT6" s="78" t="str">
-        <f t="shared" si="9"/>
-        <v>Give $2D6 Commodities to $R</v>
-      </c>
-      <c r="AU6" s="80" t="str">
-        <f t="shared" si="9"/>
-        <v>Give $D6 random Cards of each type from your hand to $R</v>
-      </c>
-      <c r="AV6" s="78" t="str">
-        <f t="shared" si="9"/>
-        <v>Lose half your Commodities</v>
-      </c>
-      <c r="AW6" s="80" t="str">
-        <f t="shared" si="9"/>
-        <v>Lose half your Coins</v>
-      </c>
-      <c r="AX6" s="81" t="str">
-        <f t="shared" si="9"/>
-        <v>Lose half your Troops</v>
-      </c>
-      <c r="AY6" s="78" t="str">
-        <f t="shared" si="9"/>
-        <v>Lose half your Spies</v>
-      </c>
-      <c r="AZ6" s="80" t="str">
-        <f t="shared" si="9"/>
-        <v>Disard half your cards of each type</v>
-      </c>
-      <c r="BA6" s="78" t="str">
-        <f t="shared" si="10"/>
-        <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
-      </c>
-      <c r="BB6" s="80" t="str">
-        <f t="shared" si="10"/>
-        <v>Downgrade an Investment by $D6 levels</v>
-      </c>
-      <c r="BC6" s="78" t="str">
-        <f t="shared" si="10"/>
-        <v>Downgrade an Investment by $D6 levels</v>
-      </c>
-      <c r="BD6" s="80" t="str">
-        <f t="shared" si="10"/>
-        <v>Demote a Leader at level $D6 by half and send it to $R</v>
-      </c>
-      <c r="BE6" s="78" t="str">
-        <f t="shared" si="10"/>
-        <v>Demote a Leader by $D6 levels</v>
-      </c>
-      <c r="BF6" s="80" t="str">
-        <f t="shared" si="10"/>
-        <v>Demote a Leader by $D6 levels</v>
-      </c>
-      <c r="BG6" s="78" t="str">
-        <f t="shared" si="10"/>
-        <v>Move your foremost Law to the back of the Queue</v>
-      </c>
-      <c r="BH6" s="78" t="str">
-        <f t="shared" si="10"/>
-        <v>Move your foremost Law $D6 spaces back in the Queue</v>
-      </c>
-      <c r="BI6" s="78" t="str">
-        <f t="shared" si="10"/>
-        <v>Move $D6 of your Laws each one space back in the Queue</v>
-      </c>
-      <c r="BJ6" s="80" t="str">
-        <f t="shared" si="10"/>
-        <v>Move your foremost Law $D6 spaces back in the Queue</v>
-      </c>
-      <c r="BK6" s="78" t="str">
-        <f t="shared" si="11"/>
-        <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
-      </c>
       <c r="BM6" s="78" t="str">
-        <f t="shared" si="12"/>
+        <f>AE2</f>
         <v>Trade up to $L3 additional Coins when Buying from the Undermarket</v>
       </c>
       <c r="BN6" s="80" t="str">
-        <f t="shared" si="12"/>
+        <f>AF2</f>
         <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
       </c>
       <c r="BO6" s="78" t="str">
-        <f t="shared" si="12"/>
+        <f>AG2</f>
         <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
       </c>
       <c r="BP6" s="80" t="str">
-        <f t="shared" si="12"/>
+        <f>AH2</f>
         <v>Provides private Monetize Action at Market Rate + $L3</v>
       </c>
       <c r="BQ6" s="78" t="str">
-        <f t="shared" si="12"/>
+        <f>AI2</f>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
       </c>
       <c r="BR6" s="78"/>
@@ -8582,295 +8584,295 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BDA35E-BFC3-134A-A064-89D65A8B31CF}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.50390625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.22265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C1" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D1" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E1" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D2">
         <v>27.7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D3">
         <v>27.7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D4">
         <v>30.75</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E6" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E7" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E8" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E10" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E11" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E12" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E13" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -8882,90 +8884,90 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC83F89-2724-CA43-A519-59213A612B31}">
   <dimension ref="A1:U55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24" style="101" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="103" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="103" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="103" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="103" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="11.85546875" style="103" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" style="103" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.9453125" style="101" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.72265625" customWidth="1"/>
+    <col min="4" max="4" width="8.33984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.27734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.22265625" style="103" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.43359375" style="103" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.22265625" style="103" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.43359375" style="103" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="11.8359375" style="103" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.9140625" style="103" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G1" t="s">
+        <v>362</v>
+      </c>
+      <c r="H1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I1" t="s">
         <v>339</v>
       </c>
-      <c r="B1" t="s">
+      <c r="J1" s="103" t="s">
+        <v>360</v>
+      </c>
+      <c r="K1" t="s">
         <v>340</v>
       </c>
-      <c r="C1" t="s">
+      <c r="L1" t="s">
         <v>341</v>
       </c>
-      <c r="D1" t="s">
+      <c r="M1" t="s">
         <v>342</v>
       </c>
-      <c r="E1" t="s">
+      <c r="N1" t="s">
         <v>343</v>
       </c>
-      <c r="F1" t="s">
-        <v>369</v>
-      </c>
-      <c r="G1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="O1" t="s">
         <v>344</v>
       </c>
-      <c r="I1" t="s">
+      <c r="P1" t="s">
         <v>345</v>
       </c>
-      <c r="J1" s="103" t="s">
-        <v>366</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="Q1" t="s">
         <v>346</v>
       </c>
-      <c r="L1" t="s">
+      <c r="R1" t="s">
         <v>347</v>
       </c>
-      <c r="M1" t="s">
+      <c r="S1" t="s">
         <v>348</v>
       </c>
-      <c r="N1" t="s">
+      <c r="T1" t="s">
         <v>349</v>
       </c>
-      <c r="O1" t="s">
-        <v>350</v>
-      </c>
-      <c r="P1" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>352</v>
-      </c>
-      <c r="R1" t="s">
-        <v>353</v>
-      </c>
-      <c r="S1" t="s">
-        <v>354</v>
-      </c>
-      <c r="T1" t="s">
-        <v>355</v>
-      </c>
       <c r="U1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="101">
         <v>46075</v>
       </c>
@@ -9009,7 +9011,7 @@
         <v>0.92638888888888893</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="101">
         <v>46089</v>
       </c>
@@ -9065,7 +9067,7 @@
         <v>0.86527777777777781</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="101">
         <v>46105</v>
       </c>
@@ -9118,7 +9120,7 @@
         <v>0.92777777777777781</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="101">
         <v>46118</v>
       </c>
@@ -9171,23 +9173,104 @@
         <v>0.9194444444444444</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6" s="101">
+        <v>46124</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
       <c r="C6" s="102" t="b">
         <v>0</v>
       </c>
       <c r="D6" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>9</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6" s="103">
+        <v>0.64097222222222228</v>
+      </c>
+      <c r="I6" s="103">
+        <v>0.74583333333333335</v>
+      </c>
+      <c r="J6" s="103">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="K6" s="103">
+        <v>0.68611111111111112</v>
+      </c>
+      <c r="L6" s="103">
+        <v>0.71250000000000002</v>
+      </c>
+      <c r="M6" s="103">
+        <v>0.74027777777777781</v>
+      </c>
+      <c r="U6" s="103">
+        <v>0.74583333333333335</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A7" s="101">
+        <v>46131</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
       <c r="C7" s="102" t="b">
         <v>0</v>
       </c>
       <c r="D7" s="102" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
+      <c r="H7" s="103">
+        <v>0.54652777777777772</v>
+      </c>
+      <c r="I7" s="103">
+        <v>0.70277777777777772</v>
+      </c>
+      <c r="J7" s="103">
+        <v>0.55694444444444446</v>
+      </c>
+      <c r="K7" s="103">
+        <v>0.57222222222222219</v>
+      </c>
+      <c r="L7" s="103">
+        <v>0.59652777777777777</v>
+      </c>
+      <c r="M7" s="103">
+        <v>0.61805555555555558</v>
+      </c>
+      <c r="N7" s="103">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="O7" s="103">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="P7" s="103">
+        <v>0.69930555555555551</v>
+      </c>
+      <c r="U7" s="103">
+        <v>0.70277777777777772</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="102" t="b">
         <v>0</v>
       </c>
@@ -9195,7 +9278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="102" t="b">
         <v>0</v>
       </c>
@@ -9203,7 +9286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="102" t="b">
         <v>0</v>
       </c>
@@ -9211,7 +9294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="102" t="b">
         <v>0</v>
       </c>
@@ -9219,7 +9302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="102" t="b">
         <v>0</v>
       </c>
@@ -9227,7 +9310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="102" t="b">
         <v>0</v>
       </c>
@@ -9235,7 +9318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="102" t="b">
         <v>0</v>
       </c>
@@ -9243,7 +9326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="102" t="b">
         <v>0</v>
       </c>
@@ -9251,7 +9334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C16" s="102" t="b">
         <v>0</v>
       </c>
@@ -9259,7 +9342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C17" s="102" t="b">
         <v>0</v>
       </c>
@@ -9267,7 +9350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C18" s="102" t="b">
         <v>0</v>
       </c>
@@ -9275,7 +9358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C19" s="102" t="b">
         <v>0</v>
       </c>
@@ -9283,7 +9366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C20" s="102" t="b">
         <v>0</v>
       </c>
@@ -9291,7 +9374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C21" s="102" t="b">
         <v>0</v>
       </c>
@@ -9299,7 +9382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C22" s="102" t="b">
         <v>0</v>
       </c>
@@ -9307,7 +9390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C23" s="102" t="b">
         <v>0</v>
       </c>
@@ -9315,7 +9398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C24" s="102" t="b">
         <v>0</v>
       </c>
@@ -9323,7 +9406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C25" s="102" t="b">
         <v>0</v>
       </c>
@@ -9331,7 +9414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C26" s="102" t="b">
         <v>0</v>
       </c>
@@ -9339,7 +9422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C27" s="102" t="b">
         <v>0</v>
       </c>
@@ -9347,7 +9430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C28" s="102" t="b">
         <v>0</v>
       </c>
@@ -9355,7 +9438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C29" s="102" t="b">
         <v>0</v>
       </c>
@@ -9363,7 +9446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C30" s="102" t="b">
         <v>0</v>
       </c>
@@ -9371,7 +9454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C31" s="102" t="b">
         <v>0</v>
       </c>
@@ -9379,7 +9462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C32" s="102" t="b">
         <v>0</v>
       </c>
@@ -9387,7 +9470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C33" s="102" t="b">
         <v>0</v>
       </c>
@@ -9395,7 +9478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C34" s="102" t="b">
         <v>0</v>
       </c>
@@ -9403,7 +9486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C35" s="102" t="b">
         <v>0</v>
       </c>
@@ -9411,7 +9494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C36" s="102" t="b">
         <v>0</v>
       </c>
@@ -9419,7 +9502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C37" s="102" t="b">
         <v>0</v>
       </c>
@@ -9427,7 +9510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C38" s="102" t="b">
         <v>0</v>
       </c>
@@ -9435,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C39" s="102" t="b">
         <v>0</v>
       </c>
@@ -9443,7 +9526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C40" s="102" t="b">
         <v>0</v>
       </c>
@@ -9451,7 +9534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C41" s="102" t="b">
         <v>0</v>
       </c>
@@ -9459,7 +9542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C42" s="102" t="b">
         <v>0</v>
       </c>
@@ -9467,7 +9550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C43" s="102" t="b">
         <v>0</v>
       </c>
@@ -9475,7 +9558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C44" s="102" t="b">
         <v>0</v>
       </c>
@@ -9483,7 +9566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C45" s="102" t="b">
         <v>0</v>
       </c>
@@ -9491,7 +9574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C46" s="102" t="b">
         <v>0</v>
       </c>
@@ -9499,7 +9582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C47" s="102" t="b">
         <v>0</v>
       </c>
@@ -9507,7 +9590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C48" s="102" t="b">
         <v>0</v>
       </c>
@@ -9515,7 +9598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C49" s="102" t="b">
         <v>0</v>
       </c>
@@ -9523,7 +9606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C50" s="102" t="b">
         <v>0</v>
       </c>
@@ -9531,7 +9614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C51" s="102" t="b">
         <v>0</v>
       </c>
@@ -9539,7 +9622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C52" s="102" t="b">
         <v>0</v>
       </c>
@@ -9547,7 +9630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C53" s="102" t="b">
         <v>0</v>
       </c>
@@ -9555,7 +9638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C54" s="102" t="b">
         <v>0</v>
       </c>
@@ -9563,7 +9646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C55" s="102" t="b">
         <v>0</v>
       </c>

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,20 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4069" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD2256F1-E359-C640-8357-E402C4190679}"/>
+  <xr:revisionPtr revIDLastSave="4260" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E9160F4-F4CF-4F20-B7DC-ADF9830D065B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
     <sheet name="Info" sheetId="2" r:id="rId2"/>
     <sheet name="Training Setups" sheetId="6" r:id="rId3"/>
     <sheet name="Provincial and Undermarket" sheetId="3" r:id="rId4"/>
-    <sheet name="Court" sheetId="4" r:id="rId5"/>
-    <sheet name="Battlefield" sheetId="5" r:id="rId6"/>
-    <sheet name="Printable Cards" sheetId="7" r:id="rId7"/>
-    <sheet name="Components" sheetId="8" r:id="rId8"/>
-    <sheet name="Playtesting" sheetId="9" r:id="rId9"/>
+    <sheet name="Printable Cards" sheetId="7" r:id="rId5"/>
+    <sheet name="Components" sheetId="8" r:id="rId6"/>
+    <sheet name="Playtesting" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="472">
   <si>
     <t>Standard Card</t>
   </si>
@@ -787,9 +785,6 @@
     <t>Greek Reserves</t>
   </si>
   <si>
-    <t>Persian</t>
-  </si>
-  <si>
     <t>Law Cards</t>
   </si>
   <si>
@@ -1460,6 +1455,10 @@
   </si>
   <si>
     <t>Provides Private Donate action with no penalty and convert $L3 additional Coins.</t>
+  </si>
+  <si>
+    <t>Persian
+Troops</t>
   </si>
 </sst>
 </file>
@@ -1470,16 +1469,9 @@
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -1524,16 +1516,14 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="28"/>
       <color rgb="FFEFBF04"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FFEFBF04"/>
+      <sz val="28"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1560,13 +1550,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1C39BB"/>
+        <fgColor rgb="FFEFBF04"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFBF04"/>
+        <fgColor rgb="FF1C39BB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2467,7 +2457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2544,29 +2534,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2626,20 +2604,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2665,16 +2637,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
@@ -2690,16 +2662,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
@@ -2732,10 +2704,7 @@
       </extLst>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2747,10 +2716,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2766,92 +2735,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2862,8 +2807,8 @@
   <colors>
     <mruColors>
       <color rgb="FFEFBF04"/>
+      <color rgb="FF1C39BB"/>
       <color rgb="FFCC3333"/>
-      <color rgb="FF1C39BB"/>
       <color rgb="FFFFFF66"/>
       <color rgb="FFE5CDA9"/>
       <color rgb="FFFFE269"/>
@@ -2884,16 +2829,144 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1371600</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>485775</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7017</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1019175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1433762</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1243263</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{263C6929-F455-4392-8FF0-0BAF1B2A42D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057399" y="9897478"/>
+          <a:ext cx="1426745" cy="224088"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="EFBF04"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800"/>
+            <a:t>Commodities</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1343025</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>495300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1657350</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1057275</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Arrow: Up 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB240F5A-E050-4CAD-8299-672EF9710C9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000">
+          <a:off x="1343025" y="4162425"/>
+          <a:ext cx="314325" cy="561975"/>
+        </a:xfrm>
+        <a:prstGeom prst="upArrow">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1371600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>1685925</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>1047750</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2949,15 +3022,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>257175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1666875</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>819150</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2979,11 +3052,7 @@
         <a:prstGeom prst="upArrow">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="90000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:noFill/>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -3014,15 +3083,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1523999</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>561974</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1914524</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>952499</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3101,15 +3170,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>1533525</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>361950</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>1924050</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>752475</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3188,16 +3257,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>1466850</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>466725</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>3</xdr:col>
       <xdr:colOff>1857375</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>857250</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3273,30 +3342,25 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1504950</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>457200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>973455</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>992505</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1895475</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>847725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+        <xdr:cNvPr id="7" name="Rectangle: Rounded Corners 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF595A18-8BC9-1AB3-2507-B99CA810F8C7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{480BC858-CF23-426C-BC86-E5772776D7F9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3304,7 +3368,90 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6477000" y="1619250"/>
+          <a:off x="5600700" y="2295525"/>
+          <a:ext cx="390525" cy="390525"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 25491"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1200" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>352425</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>973455</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>992505</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Rectangle: Rounded Corners 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFE0C256-296D-47F7-9153-C7207D362CE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="847725" y="3390900"/>
           <a:ext cx="640080" cy="640080"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -3312,11 +3459,7 @@
             <a:gd name="adj" fmla="val 25491"/>
           </a:avLst>
         </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="90000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:noFill/>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -3347,23 +3490,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>1104900</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>1714499</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>866775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
+        <xdr:cNvPr id="10" name="TextBox 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD98B757-2725-CFEA-9F1E-E10DABC43828}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8B22148-4BC1-4117-A068-36095DF6367C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3371,7 +3514,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7248525" y="1743075"/>
+          <a:off x="1619250" y="3514725"/>
           <a:ext cx="609599" cy="390525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3418,23 +3561,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>152399</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1019175</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1114925</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>780549</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1123950</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>1209675</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1754604</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>961524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="TextBox 3">
+        <xdr:cNvPr id="12" name="TextBox 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70D4C764-A3BB-E899-A2E3-E823438DB606}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99E6AFCB-FFB4-451E-AA30-683E4746CB82}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3442,8 +3585,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6296024" y="2286000"/>
-          <a:ext cx="971551" cy="190500"/>
+          <a:off x="3165307" y="9658852"/>
+          <a:ext cx="639679" cy="180975"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3475,9 +3618,10 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Commodities</a:t>
+            <a:rPr lang="en-US" sz="1800"/>
+            <a:t>Coin</a:t>
           </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3485,90 +3629,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1200150</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>790575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1685926</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>971550</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF500BE7-3C59-4CF3-A98E-31BBF855D8B8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7343775" y="2057400"/>
-          <a:ext cx="485776" cy="180975"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="EFBF04"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100"/>
-            <a:t>Coin</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>1323975</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>514350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>1638300</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1076325</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Arrow: Up 5">
+        <xdr:cNvPr id="13" name="Arrow: Up 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0389E71-98B9-440B-A547-BF3226A3D1BC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A7A64E9-7CF2-4746-A30D-260518DB83F7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3576,7 +3653,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="1323975" y="1781175"/>
+          <a:off x="1838325" y="2286000"/>
           <a:ext cx="314325" cy="561975"/>
         </a:xfrm>
         <a:prstGeom prst="upArrow">
@@ -3615,23 +3692,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1343025</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>285750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>1657350</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>847725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Arrow: Up 7">
+        <xdr:cNvPr id="14" name="Arrow: Up 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59810BE8-ABCC-4894-AD3B-0CC257658970}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E78AC844-E51C-4855-95DE-96AA56587902}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3639,7 +3716,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3390900" y="1552575"/>
+          <a:off x="3905250" y="2057400"/>
           <a:ext cx="314325" cy="561975"/>
         </a:xfrm>
         <a:prstGeom prst="upArrow">
@@ -4017,23 +4094,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5390625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.18359375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="39.01171875" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -4059,7 +4136,7 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>7</v>
       </c>
@@ -4079,21 +4156,21 @@
         <v>12</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>357</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>358</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>14</v>
@@ -4102,16 +4179,16 @@
         <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>16</v>
       </c>
@@ -4119,25 +4196,25 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="3"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>20</v>
       </c>
@@ -4151,19 +4228,19 @@
         <v>23</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -4180,16 +4257,16 @@
         <v>29</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>31</v>
       </c>
@@ -4206,16 +4283,16 @@
         <v>35</v>
       </c>
       <c r="F7" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>429</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>430</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
@@ -4223,30 +4300,30 @@
         <v>41</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F8" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>431</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>432</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>44</v>
@@ -4255,19 +4332,19 @@
         <v>39</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F9" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>434</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>40</v>
       </c>
@@ -4278,48 +4355,48 @@
         <v>49</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>435</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>436</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="2"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>47</v>
       </c>
@@ -4327,7 +4404,7 @@
         <v>57</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>50</v>
@@ -4339,13 +4416,13 @@
         <v>46</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="2"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>53</v>
       </c>
@@ -4365,13 +4442,13 @@
         <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
@@ -4391,13 +4468,13 @@
         <v>42</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>60</v>
       </c>
@@ -4405,7 +4482,7 @@
         <v>71</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>63</v>
@@ -4417,18 +4494,18 @@
         <v>65</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>66</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>76</v>
@@ -4437,19 +4514,19 @@
         <v>69</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="2"/>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>70</v>
       </c>
@@ -4466,16 +4543,16 @@
         <v>73</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="2"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>74</v>
       </c>
@@ -4489,19 +4566,19 @@
         <v>77</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>78</v>
       </c>
@@ -4515,19 +4592,19 @@
         <v>81</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>82</v>
       </c>
@@ -4541,19 +4618,19 @@
         <v>85</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>86</v>
       </c>
@@ -4567,19 +4644,19 @@
         <v>89</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>90</v>
       </c>
@@ -4593,27 +4670,27 @@
         <v>93</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="3"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>94</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>97</v>
@@ -4627,21 +4704,21 @@
       <c r="I23" s="3"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>99</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>102</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="9"/>
@@ -4649,7 +4726,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>103</v>
       </c>
@@ -4657,13 +4734,13 @@
         <v>108</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>104</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
@@ -4671,7 +4748,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>105</v>
       </c>
@@ -4679,13 +4756,13 @@
         <v>111</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>106</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4693,7 +4770,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>107</v>
       </c>
@@ -4707,7 +4784,7 @@
         <v>109</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4715,7 +4792,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>110</v>
       </c>
@@ -4729,7 +4806,7 @@
         <v>112</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4737,7 +4814,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>113</v>
       </c>
@@ -4751,7 +4828,7 @@
         <v>116</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4759,7 +4836,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>117</v>
       </c>
@@ -4781,7 +4858,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>122</v>
       </c>
@@ -4803,7 +4880,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>127</v>
       </c>
@@ -4811,13 +4888,13 @@
         <v>134</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -4825,7 +4902,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>130</v>
       </c>
@@ -4836,10 +4913,10 @@
         <v>137</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -4847,15 +4924,15 @@
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>133</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>355</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>356</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="16"/>
@@ -4865,15 +4942,15 @@
       <c r="I34" s="3"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>135</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="16"/>
@@ -4883,15 +4960,15 @@
       <c r="I35" s="3"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>138</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4901,15 +4978,15 @@
       <c r="I36" s="3"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>139</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -4919,15 +4996,15 @@
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>140</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -4937,15 +5014,15 @@
       <c r="I38" s="3"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>141</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -4955,15 +5032,15 @@
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>142</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>442</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>443</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="16"/>
@@ -4973,15 +5050,15 @@
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>143</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="16"/>
@@ -4991,7 +5068,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>144</v>
       </c>
@@ -5005,7 +5082,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>145</v>
       </c>
@@ -5019,7 +5096,7 @@
       <c r="I43" s="3"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>146</v>
       </c>
@@ -5033,7 +5110,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>147</v>
       </c>
@@ -5047,7 +5124,7 @@
       <c r="I45" s="3"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>148</v>
       </c>
@@ -5061,7 +5138,7 @@
       <c r="I46" s="3"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>149</v>
       </c>
@@ -5075,7 +5152,7 @@
       <c r="I47" s="3"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>150</v>
       </c>
@@ -5089,7 +5166,7 @@
       <c r="I48" s="3"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>151</v>
       </c>
@@ -5103,7 +5180,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>152</v>
       </c>
@@ -5117,12 +5194,12 @@
       <c r="I50" s="3"/>
       <c r="J50" s="4"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B51" s="106"/>
-      <c r="C51" s="107"/>
+      <c r="B51" s="99"/>
+      <c r="C51" s="100"/>
       <c r="D51" s="6"/>
       <c r="E51" s="16"/>
       <c r="F51" s="6"/>
@@ -5131,12 +5208,12 @@
       <c r="I51" s="3"/>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B52" s="106"/>
-      <c r="C52" s="107"/>
+      <c r="B52" s="99"/>
+      <c r="C52" s="100"/>
       <c r="D52" s="6"/>
       <c r="E52" s="16"/>
       <c r="F52" s="6"/>
@@ -5145,7 +5222,7 @@
       <c r="I52" s="3"/>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
         <v>155</v>
       </c>
@@ -5168,541 +5245,541 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D195C1D-DB02-1743-BBD2-99104C1FFD33}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.71875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.86328125" customWidth="1"/>
-    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.55859375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.26171875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.7890625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.16796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.0859375" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="49" t="s">
         <v>158</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="H1" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="I2" s="46" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" s="31" t="s">
         <v>328</v>
       </c>
-      <c r="H1" s="54" t="s">
-        <v>162</v>
-      </c>
-      <c r="I1" s="55" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="47" t="s">
-        <v>308</v>
-      </c>
-      <c r="B2" s="48" t="s">
-        <v>391</v>
-      </c>
-      <c r="C2" s="49" t="s">
+      <c r="C3" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="D2" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="E2" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>168</v>
-      </c>
-      <c r="H2" s="50" t="s">
-        <v>169</v>
-      </c>
-      <c r="I2" s="50" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="37" t="s">
-        <v>330</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>329</v>
-      </c>
-      <c r="C3" s="38" t="s">
+      <c r="D3" s="38" t="s">
+        <v>310</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="H3" s="38" t="s">
+        <v>281</v>
+      </c>
+      <c r="I3" s="38" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C4" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="D3" s="42" t="s">
-        <v>311</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="H3" s="42" t="s">
-        <v>282</v>
-      </c>
-      <c r="I3" s="42" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="81" x14ac:dyDescent="0.2">
-      <c r="A4" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="C4" s="38" t="s">
+      <c r="D4" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="I4" s="41"/>
+    </row>
+    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="D4" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="42" t="s">
-        <v>359</v>
-      </c>
-      <c r="G4" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="H4" s="42" t="s">
-        <v>179</v>
-      </c>
-      <c r="I4" s="45"/>
-    </row>
-    <row r="5" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>288</v>
-      </c>
-      <c r="C5" s="38" t="s">
+      <c r="D5" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="H5" s="38" t="s">
+        <v>280</v>
+      </c>
+      <c r="I5" s="41"/>
+    </row>
+    <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C6" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="42" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>183</v>
-      </c>
-      <c r="G5" s="42" t="s">
+      <c r="D6" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6" s="38" t="s">
         <v>326</v>
       </c>
-      <c r="H5" s="42" t="s">
-        <v>281</v>
-      </c>
-      <c r="I5" s="45"/>
-    </row>
-    <row r="6" spans="1:9" ht="108" x14ac:dyDescent="0.2">
-      <c r="A6" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="38" t="s">
+      <c r="H6" s="38" t="s">
+        <v>393</v>
+      </c>
+      <c r="I6" s="41"/>
+    </row>
+    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="C7" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="D6" s="42" t="s">
-        <v>186</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>187</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>327</v>
-      </c>
-      <c r="H6" s="42" t="s">
-        <v>394</v>
-      </c>
-      <c r="I6" s="45"/>
-    </row>
-    <row r="7" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="38" t="s">
+      <c r="D7" s="38" t="s">
+        <v>363</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>285</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>312</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="H7" s="38"/>
+      <c r="I7" s="41"/>
+    </row>
+    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="D7" s="42" t="s">
-        <v>364</v>
-      </c>
-      <c r="E7" s="42" t="s">
+      <c r="D8" s="38" t="s">
+        <v>194</v>
+      </c>
+      <c r="E8" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="F7" s="44" t="s">
-        <v>313</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="H7" s="42"/>
-      <c r="I7" s="45"/>
-    </row>
-    <row r="8" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="38" t="s">
+      <c r="F8" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="41"/>
+    </row>
+    <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="A9" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="C9" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="D8" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>287</v>
-      </c>
-      <c r="F8" s="42" t="s">
-        <v>195</v>
-      </c>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="45"/>
-    </row>
-    <row r="9" spans="1:9" ht="108" x14ac:dyDescent="0.2">
-      <c r="A9" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>197</v>
-      </c>
-      <c r="C9" s="38" t="s">
+      <c r="D9" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E9" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="41"/>
+    </row>
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>463</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>201</v>
+      </c>
+      <c r="C10" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="42" t="s">
-        <v>198</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>199</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>200</v>
-      </c>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="45"/>
-    </row>
-    <row r="10" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="37" t="s">
-        <v>464</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>201</v>
-      </c>
-      <c r="C10" s="38" t="s">
+      <c r="D10" s="38" t="s">
+        <v>370</v>
+      </c>
+      <c r="E10" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="41"/>
+    </row>
+    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>369</v>
+      </c>
+      <c r="C11" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D11" s="38"/>
+      <c r="E11" s="38" t="s">
         <v>371</v>
       </c>
-      <c r="E10" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="45"/>
-    </row>
-    <row r="11" spans="1:9" ht="68.25" x14ac:dyDescent="0.2">
-      <c r="A11" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>370</v>
-      </c>
-      <c r="C11" s="38" t="s">
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="41"/>
+    </row>
+    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42" t="s">
+      <c r="D12" s="38"/>
+      <c r="E12" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="41"/>
+    </row>
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="F13" s="40"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="41"/>
+    </row>
+    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>211</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="41"/>
+    </row>
+    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="41"/>
+    </row>
+    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="41"/>
+    </row>
+    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" s="33" t="s">
         <v>372</v>
       </c>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="45"/>
-    </row>
-    <row r="12" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42" t="s">
-        <v>206</v>
-      </c>
-      <c r="F12" s="44"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="45"/>
-    </row>
-    <row r="13" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42" t="s">
-        <v>209</v>
-      </c>
-      <c r="F13" s="44"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="45"/>
-    </row>
-    <row r="14" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="37" t="s">
+      <c r="B17" s="31" t="s">
+        <v>374</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="41"/>
+    </row>
+    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="41"/>
+    </row>
+    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="41"/>
+    </row>
+    <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A20" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="41"/>
+    </row>
+    <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="41"/>
+    </row>
+    <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="B14" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42" t="s">
-        <v>213</v>
-      </c>
-      <c r="F14" s="44"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="45"/>
-    </row>
-    <row r="15" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="37" t="s">
+      <c r="B22" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="41"/>
+    </row>
+    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="33" t="s">
         <v>214</v>
       </c>
-      <c r="B15" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="45"/>
-    </row>
-    <row r="16" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="37" t="s">
+      <c r="B23" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="41"/>
+    </row>
+    <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="35" t="s">
         <v>216</v>
       </c>
-      <c r="B16" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="45"/>
-    </row>
-    <row r="17" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="37" t="s">
+      <c r="B24" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="41"/>
+    </row>
+    <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="35" t="s">
+        <v>372</v>
+      </c>
+      <c r="B25" s="36" t="s">
         <v>373</v>
       </c>
-      <c r="B17" s="35" t="s">
-        <v>375</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>212</v>
-      </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="45"/>
-    </row>
-    <row r="18" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="B18" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="C18" s="38" t="s">
+      <c r="C25" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="45"/>
-    </row>
-    <row r="19" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="37" t="s">
-        <v>221</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="45"/>
-    </row>
-    <row r="20" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="45"/>
-    </row>
-    <row r="21" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
-      <c r="A21" s="37" t="s">
-        <v>352</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>353</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="45"/>
-    </row>
-    <row r="22" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
-      <c r="A22" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="B22" s="35" t="s">
-        <v>225</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="45"/>
-    </row>
-    <row r="23" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="B23" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="45"/>
-    </row>
-    <row r="24" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="B24" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="C24" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="45"/>
-    </row>
-    <row r="25" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="39" t="s">
-        <v>373</v>
-      </c>
-      <c r="B25" s="40" t="s">
-        <v>374</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="46"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5713,341 +5790,341 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920DF489-FE6D-4819-BD1A-323DFAE597A3}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="30.66796875" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="67"/>
-      <c r="B1" s="61" t="s">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="61"/>
+      <c r="B1" s="55" t="s">
         <v>228</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="55" t="s">
         <v>229</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="54" t="s">
         <v>230</v>
       </c>
-      <c r="E1" s="110" t="s">
+      <c r="E1" s="103" t="s">
         <v>231</v>
       </c>
-      <c r="F1" s="109" t="s">
+      <c r="F1" s="102" t="s">
         <v>232</v>
       </c>
-      <c r="G1" s="61" t="s">
+      <c r="G1" s="55" t="s">
         <v>233</v>
       </c>
       <c r="I1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="63" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" s="101" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="107" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="I2" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
-        <v>234</v>
-      </c>
-      <c r="B2" s="70" t="s">
-        <v>87</v>
-      </c>
-      <c r="C2" s="64" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="108" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" s="114" t="s">
-        <v>100</v>
-      </c>
-      <c r="G2" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="I2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>449</v>
+      </c>
+      <c r="D3" s="56" t="s">
+        <v>356</v>
+      </c>
+      <c r="E3" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="G3" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="I3" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
-        <v>235</v>
-      </c>
-      <c r="B3" s="71" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="63" t="s">
-        <v>450</v>
-      </c>
-      <c r="D3" s="62" t="s">
-        <v>357</v>
-      </c>
-      <c r="E3" s="111" t="s">
-        <v>95</v>
-      </c>
-      <c r="F3" s="59" t="s">
-        <v>324</v>
-      </c>
-      <c r="G3" s="63" t="s">
-        <v>131</v>
-      </c>
-      <c r="I3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="69" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="63" t="s">
         <v>236</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="62" t="s">
+      <c r="D4" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="E4" s="111" t="s">
+      <c r="E4" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="F4" s="62" t="s">
+      <c r="F4" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="63" t="s">
+      <c r="G4" s="57" t="s">
         <v>111</v>
       </c>
       <c r="I4" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="69" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="63" t="s">
         <v>237</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="62" t="s">
         <v>136</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="62" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="66" t="s">
+      <c r="D5" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="112" t="s">
-        <v>368</v>
-      </c>
-      <c r="F5" s="115" t="s">
+      <c r="E5" s="105" t="s">
+        <v>367</v>
+      </c>
+      <c r="F5" s="108" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="113" t="s">
-        <v>378</v>
+      <c r="G5" s="106" t="s">
+        <v>377</v>
       </c>
       <c r="I5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="86" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" s="87" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="88" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="89" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="90" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="82" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="91" t="s">
+        <v>116</v>
+      </c>
+      <c r="I6" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="92" t="s">
-        <v>238</v>
-      </c>
-      <c r="B6" s="93" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="94" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="95" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" s="96" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" s="88" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="97" t="s">
-        <v>116</v>
-      </c>
-      <c r="I6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="72" t="s">
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="66" t="s">
         <v>239</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="66" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="69" t="s">
-        <v>316</v>
+      <c r="C7" s="63" t="s">
+        <v>315</v>
       </c>
       <c r="D7" t="s">
         <v>241</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="63" t="s">
         <v>242</v>
       </c>
       <c r="F7" t="s">
         <v>243</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="63" t="s">
         <v>163</v>
       </c>
       <c r="I7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="84" t="s">
+        <v>290</v>
+      </c>
+      <c r="B8" s="84" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" s="80" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="84" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="80" t="s">
+        <v>228</v>
+      </c>
+      <c r="F8" s="84" t="s">
+        <v>229</v>
+      </c>
+      <c r="G8" s="81" t="s">
+        <v>230</v>
+      </c>
+      <c r="I8" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="90" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="53" t="s">
         <v>291</v>
       </c>
-      <c r="B8" s="90" t="s">
-        <v>231</v>
-      </c>
-      <c r="C8" s="86" t="s">
-        <v>232</v>
-      </c>
-      <c r="D8" s="90" t="s">
-        <v>233</v>
-      </c>
-      <c r="E8" s="86" t="s">
-        <v>228</v>
-      </c>
-      <c r="F8" s="90" t="s">
-        <v>229</v>
-      </c>
-      <c r="G8" s="87" t="s">
-        <v>230</v>
-      </c>
-      <c r="I8" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="59" t="s">
-        <v>292</v>
-      </c>
-      <c r="B9" s="59" t="s">
+      <c r="B9" s="53" t="s">
         <v>232</v>
       </c>
       <c r="C9" t="s">
         <v>230</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="53" t="s">
         <v>229</v>
       </c>
       <c r="E9" t="s">
         <v>233</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="53" t="s">
         <v>228</v>
       </c>
-      <c r="G9" s="71" t="s">
+      <c r="G9" s="65" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="91" t="s">
-        <v>293</v>
-      </c>
-      <c r="B10" s="91" t="s">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="85" t="s">
+        <v>292</v>
+      </c>
+      <c r="B10" s="85" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="82" t="s">
         <v>233</v>
       </c>
-      <c r="D10" s="91" t="s">
+      <c r="D10" s="85" t="s">
         <v>228</v>
       </c>
-      <c r="E10" s="88" t="s">
+      <c r="E10" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="F10" s="91" t="s">
+      <c r="F10" s="85" t="s">
         <v>231</v>
       </c>
-      <c r="G10" s="89" t="s">
+      <c r="G10" s="83" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>455</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>457</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>189</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>460</v>
-      </c>
       <c r="G15" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>184</v>
@@ -6056,13 +6133,13 @@
         <v>189</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -6071,105 +6148,105 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>414</v>
-      </c>
       <c r="I18" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I19" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="E20" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D21" t="s">
+        <v>417</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D21" t="s">
-        <v>418</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="G21" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="2"/>
       <c r="D23" s="2"/>
@@ -6177,12 +6254,12 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>223</v>
@@ -6191,19 +6268,19 @@
         <v>196</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I24" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
         <v>204</v>
@@ -6212,25 +6289,25 @@
         <v>207</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I25" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>221</v>
@@ -6239,36 +6316,36 @@
         <v>204</v>
       </c>
       <c r="E26" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>204</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I26" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="G27" s="2"/>
       <c r="I27" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -6277,10 +6354,10 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="I28" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -6289,10 +6366,10 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="I29" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -6301,7 +6378,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -6309,7 +6386,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -6317,7 +6394,7 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -6325,7 +6402,7 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -6333,7 +6410,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -6341,7 +6418,7 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -6349,7 +6426,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -6357,7 +6434,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -6365,7 +6442,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -6373,7 +6450,7 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -6381,7 +6458,7 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -6389,7 +6466,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -6397,7 +6474,7 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -6405,7 +6482,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -6413,7 +6490,7 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B48" s="3"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -6421,7 +6498,7 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -6434,2146 +6511,1993 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4430D7D8-35BC-4E32-9DE8-E2E435ADAAA0}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="37.5" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="36" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="4" width="30.66796875" style="26" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" style="26" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.14453125" style="26"/>
+    <col min="1" max="6" width="30.7109375" style="26" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="32" t="s">
-        <v>464</v>
-      </c>
-      <c r="B1" s="32" t="s">
+    <row r="1" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="126" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="128"/>
+    </row>
+    <row r="2" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="129" t="s">
+        <v>471</v>
+      </c>
+      <c r="B2" s="129" t="s">
+        <v>471</v>
+      </c>
+      <c r="C2" s="129" t="s">
+        <v>471</v>
+      </c>
+      <c r="D2" s="129" t="s">
+        <v>471</v>
+      </c>
+      <c r="E2" s="129" t="s">
+        <v>471</v>
+      </c>
+      <c r="F2" s="129" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="118">
+        <v>0</v>
+      </c>
+      <c r="B3" s="119">
+        <v>1</v>
+      </c>
+      <c r="C3" s="119">
+        <v>2</v>
+      </c>
+      <c r="D3" s="118">
+        <v>3</v>
+      </c>
+      <c r="E3" s="119">
+        <v>4</v>
+      </c>
+      <c r="F3" s="118">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="120">
+        <v>25</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="C4" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="D4" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="D1" s="32" t="s">
-        <v>308</v>
-      </c>
-      <c r="E1" s="116" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="31" t="s">
+      <c r="E4" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="F4" s="120">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="121">
+        <v>24</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="C5" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="D5" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="E5" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="E2" s="117"/>
-    </row>
-    <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="30" t="s">
+      <c r="F5" s="120">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="120">
+        <v>23</v>
+      </c>
+      <c r="B6" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="C6" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="C3" s="29" t="s">
-        <v>330</v>
-      </c>
-      <c r="D3" s="30" t="s">
+      <c r="D6" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="E6" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="E3" s="117"/>
-    </row>
-    <row r="4" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="34" t="s">
+      <c r="F6" s="123">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="121">
+        <v>22</v>
+      </c>
+      <c r="B7" s="30" t="s">
         <v>210</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="C7" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="D7" s="52" t="s">
         <v>216</v>
       </c>
-      <c r="D4" s="34" t="s">
-        <v>373</v>
-      </c>
-      <c r="E4" s="58" t="s">
-        <v>212</v>
+      <c r="E7" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="F7" s="120">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="120">
+        <v>21</v>
+      </c>
+      <c r="B8" s="98" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="111" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="112"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="123">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="121">
+        <v>20</v>
+      </c>
+      <c r="B9" s="109" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="E9" s="110" t="s">
+        <v>372</v>
+      </c>
+      <c r="F9" s="120">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="120">
+        <v>19</v>
+      </c>
+      <c r="B10" s="115" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="116" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" s="117" t="s">
+        <v>351</v>
+      </c>
+      <c r="E10" s="116" t="s">
+        <v>223</v>
+      </c>
+      <c r="F10" s="123">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="122">
+        <v>18</v>
+      </c>
+      <c r="B11" s="124">
+        <v>17</v>
+      </c>
+      <c r="C11" s="125">
+        <v>16</v>
+      </c>
+      <c r="D11" s="124">
+        <v>15</v>
+      </c>
+      <c r="E11" s="125">
+        <v>14</v>
+      </c>
+      <c r="F11" s="120">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="E1:E3"/>
+  <mergeCells count="2">
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="3" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{993D694B-0EED-4AC2-99EA-DCB06F52FB86}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CEB427C-0CB4-4E8D-8367-36F6DD891282}">
+  <dimension ref="A1:CA6"/>
+  <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="30.66796875" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" style="53"/>
+    <col min="2" max="2" width="19.7109375" style="65"/>
+    <col min="4" max="4" width="19.7109375" style="53"/>
+    <col min="6" max="6" width="19.7109375" style="53"/>
+    <col min="8" max="8" width="19.7109375" style="53"/>
+    <col min="10" max="10" width="19.7109375" style="53"/>
+    <col min="12" max="12" width="19.7109375" style="53"/>
+    <col min="14" max="14" width="19.7109375" style="53"/>
+    <col min="16" max="16" width="19.7109375" style="53"/>
+    <col min="18" max="18" width="19.7109375" style="53"/>
+    <col min="20" max="20" width="19.7109375" style="53"/>
+    <col min="22" max="22" width="19.7109375" style="53"/>
+    <col min="24" max="24" width="19.7109375" style="53"/>
+    <col min="26" max="26" width="19.7109375" style="53"/>
+    <col min="28" max="28" width="19.7109375" style="53"/>
+    <col min="30" max="30" width="19.7109375" style="71"/>
+    <col min="31" max="32" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.7109375" customWidth="1"/>
+    <col min="42" max="42" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.7109375" style="71" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19.7109375" style="71" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="19.7109375" style="53"/>
+    <col min="63" max="63" width="19.7109375" style="53"/>
+    <col min="65" max="65" width="19.7109375" style="53"/>
+    <col min="67" max="67" width="19.7109375" style="53"/>
+    <col min="69" max="70" width="19.7109375" style="53"/>
+    <col min="71" max="71" width="19.7109375" style="65"/>
+    <col min="73" max="73" width="19.7109375" style="53"/>
+    <col min="75" max="75" width="19.7109375" style="53"/>
+    <col min="77" max="77" width="19.7109375" style="53"/>
+    <col min="79" max="79" width="19.7109375" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>352</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="E1" s="118" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="56" t="s">
-        <v>210</v>
-      </c>
-      <c r="B2" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="D2" s="104" t="s">
-        <v>373</v>
-      </c>
-      <c r="E2" s="119"/>
-    </row>
-    <row r="3" spans="1:5" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="105" t="s">
-        <v>244</v>
-      </c>
-      <c r="B3" s="120" t="s">
-        <v>245</v>
-      </c>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="122"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="B3:E3"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{435A2588-0653-4FD0-85C3-EF9530FC726F}">
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="15" width="17.890625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="123">
-        <v>0</v>
-      </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="123">
-        <v>1</v>
-      </c>
-      <c r="D1" s="124"/>
-      <c r="E1" s="123">
-        <v>2</v>
-      </c>
-      <c r="F1" s="124"/>
-      <c r="G1" s="123">
-        <v>3</v>
-      </c>
-      <c r="H1" s="124"/>
-      <c r="I1" s="123">
-        <v>4</v>
-      </c>
-      <c r="J1" s="124"/>
-      <c r="K1" s="123">
-        <v>5</v>
-      </c>
-      <c r="L1" s="124"/>
-      <c r="M1" s="123">
-        <v>6</v>
-      </c>
-      <c r="N1" s="124"/>
-    </row>
-    <row r="2" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="125">
-        <v>19</v>
-      </c>
-      <c r="B2" s="136" t="s">
-        <v>246</v>
-      </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="138"/>
-      <c r="N2" s="125">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="126"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="140"/>
-      <c r="D3" s="140"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="140"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="126"/>
-    </row>
-    <row r="4" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="125">
-        <v>18</v>
-      </c>
-      <c r="B4" s="142"/>
-      <c r="C4" s="143"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
-      <c r="I4" s="143"/>
-      <c r="J4" s="143"/>
-      <c r="K4" s="143"/>
-      <c r="L4" s="143"/>
-      <c r="M4" s="144"/>
-      <c r="N4" s="125">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="126"/>
-      <c r="B5" s="127" t="s">
-        <v>247</v>
-      </c>
-      <c r="C5" s="128"/>
-      <c r="D5" s="131" t="s">
-        <v>247</v>
-      </c>
-      <c r="E5" s="132"/>
-      <c r="F5" s="131" t="s">
-        <v>247</v>
-      </c>
-      <c r="G5" s="132"/>
-      <c r="H5" s="131" t="s">
-        <v>247</v>
-      </c>
-      <c r="I5" s="132"/>
-      <c r="J5" s="131" t="s">
-        <v>247</v>
-      </c>
-      <c r="K5" s="132"/>
-      <c r="L5" s="131" t="s">
-        <v>247</v>
-      </c>
-      <c r="M5" s="135"/>
-      <c r="N5" s="126"/>
-    </row>
-    <row r="6" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="125">
-        <v>17</v>
-      </c>
-      <c r="B6" s="127"/>
-      <c r="C6" s="128"/>
-      <c r="D6" s="127"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="127"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="127"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="127"/>
-      <c r="K6" s="133"/>
-      <c r="L6" s="127"/>
-      <c r="M6" s="128"/>
-      <c r="N6" s="125">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="126"/>
-      <c r="B7" s="129"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="134"/>
-      <c r="F7" s="129"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="129"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="129"/>
-      <c r="K7" s="134"/>
-      <c r="L7" s="129"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="126"/>
-    </row>
-    <row r="8" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123">
-        <v>16</v>
-      </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="123">
-        <v>15</v>
-      </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="123">
-        <v>14</v>
-      </c>
-      <c r="F8" s="124"/>
-      <c r="G8" s="123">
-        <v>13</v>
-      </c>
-      <c r="H8" s="124"/>
-      <c r="I8" s="123">
-        <v>12</v>
-      </c>
-      <c r="J8" s="124"/>
-      <c r="K8" s="123">
-        <v>11</v>
-      </c>
-      <c r="L8" s="124"/>
-      <c r="M8" s="123">
-        <v>10</v>
-      </c>
-      <c r="N8" s="124"/>
-    </row>
-  </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="F5:G7"/>
-    <mergeCell ref="H5:I7"/>
-    <mergeCell ref="J5:K7"/>
-    <mergeCell ref="L5:M7"/>
-    <mergeCell ref="B2:M4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B5:C7"/>
-    <mergeCell ref="D5:E7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CEB427C-0CB4-4E8D-8367-36F6DD891282}">
-  <dimension ref="A1:CA6"/>
-  <sheetFormatPr defaultColWidth="19.7734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="19.7734375" style="59"/>
-    <col min="2" max="2" width="19.7734375" style="71"/>
-    <col min="4" max="4" width="19.7734375" style="59"/>
-    <col min="6" max="6" width="19.7734375" style="59"/>
-    <col min="8" max="8" width="19.7734375" style="59"/>
-    <col min="10" max="10" width="19.7734375" style="59"/>
-    <col min="12" max="12" width="19.7734375" style="59"/>
-    <col min="14" max="14" width="19.7734375" style="59"/>
-    <col min="16" max="16" width="19.7734375" style="59"/>
-    <col min="18" max="18" width="19.7734375" style="59"/>
-    <col min="20" max="20" width="19.7734375" style="59"/>
-    <col min="22" max="22" width="19.7734375" style="59"/>
-    <col min="24" max="24" width="19.7734375" style="59"/>
-    <col min="26" max="26" width="19.7734375" style="59"/>
-    <col min="28" max="28" width="19.7734375" style="59"/>
-    <col min="30" max="30" width="19.7734375" style="77"/>
-    <col min="31" max="32" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.7734375" customWidth="1"/>
-    <col min="42" max="42" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.7734375" style="77" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="19.7734375" style="59" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="19.7734375" style="77" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="19.7734375" style="59"/>
-    <col min="63" max="63" width="19.7734375" style="59"/>
-    <col min="65" max="65" width="19.7734375" style="59"/>
-    <col min="67" max="67" width="19.7734375" style="59"/>
-    <col min="69" max="70" width="19.7734375" style="59"/>
-    <col min="71" max="71" width="19.7734375" style="71"/>
-    <col min="73" max="73" width="19.7734375" style="59"/>
-    <col min="75" max="75" width="19.7734375" style="59"/>
-    <col min="77" max="77" width="19.7734375" style="59"/>
-    <col min="79" max="79" width="19.7734375" style="59"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:79" s="75" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="73" t="str">
+    <row r="1" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="67" t="str">
         <f>Cards!B2</f>
         <v>Fillibuster</v>
       </c>
-      <c r="B1" s="74" t="str">
+      <c r="B1" s="68" t="str">
         <f>Cards!B3</f>
         <v>Skillful Orators</v>
       </c>
-      <c r="C1" s="75" t="str">
+      <c r="C1" s="69" t="str">
         <f>Cards!B4</f>
         <v>Collection Stations</v>
       </c>
-      <c r="D1" s="73" t="str">
+      <c r="D1" s="67" t="str">
         <f>Cards!B5</f>
         <v>Brown Nose</v>
       </c>
-      <c r="E1" s="75" t="str">
+      <c r="E1" s="69" t="str">
         <f>Cards!B6</f>
         <v>Mysterious Windfalls</v>
       </c>
-      <c r="F1" s="73" t="str">
+      <c r="F1" s="67" t="str">
         <f>Cards!B7</f>
         <v>Lobbyists</v>
       </c>
-      <c r="G1" s="75" t="e">
-        <f>Cards!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H1" s="73" t="e">
-        <f>Cards!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I1" s="75" t="str">
+      <c r="G1" s="69" t="str">
         <f>Cards!B8</f>
         <v>Loyal Citizenry</v>
       </c>
-      <c r="J1" s="73" t="str">
+      <c r="H1" s="67" t="str">
         <f>Cards!B9</f>
         <v>Silver-Tongue</v>
       </c>
-      <c r="K1" s="75" t="str">
+      <c r="I1" s="69" t="str">
+        <f>Cards!B8</f>
+        <v>Loyal Citizenry</v>
+      </c>
+      <c r="J1" s="67" t="str">
+        <f>Cards!B9</f>
+        <v>Silver-Tongue</v>
+      </c>
+      <c r="K1" s="69" t="str">
         <f>Cards!B10</f>
         <v>Royal Bribes</v>
       </c>
-      <c r="L1" s="73" t="str">
+      <c r="L1" s="67" t="str">
         <f>Cards!B11</f>
         <v>Courtroom Gambling</v>
       </c>
-      <c r="M1" s="75" t="str">
+      <c r="M1" s="69" t="str">
         <f>Cards!B12</f>
         <v>Market Niche</v>
       </c>
-      <c r="N1" s="73" t="str">
+      <c r="N1" s="67" t="str">
         <f>Cards!B13</f>
         <v>Genius Commanders</v>
       </c>
-      <c r="O1" s="75" t="str">
+      <c r="O1" s="69" t="str">
         <f>Cards!B14</f>
         <v>Damage Redemption</v>
       </c>
-      <c r="P1" s="73" t="str">
+      <c r="P1" s="67" t="str">
         <f>Cards!B15</f>
         <v>Undeniable Advisors</v>
       </c>
-      <c r="Q1" s="75" t="str">
+      <c r="Q1" s="69" t="str">
         <f>Cards!B16</f>
         <v>Heavy Overtime</v>
       </c>
-      <c r="R1" s="73" t="str">
+      <c r="R1" s="67" t="str">
         <f>Cards!B17</f>
         <v>Bulk Purchaser</v>
       </c>
-      <c r="S1" s="75" t="str">
+      <c r="S1" s="69" t="str">
         <f>Cards!B18</f>
         <v>Valuable Cargo</v>
       </c>
-      <c r="T1" s="73" t="str">
+      <c r="T1" s="67" t="str">
         <f>Cards!B19</f>
         <v>Elite Troops</v>
       </c>
-      <c r="U1" s="75" t="str">
+      <c r="U1" s="69" t="str">
         <f>Cards!B20</f>
         <v>Bazaar</v>
       </c>
-      <c r="V1" s="73" t="str">
+      <c r="V1" s="67" t="str">
         <f>Cards!B21</f>
         <v>Caravansaray</v>
       </c>
-      <c r="W1" s="75" t="str">
+      <c r="W1" s="69" t="str">
         <f>Cards!B22</f>
         <v>War Machines</v>
       </c>
-      <c r="X1" s="73" t="str">
+      <c r="X1" s="67" t="str">
         <f>Cards!B23</f>
         <v>Mock Trials</v>
       </c>
-      <c r="Y1" s="75" t="str">
+      <c r="Y1" s="69" t="str">
         <f>Cards!B24</f>
         <v>Desperate Attorneys</v>
       </c>
-      <c r="Z1" s="73" t="str">
+      <c r="Z1" s="67" t="str">
         <f>Cards!B25</f>
         <v>Eager Laborers</v>
       </c>
-      <c r="AA1" s="75" t="str">
+      <c r="AA1" s="69" t="str">
         <f>Cards!B26</f>
         <v>Wary Guards</v>
       </c>
-      <c r="AB1" s="73" t="str">
+      <c r="AB1" s="67" t="str">
         <f>Cards!B27</f>
         <v>Information Security</v>
       </c>
-      <c r="AC1" s="75" t="str">
+      <c r="AC1" s="69" t="str">
         <f>Cards!B28</f>
         <v>Blood Pact</v>
       </c>
-      <c r="AD1" s="76" t="str">
+      <c r="AD1" s="70" t="str">
         <f>Cards!B29</f>
         <v>Expert Broker</v>
       </c>
-      <c r="AE1" s="73" t="str">
+      <c r="AE1" s="67" t="str">
         <f>Cards!B30</f>
         <v>Codependent Relationship</v>
       </c>
-      <c r="AF1" s="73" t="str">
+      <c r="AF1" s="67" t="str">
         <f>Cards!B31</f>
         <v>Dangerous Promises</v>
       </c>
-      <c r="AG1" s="75" t="str">
+      <c r="AG1" s="69" t="str">
         <f>Cards!B32</f>
         <v>Large Middle Class</v>
       </c>
-      <c r="AH1" s="73" t="str">
+      <c r="AH1" s="67" t="str">
         <f>Cards!B33</f>
         <v>Innovation Hub</v>
       </c>
-      <c r="AI1" s="75" t="str">
+      <c r="AI1" s="69" t="str">
         <f>Cards!B34</f>
         <v>Fire Temple</v>
       </c>
-      <c r="AJ1" s="73" t="str">
+      <c r="AJ1" s="67" t="str">
         <f>Cards!B35</f>
         <v>Kingdom Advocates</v>
       </c>
-      <c r="AK1" s="75" t="str">
+      <c r="AK1" s="69" t="str">
         <f>Cards!B36</f>
         <v>Soup Kitchens</v>
       </c>
-      <c r="AL1" s="73" t="str">
+      <c r="AL1" s="67" t="str">
         <f>Cards!B37</f>
         <v>Abusive Power</v>
       </c>
-      <c r="AM1" s="75" t="str">
+      <c r="AM1" s="69" t="str">
         <f>Cards!B38</f>
         <v>Painful Progress</v>
       </c>
-      <c r="AN1" s="73" t="str">
+      <c r="AN1" s="67" t="str">
         <f>Cards!B39</f>
         <v>Iron Command</v>
       </c>
-      <c r="AO1" s="75" t="str">
+      <c r="AO1" s="69" t="str">
         <f t="shared" ref="AO1:AX2" si="0">A1</f>
         <v>Fillibuster</v>
       </c>
-      <c r="AP1" s="73" t="str">
+      <c r="AP1" s="67" t="str">
         <f t="shared" si="0"/>
         <v>Skillful Orators</v>
       </c>
-      <c r="AQ1" s="75" t="str">
+      <c r="AQ1" s="69" t="str">
         <f t="shared" si="0"/>
         <v>Collection Stations</v>
       </c>
-      <c r="AR1" s="73" t="str">
+      <c r="AR1" s="67" t="str">
         <f t="shared" si="0"/>
         <v>Brown Nose</v>
       </c>
-      <c r="AS1" s="75" t="str">
+      <c r="AS1" s="69" t="str">
         <f t="shared" si="0"/>
         <v>Mysterious Windfalls</v>
       </c>
-      <c r="AT1" s="73" t="str">
+      <c r="AT1" s="67" t="str">
         <f t="shared" si="0"/>
         <v>Lobbyists</v>
       </c>
-      <c r="AU1" s="75" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="AV1" s="73" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="AW1" s="75" t="str">
+      <c r="AU1" s="69" t="str">
         <f t="shared" si="0"/>
         <v>Loyal Citizenry</v>
       </c>
-      <c r="AX1" s="76" t="str">
+      <c r="AV1" s="67" t="str">
         <f t="shared" si="0"/>
         <v>Silver-Tongue</v>
       </c>
-      <c r="AY1" s="73" t="str">
+      <c r="AW1" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v>Loyal Citizenry</v>
+      </c>
+      <c r="AX1" s="70" t="str">
+        <f t="shared" si="0"/>
+        <v>Silver-Tongue</v>
+      </c>
+      <c r="AY1" s="67" t="str">
         <f t="shared" ref="AY1:BH2" si="1">K1</f>
         <v>Royal Bribes</v>
       </c>
-      <c r="AZ1" s="75" t="str">
+      <c r="AZ1" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Courtroom Gambling</v>
       </c>
-      <c r="BA1" s="73" t="str">
+      <c r="BA1" s="67" t="str">
         <f t="shared" si="1"/>
         <v>Market Niche</v>
       </c>
-      <c r="BB1" s="75" t="str">
+      <c r="BB1" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Genius Commanders</v>
       </c>
-      <c r="BC1" s="73" t="str">
+      <c r="BC1" s="67" t="str">
         <f t="shared" si="1"/>
         <v>Damage Redemption</v>
       </c>
-      <c r="BD1" s="75" t="str">
+      <c r="BD1" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Undeniable Advisors</v>
       </c>
-      <c r="BE1" s="73" t="str">
+      <c r="BE1" s="67" t="str">
         <f t="shared" si="1"/>
         <v>Heavy Overtime</v>
       </c>
-      <c r="BF1" s="75" t="str">
+      <c r="BF1" s="69" t="str">
         <f t="shared" si="1"/>
         <v>Bulk Purchaser</v>
       </c>
-      <c r="BG1" s="73" t="str">
+      <c r="BG1" s="67" t="str">
         <f t="shared" si="1"/>
         <v>Valuable Cargo</v>
       </c>
-      <c r="BH1" s="76" t="str">
+      <c r="BH1" s="70" t="str">
         <f t="shared" si="1"/>
         <v>Elite Troops</v>
       </c>
-      <c r="BI1" s="73" t="str">
+      <c r="BI1" s="67" t="str">
         <f t="shared" ref="BI1:BR2" si="2">U1</f>
         <v>Bazaar</v>
       </c>
-      <c r="BJ1" s="75" t="str">
+      <c r="BJ1" s="69" t="str">
         <f t="shared" si="2"/>
         <v>Caravansaray</v>
       </c>
-      <c r="BK1" s="73" t="str">
+      <c r="BK1" s="67" t="str">
         <f t="shared" si="2"/>
         <v>War Machines</v>
       </c>
-      <c r="BL1" s="75" t="str">
+      <c r="BL1" s="69" t="str">
         <f t="shared" si="2"/>
         <v>Mock Trials</v>
       </c>
-      <c r="BM1" s="73" t="str">
+      <c r="BM1" s="67" t="str">
         <f t="shared" si="2"/>
         <v>Desperate Attorneys</v>
       </c>
-      <c r="BN1" s="75" t="str">
+      <c r="BN1" s="69" t="str">
         <f t="shared" si="2"/>
         <v>Eager Laborers</v>
       </c>
-      <c r="BO1" s="73" t="str">
+      <c r="BO1" s="67" t="str">
         <f t="shared" si="2"/>
         <v>Wary Guards</v>
       </c>
-      <c r="BP1" s="75" t="str">
+      <c r="BP1" s="69" t="str">
         <f t="shared" si="2"/>
         <v>Information Security</v>
       </c>
-      <c r="BQ1" s="73" t="str">
+      <c r="BQ1" s="67" t="str">
         <f t="shared" si="2"/>
         <v>Blood Pact</v>
       </c>
-      <c r="BR1" s="73" t="str">
+      <c r="BR1" s="67" t="str">
         <f t="shared" si="2"/>
         <v>Expert Broker</v>
       </c>
-      <c r="BS1" s="73"/>
-      <c r="BU1" s="73"/>
-      <c r="BW1" s="73"/>
-      <c r="BY1" s="73"/>
-      <c r="CA1" s="73"/>
-    </row>
-    <row r="2" spans="1:79" s="98" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="99" t="str">
+      <c r="BS1" s="67"/>
+      <c r="BU1" s="67"/>
+      <c r="BW1" s="67"/>
+      <c r="BY1" s="67"/>
+      <c r="CA1" s="67"/>
+    </row>
+    <row r="2" spans="1:79" s="92" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="93" t="str">
         <f>Cards!C2</f>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
       </c>
-      <c r="B2" s="99" t="str">
+      <c r="B2" s="93" t="str">
         <f>Cards!C3</f>
         <v>Move the Law $L6 additional places forward in the queue during Prioritize</v>
       </c>
-      <c r="C2" s="98" t="str">
+      <c r="C2" s="92" t="str">
         <f>Cards!C4</f>
         <v xml:space="preserve">You may keep up to $L6 additional Coins when Taxing other Players </v>
       </c>
-      <c r="D2" s="99" t="str">
+      <c r="D2" s="93" t="str">
         <f>Cards!C5</f>
         <v>Gain $L3 additional Coins during Flatter</v>
       </c>
-      <c r="E2" s="98" t="str">
+      <c r="E2" s="92" t="str">
         <f>Cards!C6</f>
         <v>Gain $L3 more Commodities per Coin when Buying from the Undermarket</v>
       </c>
-      <c r="F2" s="99" t="str">
+      <c r="F2" s="93" t="str">
         <f>Cards!C7</f>
         <v>Add $L3 additional Law cards to the bottom of the queue during Petition</v>
       </c>
-      <c r="G2" s="98" t="e">
-        <f>Cards!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H2" s="99" t="e">
-        <f>Cards!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I2" s="99" t="str">
+      <c r="G2" s="92" t="str">
         <f>Cards!C8</f>
         <v>Purchase up to $L6 additional Troops during Recruit (at normal cost)</v>
       </c>
-      <c r="J2" s="99" t="str">
+      <c r="H2" s="93" t="str">
         <f>Cards!C9</f>
         <v>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</v>
       </c>
-      <c r="K2" s="98" t="str">
+      <c r="I2" s="93" t="str">
+        <f>Cards!C8</f>
+        <v>Purchase up to $L6 additional Troops during Recruit (at normal cost)</v>
+      </c>
+      <c r="J2" s="93" t="str">
+        <f>Cards!C9</f>
+        <v>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</v>
+      </c>
+      <c r="K2" s="92" t="str">
         <f>Cards!C10</f>
         <v>Gain $L3 more Commodities per Coin when Buying from the Court</v>
       </c>
-      <c r="L2" s="99" t="str">
+      <c r="L2" s="93" t="str">
         <f>Cards!C11</f>
         <v>Gain $L3 additional Coins from outside the Royal Bank when winning a Trial</v>
       </c>
-      <c r="M2" s="98" t="str">
+      <c r="M2" s="92" t="str">
         <f>Cards!C12</f>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Undermarket</v>
       </c>
-      <c r="N2" s="99" t="str">
+      <c r="N2" s="93" t="str">
         <f>Cards!C13</f>
         <v>Draw $L6 additional cards from any decks during Brainstorm</v>
       </c>
-      <c r="O2" s="98" t="str">
+      <c r="O2" s="92" t="str">
         <f>Cards!C14</f>
         <v>Purchase $L3 Spies (at normal cost) when targeted by a Scheme</v>
       </c>
-      <c r="P2" s="99" t="str">
+      <c r="P2" s="93" t="str">
         <f>Cards!C15</f>
         <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
       </c>
-      <c r="Q2" s="98" t="str">
+      <c r="Q2" s="92" t="str">
         <f>Cards!C16</f>
         <v>You may repeat $L3 Provincial Actions per round</v>
       </c>
-      <c r="R2" s="99" t="str">
+      <c r="R2" s="93" t="str">
         <f>Cards!C17</f>
         <v>Trade up to $L3 additional Coins when Buying from the Court</v>
       </c>
-      <c r="S2" s="98" t="str">
+      <c r="S2" s="92" t="str">
         <f>Cards!C18</f>
         <v>Trade for up to $L3 additional Coins when Selling to the Court</v>
       </c>
-      <c r="T2" s="99" t="str">
+      <c r="T2" s="93" t="str">
         <f>Cards!C19</f>
         <v>Gain $L3 additional Coins from the Royal Bank when Deploying Troops</v>
       </c>
-      <c r="U2" s="98" t="str">
+      <c r="U2" s="92" t="str">
         <f>Cards!C20</f>
         <v>Provides private Buy Action at Market Rate + $L3</v>
       </c>
-      <c r="V2" s="99" t="str">
+      <c r="V2" s="93" t="str">
         <f>Cards!C21</f>
         <v>Provides private Sell Action at Market Rate - $L3</v>
       </c>
-      <c r="W2" s="98" t="str">
+      <c r="W2" s="92" t="str">
         <f>Cards!C22</f>
         <v>Purchase and immediately add up to $L3 Troops to your force when deploying them</v>
       </c>
-      <c r="X2" s="99" t="str">
+      <c r="X2" s="93" t="str">
         <f>Cards!C23</f>
         <v>Add $L3 Hits to each Roll during a Trial</v>
       </c>
-      <c r="Y2" s="98" t="str">
+      <c r="Y2" s="92" t="str">
         <f>Cards!C24</f>
         <v>Add $L6 additional dice to each Roll during a Trial</v>
       </c>
-      <c r="Z2" s="99" t="str">
+      <c r="Z2" s="93" t="str">
         <f>Cards!C25</f>
         <v>Collect $L6 additional Commodities during Collect</v>
       </c>
-      <c r="AA2" s="98" t="str">
+      <c r="AA2" s="92" t="str">
         <f>Cards!C26</f>
         <v>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</v>
       </c>
-      <c r="AB2" s="99" t="str">
+      <c r="AB2" s="93" t="str">
         <f>Cards!C27</f>
         <v>Subtract $L3 from Scheme Card rolls</v>
       </c>
-      <c r="AC2" s="98" t="str">
+      <c r="AC2" s="92" t="str">
         <f>Cards!C28</f>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Undermarket</v>
       </c>
-      <c r="AD2" s="100" t="str">
+      <c r="AD2" s="94" t="str">
         <f>Cards!C29</f>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
       </c>
-      <c r="AE2" s="99" t="str">
+      <c r="AE2" s="93" t="str">
         <f>Cards!C30</f>
         <v>Trade up to $L3 additional Coins when Buying from the Undermarket</v>
       </c>
-      <c r="AF2" s="99" t="str">
+      <c r="AF2" s="93" t="str">
         <f>Cards!C31</f>
         <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
       </c>
-      <c r="AG2" s="98" t="str">
+      <c r="AG2" s="92" t="str">
         <f>Cards!C32</f>
         <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
       </c>
-      <c r="AH2" s="99" t="str">
+      <c r="AH2" s="93" t="str">
         <f>Cards!C33</f>
         <v>Provides private Monetize Action at Market Rate + $L3</v>
       </c>
-      <c r="AI2" s="98" t="str">
+      <c r="AI2" s="92" t="str">
         <f>Cards!C34</f>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
       </c>
-      <c r="AJ2" s="99" t="str">
+      <c r="AJ2" s="93" t="str">
         <f>Cards!C35</f>
         <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
       </c>
-      <c r="AK2" s="98" t="str">
+      <c r="AK2" s="92" t="str">
         <f>Cards!C36</f>
         <v>Provides Private Donate action with no penalty and convert $L3 additional Coins.</v>
       </c>
-      <c r="AL2" s="99" t="str">
+      <c r="AL2" s="93" t="str">
         <f>Cards!C37</f>
         <v>Convert $L3 additional Coins during Undermarket Donate</v>
       </c>
-      <c r="AM2" s="98" t="str">
+      <c r="AM2" s="92" t="str">
         <f>Cards!C38</f>
         <v>You may repeat Undermarket Actions at double the penalty</v>
       </c>
-      <c r="AN2" s="99" t="str">
+      <c r="AN2" s="93" t="str">
         <f>Cards!C39</f>
         <v>Deploy $L3 additional Troops during Deploy</v>
       </c>
-      <c r="AO2" s="98" t="str">
+      <c r="AO2" s="92" t="str">
         <f t="shared" si="0"/>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
       </c>
-      <c r="AP2" s="99" t="str">
+      <c r="AP2" s="93" t="str">
         <f t="shared" si="0"/>
         <v>Move the Law $L6 additional places forward in the queue during Prioritize</v>
       </c>
-      <c r="AQ2" s="98" t="str">
+      <c r="AQ2" s="92" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">You may keep up to $L6 additional Coins when Taxing other Players </v>
       </c>
-      <c r="AR2" s="99" t="str">
+      <c r="AR2" s="93" t="str">
         <f t="shared" si="0"/>
         <v>Gain $L3 additional Coins during Flatter</v>
       </c>
-      <c r="AS2" s="98" t="str">
+      <c r="AS2" s="92" t="str">
         <f t="shared" si="0"/>
         <v>Gain $L3 more Commodities per Coin when Buying from the Undermarket</v>
       </c>
-      <c r="AT2" s="99" t="str">
+      <c r="AT2" s="93" t="str">
         <f t="shared" si="0"/>
         <v>Add $L3 additional Law cards to the bottom of the queue during Petition</v>
       </c>
-      <c r="AU2" s="98" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="AV2" s="99" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="AW2" s="98" t="str">
+      <c r="AU2" s="92" t="str">
         <f t="shared" si="0"/>
         <v>Purchase up to $L6 additional Troops during Recruit (at normal cost)</v>
       </c>
-      <c r="AX2" s="100" t="str">
+      <c r="AV2" s="93" t="str">
         <f t="shared" si="0"/>
         <v>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</v>
       </c>
-      <c r="AY2" s="99" t="str">
+      <c r="AW2" s="92" t="str">
+        <f t="shared" si="0"/>
+        <v>Purchase up to $L6 additional Troops during Recruit (at normal cost)</v>
+      </c>
+      <c r="AX2" s="94" t="str">
+        <f t="shared" si="0"/>
+        <v>Purchase up to $L6 additional Spies during Infiltrate (at normal cost)</v>
+      </c>
+      <c r="AY2" s="93" t="str">
         <f t="shared" si="1"/>
         <v>Gain $L3 more Commodities per Coin when Buying from the Court</v>
       </c>
-      <c r="AZ2" s="98" t="str">
+      <c r="AZ2" s="92" t="str">
         <f t="shared" si="1"/>
         <v>Gain $L3 additional Coins from outside the Royal Bank when winning a Trial</v>
       </c>
-      <c r="BA2" s="99" t="str">
+      <c r="BA2" s="93" t="str">
         <f t="shared" si="1"/>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Undermarket</v>
       </c>
-      <c r="BB2" s="98" t="str">
+      <c r="BB2" s="92" t="str">
         <f t="shared" si="1"/>
         <v>Draw $L6 additional cards from any decks during Brainstorm</v>
       </c>
-      <c r="BC2" s="99" t="str">
+      <c r="BC2" s="93" t="str">
         <f t="shared" si="1"/>
         <v>Purchase $L3 Spies (at normal cost) when targeted by a Scheme</v>
       </c>
-      <c r="BD2" s="98" t="str">
+      <c r="BD2" s="92" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
       </c>
-      <c r="BE2" s="99" t="str">
+      <c r="BE2" s="93" t="str">
         <f t="shared" si="1"/>
         <v>You may repeat $L3 Provincial Actions per round</v>
       </c>
-      <c r="BF2" s="98" t="str">
+      <c r="BF2" s="92" t="str">
         <f t="shared" si="1"/>
         <v>Trade up to $L3 additional Coins when Buying from the Court</v>
       </c>
-      <c r="BG2" s="99" t="str">
+      <c r="BG2" s="93" t="str">
         <f t="shared" si="1"/>
         <v>Trade for up to $L3 additional Coins when Selling to the Court</v>
       </c>
-      <c r="BH2" s="100" t="str">
+      <c r="BH2" s="94" t="str">
         <f t="shared" si="1"/>
         <v>Gain $L3 additional Coins from the Royal Bank when Deploying Troops</v>
       </c>
-      <c r="BI2" s="99" t="str">
+      <c r="BI2" s="93" t="str">
         <f t="shared" si="2"/>
         <v>Provides private Buy Action at Market Rate + $L3</v>
       </c>
-      <c r="BJ2" s="98" t="str">
+      <c r="BJ2" s="92" t="str">
         <f t="shared" si="2"/>
         <v>Provides private Sell Action at Market Rate - $L3</v>
       </c>
-      <c r="BK2" s="99" t="str">
+      <c r="BK2" s="93" t="str">
         <f t="shared" si="2"/>
         <v>Purchase and immediately add up to $L3 Troops to your force when deploying them</v>
       </c>
-      <c r="BL2" s="98" t="str">
+      <c r="BL2" s="92" t="str">
         <f t="shared" si="2"/>
         <v>Add $L3 Hits to each Roll during a Trial</v>
       </c>
-      <c r="BM2" s="99" t="str">
+      <c r="BM2" s="93" t="str">
         <f t="shared" si="2"/>
         <v>Add $L6 additional dice to each Roll during a Trial</v>
       </c>
-      <c r="BN2" s="98" t="str">
+      <c r="BN2" s="92" t="str">
         <f t="shared" si="2"/>
         <v>Collect $L6 additional Commodities during Collect</v>
       </c>
-      <c r="BO2" s="99" t="str">
+      <c r="BO2" s="93" t="str">
         <f t="shared" si="2"/>
         <v>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</v>
       </c>
-      <c r="BP2" s="98" t="str">
+      <c r="BP2" s="92" t="str">
         <f t="shared" si="2"/>
         <v>Subtract $L3 from Scheme Card rolls</v>
       </c>
-      <c r="BQ2" s="78" t="str">
+      <c r="BQ2" s="72" t="str">
         <f t="shared" si="2"/>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Undermarket</v>
       </c>
-      <c r="BR2" s="99" t="str">
+      <c r="BR2" s="93" t="str">
         <f t="shared" si="2"/>
         <v>Spend $L3 fewer Commodities per Coin when Selling to the Court</v>
       </c>
-      <c r="BS2" s="78"/>
-      <c r="BU2" s="99"/>
-      <c r="BW2" s="99"/>
-      <c r="BY2" s="99"/>
-      <c r="CA2" s="99"/>
-    </row>
-    <row r="3" spans="1:79" s="75" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="73" t="str">
+      <c r="BS2" s="72"/>
+      <c r="BU2" s="93"/>
+      <c r="BW2" s="93"/>
+      <c r="BY2" s="93"/>
+      <c r="CA2" s="93"/>
+    </row>
+    <row r="3" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="67" t="str">
         <f>Cards!D2</f>
         <v>Full Coffers</v>
       </c>
-      <c r="B3" s="74" t="str">
+      <c r="B3" s="68" t="str">
         <f>Cards!D3</f>
         <v xml:space="preserve">Decentralized Wealth </v>
       </c>
-      <c r="C3" s="75" t="str">
+      <c r="C3" s="69" t="str">
         <f>Cards!D4</f>
         <v>Second Thoughts</v>
       </c>
-      <c r="D3" s="73" t="str">
+      <c r="D3" s="67" t="str">
         <f>Cards!D5</f>
         <v>Changing Times</v>
       </c>
-      <c r="E3" s="75" t="str">
+      <c r="E3" s="69" t="str">
         <f>Cards!D6</f>
         <v>Stable Economies</v>
       </c>
-      <c r="F3" s="73" t="str">
+      <c r="F3" s="67" t="str">
         <f>Cards!D7</f>
         <v>Unreasonable Distractions</v>
       </c>
-      <c r="G3" s="75" t="str">
+      <c r="G3" s="69" t="str">
         <f>Cards!D8</f>
         <v>Irregular Partiality</v>
       </c>
-      <c r="H3" s="73" t="str">
+      <c r="H3" s="67" t="str">
         <f>Cards!D9</f>
         <v>Royal Amendment</v>
       </c>
-      <c r="I3" s="75" t="str">
+      <c r="I3" s="69" t="str">
         <f>Cards!D10</f>
         <v>Honorable Accountability</v>
       </c>
-      <c r="J3" s="73" t="str">
+      <c r="J3" s="67" t="str">
         <f>Cards!D11</f>
         <v>Frivolous Pursuits</v>
       </c>
-      <c r="K3" s="75" t="str">
+      <c r="K3" s="69" t="str">
         <f>Cards!D12</f>
         <v>Economic Backbone</v>
       </c>
-      <c r="L3" s="73" t="str">
+      <c r="L3" s="67" t="str">
         <f>Cards!D13</f>
         <v>Collective Ownership</v>
       </c>
-      <c r="M3" s="75" t="str">
+      <c r="M3" s="69" t="str">
         <f>Cards!D14</f>
         <v>Aggressive Tactics</v>
       </c>
-      <c r="N3" s="73" t="str">
+      <c r="N3" s="67" t="str">
         <f>Cards!D15</f>
         <v>Home Defense</v>
       </c>
-      <c r="O3" s="75" t="str">
+      <c r="O3" s="69" t="str">
         <f>Cards!D16</f>
         <v>Valuable Advisors</v>
       </c>
-      <c r="P3" s="73" t="str">
+      <c r="P3" s="67" t="str">
         <f>Cards!D17</f>
         <v>Chattering Windbags</v>
       </c>
-      <c r="Q3" s="75" t="str">
+      <c r="Q3" s="69" t="str">
         <f>Cards!D18</f>
         <v>Realistic Priorities</v>
       </c>
-      <c r="R3" s="73" t="str">
+      <c r="R3" s="67" t="str">
         <f>Cards!D19</f>
         <v>Threat to the Throne</v>
       </c>
-      <c r="S3" s="75" t="str">
+      <c r="S3" s="69" t="str">
         <f>Cards!D20</f>
         <v>Stone Foundations</v>
       </c>
-      <c r="T3" s="73" t="str">
+      <c r="T3" s="67" t="str">
         <f>Cards!D21</f>
         <v>Environmental Guardians</v>
       </c>
-      <c r="U3" s="75" t="str">
+      <c r="U3" s="69" t="str">
         <f>Cards!D22</f>
         <v>Resilient Officer Corps</v>
       </c>
-      <c r="V3" s="73" t="str">
+      <c r="V3" s="67" t="str">
         <f>Cards!D23</f>
         <v>Bloated Bureaucracy</v>
       </c>
-      <c r="W3" s="75" t="str">
+      <c r="W3" s="69" t="str">
         <f>Cards!D24</f>
         <v>Police Force</v>
       </c>
-      <c r="X3" s="73" t="str">
+      <c r="X3" s="67" t="str">
         <f>Cards!D25</f>
         <v>Equal Partners</v>
       </c>
-      <c r="Y3" s="75" t="str">
+      <c r="Y3" s="69" t="str">
         <f>Cards!D26</f>
         <v>Criminal Identification</v>
       </c>
-      <c r="Z3" s="73" t="str">
+      <c r="Z3" s="67" t="str">
         <f>Cards!D27</f>
         <v>Honorable Marketplace</v>
       </c>
-      <c r="AA3" s="75" t="str">
+      <c r="AA3" s="69" t="str">
         <f>Cards!D28</f>
         <v>Engaged Empire</v>
       </c>
-      <c r="AB3" s="73" t="str">
+      <c r="AB3" s="67" t="str">
         <f>Cards!D29</f>
         <v>Suspicious Advisors</v>
       </c>
-      <c r="AC3" s="75" t="str">
+      <c r="AC3" s="69" t="str">
         <f>Cards!D30</f>
         <v>Contingency Plans</v>
       </c>
-      <c r="AD3" s="76" t="str">
+      <c r="AD3" s="70" t="str">
         <f>Cards!D31</f>
         <v>Worthless Procrastinators</v>
       </c>
-      <c r="AE3" s="73" t="str">
+      <c r="AE3" s="67" t="str">
         <f>Cards!D32</f>
         <v>Stalled Front</v>
       </c>
-      <c r="AF3" s="73" t="str">
+      <c r="AF3" s="67" t="str">
         <f>Cards!D33</f>
         <v>Quality Strength</v>
       </c>
-      <c r="AG3" s="75" t="str">
+      <c r="AG3" s="69" t="str">
         <f t="shared" ref="AG3:BL3" si="3">A3</f>
         <v>Full Coffers</v>
       </c>
-      <c r="AH3" s="73" t="str">
+      <c r="AH3" s="67" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">Decentralized Wealth </v>
       </c>
-      <c r="AI3" s="75" t="str">
+      <c r="AI3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Second Thoughts</v>
       </c>
-      <c r="AJ3" s="73" t="str">
+      <c r="AJ3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Changing Times</v>
       </c>
-      <c r="AK3" s="75" t="str">
+      <c r="AK3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Stable Economies</v>
       </c>
-      <c r="AL3" s="73" t="str">
+      <c r="AL3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Unreasonable Distractions</v>
       </c>
-      <c r="AM3" s="75" t="str">
+      <c r="AM3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Irregular Partiality</v>
       </c>
-      <c r="AN3" s="73" t="str">
+      <c r="AN3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Royal Amendment</v>
       </c>
-      <c r="AO3" s="75" t="str">
+      <c r="AO3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Honorable Accountability</v>
       </c>
-      <c r="AP3" s="73" t="str">
+      <c r="AP3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Frivolous Pursuits</v>
       </c>
-      <c r="AQ3" s="75" t="str">
+      <c r="AQ3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Economic Backbone</v>
       </c>
-      <c r="AR3" s="73" t="str">
+      <c r="AR3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Collective Ownership</v>
       </c>
-      <c r="AS3" s="75" t="str">
+      <c r="AS3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Aggressive Tactics</v>
       </c>
-      <c r="AT3" s="73" t="str">
+      <c r="AT3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Home Defense</v>
       </c>
-      <c r="AU3" s="75" t="str">
+      <c r="AU3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Valuable Advisors</v>
       </c>
-      <c r="AV3" s="73" t="str">
+      <c r="AV3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Chattering Windbags</v>
       </c>
-      <c r="AW3" s="75" t="str">
+      <c r="AW3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Realistic Priorities</v>
       </c>
-      <c r="AX3" s="76" t="str">
+      <c r="AX3" s="70" t="str">
         <f t="shared" si="3"/>
         <v>Threat to the Throne</v>
       </c>
-      <c r="AY3" s="73" t="str">
+      <c r="AY3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Stone Foundations</v>
       </c>
-      <c r="AZ3" s="75" t="str">
+      <c r="AZ3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Environmental Guardians</v>
       </c>
-      <c r="BA3" s="73" t="str">
+      <c r="BA3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Resilient Officer Corps</v>
       </c>
-      <c r="BB3" s="75" t="str">
+      <c r="BB3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Bloated Bureaucracy</v>
       </c>
-      <c r="BC3" s="73" t="str">
+      <c r="BC3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Police Force</v>
       </c>
-      <c r="BD3" s="75" t="str">
+      <c r="BD3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Equal Partners</v>
       </c>
-      <c r="BE3" s="73" t="str">
+      <c r="BE3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Criminal Identification</v>
       </c>
-      <c r="BF3" s="75" t="str">
+      <c r="BF3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Honorable Marketplace</v>
       </c>
-      <c r="BG3" s="73" t="str">
+      <c r="BG3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Engaged Empire</v>
       </c>
-      <c r="BH3" s="76" t="str">
+      <c r="BH3" s="70" t="str">
         <f t="shared" si="3"/>
         <v>Suspicious Advisors</v>
       </c>
-      <c r="BI3" s="73" t="str">
+      <c r="BI3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Contingency Plans</v>
       </c>
-      <c r="BJ3" s="75" t="str">
+      <c r="BJ3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Worthless Procrastinators</v>
       </c>
-      <c r="BK3" s="73" t="str">
+      <c r="BK3" s="67" t="str">
         <f t="shared" si="3"/>
         <v>Stalled Front</v>
       </c>
-      <c r="BL3" s="75" t="str">
+      <c r="BL3" s="69" t="str">
         <f t="shared" si="3"/>
         <v>Quality Strength</v>
       </c>
-      <c r="BM3" s="73"/>
-      <c r="BN3" s="75" t="str">
-        <f>AJ1</f>
+      <c r="BM3" s="67"/>
+      <c r="BN3" s="69" t="str">
+        <f t="shared" ref="BN3:BR4" si="4">AJ1</f>
         <v>Kingdom Advocates</v>
       </c>
-      <c r="BO3" s="73" t="str">
-        <f>AK1</f>
+      <c r="BO3" s="67" t="str">
+        <f t="shared" si="4"/>
         <v>Soup Kitchens</v>
       </c>
-      <c r="BP3" s="75" t="str">
-        <f>AL1</f>
+      <c r="BP3" s="69" t="str">
+        <f t="shared" si="4"/>
         <v>Abusive Power</v>
       </c>
-      <c r="BQ3" s="73" t="str">
-        <f>AM1</f>
+      <c r="BQ3" s="67" t="str">
+        <f t="shared" si="4"/>
         <v>Painful Progress</v>
       </c>
-      <c r="BR3" s="73" t="str">
-        <f>AN1</f>
+      <c r="BR3" s="67" t="str">
+        <f t="shared" si="4"/>
         <v>Iron Command</v>
       </c>
-      <c r="BS3" s="74"/>
-      <c r="BU3" s="73"/>
-      <c r="BW3" s="73"/>
-      <c r="BY3" s="73"/>
-      <c r="CA3" s="73"/>
-    </row>
-    <row r="4" spans="1:79" s="80" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="78" t="str">
+      <c r="BS3" s="68"/>
+      <c r="BU3" s="67"/>
+      <c r="BW3" s="67"/>
+      <c r="BY3" s="67"/>
+      <c r="CA3" s="67"/>
+    </row>
+    <row r="4" spans="1:79" s="74" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="72" t="str">
         <f>Cards!E2</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
-      <c r="B4" s="79" t="str">
+      <c r="B4" s="73" t="str">
         <f>Cards!E3</f>
         <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
-      <c r="C4" s="80" t="str">
+      <c r="C4" s="74" t="str">
         <f>Cards!E4</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="D4" s="78" t="str">
+      <c r="D4" s="72" t="str">
         <f>Cards!E5</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="E4" s="80" t="str">
+      <c r="E4" s="74" t="str">
         <f>Cards!E6</f>
         <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
       </c>
-      <c r="F4" s="78" t="str">
+      <c r="F4" s="72" t="str">
         <f>Cards!E7</f>
         <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
       </c>
-      <c r="G4" s="80" t="str">
+      <c r="G4" s="74" t="str">
         <f>Cards!E8</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="H4" s="78" t="str">
+      <c r="H4" s="72" t="str">
         <f>Cards!E9</f>
         <v>Change the boundary of an active Law to $L6</v>
       </c>
-      <c r="I4" s="80" t="str">
+      <c r="I4" s="74" t="str">
         <f>Cards!E10</f>
         <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy</v>
       </c>
-      <c r="J4" s="78" t="str">
+      <c r="J4" s="72" t="str">
         <f>Cards!E11</f>
         <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy</v>
       </c>
-      <c r="K4" s="80" t="str">
+      <c r="K4" s="74" t="str">
         <f>Cards!E12</f>
         <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
       </c>
-      <c r="L4" s="78" t="str">
+      <c r="L4" s="72" t="str">
         <f>Cards!E13</f>
         <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
       </c>
-      <c r="M4" s="80" t="str">
+      <c r="M4" s="74" t="str">
         <f>Cards!E14</f>
         <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
       </c>
-      <c r="N4" s="78" t="str">
+      <c r="N4" s="72" t="str">
         <f>Cards!E15</f>
         <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
       </c>
-      <c r="O4" s="80" t="str">
+      <c r="O4" s="74" t="str">
         <f>Cards!E16</f>
         <v>Each Player must have at least $L6 sponsored Laws in the Edicts or in the Queue or they will suffer sanctions on Tax</v>
       </c>
-      <c r="P4" s="78" t="str">
+      <c r="P4" s="72" t="str">
         <f>Cards!E17</f>
         <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
       </c>
-      <c r="Q4" s="80" t="str">
+      <c r="Q4" s="74" t="str">
         <f>Cards!E18</f>
         <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
       </c>
-      <c r="R4" s="78" t="str">
+      <c r="R4" s="72" t="str">
         <f>Cards!E19</f>
         <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
       </c>
-      <c r="S4" s="80" t="str">
+      <c r="S4" s="74" t="str">
         <f>Cards!E20</f>
         <v>Each Player must Collect at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
-      <c r="T4" s="78" t="str">
+      <c r="T4" s="72" t="str">
         <f>Cards!E21</f>
         <v>No Player may Collect more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
       </c>
-      <c r="U4" s="80" t="str">
+      <c r="U4" s="74" t="str">
         <f>Cards!E22</f>
         <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
-      <c r="V4" s="78" t="str">
+      <c r="V4" s="72" t="str">
         <f>Cards!E23</f>
         <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
-      <c r="W4" s="80" t="str">
+      <c r="W4" s="74" t="str">
         <f>Cards!E24</f>
         <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Collect</v>
       </c>
-      <c r="X4" s="78" t="str">
+      <c r="X4" s="72" t="str">
         <f>Cards!E25</f>
         <v>No Player may have more than $L6 Troops or they will suffer sanctions on Collect</v>
       </c>
-      <c r="Y4" s="80" t="str">
+      <c r="Y4" s="74" t="str">
         <f>Cards!E26</f>
         <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
-      <c r="Z4" s="78" t="str">
+      <c r="Z4" s="72" t="str">
         <f>Cards!E27</f>
         <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
       </c>
-      <c r="AA4" s="80" t="str">
+      <c r="AA4" s="74" t="str">
         <f>Cards!E28</f>
         <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
-      <c r="AB4" s="78" t="str">
+      <c r="AB4" s="72" t="str">
         <f>Cards!E29</f>
         <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
       </c>
-      <c r="AC4" s="80" t="str">
+      <c r="AC4" s="74" t="str">
         <f>Cards!E30</f>
         <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
       </c>
-      <c r="AD4" s="81" t="str">
+      <c r="AD4" s="75" t="str">
         <f>Cards!E31</f>
         <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
       </c>
-      <c r="AE4" s="78" t="str">
+      <c r="AE4" s="72" t="str">
         <f>Cards!E32</f>
         <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
       </c>
-      <c r="AF4" s="78" t="str">
+      <c r="AF4" s="72" t="str">
         <f>Cards!E33</f>
         <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
       </c>
-      <c r="AG4" s="80" t="str">
-        <f t="shared" ref="AG4:BL4" si="4">A4</f>
+      <c r="AG4" s="74" t="str">
+        <f t="shared" ref="AG4:BL4" si="5">A4</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
       </c>
-      <c r="AH4" s="78" t="str">
+      <c r="AH4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
+      </c>
+      <c r="AI4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AJ4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AK4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
+      </c>
+      <c r="AL4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
+      </c>
+      <c r="AM4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AN4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>Change the boundary of an active Law to $L6</v>
+      </c>
+      <c r="AO4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy</v>
+      </c>
+      <c r="AP4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy</v>
+      </c>
+      <c r="AQ4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
+      </c>
+      <c r="AR4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
+      </c>
+      <c r="AS4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+      </c>
+      <c r="AT4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+      </c>
+      <c r="AU4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have at least $L6 sponsored Laws in the Edicts or in the Queue or they will suffer sanctions on Tax</v>
+      </c>
+      <c r="AV4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
+      </c>
+      <c r="AW4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
+      </c>
+      <c r="AX4" s="75" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
+      </c>
+      <c r="AY4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must Collect at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+      </c>
+      <c r="AZ4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may Collect more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
+      </c>
+      <c r="BA4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
+      </c>
+      <c r="BB4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
+      </c>
+      <c r="BC4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Collect</v>
+      </c>
+      <c r="BD4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Collect</v>
+      </c>
+      <c r="BE4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+      </c>
+      <c r="BF4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
+      </c>
+      <c r="BG4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
+      </c>
+      <c r="BH4" s="75" t="str">
+        <f t="shared" si="5"/>
+        <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
+      </c>
+      <c r="BI4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
+      </c>
+      <c r="BJ4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
+      </c>
+      <c r="BK4" s="72" t="str">
+        <f t="shared" si="5"/>
+        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="BL4" s="74" t="str">
+        <f t="shared" si="5"/>
+        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
+      </c>
+      <c r="BM4" s="72"/>
+      <c r="BN4" s="92" t="str">
         <f t="shared" si="4"/>
-        <v>The Royal Bank may not have more than $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
-      </c>
-      <c r="AI4" s="80" t="str">
+        <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
+      </c>
+      <c r="BO4" s="93" t="str">
         <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AJ4" s="78" t="str">
+        <v>Provides Private Donate action with no penalty and convert $L3 additional Coins.</v>
+      </c>
+      <c r="BP4" s="92" t="str">
         <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AK4" s="80" t="str">
+        <v>Convert $L3 additional Coins during Undermarket Donate</v>
+      </c>
+      <c r="BQ4" s="93" t="str">
         <f t="shared" si="4"/>
-        <v>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
-      </c>
-      <c r="AL4" s="78" t="str">
+        <v>You may repeat Undermarket Actions at double the penalty</v>
+      </c>
+      <c r="BR4" s="72" t="str">
         <f t="shared" si="4"/>
-        <v>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</v>
-      </c>
-      <c r="AM4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AN4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Change the boundary of an active Law to $L6</v>
-      </c>
-      <c r="AO4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must Sue using a Leader with at least level $L6 this round or they will suffer sanctions on Deploy</v>
-      </c>
-      <c r="AP4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may Sue using a Leader higher than level $L6 this round or they will suffer sanctions on Deploy</v>
-      </c>
-      <c r="AQ4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have an Investment with at least level $L6 or they will suffer sanctions on Infiltrate</v>
-      </c>
-      <c r="AR4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have an Investment higher than level $L6 or they will suffer sanctions on Infiltrate</v>
-      </c>
-      <c r="AS4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
-      </c>
-      <c r="AT4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
-      </c>
-      <c r="AU4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least $L6 sponsored Laws in the Edicts or in the Queue or they will suffer sanctions on Tax</v>
-      </c>
-      <c r="AV4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 sponsored Laws active or in the queue or they will suffer sanctions on Tax</v>
-      </c>
-      <c r="AW4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have a Leader with at least level $L6 or they will suffer sanctions on Sue</v>
-      </c>
-      <c r="AX4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have a Leader higher than level $L6 or they will suffer sanctions on Sue</v>
-      </c>
-      <c r="AY4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must Collect at least $L6 Commodities this round or they will suffer sanctions on Recruit</v>
-      </c>
-      <c r="AZ4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may Collect more than $L6 Commodities this round or they will suffer sanctions on Recruit</v>
-      </c>
-      <c r="BA4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
-      </c>
-      <c r="BB4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
-      </c>
-      <c r="BC4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least $L6 Troops or they will suffer sanctions on Collect</v>
-      </c>
-      <c r="BD4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 Troops or they will suffer sanctions on Collect</v>
-      </c>
-      <c r="BE4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>At least $L6 Players must use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
-      </c>
-      <c r="BF4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</v>
-      </c>
-      <c r="BG4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>At least $L6 Players must use Court Actions or all Players suffer sanctions on Flatter</v>
-      </c>
-      <c r="BH4" s="81" t="str">
-        <f t="shared" si="4"/>
-        <v>No more than $L6 Players may use Court Actions or all Players suffer sanctions on Flatter</v>
-      </c>
-      <c r="BI4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
-      </c>
-      <c r="BJ4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
-      </c>
-      <c r="BK4" s="78" t="str">
-        <f t="shared" si="4"/>
-        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
-      </c>
-      <c r="BL4" s="80" t="str">
-        <f t="shared" si="4"/>
-        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
-      </c>
-      <c r="BM4" s="78"/>
-      <c r="BN4" s="98" t="str">
-        <f>AJ2</f>
-        <v>Trade for up to $L3 additional Coins when Monetizing in the Court</v>
-      </c>
-      <c r="BO4" s="99" t="str">
-        <f>AK2</f>
-        <v>Provides Private Donate action with no penalty and convert $L3 additional Coins.</v>
-      </c>
-      <c r="BP4" s="98" t="str">
-        <f>AL2</f>
-        <v>Convert $L3 additional Coins during Undermarket Donate</v>
-      </c>
-      <c r="BQ4" s="99" t="str">
-        <f>AM2</f>
-        <v>You may repeat Undermarket Actions at double the penalty</v>
-      </c>
-      <c r="BR4" s="78" t="str">
-        <f>AN2</f>
         <v>Deploy $L3 additional Troops during Deploy</v>
       </c>
-      <c r="BS4" s="79"/>
-      <c r="BU4" s="78"/>
-      <c r="BW4" s="78"/>
-      <c r="BY4" s="78"/>
-      <c r="CA4" s="78"/>
-    </row>
-    <row r="5" spans="1:79" s="84" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="82" t="str">
+      <c r="BS4" s="73"/>
+      <c r="BU4" s="72"/>
+      <c r="BW4" s="72"/>
+      <c r="BY4" s="72"/>
+      <c r="CA4" s="72"/>
+    </row>
+    <row r="5" spans="1:79" s="78" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="76" t="str">
         <f>Cards!F2</f>
         <v>Fickle Mercenaries</v>
       </c>
-      <c r="B5" s="83" t="str">
+      <c r="B5" s="77" t="str">
         <f>Cards!F3</f>
         <v>Blatant Extortion</v>
       </c>
-      <c r="C5" s="84" t="str">
+      <c r="C5" s="78" t="str">
         <f>Cards!F4</f>
         <v>Double Agents</v>
       </c>
-      <c r="D5" s="82" t="str">
+      <c r="D5" s="76" t="str">
         <f>Cards!F5</f>
         <v>Questionable Reallocation</v>
       </c>
-      <c r="E5" s="84" t="str">
+      <c r="E5" s="78" t="str">
         <f>Cards!F6</f>
         <v>Corporate Espionage</v>
       </c>
-      <c r="F5" s="82" t="str">
+      <c r="F5" s="76" t="str">
         <f>Cards!F7</f>
         <v>Localized Famine</v>
       </c>
-      <c r="G5" s="84" t="str">
+      <c r="G5" s="78" t="str">
         <f>Cards!F8</f>
         <v>Highway Robbery</v>
       </c>
-      <c r="H5" s="82" t="str">
+      <c r="H5" s="76" t="str">
         <f>Cards!F9</f>
         <v>Camp Plague</v>
       </c>
-      <c r="I5" s="84" t="str">
+      <c r="I5" s="78" t="str">
         <f>Cards!F10</f>
         <v>Weakening Grip</v>
       </c>
-      <c r="J5" s="82" t="str">
+      <c r="J5" s="76" t="str">
         <f>Cards!F11</f>
         <v>Culture Shift</v>
       </c>
-      <c r="K5" s="84" t="str">
+      <c r="K5" s="78" t="str">
         <f>Cards!F12</f>
         <v>Corporate Takeover</v>
       </c>
-      <c r="L5" s="82" t="str">
+      <c r="L5" s="76" t="str">
         <f>Cards!F13</f>
         <v>Sabotage</v>
       </c>
-      <c r="M5" s="84" t="str">
+      <c r="M5" s="78" t="str">
         <f>Cards!F14</f>
         <v>Dangerous Monopolies</v>
       </c>
-      <c r="N5" s="82" t="str">
+      <c r="N5" s="76" t="str">
         <f>Cards!F15</f>
         <v>Betrayal</v>
       </c>
-      <c r="O5" s="84" t="str">
+      <c r="O5" s="78" t="str">
         <f>Cards!F16</f>
         <v>Assassination Attempt</v>
       </c>
-      <c r="P5" s="82" t="str">
+      <c r="P5" s="76" t="str">
         <f>Cards!F17</f>
         <v>Humiliation</v>
       </c>
-      <c r="Q5" s="84" t="str">
+      <c r="Q5" s="78" t="str">
         <f>Cards!F18</f>
         <v>Invalid Paperwork</v>
       </c>
-      <c r="R5" s="82" t="str">
+      <c r="R5" s="76" t="str">
         <f>Cards!F19</f>
         <v>Rallied Opposition</v>
       </c>
-      <c r="S5" s="84" t="str">
+      <c r="S5" s="78" t="str">
         <f>Cards!F20</f>
         <v>Waning Support</v>
       </c>
-      <c r="T5" s="82" t="str">
+      <c r="T5" s="76" t="str">
         <f>Cards!F21</f>
         <v>Misaligned Strategy</v>
       </c>
-      <c r="U5" s="82" t="str">
+      <c r="U5" s="76" t="str">
         <f>Cards!F22</f>
         <v>Blackmail</v>
       </c>
-      <c r="V5" s="82" t="str">
-        <f t="shared" ref="V5:AE6" si="5">A5</f>
+      <c r="V5" s="76" t="str">
+        <f t="shared" ref="V5:AE6" si="6">A5</f>
         <v>Fickle Mercenaries</v>
       </c>
-      <c r="W5" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="W5" s="78" t="str">
+        <f t="shared" si="6"/>
         <v>Blatant Extortion</v>
       </c>
-      <c r="X5" s="82" t="str">
-        <f t="shared" si="5"/>
+      <c r="X5" s="76" t="str">
+        <f t="shared" si="6"/>
         <v>Double Agents</v>
       </c>
-      <c r="Y5" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="Y5" s="78" t="str">
+        <f t="shared" si="6"/>
         <v>Questionable Reallocation</v>
       </c>
-      <c r="Z5" s="82" t="str">
-        <f t="shared" si="5"/>
+      <c r="Z5" s="76" t="str">
+        <f t="shared" si="6"/>
         <v>Corporate Espionage</v>
       </c>
-      <c r="AA5" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="AA5" s="78" t="str">
+        <f t="shared" si="6"/>
         <v>Localized Famine</v>
       </c>
-      <c r="AB5" s="82" t="str">
-        <f t="shared" si="5"/>
+      <c r="AB5" s="76" t="str">
+        <f t="shared" si="6"/>
         <v>Highway Robbery</v>
       </c>
-      <c r="AC5" s="84" t="str">
-        <f t="shared" si="5"/>
+      <c r="AC5" s="78" t="str">
+        <f t="shared" si="6"/>
         <v>Camp Plague</v>
       </c>
-      <c r="AD5" s="85" t="str">
-        <f t="shared" si="5"/>
+      <c r="AD5" s="79" t="str">
+        <f t="shared" si="6"/>
         <v>Weakening Grip</v>
       </c>
-      <c r="AE5" s="82" t="str">
-        <f t="shared" si="5"/>
+      <c r="AE5" s="76" t="str">
+        <f t="shared" si="6"/>
         <v>Culture Shift</v>
       </c>
-      <c r="AF5" s="82" t="str">
-        <f t="shared" ref="AF5:AO6" si="6">K5</f>
+      <c r="AF5" s="76" t="str">
+        <f t="shared" ref="AF5:AO6" si="7">K5</f>
         <v>Corporate Takeover</v>
       </c>
-      <c r="AG5" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="AG5" s="78" t="str">
+        <f t="shared" si="7"/>
         <v>Sabotage</v>
       </c>
-      <c r="AH5" s="82" t="str">
-        <f t="shared" si="6"/>
+      <c r="AH5" s="76" t="str">
+        <f t="shared" si="7"/>
         <v>Dangerous Monopolies</v>
       </c>
-      <c r="AI5" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="AI5" s="78" t="str">
+        <f t="shared" si="7"/>
         <v>Betrayal</v>
       </c>
-      <c r="AJ5" s="82" t="str">
-        <f t="shared" si="6"/>
+      <c r="AJ5" s="76" t="str">
+        <f t="shared" si="7"/>
         <v>Assassination Attempt</v>
       </c>
-      <c r="AK5" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="AK5" s="78" t="str">
+        <f t="shared" si="7"/>
         <v>Humiliation</v>
       </c>
-      <c r="AL5" s="82" t="str">
-        <f t="shared" si="6"/>
+      <c r="AL5" s="76" t="str">
+        <f t="shared" si="7"/>
         <v>Invalid Paperwork</v>
       </c>
-      <c r="AM5" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="AM5" s="78" t="str">
+        <f t="shared" si="7"/>
         <v>Rallied Opposition</v>
       </c>
-      <c r="AN5" s="82" t="str">
-        <f t="shared" si="6"/>
+      <c r="AN5" s="76" t="str">
+        <f t="shared" si="7"/>
         <v>Waning Support</v>
       </c>
-      <c r="AO5" s="84" t="str">
-        <f t="shared" si="6"/>
+      <c r="AO5" s="78" t="str">
+        <f t="shared" si="7"/>
         <v>Misaligned Strategy</v>
       </c>
-      <c r="AP5" s="82" t="str">
-        <f t="shared" ref="AP5:AY6" si="7">U5</f>
+      <c r="AP5" s="76" t="str">
+        <f t="shared" ref="AP5:AP6" si="8">U5</f>
         <v>Blackmail</v>
       </c>
-      <c r="AQ5" s="84" t="str">
-        <f t="shared" ref="AQ5:AZ6" si="8">A5</f>
+      <c r="AQ5" s="78" t="str">
+        <f t="shared" ref="AQ5:AZ6" si="9">A5</f>
         <v>Fickle Mercenaries</v>
       </c>
-      <c r="AR5" s="82" t="str">
-        <f t="shared" si="8"/>
+      <c r="AR5" s="76" t="str">
+        <f t="shared" si="9"/>
         <v>Blatant Extortion</v>
       </c>
-      <c r="AS5" s="84" t="str">
-        <f t="shared" si="8"/>
+      <c r="AS5" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Double Agents</v>
       </c>
-      <c r="AT5" s="82" t="str">
-        <f t="shared" si="8"/>
+      <c r="AT5" s="76" t="str">
+        <f t="shared" si="9"/>
         <v>Questionable Reallocation</v>
       </c>
-      <c r="AU5" s="84" t="str">
-        <f t="shared" si="8"/>
+      <c r="AU5" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Corporate Espionage</v>
       </c>
-      <c r="AV5" s="82" t="str">
-        <f t="shared" si="8"/>
+      <c r="AV5" s="76" t="str">
+        <f t="shared" si="9"/>
         <v>Localized Famine</v>
       </c>
-      <c r="AW5" s="84" t="str">
-        <f t="shared" si="8"/>
+      <c r="AW5" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Highway Robbery</v>
       </c>
-      <c r="AX5" s="85" t="str">
-        <f t="shared" si="8"/>
+      <c r="AX5" s="79" t="str">
+        <f t="shared" si="9"/>
         <v>Camp Plague</v>
       </c>
-      <c r="AY5" s="82" t="str">
-        <f t="shared" si="8"/>
+      <c r="AY5" s="76" t="str">
+        <f t="shared" si="9"/>
         <v>Weakening Grip</v>
       </c>
-      <c r="AZ5" s="84" t="str">
-        <f t="shared" si="8"/>
+      <c r="AZ5" s="78" t="str">
+        <f t="shared" si="9"/>
         <v>Culture Shift</v>
       </c>
-      <c r="BA5" s="82" t="str">
-        <f t="shared" ref="BA5:BJ6" si="9">K5</f>
+      <c r="BA5" s="76" t="str">
+        <f t="shared" ref="BA5:BJ6" si="10">K5</f>
         <v>Corporate Takeover</v>
       </c>
-      <c r="BB5" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="BB5" s="78" t="str">
+        <f t="shared" si="10"/>
         <v>Sabotage</v>
       </c>
-      <c r="BC5" s="82" t="str">
-        <f t="shared" si="9"/>
+      <c r="BC5" s="76" t="str">
+        <f t="shared" si="10"/>
         <v>Dangerous Monopolies</v>
       </c>
-      <c r="BD5" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="BD5" s="78" t="str">
+        <f t="shared" si="10"/>
         <v>Betrayal</v>
       </c>
-      <c r="BE5" s="82" t="str">
-        <f t="shared" si="9"/>
+      <c r="BE5" s="76" t="str">
+        <f t="shared" si="10"/>
         <v>Assassination Attempt</v>
       </c>
-      <c r="BF5" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="BF5" s="78" t="str">
+        <f t="shared" si="10"/>
         <v>Humiliation</v>
       </c>
-      <c r="BG5" s="82" t="str">
-        <f t="shared" si="9"/>
+      <c r="BG5" s="76" t="str">
+        <f t="shared" si="10"/>
         <v>Invalid Paperwork</v>
       </c>
-      <c r="BH5" s="82" t="str">
-        <f t="shared" si="9"/>
+      <c r="BH5" s="76" t="str">
+        <f t="shared" si="10"/>
         <v>Rallied Opposition</v>
       </c>
-      <c r="BI5" s="82" t="str">
-        <f t="shared" si="9"/>
+      <c r="BI5" s="76" t="str">
+        <f t="shared" si="10"/>
         <v>Waning Support</v>
       </c>
-      <c r="BJ5" s="84" t="str">
-        <f t="shared" si="9"/>
+      <c r="BJ5" s="78" t="str">
+        <f t="shared" si="10"/>
         <v>Misaligned Strategy</v>
       </c>
-      <c r="BK5" s="82" t="str">
-        <f t="shared" ref="BK5:BT6" si="10">U5</f>
+      <c r="BK5" s="76" t="str">
+        <f t="shared" ref="BK5:BK6" si="11">U5</f>
         <v>Blackmail</v>
       </c>
-      <c r="BM5" s="73" t="str">
-        <f>AE1</f>
+      <c r="BM5" s="67" t="str">
+        <f t="shared" ref="BM5:BQ6" si="12">AE1</f>
         <v>Codependent Relationship</v>
       </c>
-      <c r="BN5" s="75" t="str">
-        <f>AF1</f>
+      <c r="BN5" s="69" t="str">
+        <f t="shared" si="12"/>
         <v>Dangerous Promises</v>
       </c>
-      <c r="BO5" s="73" t="str">
-        <f>AG1</f>
+      <c r="BO5" s="67" t="str">
+        <f t="shared" si="12"/>
         <v>Large Middle Class</v>
       </c>
-      <c r="BP5" s="75" t="str">
-        <f>AH1</f>
+      <c r="BP5" s="69" t="str">
+        <f t="shared" si="12"/>
         <v>Innovation Hub</v>
       </c>
-      <c r="BQ5" s="73" t="str">
-        <f>AI1</f>
+      <c r="BQ5" s="67" t="str">
+        <f t="shared" si="12"/>
         <v>Fire Temple</v>
       </c>
-      <c r="BR5" s="82"/>
-      <c r="BS5" s="83"/>
-      <c r="BU5" s="82"/>
-      <c r="BW5" s="82"/>
-      <c r="BY5" s="82"/>
-      <c r="CA5" s="82"/>
-    </row>
-    <row r="6" spans="1:79" s="80" customFormat="1" ht="81.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="78" t="str">
+      <c r="BR5" s="76"/>
+      <c r="BS5" s="77"/>
+      <c r="BU5" s="76"/>
+      <c r="BW5" s="76"/>
+      <c r="BY5" s="76"/>
+      <c r="CA5" s="76"/>
+    </row>
+    <row r="6" spans="1:79" s="74" customFormat="1" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="72" t="str">
         <f>Cards!G2</f>
         <v>Give $2D6 Troops to $R</v>
       </c>
-      <c r="B6" s="79" t="str">
+      <c r="B6" s="73" t="str">
         <f>Cards!G3</f>
         <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="C6" s="80" t="str">
+      <c r="C6" s="74" t="str">
         <f>Cards!G4</f>
         <v>Give $D6 Spies to $R</v>
       </c>
-      <c r="D6" s="78" t="str">
+      <c r="D6" s="72" t="str">
         <f>Cards!G5</f>
         <v>Give $2D6 Commodities to $R</v>
       </c>
-      <c r="E6" s="80" t="str">
+      <c r="E6" s="74" t="str">
         <f>Cards!G6</f>
         <v>Give $D6 random Cards of each type from your hand to $R</v>
       </c>
-      <c r="F6" s="78" t="str">
+      <c r="F6" s="72" t="str">
         <f>Cards!G7</f>
         <v>Lose half your Commodities</v>
       </c>
-      <c r="G6" s="80" t="str">
+      <c r="G6" s="74" t="str">
         <f>Cards!G8</f>
         <v>Lose half your Coins</v>
       </c>
-      <c r="H6" s="78" t="str">
+      <c r="H6" s="72" t="str">
         <f>Cards!G9</f>
         <v>Lose half your Troops</v>
       </c>
-      <c r="I6" s="80" t="str">
+      <c r="I6" s="74" t="str">
         <f>Cards!G10</f>
         <v>Lose half your Spies</v>
       </c>
-      <c r="J6" s="78" t="str">
+      <c r="J6" s="72" t="str">
         <f>Cards!G11</f>
         <v>Disard half your cards of each type</v>
       </c>
-      <c r="K6" s="80" t="str">
+      <c r="K6" s="74" t="str">
         <f>Cards!G12</f>
         <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
       </c>
-      <c r="L6" s="78" t="str">
+      <c r="L6" s="72" t="str">
         <f>Cards!G13</f>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="M6" s="80" t="str">
+      <c r="M6" s="74" t="str">
         <f>Cards!G14</f>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="N6" s="78" t="str">
+      <c r="N6" s="72" t="str">
         <f>Cards!G15</f>
         <v>Demote a Leader at level $D6 by half and send it to $R</v>
       </c>
-      <c r="O6" s="80" t="str">
+      <c r="O6" s="74" t="str">
         <f>Cards!G16</f>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="P6" s="78" t="str">
+      <c r="P6" s="72" t="str">
         <f>Cards!G17</f>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="Q6" s="80" t="str">
+      <c r="Q6" s="74" t="str">
         <f>Cards!G18</f>
         <v>Move your foremost Law to the back of the Queue</v>
       </c>
-      <c r="R6" s="78" t="str">
+      <c r="R6" s="72" t="str">
         <f>Cards!G19</f>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="S6" s="80" t="str">
+      <c r="S6" s="74" t="str">
         <f>Cards!G20</f>
         <v>Move $D6 of your Laws each one space back in the Queue</v>
       </c>
-      <c r="T6" s="78" t="str">
+      <c r="T6" s="72" t="str">
         <f>Cards!G21</f>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="U6" s="78" t="str">
+      <c r="U6" s="72" t="str">
         <f>Cards!G22</f>
         <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="V6" s="78" t="str">
-        <f t="shared" si="5"/>
+      <c r="V6" s="72" t="str">
+        <f t="shared" si="6"/>
         <v>Give $2D6 Troops to $R</v>
       </c>
-      <c r="W6" s="80" t="str">
-        <f t="shared" si="5"/>
+      <c r="W6" s="74" t="str">
+        <f t="shared" si="6"/>
         <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="X6" s="78" t="str">
-        <f t="shared" si="5"/>
+      <c r="X6" s="72" t="str">
+        <f t="shared" si="6"/>
         <v>Give $D6 Spies to $R</v>
       </c>
-      <c r="Y6" s="80" t="str">
-        <f t="shared" si="5"/>
+      <c r="Y6" s="74" t="str">
+        <f t="shared" si="6"/>
         <v>Give $2D6 Commodities to $R</v>
       </c>
-      <c r="Z6" s="78" t="str">
-        <f t="shared" si="5"/>
+      <c r="Z6" s="72" t="str">
+        <f t="shared" si="6"/>
         <v>Give $D6 random Cards of each type from your hand to $R</v>
       </c>
-      <c r="AA6" s="80" t="str">
-        <f t="shared" si="5"/>
+      <c r="AA6" s="74" t="str">
+        <f t="shared" si="6"/>
         <v>Lose half your Commodities</v>
       </c>
-      <c r="AB6" s="78" t="str">
-        <f t="shared" si="5"/>
+      <c r="AB6" s="72" t="str">
+        <f t="shared" si="6"/>
         <v>Lose half your Coins</v>
       </c>
-      <c r="AC6" s="80" t="str">
-        <f t="shared" si="5"/>
+      <c r="AC6" s="74" t="str">
+        <f t="shared" si="6"/>
         <v>Lose half your Troops</v>
       </c>
-      <c r="AD6" s="81" t="str">
-        <f t="shared" si="5"/>
+      <c r="AD6" s="75" t="str">
+        <f t="shared" si="6"/>
         <v>Lose half your Spies</v>
       </c>
-      <c r="AE6" s="78" t="str">
-        <f t="shared" si="5"/>
+      <c r="AE6" s="72" t="str">
+        <f t="shared" si="6"/>
         <v>Disard half your cards of each type</v>
       </c>
-      <c r="AF6" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="AF6" s="72" t="str">
+        <f t="shared" si="7"/>
         <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
       </c>
-      <c r="AG6" s="80" t="str">
-        <f t="shared" si="6"/>
+      <c r="AG6" s="74" t="str">
+        <f t="shared" si="7"/>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="AH6" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="AH6" s="72" t="str">
+        <f t="shared" si="7"/>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="AI6" s="80" t="str">
-        <f t="shared" si="6"/>
+      <c r="AI6" s="74" t="str">
+        <f t="shared" si="7"/>
         <v>Demote a Leader at level $D6 by half and send it to $R</v>
       </c>
-      <c r="AJ6" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="AJ6" s="72" t="str">
+        <f t="shared" si="7"/>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="AK6" s="80" t="str">
-        <f t="shared" si="6"/>
+      <c r="AK6" s="74" t="str">
+        <f t="shared" si="7"/>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="AL6" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="AL6" s="72" t="str">
+        <f t="shared" si="7"/>
         <v>Move your foremost Law to the back of the Queue</v>
       </c>
-      <c r="AM6" s="80" t="str">
-        <f t="shared" si="6"/>
+      <c r="AM6" s="74" t="str">
+        <f t="shared" si="7"/>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="AN6" s="78" t="str">
-        <f t="shared" si="6"/>
+      <c r="AN6" s="72" t="str">
+        <f t="shared" si="7"/>
         <v>Move $D6 of your Laws each one space back in the Queue</v>
       </c>
-      <c r="AO6" s="80" t="str">
-        <f t="shared" si="6"/>
+      <c r="AO6" s="74" t="str">
+        <f t="shared" si="7"/>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="AP6" s="78" t="str">
-        <f t="shared" si="7"/>
+      <c r="AP6" s="72" t="str">
+        <f t="shared" si="8"/>
         <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="AQ6" s="80" t="str">
-        <f t="shared" si="8"/>
+      <c r="AQ6" s="74" t="str">
+        <f t="shared" si="9"/>
         <v>Give $2D6 Troops to $R</v>
       </c>
-      <c r="AR6" s="78" t="str">
-        <f t="shared" si="8"/>
+      <c r="AR6" s="72" t="str">
+        <f t="shared" si="9"/>
         <v>Give $D6 Coins to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="AS6" s="80" t="str">
-        <f t="shared" si="8"/>
+      <c r="AS6" s="74" t="str">
+        <f t="shared" si="9"/>
         <v>Give $D6 Spies to $R</v>
       </c>
-      <c r="AT6" s="78" t="str">
-        <f t="shared" si="8"/>
+      <c r="AT6" s="72" t="str">
+        <f t="shared" si="9"/>
         <v>Give $2D6 Commodities to $R</v>
       </c>
-      <c r="AU6" s="80" t="str">
-        <f t="shared" si="8"/>
+      <c r="AU6" s="74" t="str">
+        <f t="shared" si="9"/>
         <v>Give $D6 random Cards of each type from your hand to $R</v>
       </c>
-      <c r="AV6" s="78" t="str">
-        <f t="shared" si="8"/>
+      <c r="AV6" s="72" t="str">
+        <f t="shared" si="9"/>
         <v>Lose half your Commodities</v>
       </c>
-      <c r="AW6" s="80" t="str">
-        <f t="shared" si="8"/>
+      <c r="AW6" s="74" t="str">
+        <f t="shared" si="9"/>
         <v>Lose half your Coins</v>
       </c>
-      <c r="AX6" s="81" t="str">
-        <f t="shared" si="8"/>
+      <c r="AX6" s="75" t="str">
+        <f t="shared" si="9"/>
         <v>Lose half your Troops</v>
       </c>
-      <c r="AY6" s="78" t="str">
-        <f t="shared" si="8"/>
+      <c r="AY6" s="72" t="str">
+        <f t="shared" si="9"/>
         <v>Lose half your Spies</v>
       </c>
-      <c r="AZ6" s="80" t="str">
-        <f t="shared" si="8"/>
+      <c r="AZ6" s="74" t="str">
+        <f t="shared" si="9"/>
         <v>Disard half your cards of each type</v>
       </c>
-      <c r="BA6" s="78" t="str">
-        <f t="shared" si="9"/>
+      <c r="BA6" s="72" t="str">
+        <f t="shared" si="10"/>
         <v>Downgrade an Investment at level $D6 by half and send it to $R</v>
       </c>
-      <c r="BB6" s="80" t="str">
-        <f t="shared" si="9"/>
+      <c r="BB6" s="74" t="str">
+        <f t="shared" si="10"/>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="BC6" s="78" t="str">
-        <f t="shared" si="9"/>
+      <c r="BC6" s="72" t="str">
+        <f t="shared" si="10"/>
         <v>Downgrade an Investment by $D6 levels</v>
       </c>
-      <c r="BD6" s="80" t="str">
-        <f t="shared" si="9"/>
+      <c r="BD6" s="74" t="str">
+        <f t="shared" si="10"/>
         <v>Demote a Leader at level $D6 by half and send it to $R</v>
       </c>
-      <c r="BE6" s="78" t="str">
-        <f t="shared" si="9"/>
+      <c r="BE6" s="72" t="str">
+        <f t="shared" si="10"/>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="BF6" s="80" t="str">
-        <f t="shared" si="9"/>
+      <c r="BF6" s="74" t="str">
+        <f t="shared" si="10"/>
         <v>Demote a Leader by $D6 levels</v>
       </c>
-      <c r="BG6" s="78" t="str">
-        <f t="shared" si="9"/>
+      <c r="BG6" s="72" t="str">
+        <f t="shared" si="10"/>
         <v>Move your foremost Law to the back of the Queue</v>
       </c>
-      <c r="BH6" s="78" t="str">
-        <f t="shared" si="9"/>
+      <c r="BH6" s="72" t="str">
+        <f t="shared" si="10"/>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="BI6" s="78" t="str">
-        <f t="shared" si="9"/>
+      <c r="BI6" s="72" t="str">
+        <f t="shared" si="10"/>
         <v>Move $D6 of your Laws each one space back in the Queue</v>
       </c>
-      <c r="BJ6" s="80" t="str">
-        <f t="shared" si="9"/>
+      <c r="BJ6" s="74" t="str">
+        <f t="shared" si="10"/>
         <v>Move your foremost Law $D6 spaces back in the Queue</v>
       </c>
-      <c r="BK6" s="78" t="str">
-        <f t="shared" si="10"/>
+      <c r="BK6" s="72" t="str">
+        <f t="shared" si="11"/>
         <v>Pay $D6 Coins to the holder of the King's Favor then give the King's Favor to $R. Perform an Emergency Trade if needed.</v>
       </c>
-      <c r="BM6" s="78" t="str">
-        <f>AE2</f>
+      <c r="BM6" s="72" t="str">
+        <f t="shared" si="12"/>
         <v>Trade up to $L3 additional Coins when Buying from the Undermarket</v>
       </c>
-      <c r="BN6" s="80" t="str">
-        <f>AF2</f>
+      <c r="BN6" s="74" t="str">
+        <f t="shared" si="12"/>
         <v>Trade for up to $L3 additional Coins when Selling to the Undermarket</v>
       </c>
-      <c r="BO6" s="78" t="str">
-        <f>AG2</f>
+      <c r="BO6" s="72" t="str">
+        <f t="shared" si="12"/>
         <v>Trade for up to $L3 additional Coins when Monetizing in the Undermarket</v>
       </c>
-      <c r="BP6" s="80" t="str">
-        <f>AH2</f>
+      <c r="BP6" s="74" t="str">
+        <f t="shared" si="12"/>
         <v>Provides private Monetize Action at Market Rate + $L3</v>
       </c>
-      <c r="BQ6" s="78" t="str">
-        <f>AI2</f>
+      <c r="BQ6" s="72" t="str">
+        <f t="shared" si="12"/>
         <v>Spend $L3 fewer Cards per Coin when Monetizing in the Court</v>
       </c>
-      <c r="BR6" s="78"/>
-      <c r="BS6" s="79"/>
-      <c r="BU6" s="78"/>
-      <c r="BW6" s="78"/>
-      <c r="BY6" s="78"/>
-      <c r="CA6" s="78"/>
+      <c r="BR6" s="72"/>
+      <c r="BS6" s="73"/>
+      <c r="BU6" s="72"/>
+      <c r="BW6" s="72"/>
+      <c r="BY6" s="72"/>
+      <c r="CA6" s="72"/>
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8581,298 +8505,298 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BDA35E-BFC3-134A-A064-89D65A8B31CF}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.50390625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C1" t="s">
         <v>267</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>268</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>269</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>270</v>
       </c>
-      <c r="F1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D2">
         <v>27.7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D3">
         <v>27.7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D4">
         <v>30.75</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E6" t="s">
         <v>273</v>
       </c>
-      <c r="E6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E7" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E8" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>272</v>
+      </c>
+      <c r="E10" t="s">
         <v>273</v>
       </c>
-      <c r="E10" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E11" t="s">
         <v>273</v>
       </c>
-      <c r="E11" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E12" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E13" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -8881,103 +8805,103 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC83F89-2724-CA43-A519-59213A612B31}">
   <dimension ref="A1:U55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.9453125" style="101" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.72265625" customWidth="1"/>
-    <col min="4" max="4" width="8.33984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.27734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.22265625" style="103" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.43359375" style="103" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.22265625" style="103" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.43359375" style="103" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="11.8359375" style="103" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.9140625" style="103" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" style="95" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="97" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="97" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="97" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="97" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="11.85546875" style="97" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" style="97" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" t="s">
         <v>333</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>334</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>335</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>336</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G1" t="s">
+        <v>361</v>
+      </c>
+      <c r="H1" t="s">
         <v>337</v>
       </c>
-      <c r="F1" t="s">
-        <v>363</v>
-      </c>
-      <c r="G1" t="s">
-        <v>362</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>338</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" s="97" t="s">
+        <v>359</v>
+      </c>
+      <c r="K1" t="s">
         <v>339</v>
       </c>
-      <c r="J1" s="103" t="s">
+      <c r="L1" t="s">
+        <v>340</v>
+      </c>
+      <c r="M1" t="s">
+        <v>341</v>
+      </c>
+      <c r="N1" t="s">
+        <v>342</v>
+      </c>
+      <c r="O1" t="s">
+        <v>343</v>
+      </c>
+      <c r="P1" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>345</v>
+      </c>
+      <c r="R1" t="s">
+        <v>346</v>
+      </c>
+      <c r="S1" t="s">
+        <v>347</v>
+      </c>
+      <c r="T1" t="s">
+        <v>348</v>
+      </c>
+      <c r="U1" t="s">
         <v>360</v>
       </c>
-      <c r="K1" t="s">
-        <v>340</v>
-      </c>
-      <c r="L1" t="s">
-        <v>341</v>
-      </c>
-      <c r="M1" t="s">
-        <v>342</v>
-      </c>
-      <c r="N1" t="s">
-        <v>343</v>
-      </c>
-      <c r="O1" t="s">
-        <v>344</v>
-      </c>
-      <c r="P1" t="s">
-        <v>345</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>346</v>
-      </c>
-      <c r="R1" t="s">
-        <v>347</v>
-      </c>
-      <c r="S1" t="s">
-        <v>348</v>
-      </c>
-      <c r="T1" t="s">
-        <v>349</v>
-      </c>
-      <c r="U1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="101">
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="95">
         <v>46075</v>
       </c>
       <c r="B2">
         <v>6</v>
       </c>
-      <c r="C2" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D2" s="102" t="b">
+      <c r="C2" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="96" t="b">
         <v>0</v>
       </c>
       <c r="E2">
@@ -8986,42 +8910,42 @@
       <c r="F2">
         <v>17</v>
       </c>
-      <c r="H2" s="103">
+      <c r="H2" s="97">
         <v>0.79166666666666663</v>
       </c>
-      <c r="I2" s="103">
+      <c r="I2" s="97">
         <v>0.93055555555555558</v>
       </c>
-      <c r="K2" s="103">
+      <c r="K2" s="97">
         <v>0.81458333333333333</v>
       </c>
-      <c r="L2" s="103">
+      <c r="L2" s="97">
         <v>0.83125000000000004</v>
       </c>
-      <c r="M2" s="103">
+      <c r="M2" s="97">
         <v>0.85486111111111107</v>
       </c>
-      <c r="N2" s="103">
+      <c r="N2" s="97">
         <v>0.87777777777777777</v>
       </c>
-      <c r="O2" s="103">
+      <c r="O2" s="97">
         <v>0.90069444444444446</v>
       </c>
-      <c r="P2" s="103">
+      <c r="P2" s="97">
         <v>0.92638888888888893</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="101">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="95">
         <v>46089</v>
       </c>
       <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" s="102" t="b">
+      <c r="C3" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="96" t="b">
         <v>0</v>
       </c>
       <c r="E3">
@@ -9033,51 +8957,51 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="103">
+      <c r="H3" s="97">
         <v>0.68541666666666667</v>
       </c>
-      <c r="I3" s="103">
+      <c r="I3" s="97">
         <v>0.86527777777777781</v>
       </c>
-      <c r="J3" s="103">
+      <c r="J3" s="97">
         <v>0.6958333333333333</v>
       </c>
-      <c r="K3" s="103">
+      <c r="K3" s="97">
         <v>0.70763888888888893</v>
       </c>
-      <c r="L3" s="103">
+      <c r="L3" s="97">
         <v>0.7270833333333333</v>
       </c>
-      <c r="M3" s="103">
+      <c r="M3" s="97">
         <v>0.75069444444444444</v>
       </c>
-      <c r="N3" s="103">
+      <c r="N3" s="97">
         <v>0.77500000000000002</v>
       </c>
-      <c r="O3" s="103">
+      <c r="O3" s="97">
         <v>0.80347222222222225</v>
       </c>
-      <c r="P3" s="103">
+      <c r="P3" s="97">
         <v>0.82986111111111116</v>
       </c>
-      <c r="Q3" s="103">
+      <c r="Q3" s="97">
         <v>0.86041666666666672</v>
       </c>
-      <c r="U3" s="103">
+      <c r="U3" s="97">
         <v>0.86527777777777781</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A4" s="101">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="95">
         <v>46105</v>
       </c>
       <c r="B4">
         <v>6</v>
       </c>
-      <c r="C4" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="102" t="b">
+      <c r="C4" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="96" t="b">
         <v>0</v>
       </c>
       <c r="E4">
@@ -9089,48 +9013,48 @@
       <c r="G4">
         <v>10</v>
       </c>
-      <c r="H4" s="103">
+      <c r="H4" s="97">
         <v>0.77500000000000002</v>
       </c>
-      <c r="I4" s="103">
+      <c r="I4" s="97">
         <v>0.92777777777777781</v>
       </c>
-      <c r="J4" s="103">
+      <c r="J4" s="97">
         <v>0.78472222222222221</v>
       </c>
-      <c r="K4" s="103">
+      <c r="K4" s="97">
         <v>0.79236111111111107</v>
       </c>
-      <c r="L4" s="103">
+      <c r="L4" s="97">
         <v>0.81111111111111112</v>
       </c>
-      <c r="M4" s="103">
+      <c r="M4" s="97">
         <v>0.83194444444444449</v>
       </c>
-      <c r="N4" s="103">
+      <c r="N4" s="97">
         <v>0.85277777777777775</v>
       </c>
-      <c r="O4" s="103">
+      <c r="O4" s="97">
         <v>0.88263888888888886</v>
       </c>
-      <c r="P4" s="103">
+      <c r="P4" s="97">
         <v>0.92083333333333328</v>
       </c>
-      <c r="U4" s="103">
+      <c r="U4" s="97">
         <v>0.92777777777777781</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A5" s="101">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="95">
         <v>46118</v>
       </c>
       <c r="B5">
         <v>6</v>
       </c>
-      <c r="C5" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="102" t="b">
+      <c r="C5" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="96" t="b">
         <v>0</v>
       </c>
       <c r="E5">
@@ -9142,48 +9066,48 @@
       <c r="G5">
         <v>11</v>
       </c>
-      <c r="H5" s="103">
+      <c r="H5" s="97">
         <v>0.78333333333333333</v>
       </c>
-      <c r="I5" s="103">
+      <c r="I5" s="97">
         <v>0.9194444444444444</v>
       </c>
-      <c r="J5" s="103">
+      <c r="J5" s="97">
         <v>0.7944444444444444</v>
       </c>
-      <c r="K5" s="103">
+      <c r="K5" s="97">
         <v>0.8041666666666667</v>
       </c>
-      <c r="L5" s="103">
+      <c r="L5" s="97">
         <v>0.82291666666666663</v>
       </c>
-      <c r="M5" s="103">
+      <c r="M5" s="97">
         <v>0.84166666666666667</v>
       </c>
-      <c r="N5" s="103">
+      <c r="N5" s="97">
         <v>0.8666666666666667</v>
       </c>
-      <c r="O5" s="103">
+      <c r="O5" s="97">
         <v>0.88958333333333328</v>
       </c>
-      <c r="P5" s="103">
+      <c r="P5" s="97">
         <v>0.91388888888888886</v>
       </c>
-      <c r="U5" s="103">
+      <c r="U5" s="97">
         <v>0.9194444444444444</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A6" s="101">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="95">
         <v>46124</v>
       </c>
       <c r="B6">
         <v>6</v>
       </c>
-      <c r="C6" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="102" t="b">
+      <c r="C6" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="96" t="b">
         <v>1</v>
       </c>
       <c r="E6">
@@ -9195,39 +9119,39 @@
       <c r="G6">
         <v>5</v>
       </c>
-      <c r="H6" s="103">
+      <c r="H6" s="97">
         <v>0.64097222222222228</v>
       </c>
-      <c r="I6" s="103">
+      <c r="I6" s="97">
         <v>0.74583333333333335</v>
       </c>
-      <c r="J6" s="103">
+      <c r="J6" s="97">
         <v>0.65833333333333333</v>
       </c>
-      <c r="K6" s="103">
+      <c r="K6" s="97">
         <v>0.68611111111111112</v>
       </c>
-      <c r="L6" s="103">
+      <c r="L6" s="97">
         <v>0.71250000000000002</v>
       </c>
-      <c r="M6" s="103">
+      <c r="M6" s="97">
         <v>0.74027777777777781</v>
       </c>
-      <c r="U6" s="103">
+      <c r="U6" s="97">
         <v>0.74583333333333335</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A7" s="101">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="95">
         <v>46131</v>
       </c>
       <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" s="102" t="b">
+      <c r="C7" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" s="96" t="b">
         <v>0</v>
       </c>
       <c r="E7">
@@ -9239,418 +9163,418 @@
       <c r="G7">
         <v>6</v>
       </c>
-      <c r="H7" s="103">
+      <c r="H7" s="97">
         <v>0.54652777777777772</v>
       </c>
-      <c r="I7" s="103">
+      <c r="I7" s="97">
         <v>0.70277777777777772</v>
       </c>
-      <c r="J7" s="103">
+      <c r="J7" s="97">
         <v>0.55694444444444446</v>
       </c>
-      <c r="K7" s="103">
+      <c r="K7" s="97">
         <v>0.57222222222222219</v>
       </c>
-      <c r="L7" s="103">
+      <c r="L7" s="97">
         <v>0.59652777777777777</v>
       </c>
-      <c r="M7" s="103">
+      <c r="M7" s="97">
         <v>0.61805555555555558</v>
       </c>
-      <c r="N7" s="103">
+      <c r="N7" s="97">
         <v>0.64583333333333337</v>
       </c>
-      <c r="O7" s="103">
+      <c r="O7" s="97">
         <v>0.67500000000000004</v>
       </c>
-      <c r="P7" s="103">
+      <c r="P7" s="97">
         <v>0.69930555555555551</v>
       </c>
-      <c r="U7" s="103">
+      <c r="U7" s="97">
         <v>0.70277777777777772</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C8" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C9" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C10" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C11" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C12" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C13" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C14" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C15" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="C16" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C17" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C18" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C19" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C20" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C21" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C22" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C23" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C24" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C25" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C26" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C27" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C28" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C29" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C30" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C31" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C32" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C33" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C34" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C35" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D35" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C36" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C37" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C38" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C39" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D39" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C40" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D40" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C41" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D41" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C42" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C43" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D43" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C44" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D44" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C45" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D45" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C46" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D46" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C47" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D47" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C48" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D48" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C49" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D49" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C50" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D50" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C51" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D51" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C52" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D52" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C53" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D53" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C54" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" s="102" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C55" s="102" t="b">
-        <v>0</v>
-      </c>
-      <c r="D55" s="102" t="b">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C8" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C9" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C10" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C11" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C12" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C13" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C14" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C15" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C16" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C17" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C21" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C25" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C26" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C28" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C29" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C30" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C31" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C32" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C33" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C34" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C35" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C36" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C37" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C38" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C39" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C40" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C41" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D41" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C42" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C43" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C44" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C45" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C46" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C47" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C48" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C49" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C50" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C51" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C52" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C53" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C54" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" s="96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C55" s="96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" s="96" t="b">
         <v>0</v>
       </c>
     </row>

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4260" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E9160F4-F4CF-4F20-B7DC-ADF9830D065B}"/>
+  <xr:revisionPtr revIDLastSave="4334" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7FF52B8-417B-4081-8740-AA1E8D3555A0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7755" yWindow="3660" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="469">
   <si>
     <t>Standard Card</t>
   </si>
@@ -272,9 +272,6 @@
     <t>Heavy Overtme</t>
   </si>
   <si>
-    <t>You may repeat $L3 Provincial Actions per round</t>
-  </si>
-  <si>
     <t>Realistic Priorities</t>
   </si>
   <si>
@@ -407,9 +404,6 @@
     <t>Contingency Plans</t>
   </si>
   <si>
-    <t>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</t>
-  </si>
-  <si>
     <t>4D</t>
   </si>
   <si>
@@ -422,9 +416,6 @@
     <t>Worthless Procrastinators</t>
   </si>
   <si>
-    <t>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</t>
-  </si>
-  <si>
     <t>5D</t>
   </si>
   <si>
@@ -1016,9 +1007,6 @@
     <t>Desperate Attorneys</t>
   </si>
   <si>
-    <t>Mock Trials</t>
-  </si>
-  <si>
     <t>Players return one held Favor for each of their leader levels to each other if they have one</t>
   </si>
   <si>
@@ -1142,9 +1130,6 @@
     <t>Trade for up to $L3 additional Coins when Monetizing in the Court</t>
   </si>
   <si>
-    <t>Heavy Overtime</t>
-  </si>
-  <si>
     <t>Courtroom Gambling</t>
   </si>
   <si>
@@ -1178,15 +1163,6 @@
     <t>Abusive Power</t>
   </si>
   <si>
-    <t>Soup Kitchens</t>
-  </si>
-  <si>
-    <t>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</t>
-  </si>
-  <si>
-    <t>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</t>
-  </si>
-  <si>
     <t>Stalled Front</t>
   </si>
   <si>
@@ -1211,9 +1187,6 @@
     <t>No more than $L6 Players may use Undermarket Actions or all Players suffer sanctions on Prioritize</t>
   </si>
   <si>
-    <t xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </t>
-  </si>
-  <si>
     <t>Send Troops up to Leader's Level to the Battlefield and gain half Troops in Coins</t>
   </si>
   <si>
@@ -1376,9 +1349,6 @@
     <t>Honorable Accountability</t>
   </si>
   <si>
-    <t>Add $L3 Hits to each Roll during a Trial</t>
-  </si>
-  <si>
     <t>Add $L6 additional dice to each Roll during a Trial</t>
   </si>
   <si>
@@ -1452,13 +1422,34 @@
   </si>
   <si>
     <t>Collect 4 Commodities</t>
-  </si>
-  <si>
-    <t>Provides Private Donate action with no penalty and convert $L3 additional Coins.</t>
   </si>
   <si>
     <t>Persian
 Troops</t>
+  </si>
+  <si>
+    <t>Each Player must Deploy at least $L6 Troops or they will suffer sanctions on Donate</t>
+  </si>
+  <si>
+    <t>No Player may Deploy more than $L6 Troops or they will suffer sanctions on Donate</t>
+  </si>
+  <si>
+    <t>Each Player must have at least $L6 Cards of each type in hand or they will suffer sanctions on Monetize</t>
+  </si>
+  <si>
+    <t>No Player may have more than $L6 Cards of each type in their hand or they will suffer sanctions on Monetize</t>
+  </si>
+  <si>
+    <t>Mock Trials</t>
+  </si>
+  <si>
+    <t>You may repeat $L3 Court Actions per round</t>
+  </si>
+  <si>
+    <t>Inspiring Command</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You may repeat Provincial Actions with level 7 - $L6 (or higher) Leaders </t>
   </si>
 </sst>
 </file>
@@ -2741,6 +2732,45 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2750,42 +2780,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2794,9 +2788,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4156,7 +4147,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
@@ -4167,10 +4158,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>14</v>
@@ -4179,10 +4170,10 @@
         <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
@@ -4196,19 +4187,19 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="3"/>
@@ -4228,13 +4219,13 @@
         <v>23</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
@@ -4257,10 +4248,10 @@
         <v>29</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3"/>
@@ -4283,10 +4274,10 @@
         <v>35</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3"/>
@@ -4300,19 +4291,19 @@
         <v>41</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
@@ -4323,7 +4314,7 @@
         <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>44</v>
@@ -4332,13 +4323,13 @@
         <v>39</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
@@ -4355,16 +4346,16 @@
         <v>49</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
@@ -4375,22 +4366,22 @@
         <v>43</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="2"/>
@@ -4404,7 +4395,7 @@
         <v>57</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>50</v>
@@ -4416,7 +4407,7 @@
         <v>46</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="2"/>
@@ -4442,7 +4433,7 @@
         <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
@@ -4468,7 +4459,7 @@
         <v>42</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
@@ -4479,10 +4470,10 @@
         <v>60</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>71</v>
+        <v>467</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>389</v>
+        <v>468</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>63</v>
@@ -4494,7 +4485,7 @@
         <v>65</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3"/>
@@ -4505,22 +4496,22 @@
         <v>66</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>366</v>
+        <v>71</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>76</v>
+        <v>466</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="2"/>
@@ -4531,10 +4522,10 @@
         <v>70</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>79</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>80</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>72</v>
@@ -4543,10 +4534,10 @@
         <v>73</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="2"/>
@@ -4557,22 +4548,22 @@
         <v>74</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>84</v>
-      </c>
       <c r="D18" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
@@ -4580,25 +4571,25 @@
     </row>
     <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>88</v>
-      </c>
       <c r="D19" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
@@ -4606,25 +4597,25 @@
     </row>
     <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>92</v>
-      </c>
       <c r="D20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
@@ -4632,25 +4623,25 @@
     </row>
     <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>96</v>
-      </c>
       <c r="D21" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
@@ -4658,25 +4649,25 @@
     </row>
     <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>101</v>
-      </c>
       <c r="D22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="3"/>
@@ -4684,19 +4675,19 @@
     </row>
     <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>444</v>
+        <v>441</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>370</v>
       </c>
       <c r="D23" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>97</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>98</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7"/>
@@ -4706,19 +4697,19 @@
     </row>
     <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>323</v>
+        <v>465</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="9"/>
@@ -4728,19 +4719,19 @@
     </row>
     <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>467</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="E25" s="15" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
@@ -4750,19 +4741,19 @@
     </row>
     <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="E26" s="15" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4772,19 +4763,19 @@
     </row>
     <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>115</v>
-      </c>
       <c r="D27" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4794,19 +4785,19 @@
     </row>
     <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>119</v>
-      </c>
       <c r="D28" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4816,19 +4807,19 @@
     </row>
     <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4838,19 +4829,19 @@
     </row>
     <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>121</v>
+        <v>463</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7"/>
@@ -4860,19 +4851,19 @@
     </row>
     <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>126</v>
+        <v>464</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7"/>
@@ -4880,21 +4871,21 @@
       <c r="I31" s="3"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>379</v>
+        <v>461</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -4904,19 +4895,19 @@
     </row>
     <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>380</v>
+        <v>462</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -4926,13 +4917,13 @@
     </row>
     <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="16"/>
@@ -4944,13 +4935,13 @@
     </row>
     <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="16"/>
@@ -4960,15 +4951,15 @@
       <c r="I35" s="3"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>378</v>
+        <v>432</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>470</v>
+        <v>433</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4980,13 +4971,13 @@
     </row>
     <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -4998,13 +4989,13 @@
     </row>
     <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -5016,13 +5007,13 @@
     </row>
     <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -5032,16 +5023,12 @@
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>442</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="15"/>
       <c r="D40" s="6"/>
       <c r="E40" s="16"/>
       <c r="F40" s="6"/>
@@ -5050,16 +5037,12 @@
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>375</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="15"/>
       <c r="D41" s="6"/>
       <c r="E41" s="16"/>
       <c r="F41" s="6"/>
@@ -5070,7 +5053,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="16"/>
@@ -5084,7 +5067,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="16"/>
@@ -5098,7 +5081,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="16"/>
@@ -5112,7 +5095,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="16"/>
@@ -5126,7 +5109,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="16"/>
@@ -5140,7 +5123,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="16"/>
@@ -5154,7 +5137,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="16"/>
@@ -5168,7 +5151,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="16"/>
@@ -5182,7 +5165,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="16"/>
@@ -5196,7 +5179,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B51" s="99"/>
       <c r="C51" s="100"/>
@@ -5210,7 +5193,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B52" s="99"/>
       <c r="C52" s="100"/>
@@ -5224,7 +5207,7 @@
     </row>
     <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B53" s="10"/>
       <c r="C53" s="17"/>
@@ -5260,215 +5243,215 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="E1" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="F1" s="50" t="s">
         <v>158</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="G1" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="H1" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="I1" s="51" t="s">
         <v>160</v>
-      </c>
-      <c r="F1" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="G1" s="50" t="s">
-        <v>327</v>
-      </c>
-      <c r="H1" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="I1" s="51" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="C2" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="F2" s="46" t="s">
         <v>164</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="G2" s="46" t="s">
         <v>165</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="H2" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="F2" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="G2" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="H2" s="46" t="s">
-        <v>169</v>
-      </c>
       <c r="I2" s="46" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E3" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="H3" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="I3" s="38" t="s">
         <v>170</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="G3" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="H3" s="38" t="s">
-        <v>281</v>
-      </c>
-      <c r="I3" s="38" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="F4" s="38" t="s">
+        <v>354</v>
+      </c>
+      <c r="G4" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="C4" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="D4" s="38" t="s">
+      <c r="H4" s="38" t="s">
         <v>176</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>177</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="G4" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="H4" s="38" t="s">
-        <v>179</v>
       </c>
       <c r="I4" s="41"/>
     </row>
     <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="F5" s="38" t="s">
-        <v>183</v>
-      </c>
       <c r="G5" s="38" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H5" s="38" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="E6" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="F6" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>186</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>187</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>188</v>
-      </c>
       <c r="G6" s="38" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="41"/>
     </row>
     <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>283</v>
+      </c>
+      <c r="F8" s="38" t="s">
         <v>192</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>194</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>286</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>195</v>
       </c>
       <c r="G8" s="38"/>
       <c r="H8" s="38"/>
@@ -5476,22 +5459,22 @@
     </row>
     <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="E9" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="F9" s="38" t="s">
         <v>197</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="D9" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>200</v>
       </c>
       <c r="G9" s="38"/>
       <c r="H9" s="38"/>
@@ -5499,19 +5482,19 @@
     </row>
     <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F10" s="38"/>
       <c r="G10" s="38"/>
@@ -5520,17 +5503,17 @@
     </row>
     <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D11" s="38"/>
       <c r="E11" s="38" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
@@ -5539,17 +5522,17 @@
     </row>
     <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D12" s="38"/>
       <c r="E12" s="38" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="38"/>
@@ -5558,17 +5541,17 @@
     </row>
     <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="38"/>
@@ -5577,17 +5560,17 @@
     </row>
     <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="38" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="38"/>
@@ -5596,13 +5579,13 @@
     </row>
     <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D15" s="38"/>
       <c r="E15" s="38"/>
@@ -5613,13 +5596,13 @@
     </row>
     <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D16" s="38"/>
       <c r="E16" s="38"/>
@@ -5630,13 +5613,13 @@
     </row>
     <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -5647,13 +5630,13 @@
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D18" s="38"/>
       <c r="E18" s="38"/>
@@ -5664,13 +5647,13 @@
     </row>
     <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D19" s="38"/>
       <c r="E19" s="38"/>
@@ -5681,13 +5664,13 @@
     </row>
     <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="33" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D20" s="38"/>
       <c r="E20" s="38"/>
@@ -5698,13 +5681,13 @@
     </row>
     <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="33" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D21" s="38"/>
       <c r="E21" s="38"/>
@@ -5715,13 +5698,13 @@
     </row>
     <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D22" s="38"/>
       <c r="E22" s="38"/>
@@ -5732,13 +5715,13 @@
     </row>
     <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="33" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D23" s="38"/>
       <c r="E23" s="38"/>
@@ -5749,13 +5732,13 @@
     </row>
     <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D24" s="38"/>
       <c r="E24" s="38"/>
@@ -5766,13 +5749,13 @@
     </row>
     <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="35" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -5799,33 +5782,33 @@
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="61"/>
       <c r="B1" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="103" t="s">
         <v>228</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="F1" s="102" t="s">
         <v>229</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="G1" s="55" t="s">
         <v>230</v>
       </c>
-      <c r="E1" s="103" t="s">
-        <v>231</v>
-      </c>
-      <c r="F1" s="102" t="s">
-        <v>232</v>
-      </c>
-      <c r="G1" s="55" t="s">
-        <v>233</v>
-      </c>
       <c r="I1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="63" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" s="58" t="s">
         <v>67</v>
@@ -5834,47 +5817,47 @@
         <v>71</v>
       </c>
       <c r="E2" s="101" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F2" s="107" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G2" s="58" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="63" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B3" s="65" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E3" s="104" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F3" s="53" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I3" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="63" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B4" s="57" t="s">
         <v>61</v>
@@ -5883,27 +5866,27 @@
         <v>21</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E4" s="104" t="s">
         <v>75</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I4" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="63" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B5" s="62" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C5" s="62" t="s">
         <v>57</v>
@@ -5912,24 +5895,24 @@
         <v>17</v>
       </c>
       <c r="E5" s="105" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="F5" s="108" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G5" s="106" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="I5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="86" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B6" s="87" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="88" t="s">
         <v>34</v>
@@ -5938,205 +5921,205 @@
         <v>69</v>
       </c>
       <c r="E6" s="90" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F6" s="82" t="s">
         <v>58</v>
       </c>
       <c r="G6" s="91" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="66" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" s="66" t="s">
+        <v>237</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="63" t="s">
         <v>239</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="F7" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="63" t="s">
-        <v>315</v>
-      </c>
-      <c r="D7" t="s">
-        <v>241</v>
-      </c>
-      <c r="E7" s="63" t="s">
-        <v>242</v>
-      </c>
-      <c r="F7" t="s">
-        <v>243</v>
-      </c>
       <c r="G7" s="63" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="84" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B8" s="84" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C8" s="80" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D8" s="84" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F8" s="84" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G8" s="81" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="I8" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="53" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="E9" t="s">
         <v>230</v>
       </c>
-      <c r="D9" s="53" t="s">
-        <v>229</v>
-      </c>
-      <c r="E9" t="s">
-        <v>233</v>
-      </c>
       <c r="F9" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" s="65" t="s">
         <v>228</v>
-      </c>
-      <c r="G9" s="65" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="85" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B10" s="85" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="82" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="82" t="s">
-        <v>233</v>
-      </c>
       <c r="D10" s="85" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>229</v>
+      </c>
+      <c r="F10" s="85" t="s">
         <v>228</v>
       </c>
-      <c r="E10" s="82" t="s">
-        <v>232</v>
-      </c>
-      <c r="F10" s="85" t="s">
-        <v>231</v>
-      </c>
       <c r="G10" s="83" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -6150,99 +6133,99 @@
     </row>
     <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="I18" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="I19" t="s">
         <v>297</v>
-      </c>
-      <c r="I19" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E20" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D21" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G22" s="2"/>
     </row>
@@ -6256,93 +6239,93 @@
     </row>
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="I24" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="I25" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I26" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G27" s="2"/>
       <c r="I27" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -6354,7 +6337,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="I28" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -6366,7 +6349,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="I29" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -6519,208 +6502,208 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="126" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="128"/>
+      <c r="A1" s="127" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="129"/>
     </row>
     <row r="2" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="129" t="s">
-        <v>471</v>
-      </c>
-      <c r="B2" s="129" t="s">
-        <v>471</v>
-      </c>
-      <c r="C2" s="129" t="s">
-        <v>471</v>
-      </c>
-      <c r="D2" s="129" t="s">
-        <v>471</v>
-      </c>
-      <c r="E2" s="129" t="s">
-        <v>471</v>
-      </c>
-      <c r="F2" s="129" t="s">
-        <v>471</v>
+      <c r="A2" s="123" t="s">
+        <v>460</v>
+      </c>
+      <c r="B2" s="123" t="s">
+        <v>460</v>
+      </c>
+      <c r="C2" s="123" t="s">
+        <v>460</v>
+      </c>
+      <c r="D2" s="123" t="s">
+        <v>460</v>
+      </c>
+      <c r="E2" s="123" t="s">
+        <v>460</v>
+      </c>
+      <c r="F2" s="123" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="118">
-        <v>0</v>
-      </c>
-      <c r="B3" s="119">
+      <c r="A3" s="115">
+        <v>0</v>
+      </c>
+      <c r="B3" s="116">
         <v>1</v>
       </c>
-      <c r="C3" s="119">
+      <c r="C3" s="116">
         <v>2</v>
       </c>
-      <c r="D3" s="118">
+      <c r="D3" s="115">
         <v>3</v>
       </c>
-      <c r="E3" s="119">
+      <c r="E3" s="116">
         <v>4</v>
       </c>
-      <c r="F3" s="118">
+      <c r="F3" s="115">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="120">
+      <c r="A4" s="117">
         <v>25</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="F4" s="120">
+        <v>304</v>
+      </c>
+      <c r="F4" s="117">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="121">
+      <c r="A5" s="118">
         <v>24</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="D5" s="114" t="s">
-        <v>184</v>
+        <v>177</v>
+      </c>
+      <c r="D5" s="111" t="s">
+        <v>181</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="120">
+        <v>186</v>
+      </c>
+      <c r="F5" s="117">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="120">
+      <c r="A6" s="117">
         <v>23</v>
       </c>
       <c r="B6" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="D6" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" s="120">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="118">
+        <v>22</v>
+      </c>
+      <c r="B7" s="30" t="s">
         <v>207</v>
       </c>
-      <c r="D6" s="29" t="s">
-        <v>329</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>203</v>
-      </c>
-      <c r="F6" s="123">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="121">
-        <v>22</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>210</v>
-      </c>
       <c r="C7" s="30" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>372</v>
-      </c>
-      <c r="F7" s="120">
+        <v>367</v>
+      </c>
+      <c r="F7" s="117">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="120">
+      <c r="A8" s="117">
         <v>21</v>
       </c>
       <c r="B8" s="98" t="s">
-        <v>244</v>
-      </c>
-      <c r="C8" s="111" t="s">
-        <v>245</v>
-      </c>
-      <c r="D8" s="112"/>
-      <c r="E8" s="113"/>
-      <c r="F8" s="123">
+        <v>241</v>
+      </c>
+      <c r="C8" s="124" t="s">
+        <v>242</v>
+      </c>
+      <c r="D8" s="125"/>
+      <c r="E8" s="126"/>
+      <c r="F8" s="120">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="121">
+      <c r="A9" s="118">
         <v>20</v>
       </c>
       <c r="B9" s="109" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E9" s="110" t="s">
-        <v>372</v>
-      </c>
-      <c r="F9" s="120">
+        <v>367</v>
+      </c>
+      <c r="F9" s="117">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="120">
+      <c r="A10" s="117">
         <v>19</v>
       </c>
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="112" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="113" t="s">
         <v>218</v>
       </c>
-      <c r="C10" s="116" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="117" t="s">
-        <v>351</v>
-      </c>
-      <c r="E10" s="116" t="s">
-        <v>223</v>
-      </c>
-      <c r="F10" s="123">
+      <c r="D10" s="114" t="s">
+        <v>347</v>
+      </c>
+      <c r="E10" s="113" t="s">
+        <v>220</v>
+      </c>
+      <c r="F10" s="120">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="122">
+      <c r="A11" s="119">
         <v>18</v>
       </c>
-      <c r="B11" s="124">
+      <c r="B11" s="121">
         <v>17</v>
       </c>
-      <c r="C11" s="125">
+      <c r="C11" s="122">
         <v>16</v>
       </c>
-      <c r="D11" s="124">
+      <c r="D11" s="121">
         <v>15</v>
       </c>
-      <c r="E11" s="125">
+      <c r="E11" s="122">
         <v>14</v>
       </c>
-      <c r="F11" s="120">
+      <c r="F11" s="117">
         <v>13</v>
       </c>
     </row>
@@ -6860,11 +6843,11 @@
       </c>
       <c r="P1" s="67" t="str">
         <f>Cards!B15</f>
-        <v>Undeniable Advisors</v>
+        <v>Inspiring Command</v>
       </c>
       <c r="Q1" s="69" t="str">
         <f>Cards!B16</f>
-        <v>Heavy Overtime</v>
+        <v>Undeniable Advisors</v>
       </c>
       <c r="R1" s="67" t="str">
         <f>Cards!B17</f>
@@ -6892,11 +6875,11 @@
       </c>
       <c r="X1" s="67" t="str">
         <f>Cards!B23</f>
-        <v>Mock Trials</v>
+        <v>Boasting Propaganda</v>
       </c>
       <c r="Y1" s="69" t="str">
         <f>Cards!B24</f>
-        <v>Desperate Attorneys</v>
+        <v>Mock Trials</v>
       </c>
       <c r="Z1" s="67" t="str">
         <f>Cards!B25</f>
@@ -6944,7 +6927,7 @@
       </c>
       <c r="AK1" s="69" t="str">
         <f>Cards!B36</f>
-        <v>Soup Kitchens</v>
+        <v>One Man's Trash</v>
       </c>
       <c r="AL1" s="67" t="str">
         <f>Cards!B37</f>
@@ -7020,11 +7003,11 @@
       </c>
       <c r="BD1" s="69" t="str">
         <f t="shared" si="1"/>
-        <v>Undeniable Advisors</v>
+        <v>Inspiring Command</v>
       </c>
       <c r="BE1" s="67" t="str">
         <f t="shared" si="1"/>
-        <v>Heavy Overtime</v>
+        <v>Undeniable Advisors</v>
       </c>
       <c r="BF1" s="69" t="str">
         <f t="shared" si="1"/>
@@ -7052,11 +7035,11 @@
       </c>
       <c r="BL1" s="69" t="str">
         <f t="shared" si="2"/>
-        <v>Mock Trials</v>
+        <v>Boasting Propaganda</v>
       </c>
       <c r="BM1" s="67" t="str">
         <f t="shared" si="2"/>
-        <v>Desperate Attorneys</v>
+        <v>Mock Trials</v>
       </c>
       <c r="BN1" s="69" t="str">
         <f t="shared" si="2"/>
@@ -7147,11 +7130,11 @@
       </c>
       <c r="P2" s="93" t="str">
         <f>Cards!C15</f>
-        <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
+        <v xml:space="preserve">You may repeat Provincial Actions with level 7 - $L6 (or higher) Leaders </v>
       </c>
       <c r="Q2" s="92" t="str">
         <f>Cards!C16</f>
-        <v>You may repeat $L3 Provincial Actions per round</v>
+        <v>You may repeat $L3 Court Actions per round</v>
       </c>
       <c r="R2" s="93" t="str">
         <f>Cards!C17</f>
@@ -7179,7 +7162,7 @@
       </c>
       <c r="X2" s="93" t="str">
         <f>Cards!C23</f>
-        <v>Add $L3 Hits to each Roll during a Trial</v>
+        <v>Convert $L3 additional Coins during Court Donate</v>
       </c>
       <c r="Y2" s="92" t="str">
         <f>Cards!C24</f>
@@ -7231,7 +7214,7 @@
       </c>
       <c r="AK2" s="92" t="str">
         <f>Cards!C36</f>
-        <v>Provides Private Donate action with no penalty and convert $L3 additional Coins.</v>
+        <v>Draw $L6 additional cards from the top of any discard pile during Brainstorm</v>
       </c>
       <c r="AL2" s="93" t="str">
         <f>Cards!C37</f>
@@ -7307,11 +7290,11 @@
       </c>
       <c r="BD2" s="92" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">You may repeat Court Actions with level 7 - $L6 (or higher) Leaders </v>
+        <v xml:space="preserve">You may repeat Provincial Actions with level 7 - $L6 (or higher) Leaders </v>
       </c>
       <c r="BE2" s="93" t="str">
         <f t="shared" si="1"/>
-        <v>You may repeat $L3 Provincial Actions per round</v>
+        <v>You may repeat $L3 Court Actions per round</v>
       </c>
       <c r="BF2" s="92" t="str">
         <f t="shared" si="1"/>
@@ -7339,7 +7322,7 @@
       </c>
       <c r="BL2" s="92" t="str">
         <f t="shared" si="2"/>
-        <v>Add $L3 Hits to each Roll during a Trial</v>
+        <v>Convert $L3 additional Coins during Court Donate</v>
       </c>
       <c r="BM2" s="93" t="str">
         <f t="shared" si="2"/>
@@ -7635,7 +7618,7 @@
       </c>
       <c r="BO3" s="67" t="str">
         <f t="shared" si="4"/>
-        <v>Soup Kitchens</v>
+        <v>One Man's Trash</v>
       </c>
       <c r="BP3" s="69" t="str">
         <f t="shared" si="4"/>
@@ -7770,19 +7753,19 @@
       </c>
       <c r="AC4" s="74" t="str">
         <f>Cards!E30</f>
-        <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
+        <v>Each Player must have at least $L6 Cards of each type in hand or they will suffer sanctions on Monetize</v>
       </c>
       <c r="AD4" s="75" t="str">
         <f>Cards!E31</f>
-        <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
+        <v>No Player may have more than $L6 Cards of each type in their hand or they will suffer sanctions on Monetize</v>
       </c>
       <c r="AE4" s="72" t="str">
         <f>Cards!E32</f>
-        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
+        <v>Each Player must Deploy at least $L6 Troops or they will suffer sanctions on Donate</v>
       </c>
       <c r="AF4" s="72" t="str">
         <f>Cards!E33</f>
-        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
+        <v>No Player may Deploy more than $L6 Troops or they will suffer sanctions on Donate</v>
       </c>
       <c r="AG4" s="74" t="str">
         <f t="shared" ref="AG4:BL4" si="5">A4</f>
@@ -7898,19 +7881,19 @@
       </c>
       <c r="BI4" s="72" t="str">
         <f t="shared" si="5"/>
-        <v>Each Player must have at least $L6 Cards in hand or they will suffer sanctions on Monetize</v>
+        <v>Each Player must have at least $L6 Cards of each type in hand or they will suffer sanctions on Monetize</v>
       </c>
       <c r="BJ4" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>No Player may have more than $L6 Cards in their hand or they will suffer sanctions on Monetize</v>
+        <v>No Player may have more than $L6 Cards of each type in their hand or they will suffer sanctions on Monetize</v>
       </c>
       <c r="BK4" s="72" t="str">
         <f t="shared" si="5"/>
-        <v>At least $L6 Players must use Deploy or all Players suffer sanctions on Donate</v>
+        <v>Each Player must Deploy at least $L6 Troops or they will suffer sanctions on Donate</v>
       </c>
       <c r="BL4" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>No more than $L6 Players may use Deploy or all Players suffer sanctions on Donate</v>
+        <v>No Player may Deploy more than $L6 Troops or they will suffer sanctions on Donate</v>
       </c>
       <c r="BM4" s="72"/>
       <c r="BN4" s="92" t="str">
@@ -7919,7 +7902,7 @@
       </c>
       <c r="BO4" s="93" t="str">
         <f t="shared" si="4"/>
-        <v>Provides Private Donate action with no penalty and convert $L3 additional Coins.</v>
+        <v>Draw $L6 additional cards from the top of any discard pile during Brainstorm</v>
       </c>
       <c r="BP4" s="92" t="str">
         <f t="shared" si="4"/>
@@ -8519,31 +8502,31 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E1" t="s">
         <v>266</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>267</v>
-      </c>
-      <c r="D1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F1" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D2">
         <v>27.7</v>
@@ -8551,14 +8534,14 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D3">
         <v>27.7</v>
@@ -8566,14 +8549,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D4">
         <v>30.75</v>
@@ -8581,222 +8564,222 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E10" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E11" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E13" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -8817,8 +8800,7 @@
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" style="97" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="97" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.42578125" style="97" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.28515625" style="97" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" style="97" bestFit="1" customWidth="1"/>
     <col min="12" max="19" width="11.85546875" style="97" bestFit="1" customWidth="1"/>
@@ -8828,67 +8810,67 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E1" t="s">
         <v>332</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
+        <v>358</v>
+      </c>
+      <c r="G1" t="s">
+        <v>357</v>
+      </c>
+      <c r="H1" t="s">
         <v>333</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
         <v>334</v>
       </c>
-      <c r="D1" t="s">
+      <c r="J1" s="97" t="s">
+        <v>355</v>
+      </c>
+      <c r="K1" t="s">
         <v>335</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>336</v>
       </c>
-      <c r="F1" t="s">
-        <v>362</v>
-      </c>
-      <c r="G1" t="s">
-        <v>361</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="M1" t="s">
         <v>337</v>
       </c>
-      <c r="I1" t="s">
+      <c r="N1" t="s">
         <v>338</v>
       </c>
-      <c r="J1" s="97" t="s">
-        <v>359</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="O1" t="s">
         <v>339</v>
       </c>
-      <c r="L1" t="s">
+      <c r="P1" t="s">
         <v>340</v>
       </c>
-      <c r="M1" t="s">
+      <c r="Q1" t="s">
         <v>341</v>
       </c>
-      <c r="N1" t="s">
+      <c r="R1" t="s">
         <v>342</v>
       </c>
-      <c r="O1" t="s">
+      <c r="S1" t="s">
         <v>343</v>
       </c>
-      <c r="P1" t="s">
+      <c r="T1" t="s">
         <v>344</v>
       </c>
-      <c r="Q1" t="s">
-        <v>345</v>
-      </c>
-      <c r="R1" t="s">
-        <v>346</v>
-      </c>
-      <c r="S1" t="s">
-        <v>347</v>
-      </c>
-      <c r="T1" t="s">
-        <v>348</v>
-      </c>
       <c r="U1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
@@ -9195,27 +9177,150 @@
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="95">
+        <v>46138</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
       <c r="C8" s="96" t="b">
         <v>0</v>
       </c>
       <c r="D8" s="96" t="b">
         <v>0</v>
       </c>
+      <c r="E8">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8" s="97">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="I8" s="97">
+        <v>0.69513888888888886</v>
+      </c>
+      <c r="J8" s="97">
+        <v>0.64444444444444449</v>
+      </c>
+      <c r="K8" s="97">
+        <v>0.65416666666666667</v>
+      </c>
+      <c r="L8" s="97">
+        <v>0.67013888888888884</v>
+      </c>
+      <c r="M8" s="97">
+        <v>0.69166666666666665</v>
+      </c>
+      <c r="U8" s="97">
+        <v>0.69513888888888886</v>
+      </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="95">
+        <v>46145</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
       <c r="C9" s="96" t="b">
         <v>0</v>
       </c>
       <c r="D9" s="96" t="b">
         <v>0</v>
       </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>18</v>
+      </c>
+      <c r="H9" s="97">
+        <v>0.60624999999999996</v>
+      </c>
+      <c r="I9" s="97">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="J9" s="97">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="K9" s="97">
+        <v>0.62222222222222223</v>
+      </c>
+      <c r="L9" s="97">
+        <v>0.64027777777777772</v>
+      </c>
+      <c r="M9" s="97">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="N9" s="97">
+        <v>0.6791666666666667</v>
+      </c>
+      <c r="O9" s="97">
+        <v>0.69722222222222219</v>
+      </c>
+      <c r="P9" s="97">
+        <v>0.71250000000000002</v>
+      </c>
+      <c r="U9" s="97">
+        <v>0.71666666666666667</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="95">
+        <v>46152</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
       <c r="C10" s="96" t="b">
         <v>0</v>
       </c>
       <c r="D10" s="96" t="b">
         <v>0</v>
+      </c>
+      <c r="E10">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>21</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="97">
+        <v>0.54791666666666672</v>
+      </c>
+      <c r="I10" s="97">
+        <v>0.625</v>
+      </c>
+      <c r="J10" s="97">
+        <v>0.55347222222222225</v>
+      </c>
+      <c r="K10" s="97">
+        <v>0.56180555555555556</v>
+      </c>
+      <c r="L10" s="97">
+        <v>0.57361111111111107</v>
+      </c>
+      <c r="M10" s="97">
+        <v>0.58611111111111114</v>
+      </c>
+      <c r="N10" s="97">
+        <v>0.60486111111111107</v>
+      </c>
+      <c r="O10" s="97">
+        <v>0.61875000000000002</v>
+      </c>
+      <c r="U10" s="97">
+        <v>0.625</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4334" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7FF52B8-417B-4081-8740-AA1E8D3555A0}"/>
+  <xr:revisionPtr revIDLastSave="4349" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09ACA5EE-1C52-ED4B-B3FE-21E376819C86}"/>
   <bookViews>
-    <workbookView xWindow="7755" yWindow="3660" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -2732,7 +2732,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4085,23 +4085,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="39" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5390625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.18359375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="39.01171875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -4127,7 +4127,7 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
         <v>7</v>
       </c>
@@ -4153,7 +4153,7 @@
       <c r="I2" s="2"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
@@ -4179,7 +4179,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>16</v>
       </c>
@@ -4205,7 +4205,7 @@
       <c r="I4" s="3"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>20</v>
       </c>
@@ -4231,7 +4231,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -4257,7 +4257,7 @@
       <c r="I6" s="3"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>31</v>
       </c>
@@ -4283,7 +4283,7 @@
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
@@ -4309,7 +4309,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>38</v>
       </c>
@@ -4335,7 +4335,7 @@
       <c r="I9" s="3"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>40</v>
       </c>
@@ -4361,7 +4361,7 @@
       <c r="I10" s="2"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>43</v>
       </c>
@@ -4387,7 +4387,7 @@
       <c r="I11" s="2"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>47</v>
       </c>
@@ -4413,7 +4413,7 @@
       <c r="I12" s="2"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>53</v>
       </c>
@@ -4439,7 +4439,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
@@ -4465,7 +4465,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>60</v>
       </c>
@@ -4491,7 +4491,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>66</v>
       </c>
@@ -4517,7 +4517,7 @@
       <c r="I16" s="2"/>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>70</v>
       </c>
@@ -4543,7 +4543,7 @@
       <c r="I17" s="2"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>74</v>
       </c>
@@ -4569,7 +4569,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>77</v>
       </c>
@@ -4595,7 +4595,7 @@
       <c r="I19" s="2"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>81</v>
       </c>
@@ -4621,7 +4621,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>85</v>
       </c>
@@ -4647,7 +4647,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
         <v>89</v>
       </c>
@@ -4673,7 +4673,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>93</v>
       </c>
@@ -4695,7 +4695,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>98</v>
       </c>
@@ -4717,7 +4717,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>102</v>
       </c>
@@ -4739,7 +4739,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>104</v>
       </c>
@@ -4761,7 +4761,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>106</v>
       </c>
@@ -4783,7 +4783,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>109</v>
       </c>
@@ -4805,7 +4805,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
         <v>112</v>
       </c>
@@ -4827,7 +4827,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
         <v>116</v>
       </c>
@@ -4849,7 +4849,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
         <v>120</v>
       </c>
@@ -4871,7 +4871,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
         <v>124</v>
       </c>
@@ -4893,7 +4893,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
         <v>127</v>
       </c>
@@ -4915,7 +4915,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
         <v>130</v>
       </c>
@@ -4933,7 +4933,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
         <v>132</v>
       </c>
@@ -4951,7 +4951,7 @@
       <c r="I35" s="3"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
         <v>135</v>
       </c>
@@ -4969,7 +4969,7 @@
       <c r="I36" s="3"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
         <v>136</v>
       </c>
@@ -4987,7 +4987,7 @@
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
         <v>137</v>
       </c>
@@ -5005,7 +5005,7 @@
       <c r="I38" s="3"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
         <v>138</v>
       </c>
@@ -5023,7 +5023,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
         <v>139</v>
       </c>
@@ -5037,7 +5037,7 @@
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
         <v>140</v>
       </c>
@@ -5051,7 +5051,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
         <v>141</v>
       </c>
@@ -5065,7 +5065,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
         <v>142</v>
       </c>
@@ -5079,7 +5079,7 @@
       <c r="I43" s="3"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="11" t="s">
         <v>143</v>
       </c>
@@ -5093,7 +5093,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="11" t="s">
         <v>144</v>
       </c>
@@ -5107,7 +5107,7 @@
       <c r="I45" s="3"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="11" t="s">
         <v>145</v>
       </c>
@@ -5121,7 +5121,7 @@
       <c r="I46" s="3"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
         <v>146</v>
       </c>
@@ -5135,7 +5135,7 @@
       <c r="I47" s="3"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
         <v>147</v>
       </c>
@@ -5149,7 +5149,7 @@
       <c r="I48" s="3"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="11" t="s">
         <v>148</v>
       </c>
@@ -5163,7 +5163,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="11" t="s">
         <v>149</v>
       </c>
@@ -5177,7 +5177,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="4"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
         <v>150</v>
       </c>
@@ -5191,7 +5191,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="11" t="s">
         <v>151</v>
       </c>
@@ -5205,7 +5205,7 @@
       <c r="I52" s="3"/>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>152</v>
       </c>
@@ -5228,20 +5228,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D195C1D-DB02-1743-BBD2-99104C1FFD33}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.71875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" customWidth="1"/>
+    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.55859375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.26171875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.7890625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.16796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.0859375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
         <v>153</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A2" s="43" t="s">
         <v>304</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A3" s="33" t="s">
         <v>325</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="81" x14ac:dyDescent="0.2">
       <c r="A4" s="33" t="s">
         <v>171</v>
       </c>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="I4" s="41"/>
     </row>
-    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A5" s="33" t="s">
         <v>177</v>
       </c>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="I5" s="41"/>
     </row>
-    <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="108" x14ac:dyDescent="0.2">
       <c r="A6" s="33" t="s">
         <v>181</v>
       </c>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="I6" s="41"/>
     </row>
-    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A7" s="33" t="s">
         <v>186</v>
       </c>
@@ -5434,7 +5434,7 @@
       <c r="H7" s="38"/>
       <c r="I7" s="41"/>
     </row>
-    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A8" s="33" t="s">
         <v>189</v>
       </c>
@@ -5457,7 +5457,7 @@
       <c r="H8" s="38"/>
       <c r="I8" s="41"/>
     </row>
-    <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="108" x14ac:dyDescent="0.2">
       <c r="A9" s="33" t="s">
         <v>193</v>
       </c>
@@ -5480,7 +5480,7 @@
       <c r="H9" s="38"/>
       <c r="I9" s="41"/>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
         <v>453</v>
       </c>
@@ -5501,7 +5501,7 @@
       <c r="H10" s="38"/>
       <c r="I10" s="41"/>
     </row>
-    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A11" s="33" t="s">
         <v>200</v>
       </c>
@@ -5520,7 +5520,7 @@
       <c r="H11" s="38"/>
       <c r="I11" s="41"/>
     </row>
-    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A12" s="33" t="s">
         <v>201</v>
       </c>
@@ -5539,7 +5539,7 @@
       <c r="H12" s="38"/>
       <c r="I12" s="41"/>
     </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A13" s="33" t="s">
         <v>204</v>
       </c>
@@ -5558,7 +5558,7 @@
       <c r="H13" s="38"/>
       <c r="I13" s="41"/>
     </row>
-    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A14" s="33" t="s">
         <v>207</v>
       </c>
@@ -5577,7 +5577,7 @@
       <c r="H14" s="38"/>
       <c r="I14" s="41"/>
     </row>
-    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A15" s="33" t="s">
         <v>211</v>
       </c>
@@ -5594,7 +5594,7 @@
       <c r="H15" s="38"/>
       <c r="I15" s="41"/>
     </row>
-    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A16" s="33" t="s">
         <v>213</v>
       </c>
@@ -5611,7 +5611,7 @@
       <c r="H16" s="38"/>
       <c r="I16" s="41"/>
     </row>
-    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A17" s="33" t="s">
         <v>367</v>
       </c>
@@ -5628,7 +5628,7 @@
       <c r="H17" s="38"/>
       <c r="I17" s="41"/>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A18" s="33" t="s">
         <v>215</v>
       </c>
@@ -5645,7 +5645,7 @@
       <c r="H18" s="38"/>
       <c r="I18" s="41"/>
     </row>
-    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A19" s="33" t="s">
         <v>218</v>
       </c>
@@ -5662,7 +5662,7 @@
       <c r="H19" s="38"/>
       <c r="I19" s="41"/>
     </row>
-    <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A20" s="33" t="s">
         <v>220</v>
       </c>
@@ -5679,7 +5679,7 @@
       <c r="H20" s="38"/>
       <c r="I20" s="41"/>
     </row>
-    <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A21" s="33" t="s">
         <v>347</v>
       </c>
@@ -5696,7 +5696,7 @@
       <c r="H21" s="38"/>
       <c r="I21" s="41"/>
     </row>
-    <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A22" s="33" t="s">
         <v>207</v>
       </c>
@@ -5713,7 +5713,7 @@
       <c r="H22" s="38"/>
       <c r="I22" s="41"/>
     </row>
-    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A23" s="33" t="s">
         <v>211</v>
       </c>
@@ -5730,7 +5730,7 @@
       <c r="H23" s="38"/>
       <c r="I23" s="41"/>
     </row>
-    <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
         <v>213</v>
       </c>
@@ -5747,7 +5747,7 @@
       <c r="H24" s="38"/>
       <c r="I24" s="41"/>
     </row>
-    <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
         <v>367</v>
       </c>
@@ -5773,13 +5773,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920DF489-FE6D-4819-BD1A-323DFAE597A3}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="30.66796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61"/>
       <c r="B1" s="55" t="s">
         <v>225</v>
@@ -5803,7 +5803,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="63" t="s">
         <v>231</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="63" t="s">
         <v>232</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="63" t="s">
         <v>233</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="63" t="s">
         <v>234</v>
       </c>
@@ -5907,7 +5907,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="86" t="s">
         <v>235</v>
       </c>
@@ -5933,7 +5933,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="66" t="s">
         <v>236</v>
       </c>
@@ -5959,7 +5959,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="84" t="s">
         <v>287</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="53" t="s">
         <v>288</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="85" t="s">
         <v>289</v>
       </c>
@@ -6031,12 +6031,12 @@
         <v>226</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>313</v>
       </c>
@@ -6059,7 +6059,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
         <v>292</v>
@@ -6080,7 +6080,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
         <v>447</v>
@@ -6101,7 +6101,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
         <v>450</v>
@@ -6122,7 +6122,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -6131,7 +6131,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>314</v>
       </c>
@@ -6157,7 +6157,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
         <v>453</v>
@@ -6181,7 +6181,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
         <v>292</v>
@@ -6202,7 +6202,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
@@ -6221,7 +6221,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
       <c r="B22" s="2"/>
       <c r="D22" s="2" t="s">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
       <c r="B23" s="2"/>
       <c r="D23" s="2"/>
@@ -6237,7 +6237,7 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>315</v>
       </c>
@@ -6263,7 +6263,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
         <v>201</v>
@@ -6287,7 +6287,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
         <v>414</v>
@@ -6311,7 +6311,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
@@ -6328,7 +6328,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -6340,7 +6340,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -6352,7 +6352,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -6361,7 +6361,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -6369,7 +6369,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -6377,7 +6377,7 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -6385,7 +6385,7 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -6393,7 +6393,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -6401,7 +6401,7 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -6409,7 +6409,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -6417,7 +6417,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -6425,7 +6425,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -6433,7 +6433,7 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -6441,7 +6441,7 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -6449,7 +6449,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -6457,7 +6457,7 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -6465,7 +6465,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -6473,7 +6473,7 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="3"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -6481,7 +6481,7 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -6495,10 +6495,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4430D7D8-35BC-4E32-9DE8-E2E435ADAAA0}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="36" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="37.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="6" width="30.7109375" style="26" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="26"/>
+    <col min="1" max="6" width="30.66796875" style="26" customWidth="1"/>
+    <col min="7" max="16384" width="9.14453125" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -6721,66 +6721,66 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CEB427C-0CB4-4E8D-8367-36F6DD891282}">
   <dimension ref="A1:CA6"/>
-  <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.7734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" style="53"/>
-    <col min="2" max="2" width="19.7109375" style="65"/>
-    <col min="4" max="4" width="19.7109375" style="53"/>
-    <col min="6" max="6" width="19.7109375" style="53"/>
-    <col min="8" max="8" width="19.7109375" style="53"/>
-    <col min="10" max="10" width="19.7109375" style="53"/>
-    <col min="12" max="12" width="19.7109375" style="53"/>
-    <col min="14" max="14" width="19.7109375" style="53"/>
-    <col min="16" max="16" width="19.7109375" style="53"/>
-    <col min="18" max="18" width="19.7109375" style="53"/>
-    <col min="20" max="20" width="19.7109375" style="53"/>
-    <col min="22" max="22" width="19.7109375" style="53"/>
-    <col min="24" max="24" width="19.7109375" style="53"/>
-    <col min="26" max="26" width="19.7109375" style="53"/>
-    <col min="28" max="28" width="19.7109375" style="53"/>
-    <col min="30" max="30" width="19.7109375" style="71"/>
-    <col min="31" max="32" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.7109375" customWidth="1"/>
-    <col min="42" max="42" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.7109375" style="71" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="19.7109375" style="71" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="19.7109375" style="53"/>
-    <col min="63" max="63" width="19.7109375" style="53"/>
-    <col min="65" max="65" width="19.7109375" style="53"/>
-    <col min="67" max="67" width="19.7109375" style="53"/>
-    <col min="69" max="70" width="19.7109375" style="53"/>
-    <col min="71" max="71" width="19.7109375" style="65"/>
-    <col min="73" max="73" width="19.7109375" style="53"/>
-    <col min="75" max="75" width="19.7109375" style="53"/>
-    <col min="77" max="77" width="19.7109375" style="53"/>
-    <col min="79" max="79" width="19.7109375" style="53"/>
+    <col min="1" max="1" width="19.7734375" style="53"/>
+    <col min="2" max="2" width="19.7734375" style="65"/>
+    <col min="4" max="4" width="19.7734375" style="53"/>
+    <col min="6" max="6" width="19.7734375" style="53"/>
+    <col min="8" max="8" width="19.7734375" style="53"/>
+    <col min="10" max="10" width="19.7734375" style="53"/>
+    <col min="12" max="12" width="19.7734375" style="53"/>
+    <col min="14" max="14" width="19.7734375" style="53"/>
+    <col min="16" max="16" width="19.7734375" style="53"/>
+    <col min="18" max="18" width="19.7734375" style="53"/>
+    <col min="20" max="20" width="19.7734375" style="53"/>
+    <col min="22" max="22" width="19.7734375" style="53"/>
+    <col min="24" max="24" width="19.7734375" style="53"/>
+    <col min="26" max="26" width="19.7734375" style="53"/>
+    <col min="28" max="28" width="19.7734375" style="53"/>
+    <col min="30" max="30" width="19.7734375" style="71"/>
+    <col min="31" max="32" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.7734375" customWidth="1"/>
+    <col min="42" max="42" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.7734375" style="71" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19.7734375" style="71" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="19.7734375" style="53"/>
+    <col min="63" max="63" width="19.7734375" style="53"/>
+    <col min="65" max="65" width="19.7734375" style="53"/>
+    <col min="67" max="67" width="19.7734375" style="53"/>
+    <col min="69" max="70" width="19.7734375" style="53"/>
+    <col min="71" max="71" width="19.7734375" style="65"/>
+    <col min="73" max="73" width="19.7734375" style="53"/>
+    <col min="75" max="75" width="19.7734375" style="53"/>
+    <col min="77" max="77" width="19.7734375" style="53"/>
+    <col min="79" max="79" width="19.7734375" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="67" t="str">
         <f>Cards!B2</f>
         <v>Fillibuster</v>
@@ -7067,7 +7067,7 @@
       <c r="BY1" s="67"/>
       <c r="CA1" s="67"/>
     </row>
-    <row r="2" spans="1:79" s="92" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:79" s="92" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="93" t="str">
         <f>Cards!C2</f>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
@@ -7354,7 +7354,7 @@
       <c r="BY2" s="93"/>
       <c r="CA2" s="93"/>
     </row>
-    <row r="3" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="67" t="str">
         <f>Cards!D2</f>
         <v>Full Coffers</v>
@@ -7638,7 +7638,7 @@
       <c r="BY3" s="67"/>
       <c r="CA3" s="67"/>
     </row>
-    <row r="4" spans="1:79" s="74" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:79" s="74" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="72" t="str">
         <f>Cards!E2</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
@@ -7922,7 +7922,7 @@
       <c r="BY4" s="72"/>
       <c r="CA4" s="72"/>
     </row>
-    <row r="5" spans="1:79" s="78" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:79" s="78" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="76" t="str">
         <f>Cards!F2</f>
         <v>Fickle Mercenaries</v>
@@ -8202,7 +8202,7 @@
       <c r="BY5" s="76"/>
       <c r="CA5" s="76"/>
     </row>
-    <row r="6" spans="1:79" s="74" customFormat="1" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:79" s="74" customFormat="1" ht="81.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="72" t="str">
         <f>Cards!G2</f>
         <v>Give $2D6 Troops to $R</v>
@@ -8491,16 +8491,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BDA35E-BFC3-134A-A064-89D65A8B31CF}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.50390625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.22265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>263</v>
       </c>
@@ -8517,7 +8517,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>244</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>245</v>
       </c>
@@ -8547,7 +8547,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>246</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>247</v>
       </c>
@@ -8574,7 +8574,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>259</v>
       </c>
@@ -8589,7 +8589,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>248</v>
       </c>
@@ -8604,7 +8604,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>249</v>
       </c>
@@ -8619,7 +8619,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>250</v>
       </c>
@@ -8631,7 +8631,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>251</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>252</v>
       </c>
@@ -8661,7 +8661,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>253</v>
       </c>
@@ -8676,7 +8676,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>254</v>
       </c>
@@ -8691,7 +8691,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>255</v>
       </c>
@@ -8702,7 +8702,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>256</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>257</v>
       </c>
@@ -8724,7 +8724,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>258</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>262</v>
       </c>
@@ -8747,7 +8747,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>261</v>
       </c>
@@ -8759,7 +8759,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>260</v>
       </c>
@@ -8771,7 +8771,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>275</v>
       </c>
@@ -8791,24 +8791,24 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC83F89-2724-CA43-A519-59213A612B31}">
   <dimension ref="A1:U55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24" style="95" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.42578125" style="97" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="97" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="97" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="11.85546875" style="97" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" style="97" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.9453125" style="95" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.72265625" customWidth="1"/>
+    <col min="4" max="4" width="8.33984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.27734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.43359375" style="97" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.22265625" style="97" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.43359375" style="97" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="11.8359375" style="97" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.9140625" style="97" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>328</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="95">
         <v>46075</v>
       </c>
@@ -8917,7 +8917,7 @@
         <v>0.92638888888888893</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="95">
         <v>46089</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>0.86527777777777781</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="95">
         <v>46105</v>
       </c>
@@ -9026,7 +9026,7 @@
         <v>0.92777777777777781</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="95">
         <v>46118</v>
       </c>
@@ -9079,7 +9079,7 @@
         <v>0.9194444444444444</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="95">
         <v>46124</v>
       </c>
@@ -9123,7 +9123,7 @@
         <v>0.74583333333333335</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="95">
         <v>46131</v>
       </c>
@@ -9176,7 +9176,7 @@
         <v>0.70277777777777772</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="95">
         <v>46138</v>
       </c>
@@ -9220,7 +9220,7 @@
         <v>0.69513888888888886</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="95">
         <v>46145</v>
       </c>
@@ -9273,7 +9273,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="95">
         <v>46152</v>
       </c>
@@ -9323,15 +9323,60 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="95">
+        <v>46158</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
       <c r="C11" s="96" t="b">
         <v>0</v>
       </c>
       <c r="D11" s="96" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>24</v>
+      </c>
+      <c r="G11">
+        <v>12</v>
+      </c>
+      <c r="H11" s="97">
+        <v>0.84236111111111112</v>
+      </c>
+      <c r="I11" s="97">
+        <v>0.99236111111111114</v>
+      </c>
+      <c r="J11" s="97">
+        <v>0.85902777777777772</v>
+      </c>
+      <c r="K11" s="97">
+        <v>0.87222222222222223</v>
+      </c>
+      <c r="L11" s="97">
+        <v>0.88958333333333328</v>
+      </c>
+      <c r="M11" s="97">
+        <v>0.90625</v>
+      </c>
+      <c r="N11" s="97">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="O11" s="97">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="P11" s="97">
+        <v>0.98888888888888893</v>
+      </c>
+      <c r="U11" s="97">
+        <v>0.99236111111111114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="96" t="b">
         <v>0</v>
       </c>
@@ -9339,7 +9384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="96" t="b">
         <v>0</v>
       </c>
@@ -9347,7 +9392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="96" t="b">
         <v>0</v>
       </c>
@@ -9355,7 +9400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="96" t="b">
         <v>0</v>
       </c>
@@ -9363,7 +9408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C16" s="96" t="b">
         <v>0</v>
       </c>
@@ -9371,7 +9416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C17" s="96" t="b">
         <v>0</v>
       </c>
@@ -9379,7 +9424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C18" s="96" t="b">
         <v>0</v>
       </c>
@@ -9387,7 +9432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C19" s="96" t="b">
         <v>0</v>
       </c>
@@ -9395,7 +9440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C20" s="96" t="b">
         <v>0</v>
       </c>
@@ -9403,7 +9448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C21" s="96" t="b">
         <v>0</v>
       </c>
@@ -9411,7 +9456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C22" s="96" t="b">
         <v>0</v>
       </c>
@@ -9419,7 +9464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C23" s="96" t="b">
         <v>0</v>
       </c>
@@ -9427,7 +9472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C24" s="96" t="b">
         <v>0</v>
       </c>
@@ -9435,7 +9480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C25" s="96" t="b">
         <v>0</v>
       </c>
@@ -9443,7 +9488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C26" s="96" t="b">
         <v>0</v>
       </c>
@@ -9451,7 +9496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C27" s="96" t="b">
         <v>0</v>
       </c>
@@ -9459,7 +9504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C28" s="96" t="b">
         <v>0</v>
       </c>
@@ -9467,7 +9512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C29" s="96" t="b">
         <v>0</v>
       </c>
@@ -9475,7 +9520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C30" s="96" t="b">
         <v>0</v>
       </c>
@@ -9483,7 +9528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C31" s="96" t="b">
         <v>0</v>
       </c>
@@ -9491,7 +9536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C32" s="96" t="b">
         <v>0</v>
       </c>
@@ -9499,7 +9544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C33" s="96" t="b">
         <v>0</v>
       </c>
@@ -9507,7 +9552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C34" s="96" t="b">
         <v>0</v>
       </c>
@@ -9515,7 +9560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C35" s="96" t="b">
         <v>0</v>
       </c>
@@ -9523,7 +9568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C36" s="96" t="b">
         <v>0</v>
       </c>
@@ -9531,7 +9576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C37" s="96" t="b">
         <v>0</v>
       </c>
@@ -9539,7 +9584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C38" s="96" t="b">
         <v>0</v>
       </c>
@@ -9547,7 +9592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C39" s="96" t="b">
         <v>0</v>
       </c>
@@ -9555,7 +9600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C40" s="96" t="b">
         <v>0</v>
       </c>
@@ -9563,7 +9608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C41" s="96" t="b">
         <v>0</v>
       </c>
@@ -9571,7 +9616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C42" s="96" t="b">
         <v>0</v>
       </c>
@@ -9579,7 +9624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C43" s="96" t="b">
         <v>0</v>
       </c>
@@ -9587,7 +9632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C44" s="96" t="b">
         <v>0</v>
       </c>
@@ -9595,7 +9640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C45" s="96" t="b">
         <v>0</v>
       </c>
@@ -9603,7 +9648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C46" s="96" t="b">
         <v>0</v>
       </c>
@@ -9611,7 +9656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C47" s="96" t="b">
         <v>0</v>
       </c>
@@ -9619,7 +9664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C48" s="96" t="b">
         <v>0</v>
       </c>
@@ -9627,7 +9672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C49" s="96" t="b">
         <v>0</v>
       </c>
@@ -9635,7 +9680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C50" s="96" t="b">
         <v>0</v>
       </c>
@@ -9643,7 +9688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C51" s="96" t="b">
         <v>0</v>
       </c>
@@ -9651,7 +9696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C52" s="96" t="b">
         <v>0</v>
       </c>
@@ -9659,7 +9704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C53" s="96" t="b">
         <v>0</v>
       </c>
@@ -9667,7 +9712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C54" s="96" t="b">
         <v>0</v>
       </c>
@@ -9675,7 +9720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C55" s="96" t="b">
         <v>0</v>
       </c>

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4349" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09ACA5EE-1C52-ED4B-B3FE-21E376819C86}"/>
+  <xr:revisionPtr revIDLastSave="4360" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A30327A-1BCC-0146-A681-773EE6088D85}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="478">
   <si>
     <t>Standard Card</t>
   </si>
@@ -221,9 +221,6 @@
     <t>Aggressive Tactics</t>
   </si>
   <si>
-    <t>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</t>
-  </si>
-  <si>
     <t>AS</t>
   </si>
   <si>
@@ -236,9 +233,6 @@
     <t>Home Defense</t>
   </si>
   <si>
-    <t>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</t>
-  </si>
-  <si>
     <t>Betrayal</t>
   </si>
   <si>
@@ -333,9 +327,6 @@
   </si>
   <si>
     <t>Bloated Bureaucracy</t>
-  </si>
-  <si>
-    <t>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</t>
   </si>
   <si>
     <t>10S</t>
@@ -1450,6 +1441,27 @@
   </si>
   <si>
     <t xml:space="preserve">You may repeat Provincial Actions with level 7 - $L6 (or higher) Leaders </t>
+  </si>
+  <si>
+    <t>No Player may have more than 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</t>
+  </si>
+  <si>
+    <t>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition</t>
+  </si>
+  <si>
+    <t>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition</t>
+  </si>
+  <si>
+    <t>Each Player must Donate at least $L6 Coins or they will suffer sanctions on Postpone &amp; Prioritize</t>
+  </si>
+  <si>
+    <t>No Player may Donate more than $L6 Coins or they will suffer sanctions on Postpone &amp; Prioritize</t>
+  </si>
+  <si>
+    <t>Centralized Economy</t>
+  </si>
+  <si>
+    <t>Partisan Contributions</t>
   </si>
 </sst>
 </file>
@@ -4147,7 +4159,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
@@ -4158,10 +4170,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>14</v>
@@ -4170,10 +4182,10 @@
         <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
@@ -4187,19 +4199,19 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="3"/>
@@ -4219,13 +4231,13 @@
         <v>23</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
@@ -4248,10 +4260,10 @@
         <v>29</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3"/>
@@ -4274,10 +4286,10 @@
         <v>35</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3"/>
@@ -4291,19 +4303,19 @@
         <v>41</v>
       </c>
       <c r="C8" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>317</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>421</v>
-      </c>
       <c r="G8" s="9" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
@@ -4314,7 +4326,7 @@
         <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>44</v>
@@ -4323,13 +4335,13 @@
         <v>39</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
@@ -4346,16 +4358,16 @@
         <v>49</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="E10" s="15" t="s">
-        <v>437</v>
-      </c>
       <c r="F10" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
@@ -4366,22 +4378,22 @@
         <v>43</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="2"/>
@@ -4395,7 +4407,7 @@
         <v>57</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>50</v>
@@ -4407,7 +4419,7 @@
         <v>46</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="2"/>
@@ -4418,10 +4430,10 @@
         <v>53</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>61</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>62</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>54</v>
@@ -4433,59 +4445,59 @@
         <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>59</v>
+        <v>467</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>42</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C15" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>468</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="F15" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="G15" s="7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3"/>
@@ -4493,25 +4505,25 @@
     </row>
     <row r="16" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="2"/>
@@ -4519,25 +4531,25 @@
     </row>
     <row r="17" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>72</v>
-      </c>
       <c r="E17" s="15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="2"/>
@@ -4545,25 +4557,25 @@
     </row>
     <row r="18" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="E18" s="15" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
@@ -4571,25 +4583,25 @@
     </row>
     <row r="19" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
@@ -4597,25 +4609,25 @@
     </row>
     <row r="20" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
@@ -4623,25 +4635,25 @@
     </row>
     <row r="21" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
@@ -4649,45 +4661,45 @@
     </row>
     <row r="22" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="3"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>97</v>
+        <v>466</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7"/>
@@ -4697,19 +4709,19 @@
     </row>
     <row r="24" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>101</v>
-      </c>
       <c r="E24" s="15" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="9"/>
@@ -4719,19 +4731,19 @@
     </row>
     <row r="25" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
@@ -4741,19 +4753,19 @@
     </row>
     <row r="26" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4763,19 +4775,19 @@
     </row>
     <row r="27" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4785,19 +4797,19 @@
     </row>
     <row r="28" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4807,19 +4819,19 @@
     </row>
     <row r="29" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>115</v>
-      </c>
       <c r="E29" s="15" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4829,19 +4841,19 @@
     </row>
     <row r="30" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="E30" s="15" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7"/>
@@ -4851,19 +4863,19 @@
     </row>
     <row r="31" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="E31" s="15" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7"/>
@@ -4873,19 +4885,19 @@
     </row>
     <row r="32" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -4895,19 +4907,19 @@
     </row>
     <row r="33" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -4915,36 +4927,44 @@
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="16"/>
+        <v>348</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>469</v>
+      </c>
       <c r="F34" s="6"/>
       <c r="G34" s="7"/>
       <c r="H34" s="4"/>
       <c r="I34" s="3"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>361</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="16"/>
+        <v>358</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>470</v>
+      </c>
       <c r="F35" s="6"/>
       <c r="G35" s="7"/>
       <c r="H35" s="4"/>
@@ -4953,13 +4973,13 @@
     </row>
     <row r="36" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4971,13 +4991,13 @@
     </row>
     <row r="37" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -4989,13 +5009,13 @@
     </row>
     <row r="38" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -5007,13 +5027,13 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -5025,7 +5045,7 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="15"/>
@@ -5039,7 +5059,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="15"/>
@@ -5053,7 +5073,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="16"/>
@@ -5067,7 +5087,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="16"/>
@@ -5081,7 +5101,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="16"/>
@@ -5095,7 +5115,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="16"/>
@@ -5109,7 +5129,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="16"/>
@@ -5123,7 +5143,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="16"/>
@@ -5137,7 +5157,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="16"/>
@@ -5151,7 +5171,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="11" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="16"/>
@@ -5165,7 +5185,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="11" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="16"/>
@@ -5179,7 +5199,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B51" s="99"/>
       <c r="C51" s="100"/>
@@ -5193,7 +5213,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B52" s="99"/>
       <c r="C52" s="100"/>
@@ -5207,7 +5227,7 @@
     </row>
     <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B53" s="10"/>
       <c r="C53" s="17"/>
@@ -5243,215 +5263,215 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="E1" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="F1" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="G1" s="50" t="s">
+        <v>320</v>
+      </c>
+      <c r="H1" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="I1" s="51" t="s">
         <v>157</v>
-      </c>
-      <c r="F1" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="G1" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="H1" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="I1" s="51" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A2" s="43" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C2" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2" s="46" t="s">
         <v>161</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="G2" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="H2" s="46" t="s">
         <v>163</v>
       </c>
-      <c r="F2" s="46" t="s">
-        <v>164</v>
-      </c>
-      <c r="G2" s="46" t="s">
-        <v>165</v>
-      </c>
-      <c r="H2" s="46" t="s">
-        <v>166</v>
-      </c>
       <c r="I2" s="46" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A3" s="33" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E3" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="H3" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="I3" s="38" t="s">
         <v>167</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>168</v>
-      </c>
-      <c r="G3" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="H3" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="I3" s="38" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="81" x14ac:dyDescent="0.2">
       <c r="A4" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="F4" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="G4" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="C4" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="D4" s="38" t="s">
+      <c r="H4" s="38" t="s">
         <v>173</v>
-      </c>
-      <c r="E4" s="38" t="s">
-        <v>174</v>
-      </c>
-      <c r="F4" s="38" t="s">
-        <v>354</v>
-      </c>
-      <c r="G4" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="H4" s="38" t="s">
-        <v>176</v>
       </c>
       <c r="I4" s="41"/>
     </row>
     <row r="5" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A5" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="D5" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>179</v>
-      </c>
-      <c r="F5" s="38" t="s">
-        <v>180</v>
-      </c>
       <c r="G5" s="38" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H5" s="38" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:9" ht="108" x14ac:dyDescent="0.2">
       <c r="A6" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="F6" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>184</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>185</v>
-      </c>
       <c r="G6" s="38" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A7" s="33" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E7" s="38" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="41"/>
     </row>
     <row r="8" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A8" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>280</v>
+      </c>
+      <c r="F8" s="38" t="s">
         <v>189</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>283</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>192</v>
       </c>
       <c r="G8" s="38"/>
       <c r="H8" s="38"/>
@@ -5459,22 +5479,22 @@
     </row>
     <row r="9" spans="1:9" ht="108" x14ac:dyDescent="0.2">
       <c r="A9" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="F9" s="38" t="s">
         <v>194</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="D9" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="E9" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>197</v>
       </c>
       <c r="G9" s="38"/>
       <c r="H9" s="38"/>
@@ -5482,19 +5502,19 @@
     </row>
     <row r="10" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C10" s="34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E10" s="38" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F10" s="38"/>
       <c r="G10" s="38"/>
@@ -5503,17 +5523,17 @@
     </row>
     <row r="11" spans="1:9" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A11" s="33" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D11" s="38"/>
       <c r="E11" s="38" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
@@ -5522,17 +5542,17 @@
     </row>
     <row r="12" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A12" s="33" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D12" s="38"/>
       <c r="E12" s="38" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="38"/>
@@ -5541,17 +5561,17 @@
     </row>
     <row r="13" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A13" s="33" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="38"/>
@@ -5560,17 +5580,17 @@
     </row>
     <row r="14" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A14" s="33" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="38" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="38"/>
@@ -5579,13 +5599,13 @@
     </row>
     <row r="15" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A15" s="33" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D15" s="38"/>
       <c r="E15" s="38"/>
@@ -5596,13 +5616,13 @@
     </row>
     <row r="16" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A16" s="33" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D16" s="38"/>
       <c r="E16" s="38"/>
@@ -5613,13 +5633,13 @@
     </row>
     <row r="17" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A17" s="33" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -5630,13 +5650,13 @@
     </row>
     <row r="18" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A18" s="33" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C18" s="34" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D18" s="38"/>
       <c r="E18" s="38"/>
@@ -5647,13 +5667,13 @@
     </row>
     <row r="19" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A19" s="33" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C19" s="34" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D19" s="38"/>
       <c r="E19" s="38"/>
@@ -5664,13 +5684,13 @@
     </row>
     <row r="20" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A20" s="33" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D20" s="38"/>
       <c r="E20" s="38"/>
@@ -5681,13 +5701,13 @@
     </row>
     <row r="21" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A21" s="33" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C21" s="34" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D21" s="38"/>
       <c r="E21" s="38"/>
@@ -5698,13 +5718,13 @@
     </row>
     <row r="22" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A22" s="33" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D22" s="38"/>
       <c r="E22" s="38"/>
@@ -5715,13 +5735,13 @@
     </row>
     <row r="23" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A23" s="33" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D23" s="38"/>
       <c r="E23" s="38"/>
@@ -5732,13 +5752,13 @@
     </row>
     <row r="24" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D24" s="38"/>
       <c r="E24" s="38"/>
@@ -5749,13 +5769,13 @@
     </row>
     <row r="25" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -5782,111 +5802,111 @@
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61"/>
       <c r="B1" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="E1" s="103" t="s">
         <v>225</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="F1" s="102" t="s">
         <v>226</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="G1" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="E1" s="103" t="s">
-        <v>228</v>
-      </c>
-      <c r="F1" s="102" t="s">
-        <v>229</v>
-      </c>
-      <c r="G1" s="55" t="s">
-        <v>230</v>
-      </c>
       <c r="I1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="63" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" s="101" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F2" s="107" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G2" s="58" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="63" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B3" s="65" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E3" s="104" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F3" s="53" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="63" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" s="57" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E4" s="104" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F4" s="56" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="G4" s="57" t="s">
-        <v>110</v>
-      </c>
       <c r="I4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="63" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B5" s="62" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C5" s="62" t="s">
         <v>57</v>
@@ -5895,231 +5915,231 @@
         <v>17</v>
       </c>
       <c r="E5" s="105" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F5" s="108" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G5" s="106" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="86" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B6" s="87" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C6" s="88" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="89" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E6" s="90" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F6" s="82" t="s">
         <v>58</v>
       </c>
       <c r="G6" s="91" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="66" t="s">
+        <v>233</v>
+      </c>
+      <c r="B7" s="66" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>309</v>
+      </c>
+      <c r="D7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E7" s="63" t="s">
         <v>236</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="F7" t="s">
         <v>237</v>
       </c>
-      <c r="C7" s="63" t="s">
-        <v>312</v>
-      </c>
-      <c r="D7" t="s">
-        <v>238</v>
-      </c>
-      <c r="E7" s="63" t="s">
-        <v>239</v>
-      </c>
-      <c r="F7" t="s">
-        <v>240</v>
-      </c>
       <c r="G7" s="63" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="I7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="84" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B8" s="84" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C8" s="80" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D8" s="84" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E8" s="80" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F8" s="84" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G8" s="81" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I8" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="53" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B9" s="53" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="E9" t="s">
         <v>227</v>
       </c>
-      <c r="D9" s="53" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" t="s">
-        <v>230</v>
-      </c>
       <c r="F9" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="G9" s="65" t="s">
         <v>225</v>
-      </c>
-      <c r="G9" s="65" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="85" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B10" s="85" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="82" t="s">
         <v>227</v>
       </c>
-      <c r="C10" s="82" t="s">
-        <v>230</v>
-      </c>
       <c r="D10" s="85" t="s">
+        <v>222</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" s="85" t="s">
         <v>225</v>
       </c>
-      <c r="E10" s="82" t="s">
-        <v>229</v>
-      </c>
-      <c r="F10" s="85" t="s">
-        <v>228</v>
-      </c>
       <c r="G10" s="83" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -6133,99 +6153,99 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="I18" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="I19" t="s">
         <v>294</v>
-      </c>
-      <c r="I19" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E20" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D21" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
       <c r="B22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G22" s="2"/>
     </row>
@@ -6239,93 +6259,93 @@
     </row>
     <row r="24" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="I24" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="I25" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E26" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I26" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G27" s="2"/>
       <c r="I27" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
@@ -6337,7 +6357,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="I28" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
@@ -6349,7 +6369,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="I29" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
@@ -6503,7 +6523,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="127" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B1" s="128"/>
       <c r="C1" s="128"/>
@@ -6513,22 +6533,22 @@
     </row>
     <row r="2" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="123" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B2" s="123" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C2" s="123" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D2" s="123" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E2" s="123" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F2" s="123" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -6556,16 +6576,16 @@
         <v>25</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F4" s="117">
         <v>6</v>
@@ -6576,16 +6596,16 @@
         <v>24</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D5" s="111" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F5" s="117">
         <v>7</v>
@@ -6596,16 +6616,16 @@
         <v>23</v>
       </c>
       <c r="B6" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="C6" s="28" t="s">
-        <v>204</v>
-      </c>
       <c r="D6" s="29" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F6" s="120">
         <v>8</v>
@@ -6616,16 +6636,16 @@
         <v>22</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F7" s="117">
         <v>9</v>
@@ -6636,10 +6656,10 @@
         <v>21</v>
       </c>
       <c r="B8" s="98" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C8" s="124" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D8" s="125"/>
       <c r="E8" s="126"/>
@@ -6652,16 +6672,16 @@
         <v>20</v>
       </c>
       <c r="B9" s="109" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E9" s="110" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F9" s="117">
         <v>11</v>
@@ -6672,16 +6692,16 @@
         <v>19</v>
       </c>
       <c r="B10" s="112" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="113" t="s">
         <v>215</v>
       </c>
-      <c r="C10" s="113" t="s">
-        <v>218</v>
-      </c>
       <c r="D10" s="114" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E10" s="113" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F10" s="120">
         <v>12</v>
@@ -7689,11 +7709,11 @@
       </c>
       <c r="M4" s="74" t="str">
         <f>Cards!E14</f>
-        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition</v>
       </c>
       <c r="N4" s="72" t="str">
         <f>Cards!E15</f>
-        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition</v>
       </c>
       <c r="O4" s="74" t="str">
         <f>Cards!E16</f>
@@ -7725,7 +7745,7 @@
       </c>
       <c r="V4" s="72" t="str">
         <f>Cards!E23</f>
-        <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
+        <v>No Player may have more than 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
       <c r="W4" s="74" t="str">
         <f>Cards!E24</f>
@@ -7817,11 +7837,11 @@
       </c>
       <c r="AS4" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+        <v>Each Player must deploy at least $L6 Troops or they will suffer sanctions on Petition</v>
       </c>
       <c r="AT4" s="72" t="str">
         <f t="shared" si="5"/>
-        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition &amp; Postpone</v>
+        <v>No Player may deploy more than $L6 Troops or they will suffer sanctions on Petition</v>
       </c>
       <c r="AU4" s="74" t="str">
         <f t="shared" si="5"/>
@@ -7853,7 +7873,7 @@
       </c>
       <c r="BB4" s="74" t="str">
         <f t="shared" si="5"/>
-        <v>No Player may have more than $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
+        <v>No Player may have more than 3 + $L6 Leaders or they will suffer sanctions on Build &amp; Upgrade</v>
       </c>
       <c r="BC4" s="72" t="str">
         <f t="shared" si="5"/>
@@ -8502,31 +8522,31 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" t="s">
         <v>263</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>264</v>
-      </c>
-      <c r="D1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D2">
         <v>27.7</v>
@@ -8534,14 +8554,14 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D3">
         <v>27.7</v>
@@ -8549,14 +8569,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D4">
         <v>30.75</v>
@@ -8564,222 +8584,222 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E10" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E13" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -8810,67 +8830,67 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D1" t="s">
         <v>328</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>329</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G1" t="s">
+        <v>354</v>
+      </c>
+      <c r="H1" t="s">
         <v>330</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>331</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" s="97" t="s">
+        <v>352</v>
+      </c>
+      <c r="K1" t="s">
         <v>332</v>
       </c>
-      <c r="F1" t="s">
-        <v>358</v>
-      </c>
-      <c r="G1" t="s">
-        <v>357</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>333</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>334</v>
       </c>
-      <c r="J1" s="97" t="s">
-        <v>355</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>335</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>336</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>337</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>338</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>339</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>340</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>341</v>
       </c>
-      <c r="R1" t="s">
-        <v>342</v>
-      </c>
-      <c r="S1" t="s">
-        <v>343</v>
-      </c>
-      <c r="T1" t="s">
-        <v>344</v>
-      </c>
       <c r="U1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4360" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A30327A-1BCC-0146-A681-773EE6088D85}"/>
+  <xr:revisionPtr revIDLastSave="4361" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{814644E0-E163-4C0A-B310-8877049B5630}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="472">
   <si>
     <t>Standard Card</t>
   </si>
@@ -993,9 +993,6 @@
   </si>
   <si>
     <t>Accuse Veteran</t>
-  </si>
-  <si>
-    <t>Desperate Attorneys</t>
   </si>
   <si>
     <t>Players return one held Favor for each of their leader levels to each other if they have one</t>
@@ -2744,7 +2741,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4097,23 +4094,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.6171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5390625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.18359375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="39.01171875" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -4139,7 +4136,7 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>7</v>
       </c>
@@ -4159,21 +4156,21 @@
         <v>12</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>349</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>350</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>14</v>
@@ -4182,16 +4179,16 @@
         <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>16</v>
       </c>
@@ -4199,7 +4196,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
@@ -4211,13 +4208,13 @@
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="3"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>20</v>
       </c>
@@ -4237,13 +4234,13 @@
         <v>24</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -4260,16 +4257,16 @@
         <v>29</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>31</v>
       </c>
@@ -4286,16 +4283,16 @@
         <v>35</v>
       </c>
       <c r="F7" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>416</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>417</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
@@ -4303,7 +4300,7 @@
         <v>41</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>315</v>
@@ -4312,21 +4309,21 @@
         <v>314</v>
       </c>
       <c r="F8" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="G8" s="9" t="s">
         <v>418</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>419</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>44</v>
@@ -4338,16 +4335,16 @@
         <v>314</v>
       </c>
       <c r="F9" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>420</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>421</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>40</v>
       </c>
@@ -4358,48 +4355,48 @@
         <v>49</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="F10" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>422</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>423</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="2"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>47</v>
       </c>
@@ -4407,7 +4404,7 @@
         <v>57</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>50</v>
@@ -4419,13 +4416,13 @@
         <v>46</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="2"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>53</v>
       </c>
@@ -4445,13 +4442,13 @@
         <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
@@ -4465,45 +4462,45 @@
         <v>58</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>42</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>59</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>464</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>465</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>62</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>63</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>64</v>
       </c>
@@ -4511,25 +4508,25 @@
         <v>69</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="2"/>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>68</v>
       </c>
@@ -4546,16 +4543,16 @@
         <v>71</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="2"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>72</v>
       </c>
@@ -4569,19 +4566,19 @@
         <v>74</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>75</v>
       </c>
@@ -4595,19 +4592,19 @@
         <v>78</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>79</v>
       </c>
@@ -4621,19 +4618,19 @@
         <v>82</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>83</v>
       </c>
@@ -4647,19 +4644,19 @@
         <v>86</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>87</v>
       </c>
@@ -4673,33 +4670,33 @@
         <v>90</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="3"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>94</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7"/>
@@ -4707,21 +4704,21 @@
       <c r="I23" s="3"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>95</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="9"/>
@@ -4729,7 +4726,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>99</v>
       </c>
@@ -4737,13 +4734,13 @@
         <v>104</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
@@ -4751,7 +4748,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>101</v>
       </c>
@@ -4759,13 +4756,13 @@
         <v>107</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>102</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4773,7 +4770,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>103</v>
       </c>
@@ -4787,7 +4784,7 @@
         <v>105</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4795,7 +4792,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>106</v>
       </c>
@@ -4809,7 +4806,7 @@
         <v>108</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4817,7 +4814,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>109</v>
       </c>
@@ -4831,7 +4828,7 @@
         <v>112</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4839,7 +4836,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>113</v>
       </c>
@@ -4853,7 +4850,7 @@
         <v>116</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7"/>
@@ -4861,7 +4858,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>117</v>
       </c>
@@ -4875,7 +4872,7 @@
         <v>120</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7"/>
@@ -4883,7 +4880,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>121</v>
       </c>
@@ -4891,13 +4888,13 @@
         <v>128</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -4905,7 +4902,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>124</v>
       </c>
@@ -4916,10 +4913,10 @@
         <v>131</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -4927,21 +4924,21 @@
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>127</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>348</v>
-      </c>
       <c r="D34" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="7"/>
@@ -4949,21 +4946,21 @@
       <c r="I34" s="3"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>129</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="7"/>
@@ -4971,15 +4968,15 @@
       <c r="I35" s="3"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>132</v>
       </c>
       <c r="B36" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>429</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>430</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4989,15 +4986,15 @@
       <c r="I36" s="3"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>133</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -5007,15 +5004,15 @@
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>134</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -5025,15 +5022,15 @@
       <c r="I38" s="3"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>135</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -5043,7 +5040,7 @@
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>136</v>
       </c>
@@ -5057,7 +5054,7 @@
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>137</v>
       </c>
@@ -5071,7 +5068,7 @@
       <c r="I41" s="3"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>138</v>
       </c>
@@ -5085,7 +5082,7 @@
       <c r="I42" s="3"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>139</v>
       </c>
@@ -5099,7 +5096,7 @@
       <c r="I43" s="3"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>140</v>
       </c>
@@ -5113,7 +5110,7 @@
       <c r="I44" s="3"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>141</v>
       </c>
@@ -5127,7 +5124,7 @@
       <c r="I45" s="3"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>142</v>
       </c>
@@ -5141,7 +5138,7 @@
       <c r="I46" s="3"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>143</v>
       </c>
@@ -5155,7 +5152,7 @@
       <c r="I47" s="3"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>144</v>
       </c>
@@ -5169,7 +5166,7 @@
       <c r="I48" s="3"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>145</v>
       </c>
@@ -5183,7 +5180,7 @@
       <c r="I49" s="3"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>146</v>
       </c>
@@ -5197,7 +5194,7 @@
       <c r="I50" s="3"/>
       <c r="J50" s="4"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>147</v>
       </c>
@@ -5211,7 +5208,7 @@
       <c r="I51" s="3"/>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>148</v>
       </c>
@@ -5225,7 +5222,7 @@
       <c r="I52" s="3"/>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
         <v>149</v>
       </c>
@@ -5248,20 +5245,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D195C1D-DB02-1743-BBD2-99104C1FFD33}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.71875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.86328125" customWidth="1"/>
-    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.55859375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.26171875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.7890625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.16796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.0859375" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="47" t="s">
         <v>150</v>
       </c>
@@ -5281,7 +5278,7 @@
         <v>155</v>
       </c>
       <c r="G1" s="50" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1" s="50" t="s">
         <v>156</v>
@@ -5290,12 +5287,12 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
         <v>301</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C2" s="45" t="s">
         <v>158</v>
@@ -5316,15 +5313,15 @@
         <v>163</v>
       </c>
       <c r="I2" s="46" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C3" s="34" t="s">
         <v>158</v>
@@ -5348,7 +5345,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="81" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
         <v>168</v>
       </c>
@@ -5365,7 +5362,7 @@
         <v>171</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G4" s="38" t="s">
         <v>172</v>
@@ -5375,7 +5372,7 @@
       </c>
       <c r="I4" s="41"/>
     </row>
-    <row r="5" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="33" t="s">
         <v>174</v>
       </c>
@@ -5395,14 +5392,14 @@
         <v>177</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H5" s="38" t="s">
         <v>274</v>
       </c>
       <c r="I5" s="41"/>
     </row>
-    <row r="6" spans="1:9" ht="108" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A6" s="33" t="s">
         <v>178</v>
       </c>
@@ -5422,14 +5419,14 @@
         <v>182</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I6" s="41"/>
     </row>
-    <row r="7" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
         <v>183</v>
       </c>
@@ -5440,7 +5437,7 @@
         <v>158</v>
       </c>
       <c r="D7" s="38" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E7" s="38" t="s">
         <v>279</v>
@@ -5454,7 +5451,7 @@
       <c r="H7" s="38"/>
       <c r="I7" s="41"/>
     </row>
-    <row r="8" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="33" t="s">
         <v>186</v>
       </c>
@@ -5477,7 +5474,7 @@
       <c r="H8" s="38"/>
       <c r="I8" s="41"/>
     </row>
-    <row r="9" spans="1:9" ht="108" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="33" t="s">
         <v>190</v>
       </c>
@@ -5500,9 +5497,9 @@
       <c r="H9" s="38"/>
       <c r="I9" s="41"/>
     </row>
-    <row r="10" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B10" s="31" t="s">
         <v>195</v>
@@ -5511,7 +5508,7 @@
         <v>158</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E10" s="38" t="s">
         <v>196</v>
@@ -5521,26 +5518,26 @@
       <c r="H10" s="38"/>
       <c r="I10" s="41"/>
     </row>
-    <row r="11" spans="1:9" ht="68.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
         <v>197</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>158</v>
       </c>
       <c r="D11" s="38"/>
       <c r="E11" s="38" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
       <c r="H11" s="38"/>
       <c r="I11" s="41"/>
     </row>
-    <row r="12" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
         <v>198</v>
       </c>
@@ -5559,7 +5556,7 @@
       <c r="H12" s="38"/>
       <c r="I12" s="41"/>
     </row>
-    <row r="13" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
         <v>201</v>
       </c>
@@ -5578,7 +5575,7 @@
       <c r="H13" s="38"/>
       <c r="I13" s="41"/>
     </row>
-    <row r="14" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
         <v>204</v>
       </c>
@@ -5597,7 +5594,7 @@
       <c r="H14" s="38"/>
       <c r="I14" s="41"/>
     </row>
-    <row r="15" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>208</v>
       </c>
@@ -5614,7 +5611,7 @@
       <c r="H15" s="38"/>
       <c r="I15" s="41"/>
     </row>
-    <row r="16" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
         <v>210</v>
       </c>
@@ -5631,12 +5628,12 @@
       <c r="H16" s="38"/>
       <c r="I16" s="41"/>
     </row>
-    <row r="17" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C17" s="34" t="s">
         <v>206</v>
@@ -5648,7 +5645,7 @@
       <c r="H17" s="38"/>
       <c r="I17" s="41"/>
     </row>
-    <row r="18" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
         <v>212</v>
       </c>
@@ -5665,7 +5662,7 @@
       <c r="H18" s="38"/>
       <c r="I18" s="41"/>
     </row>
-    <row r="19" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
         <v>215</v>
       </c>
@@ -5682,7 +5679,7 @@
       <c r="H19" s="38"/>
       <c r="I19" s="41"/>
     </row>
-    <row r="20" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="33" t="s">
         <v>217</v>
       </c>
@@ -5699,12 +5696,12 @@
       <c r="H20" s="38"/>
       <c r="I20" s="41"/>
     </row>
-    <row r="21" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="B21" s="31" t="s">
         <v>344</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>345</v>
       </c>
       <c r="C21" s="34" t="s">
         <v>214</v>
@@ -5716,7 +5713,7 @@
       <c r="H21" s="38"/>
       <c r="I21" s="41"/>
     </row>
-    <row r="22" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
         <v>204</v>
       </c>
@@ -5733,7 +5730,7 @@
       <c r="H22" s="38"/>
       <c r="I22" s="41"/>
     </row>
-    <row r="23" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="33" t="s">
         <v>208</v>
       </c>
@@ -5750,7 +5747,7 @@
       <c r="H23" s="38"/>
       <c r="I23" s="41"/>
     </row>
-    <row r="24" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="35" t="s">
         <v>210</v>
       </c>
@@ -5767,12 +5764,12 @@
       <c r="H24" s="38"/>
       <c r="I24" s="41"/>
     </row>
-    <row r="25" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="35" t="s">
+        <v>363</v>
+      </c>
+      <c r="B25" s="36" t="s">
         <v>364</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>365</v>
       </c>
       <c r="C25" s="37" t="s">
         <v>214</v>
@@ -5793,13 +5790,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920DF489-FE6D-4819-BD1A-323DFAE597A3}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="30.66796875" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="61"/>
       <c r="B1" s="55" t="s">
         <v>222</v>
@@ -5823,7 +5820,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="63" t="s">
         <v>228</v>
       </c>
@@ -5849,7 +5846,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="63" t="s">
         <v>229</v>
       </c>
@@ -5857,16 +5854,16 @@
         <v>41</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E3" s="104" t="s">
         <v>92</v>
       </c>
       <c r="F3" s="53" t="s">
-        <v>317</v>
+        <v>461</v>
       </c>
       <c r="G3" s="57" t="s">
         <v>125</v>
@@ -5875,7 +5872,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="63" t="s">
         <v>230</v>
       </c>
@@ -5898,10 +5895,10 @@
         <v>107</v>
       </c>
       <c r="I4" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="63" t="s">
         <v>231</v>
       </c>
@@ -5915,19 +5912,19 @@
         <v>17</v>
       </c>
       <c r="E5" s="105" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F5" s="108" t="s">
         <v>80</v>
       </c>
       <c r="G5" s="106" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I5" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="86" t="s">
         <v>232</v>
       </c>
@@ -5953,7 +5950,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="66" t="s">
         <v>233</v>
       </c>
@@ -5979,7 +5976,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="84" t="s">
         <v>284</v>
       </c>
@@ -6005,7 +6002,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="53" t="s">
         <v>285</v>
       </c>
@@ -6028,7 +6025,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="85" t="s">
         <v>286</v>
       </c>
@@ -6051,59 +6048,59 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>310</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>289</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>296</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
         <v>289</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>295</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>183</v>
@@ -6112,22 +6109,22 @@
         <v>291</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>178</v>
@@ -6136,13 +6133,13 @@
         <v>183</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -6151,7 +6148,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>311</v>
       </c>
@@ -6165,25 +6162,25 @@
         <v>293</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>292</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I18" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>289</v>
@@ -6201,38 +6198,38 @@
         <v>294</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
         <v>289</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>290</v>
       </c>
       <c r="E20" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
         <v>289</v>
       </c>
       <c r="D21" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>290</v>
@@ -6241,7 +6238,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="2"/>
       <c r="D22" s="2" t="s">
@@ -6249,7 +6246,7 @@
       </c>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="2"/>
       <c r="D23" s="2"/>
@@ -6257,7 +6254,7 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>312</v>
       </c>
@@ -6274,16 +6271,16 @@
         <v>297</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>305</v>
       </c>
       <c r="I24" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
         <v>198</v>
@@ -6298,19 +6295,19 @@
         <v>316</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I25" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>215</v>
@@ -6319,7 +6316,7 @@
         <v>198</v>
       </c>
       <c r="E26" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>198</v>
@@ -6331,14 +6328,14 @@
         <v>303</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
         <v>300</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>301</v>
@@ -6348,7 +6345,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -6357,10 +6354,10 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="I28" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -6369,10 +6366,10 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="I29" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -6381,7 +6378,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -6389,7 +6386,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -6397,7 +6394,7 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -6405,7 +6402,7 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -6413,7 +6410,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -6421,7 +6418,7 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -6429,7 +6426,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -6437,7 +6434,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -6445,7 +6442,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -6453,7 +6450,7 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -6461,7 +6458,7 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -6469,7 +6466,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -6477,7 +6474,7 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -6485,7 +6482,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -6493,7 +6490,7 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B48" s="3"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -6501,7 +6498,7 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -6515,10 +6512,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4430D7D8-35BC-4E32-9DE8-E2E435ADAAA0}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="37.5" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="36" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="6" width="30.66796875" style="26" customWidth="1"/>
-    <col min="7" max="16384" width="9.14453125" style="26"/>
+    <col min="1" max="6" width="30.7109375" style="26" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -6533,22 +6530,22 @@
     </row>
     <row r="2" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="123" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B2" s="123" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C2" s="123" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D2" s="123" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E2" s="123" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F2" s="123" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -6576,7 +6573,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C4" s="28" t="s">
         <v>186</v>
@@ -6622,7 +6619,7 @@
         <v>201</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E6" s="28" t="s">
         <v>197</v>
@@ -6645,7 +6642,7 @@
         <v>210</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F7" s="117">
         <v>9</v>
@@ -6681,7 +6678,7 @@
         <v>210</v>
       </c>
       <c r="E9" s="110" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F9" s="117">
         <v>11</v>
@@ -6698,7 +6695,7 @@
         <v>215</v>
       </c>
       <c r="D10" s="114" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E10" s="113" t="s">
         <v>217</v>
@@ -6741,66 +6738,66 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CEB427C-0CB4-4E8D-8367-36F6DD891282}">
   <dimension ref="A1:CA6"/>
-  <sheetFormatPr defaultColWidth="19.7734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7734375" style="53"/>
-    <col min="2" max="2" width="19.7734375" style="65"/>
-    <col min="4" max="4" width="19.7734375" style="53"/>
-    <col min="6" max="6" width="19.7734375" style="53"/>
-    <col min="8" max="8" width="19.7734375" style="53"/>
-    <col min="10" max="10" width="19.7734375" style="53"/>
-    <col min="12" max="12" width="19.7734375" style="53"/>
-    <col min="14" max="14" width="19.7734375" style="53"/>
-    <col min="16" max="16" width="19.7734375" style="53"/>
-    <col min="18" max="18" width="19.7734375" style="53"/>
-    <col min="20" max="20" width="19.7734375" style="53"/>
-    <col min="22" max="22" width="19.7734375" style="53"/>
-    <col min="24" max="24" width="19.7734375" style="53"/>
-    <col min="26" max="26" width="19.7734375" style="53"/>
-    <col min="28" max="28" width="19.7734375" style="53"/>
-    <col min="30" max="30" width="19.7734375" style="71"/>
-    <col min="31" max="32" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.7734375" customWidth="1"/>
-    <col min="42" max="42" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.7734375" style="71" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="19.7734375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="19.7734375" style="71" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="19.7734375" style="53"/>
-    <col min="63" max="63" width="19.7734375" style="53"/>
-    <col min="65" max="65" width="19.7734375" style="53"/>
-    <col min="67" max="67" width="19.7734375" style="53"/>
-    <col min="69" max="70" width="19.7734375" style="53"/>
-    <col min="71" max="71" width="19.7734375" style="65"/>
-    <col min="73" max="73" width="19.7734375" style="53"/>
-    <col min="75" max="75" width="19.7734375" style="53"/>
-    <col min="77" max="77" width="19.7734375" style="53"/>
-    <col min="79" max="79" width="19.7734375" style="53"/>
+    <col min="1" max="1" width="19.7109375" style="53"/>
+    <col min="2" max="2" width="19.7109375" style="65"/>
+    <col min="4" max="4" width="19.7109375" style="53"/>
+    <col min="6" max="6" width="19.7109375" style="53"/>
+    <col min="8" max="8" width="19.7109375" style="53"/>
+    <col min="10" max="10" width="19.7109375" style="53"/>
+    <col min="12" max="12" width="19.7109375" style="53"/>
+    <col min="14" max="14" width="19.7109375" style="53"/>
+    <col min="16" max="16" width="19.7109375" style="53"/>
+    <col min="18" max="18" width="19.7109375" style="53"/>
+    <col min="20" max="20" width="19.7109375" style="53"/>
+    <col min="22" max="22" width="19.7109375" style="53"/>
+    <col min="24" max="24" width="19.7109375" style="53"/>
+    <col min="26" max="26" width="19.7109375" style="53"/>
+    <col min="28" max="28" width="19.7109375" style="53"/>
+    <col min="30" max="30" width="19.7109375" style="71"/>
+    <col min="31" max="32" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.7109375" customWidth="1"/>
+    <col min="42" max="42" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.7109375" style="71" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19.7109375" style="71" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="19.7109375" style="53"/>
+    <col min="63" max="63" width="19.7109375" style="53"/>
+    <col min="65" max="65" width="19.7109375" style="53"/>
+    <col min="67" max="67" width="19.7109375" style="53"/>
+    <col min="69" max="70" width="19.7109375" style="53"/>
+    <col min="71" max="71" width="19.7109375" style="65"/>
+    <col min="73" max="73" width="19.7109375" style="53"/>
+    <col min="75" max="75" width="19.7109375" style="53"/>
+    <col min="77" max="77" width="19.7109375" style="53"/>
+    <col min="79" max="79" width="19.7109375" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="67" t="str">
         <f>Cards!B2</f>
         <v>Fillibuster</v>
@@ -7087,7 +7084,7 @@
       <c r="BY1" s="67"/>
       <c r="CA1" s="67"/>
     </row>
-    <row r="2" spans="1:79" s="92" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:79" s="92" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="93" t="str">
         <f>Cards!C2</f>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
@@ -7374,7 +7371,7 @@
       <c r="BY2" s="93"/>
       <c r="CA2" s="93"/>
     </row>
-    <row r="3" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="67" t="str">
         <f>Cards!D2</f>
         <v>Full Coffers</v>
@@ -7658,7 +7655,7 @@
       <c r="BY3" s="67"/>
       <c r="CA3" s="67"/>
     </row>
-    <row r="4" spans="1:79" s="74" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:79" s="74" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="72" t="str">
         <f>Cards!E2</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
@@ -7942,7 +7939,7 @@
       <c r="BY4" s="72"/>
       <c r="CA4" s="72"/>
     </row>
-    <row r="5" spans="1:79" s="78" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:79" s="78" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="76" t="str">
         <f>Cards!F2</f>
         <v>Fickle Mercenaries</v>
@@ -8222,7 +8219,7 @@
       <c r="BY5" s="76"/>
       <c r="CA5" s="76"/>
     </row>
-    <row r="6" spans="1:79" s="74" customFormat="1" ht="81.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:79" s="74" customFormat="1" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="72" t="str">
         <f>Cards!G2</f>
         <v>Give $2D6 Troops to $R</v>
@@ -8511,16 +8508,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BDA35E-BFC3-134A-A064-89D65A8B31CF}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.50390625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.22265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>260</v>
       </c>
@@ -8537,7 +8534,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>241</v>
       </c>
@@ -8552,7 +8549,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>242</v>
       </c>
@@ -8567,7 +8564,7 @@
         <v>27.7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>243</v>
       </c>
@@ -8582,7 +8579,7 @@
         <v>30.75</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>244</v>
       </c>
@@ -8594,7 +8591,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>256</v>
       </c>
@@ -8609,7 +8606,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>245</v>
       </c>
@@ -8624,7 +8621,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>246</v>
       </c>
@@ -8639,7 +8636,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>247</v>
       </c>
@@ -8651,7 +8648,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>248</v>
       </c>
@@ -8666,7 +8663,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>249</v>
       </c>
@@ -8681,7 +8678,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>250</v>
       </c>
@@ -8696,7 +8693,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>251</v>
       </c>
@@ -8711,7 +8708,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>252</v>
       </c>
@@ -8722,7 +8719,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>253</v>
       </c>
@@ -8733,7 +8730,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>254</v>
       </c>
@@ -8744,7 +8741,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>255</v>
       </c>
@@ -8755,7 +8752,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>259</v>
       </c>
@@ -8767,7 +8764,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>258</v>
       </c>
@@ -8779,7 +8776,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>257</v>
       </c>
@@ -8791,7 +8788,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>272</v>
       </c>
@@ -8811,89 +8808,89 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC83F89-2724-CA43-A519-59213A612B31}">
   <dimension ref="A1:U55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.9453125" style="95" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.72265625" customWidth="1"/>
-    <col min="4" max="4" width="8.33984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.27734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5078125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.43359375" style="97" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.22265625" style="97" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.43359375" style="97" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="11.8359375" style="97" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.9140625" style="97" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" style="95" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.42578125" style="97" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="97" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="97" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="11.85546875" style="97" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.85546875" style="97" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" t="s">
         <v>325</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>326</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>327</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>328</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G1" t="s">
+        <v>353</v>
+      </c>
+      <c r="H1" t="s">
         <v>329</v>
       </c>
-      <c r="F1" t="s">
-        <v>355</v>
-      </c>
-      <c r="G1" t="s">
-        <v>354</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>330</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" s="97" t="s">
+        <v>351</v>
+      </c>
+      <c r="K1" t="s">
         <v>331</v>
       </c>
-      <c r="J1" s="97" t="s">
+      <c r="L1" t="s">
+        <v>332</v>
+      </c>
+      <c r="M1" t="s">
+        <v>333</v>
+      </c>
+      <c r="N1" t="s">
+        <v>334</v>
+      </c>
+      <c r="O1" t="s">
+        <v>335</v>
+      </c>
+      <c r="P1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>337</v>
+      </c>
+      <c r="R1" t="s">
+        <v>338</v>
+      </c>
+      <c r="S1" t="s">
+        <v>339</v>
+      </c>
+      <c r="T1" t="s">
+        <v>340</v>
+      </c>
+      <c r="U1" t="s">
         <v>352</v>
       </c>
-      <c r="K1" t="s">
-        <v>332</v>
-      </c>
-      <c r="L1" t="s">
-        <v>333</v>
-      </c>
-      <c r="M1" t="s">
-        <v>334</v>
-      </c>
-      <c r="N1" t="s">
-        <v>335</v>
-      </c>
-      <c r="O1" t="s">
-        <v>336</v>
-      </c>
-      <c r="P1" t="s">
-        <v>337</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>338</v>
-      </c>
-      <c r="R1" t="s">
-        <v>339</v>
-      </c>
-      <c r="S1" t="s">
-        <v>340</v>
-      </c>
-      <c r="T1" t="s">
-        <v>341</v>
-      </c>
-      <c r="U1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="95">
         <v>46075</v>
       </c>
@@ -8937,7 +8934,7 @@
         <v>0.92638888888888893</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="95">
         <v>46089</v>
       </c>
@@ -8993,7 +8990,7 @@
         <v>0.86527777777777781</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="95">
         <v>46105</v>
       </c>
@@ -9046,7 +9043,7 @@
         <v>0.92777777777777781</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="95">
         <v>46118</v>
       </c>
@@ -9099,7 +9096,7 @@
         <v>0.9194444444444444</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="95">
         <v>46124</v>
       </c>
@@ -9143,7 +9140,7 @@
         <v>0.74583333333333335</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="95">
         <v>46131</v>
       </c>
@@ -9196,7 +9193,7 @@
         <v>0.70277777777777772</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="95">
         <v>46138</v>
       </c>
@@ -9240,7 +9237,7 @@
         <v>0.69513888888888886</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="95">
         <v>46145</v>
       </c>
@@ -9293,7 +9290,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="95">
         <v>46152</v>
       </c>
@@ -9343,7 +9340,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="95">
         <v>46158</v>
       </c>
@@ -9396,7 +9393,7 @@
         <v>0.99236111111111114</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C12" s="96" t="b">
         <v>0</v>
       </c>
@@ -9404,7 +9401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C13" s="96" t="b">
         <v>0</v>
       </c>
@@ -9412,7 +9409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C14" s="96" t="b">
         <v>0</v>
       </c>
@@ -9420,7 +9417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C15" s="96" t="b">
         <v>0</v>
       </c>
@@ -9428,7 +9425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="C16" s="96" t="b">
         <v>0</v>
       </c>
@@ -9436,7 +9433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C17" s="96" t="b">
         <v>0</v>
       </c>
@@ -9444,7 +9441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C18" s="96" t="b">
         <v>0</v>
       </c>
@@ -9452,7 +9449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C19" s="96" t="b">
         <v>0</v>
       </c>
@@ -9460,7 +9457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C20" s="96" t="b">
         <v>0</v>
       </c>
@@ -9468,7 +9465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C21" s="96" t="b">
         <v>0</v>
       </c>
@@ -9476,7 +9473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C22" s="96" t="b">
         <v>0</v>
       </c>
@@ -9484,7 +9481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C23" s="96" t="b">
         <v>0</v>
       </c>
@@ -9492,7 +9489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C24" s="96" t="b">
         <v>0</v>
       </c>
@@ -9500,7 +9497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C25" s="96" t="b">
         <v>0</v>
       </c>
@@ -9508,7 +9505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C26" s="96" t="b">
         <v>0</v>
       </c>
@@ -9516,7 +9513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C27" s="96" t="b">
         <v>0</v>
       </c>
@@ -9524,7 +9521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C28" s="96" t="b">
         <v>0</v>
       </c>
@@ -9532,7 +9529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C29" s="96" t="b">
         <v>0</v>
       </c>
@@ -9540,7 +9537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C30" s="96" t="b">
         <v>0</v>
       </c>
@@ -9548,7 +9545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C31" s="96" t="b">
         <v>0</v>
       </c>
@@ -9556,7 +9553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C32" s="96" t="b">
         <v>0</v>
       </c>
@@ -9564,7 +9561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C33" s="96" t="b">
         <v>0</v>
       </c>
@@ -9572,7 +9569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C34" s="96" t="b">
         <v>0</v>
       </c>
@@ -9580,7 +9577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C35" s="96" t="b">
         <v>0</v>
       </c>
@@ -9588,7 +9585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C36" s="96" t="b">
         <v>0</v>
       </c>
@@ -9596,7 +9593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C37" s="96" t="b">
         <v>0</v>
       </c>
@@ -9604,7 +9601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C38" s="96" t="b">
         <v>0</v>
       </c>
@@ -9612,7 +9609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C39" s="96" t="b">
         <v>0</v>
       </c>
@@ -9620,7 +9617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C40" s="96" t="b">
         <v>0</v>
       </c>
@@ -9628,7 +9625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C41" s="96" t="b">
         <v>0</v>
       </c>
@@ -9636,7 +9633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C42" s="96" t="b">
         <v>0</v>
       </c>
@@ -9644,7 +9641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C43" s="96" t="b">
         <v>0</v>
       </c>
@@ -9652,7 +9649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C44" s="96" t="b">
         <v>0</v>
       </c>
@@ -9660,7 +9657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C45" s="96" t="b">
         <v>0</v>
       </c>
@@ -9668,7 +9665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C46" s="96" t="b">
         <v>0</v>
       </c>
@@ -9676,7 +9673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C47" s="96" t="b">
         <v>0</v>
       </c>
@@ -9684,7 +9681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C48" s="96" t="b">
         <v>0</v>
       </c>
@@ -9692,7 +9689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C49" s="96" t="b">
         <v>0</v>
       </c>
@@ -9700,7 +9697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C50" s="96" t="b">
         <v>0</v>
       </c>
@@ -9708,7 +9705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C51" s="96" t="b">
         <v>0</v>
       </c>
@@ -9716,7 +9713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C52" s="96" t="b">
         <v>0</v>
       </c>
@@ -9724,7 +9721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C53" s="96" t="b">
         <v>0</v>
       </c>
@@ -9732,7 +9729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C54" s="96" t="b">
         <v>0</v>
       </c>
@@ -9740,7 +9737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C55" s="96" t="b">
         <v>0</v>
       </c>

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4361" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{814644E0-E163-4C0A-B310-8877049B5630}"/>
+  <xr:revisionPtr revIDLastSave="4363" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B5A9EBE-F8CB-C648-82A1-9886ADB36BD6}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="474">
   <si>
     <t>Standard Card</t>
   </si>
@@ -377,9 +377,6 @@
     <t>Information Security</t>
   </si>
   <si>
-    <t>Subtract $L3 from Scheme Card rolls</t>
-  </si>
-  <si>
     <t>Suspicious Advisors</t>
   </si>
   <si>
@@ -1230,9 +1227,6 @@
   </si>
   <si>
     <t>Target Player rolls a die. If the result is a 6 or is higher than half their Troops, the Scheme is executed. Otherwise, the Scheme fails. (Scheme Guard Roll)</t>
-  </si>
-  <si>
-    <t>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</t>
   </si>
   <si>
     <t>Deploy 2 Troops for no Coins.</t>
@@ -1459,6 +1453,12 @@
   </si>
   <si>
     <t>Partisan Contributions</t>
+  </si>
+  <si>
+    <t>Subtract $L3 from Scheme Damage rolls</t>
+  </si>
+  <si>
+    <t>Subtract $L3 from Scheme Evasion rolls. An unmodified 6 always succeeds.</t>
   </si>
 </sst>
 </file>
@@ -2741,7 +2741,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4094,23 +4094,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="39" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5390625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.58984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.18359375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="39.01171875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -4136,7 +4136,7 @@
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
         <v>7</v>
       </c>
@@ -4156,21 +4156,21 @@
         <v>12</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
       <c r="J2" s="4"/>
     </row>
-    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>348</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>349</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>14</v>
@@ -4179,16 +4179,16 @@
         <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>16</v>
       </c>
@@ -4196,25 +4196,25 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="3"/>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>20</v>
       </c>
@@ -4228,19 +4228,19 @@
         <v>23</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -4257,16 +4257,16 @@
         <v>29</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
         <v>31</v>
       </c>
@@ -4283,16 +4283,16 @@
         <v>35</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
@@ -4300,30 +4300,30 @@
         <v>41</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>44</v>
@@ -4332,19 +4332,19 @@
         <v>39</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
         <v>40</v>
       </c>
@@ -4355,48 +4355,48 @@
         <v>49</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>43</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>45</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="2"/>
       <c r="J11" s="4"/>
     </row>
-    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
         <v>47</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>57</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>50</v>
@@ -4416,13 +4416,13 @@
         <v>46</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="2"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
         <v>53</v>
       </c>
@@ -4442,13 +4442,13 @@
         <v>52</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>56</v>
       </c>
@@ -4462,45 +4462,45 @@
         <v>58</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>42</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>59</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>62</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>63</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H15" s="4"/>
       <c r="I15" s="3"/>
       <c r="J15" s="4"/>
     </row>
-    <row r="16" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
         <v>64</v>
       </c>
@@ -4508,25 +4508,25 @@
         <v>69</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="2"/>
       <c r="J16" s="4"/>
     </row>
-    <row r="17" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>68</v>
       </c>
@@ -4543,16 +4543,16 @@
         <v>71</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="2"/>
       <c r="J17" s="4"/>
     </row>
-    <row r="18" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
         <v>72</v>
       </c>
@@ -4566,19 +4566,19 @@
         <v>74</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>36</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="2"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A19" s="11" t="s">
         <v>75</v>
       </c>
@@ -4592,19 +4592,19 @@
         <v>78</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="2"/>
       <c r="J19" s="4"/>
     </row>
-    <row r="20" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>79</v>
       </c>
@@ -4618,19 +4618,19 @@
         <v>82</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H20" s="4"/>
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>83</v>
       </c>
@@ -4644,19 +4644,19 @@
         <v>86</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H21" s="4"/>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A22" s="11" t="s">
         <v>87</v>
       </c>
@@ -4670,33 +4670,33 @@
         <v>90</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H22" s="4"/>
       <c r="I22" s="3"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>94</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="7"/>
@@ -4704,21 +4704,21 @@
       <c r="I23" s="3"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>95</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="9"/>
@@ -4726,7 +4726,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>99</v>
       </c>
@@ -4734,13 +4734,13 @@
         <v>104</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>100</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="7"/>
@@ -4748,7 +4748,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A26" s="11" t="s">
         <v>101</v>
       </c>
@@ -4756,13 +4756,13 @@
         <v>107</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>396</v>
+        <v>471</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>102</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="7"/>
@@ -4770,7 +4770,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>103</v>
       </c>
@@ -4778,13 +4778,13 @@
         <v>110</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>111</v>
+        <v>470</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>105</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="7"/>
@@ -4792,21 +4792,21 @@
       <c r="I27" s="3"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>106</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>114</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>115</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>108</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="7"/>
@@ -4814,21 +4814,21 @@
       <c r="I28" s="3"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
         <v>109</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>119</v>
-      </c>
       <c r="D29" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="7"/>
@@ -4836,21 +4836,21 @@
       <c r="I29" s="3"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>123</v>
-      </c>
       <c r="D30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="7"/>
@@ -4858,21 +4858,21 @@
       <c r="I30" s="3"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="C31" s="15" t="s">
-        <v>126</v>
-      </c>
       <c r="D31" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="7"/>
@@ -4880,21 +4880,21 @@
       <c r="I31" s="3"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="7"/>
@@ -4902,21 +4902,21 @@
       <c r="I32" s="3"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B33" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>131</v>
-      </c>
       <c r="D33" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="7"/>
@@ -4924,21 +4924,21 @@
       <c r="I33" s="3"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>347</v>
-      </c>
       <c r="D34" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="7"/>
@@ -4946,21 +4946,21 @@
       <c r="I34" s="3"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="7"/>
@@ -4968,15 +4968,15 @@
       <c r="I35" s="3"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="16"/>
@@ -4986,15 +4986,15 @@
       <c r="I36" s="3"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="16"/>
@@ -5004,15 +5004,15 @@
       <c r="I37" s="3"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="16"/>
@@ -5022,15 +5022,15 @@
       <c r="I38" s="3"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="16"/>
@@ -5040,9 +5040,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="15"/>
@@ -5054,9 +5054,9 @@
       <c r="I40" s="3"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="15"/>
@@ -5068,9 +5068,9 @@
       <c r="I41" s="3"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="16"/>
@@ -5082,9 +5082,9 @@
       <c r="I42" s="3"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="16"/>
@@ -5096,9 +5096,9 @@
       <c r="I43" s="3"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="16"/>
@@ -5110,9 +5110,9 @@
       <c r="I44" s="3"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="16"/>
@@ -5124,9 +5124,9 @@
       <c r="I45" s="3"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="16"/>
@@ -5138,9 +5138,9 @@
       <c r="I46" s="3"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="16"/>
@@ -5152,9 +5152,9 @@
       <c r="I47" s="3"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="16"/>
@@ -5166,9 +5166,9 @@
       <c r="I48" s="3"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="16"/>
@@ -5180,9 +5180,9 @@
       <c r="I49" s="3"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="16"/>
@@ -5194,9 +5194,9 @@
       <c r="I50" s="3"/>
       <c r="J50" s="4"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B51" s="99"/>
       <c r="C51" s="100"/>
@@ -5208,9 +5208,9 @@
       <c r="I51" s="3"/>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B52" s="99"/>
       <c r="C52" s="100"/>
@@ -5222,9 +5222,9 @@
       <c r="I52" s="3"/>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B53" s="10"/>
       <c r="C53" s="17"/>
@@ -5245,364 +5245,364 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D195C1D-DB02-1743-BBD2-99104C1FFD33}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="37.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="39.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="34.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="40.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.71875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.86328125" customWidth="1"/>
+    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.55859375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="37.26171875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.7890625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="39.546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="34.16796875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="40.0859375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="B1" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="C1" s="49" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="D1" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="D1" s="50" t="s">
+      <c r="E1" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="F1" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="G1" s="50" t="s">
+        <v>318</v>
+      </c>
+      <c r="H1" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="I1" s="51" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>376</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="G2" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="I2" s="46" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="B3" s="31" t="s">
         <v>319</v>
       </c>
-      <c r="H1" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="I1" s="51" t="s">
+      <c r="C3" s="34" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>301</v>
-      </c>
-      <c r="B2" s="44" t="s">
-        <v>377</v>
-      </c>
-      <c r="C2" s="45" t="s">
-        <v>158</v>
-      </c>
-      <c r="D2" s="46" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="F2" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="G2" s="46" t="s">
-        <v>162</v>
-      </c>
-      <c r="H2" s="46" t="s">
+      <c r="D3" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="E3" s="38" t="s">
         <v>163</v>
       </c>
-      <c r="I2" s="46" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
-        <v>321</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>320</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="38" t="s">
-        <v>304</v>
-      </c>
-      <c r="E3" s="38" t="s">
+      <c r="F3" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="G3" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="H3" s="38" t="s">
+        <v>274</v>
+      </c>
+      <c r="I3" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="H3" s="38" t="s">
-        <v>275</v>
-      </c>
-      <c r="I3" s="38" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="81" x14ac:dyDescent="0.2">
+      <c r="A4" s="33" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="105" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="B4" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="C4" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D4" s="38" t="s">
+      <c r="E4" s="38" t="s">
         <v>170</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="F4" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="G4" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="F4" s="38" t="s">
-        <v>350</v>
-      </c>
-      <c r="G4" s="38" t="s">
+      <c r="H4" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="H4" s="38" t="s">
+      <c r="I4" s="41"/>
+    </row>
+    <row r="5" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="I4" s="41"/>
-    </row>
-    <row r="5" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
+      <c r="B5" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>281</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D5" s="38" t="s">
+      <c r="E5" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="E5" s="38" t="s">
+      <c r="F5" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="G5" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="H5" s="38" t="s">
+        <v>273</v>
+      </c>
+      <c r="I5" s="41"/>
+    </row>
+    <row r="6" spans="1:9" ht="108" x14ac:dyDescent="0.2">
+      <c r="A6" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="B6" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="G6" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="H5" s="38" t="s">
-        <v>274</v>
-      </c>
-      <c r="I5" s="41"/>
-    </row>
-    <row r="6" spans="1:9" ht="135" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>181</v>
-      </c>
-      <c r="F6" s="38" t="s">
+      <c r="H6" s="38" t="s">
+        <v>379</v>
+      </c>
+      <c r="I6" s="41"/>
+    </row>
+    <row r="7" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="G6" s="38" t="s">
-        <v>318</v>
-      </c>
-      <c r="H6" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="I6" s="41"/>
-    </row>
-    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
+      <c r="B7" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="B7" s="32" t="s">
+      <c r="C7" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>354</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>278</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>305</v>
+      </c>
+      <c r="G7" s="38" t="s">
         <v>184</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" s="38" t="s">
-        <v>355</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>306</v>
-      </c>
-      <c r="G7" s="38" t="s">
-        <v>185</v>
       </c>
       <c r="H7" s="38"/>
       <c r="I7" s="41"/>
     </row>
-    <row r="8" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A8" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="B8" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="C8" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="C8" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D8" s="38" t="s">
+      <c r="E8" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="F8" s="38" t="s">
         <v>188</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>280</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>189</v>
       </c>
       <c r="G8" s="38"/>
       <c r="H8" s="38"/>
       <c r="I8" s="41"/>
     </row>
-    <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="108" x14ac:dyDescent="0.2">
       <c r="A9" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="B9" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="C9" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D9" s="38" t="s">
+      <c r="E9" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="F9" s="38" t="s">
         <v>193</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>194</v>
       </c>
       <c r="G9" s="38"/>
       <c r="H9" s="38"/>
       <c r="I9" s="41"/>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B10" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>360</v>
+      </c>
+      <c r="E10" s="38" t="s">
         <v>195</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D10" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>196</v>
       </c>
       <c r="F10" s="38"/>
       <c r="G10" s="38"/>
       <c r="H10" s="38"/>
       <c r="I10" s="41"/>
     </row>
-    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="68.25" x14ac:dyDescent="0.2">
       <c r="A11" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D11" s="38"/>
       <c r="E11" s="38" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F11" s="38"/>
       <c r="G11" s="38"/>
       <c r="H11" s="38"/>
       <c r="I11" s="41"/>
     </row>
-    <row r="12" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A12" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="B12" s="31" t="s">
-        <v>199</v>
-      </c>
       <c r="C12" s="34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" s="38"/>
       <c r="E12" s="38" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="38"/>
       <c r="H12" s="38"/>
       <c r="I12" s="41"/>
     </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A13" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="B13" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="B13" s="31" t="s">
-        <v>202</v>
-      </c>
       <c r="C13" s="34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F13" s="40"/>
       <c r="G13" s="38"/>
       <c r="H13" s="38"/>
       <c r="I13" s="41"/>
     </row>
-    <row r="14" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A14" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="B14" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="C14" s="34" t="s">
         <v>205</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>206</v>
       </c>
       <c r="D14" s="38"/>
       <c r="E14" s="38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F14" s="40"/>
       <c r="G14" s="38"/>
       <c r="H14" s="38"/>
       <c r="I14" s="41"/>
     </row>
-    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A15" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="B15" s="31" t="s">
         <v>208</v>
       </c>
-      <c r="B15" s="31" t="s">
-        <v>209</v>
-      </c>
       <c r="C15" s="34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D15" s="38"/>
       <c r="E15" s="38"/>
@@ -5611,15 +5611,15 @@
       <c r="H15" s="38"/>
       <c r="I15" s="41"/>
     </row>
-    <row r="16" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A16" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="B16" s="31" t="s">
-        <v>211</v>
-      </c>
       <c r="C16" s="34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D16" s="38"/>
       <c r="E16" s="38"/>
@@ -5628,15 +5628,15 @@
       <c r="H16" s="38"/>
       <c r="I16" s="41"/>
     </row>
-    <row r="17" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A17" s="33" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -5645,15 +5645,15 @@
       <c r="H17" s="38"/>
       <c r="I17" s="41"/>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A18" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="B18" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="C18" s="34" t="s">
         <v>213</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>214</v>
       </c>
       <c r="D18" s="38"/>
       <c r="E18" s="38"/>
@@ -5662,15 +5662,15 @@
       <c r="H18" s="38"/>
       <c r="I18" s="41"/>
     </row>
-    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A19" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>216</v>
-      </c>
       <c r="C19" s="34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D19" s="38"/>
       <c r="E19" s="38"/>
@@ -5679,15 +5679,15 @@
       <c r="H19" s="38"/>
       <c r="I19" s="41"/>
     </row>
-    <row r="20" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A20" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="B20" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>218</v>
-      </c>
       <c r="C20" s="34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D20" s="38"/>
       <c r="E20" s="38"/>
@@ -5696,15 +5696,15 @@
       <c r="H20" s="38"/>
       <c r="I20" s="41"/>
     </row>
-    <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A21" s="33" t="s">
+        <v>342</v>
+      </c>
+      <c r="B21" s="31" t="s">
         <v>343</v>
       </c>
-      <c r="B21" s="31" t="s">
-        <v>344</v>
-      </c>
       <c r="C21" s="34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D21" s="38"/>
       <c r="E21" s="38"/>
@@ -5713,15 +5713,15 @@
       <c r="H21" s="38"/>
       <c r="I21" s="41"/>
     </row>
-    <row r="22" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A22" s="33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D22" s="38"/>
       <c r="E22" s="38"/>
@@ -5730,15 +5730,15 @@
       <c r="H22" s="38"/>
       <c r="I22" s="41"/>
     </row>
-    <row r="23" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="54.75" x14ac:dyDescent="0.2">
       <c r="A23" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C23" s="34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D23" s="38"/>
       <c r="E23" s="38"/>
@@ -5747,15 +5747,15 @@
       <c r="H23" s="38"/>
       <c r="I23" s="41"/>
     </row>
-    <row r="24" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D24" s="38"/>
       <c r="E24" s="38"/>
@@ -5764,15 +5764,15 @@
       <c r="H24" s="38"/>
       <c r="I24" s="41"/>
     </row>
-    <row r="25" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="42" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
+        <v>362</v>
+      </c>
+      <c r="B25" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="B25" s="36" t="s">
-        <v>364</v>
-      </c>
       <c r="C25" s="37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D25" s="39"/>
       <c r="E25" s="39"/>
@@ -5790,39 +5790,39 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{920DF489-FE6D-4819-BD1A-323DFAE597A3}">
   <dimension ref="A1:I49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="30.66796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61"/>
       <c r="B1" s="55" t="s">
+        <v>221</v>
+      </c>
+      <c r="C1" s="55" t="s">
         <v>222</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="D1" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="E1" s="103" t="s">
         <v>224</v>
       </c>
-      <c r="E1" s="103" t="s">
+      <c r="F1" s="102" t="s">
         <v>225</v>
       </c>
-      <c r="F1" s="102" t="s">
+      <c r="G1" s="55" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="55" t="s">
+      <c r="I1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="63" t="s">
         <v>227</v>
-      </c>
-      <c r="I1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
-        <v>228</v>
       </c>
       <c r="B2" s="64" t="s">
         <v>84</v>
@@ -5840,41 +5840,41 @@
         <v>96</v>
       </c>
       <c r="G2" s="58" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="63" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B3" s="65" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E3" s="104" t="s">
         <v>92</v>
       </c>
       <c r="F3" s="53" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="63" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B4" s="57" t="s">
         <v>60</v>
@@ -5895,15 +5895,15 @@
         <v>107</v>
       </c>
       <c r="I4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="63" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B5" s="62" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C5" s="62" t="s">
         <v>57</v>
@@ -5912,21 +5912,21 @@
         <v>17</v>
       </c>
       <c r="E5" s="105" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F5" s="108" t="s">
         <v>80</v>
       </c>
       <c r="G5" s="106" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="86" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B6" s="87" t="s">
         <v>98</v>
@@ -5944,202 +5944,202 @@
         <v>58</v>
       </c>
       <c r="G6" s="91" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="66" t="s">
+        <v>232</v>
+      </c>
+      <c r="B7" s="66" t="s">
+        <v>233</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>308</v>
+      </c>
+      <c r="D7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="F7" t="s">
+        <v>236</v>
+      </c>
+      <c r="G7" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="I7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="84" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="66" t="s">
-        <v>233</v>
-      </c>
-      <c r="B7" s="66" t="s">
-        <v>234</v>
-      </c>
-      <c r="C7" s="63" t="s">
+      <c r="B8" s="84" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="80" t="s">
+        <v>225</v>
+      </c>
+      <c r="D8" s="84" t="s">
+        <v>226</v>
+      </c>
+      <c r="E8" s="80" t="s">
+        <v>221</v>
+      </c>
+      <c r="F8" s="84" t="s">
+        <v>222</v>
+      </c>
+      <c r="G8" s="81" t="s">
+        <v>223</v>
+      </c>
+      <c r="I8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="B9" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>222</v>
+      </c>
+      <c r="E9" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="G9" s="65" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="85" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>226</v>
+      </c>
+      <c r="D10" s="85" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="82" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" s="85" t="s">
+        <v>224</v>
+      </c>
+      <c r="G10" s="83" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D7" t="s">
-        <v>235</v>
-      </c>
-      <c r="E7" s="63" t="s">
-        <v>236</v>
-      </c>
-      <c r="F7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G7" s="63" t="s">
-        <v>157</v>
-      </c>
-      <c r="I7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="84" t="s">
-        <v>284</v>
-      </c>
-      <c r="B8" s="84" t="s">
-        <v>225</v>
-      </c>
-      <c r="C8" s="80" t="s">
-        <v>226</v>
-      </c>
-      <c r="D8" s="84" t="s">
-        <v>227</v>
-      </c>
-      <c r="E8" s="80" t="s">
-        <v>222</v>
-      </c>
-      <c r="F8" s="84" t="s">
-        <v>223</v>
-      </c>
-      <c r="G8" s="81" t="s">
-        <v>224</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="B13" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="53" t="s">
-        <v>285</v>
-      </c>
-      <c r="B9" s="53" t="s">
-        <v>226</v>
-      </c>
-      <c r="C9" t="s">
-        <v>224</v>
-      </c>
-      <c r="D9" s="53" t="s">
-        <v>223</v>
-      </c>
-      <c r="E9" t="s">
-        <v>227</v>
-      </c>
-      <c r="F9" s="53" t="s">
-        <v>222</v>
-      </c>
-      <c r="G9" s="65" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="85" t="s">
-        <v>286</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>224</v>
-      </c>
-      <c r="C10" s="82" t="s">
-        <v>227</v>
-      </c>
-      <c r="D10" s="85" t="s">
-        <v>222</v>
-      </c>
-      <c r="E10" s="82" t="s">
-        <v>226</v>
-      </c>
-      <c r="F10" s="85" t="s">
-        <v>225</v>
-      </c>
-      <c r="G10" s="83" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>289</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="3"/>
       <c r="B14" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="3"/>
       <c r="B15" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>445</v>
-      </c>
       <c r="G15" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
       <c r="B16" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -6148,105 +6148,105 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I18" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I19" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
       <c r="B20" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="E20" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D21" t="s">
+        <v>402</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D21" t="s">
-        <v>404</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>290</v>
-      </c>
       <c r="G21" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
       <c r="B22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
       <c r="B23" s="2"/>
       <c r="D23" s="2"/>
@@ -6254,98 +6254,98 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I24" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I25" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
       <c r="B26" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E26" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I26" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="G27" s="2"/>
       <c r="I27" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -6354,10 +6354,10 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="I28" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -6366,10 +6366,10 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="I29" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -6378,7 +6378,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -6386,7 +6386,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -6394,7 +6394,7 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -6402,7 +6402,7 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -6410,7 +6410,7 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -6418,7 +6418,7 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -6426,7 +6426,7 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -6434,7 +6434,7 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -6442,7 +6442,7 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -6450,7 +6450,7 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -6458,7 +6458,7 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -6466,7 +6466,7 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -6474,7 +6474,7 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -6482,7 +6482,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -6490,7 +6490,7 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="3"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -6498,7 +6498,7 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -6512,15 +6512,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4430D7D8-35BC-4E32-9DE8-E2E435ADAAA0}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="36" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="37.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="6" width="30.7109375" style="26" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="26"/>
+    <col min="1" max="6" width="30.66796875" style="26" customWidth="1"/>
+    <col min="7" max="16384" width="9.14453125" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="127" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1" s="128"/>
       <c r="C1" s="128"/>
@@ -6530,22 +6530,22 @@
     </row>
     <row r="2" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="123" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B2" s="123" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C2" s="123" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D2" s="123" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E2" s="123" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F2" s="123" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="99.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
@@ -6573,16 +6573,16 @@
         <v>25</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F4" s="117">
         <v>6</v>
@@ -6593,16 +6593,16 @@
         <v>24</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D5" s="111" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F5" s="117">
         <v>7</v>
@@ -6613,16 +6613,16 @@
         <v>23</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F6" s="120">
         <v>8</v>
@@ -6633,16 +6633,16 @@
         <v>22</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F7" s="117">
         <v>9</v>
@@ -6653,10 +6653,10 @@
         <v>21</v>
       </c>
       <c r="B8" s="98" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="124" t="s">
         <v>238</v>
-      </c>
-      <c r="C8" s="124" t="s">
-        <v>239</v>
       </c>
       <c r="D8" s="125"/>
       <c r="E8" s="126"/>
@@ -6669,16 +6669,16 @@
         <v>20</v>
       </c>
       <c r="B9" s="109" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E9" s="110" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F9" s="117">
         <v>11</v>
@@ -6689,16 +6689,16 @@
         <v>19</v>
       </c>
       <c r="B10" s="112" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C10" s="113" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" s="114" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E10" s="113" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F10" s="120">
         <v>12</v>
@@ -6738,66 +6738,66 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CEB427C-0CB4-4E8D-8367-36F6DD891282}">
   <dimension ref="A1:CA6"/>
-  <sheetFormatPr defaultColWidth="19.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19.7734375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" style="53"/>
-    <col min="2" max="2" width="19.7109375" style="65"/>
-    <col min="4" max="4" width="19.7109375" style="53"/>
-    <col min="6" max="6" width="19.7109375" style="53"/>
-    <col min="8" max="8" width="19.7109375" style="53"/>
-    <col min="10" max="10" width="19.7109375" style="53"/>
-    <col min="12" max="12" width="19.7109375" style="53"/>
-    <col min="14" max="14" width="19.7109375" style="53"/>
-    <col min="16" max="16" width="19.7109375" style="53"/>
-    <col min="18" max="18" width="19.7109375" style="53"/>
-    <col min="20" max="20" width="19.7109375" style="53"/>
-    <col min="22" max="22" width="19.7109375" style="53"/>
-    <col min="24" max="24" width="19.7109375" style="53"/>
-    <col min="26" max="26" width="19.7109375" style="53"/>
-    <col min="28" max="28" width="19.7109375" style="53"/>
-    <col min="30" max="30" width="19.7109375" style="71"/>
-    <col min="31" max="32" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="19.7109375" customWidth="1"/>
-    <col min="42" max="42" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.7109375" style="71" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="19.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="19.7109375" style="71" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="19.7109375" style="53"/>
-    <col min="63" max="63" width="19.7109375" style="53"/>
-    <col min="65" max="65" width="19.7109375" style="53"/>
-    <col min="67" max="67" width="19.7109375" style="53"/>
-    <col min="69" max="70" width="19.7109375" style="53"/>
-    <col min="71" max="71" width="19.7109375" style="65"/>
-    <col min="73" max="73" width="19.7109375" style="53"/>
-    <col min="75" max="75" width="19.7109375" style="53"/>
-    <col min="77" max="77" width="19.7109375" style="53"/>
-    <col min="79" max="79" width="19.7109375" style="53"/>
+    <col min="1" max="1" width="19.7734375" style="53"/>
+    <col min="2" max="2" width="19.7734375" style="65"/>
+    <col min="4" max="4" width="19.7734375" style="53"/>
+    <col min="6" max="6" width="19.7734375" style="53"/>
+    <col min="8" max="8" width="19.7734375" style="53"/>
+    <col min="10" max="10" width="19.7734375" style="53"/>
+    <col min="12" max="12" width="19.7734375" style="53"/>
+    <col min="14" max="14" width="19.7734375" style="53"/>
+    <col min="16" max="16" width="19.7734375" style="53"/>
+    <col min="18" max="18" width="19.7734375" style="53"/>
+    <col min="20" max="20" width="19.7734375" style="53"/>
+    <col min="22" max="22" width="19.7734375" style="53"/>
+    <col min="24" max="24" width="19.7734375" style="53"/>
+    <col min="26" max="26" width="19.7734375" style="53"/>
+    <col min="28" max="28" width="19.7734375" style="53"/>
+    <col min="30" max="30" width="19.7734375" style="71"/>
+    <col min="31" max="32" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="19.7734375" customWidth="1"/>
+    <col min="42" max="42" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.7734375" style="71" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="19.7734375" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="19.7734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="19.7734375" style="71" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="19.7734375" style="53"/>
+    <col min="63" max="63" width="19.7734375" style="53"/>
+    <col min="65" max="65" width="19.7734375" style="53"/>
+    <col min="67" max="67" width="19.7734375" style="53"/>
+    <col min="69" max="70" width="19.7734375" style="53"/>
+    <col min="71" max="71" width="19.7734375" style="65"/>
+    <col min="73" max="73" width="19.7734375" style="53"/>
+    <col min="75" max="75" width="19.7734375" style="53"/>
+    <col min="77" max="77" width="19.7734375" style="53"/>
+    <col min="79" max="79" width="19.7734375" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="67" t="str">
         <f>Cards!B2</f>
         <v>Fillibuster</v>
@@ -7084,7 +7084,7 @@
       <c r="BY1" s="67"/>
       <c r="CA1" s="67"/>
     </row>
-    <row r="2" spans="1:79" s="92" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:79" s="92" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="93" t="str">
         <f>Cards!C2</f>
         <v>Move the deliberated Law $L6 additional places back in the queue during Postpone</v>
@@ -7191,11 +7191,11 @@
       </c>
       <c r="AA2" s="92" t="str">
         <f>Cards!C26</f>
-        <v>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</v>
+        <v>Subtract $L3 from Scheme Evasion rolls. An unmodified 6 always succeeds.</v>
       </c>
       <c r="AB2" s="93" t="str">
         <f>Cards!C27</f>
-        <v>Subtract $L3 from Scheme Card rolls</v>
+        <v>Subtract $L3 from Scheme Damage rolls</v>
       </c>
       <c r="AC2" s="92" t="str">
         <f>Cards!C28</f>
@@ -7351,11 +7351,11 @@
       </c>
       <c r="BO2" s="93" t="str">
         <f t="shared" si="2"/>
-        <v>Subtract $L3 from Scheme Guard rolls. An unmodified 6 always succeeds.</v>
+        <v>Subtract $L3 from Scheme Evasion rolls. An unmodified 6 always succeeds.</v>
       </c>
       <c r="BP2" s="92" t="str">
         <f t="shared" si="2"/>
-        <v>Subtract $L3 from Scheme Card rolls</v>
+        <v>Subtract $L3 from Scheme Damage rolls</v>
       </c>
       <c r="BQ2" s="72" t="str">
         <f t="shared" si="2"/>
@@ -7371,7 +7371,7 @@
       <c r="BY2" s="93"/>
       <c r="CA2" s="93"/>
     </row>
-    <row r="3" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:79" s="69" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="67" t="str">
         <f>Cards!D2</f>
         <v>Full Coffers</v>
@@ -7655,7 +7655,7 @@
       <c r="BY3" s="67"/>
       <c r="CA3" s="67"/>
     </row>
-    <row r="4" spans="1:79" s="74" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:79" s="74" customFormat="1" ht="105.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="72" t="str">
         <f>Cards!E2</f>
         <v>The Royal Bank must have at least $L6 Coins or all Players suffer sanctions on Undermarket Actions</v>
@@ -7939,7 +7939,7 @@
       <c r="BY4" s="72"/>
       <c r="CA4" s="72"/>
     </row>
-    <row r="5" spans="1:79" s="78" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:79" s="78" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="76" t="str">
         <f>Cards!F2</f>
         <v>Fickle Mercenaries</v>
@@ -8219,7 +8219,7 @@
       <c r="BY5" s="76"/>
       <c r="CA5" s="76"/>
     </row>
-    <row r="6" spans="1:79" s="74" customFormat="1" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:79" s="74" customFormat="1" ht="81.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="72" t="str">
         <f>Cards!G2</f>
         <v>Give $2D6 Troops to $R</v>
@@ -8508,295 +8508,295 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29BDA35E-BFC3-134A-A064-89D65A8B31CF}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.50390625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.10546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.22265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1" t="s">
         <v>260</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>261</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>262</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>263</v>
       </c>
-      <c r="F1" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B2">
         <f>30*2</f>
         <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D2">
         <v>27.7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B3">
         <f>34*2</f>
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D3">
         <v>27.7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B4">
         <f>18*3</f>
         <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D4">
         <v>30.75</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B5">
         <f>2*6+6*6</f>
         <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B6">
         <f>1*6+10*6</f>
         <v>66</v>
       </c>
       <c r="C6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E6" t="s">
         <v>266</v>
       </c>
-      <c r="E6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B7">
         <f>10*6+10</f>
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E7" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B8">
         <f>2*8*6</f>
         <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E8" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B9">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B10">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>265</v>
+      </c>
+      <c r="E10" t="s">
         <v>266</v>
       </c>
-      <c r="E10" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B11">
         <f>(30*6-B10)/5</f>
         <v>30</v>
       </c>
       <c r="C11" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" t="s">
         <v>266</v>
       </c>
-      <c r="E11" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B12">
         <f>5*6</f>
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E12" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B13">
         <f>(15*6-B12)/5</f>
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E13" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B18">
         <f>10*6</f>
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B19">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B20">
         <f>5*7</f>
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -8808,89 +8808,89 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC83F89-2724-CA43-A519-59213A612B31}">
   <dimension ref="A1:U55"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24" style="95" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.42578125" style="97" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="97" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="97" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="11.85546875" style="97" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.85546875" style="97" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.9453125" style="95" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.72265625" customWidth="1"/>
+    <col min="4" max="4" width="8.33984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.27734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5078125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.97265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.43359375" style="97" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.22265625" style="97" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.43359375" style="97" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="11.8359375" style="97" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.9140625" style="97" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5078125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B1" t="s">
         <v>324</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>325</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>326</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>327</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>353</v>
+      </c>
+      <c r="G1" t="s">
+        <v>352</v>
+      </c>
+      <c r="H1" t="s">
         <v>328</v>
       </c>
-      <c r="F1" t="s">
-        <v>354</v>
-      </c>
-      <c r="G1" t="s">
-        <v>353</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>329</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" s="97" t="s">
+        <v>350</v>
+      </c>
+      <c r="K1" t="s">
         <v>330</v>
       </c>
-      <c r="J1" s="97" t="s">
+      <c r="L1" t="s">
+        <v>331</v>
+      </c>
+      <c r="M1" t="s">
+        <v>332</v>
+      </c>
+      <c r="N1" t="s">
+        <v>333</v>
+      </c>
+      <c r="O1" t="s">
+        <v>334</v>
+      </c>
+      <c r="P1" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>336</v>
+      </c>
+      <c r="R1" t="s">
+        <v>337</v>
+      </c>
+      <c r="S1" t="s">
+        <v>338</v>
+      </c>
+      <c r="T1" t="s">
+        <v>339</v>
+      </c>
+      <c r="U1" t="s">
         <v>351</v>
       </c>
-      <c r="K1" t="s">
-        <v>331</v>
-      </c>
-      <c r="L1" t="s">
-        <v>332</v>
-      </c>
-      <c r="M1" t="s">
-        <v>333</v>
-      </c>
-      <c r="N1" t="s">
-        <v>334</v>
-      </c>
-      <c r="O1" t="s">
-        <v>335</v>
-      </c>
-      <c r="P1" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>337</v>
-      </c>
-      <c r="R1" t="s">
-        <v>338</v>
-      </c>
-      <c r="S1" t="s">
-        <v>339</v>
-      </c>
-      <c r="T1" t="s">
-        <v>340</v>
-      </c>
-      <c r="U1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="95">
         <v>46075</v>
       </c>
@@ -8934,7 +8934,7 @@
         <v>0.92638888888888893</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="95">
         <v>46089</v>
       </c>
@@ -8990,7 +8990,7 @@
         <v>0.86527777777777781</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="95">
         <v>46105</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>0.92777777777777781</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="95">
         <v>46118</v>
       </c>
@@ -9096,7 +9096,7 @@
         <v>0.9194444444444444</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="95">
         <v>46124</v>
       </c>
@@ -9140,7 +9140,7 @@
         <v>0.74583333333333335</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="95">
         <v>46131</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>0.70277777777777772</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="95">
         <v>46138</v>
       </c>
@@ -9237,7 +9237,7 @@
         <v>0.69513888888888886</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="95">
         <v>46145</v>
       </c>
@@ -9290,7 +9290,7 @@
         <v>0.71666666666666667</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="95">
         <v>46152</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>0.625</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="95">
         <v>46158</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>0.99236111111111114</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="96" t="b">
         <v>0</v>
       </c>
@@ -9401,7 +9401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="96" t="b">
         <v>0</v>
       </c>
@@ -9409,7 +9409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="96" t="b">
         <v>0</v>
       </c>
@@ -9417,7 +9417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="96" t="b">
         <v>0</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C16" s="96" t="b">
         <v>0</v>
       </c>
@@ -9433,7 +9433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C17" s="96" t="b">
         <v>0</v>
       </c>
@@ -9441,7 +9441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C18" s="96" t="b">
         <v>0</v>
       </c>
@@ -9449,7 +9449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C19" s="96" t="b">
         <v>0</v>
       </c>
@@ -9457,7 +9457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C20" s="96" t="b">
         <v>0</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C21" s="96" t="b">
         <v>0</v>
       </c>
@@ -9473,7 +9473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C22" s="96" t="b">
         <v>0</v>
       </c>
@@ -9481,7 +9481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C23" s="96" t="b">
         <v>0</v>
       </c>
@@ -9489,7 +9489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C24" s="96" t="b">
         <v>0</v>
       </c>
@@ -9497,7 +9497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C25" s="96" t="b">
         <v>0</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C26" s="96" t="b">
         <v>0</v>
       </c>
@@ -9513,7 +9513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C27" s="96" t="b">
         <v>0</v>
       </c>
@@ -9521,7 +9521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C28" s="96" t="b">
         <v>0</v>
       </c>
@@ -9529,7 +9529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C29" s="96" t="b">
         <v>0</v>
       </c>
@@ -9537,7 +9537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C30" s="96" t="b">
         <v>0</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C31" s="96" t="b">
         <v>0</v>
       </c>
@@ -9553,7 +9553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C32" s="96" t="b">
         <v>0</v>
       </c>
@@ -9561,7 +9561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C33" s="96" t="b">
         <v>0</v>
       </c>
@@ -9569,7 +9569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C34" s="96" t="b">
         <v>0</v>
       </c>
@@ -9577,7 +9577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C35" s="96" t="b">
         <v>0</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C36" s="96" t="b">
         <v>0</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C37" s="96" t="b">
         <v>0</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C38" s="96" t="b">
         <v>0</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C39" s="96" t="b">
         <v>0</v>
       </c>
@@ -9617,7 +9617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C40" s="96" t="b">
         <v>0</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C41" s="96" t="b">
         <v>0</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C42" s="96" t="b">
         <v>0</v>
       </c>
@@ -9641,7 +9641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C43" s="96" t="b">
         <v>0</v>
       </c>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C44" s="96" t="b">
         <v>0</v>
       </c>
@@ -9657,7 +9657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C45" s="96" t="b">
         <v>0</v>
       </c>
@@ -9665,7 +9665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C46" s="96" t="b">
         <v>0</v>
       </c>
@@ -9673,7 +9673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C47" s="96" t="b">
         <v>0</v>
       </c>
@@ -9681,7 +9681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C48" s="96" t="b">
         <v>0</v>
       </c>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C49" s="96" t="b">
         <v>0</v>
       </c>
@@ -9697,7 +9697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C50" s="96" t="b">
         <v>0</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C51" s="96" t="b">
         <v>0</v>
       </c>
@@ -9713,7 +9713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C52" s="96" t="b">
         <v>0</v>
       </c>
@@ -9721,7 +9721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C53" s="96" t="b">
         <v>0</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C54" s="96" t="b">
         <v>0</v>
       </c>
@@ -9737,7 +9737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C55" s="96" t="b">
         <v>0</v>
       </c>

--- a/ShiftingSands.xlsx
+++ b/ShiftingSands.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/736bb1ccd5622dcc/Documents/BoardGames/ShiftingSands/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4363" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B5A9EBE-F8CB-C648-82A1-9886ADB36BD6}"/>
+  <xr:revisionPtr revIDLastSave="4419" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A93B122E-B6FD-BD44-88EB-0C51F1B2CD6B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="472">
   <si>
     <t>Standard Card</t>
   </si>
@@ -131,9 +131,6 @@
     <t>Stable Economies</t>
   </si>
   <si>
-    <t>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</t>
-  </si>
-  <si>
     <t>Blackmail</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
     <t>Unreasonable Distractions</t>
   </si>
   <si>
-    <t>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Promote &amp; Commission</t>
-  </si>
-  <si>
     <t>Invalid Paperwork</t>
   </si>
   <si>
@@ -335,9 +329,6 @@
     <t>War Machines</t>
   </si>
   <si>
-    <t>Purchase and immediately add up to $L3 Troops to your force when deploying them</t>
-  </si>
-  <si>
     <t>Police Force</t>
   </si>
   <si>
@@ -839,9 +830,6 @@
     <t>Card</t>
   </si>
   <si>
-    <t>Punchboard</t>
-  </si>
-  <si>
     <t>Wood</t>
   </si>
   <si>
@@ -854,9 +842,6 @@
     <t>Plastic</t>
   </si>
   <si>
-    <t>Mini</t>
-  </si>
-  <si>
     <t>Scheme Envelopes</t>
   </si>
   <si>
@@ -1173,9 +1158,6 @@
   </si>
   <si>
     <t>Send Troops up to Leader's Level to the Battlefield and gain half Troops in Coins</t>
-  </si>
-  <si>
-    <t>You may repeat Undermarket Actions at double the penalty</t>
   </si>
   <si>
     <t>Painful Progress</t>
@@ -1459,6 +1441,24 @@
   </si>
   <si>
     <t>Subtract $L3 from Scheme Evasion rolls. An unmodified 6 always succeeds.</t>
+  </si>
+  <si>
+    <t>Each Player must have at least 3 + $L6 Investments or they will suffer sanctions on Commission</t>
+  </si>
+  <si>
+    <t>No Player may have more than 3 + $L6 Investments or they will suffer sanctions on Commission</t>
+  </si>
+  <si>
+    <t>You may pay 7 - $L6 Commodities to repeat Undermarket Actions</t>
+  </si>
+  <si>
+    <t>After deploying, purchase and immediately deploy up to $L3 Troops, but no more than your deployed Troops.</t>
+  </si>
+  <si>
+    <t>Plastic Magnet</t>
+  </si>
+  <si>
+    <t>Plastic Mini</t>
   </si>
 </sst>
 </file>
@@ -4156,7 +4156,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
@@ -4167,10 +4167,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>14</v>
@@ -4179,10 +4179,10 @@
         <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="2"/>
@@ -4196,19 +4196,19 @@
         <v>17</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="3"/>
@@ -4228,13 +4228,13 @@
         <v>23</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
@@ -4254,13 +4254,13 @@
         <v>28</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>29</v>
+        <v>466</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3"/>
@@ -4268,25 +4268,25 @@
     </row>
     <row r="7" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="D7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>34</v>
-      </c>
       <c r="E7" s="18" t="s">
-        <v>35</v>
+        <v>467</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="3"/>
@@ -4294,25 +4294,25 @@
     </row>
     <row r="8" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
@@ -4320,25 +4320,25 @@
     </row>
     <row r="9" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="3"/>
@@ -4346,25 +4346,25 @@
     </row>
     <row r="10" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="2"/>
@@ -4372,25 +4372,25 @@
     </row>
     <row r="11" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>45</v>
-      </c>
       <c r="E11" s="15" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="2"/>
@@ -4398,25 +4398,25 @@
     </row>
     <row r="12" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="2"/>
@@ -4424,25 +4424,25 @@
     </row>
     <row r="13" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>55</v>
-      </c>
       <c r="F13" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="2"/>
@@ -4450,25 +4450,25 @@
     </row>
     <row r="14" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="E14" s="15" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="3"/>
@@ -4476,25 +4476,25 @@
     </row>
     <row r="15" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="C15" s="15" t="s">
-        <